--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08278465270996</t>
+    <t xml:space="preserve">8.08278369903564</t>
   </si>
   <si>
     <t xml:space="preserve">8.05997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06757736206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12840557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11319923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9002947807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87748336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591617584229</t>
+    <t xml:space="preserve">8.06757640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1284065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11319828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90029239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87748193740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591569900513</t>
   </si>
   <si>
     <t xml:space="preserve">7.5277099609375</t>
@@ -74,88 +74,88 @@
     <t xml:space="preserve">7.48969125747681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95351982116699</t>
+    <t xml:space="preserve">7.95352029800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.79384183883667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67978525161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62655830383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71020078659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89268922805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82425546646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60374927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69499444961548</t>
+    <t xml:space="preserve">7.67978668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62655925750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71020126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89268970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8242564201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60374689102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69499397277832</t>
   </si>
   <si>
     <t xml:space="preserve">7.98393487930298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84706783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91550207138062</t>
+    <t xml:space="preserve">7.84706735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91550254821777</t>
   </si>
   <si>
     <t xml:space="preserve">8.01435089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20444488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10559463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24246406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25006675720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30329132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15121746063232</t>
+    <t xml:space="preserve">8.20444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10559558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24246215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25006771087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3032922744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15121650695801</t>
   </si>
   <si>
     <t xml:space="preserve">8.23485946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35651874542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21965217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36412334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29568862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38693332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14361476898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18923568725586</t>
+    <t xml:space="preserve">8.356520652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28808498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.219651222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36412239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29568958282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38693428039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14361381530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18923664093018</t>
   </si>
   <si>
     <t xml:space="preserve">8.40974426269531</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">8.37932968139648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51619720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82034873962402</t>
+    <t xml:space="preserve">8.51619815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75191402435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82034683227539</t>
   </si>
   <si>
     <t xml:space="preserve">8.80514049530029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82795238494873</t>
+    <t xml:space="preserve">8.82794952392578</t>
   </si>
   <si>
     <t xml:space="preserve">9.01044082641602</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">9.09408283233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98002529144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12449741363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1929292678833</t>
+    <t xml:space="preserve">8.9800271987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12449645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19293117523193</t>
   </si>
   <si>
     <t xml:space="preserve">8.78993225097656</t>
@@ -212,109 +212,109 @@
     <t xml:space="preserve">9.08647727966309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20053386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34500598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13970565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6111364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67196846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65676021575928</t>
+    <t xml:space="preserve">9.20053482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34500503540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13970375061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61113739013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67196750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65675830841064</t>
   </si>
   <si>
     <t xml:space="preserve">9.80883502960205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90007972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77081489562988</t>
+    <t xml:space="preserve">9.90008068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7708158493042</t>
   </si>
   <si>
     <t xml:space="preserve">9.73252964019775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47217845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49514961242676</t>
+    <t xml:space="preserve">9.4721794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49515151977539</t>
   </si>
   <si>
     <t xml:space="preserve">9.57172393798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70190048217773</t>
+    <t xml:space="preserve">9.70189952850342</t>
   </si>
   <si>
     <t xml:space="preserve">9.77847385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67892837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69424247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61001300811768</t>
+    <t xml:space="preserve">9.67892742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69424152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61001110076904</t>
   </si>
   <si>
     <t xml:space="preserve">9.6482982635498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51046562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41857719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26542949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22714328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18885517120361</t>
+    <t xml:space="preserve">9.51046657562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41857624053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26542854309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22714233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1888542175293</t>
   </si>
   <si>
     <t xml:space="preserve">9.11228084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34200382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.632981300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20417022705078</t>
+    <t xml:space="preserve">9.34200286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63298320770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20416927337646</t>
   </si>
   <si>
     <t xml:space="preserve">9.21182823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3037166595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72487258911133</t>
+    <t xml:space="preserve">9.30371570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7248706817627</t>
   </si>
   <si>
     <t xml:space="preserve">9.34965991973877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38794803619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59469509124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53343677520752</t>
+    <t xml:space="preserve">9.38794898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59469604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53343772888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.75550079345703</t>
@@ -323,34 +323,34 @@
     <t xml:space="preserve">9.76315975189209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7708158493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62532520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.456862449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78613185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74784374237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71721458435059</t>
+    <t xml:space="preserve">9.77081680297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62532615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45686340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78612995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74784278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7172155380249</t>
   </si>
   <si>
     <t xml:space="preserve">9.68658542633057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67126846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36497592926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56406784057617</t>
+    <t xml:space="preserve">9.6712703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36497497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56406688690186</t>
   </si>
   <si>
     <t xml:space="preserve">9.57938098907471</t>
@@ -362,22 +362,22 @@
     <t xml:space="preserve">9.70955657958984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66361236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7401876449585</t>
+    <t xml:space="preserve">9.66361331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74018669128418</t>
   </si>
   <si>
     <t xml:space="preserve">9.51812076568604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44920539855957</t>
+    <t xml:space="preserve">9.4492073059082</t>
   </si>
   <si>
     <t xml:space="preserve">9.39560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35731792449951</t>
+    <t xml:space="preserve">9.3573169708252</t>
   </si>
   <si>
     <t xml:space="preserve">9.54109477996826</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">9.80144500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55640983581543</t>
+    <t xml:space="preserve">9.55641174316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.79378890991211</t>
@@ -398,79 +398,79 @@
     <t xml:space="preserve">9.86270332336426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90865135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93927764892578</t>
+    <t xml:space="preserve">9.90864944458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9392786026001</t>
   </si>
   <si>
     <t xml:space="preserve">9.92396354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2226028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2685461044312</t>
+    <t xml:space="preserve">10.222601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2685441970825</t>
   </si>
   <si>
     <t xml:space="preserve">10.283860206604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3910646438599</t>
+    <t xml:space="preserve">10.3910627365112</t>
   </si>
   <si>
     <t xml:space="preserve">10.4829521179199</t>
   </si>
   <si>
-    <t xml:space="preserve">10.582498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7050170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6437587738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.720329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3374633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4523229598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1843156814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.077112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0694541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2379159927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617971420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95459461212158</t>
+    <t xml:space="preserve">10.5824966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7050180435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6437568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7203302383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3374614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4523220062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1843166351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0771131515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0694551467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2379179000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95459365844727</t>
   </si>
   <si>
     <t xml:space="preserve">9.87036228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82441711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0388250350952</t>
+    <t xml:space="preserve">9.82441806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0388231277466</t>
   </si>
   <si>
     <t xml:space="preserve">9.98522281646729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85504722595215</t>
+    <t xml:space="preserve">9.85504817962646</t>
   </si>
   <si>
     <t xml:space="preserve">9.93162059783936</t>
@@ -479,37 +479,37 @@
     <t xml:space="preserve">9.94693565368652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89333343505859</t>
+    <t xml:space="preserve">9.89333438873291</t>
   </si>
   <si>
     <t xml:space="preserve">10.0541391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97756576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567638397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1613416671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288972854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5671825408936</t>
+    <t xml:space="preserve">9.97756481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1613426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288963317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5671834945679</t>
   </si>
   <si>
     <t xml:space="preserve">10.490611076355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2991771697998</t>
+    <t xml:space="preserve">10.2991743087769</t>
   </si>
   <si>
     <t xml:space="preserve">10.2608890533447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4063787460327</t>
+    <t xml:space="preserve">10.4063777923584</t>
   </si>
   <si>
     <t xml:space="preserve">10.4140357971191</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">10.2455739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153984069824</t>
+    <t xml:space="preserve">10.1153974533081</t>
   </si>
   <si>
     <t xml:space="preserve">10.3221473693848</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">10.2915182113647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.398720741272</t>
+    <t xml:space="preserve">10.3987216949463</t>
   </si>
   <si>
     <t xml:space="preserve">10.4982662200928</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">10.4293508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6054706573486</t>
+    <t xml:space="preserve">10.6054716110229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5901565551758</t>
@@ -545,43 +545,43 @@
     <t xml:space="preserve">10.3757486343384</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2532300949097</t>
+    <t xml:space="preserve">10.253231048584</t>
   </si>
   <si>
     <t xml:space="preserve">10.1460275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3068332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4752960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5212383270264</t>
+    <t xml:space="preserve">10.3068323135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4752969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5212392807007</t>
   </si>
   <si>
     <t xml:space="preserve">10.4446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3298053741455</t>
+    <t xml:space="preserve">10.3298034667969</t>
   </si>
   <si>
     <t xml:space="preserve">10.1230554580688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4216928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7815895080566</t>
+    <t xml:space="preserve">10.4216938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.781590461731</t>
   </si>
   <si>
     <t xml:space="preserve">11.2027463912964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1797733306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1338300704956</t>
+    <t xml:space="preserve">11.1797742843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1338291168213</t>
   </si>
   <si>
     <t xml:space="preserve">11.3329229354858</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">11.2793207168579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3788661956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6775045394897</t>
+    <t xml:space="preserve">11.378867149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6775035858154</t>
   </si>
   <si>
     <t xml:space="preserve">11.7081336975098</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8383083343506</t>
+    <t xml:space="preserve">11.8383102416992</t>
   </si>
   <si>
     <t xml:space="preserve">11.6851596832275</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">11.6468744277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5473289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.401837348938</t>
+    <t xml:space="preserve">11.5473279953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4018383026123</t>
   </si>
   <si>
     <t xml:space="preserve">11.5243558883667</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">11.7923641204834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.228835105896</t>
+    <t xml:space="preserve">12.2288360595703</t>
   </si>
   <si>
     <t xml:space="preserve">12.2441492080688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3513526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4049558639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5198154449463</t>
+    <t xml:space="preserve">12.3513536453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4049549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5198173522949</t>
   </si>
   <si>
     <t xml:space="preserve">13.2549228668213</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">13.6301355361938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7832832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2472667694092</t>
+    <t xml:space="preserve">13.7832822799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2472658157349</t>
   </si>
   <si>
     <t xml:space="preserve">12.8184547424316</t>
@@ -668,19 +668,19 @@
     <t xml:space="preserve">12.6346769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7112493515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0252027511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8643960952759</t>
+    <t xml:space="preserve">12.7112483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0252017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8643980026245</t>
   </si>
   <si>
     <t xml:space="preserve">13.2396078109741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2166376113892</t>
+    <t xml:space="preserve">13.2166385650635</t>
   </si>
   <si>
     <t xml:space="preserve">13.2089796066284</t>
@@ -689,127 +689,127 @@
     <t xml:space="preserve">13.7373390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3621263504028</t>
+    <t xml:space="preserve">13.3621273040771</t>
   </si>
   <si>
     <t xml:space="preserve">13.4004144668579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7143669128418</t>
+    <t xml:space="preserve">13.7143659591675</t>
   </si>
   <si>
     <t xml:space="preserve">13.5688762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5152740478516</t>
+    <t xml:space="preserve">13.5152750015259</t>
   </si>
   <si>
     <t xml:space="preserve">13.6684217453003</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6148204803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3192987442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3958730697632</t>
+    <t xml:space="preserve">13.614821434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.319296836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3958721160889</t>
   </si>
   <si>
     <t xml:space="preserve">14.3882179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4341630935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5490226745605</t>
+    <t xml:space="preserve">14.4341592788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5490207672119</t>
   </si>
   <si>
     <t xml:space="preserve">14.6791944503784</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2810115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.326958656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4265050888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3422698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5337076187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2733545303345</t>
+    <t xml:space="preserve">14.2810134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3269596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4265041351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3422708511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5337066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2733554840088</t>
   </si>
   <si>
     <t xml:space="preserve">14.0359764099121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0512924194336</t>
+    <t xml:space="preserve">14.0512914657593</t>
   </si>
   <si>
     <t xml:space="preserve">13.9897298812866</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1282424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975734710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4976100921631</t>
+    <t xml:space="preserve">14.1282434463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.397572517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4976110458374</t>
   </si>
   <si>
     <t xml:space="preserve">14.0820713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1436347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590599060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5745601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5976457595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6592063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3437042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3667907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3514013290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2513647079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0435953140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5437812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5822534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129262924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5360803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4899110794067</t>
+    <t xml:space="preserve">14.1436338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.574559211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5976438522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6592054367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3437051773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3667917251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3514003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2513656616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0435962677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5437793731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.58225440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3129253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5360832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4899139404297</t>
   </si>
   <si>
     <t xml:space="preserve">14.6976804733276</t>
@@ -833,229 +833,229 @@
     <t xml:space="preserve">13.9127788543701</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8973875045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.243670463562</t>
+    <t xml:space="preserve">13.8973894119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2436695098877</t>
   </si>
   <si>
     <t xml:space="preserve">14.389874458313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4129619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3821811676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4437427520752</t>
+    <t xml:space="preserve">14.4129610061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3821792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4437437057495</t>
   </si>
   <si>
     <t xml:space="preserve">14.5591697692871</t>
   </si>
   <si>
-    <t xml:space="preserve">14.736156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5053052902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5283889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.551477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4360494613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2744483947754</t>
+    <t xml:space="preserve">14.7361555099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5053024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5283880233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283533096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514764785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4360504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2744493484497</t>
   </si>
   <si>
     <t xml:space="preserve">14.051290512085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.966646194458</t>
+    <t xml:space="preserve">13.9666423797607</t>
   </si>
   <si>
     <t xml:space="preserve">13.6742305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1205472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1590223312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1513271331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8512153625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9743404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1744136810303</t>
+    <t xml:space="preserve">14.1205463409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1590232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1513261795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8512172698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9743413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1744117736816</t>
   </si>
   <si>
     <t xml:space="preserve">14.2051935195923</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0051193237305</t>
+    <t xml:space="preserve">14.0051212310791</t>
   </si>
   <si>
     <t xml:space="preserve">14.3052310943604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3590974807739</t>
+    <t xml:space="preserve">14.3590965270996</t>
   </si>
   <si>
     <t xml:space="preserve">14.2975339889526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4206562042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3283157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.336012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3744850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2359743118286</t>
+    <t xml:space="preserve">14.4206581115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.328314781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.336009979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3744869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2359733581543</t>
   </si>
   <si>
     <t xml:space="preserve">14.5129985809326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2205848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1974983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3902454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2440366744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2517309188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1670827865601</t>
+    <t xml:space="preserve">14.2205839157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1974992752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3902397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2440357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2517318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1670837402344</t>
   </si>
   <si>
     <t xml:space="preserve">15.105523109436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1978635787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0670471191406</t>
+    <t xml:space="preserve">15.197865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0670480728149</t>
   </si>
   <si>
     <t xml:space="preserve">14.9208402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9285373687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8823680877686</t>
+    <t xml:space="preserve">14.9285354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8823661804199</t>
   </si>
   <si>
     <t xml:space="preserve">14.5206937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2898426055908</t>
+    <t xml:space="preserve">14.2898406982422</t>
   </si>
   <si>
     <t xml:space="preserve">14.7515439987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6438131332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5668611526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6515111923218</t>
+    <t xml:space="preserve">14.6438150405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5668630599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6515121459961</t>
   </si>
   <si>
     <t xml:space="preserve">14.7438526153564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7900238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8361940383911</t>
+    <t xml:space="preserve">14.7900218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8361930847168</t>
   </si>
   <si>
     <t xml:space="preserve">14.7746334075928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6361198425293</t>
+    <t xml:space="preserve">14.6361207962036</t>
   </si>
   <si>
     <t xml:space="preserve">14.7207660675049</t>
   </si>
   <si>
-    <t xml:space="preserve">14.45143699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4668254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5899496078491</t>
+    <t xml:space="preserve">14.4514360427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4668273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5899505615234</t>
   </si>
   <si>
     <t xml:space="preserve">14.8131093978882</t>
   </si>
   <si>
-    <t xml:space="preserve">14.851583480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1439990997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2902088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3440732955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5441427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5826215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5056715011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4287185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2209482192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9747076034546</t>
+    <t xml:space="preserve">14.8515853881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1439971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.290207862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3440742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5441446304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5826206207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.505669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4287214279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2209510803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9747066497803</t>
   </si>
   <si>
     <t xml:space="preserve">15.1286087036133</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9289026260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7365207672119</t>
+    <t xml:space="preserve">15.9289035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7365217208862</t>
   </si>
   <si>
     <t xml:space="preserve">15.8134727478027</t>
@@ -1064,49 +1064,49 @@
     <t xml:space="preserve">16.2367057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0828037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6210966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0058517456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1212768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6980495452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7749996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671194076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9131450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8977546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8054132461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0208806991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0516538619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8208045959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0362672805786</t>
+    <t xml:space="preserve">16.0828056335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6210947036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0058498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.121280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6980485916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.774998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671184539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9131441116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8977556228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8054141998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1747779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0208778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0516557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8208055496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0362682342529</t>
   </si>
   <si>
     <t xml:space="preserve">13.9281692504883</t>
@@ -1121,43 +1121,43 @@
     <t xml:space="preserve">14.4822187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5588035583496</t>
+    <t xml:space="preserve">13.5588026046753</t>
   </si>
   <si>
     <t xml:space="preserve">13.7127065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5434141159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3125610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2048282623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4510736465454</t>
+    <t xml:space="preserve">13.5434122085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3125591278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2048263549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4510717391968</t>
   </si>
   <si>
     <t xml:space="preserve">13.4356832504272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2817783355713</t>
+    <t xml:space="preserve">13.2817811965942</t>
   </si>
   <si>
     <t xml:space="preserve">13.6511459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3895130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1432666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0663175582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0047550201416</t>
+    <t xml:space="preserve">13.3895120620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1432676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0663166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0047569274902</t>
   </si>
   <si>
     <t xml:space="preserve">13.0509262084961</t>
@@ -1166,34 +1166,34 @@
     <t xml:space="preserve">13.2971706390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2356100082397</t>
+    <t xml:space="preserve">13.2356090545654</t>
   </si>
   <si>
     <t xml:space="preserve">13.6357545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8666076660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6819248199463</t>
+    <t xml:space="preserve">13.8666086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6819257736206</t>
   </si>
   <si>
     <t xml:space="preserve">13.8819980621338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7130727767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9589490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9512166976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8893489837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7656135559082</t>
+    <t xml:space="preserve">14.7130737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.958948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9512147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8893480300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7656106948853</t>
   </si>
   <si>
     <t xml:space="preserve">13.9976177215576</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">14.074951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5026760101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8066596984863</t>
+    <t xml:space="preserve">13.5026731491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.806658744812</t>
   </si>
   <si>
     <t xml:space="preserve">13.3170690536499</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">13.146933555603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2397356033325</t>
+    <t xml:space="preserve">13.2397346496582</t>
   </si>
   <si>
     <t xml:space="preserve">13.6109428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5336074829102</t>
+    <t xml:space="preserve">13.5336093902588</t>
   </si>
   <si>
     <t xml:space="preserve">13.7192125320435</t>
@@ -1235,58 +1235,58 @@
     <t xml:space="preserve">13.5645427703857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3789396286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3016042709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5490732192993</t>
+    <t xml:space="preserve">13.3789386749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3016061782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5490741729736</t>
   </si>
   <si>
     <t xml:space="preserve">13.8274822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8738822937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6573457717896</t>
+    <t xml:space="preserve">13.8738832473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6573438644409</t>
   </si>
   <si>
     <t xml:space="preserve">14.0594844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1213521957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0285511016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8584146499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9048147201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.966682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1986875534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058874130249</t>
+    <t xml:space="preserve">14.1213531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0285501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8584136962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9048156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9666843414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1986894607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058864593506</t>
   </si>
   <si>
     <t xml:space="preserve">13.9202814102173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1677541732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5389595031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4925603866577</t>
+    <t xml:space="preserve">14.1677551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5389604568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4925622940063</t>
   </si>
   <si>
     <t xml:space="preserve">14.4306945800781</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">14.2914905548096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3533582687378</t>
+    <t xml:space="preserve">14.3533592224121</t>
   </si>
   <si>
     <t xml:space="preserve">14.4616250991821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.600830078125</t>
+    <t xml:space="preserve">14.6008281707764</t>
   </si>
   <si>
     <t xml:space="preserve">13.7810802459717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3842926025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5080308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3224248886108</t>
+    <t xml:space="preserve">14.3842935562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5080270767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3224229812622</t>
   </si>
   <si>
     <t xml:space="preserve">14.5698976516724</t>
@@ -1325,28 +1325,28 @@
     <t xml:space="preserve">14.3069562911987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1368217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1522874832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6882753372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0130825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.440806388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4872064590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.672812461853</t>
+    <t xml:space="preserve">14.1368207931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.152286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6882772445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0130844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2088022232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4408082962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.487208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6728115081787</t>
   </si>
   <si>
     <t xml:space="preserve">13.7037439346313</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">12.6829233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5746545791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6519918441772</t>
+    <t xml:space="preserve">12.5746555328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6519899368286</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0231990814209</t>
+    <t xml:space="preserve">13.0231981277466</t>
   </si>
   <si>
     <t xml:space="preserve">12.6674575805664</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">12.2189149856567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5591888427734</t>
+    <t xml:space="preserve">12.5591897964478</t>
   </si>
   <si>
     <t xml:space="preserve">12.2962503433228</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">11.7394371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9714431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9405088424683</t>
+    <t xml:space="preserve">11.9714422225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9405078887939</t>
   </si>
   <si>
     <t xml:space="preserve">12.095178604126</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">12.1570463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.064245223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8786420822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8477067947388</t>
+    <t xml:space="preserve">12.0642461776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.87864112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8477058410645</t>
   </si>
   <si>
     <t xml:space="preserve">11.6621036529541</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">11.6002359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5074338912964</t>
+    <t xml:space="preserve">11.5074329376221</t>
   </si>
   <si>
     <t xml:space="preserve">11.1362266540527</t>
@@ -1427,25 +1427,25 @@
     <t xml:space="preserve">10.8887538909912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2599620819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9351558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.012490272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3682308197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4455652236938</t>
+    <t xml:space="preserve">11.2599630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9351539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0124912261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3682298660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4455671310425</t>
   </si>
   <si>
     <t xml:space="preserve">11.5847673416138</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5175466537476</t>
+    <t xml:space="preserve">10.5175476074219</t>
   </si>
   <si>
     <t xml:space="preserve">10.828667640686</t>
@@ -1454,25 +1454,25 @@
     <t xml:space="preserve">11.3458576202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2973718643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9418029785156</t>
+    <t xml:space="preserve">11.2973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9418039321899</t>
   </si>
   <si>
     <t xml:space="preserve">11.0226154327393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.618558883667</t>
+    <t xml:space="preserve">10.6185598373413</t>
   </si>
   <si>
     <t xml:space="preserve">11.1195878982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7983999252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2165613174438</t>
+    <t xml:space="preserve">11.7984008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2165603637695</t>
   </si>
   <si>
     <t xml:space="preserve">11.0711002349854</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">10.9902896881104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2327222824097</t>
+    <t xml:space="preserve">11.232723236084</t>
   </si>
   <si>
     <t xml:space="preserve">11.2488851547241</t>
@@ -1490,31 +1490,31 @@
     <t xml:space="preserve">11.2003984451294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6832084655762</t>
+    <t xml:space="preserve">10.6832075119019</t>
   </si>
   <si>
     <t xml:space="preserve">10.9094791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8609924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4751567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5721273422241</t>
+    <t xml:space="preserve">10.8609914779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4751558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5721282958984</t>
   </si>
   <si>
     <t xml:space="preserve">11.6367778778076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5559682846069</t>
+    <t xml:space="preserve">11.5559663772583</t>
   </si>
   <si>
     <t xml:space="preserve">11.4266691207886</t>
   </si>
   <si>
-    <t xml:space="preserve">11.523642539978</t>
+    <t xml:space="preserve">11.5236415863037</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801809310913</t>
@@ -1526,43 +1526,43 @@
     <t xml:space="preserve">11.0549392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9579658508301</t>
+    <t xml:space="preserve">10.9579648971558</t>
   </si>
   <si>
     <t xml:space="preserve">10.9741268157959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8448305130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8125038146973</t>
+    <t xml:space="preserve">10.8448295593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8125047683716</t>
   </si>
   <si>
     <t xml:space="preserve">11.1357488632202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0872621536255</t>
+    <t xml:space="preserve">11.0872640609741</t>
   </si>
   <si>
     <t xml:space="preserve">11.3296957015991</t>
   </si>
   <si>
-    <t xml:space="preserve">11.604453086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8792104721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8630495071411</t>
+    <t xml:space="preserve">11.6044521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8792095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8630475997925</t>
   </si>
   <si>
     <t xml:space="preserve">11.7337503433228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6529388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8468866348267</t>
+    <t xml:space="preserve">11.6529407501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8468856811523</t>
   </si>
   <si>
     <t xml:space="preserve">11.4589939117432</t>
@@ -1574,49 +1574,49 @@
     <t xml:space="preserve">11.362021446228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0387773513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6508846282959</t>
+    <t xml:space="preserve">11.0387754440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6508836746216</t>
   </si>
   <si>
     <t xml:space="preserve">10.5539112091064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5215864181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1013698577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98823356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3922882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2953157424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3761262893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3599634170532</t>
+    <t xml:space="preserve">10.5215873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1013708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9882345199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3922872543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114786148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2953147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.376127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3599643707275</t>
   </si>
   <si>
     <t xml:space="preserve">10.6023969650269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5862340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3438014984131</t>
+    <t xml:space="preserve">10.5862350463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3438034057617</t>
   </si>
   <si>
     <t xml:space="preserve">10.5700731277466</t>
@@ -1628,52 +1628,52 @@
     <t xml:space="preserve">11.1034240722656</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1842365264893</t>
+    <t xml:space="preserve">11.1842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">11.1519117355347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4730987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.456937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4084520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6670455932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2465229034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5067520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5880746841431</t>
+    <t xml:space="preserve">10.4730997085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4569387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4084510803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.667046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2465219497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5067510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5880727767944</t>
   </si>
   <si>
     <t xml:space="preserve">10.7669811248779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9458894729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9621534347534</t>
+    <t xml:space="preserve">10.9458885192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9621524810791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7507162094116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.344108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4416933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3115797042847</t>
+    <t xml:space="preserve">10.3441076278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4416942596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3115787506104</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278436660767</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">10.4904861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5230150222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5555438995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8157739639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8483028411865</t>
+    <t xml:space="preserve">10.5230159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5555448532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8157749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8483018875122</t>
   </si>
   <si>
     <t xml:space="preserve">11.1410598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9946804046631</t>
+    <t xml:space="preserve">10.9946813583374</t>
   </si>
   <si>
     <t xml:space="preserve">10.8808307647705</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">11.0922679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8970947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5718088150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.669394493103</t>
+    <t xml:space="preserve">10.8970956802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5718078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6693954467773</t>
   </si>
   <si>
     <t xml:space="preserve">10.6368656158447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6531295776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9133586883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8320369720459</t>
+    <t xml:space="preserve">10.653130531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9133596420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8320379257202</t>
   </si>
   <si>
     <t xml:space="preserve">11.1085319519043</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">11.3037033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2223815917969</t>
+    <t xml:space="preserve">11.2223825454712</t>
   </si>
   <si>
     <t xml:space="preserve">11.5639324188232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.433819770813</t>
+    <t xml:space="preserve">11.4338178634644</t>
   </si>
   <si>
     <t xml:space="preserve">11.1573247909546</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">11.7103118896484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7428398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5476684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6452531814575</t>
+    <t xml:space="preserve">11.7428407669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5476675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6452541351318</t>
   </si>
   <si>
     <t xml:space="preserve">10.701922416687</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">10.7344522476196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6856594085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6043376922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8645658493042</t>
+    <t xml:space="preserve">10.6856603622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6043367385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8645648956299</t>
   </si>
   <si>
     <t xml:space="preserve">10.4742231369019</t>
@@ -1796,37 +1796,37 @@
     <t xml:space="preserve">11.6289901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5151395797729</t>
+    <t xml:space="preserve">11.5151386260986</t>
   </si>
   <si>
     <t xml:space="preserve">11.2061166763306</t>
   </si>
   <si>
-    <t xml:space="preserve">11.059739112854</t>
+    <t xml:space="preserve">11.0597381591797</t>
   </si>
   <si>
     <t xml:space="preserve">11.076003074646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1898536682129</t>
+    <t xml:space="preserve">11.1898546218872</t>
   </si>
   <si>
     <t xml:space="preserve">11.3850250244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4012889862061</t>
+    <t xml:space="preserve">11.4012899398804</t>
   </si>
   <si>
     <t xml:space="preserve">11.2549104690552</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3524961471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4500827789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0518636703491</t>
+    <t xml:space="preserve">11.3524971008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4500818252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0518627166748</t>
   </si>
   <si>
     <t xml:space="preserve">12.3771476745605</t>
@@ -1838,118 +1838,118 @@
     <t xml:space="preserve">12.1657123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3446207046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2470331192017</t>
+    <t xml:space="preserve">12.3446197509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.247034072876</t>
   </si>
   <si>
     <t xml:space="preserve">12.5235271453857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3934116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4422063827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6048498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3608837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.27956199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4096765518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3283548355103</t>
+    <t xml:space="preserve">12.3934144973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4422054290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6048488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3608827590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2795629501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4096784591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3283557891846</t>
   </si>
   <si>
     <t xml:space="preserve">11.5964622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.466347694397</t>
+    <t xml:space="preserve">11.4663486480713</t>
   </si>
   <si>
     <t xml:space="preserve">11.8404273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2958269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.556056022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4584703445435</t>
+    <t xml:space="preserve">12.2958278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5560569763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4584693908691</t>
   </si>
   <si>
     <t xml:space="preserve">12.3120908737183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1331853866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9705419540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0681266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9380130767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0355987548828</t>
+    <t xml:space="preserve">12.1331834793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9705400466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0681257247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9380121231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0355978012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.8729553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9542770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9217481613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6777830123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7916345596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7753686904907</t>
+    <t xml:space="preserve">11.9542760848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9217472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6777820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7916316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7753677368164</t>
   </si>
   <si>
     <t xml:space="preserve">11.1735877990723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3687601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1247959136963</t>
+    <t xml:space="preserve">11.3687610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1247968673706</t>
   </si>
   <si>
     <t xml:space="preserve">10.7832450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7995080947876</t>
+    <t xml:space="preserve">10.7995090484619</t>
   </si>
   <si>
     <t xml:space="preserve">10.4579582214355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4091653823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5392789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3766374588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2302589416504</t>
+    <t xml:space="preserve">10.4091663360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5392808914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.376636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2302570343018</t>
   </si>
   <si>
     <t xml:space="preserve">10.3603715896606</t>
@@ -1964,46 +1964,46 @@
     <t xml:space="preserve">9.53089332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41704273223877</t>
+    <t xml:space="preserve">9.41704177856445</t>
   </si>
   <si>
     <t xml:space="preserve">9.1893424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84779071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75020599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62008953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60382556915283</t>
+    <t xml:space="preserve">8.8477897644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75020408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62009143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60382652282715</t>
   </si>
   <si>
     <t xml:space="preserve">8.50624084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81500577926636</t>
+    <t xml:space="preserve">7.81500673294067</t>
   </si>
   <si>
     <t xml:space="preserve">7.42466306686401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34334087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42440700531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70090007781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4325385093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11538410186768</t>
+    <t xml:space="preserve">7.3433403968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4244065284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70089960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43253898620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11538457870483</t>
   </si>
   <si>
     <t xml:space="preserve">5.48920822143555</t>
@@ -2012,49 +2012,49 @@
     <t xml:space="preserve">5.52173709869385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77383422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86328744888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73317384719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61119079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30216884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59492683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56239795684814</t>
+    <t xml:space="preserve">5.77383375167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86328792572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73317432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6111912727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30216836929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5949273109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5623984336853</t>
   </si>
   <si>
     <t xml:space="preserve">5.58679389953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.529869556427</t>
+    <t xml:space="preserve">5.52986907958984</t>
   </si>
   <si>
     <t xml:space="preserve">5.69251251220703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71690988540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01779937744141</t>
+    <t xml:space="preserve">5.71690893173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01779890060425</t>
   </si>
   <si>
     <t xml:space="preserve">5.74943780899048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18044185638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13164949417114</t>
+    <t xml:space="preserve">6.18044137954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13164901733398</t>
   </si>
   <si>
     <t xml:space="preserve">6.05845975875854</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">6.5301251411438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61144733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70903205871582</t>
+    <t xml:space="preserve">6.61144685745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70903253555298</t>
   </si>
   <si>
     <t xml:space="preserve">6.44067144393921</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">6.50572872161865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5219931602478</t>
+    <t xml:space="preserve">6.52199363708496</t>
   </si>
   <si>
     <t xml:space="preserve">6.39187860488892</t>
@@ -2096,19 +2096,19 @@
     <t xml:space="preserve">6.0015344619751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96900653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12351655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20483827590942</t>
+    <t xml:space="preserve">5.96900606155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12351703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20483922958374</t>
   </si>
   <si>
     <t xml:space="preserve">6.18857383728027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30242490768433</t>
+    <t xml:space="preserve">6.30242443084717</t>
   </si>
   <si>
     <t xml:space="preserve">6.49759578704834</t>
@@ -2117,31 +2117,31 @@
     <t xml:space="preserve">6.63584327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87167549133301</t>
+    <t xml:space="preserve">6.87167501449585</t>
   </si>
   <si>
     <t xml:space="preserve">6.79035425186157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77408981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75782632827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91233730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39213514328003</t>
+    <t xml:space="preserve">6.77409029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75782537460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9123363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39213371276855</t>
   </si>
   <si>
     <t xml:space="preserve">7.59543800354004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40026664733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36773777008057</t>
+    <t xml:space="preserve">7.40026569366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36773824691772</t>
   </si>
   <si>
     <t xml:space="preserve">7.1969633102417</t>
@@ -2150,64 +2150,64 @@
     <t xml:space="preserve">6.80661869049072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.896071434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0587158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83914709091187</t>
+    <t xml:space="preserve">6.89607191085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05871534347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83914661407471</t>
   </si>
   <si>
     <t xml:space="preserve">6.85541200637817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97739315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05058431625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14003610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94486570358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31894540786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28641605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15630197525024</t>
+    <t xml:space="preserve">6.97739362716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05058288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14003658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94486522674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31894445419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15630102157593</t>
   </si>
   <si>
     <t xml:space="preserve">7.08311176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00992250442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02618646621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1644344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95299768447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01805448532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66837120056152</t>
+    <t xml:space="preserve">7.00992298126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02618741989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16443395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9529972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0180549621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66837215423584</t>
   </si>
   <si>
     <t xml:space="preserve">6.51386117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47319984436035</t>
+    <t xml:space="preserve">6.47320032119751</t>
   </si>
   <si>
     <t xml:space="preserve">6.73342943191528</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">6.71716499328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78222274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56265306472778</t>
+    <t xml:space="preserve">6.78222131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56265354156494</t>
   </si>
   <si>
     <t xml:space="preserve">6.58705043792725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60331439971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40001106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27802801132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35935020446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34308576583862</t>
+    <t xml:space="preserve">6.6033148765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40001058578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27802848815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35934925079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34308624267578</t>
   </si>
   <si>
     <t xml:space="preserve">6.26989603042603</t>
@@ -2246,31 +2246,31 @@
     <t xml:space="preserve">6.21297073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19670581817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97713851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09912014007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94460964202881</t>
+    <t xml:space="preserve">6.19670724868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97713804244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09912061691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94460916519165</t>
   </si>
   <si>
     <t xml:space="preserve">5.78196620941162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88768434524536</t>
+    <t xml:space="preserve">5.8876838684082</t>
   </si>
   <si>
     <t xml:space="preserve">5.80636310577393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79009866714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72504138946533</t>
+    <t xml:space="preserve">5.79009914398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72504091262817</t>
   </si>
   <si>
     <t xml:space="preserve">5.76570224761963</t>
@@ -2282,40 +2282,40 @@
     <t xml:space="preserve">6.00966644287109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98527097702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05032777786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16417741775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22110319137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92834520339966</t>
+    <t xml:space="preserve">5.98527002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05032730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16417789459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22110271453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">6.107253074646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0340633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31055688858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17231035232544</t>
+    <t xml:space="preserve">6.03406286239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31055736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17230987548828</t>
   </si>
   <si>
     <t xml:space="preserve">5.92021369934082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75756978988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70064449310303</t>
+    <t xml:space="preserve">5.75756931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70064496994019</t>
   </si>
   <si>
     <t xml:space="preserve">5.38349056243896</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">5.00127935409546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96875047683716</t>
+    <t xml:space="preserve">4.96875</t>
   </si>
   <si>
     <t xml:space="preserve">5.01754331588745</t>
@@ -2339,25 +2339,25 @@
     <t xml:space="preserve">5.24524307250977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40788698196411</t>
+    <t xml:space="preserve">5.40788745880127</t>
   </si>
   <si>
     <t xml:space="preserve">6.32682085037231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28615951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36748170852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30268001556396</t>
+    <t xml:space="preserve">6.28615999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36748218536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30267953872681</t>
   </si>
   <si>
     <t xml:space="preserve">7.54664516448975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35960578918457</t>
+    <t xml:space="preserve">7.35960626602173</t>
   </si>
   <si>
     <t xml:space="preserve">7.23762273788452</t>
@@ -2366,73 +2366,73 @@
     <t xml:space="preserve">7.22949075698853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12377166748047</t>
+    <t xml:space="preserve">7.12377309799194</t>
   </si>
   <si>
     <t xml:space="preserve">7.07498025894165</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17256593704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21322679519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06684732437134</t>
+    <t xml:space="preserve">7.17256450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21322631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0668478012085</t>
   </si>
   <si>
     <t xml:space="preserve">6.9611291885376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92046928405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27828454971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92860221862793</t>
+    <t xml:space="preserve">6.92046880722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27828407287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92860078811646</t>
   </si>
   <si>
     <t xml:space="preserve">6.99365901947021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10750818252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29454898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45719194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26201915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18069839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31081247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47345638275146</t>
+    <t xml:space="preserve">7.10750722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29454803466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45719146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26202011108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18069791793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31081295013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47345542907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.48972034454346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70115661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70928859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44905853271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40839862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82288408279419</t>
+    <t xml:space="preserve">7.70115756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70928812026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.449059009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40839910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82288312911987</t>
   </si>
   <si>
     <t xml:space="preserve">6.879807472229</t>
@@ -2441,43 +2441,43 @@
     <t xml:space="preserve">6.86354351043701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0912446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3840012550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53851366043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60356950759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57104158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78247737884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99391317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9451208114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86379909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82313871383667</t>
+    <t xml:space="preserve">7.09124422073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38400077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53851413726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60357046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57104206085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78247785568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9939136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94512128829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86379957199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82313776016235</t>
   </si>
   <si>
     <t xml:space="preserve">7.90446043014526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79874229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83127069473267</t>
+    <t xml:space="preserve">7.79874277114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83127117156982</t>
   </si>
   <si>
     <t xml:space="preserve">7.72555208206177</t>
@@ -2486,16 +2486,16 @@
     <t xml:space="preserve">7.57917356491089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61983394622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44092655181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5629096031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84753465652466</t>
+    <t xml:space="preserve">7.61983489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44092702865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56290912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84753513336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.2622766494751</t>
@@ -2504,58 +2504,58 @@
     <t xml:space="preserve">8.13216114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14842510223389</t>
+    <t xml:space="preserve">8.1484260559082</t>
   </si>
   <si>
     <t xml:space="preserve">8.0508394241333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11589431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87193202972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55477714538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69302368164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75808143615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37612724304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24601078033447</t>
+    <t xml:space="preserve">8.11589622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87193298339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5547776222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69302415847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75808238983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37612533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24601173400879</t>
   </si>
   <si>
     <t xml:space="preserve">8.21348285675049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0589714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79061031341553</t>
+    <t xml:space="preserve">8.05897045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79060935974121</t>
   </si>
   <si>
     <t xml:space="preserve">8.07523536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12402725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9857816696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92072534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.018310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06710338592529</t>
+    <t xml:space="preserve">8.12402820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98578214645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92072439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01830959320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06710243225098</t>
   </si>
   <si>
     <t xml:space="preserve">7.9532527923584</t>
@@ -2564,31 +2564,31 @@
     <t xml:space="preserve">7.71742010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73368406295776</t>
+    <t xml:space="preserve">7.73368549346924</t>
   </si>
   <si>
     <t xml:space="preserve">7.92885637283325</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0833683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57129669189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65261936187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45744609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44118213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53990936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37536430358887</t>
+    <t xml:space="preserve">8.08336734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57129764556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65261840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45744705200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44118309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53991031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37536525726318</t>
   </si>
   <si>
     <t xml:space="preserve">8.30954647064209</t>
@@ -2597,40 +2597,40 @@
     <t xml:space="preserve">8.50700092315674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06645488739014</t>
+    <t xml:space="preserve">8.91836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06645584106445</t>
   </si>
   <si>
     <t xml:space="preserve">9.34618282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39554786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46136569976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52718353271484</t>
+    <t xml:space="preserve">9.39554691314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46136474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52718257904053</t>
   </si>
   <si>
     <t xml:space="preserve">9.60945606231689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56009101867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54363822937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32972812652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36263751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37909126281738</t>
+    <t xml:space="preserve">9.56009197235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5436372756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32972717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36263656616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37909030914307</t>
   </si>
   <si>
     <t xml:space="preserve">9.2145471572876</t>
@@ -2639,28 +2639,28 @@
     <t xml:space="preserve">9.16518306732178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01709175109863</t>
+    <t xml:space="preserve">9.01709079742432</t>
   </si>
   <si>
     <t xml:space="preserve">8.88545608520508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03354549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11581993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81963634490967</t>
+    <t xml:space="preserve">9.03354644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11581897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81963729858398</t>
   </si>
   <si>
     <t xml:space="preserve">8.73736476898193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83609199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95127391815186</t>
+    <t xml:space="preserve">8.83609294891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95127487182617</t>
   </si>
   <si>
     <t xml:space="preserve">8.90190982818604</t>
@@ -2675,46 +2675,46 @@
     <t xml:space="preserve">8.57281970977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58927345275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63863754272461</t>
+    <t xml:space="preserve">8.58927440643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63863658905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.60572814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40827465057373</t>
+    <t xml:space="preserve">8.40827369689941</t>
   </si>
   <si>
     <t xml:space="preserve">8.24372863769531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29309177398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34245491027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77027416229248</t>
+    <t xml:space="preserve">8.2930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34245586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77027320861816</t>
   </si>
   <si>
     <t xml:space="preserve">8.85254669189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68800067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80318164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08290958404541</t>
+    <t xml:space="preserve">8.68800163269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80318355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08291053771973</t>
   </si>
   <si>
     <t xml:space="preserve">9.099365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18163776397705</t>
+    <t xml:space="preserve">9.18163871765137</t>
   </si>
   <si>
     <t xml:space="preserve">8.70445537567139</t>
@@ -2723,58 +2723,58 @@
     <t xml:space="preserve">8.75382041931152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6550931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62218189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55636405944824</t>
+    <t xml:space="preserve">8.65509223937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62218284606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55636310577393</t>
   </si>
   <si>
     <t xml:space="preserve">8.96772861480713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9841833114624</t>
+    <t xml:space="preserve">8.98418235778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.35891056060791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27663707733154</t>
+    <t xml:space="preserve">8.27663803100586</t>
   </si>
   <si>
     <t xml:space="preserve">8.18613719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26018333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14500141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98045444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99691009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20259094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94754648208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93931818008423</t>
+    <t xml:space="preserve">8.26018238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14500045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98045539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99690961837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20259189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94754457473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93931770324707</t>
   </si>
   <si>
     <t xml:space="preserve">8.03804683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12854766845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98868274688721</t>
+    <t xml:space="preserve">8.12854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98868227005005</t>
   </si>
   <si>
     <t xml:space="preserve">8.13677406311035</t>
@@ -2783,46 +2783,46 @@
     <t xml:space="preserve">7.89818286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9557728767395</t>
+    <t xml:space="preserve">7.95577383041382</t>
   </si>
   <si>
     <t xml:space="preserve">8.01336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83236455917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97222852706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08740901947021</t>
+    <t xml:space="preserve">7.83236360549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97222805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08740997314453</t>
   </si>
   <si>
     <t xml:space="preserve">8.10386562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16968250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05000114440918</t>
+    <t xml:space="preserve">8.16968154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0500020980835</t>
   </si>
   <si>
     <t xml:space="preserve">9.00063800811768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13227367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8899564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87349987030029</t>
+    <t xml:space="preserve">9.13227462768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87350034713745</t>
   </si>
   <si>
     <t xml:space="preserve">7.569091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60200071334839</t>
+    <t xml:space="preserve">7.60199975967407</t>
   </si>
   <si>
     <t xml:space="preserve">7.59377241134644</t>
@@ -2834,46 +2834,46 @@
     <t xml:space="preserve">7.21531915664673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12481880187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39631843566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30581951141357</t>
+    <t xml:space="preserve">7.12481832504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3963189125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30581855773926</t>
   </si>
   <si>
     <t xml:space="preserve">7.24000120162964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69250011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55263614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52795600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745565414429</t>
+    <t xml:space="preserve">7.69250106811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55263757705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52795505523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745517730713</t>
   </si>
   <si>
     <t xml:space="preserve">7.33872747421265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4621376991272</t>
+    <t xml:space="preserve">7.46213674545288</t>
   </si>
   <si>
     <t xml:space="preserve">7.4045467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44568252563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65959215164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70895528793335</t>
+    <t xml:space="preserve">7.44568300247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65959167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70895481109619</t>
   </si>
   <si>
     <t xml:space="preserve">7.79945468902588</t>
@@ -2882,22 +2882,22 @@
     <t xml:space="preserve">8.21081829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12031936645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07918167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79122829437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85704660415649</t>
+    <t xml:space="preserve">8.12031841278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07918262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79122924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85704612731934</t>
   </si>
   <si>
     <t xml:space="preserve">8.02159214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91463661193848</t>
+    <t xml:space="preserve">7.91463708877563</t>
   </si>
   <si>
     <t xml:space="preserve">7.81590938568115</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">7.70072746276855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67604637145996</t>
+    <t xml:space="preserve">7.67604684829712</t>
   </si>
   <si>
     <t xml:space="preserve">7.42922735214233</t>
@@ -2918,55 +2918,55 @@
     <t xml:space="preserve">7.29759120941162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66781902313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48681974411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61022806167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6842737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51149988174438</t>
+    <t xml:space="preserve">7.66781997680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48681831359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61022758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68427324295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5115008354187</t>
   </si>
   <si>
     <t xml:space="preserve">7.41277408599854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76654624938965</t>
+    <t xml:space="preserve">7.76654577255249</t>
   </si>
   <si>
     <t xml:space="preserve">7.65136432647705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73363637924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82413721084595</t>
+    <t xml:space="preserve">7.7336368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82413625717163</t>
   </si>
   <si>
     <t xml:space="preserve">7.71718263626099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58554697036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4703631401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90268325805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72168302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.894455909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10836458206177</t>
+    <t xml:space="preserve">7.58554601669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47036361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9026837348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72168254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89445543289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10836505889893</t>
   </si>
   <si>
     <t xml:space="preserve">7.28936386108398</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">7.50327444076538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37163782119751</t>
+    <t xml:space="preserve">7.37163734436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.42100048065186</t>
@@ -2996,43 +2996,43 @@
     <t xml:space="preserve">8.02981948852539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09563636779785</t>
+    <t xml:space="preserve">8.09563732147217</t>
   </si>
   <si>
     <t xml:space="preserve">8.07095527648926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75009202957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80768299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84059190750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84881925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54441070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72541093826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31404638290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77477264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73959684371948</t>
+    <t xml:space="preserve">7.75009250640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80768203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84059143066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8488187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54441022872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72540998458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31404590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77477312088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7395977973938</t>
   </si>
   <si>
     <t xml:space="preserve">7.63831615447998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61299562454224</t>
+    <t xml:space="preserve">7.61299514770508</t>
   </si>
   <si>
     <t xml:space="preserve">7.80711793899536</t>
@@ -3050,25 +3050,25 @@
     <t xml:space="preserve">7.76491785049438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81555891036987</t>
+    <t xml:space="preserve">7.81555986404419</t>
   </si>
   <si>
     <t xml:space="preserve">7.79023694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64675569534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35979127883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13190793991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25007009506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05594730377197</t>
+    <t xml:space="preserve">7.64675664901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35979175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13190746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25007057189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05594682693481</t>
   </si>
   <si>
     <t xml:space="preserve">7.04750680923462</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">7.00530624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16566848754883</t>
+    <t xml:space="preserve">7.16566896438599</t>
   </si>
   <si>
     <t xml:space="preserve">7.03062677383423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03906679153442</t>
+    <t xml:space="preserve">7.03906631469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.11502838134766</t>
@@ -3092,61 +3092,61 @@
     <t xml:space="preserve">7.17410850524902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09814739227295</t>
+    <t xml:space="preserve">7.09814691543579</t>
   </si>
   <si>
     <t xml:space="preserve">7.01374673843384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92090463638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99686527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75210189819336</t>
+    <t xml:space="preserve">6.9209041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99686574935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75210237503052</t>
   </si>
   <si>
     <t xml:space="preserve">6.76898288726807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86182451248169</t>
+    <t xml:space="preserve">6.86182403564453</t>
   </si>
   <si>
     <t xml:space="preserve">6.98842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93778514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92934465408325</t>
+    <t xml:space="preserve">6.93778610229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92934513092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.83650350570679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89558506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91246461868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76054239273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68458127975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69302129745483</t>
+    <t xml:space="preserve">6.89558458328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9124641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76054286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68458080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69302177429199</t>
   </si>
   <si>
     <t xml:space="preserve">6.9462251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14034795761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02218675613403</t>
+    <t xml:space="preserve">7.14034843444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02218627929688</t>
   </si>
   <si>
     <t xml:space="preserve">6.96310567855835</t>
@@ -3182,16 +3182,16 @@
     <t xml:space="preserve">6.35541677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40605735778809</t>
+    <t xml:space="preserve">6.40605783462524</t>
   </si>
   <si>
     <t xml:space="preserve">6.21193408966064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22037410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24569511413574</t>
+    <t xml:space="preserve">6.220374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">6.16129398345947</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">6.28789520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16973304748535</t>
+    <t xml:space="preserve">6.16973352432251</t>
   </si>
   <si>
     <t xml:space="preserve">6.11909294128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14441394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04313135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08533191680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06845188140869</t>
+    <t xml:space="preserve">6.14441347122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04313182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08533239364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06845235824585</t>
   </si>
   <si>
     <t xml:space="preserve">5.88276863098145</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">5.95873022079468</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00093126296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98405075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92496919631958</t>
+    <t xml:space="preserve">6.00093078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98405122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92496967315674</t>
   </si>
   <si>
     <t xml:space="preserve">6.03469181060791</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">5.87432909011841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69708585739136</t>
+    <t xml:space="preserve">5.69708633422852</t>
   </si>
   <si>
     <t xml:space="preserve">5.62956523895264</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">5.67176580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51140356063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4945240020752</t>
+    <t xml:space="preserve">5.51140403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49452352523804</t>
   </si>
   <si>
     <t xml:space="preserve">5.57892465591431</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">5.64644527435303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58736515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82368850708008</t>
+    <t xml:space="preserve">5.5873646736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82368803024292</t>
   </si>
   <si>
     <t xml:space="preserve">6.07689189910889</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">6.00937128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90808916091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85744857788086</t>
+    <t xml:space="preserve">5.90808963775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85744905471802</t>
   </si>
   <si>
     <t xml:space="preserve">5.89964914321899</t>
@@ -3317,19 +3317,19 @@
     <t xml:space="preserve">5.72240686416626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7561674118042</t>
+    <t xml:space="preserve">5.75616693496704</t>
   </si>
   <si>
     <t xml:space="preserve">5.77304744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74772691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89120864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76460742950439</t>
+    <t xml:space="preserve">5.747727394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8912091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76460695266724</t>
   </si>
   <si>
     <t xml:space="preserve">5.95029020309448</t>
@@ -3347,16 +3347,16 @@
     <t xml:space="preserve">5.7308464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80680799484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65488576889038</t>
+    <t xml:space="preserve">5.80680847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65488529205322</t>
   </si>
   <si>
     <t xml:space="preserve">5.68020582199097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78148746490479</t>
+    <t xml:space="preserve">5.78148698806763</t>
   </si>
   <si>
     <t xml:space="preserve">6.01781129837036</t>
@@ -3383,10 +3383,10 @@
     <t xml:space="preserve">6.23725414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27945518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20349407196045</t>
+    <t xml:space="preserve">6.27945566177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20349359512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001138687134</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">6.38917684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36385679244995</t>
+    <t xml:space="preserve">6.36385631561279</t>
   </si>
   <si>
     <t xml:space="preserve">6.43137788772583</t>
@@ -3413,10 +3413,10 @@
     <t xml:space="preserve">6.3469762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32165622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30477523803711</t>
+    <t xml:space="preserve">6.32165575027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30477571487427</t>
   </si>
   <si>
     <t xml:space="preserve">6.37229681015015</t>
@@ -3425,28 +3425,28 @@
     <t xml:space="preserve">6.31321573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97561073303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84056854248047</t>
+    <t xml:space="preserve">5.97561025619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84056806564331</t>
   </si>
   <si>
     <t xml:space="preserve">5.83212852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58329963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10221195220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09377193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27101469039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39761686325073</t>
+    <t xml:space="preserve">6.58330011367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10221242904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09377241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27101516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39761734008789</t>
   </si>
   <si>
     <t xml:space="preserve">6.43302392959595</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">6.47591114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27863216400146</t>
+    <t xml:space="preserve">6.27863168716431</t>
   </si>
   <si>
     <t xml:space="preserve">6.57026195526123</t>
@@ -3476,34 +3476,34 @@
     <t xml:space="preserve">6.88762426376343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87047004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80185079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73323202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70750045776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.690345287323</t>
+    <t xml:space="preserve">6.87047052383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80185127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73323154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70749998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69034576416016</t>
   </si>
   <si>
     <t xml:space="preserve">6.64745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61314868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81042766571045</t>
+    <t xml:space="preserve">6.61314821243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81042814254761</t>
   </si>
   <si>
     <t xml:space="preserve">6.86189222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74180936813354</t>
+    <t xml:space="preserve">6.7418098449707</t>
   </si>
   <si>
     <t xml:space="preserve">6.83616018295288</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">6.79327344894409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72465515136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69892263412476</t>
+    <t xml:space="preserve">6.72465467453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6989221572876</t>
   </si>
   <si>
     <t xml:space="preserve">6.71607732772827</t>
@@ -3524,19 +3524,19 @@
     <t xml:space="preserve">6.63888072967529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62172603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3815598487854</t>
+    <t xml:space="preserve">6.62172651290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38156032562256</t>
   </si>
   <si>
     <t xml:space="preserve">6.39871501922607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40729141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5273756980896</t>
+    <t xml:space="preserve">6.40729188919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52737522125244</t>
   </si>
   <si>
     <t xml:space="preserve">6.5359525680542</t>
@@ -3545,19 +3545,19 @@
     <t xml:space="preserve">6.5959939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63030290603638</t>
+    <t xml:space="preserve">6.63030338287354</t>
   </si>
   <si>
     <t xml:space="preserve">6.57883977890015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48448848724365</t>
+    <t xml:space="preserve">6.48448801040649</t>
   </si>
   <si>
     <t xml:space="preserve">6.65603590011597</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76754140853882</t>
+    <t xml:space="preserve">6.76754093170166</t>
   </si>
   <si>
     <t xml:space="preserve">6.85331439971924</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">6.93051147460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94766664505005</t>
+    <t xml:space="preserve">6.94766616821289</t>
   </si>
   <si>
     <t xml:space="preserve">6.87904739379883</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">6.99913024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92193365097046</t>
+    <t xml:space="preserve">6.92193412780762</t>
   </si>
   <si>
     <t xml:space="preserve">6.91335678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12779140472412</t>
+    <t xml:space="preserve">7.12779092788696</t>
   </si>
   <si>
     <t xml:space="preserve">7.24787330627441</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">7.17925500869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0763258934021</t>
+    <t xml:space="preserve">7.07632637023926</t>
   </si>
   <si>
     <t xml:space="preserve">7.09348154067993</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">7.14494562149048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15352296829224</t>
+    <t xml:space="preserve">7.15352249145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.01628589630127</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">6.42444658279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26147699356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20143508911133</t>
+    <t xml:space="preserve">6.26147747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20143556594849</t>
   </si>
   <si>
     <t xml:space="preserve">6.3215184211731</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">6.21858978271484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34725093841553</t>
+    <t xml:space="preserve">6.34725046157837</t>
   </si>
   <si>
     <t xml:space="preserve">6.29578638076782</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">6.03846502304077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00415563583374</t>
+    <t xml:space="preserve">6.0041561126709</t>
   </si>
   <si>
     <t xml:space="preserve">5.89264965057373</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">6.41586923599243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56168460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68176746368408</t>
+    <t xml:space="preserve">6.56168508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68176794052124</t>
   </si>
   <si>
     <t xml:space="preserve">7.05917167663574</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">7.23929643630981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29933786392212</t>
+    <t xml:space="preserve">7.29933834075928</t>
   </si>
   <si>
     <t xml:space="preserve">7.37653541564941</t>
@@ -3749,67 +3749,67 @@
     <t xml:space="preserve">7.3851113319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47946262359619</t>
+    <t xml:space="preserve">7.47946310043335</t>
   </si>
   <si>
     <t xml:space="preserve">7.46230840682983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50519514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49661779403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59954595565796</t>
+    <t xml:space="preserve">7.50519466400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49661731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5995454788208</t>
   </si>
   <si>
     <t xml:space="preserve">7.53092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48803901672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40226602554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51377201080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35938024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34222507476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66816377639771</t>
+    <t xml:space="preserve">7.48803949356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40226650238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51377248764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35937976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34222459793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66816425323486</t>
   </si>
   <si>
     <t xml:space="preserve">7.8139796257019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6853199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67674255371094</t>
+    <t xml:space="preserve">7.68531942367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67674207687378</t>
   </si>
   <si>
     <t xml:space="preserve">7.60812282562256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69389677047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90833234786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0713005065918</t>
+    <t xml:space="preserve">7.69389772415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90833139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07130146026611</t>
   </si>
   <si>
     <t xml:space="preserve">8.29431247711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2342700958252</t>
+    <t xml:space="preserve">8.23427104949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.37150859832764</t>
@@ -69824,7 +69824,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6493634259</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>183868</v>
@@ -69845,6 +69845,32 @@
         <v>1486</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494444444</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>401719</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>9.71000003814697</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>9.77000045776367</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>9.89999961853027</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13601112365723</t>
+    <t xml:space="preserve">8.13600921630859</t>
   </si>
   <si>
     <t xml:space="preserve">FILA.MI</t>
@@ -47,112 +47,112 @@
     <t xml:space="preserve">8.08278369903564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05997276306152</t>
+    <t xml:space="preserve">8.05997371673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.06757640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1284065246582</t>
+    <t xml:space="preserve">8.12840557098389</t>
   </si>
   <si>
     <t xml:space="preserve">8.11319828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90029239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87748193740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591569900513</t>
+    <t xml:space="preserve">7.90029382705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87748336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591617584229</t>
   </si>
   <si>
     <t xml:space="preserve">7.5277099609375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48969125747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95352029800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79384183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67978668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62655925750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71020126342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89268970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8242564201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60374689102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69499397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98393487930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84706735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91550254821777</t>
+    <t xml:space="preserve">7.48969221115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95352077484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79384088516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67978477478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62655878067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71019887924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89269113540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82425546646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6037483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69499349594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98393535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84706783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91550302505493</t>
   </si>
   <si>
     <t xml:space="preserve">8.01435089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10559558868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24246215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25006771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3032922744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15121650695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23485946655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.356520652771</t>
+    <t xml:space="preserve">8.20444297790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10559463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24246311187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25006580352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30329132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15121841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23486042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35651874542236</t>
   </si>
   <si>
     <t xml:space="preserve">8.28808498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.219651222229</t>
+    <t xml:space="preserve">8.21965026855469</t>
   </si>
   <si>
     <t xml:space="preserve">8.36412239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29568958282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38693428039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14361381530762</t>
+    <t xml:space="preserve">8.29568672180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38693332672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1436128616333</t>
   </si>
   <si>
     <t xml:space="preserve">8.18923664093018</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">8.40974426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40214157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37932968139648</t>
+    <t xml:space="preserve">8.40214061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37932872772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.51619815826416</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">8.75191402435303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82034683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80514049530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82794952392578</t>
+    <t xml:space="preserve">8.82034778594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80513858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82795333862305</t>
   </si>
   <si>
     <t xml:space="preserve">9.01044082641602</t>
@@ -188,144 +188,144 @@
     <t xml:space="preserve">9.09408283233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9800271987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12449645996094</t>
+    <t xml:space="preserve">8.98002529144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12449836730957</t>
   </si>
   <si>
     <t xml:space="preserve">9.19293117523193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78993225097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11689281463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17772388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03325271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08647727966309</t>
+    <t xml:space="preserve">8.78993320465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11689376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17772483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03325176239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08647918701172</t>
   </si>
   <si>
     <t xml:space="preserve">9.20053482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34500503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13970375061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61113739013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67196750640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65675830841064</t>
+    <t xml:space="preserve">9.34500694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13970565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61113548278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67196846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65675926208496</t>
   </si>
   <si>
     <t xml:space="preserve">9.80883502960205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90008068084717</t>
+    <t xml:space="preserve">9.90007972717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77081680297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73252868652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47217750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49514865875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57172393798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70190048217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77847290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67892742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69424247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61001396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6482982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51046562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41857624053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2654275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22714138031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1888542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11228084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34200477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63298320770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20417022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21182823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3037166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72487258911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34966087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38794708251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59469699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5334358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75550174713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76315975189209</t>
   </si>
   <si>
     <t xml:space="preserve">9.7708158493042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73252964019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4721794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49515151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57172393798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70189952850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67892742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69424152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61001110076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6482982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51046657562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41857624053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26542854309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22714233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1888542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11228084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34200286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63298320770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20416927337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21182823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30371570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7248706817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34965991973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38794898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59469604492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53343772888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75550079345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76315975189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77081680297852</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.62532615661621</t>
   </si>
   <si>
@@ -335,28 +335,28 @@
     <t xml:space="preserve">9.78612995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74784278869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7172155380249</t>
+    <t xml:space="preserve">9.74784374237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71721458435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.68658542633057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6712703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36497497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56406688690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57938098907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80910301208496</t>
+    <t xml:space="preserve">9.67126941680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36497402191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56406879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57938003540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80910205841064</t>
   </si>
   <si>
     <t xml:space="preserve">9.70955657958984</t>
@@ -365,28 +365,28 @@
     <t xml:space="preserve">9.66361331939697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74018669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51812076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4492073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39560508728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3573169708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54109477996826</t>
+    <t xml:space="preserve">9.7401876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51812267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44920635223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39560413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35731506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54109287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.41091823577881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80144500732422</t>
+    <t xml:space="preserve">9.80144596099854</t>
   </si>
   <si>
     <t xml:space="preserve">9.55641174316406</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">9.79378890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86270332336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90864944458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9392786026001</t>
+    <t xml:space="preserve">9.86270427703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90865039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93927669525146</t>
   </si>
   <si>
     <t xml:space="preserve">9.92396354675293</t>
@@ -410,31 +410,31 @@
     <t xml:space="preserve">10.222601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2685441970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.283860206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3910627365112</t>
+    <t xml:space="preserve">10.2685461044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838621139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3910646438599</t>
   </si>
   <si>
     <t xml:space="preserve">10.4829521179199</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5824966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7050180435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6437568664551</t>
+    <t xml:space="preserve">10.582498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7050161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6437578201294</t>
   </si>
   <si>
     <t xml:space="preserve">10.7203302383423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3374614715576</t>
+    <t xml:space="preserve">10.3374633789062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4523220062256</t>
@@ -443,79 +443,79 @@
     <t xml:space="preserve">10.1843166351318</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0771131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0694551467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2379179000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95459365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87036228179932</t>
+    <t xml:space="preserve">10.077112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0694532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617952346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95459270477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87036323547363</t>
   </si>
   <si>
     <t xml:space="preserve">9.82441806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0388231277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98522281646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85504817962646</t>
+    <t xml:space="preserve">10.0388250350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98522186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85504722595215</t>
   </si>
   <si>
     <t xml:space="preserve">9.93162059783936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94693565368652</t>
+    <t xml:space="preserve">9.94693660736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.89333438873291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0541391372681</t>
+    <t xml:space="preserve">10.0541400909424</t>
   </si>
   <si>
     <t xml:space="preserve">9.97756481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1613426208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288963317871</t>
+    <t xml:space="preserve">9.88567638397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1613416671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288972854614</t>
   </si>
   <si>
     <t xml:space="preserve">10.5671834945679</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490611076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2991743087769</t>
+    <t xml:space="preserve">10.4906101226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2991752624512</t>
   </si>
   <si>
     <t xml:space="preserve">10.2608890533447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4063777923584</t>
+    <t xml:space="preserve">10.4063787460327</t>
   </si>
   <si>
     <t xml:space="preserve">10.4140357971191</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2455739974976</t>
+    <t xml:space="preserve">10.2455730438232</t>
   </si>
   <si>
     <t xml:space="preserve">10.1153974533081</t>
@@ -527,34 +527,34 @@
     <t xml:space="preserve">10.2915182113647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3987216949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4982662200928</t>
+    <t xml:space="preserve">10.398720741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4982671737671</t>
   </si>
   <si>
     <t xml:space="preserve">10.4293508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6054716110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5901565551758</t>
+    <t xml:space="preserve">10.6054697036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5901556015015</t>
   </si>
   <si>
     <t xml:space="preserve">10.3757486343384</t>
   </si>
   <si>
-    <t xml:space="preserve">10.253231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1460275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3068323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4752969741821</t>
+    <t xml:space="preserve">10.2532320022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1460266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3068342208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4752950668335</t>
   </si>
   <si>
     <t xml:space="preserve">10.5212392807007</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">10.4446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3298034667969</t>
+    <t xml:space="preserve">10.3298053741455</t>
   </si>
   <si>
     <t xml:space="preserve">10.1230554580688</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">10.4216938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.781590461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2027463912964</t>
+    <t xml:space="preserve">10.7815895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2027454376221</t>
   </si>
   <si>
     <t xml:space="preserve">11.1797742843628</t>
@@ -584,43 +584,43 @@
     <t xml:space="preserve">11.1338291168213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3329229354858</t>
+    <t xml:space="preserve">11.3329219818115</t>
   </si>
   <si>
     <t xml:space="preserve">11.2946348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.409496307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2793207168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.378867149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6775035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7081336975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8383102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6851596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6468744277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5473279953003</t>
+    <t xml:space="preserve">11.4094953536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2793188095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3788652420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6775045394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7081346511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8383092880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6851615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6468753814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5473289489746</t>
   </si>
   <si>
     <t xml:space="preserve">11.4018383026123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5243558883667</t>
+    <t xml:space="preserve">11.524356842041</t>
   </si>
   <si>
     <t xml:space="preserve">11.6392164230347</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">11.7157907485962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7923641204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2288360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2441492080688</t>
+    <t xml:space="preserve">11.7923631668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.228835105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2441501617432</t>
   </si>
   <si>
     <t xml:space="preserve">12.3513536453247</t>
@@ -644,25 +644,25 @@
     <t xml:space="preserve">12.4049549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5198173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2549228668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5918464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6301355361938</t>
+    <t xml:space="preserve">12.5198154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2549247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5918474197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6301345825195</t>
   </si>
   <si>
     <t xml:space="preserve">13.7832822799683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2472658157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8184547424316</t>
+    <t xml:space="preserve">13.2472677230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8184537887573</t>
   </si>
   <si>
     <t xml:space="preserve">12.6346769332886</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">12.7112483978271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0252017974854</t>
+    <t xml:space="preserve">13.0251998901367</t>
   </si>
   <si>
     <t xml:space="preserve">12.8643980026245</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">13.2396078109741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2166385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2089796066284</t>
+    <t xml:space="preserve">13.2166376113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2089815139771</t>
   </si>
   <si>
     <t xml:space="preserve">13.7373390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3621273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4004144668579</t>
+    <t xml:space="preserve">13.3621282577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4004154205322</t>
   </si>
   <si>
     <t xml:space="preserve">13.7143659591675</t>
@@ -704,139 +704,139 @@
     <t xml:space="preserve">13.5152750015259</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6684217453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.614821434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.319296836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3958721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3882179260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4341592788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5490207672119</t>
+    <t xml:space="preserve">13.668420791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6148195266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.319299697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3958730697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3882141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4341621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5490188598633</t>
   </si>
   <si>
     <t xml:space="preserve">14.6791944503784</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2810134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3269596099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4265041351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3422708511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5337066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2733554840088</t>
+    <t xml:space="preserve">14.2810144424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.326958656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4265060424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3422727584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5337076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2733564376831</t>
   </si>
   <si>
     <t xml:space="preserve">14.0359764099121</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0512914657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9897298812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1282434463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.397572517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4976110458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0820713043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1436338424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590608596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.574559211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5976438522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6592054367065</t>
+    <t xml:space="preserve">14.0512952804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9897289276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1282405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.497612953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0820722579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1436328887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590589523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5745601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5976448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6592044830322</t>
   </si>
   <si>
     <t xml:space="preserve">14.3437051773071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3667917251587</t>
+    <t xml:space="preserve">14.3667898178101</t>
   </si>
   <si>
     <t xml:space="preserve">14.3514003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2513656616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0435962677002</t>
+    <t xml:space="preserve">14.2513666152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0435953140259</t>
   </si>
   <si>
     <t xml:space="preserve">14.5437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.58225440979</t>
+    <t xml:space="preserve">14.5822534561157</t>
   </si>
   <si>
     <t xml:space="preserve">14.3129253387451</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5360832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4899139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6976804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6207304000854</t>
+    <t xml:space="preserve">14.5360813140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4899129867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.697681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6207313537598</t>
   </si>
   <si>
     <t xml:space="preserve">14.4591341018677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7742671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0974617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8896923065186</t>
+    <t xml:space="preserve">13.7742681503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0974636077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8896932601929</t>
   </si>
   <si>
     <t xml:space="preserve">13.9127788543701</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8973894119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2436695098877</t>
+    <t xml:space="preserve">13.897388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.243670463562</t>
   </si>
   <si>
     <t xml:space="preserve">14.389874458313</t>
@@ -845,121 +845,121 @@
     <t xml:space="preserve">14.4129610061646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3821792602539</t>
+    <t xml:space="preserve">14.3821811676025</t>
   </si>
   <si>
     <t xml:space="preserve">14.4437437057495</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5591697692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7361555099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5053024291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5283880233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283533096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514764785767</t>
+    <t xml:space="preserve">14.5591716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.736156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5053043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5283899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283514022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.551474571228</t>
   </si>
   <si>
     <t xml:space="preserve">14.4360504150391</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2744493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.051290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9666423797607</t>
+    <t xml:space="preserve">14.2744483947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512933731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9666471481323</t>
   </si>
   <si>
     <t xml:space="preserve">13.6742305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1205463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1590232849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1513261795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8512172698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9743413925171</t>
+    <t xml:space="preserve">14.120548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1590251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1513271331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8512153625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9743394851685</t>
   </si>
   <si>
     <t xml:space="preserve">14.1744117736816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2051935195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0051212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3052310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3590965270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2975339889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4206581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.328314781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.336009979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3744869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2359733581543</t>
+    <t xml:space="preserve">14.2051954269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0051183700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3052320480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3590974807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.297534942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4206562042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3283157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3360109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3744897842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2359743118286</t>
   </si>
   <si>
     <t xml:space="preserve">14.5129985809326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2205839157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1974992752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3902397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2440357208252</t>
+    <t xml:space="preserve">14.2205829620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1974983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3902416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2440347671509</t>
   </si>
   <si>
     <t xml:space="preserve">15.2517318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1670837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.105523109436</t>
+    <t xml:space="preserve">15.1670846939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1055250167847</t>
   </si>
   <si>
     <t xml:space="preserve">15.197865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0670480728149</t>
+    <t xml:space="preserve">15.0670461654663</t>
   </si>
   <si>
     <t xml:space="preserve">14.9208402633667</t>
@@ -968,46 +968,46 @@
     <t xml:space="preserve">14.9285354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8823661804199</t>
+    <t xml:space="preserve">14.8823652267456</t>
   </si>
   <si>
     <t xml:space="preserve">14.5206937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2898406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7515439987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6438150405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5668630599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6515121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7438526153564</t>
+    <t xml:space="preserve">14.2898397445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7515468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6438140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5668649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6515130996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7438507080078</t>
   </si>
   <si>
     <t xml:space="preserve">14.7900218963623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8361930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7746334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6361207962036</t>
+    <t xml:space="preserve">14.8361911773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7746315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6361198425293</t>
   </si>
   <si>
     <t xml:space="preserve">14.7207660675049</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4514360427856</t>
+    <t xml:space="preserve">14.45143699646</t>
   </si>
   <si>
     <t xml:space="preserve">14.4668273925781</t>
@@ -1016,136 +1016,136 @@
     <t xml:space="preserve">14.5899505615234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8131093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8515853881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1439971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.290207862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3440742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5441446304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5826206207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.505669593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4287214279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2209510803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9747066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1286087036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9289035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7365217208862</t>
+    <t xml:space="preserve">14.8131084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8515844345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1439981460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2902069091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3440704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5441465377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5826215744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5056715011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4287185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2209501266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.974705696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.128607749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9288988113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7365207672119</t>
   </si>
   <si>
     <t xml:space="preserve">15.8134727478027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2367057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0828056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6210947036743</t>
+    <t xml:space="preserve">16.2367038726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0828037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6210966110229</t>
   </si>
   <si>
     <t xml:space="preserve">16.0058498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.121280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6980485916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.774998664856</t>
+    <t xml:space="preserve">16.1212787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6980476379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7749977111816</t>
   </si>
   <si>
     <t xml:space="preserve">15.2671184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9131441116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8977556228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8054141998291</t>
+    <t xml:space="preserve">14.9131460189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8977537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8054151535034</t>
   </si>
   <si>
     <t xml:space="preserve">15.1747779846191</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0208778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0516557693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8208055496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0362682342529</t>
+    <t xml:space="preserve">15.0208768844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0516548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8208045959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0362691879272</t>
   </si>
   <si>
     <t xml:space="preserve">13.9281692504883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1128520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2821445465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4822187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5588026046753</t>
+    <t xml:space="preserve">14.1128530502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2821435928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4822177886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5588035583496</t>
   </si>
   <si>
     <t xml:space="preserve">13.7127065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5434122085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3125591278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2048263549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4510717391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4356832504272</t>
+    <t xml:space="preserve">13.5434131622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3125610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2048282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4510726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4356822967529</t>
   </si>
   <si>
     <t xml:space="preserve">13.2817811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6511459350586</t>
+    <t xml:space="preserve">13.6511449813843</t>
   </si>
   <si>
     <t xml:space="preserve">13.3895120620728</t>
@@ -1157,34 +1157,34 @@
     <t xml:space="preserve">13.0663166046143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0047569274902</t>
+    <t xml:space="preserve">13.0047550201416</t>
   </si>
   <si>
     <t xml:space="preserve">13.0509262084961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2971706390381</t>
+    <t xml:space="preserve">13.2971715927124</t>
   </si>
   <si>
     <t xml:space="preserve">13.2356090545654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6357545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8666086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6819257736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8819980621338</t>
+    <t xml:space="preserve">13.6357536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8666095733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6819248199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8819971084595</t>
   </si>
   <si>
     <t xml:space="preserve">14.7130737304688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.958948135376</t>
+    <t xml:space="preserve">13.9589500427246</t>
   </si>
   <si>
     <t xml:space="preserve">13.9512147903442</t>
@@ -1193,40 +1193,40 @@
     <t xml:space="preserve">13.8893480300903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7656106948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9976177215576</t>
+    <t xml:space="preserve">13.7656116485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9976167678833</t>
   </si>
   <si>
     <t xml:space="preserve">14.074951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5026731491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.806658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3170690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.146933555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2397346496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6109428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5336093902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7192125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4253387451172</t>
+    <t xml:space="preserve">13.5026741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8066596984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3170700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1469345092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2397375106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6109418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5336065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7192106246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4253377914429</t>
   </si>
   <si>
     <t xml:space="preserve">13.4562749862671</t>
@@ -1235,76 +1235,76 @@
     <t xml:space="preserve">13.5645427703857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3789386749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3016061782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5490741729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8274822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8738832473755</t>
+    <t xml:space="preserve">13.3789396286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3016042709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5490751266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8274793624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8738813400269</t>
   </si>
   <si>
     <t xml:space="preserve">13.6573438644409</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0594844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1213531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0285501480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8584136962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9048156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9666843414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1986894607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058864593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9202814102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1677551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5389604568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4925622940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4306945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3688230514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2914905548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3533592224121</t>
+    <t xml:space="preserve">14.0594835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1213541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0285511016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8584146499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9048147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.966682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1986865997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058855056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9202823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1677560806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5389614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4925603866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4306926727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.368824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2914896011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3533554077148</t>
   </si>
   <si>
     <t xml:space="preserve">14.4616250991821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008281707764</t>
+    <t xml:space="preserve">14.600830078125</t>
   </si>
   <si>
     <t xml:space="preserve">13.7810802459717</t>
@@ -1313,64 +1313,64 @@
     <t xml:space="preserve">14.3842935562134</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5080270767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3224229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5698976516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3069562911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1368207931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.152286529541</t>
+    <t xml:space="preserve">14.5080308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3224258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.569899559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3069553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1368188858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1522874832153</t>
   </si>
   <si>
     <t xml:space="preserve">13.6882772445679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0130844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2088022232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4408082962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.487208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6728115081787</t>
+    <t xml:space="preserve">14.0130834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2088012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4408054351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4872064590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6728105545044</t>
   </si>
   <si>
     <t xml:space="preserve">13.7037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5800085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6983919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6829233169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5746555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6519899368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9149284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0231981277466</t>
+    <t xml:space="preserve">13.5800075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6983909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6829242706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5746545791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6519908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9149293899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0231990814209</t>
   </si>
   <si>
     <t xml:space="preserve">12.6674575805664</t>
@@ -1379,19 +1379,19 @@
     <t xml:space="preserve">12.2189149856567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5591897964478</t>
+    <t xml:space="preserve">12.5591888427734</t>
   </si>
   <si>
     <t xml:space="preserve">12.2962503433228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7394371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9714422225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9405078887939</t>
+    <t xml:space="preserve">11.7394380569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9714441299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9405088424683</t>
   </si>
   <si>
     <t xml:space="preserve">12.095178604126</t>
@@ -1406,16 +1406,16 @@
     <t xml:space="preserve">11.87864112854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8477058410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6621036529541</t>
+    <t xml:space="preserve">11.8477087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621046066284</t>
   </si>
   <si>
     <t xml:space="preserve">11.6002359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5074329376221</t>
+    <t xml:space="preserve">11.5074338912964</t>
   </si>
   <si>
     <t xml:space="preserve">11.1362266540527</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">10.8887538909912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2599630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9351539611816</t>
+    <t xml:space="preserve">11.2599620819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9351558685303</t>
   </si>
   <si>
     <t xml:space="preserve">11.0124912261963</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3682298660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4455671310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5847673416138</t>
+    <t xml:space="preserve">11.3682308197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4455661773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5847682952881</t>
   </si>
   <si>
     <t xml:space="preserve">10.5175476074219</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">11.3458576202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9418039321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0226154327393</t>
+    <t xml:space="preserve">11.2973718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9418029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0226144790649</t>
   </si>
   <si>
     <t xml:space="preserve">10.6185598373413</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">11.1195878982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7984008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2165603637695</t>
+    <t xml:space="preserve">11.7983999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2165613174438</t>
   </si>
   <si>
     <t xml:space="preserve">11.0711002349854</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">11.2488851547241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2003984451294</t>
+    <t xml:space="preserve">11.2003993988037</t>
   </si>
   <si>
     <t xml:space="preserve">10.6832075119019</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">10.9094791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8609914779663</t>
+    <t xml:space="preserve">10.8609933853149</t>
   </si>
   <si>
     <t xml:space="preserve">11.4751558303833</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">11.4266691207886</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5236415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7801809310913</t>
+    <t xml:space="preserve">11.523642539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7801818847656</t>
   </si>
   <si>
     <t xml:space="preserve">10.8933162689209</t>
@@ -1526,16 +1526,16 @@
     <t xml:space="preserve">11.0549392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9579648971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9741268157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8448295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8125047683716</t>
+    <t xml:space="preserve">10.9579658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9741277694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8448305130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8125066757202</t>
   </si>
   <si>
     <t xml:space="preserve">11.1357488632202</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">11.0872640609741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3296957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6044521331787</t>
+    <t xml:space="preserve">11.3296966552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.604453086853</t>
   </si>
   <si>
     <t xml:space="preserve">11.8792095184326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8630475997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7337503433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6529407501221</t>
+    <t xml:space="preserve">11.8630485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7337493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6529388427734</t>
   </si>
   <si>
     <t xml:space="preserve">11.8468856811523</t>
@@ -1571,37 +1571,37 @@
     <t xml:space="preserve">11.2650461196899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.362021446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0387754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6508836746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5539112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5215873718262</t>
+    <t xml:space="preserve">11.3620204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0387773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6508846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5539121627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5215864181519</t>
   </si>
   <si>
     <t xml:space="preserve">10.1013708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9882345199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3922872543335</t>
+    <t xml:space="preserve">9.98823356628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3922882080078</t>
   </si>
   <si>
     <t xml:space="preserve">10.3114786148071</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2953147888184</t>
+    <t xml:space="preserve">10.2953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">10.376127243042</t>
@@ -1610,16 +1610,16 @@
     <t xml:space="preserve">10.3599643707275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6023969650269</t>
+    <t xml:space="preserve">10.6023979187012</t>
   </si>
   <si>
     <t xml:space="preserve">10.5862350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3438034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5700731277466</t>
+    <t xml:space="preserve">10.3438024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5700750350952</t>
   </si>
   <si>
     <t xml:space="preserve">10.7963428497314</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">11.1034240722656</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1842355728149</t>
+    <t xml:space="preserve">11.1842365264893</t>
   </si>
   <si>
     <t xml:space="preserve">11.1519117355347</t>
@@ -1637,43 +1637,43 @@
     <t xml:space="preserve">10.4730997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4569387435913</t>
+    <t xml:space="preserve">10.456937789917</t>
   </si>
   <si>
     <t xml:space="preserve">10.4084510803223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.667046546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2465219497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5067510604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5880727767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7669811248779</t>
+    <t xml:space="preserve">10.6670455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2465229034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5067520141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5880737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7669801712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9458885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9621524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7507162094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3441076278687</t>
+    <t xml:space="preserve">10.9621515274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7507152557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.344108581543</t>
   </si>
   <si>
     <t xml:space="preserve">10.4416942596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3115787506104</t>
+    <t xml:space="preserve">10.311580657959</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278436660767</t>
@@ -1682,49 +1682,49 @@
     <t xml:space="preserve">10.4254293441772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4904861450195</t>
+    <t xml:space="preserve">10.4904880523682</t>
   </si>
   <si>
     <t xml:space="preserve">10.5230159759521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555448532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8157749176025</t>
+    <t xml:space="preserve">10.5555429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8157739639282</t>
   </si>
   <si>
     <t xml:space="preserve">10.8483018875122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1410598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9946813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8808307647705</t>
+    <t xml:space="preserve">11.1410608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9946804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8808317184448</t>
   </si>
   <si>
     <t xml:space="preserve">11.0922679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8970956802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5718078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6693954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6368656158447</t>
+    <t xml:space="preserve">10.8970947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5718088150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6693935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.636866569519</t>
   </si>
   <si>
     <t xml:space="preserve">10.653130531311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133596420288</t>
+    <t xml:space="preserve">10.9133586883545</t>
   </si>
   <si>
     <t xml:space="preserve">10.8320379257202</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">11.5639324188232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4338178634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1573247909546</t>
+    <t xml:space="preserve">11.433819770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1573238372803</t>
   </si>
   <si>
     <t xml:space="preserve">11.2386465072632</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">11.7103118896484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7428407669067</t>
+    <t xml:space="preserve">11.7428398132324</t>
   </si>
   <si>
     <t xml:space="preserve">11.5476675033569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6452541351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.701922416687</t>
+    <t xml:space="preserve">11.6452531814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7019233703613</t>
   </si>
   <si>
     <t xml:space="preserve">10.7344522476196</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">10.6856603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8645648956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4742231369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6206016540527</t>
+    <t xml:space="preserve">10.6043376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8645668029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4742221832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6206026077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.2874393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6127262115479</t>
+    <t xml:space="preserve">11.6127252578735</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314044952393</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.6289901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5151386260986</t>
+    <t xml:space="preserve">11.5151405334473</t>
   </si>
   <si>
     <t xml:space="preserve">11.2061166763306</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">11.0597381591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.076003074646</t>
+    <t xml:space="preserve">11.0760021209717</t>
   </si>
   <si>
     <t xml:space="preserve">11.1898546218872</t>
@@ -1814,91 +1814,91 @@
     <t xml:space="preserve">11.3850250244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4012899398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2549104690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3524971008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4500818252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0518627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3771476745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4259414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1657123565674</t>
+    <t xml:space="preserve">11.4012889862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2549095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.450080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0518617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3771486282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4259424209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1657133102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.3446197509766</t>
   </si>
   <si>
-    <t xml:space="preserve">12.247034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5235271453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3934144973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4422054290771</t>
+    <t xml:space="preserve">12.2470350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5235280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3934116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4422063827515</t>
   </si>
   <si>
     <t xml:space="preserve">12.6048488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3608827590942</t>
+    <t xml:space="preserve">12.3608846664429</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795629501343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4096784591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3283557891846</t>
+    <t xml:space="preserve">12.4096775054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3283567428589</t>
   </si>
   <si>
     <t xml:space="preserve">11.5964622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4663486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8404273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2958278656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5560569763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4584693908691</t>
+    <t xml:space="preserve">11.4663467407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8404264450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2958269119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5560550689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4584703445435</t>
   </si>
   <si>
     <t xml:space="preserve">12.3120908737183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1331834793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9705400466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0681257247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9380121231079</t>
+    <t xml:space="preserve">12.1331844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9705410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0681266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9380111694336</t>
   </si>
   <si>
     <t xml:space="preserve">12.0355978012085</t>
@@ -1910,28 +1910,28 @@
     <t xml:space="preserve">11.9542760848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9217472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6777820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7916316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7753677368164</t>
+    <t xml:space="preserve">11.9217481613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6777830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.791633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7753686904907</t>
   </si>
   <si>
     <t xml:space="preserve">11.1735877990723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3687610626221</t>
+    <t xml:space="preserve">11.3687601089478</t>
   </si>
   <si>
     <t xml:space="preserve">11.1247968673706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7832450866699</t>
+    <t xml:space="preserve">10.7832469940186</t>
   </si>
   <si>
     <t xml:space="preserve">10.7995090484619</t>
@@ -1943,70 +1943,70 @@
     <t xml:space="preserve">10.4091663360596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5392808914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.376636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2302570343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3603715896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36824989318848</t>
+    <t xml:space="preserve">10.5392818450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3766374588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2302589416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.360372543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36824893951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.25439929962158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53089332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41704177856445</t>
+    <t xml:space="preserve">9.53089237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41704082489014</t>
   </si>
   <si>
     <t xml:space="preserve">9.1893424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8477897644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75020408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62009143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60382652282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50624084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81500673294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42466306686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3433403968811</t>
+    <t xml:space="preserve">8.84779071807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75020503997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62009048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60382556915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50623893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81500482559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42466402053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34334087371826</t>
   </si>
   <si>
     <t xml:space="preserve">6.4244065284729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70089960098267</t>
+    <t xml:space="preserve">6.70090007781982</t>
   </si>
   <si>
     <t xml:space="preserve">6.43253898620605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11538457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48920822143555</t>
+    <t xml:space="preserve">6.11538505554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48920869827271</t>
   </si>
   <si>
     <t xml:space="preserve">5.52173709869385</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">5.86328792572021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73317432403564</t>
+    <t xml:space="preserve">5.73317337036133</t>
   </si>
   <si>
     <t xml:space="preserve">5.6111912727356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30216836929321</t>
+    <t xml:space="preserve">5.30216884613037</t>
   </si>
   <si>
     <t xml:space="preserve">5.5949273109436</t>
@@ -2042,22 +2042,22 @@
     <t xml:space="preserve">5.69251251220703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71690893173218</t>
+    <t xml:space="preserve">5.71690988540649</t>
   </si>
   <si>
     <t xml:space="preserve">6.01779890060425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74943780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18044137954712</t>
+    <t xml:space="preserve">5.74943733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18044233322144</t>
   </si>
   <si>
     <t xml:space="preserve">6.13164901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05845975875854</t>
+    <t xml:space="preserve">6.05845928192139</t>
   </si>
   <si>
     <t xml:space="preserve">6.09098815917969</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">6.5301251411438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61144685745239</t>
+    <t xml:space="preserve">6.61144638061523</t>
   </si>
   <si>
     <t xml:space="preserve">6.70903253555298</t>
@@ -2087,25 +2087,25 @@
     <t xml:space="preserve">6.50572872161865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52199363708496</t>
+    <t xml:space="preserve">6.52199268341064</t>
   </si>
   <si>
     <t xml:space="preserve">6.39187860488892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0015344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96900606155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12351703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20483922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18857383728027</t>
+    <t xml:space="preserve">6.00153493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9690055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12351751327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20483875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18857431411743</t>
   </si>
   <si>
     <t xml:space="preserve">6.30242443084717</t>
@@ -2114,34 +2114,34 @@
     <t xml:space="preserve">6.49759578704834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63584327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87167501449585</t>
+    <t xml:space="preserve">6.63584280014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87167549133301</t>
   </si>
   <si>
     <t xml:space="preserve">6.79035425186157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77409029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75782537460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9123363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39213371276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59543800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40026569366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36773824691772</t>
+    <t xml:space="preserve">6.77408981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75782585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91233682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39213466644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59543895721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40026664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36773777008057</t>
   </si>
   <si>
     <t xml:space="preserve">7.1969633102417</t>
@@ -2150,55 +2150,55 @@
     <t xml:space="preserve">6.80661869049072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89607191085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05871534347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83914661407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85541200637817</t>
+    <t xml:space="preserve">6.89607095718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0587158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83914709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85541105270386</t>
   </si>
   <si>
     <t xml:space="preserve">6.97739362716675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05058288574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14003658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94486522674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31894445419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28641510009766</t>
+    <t xml:space="preserve">7.05058336257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14003753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94486570358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31894397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28641653060913</t>
   </si>
   <si>
     <t xml:space="preserve">7.15630102157593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08311176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00992298126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02618741989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16443395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9529972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0180549621582</t>
+    <t xml:space="preserve">7.08311223983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00992155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0261869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16443300247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95299816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01805448532104</t>
   </si>
   <si>
     <t xml:space="preserve">6.66837215423584</t>
@@ -2207,70 +2207,70 @@
     <t xml:space="preserve">6.51386117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47320032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73342943191528</t>
+    <t xml:space="preserve">6.47319984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73342895507812</t>
   </si>
   <si>
     <t xml:space="preserve">6.71716499328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78222131729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56265354156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58705043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6033148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40001058578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27802848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35934925079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34308624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26989603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21297073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19670724868774</t>
+    <t xml:space="preserve">6.78222227096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56265306472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5870509147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60331392288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40001010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27802753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35935020446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34308576583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26989650726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21297121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19670581817627</t>
   </si>
   <si>
     <t xml:space="preserve">5.97713804244995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09912061691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94460916519165</t>
+    <t xml:space="preserve">6.09912014007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94461011886597</t>
   </si>
   <si>
     <t xml:space="preserve">5.78196620941162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8876838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80636310577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79009914398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72504091262817</t>
+    <t xml:space="preserve">5.88768434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80636262893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79009819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72504043579102</t>
   </si>
   <si>
     <t xml:space="preserve">5.76570224761963</t>
@@ -2282,70 +2282,70 @@
     <t xml:space="preserve">6.00966644287109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98527002334595</t>
+    <t xml:space="preserve">5.98527050018311</t>
   </si>
   <si>
     <t xml:space="preserve">6.05032730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16417789459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22110271453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9283447265625</t>
+    <t xml:space="preserve">6.16417837142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22110319137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92834520339966</t>
   </si>
   <si>
     <t xml:space="preserve">6.107253074646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03406286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31055736541748</t>
+    <t xml:space="preserve">6.0340633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31055784225464</t>
   </si>
   <si>
     <t xml:space="preserve">6.17230987548828</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92021369934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75756931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70064496994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38349056243896</t>
+    <t xml:space="preserve">5.92021322250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75757026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70064449310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38349008560181</t>
   </si>
   <si>
     <t xml:space="preserve">5.21271467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00127935409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01754331588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0419397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24524307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40788745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32682085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28615999221802</t>
+    <t xml:space="preserve">5.0012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96875047683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01754379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04193925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24524402618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40788698196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32682132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28616046905518</t>
   </si>
   <si>
     <t xml:space="preserve">6.36748218536377</t>
@@ -2354,88 +2354,88 @@
     <t xml:space="preserve">7.30267953872681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35960626602173</t>
+    <t xml:space="preserve">7.5466456413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35960531234741</t>
   </si>
   <si>
     <t xml:space="preserve">7.23762273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22949075698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12377309799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07498025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17256450653076</t>
+    <t xml:space="preserve">7.22949171066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12377262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07497930526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17256593704224</t>
   </si>
   <si>
     <t xml:space="preserve">7.21322631835938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0668478012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9611291885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92046880722046</t>
+    <t xml:space="preserve">7.06684732437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96113061904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92046976089478</t>
   </si>
   <si>
     <t xml:space="preserve">7.27828407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92860078811646</t>
+    <t xml:space="preserve">6.9286003112793</t>
   </si>
   <si>
     <t xml:space="preserve">6.99365901947021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10750722885132</t>
+    <t xml:space="preserve">7.10750865936279</t>
   </si>
   <si>
     <t xml:space="preserve">7.29454803466797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45719146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26202011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18069791793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31081295013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47345542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48972034454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70115756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70928812026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40839910507202</t>
+    <t xml:space="preserve">7.45719051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26201915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18069839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31081199645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47345590591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4897198677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70115661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70928764343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44905948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40839719772339</t>
   </si>
   <si>
     <t xml:space="preserve">6.82288312911987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.879807472229</t>
+    <t xml:space="preserve">6.87980842590332</t>
   </si>
   <si>
     <t xml:space="preserve">6.86354351043701</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">7.09124422073364</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38400077819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53851413726807</t>
+    <t xml:space="preserve">7.38400173187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53851318359375</t>
   </si>
   <si>
     <t xml:space="preserve">7.60357046127319</t>
@@ -2456,97 +2456,97 @@
     <t xml:space="preserve">7.57104206085205</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247785568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9939136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94512128829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86379957199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82313776016235</t>
+    <t xml:space="preserve">7.78247737884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99391412734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94512176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86379909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82313871383667</t>
   </si>
   <si>
     <t xml:space="preserve">7.90446043014526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79874277114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83127117156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72555208206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57917356491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61983489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44092702865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56290912628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84753513336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2622766494751</t>
+    <t xml:space="preserve">7.79874324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83127069473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72555303573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57917308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61983442306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44092607498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5629096031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84753561019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26227474212646</t>
   </si>
   <si>
     <t xml:space="preserve">8.13216114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1484260559082</t>
+    <t xml:space="preserve">8.14842510223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.0508394241333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11589622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87193298339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5547776222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69302415847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75808238983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37612533569336</t>
+    <t xml:space="preserve">8.11589527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87193202972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55477714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69302463531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75808143615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37612628936768</t>
   </si>
   <si>
     <t xml:space="preserve">8.24601173400879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21348285675049</t>
+    <t xml:space="preserve">8.21348190307617</t>
   </si>
   <si>
     <t xml:space="preserve">8.05897045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79060935974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07523536682129</t>
+    <t xml:space="preserve">7.79061031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07523632049561</t>
   </si>
   <si>
     <t xml:space="preserve">8.12402820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98578214645386</t>
+    <t xml:space="preserve">7.98578262329102</t>
   </si>
   <si>
     <t xml:space="preserve">7.92072439193726</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">8.01830959320068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06710243225098</t>
+    <t xml:space="preserve">8.06710338592529</t>
   </si>
   <si>
     <t xml:space="preserve">7.9532527923584</t>
@@ -2564,31 +2564,31 @@
     <t xml:space="preserve">7.71742010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73368549346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92885637283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08336734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57129764556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65261840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45744705200195</t>
+    <t xml:space="preserve">7.73368406295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92885732650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0833683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57129669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65261936187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45744800567627</t>
   </si>
   <si>
     <t xml:space="preserve">8.44118309020996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53991031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37536525726318</t>
+    <t xml:space="preserve">8.53990840911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37536430358887</t>
   </si>
   <si>
     <t xml:space="preserve">8.30954647064209</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">9.39554691314697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46136474609375</t>
+    <t xml:space="preserve">9.46136379241943</t>
   </si>
   <si>
     <t xml:space="preserve">9.52718257904053</t>
@@ -2624,31 +2624,31 @@
     <t xml:space="preserve">9.5436372756958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32972717285156</t>
+    <t xml:space="preserve">9.32972812652588</t>
   </si>
   <si>
     <t xml:space="preserve">9.36263656616211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37909030914307</t>
+    <t xml:space="preserve">9.3790922164917</t>
   </si>
   <si>
     <t xml:space="preserve">9.2145471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16518306732178</t>
+    <t xml:space="preserve">9.16518402099609</t>
   </si>
   <si>
     <t xml:space="preserve">9.01709079742432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88545608520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03354644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11581897735596</t>
+    <t xml:space="preserve">8.88545513153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03354549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11581802368164</t>
   </si>
   <si>
     <t xml:space="preserve">8.81963729858398</t>
@@ -2660,37 +2660,37 @@
     <t xml:space="preserve">8.83609294891357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95127487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90190982818604</t>
+    <t xml:space="preserve">8.95127391815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90190887451172</t>
   </si>
   <si>
     <t xml:space="preserve">8.72091007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42472743988037</t>
+    <t xml:space="preserve">8.42472839355469</t>
   </si>
   <si>
     <t xml:space="preserve">8.57281970977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58927440643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63863658905029</t>
+    <t xml:space="preserve">8.58927345275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63863754272461</t>
   </si>
   <si>
     <t xml:space="preserve">8.60572814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40827369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24372863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2930908203125</t>
+    <t xml:space="preserve">8.40827465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.243727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29309177398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.34245586395264</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">8.85254669189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68800163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80318355560303</t>
+    <t xml:space="preserve">8.68800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80318260192871</t>
   </si>
   <si>
     <t xml:space="preserve">9.08291053771973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.099365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18163871765137</t>
+    <t xml:space="preserve">9.09936428070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18163776397705</t>
   </si>
   <si>
     <t xml:space="preserve">8.70445537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75382041931152</t>
+    <t xml:space="preserve">8.75381946563721</t>
   </si>
   <si>
     <t xml:space="preserve">8.65509223937988</t>
@@ -2729,10 +2729,10 @@
     <t xml:space="preserve">8.62218284606934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55636310577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96772861480713</t>
+    <t xml:space="preserve">8.55636405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96772766113281</t>
   </si>
   <si>
     <t xml:space="preserve">8.98418235778809</t>
@@ -2744,67 +2744,67 @@
     <t xml:space="preserve">8.27663803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18613719940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26018238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14500045776367</t>
+    <t xml:space="preserve">8.18613815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2601842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14500141143799</t>
   </si>
   <si>
     <t xml:space="preserve">7.98045539855957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99690961837769</t>
+    <t xml:space="preserve">7.99690914154053</t>
   </si>
   <si>
     <t xml:space="preserve">8.20259189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94754457473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93931770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03804683685303</t>
+    <t xml:space="preserve">7.94754552841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93931818008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03804588317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.12854671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98868227005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13677406311035</t>
+    <t xml:space="preserve">7.98868274688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13677501678467</t>
   </si>
   <si>
     <t xml:space="preserve">7.89818286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95577383041382</t>
+    <t xml:space="preserve">7.9557728767395</t>
   </si>
   <si>
     <t xml:space="preserve">8.01336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83236360549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97222805023193</t>
+    <t xml:space="preserve">7.8323655128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97222900390625</t>
   </si>
   <si>
     <t xml:space="preserve">8.08740997314453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10386562347412</t>
+    <t xml:space="preserve">8.1038646697998</t>
   </si>
   <si>
     <t xml:space="preserve">8.16968154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0500020980835</t>
+    <t xml:space="preserve">9.05000114440918</t>
   </si>
   <si>
     <t xml:space="preserve">9.00063800811768</t>
@@ -2816,40 +2816,40 @@
     <t xml:space="preserve">7.88995552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87350034713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60199975967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59377241134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15772819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21531915664673</t>
+    <t xml:space="preserve">7.87349987030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56909132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60200071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59377336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15772867202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21531867980957</t>
   </si>
   <si>
     <t xml:space="preserve">7.12481832504272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3963189125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30581855773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24000120162964</t>
+    <t xml:space="preserve">7.39631843566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30581951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2400016784668</t>
   </si>
   <si>
     <t xml:space="preserve">7.69250106811523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55263757705688</t>
+    <t xml:space="preserve">7.55263710021973</t>
   </si>
   <si>
     <t xml:space="preserve">7.52795505523682</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">7.33872747421265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46213674545288</t>
+    <t xml:space="preserve">7.46213722229004</t>
   </si>
   <si>
     <t xml:space="preserve">7.4045467376709</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">7.65959167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70895481109619</t>
+    <t xml:space="preserve">7.70895528793335</t>
   </si>
   <si>
     <t xml:space="preserve">7.79945468902588</t>
@@ -2885,43 +2885,43 @@
     <t xml:space="preserve">8.12031841278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07918262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79122924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85704612731934</t>
+    <t xml:space="preserve">8.07918167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79122829437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85704660415649</t>
   </si>
   <si>
     <t xml:space="preserve">8.02159214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91463708877563</t>
+    <t xml:space="preserve">7.91463661193848</t>
   </si>
   <si>
     <t xml:space="preserve">7.81590938568115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78300094604492</t>
+    <t xml:space="preserve">7.78299999237061</t>
   </si>
   <si>
     <t xml:space="preserve">7.70072746276855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67604684829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42922735214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29759120941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66781997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48681831359863</t>
+    <t xml:space="preserve">7.6760458946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42922782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29759073257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66781854629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48681926727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.61022758483887</t>
@@ -2933,31 +2933,31 @@
     <t xml:space="preserve">7.5115008354187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41277408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76654577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65136432647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7336368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82413625717163</t>
+    <t xml:space="preserve">7.41277456283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76654624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65136480331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73363637924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82413721084595</t>
   </si>
   <si>
     <t xml:space="preserve">7.71718263626099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58554601669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47036361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9026837348938</t>
+    <t xml:space="preserve">7.58554649353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47036457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90268325805664</t>
   </si>
   <si>
     <t xml:space="preserve">6.72168254852295</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">7.10836505889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28936386108398</t>
+    <t xml:space="preserve">7.28936433792114</t>
   </si>
   <si>
     <t xml:space="preserve">7.49504613876343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50327444076538</t>
+    <t xml:space="preserve">7.50327348709106</t>
   </si>
   <si>
     <t xml:space="preserve">7.37163734436035</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">8.15322780609131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02981948852539</t>
+    <t xml:space="preserve">8.02981853485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.09563732147217</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">8.07095527648926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75009250640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80768203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84059143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8488187789917</t>
+    <t xml:space="preserve">7.75009202957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80768299102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84059190750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84882020950317</t>
   </si>
   <si>
     <t xml:space="preserve">7.54441022872925</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">7.72540998458862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31404590606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77477312088013</t>
+    <t xml:space="preserve">7.31404638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77477359771729</t>
   </si>
   <si>
     <t xml:space="preserve">7.7395977973938</t>
@@ -3053,19 +3053,19 @@
     <t xml:space="preserve">7.81555986404419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79023694992065</t>
+    <t xml:space="preserve">7.79023790359497</t>
   </si>
   <si>
     <t xml:space="preserve">7.64675664901733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35979175567627</t>
+    <t xml:space="preserve">7.35979127883911</t>
   </si>
   <si>
     <t xml:space="preserve">7.13190746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25007057189941</t>
+    <t xml:space="preserve">7.25007104873657</t>
   </si>
   <si>
     <t xml:space="preserve">7.05594682693481</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">7.03062677383423</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03906631469727</t>
+    <t xml:space="preserve">7.03906679153442</t>
   </si>
   <si>
     <t xml:space="preserve">7.11502838134766</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">7.17410850524902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09814691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01374673843384</t>
+    <t xml:space="preserve">7.09814739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.013747215271</t>
   </si>
   <si>
     <t xml:space="preserve">6.9209041595459</t>
@@ -3110,19 +3110,19 @@
     <t xml:space="preserve">6.76898288726807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86182403564453</t>
+    <t xml:space="preserve">6.86182451248169</t>
   </si>
   <si>
     <t xml:space="preserve">6.98842620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93778610229492</t>
+    <t xml:space="preserve">6.93778562545776</t>
   </si>
   <si>
     <t xml:space="preserve">6.92934513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83650350570679</t>
+    <t xml:space="preserve">6.83650398254395</t>
   </si>
   <si>
     <t xml:space="preserve">6.89558458328247</t>
@@ -3131,25 +3131,25 @@
     <t xml:space="preserve">6.9124641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76054286956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68458080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69302177429199</t>
+    <t xml:space="preserve">6.76054239273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68458127975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69302129745483</t>
   </si>
   <si>
     <t xml:space="preserve">6.9462251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14034843444824</t>
+    <t xml:space="preserve">7.14034795761108</t>
   </si>
   <si>
     <t xml:space="preserve">7.02218627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96310567855835</t>
+    <t xml:space="preserve">6.96310520172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.06438732147217</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">6.56641912460327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38073682785034</t>
+    <t xml:space="preserve">6.3807373046875</t>
   </si>
   <si>
     <t xml:space="preserve">6.46513795852661</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">6.220374584198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24569463729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16129398345947</t>
+    <t xml:space="preserve">6.24569511413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16129350662231</t>
   </si>
   <si>
     <t xml:space="preserve">6.33009624481201</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">6.04313182830811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08533239364624</t>
+    <t xml:space="preserve">6.08533191680908</t>
   </si>
   <si>
     <t xml:space="preserve">6.06845235824585</t>
@@ -3227,16 +3227,16 @@
     <t xml:space="preserve">5.88276863098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95873022079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00093078613281</t>
+    <t xml:space="preserve">5.95873069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00093126296997</t>
   </si>
   <si>
     <t xml:space="preserve">5.98405122756958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92496967315674</t>
+    <t xml:space="preserve">5.92496919631958</t>
   </si>
   <si>
     <t xml:space="preserve">6.03469181060791</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">5.59580516815186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66332578659058</t>
+    <t xml:space="preserve">5.66332530975342</t>
   </si>
   <si>
     <t xml:space="preserve">5.67176580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51140403747559</t>
+    <t xml:space="preserve">5.51140356063843</t>
   </si>
   <si>
     <t xml:space="preserve">5.49452352523804</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">5.57892465591431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64644527435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5873646736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82368803024292</t>
+    <t xml:space="preserve">5.64644575119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58736515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82368850708008</t>
   </si>
   <si>
     <t xml:space="preserve">6.07689189910889</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">6.00937128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90808963775635</t>
+    <t xml:space="preserve">5.90808916091919</t>
   </si>
   <si>
     <t xml:space="preserve">5.85744905471802</t>
@@ -3317,22 +3317,22 @@
     <t xml:space="preserve">5.72240686416626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75616693496704</t>
+    <t xml:space="preserve">5.7561674118042</t>
   </si>
   <si>
     <t xml:space="preserve">5.77304744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.747727394104</t>
+    <t xml:space="preserve">5.74772691726685</t>
   </si>
   <si>
     <t xml:space="preserve">5.8912091255188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76460695266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95029020309448</t>
+    <t xml:space="preserve">5.76460742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95028972625732</t>
   </si>
   <si>
     <t xml:space="preserve">5.81524753570557</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">5.84900856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7308464050293</t>
+    <t xml:space="preserve">5.73084592819214</t>
   </si>
   <si>
     <t xml:space="preserve">5.80680847167969</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">5.68020582199097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78148698806763</t>
+    <t xml:space="preserve">5.78148746490479</t>
   </si>
   <si>
     <t xml:space="preserve">6.01781129837036</t>
@@ -3383,10 +3383,10 @@
     <t xml:space="preserve">6.23725414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27945566177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20349359512329</t>
+    <t xml:space="preserve">6.27945518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20349407196045</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001138687134</t>
@@ -3407,16 +3407,16 @@
     <t xml:space="preserve">6.43137788772583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33853673934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3469762802124</t>
+    <t xml:space="preserve">6.33853626251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">6.32165575027466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30477571487427</t>
+    <t xml:space="preserve">6.30477523803711</t>
   </si>
   <si>
     <t xml:space="preserve">6.37229681015015</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">6.31321573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97561025619507</t>
+    <t xml:space="preserve">5.97561073303223</t>
   </si>
   <si>
     <t xml:space="preserve">5.84056806564331</t>
@@ -3434,10 +3434,10 @@
     <t xml:space="preserve">5.83212852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58330011367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10221242904663</t>
+    <t xml:space="preserve">6.58329963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10221195220947</t>
   </si>
   <si>
     <t xml:space="preserve">6.09377241134644</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">6.47591114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27863168716431</t>
+    <t xml:space="preserve">6.27863216400146</t>
   </si>
   <si>
     <t xml:space="preserve">6.57026195526123</t>
@@ -3476,34 +3476,34 @@
     <t xml:space="preserve">6.88762426376343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87047052383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80185127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73323154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70749998092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69034576416016</t>
+    <t xml:space="preserve">6.87047004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80185079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73323202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70750045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.690345287323</t>
   </si>
   <si>
     <t xml:space="preserve">6.64745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61314821243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81042814254761</t>
+    <t xml:space="preserve">6.61314868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81042766571045</t>
   </si>
   <si>
     <t xml:space="preserve">6.86189222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418098449707</t>
+    <t xml:space="preserve">6.74180936813354</t>
   </si>
   <si>
     <t xml:space="preserve">6.83616018295288</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">6.79327344894409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72465467453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6989221572876</t>
+    <t xml:space="preserve">6.72465515136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69892263412476</t>
   </si>
   <si>
     <t xml:space="preserve">6.71607732772827</t>
@@ -3524,19 +3524,19 @@
     <t xml:space="preserve">6.63888072967529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62172651290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38156032562256</t>
+    <t xml:space="preserve">6.62172603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3815598487854</t>
   </si>
   <si>
     <t xml:space="preserve">6.39871501922607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40729188919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52737522125244</t>
+    <t xml:space="preserve">6.40729141235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5273756980896</t>
   </si>
   <si>
     <t xml:space="preserve">6.5359525680542</t>
@@ -3545,19 +3545,19 @@
     <t xml:space="preserve">6.5959939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63030338287354</t>
+    <t xml:space="preserve">6.63030290603638</t>
   </si>
   <si>
     <t xml:space="preserve">6.57883977890015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48448801040649</t>
+    <t xml:space="preserve">6.48448848724365</t>
   </si>
   <si>
     <t xml:space="preserve">6.65603590011597</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76754093170166</t>
+    <t xml:space="preserve">6.76754140853882</t>
   </si>
   <si>
     <t xml:space="preserve">6.85331439971924</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">6.93051147460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94766616821289</t>
+    <t xml:space="preserve">6.94766664505005</t>
   </si>
   <si>
     <t xml:space="preserve">6.87904739379883</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">6.99913024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92193412780762</t>
+    <t xml:space="preserve">6.92193365097046</t>
   </si>
   <si>
     <t xml:space="preserve">6.91335678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12779092788696</t>
+    <t xml:space="preserve">7.12779140472412</t>
   </si>
   <si>
     <t xml:space="preserve">7.24787330627441</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">7.17925500869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07632637023926</t>
+    <t xml:space="preserve">7.0763258934021</t>
   </si>
   <si>
     <t xml:space="preserve">7.09348154067993</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">7.14494562149048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15352249145508</t>
+    <t xml:space="preserve">7.15352296829224</t>
   </si>
   <si>
     <t xml:space="preserve">7.01628589630127</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">6.42444658279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26147747039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20143556594849</t>
+    <t xml:space="preserve">6.26147699356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20143508911133</t>
   </si>
   <si>
     <t xml:space="preserve">6.3215184211731</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">6.21858978271484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34725046157837</t>
+    <t xml:space="preserve">6.34725093841553</t>
   </si>
   <si>
     <t xml:space="preserve">6.29578638076782</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">6.03846502304077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0041561126709</t>
+    <t xml:space="preserve">6.00415563583374</t>
   </si>
   <si>
     <t xml:space="preserve">5.89264965057373</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">6.41586923599243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56168508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68176794052124</t>
+    <t xml:space="preserve">6.56168460845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68176746368408</t>
   </si>
   <si>
     <t xml:space="preserve">7.05917167663574</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">7.23929643630981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29933834075928</t>
+    <t xml:space="preserve">7.29933786392212</t>
   </si>
   <si>
     <t xml:space="preserve">7.37653541564941</t>
@@ -3749,67 +3749,67 @@
     <t xml:space="preserve">7.3851113319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47946310043335</t>
+    <t xml:space="preserve">7.47946262359619</t>
   </si>
   <si>
     <t xml:space="preserve">7.46230840682983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50519466400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49661731719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5995454788208</t>
+    <t xml:space="preserve">7.50519514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49661779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59954595565796</t>
   </si>
   <si>
     <t xml:space="preserve">7.53092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48803949356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40226650238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51377248764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35937976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34222459793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66816425323486</t>
+    <t xml:space="preserve">7.48803901672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40226602554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51377201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35938024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34222507476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66816377639771</t>
   </si>
   <si>
     <t xml:space="preserve">7.8139796257019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68531942367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67674207687378</t>
+    <t xml:space="preserve">7.6853199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67674255371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.60812282562256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69389772415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90833139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07130146026611</t>
+    <t xml:space="preserve">7.69389677047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90833234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0713005065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.29431247711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23427104949951</t>
+    <t xml:space="preserve">8.2342700958252</t>
   </si>
   <si>
     <t xml:space="preserve">8.37150859832764</t>
@@ -69850,7 +69850,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494444444</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>401719</v>
@@ -69871,6 +69871,32 @@
         <v>1489</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6493402778</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>197328</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>9.82999992370605</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>9.97999954223633</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>9.92000007629395</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1488</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13600921630859</t>
+    <t xml:space="preserve">8.13601112365723</t>
   </si>
   <si>
     <t xml:space="preserve">FILA.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">8.08278465270996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05997180938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06757640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12840557098389</t>
+    <t xml:space="preserve">8.05997371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06757736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1284065246582</t>
   </si>
   <si>
     <t xml:space="preserve">8.11319923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90029430389404</t>
+    <t xml:space="preserve">7.9002947807312</t>
   </si>
   <si>
     <t xml:space="preserve">7.87748146057129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94591522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52771043777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48969030380249</t>
+    <t xml:space="preserve">7.9459171295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52771234512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48969125747681</t>
   </si>
   <si>
     <t xml:space="preserve">7.95352029800415</t>
@@ -80,22 +80,22 @@
     <t xml:space="preserve">7.79384136199951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67978525161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62655973434448</t>
+    <t xml:space="preserve">7.67978382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62655735015869</t>
   </si>
   <si>
     <t xml:space="preserve">7.71020078659058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89269256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82425546646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60374784469604</t>
+    <t xml:space="preserve">7.89269065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82425594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60374879837036</t>
   </si>
   <si>
     <t xml:space="preserve">7.69499254226685</t>
@@ -107,37 +107,37 @@
     <t xml:space="preserve">7.84706783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91550207138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01434993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20444393157959</t>
+    <t xml:space="preserve">7.9155011177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0143518447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20444488525391</t>
   </si>
   <si>
     <t xml:space="preserve">8.10559558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24246215820312</t>
+    <t xml:space="preserve">8.24246120452881</t>
   </si>
   <si>
     <t xml:space="preserve">8.25006580352783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30329322814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15121936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23485851287842</t>
+    <t xml:space="preserve">8.30329132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15121746063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2348575592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.35651874542236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28808498382568</t>
+    <t xml:space="preserve">8.2880859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.21965217590332</t>
@@ -149,34 +149,34 @@
     <t xml:space="preserve">8.29568862915039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38693332672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14361190795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18923664093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40974617004395</t>
+    <t xml:space="preserve">8.38693428039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14361476898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18923568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40974521636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.40213966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37932968139648</t>
+    <t xml:space="preserve">8.37932872772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.51619625091553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75191497802734</t>
+    <t xml:space="preserve">8.75191307067871</t>
   </si>
   <si>
     <t xml:space="preserve">8.82034778594971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80514049530029</t>
+    <t xml:space="preserve">8.80513954162598</t>
   </si>
   <si>
     <t xml:space="preserve">8.8279504776001</t>
@@ -188,73 +188,73 @@
     <t xml:space="preserve">9.09408283233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98002624511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12449741363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19293117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78993225097656</t>
+    <t xml:space="preserve">8.98002529144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12449836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19293022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78993129730225</t>
   </si>
   <si>
     <t xml:space="preserve">9.11689281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17772388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03325080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08647727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20053386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34500503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13970565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6111364364624</t>
+    <t xml:space="preserve">9.1777229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03325176239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08647918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20053482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34500694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13970470428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61113834381104</t>
   </si>
   <si>
     <t xml:space="preserve">9.67196750640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65676021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80883312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90008163452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7708158493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73252868652344</t>
+    <t xml:space="preserve">9.65675830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80883502960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90008068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77081489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73252773284912</t>
   </si>
   <si>
     <t xml:space="preserve">9.47217750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49515151977539</t>
+    <t xml:space="preserve">9.49515056610107</t>
   </si>
   <si>
     <t xml:space="preserve">9.5717248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7018985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77847290039062</t>
+    <t xml:space="preserve">9.70190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77847385406494</t>
   </si>
   <si>
     <t xml:space="preserve">9.67892837524414</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">9.69424247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61001300811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64829921722412</t>
+    <t xml:space="preserve">9.61001205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64830017089844</t>
   </si>
   <si>
     <t xml:space="preserve">9.51046466827393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41857624053955</t>
+    <t xml:space="preserve">9.41857528686523</t>
   </si>
   <si>
     <t xml:space="preserve">9.26542854309082</t>
@@ -284,61 +284,61 @@
     <t xml:space="preserve">9.18885517120361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11228275299072</t>
+    <t xml:space="preserve">9.11228179931641</t>
   </si>
   <si>
     <t xml:space="preserve">9.34200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63298320770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20416927337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21182727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30371570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72487163543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34966087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38794803619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59469699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53343677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75550079345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76315975189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62532711029053</t>
+    <t xml:space="preserve">9.63298225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20417022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21182632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30371475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7248706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34965896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38794708251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59469795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53343772888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75549983978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316070556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62532806396484</t>
   </si>
   <si>
     <t xml:space="preserve">9.45686435699463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78613090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74784374237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7172155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68658542633057</t>
+    <t xml:space="preserve">9.78613185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74784183502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71721458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68658447265625</t>
   </si>
   <si>
     <t xml:space="preserve">9.6712703704834</t>
@@ -350,133 +350,133 @@
     <t xml:space="preserve">9.56406688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57938098907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80910301208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70955657958984</t>
+    <t xml:space="preserve">9.57938289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80910205841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70955753326416</t>
   </si>
   <si>
     <t xml:space="preserve">9.66361236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74018669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51812171936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4492073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39560604095459</t>
+    <t xml:space="preserve">9.7401876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51812267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44920539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39560413360596</t>
   </si>
   <si>
     <t xml:space="preserve">9.35731792449951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54109477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41091918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80144500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55640888214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79378890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86270523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90865039825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9392786026001</t>
+    <t xml:space="preserve">9.54109573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41091823577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8014440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55641078948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79378795623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86270427703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90864944458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93927764892578</t>
   </si>
   <si>
     <t xml:space="preserve">9.92396450042725</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2226009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838621139526</t>
+    <t xml:space="preserve">10.2225999832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2685461044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2838611602783</t>
   </si>
   <si>
     <t xml:space="preserve">10.3910636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4829502105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.582498550415</t>
+    <t xml:space="preserve">10.4829521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5824995040894</t>
   </si>
   <si>
     <t xml:space="preserve">10.7050170898438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6437568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7203321456909</t>
+    <t xml:space="preserve">10.6437578201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7203302383423</t>
   </si>
   <si>
     <t xml:space="preserve">10.3374614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4523239135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1843147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0771102905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0694541931152</t>
+    <t xml:space="preserve">10.4523220062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1843156814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.077112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0694551467896</t>
   </si>
   <si>
     <t xml:space="preserve">10.2379159927368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0617961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95459270477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87036323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8244161605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0388231277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98522186279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85504913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93161964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94693660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89333438873291</t>
+    <t xml:space="preserve">10.0617971420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95459461212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.870361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82441806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0388240814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98522281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85504817962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93162059783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94693565368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89333343505859</t>
   </si>
   <si>
     <t xml:space="preserve">10.0541391372681</t>
@@ -485,37 +485,37 @@
     <t xml:space="preserve">9.97756576538086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567638397217</t>
+    <t xml:space="preserve">9.88567733764648</t>
   </si>
   <si>
     <t xml:space="preserve">10.1613435745239</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5288963317871</t>
+    <t xml:space="preserve">10.5288982391357</t>
   </si>
   <si>
     <t xml:space="preserve">10.5671834945679</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4906101226807</t>
+    <t xml:space="preserve">10.4906091690063</t>
   </si>
   <si>
     <t xml:space="preserve">10.2991743087769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2608871459961</t>
+    <t xml:space="preserve">10.2608880996704</t>
   </si>
   <si>
     <t xml:space="preserve">10.4063787460327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4140367507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2455739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153974533081</t>
+    <t xml:space="preserve">10.4140357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2455730438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153984069824</t>
   </si>
   <si>
     <t xml:space="preserve">10.3221473693848</t>
@@ -524,22 +524,22 @@
     <t xml:space="preserve">10.2915182113647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.398720741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4982681274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4293518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6054706573486</t>
+    <t xml:space="preserve">10.3987216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4982671737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4293479919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6054716110229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5901556015015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3757476806641</t>
+    <t xml:space="preserve">10.3757495880127</t>
   </si>
   <si>
     <t xml:space="preserve">10.253231048584</t>
@@ -548,55 +548,55 @@
     <t xml:space="preserve">10.1460266113281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3068323135376</t>
+    <t xml:space="preserve">10.3068332672119</t>
   </si>
   <si>
     <t xml:space="preserve">10.4752950668335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5212392807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4446640014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3298034667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1230564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4216938018799</t>
+    <t xml:space="preserve">10.521240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4446678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3298053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1230573654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4216928482056</t>
   </si>
   <si>
     <t xml:space="preserve">10.781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2027454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1797742843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.133828163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3329229354858</t>
+    <t xml:space="preserve">11.2027463912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1797733306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1338291168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3329210281372</t>
   </si>
   <si>
     <t xml:space="preserve">11.2946348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.409496307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2793188095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3788661956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6775026321411</t>
+    <t xml:space="preserve">11.4094944000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2793197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3788652420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6775035858154</t>
   </si>
   <si>
     <t xml:space="preserve">11.7081346511841</t>
@@ -605,43 +605,43 @@
     <t xml:space="preserve">11.8383083343506</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851596832275</t>
+    <t xml:space="preserve">11.6851615905762</t>
   </si>
   <si>
     <t xml:space="preserve">11.6468753814697</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5473289489746</t>
+    <t xml:space="preserve">11.5473299026489</t>
   </si>
   <si>
     <t xml:space="preserve">11.401837348938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.524356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6392154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157897949219</t>
+    <t xml:space="preserve">11.5243558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.639217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157888412476</t>
   </si>
   <si>
     <t xml:space="preserve">11.7923641204834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.228835105896</t>
+    <t xml:space="preserve">12.2288360595703</t>
   </si>
   <si>
     <t xml:space="preserve">12.2441492080688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3513536453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.404953956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5198163986206</t>
+    <t xml:space="preserve">12.3513517379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4049549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5198154449463</t>
   </si>
   <si>
     <t xml:space="preserve">13.254921913147</t>
@@ -650,88 +650,88 @@
     <t xml:space="preserve">13.5918483734131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6301355361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7832832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2472667694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8184537887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6346759796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7112503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0252027511597</t>
+    <t xml:space="preserve">13.6301374435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7832822799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2472658157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.818452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6346769332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7112493515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.025200843811</t>
   </si>
   <si>
     <t xml:space="preserve">12.8643980026245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2396087646484</t>
+    <t xml:space="preserve">13.2396068572998</t>
   </si>
   <si>
     <t xml:space="preserve">13.2166376113892</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2089786529541</t>
+    <t xml:space="preserve">13.2089796066284</t>
   </si>
   <si>
     <t xml:space="preserve">13.7373390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3621273040771</t>
+    <t xml:space="preserve">13.3621253967285</t>
   </si>
   <si>
     <t xml:space="preserve">13.4004144668579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7143669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5688762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5152750015259</t>
+    <t xml:space="preserve">13.7143659591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5688772201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5152759552002</t>
   </si>
   <si>
     <t xml:space="preserve">13.6684217453003</t>
   </si>
   <si>
-    <t xml:space="preserve">13.614821434021</t>
+    <t xml:space="preserve">13.6148195266724</t>
   </si>
   <si>
     <t xml:space="preserve">14.319299697876</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3958749771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3882169723511</t>
+    <t xml:space="preserve">14.3958740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3882179260254</t>
   </si>
   <si>
     <t xml:space="preserve">14.4341611862183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5490198135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6791982650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2810144424438</t>
+    <t xml:space="preserve">14.5490217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6791954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2810125350952</t>
   </si>
   <si>
     <t xml:space="preserve">14.3269567489624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4265050888062</t>
+    <t xml:space="preserve">14.4265022277832</t>
   </si>
   <si>
     <t xml:space="preserve">14.3422708511353</t>
@@ -740,58 +740,58 @@
     <t xml:space="preserve">14.5337066650391</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2733564376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0359783172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512914657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9897308349609</t>
+    <t xml:space="preserve">14.2733545303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0359754562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9897289276123</t>
   </si>
   <si>
     <t xml:space="preserve">14.1282415390015</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3975734710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4976110458374</t>
+    <t xml:space="preserve">14.3975706100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4976072311401</t>
   </si>
   <si>
     <t xml:space="preserve">14.0820713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1436328887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590599060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5745611190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5976428985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6592025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3437070846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3667907714844</t>
+    <t xml:space="preserve">14.1436338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590579986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5745601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5976448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6592082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3437051773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3667917251587</t>
   </si>
   <si>
     <t xml:space="preserve">14.3514003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2513656616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0435943603516</t>
+    <t xml:space="preserve">14.2513647079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0435962677002</t>
   </si>
   <si>
     <t xml:space="preserve">14.5437793731689</t>
@@ -800,40 +800,40 @@
     <t xml:space="preserve">14.5822525024414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3129253387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5360841751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4899129867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6976823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6207284927368</t>
+    <t xml:space="preserve">14.3129272460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5360822677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4899120330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6976804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6207304000854</t>
   </si>
   <si>
     <t xml:space="preserve">14.4591341018677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7742671966553</t>
+    <t xml:space="preserve">13.774266242981</t>
   </si>
   <si>
     <t xml:space="preserve">14.0974626541138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8896951675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9127798080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8973903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2436714172363</t>
+    <t xml:space="preserve">13.8896942138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9127788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.897388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.243670463562</t>
   </si>
   <si>
     <t xml:space="preserve">14.3898763656616</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">14.4129610061646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3821811676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4437417984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5591707229614</t>
+    <t xml:space="preserve">14.3821821212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4437427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5591697692871</t>
   </si>
   <si>
     <t xml:space="preserve">14.736156463623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5053014755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5283880233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.428352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514755249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4360475540161</t>
+    <t xml:space="preserve">14.5053033828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5283899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283533096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.551474571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4360494613647</t>
   </si>
   <si>
     <t xml:space="preserve">14.2744493484497</t>
@@ -875,85 +875,85 @@
     <t xml:space="preserve">14.051290512085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.966646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6742315292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1205463409424</t>
+    <t xml:space="preserve">13.9666452407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6742286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.120548248291</t>
   </si>
   <si>
     <t xml:space="preserve">14.1590223312378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1513271331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8512172698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9743423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1744136810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.205192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3052310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.359094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2975358963013</t>
+    <t xml:space="preserve">14.151328086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8512182235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9743404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.174412727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2051944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0051212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305230140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3590965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.297534942627</t>
   </si>
   <si>
     <t xml:space="preserve">14.4206581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3283176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.336012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3744869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.23597240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5129985809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2205848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1974964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3902406692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2440366744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.25172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1670837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1055221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978607177734</t>
+    <t xml:space="preserve">14.3283166885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3360109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3744888305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2359752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.512996673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2205829620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1974992752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3902425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2440338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2517337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.167085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1055192947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1978626251221</t>
   </si>
   <si>
     <t xml:space="preserve">15.0670471191406</t>
@@ -962,91 +962,91 @@
     <t xml:space="preserve">14.9208402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9285354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8823652267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5206918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2898387908936</t>
+    <t xml:space="preserve">14.9285364151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.882363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5206928253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2898416519165</t>
   </si>
   <si>
     <t xml:space="preserve">14.7515459060669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.643816947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5668621063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6515121459961</t>
+    <t xml:space="preserve">14.6438159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5668640136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6515111923218</t>
   </si>
   <si>
     <t xml:space="preserve">14.7438516616821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7900218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8361949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7746334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6361227035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4514350891113</t>
+    <t xml:space="preserve">14.7900228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8361930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7746324539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.636118888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4514389038086</t>
   </si>
   <si>
     <t xml:space="preserve">14.4668283462524</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5899496078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8131084442139</t>
+    <t xml:space="preserve">14.5899486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8131103515625</t>
   </si>
   <si>
     <t xml:space="preserve">14.8515844345093</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1440019607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2902069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3440704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5441455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5826187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5056686401367</t>
+    <t xml:space="preserve">15.1439990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2902059555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3440723419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5441417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5826206207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5056705474854</t>
   </si>
   <si>
     <t xml:space="preserve">15.4287185668945</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2209510803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9747066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1286096572876</t>
+    <t xml:space="preserve">15.2209501266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9747076034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1286087036133</t>
   </si>
   <si>
     <t xml:space="preserve">15.9289026260376</t>
@@ -1055,82 +1055,82 @@
     <t xml:space="preserve">15.7365226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8134727478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2367057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0828037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6210975646973</t>
+    <t xml:space="preserve">15.8134746551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.236701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0828056335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6210956573486</t>
   </si>
   <si>
     <t xml:space="preserve">16.0058517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1212768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6980457305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7749996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671194076538</t>
+    <t xml:space="preserve">16.1212787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6980476379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7749977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671222686768</t>
   </si>
   <si>
     <t xml:space="preserve">14.9131460189819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8977546691895</t>
+    <t xml:space="preserve">14.8977537155151</t>
   </si>
   <si>
     <t xml:space="preserve">14.8054141998291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1747779846191</t>
+    <t xml:space="preserve">15.1747789382935</t>
   </si>
   <si>
     <t xml:space="preserve">15.0208759307861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0516576766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8208055496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0362682342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9281702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1128511428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2821435928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4822187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5588045120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7127056121826</t>
+    <t xml:space="preserve">15.0516538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8208017349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0362672805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.928168296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1128520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2821455001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4822177886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5588035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7127075195312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5434131622314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3125619888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2048282623291</t>
+    <t xml:space="preserve">13.3125581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2048292160034</t>
   </si>
   <si>
     <t xml:space="preserve">13.4510736465454</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">13.4356813430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2817792892456</t>
+    <t xml:space="preserve">13.2817802429199</t>
   </si>
   <si>
     <t xml:space="preserve">13.65114402771</t>
@@ -1148,103 +1148,103 @@
     <t xml:space="preserve">13.3895111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1432657241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0663156509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0047540664673</t>
+    <t xml:space="preserve">13.1432676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0663166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0047559738159</t>
   </si>
   <si>
     <t xml:space="preserve">13.0509262084961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2971687316895</t>
+    <t xml:space="preserve">13.2971696853638</t>
   </si>
   <si>
     <t xml:space="preserve">13.2356090545654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6357526779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8666076660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6819248199463</t>
+    <t xml:space="preserve">13.6357545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8666095733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6819257736206</t>
   </si>
   <si>
     <t xml:space="preserve">13.8819971084595</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7130727767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9589490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9512157440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.889349937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7656145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9976186752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.074951171875</t>
+    <t xml:space="preserve">14.7130746841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9589509963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9512147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8893489837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7656135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.997615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0749521255493</t>
   </si>
   <si>
     <t xml:space="preserve">13.5026741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8066596984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3170700073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.146933555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2397365570068</t>
+    <t xml:space="preserve">12.806658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3170690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1469326019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2397346496582</t>
   </si>
   <si>
     <t xml:space="preserve">13.6109428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5336093902588</t>
+    <t xml:space="preserve">13.5336074829102</t>
   </si>
   <si>
     <t xml:space="preserve">13.7192125320435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4253377914429</t>
+    <t xml:space="preserve">13.4253396987915</t>
   </si>
   <si>
     <t xml:space="preserve">13.4562730789185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5645427703857</t>
+    <t xml:space="preserve">13.5645418167114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3789377212524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3016042709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5490770339966</t>
+    <t xml:space="preserve">13.3016033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5490741729736</t>
   </si>
   <si>
     <t xml:space="preserve">13.8274803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8738822937012</t>
+    <t xml:space="preserve">13.8738813400269</t>
   </si>
   <si>
     <t xml:space="preserve">13.6573438644409</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">14.0594835281372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1213512420654</t>
+    <t xml:space="preserve">14.1213521957397</t>
   </si>
   <si>
     <t xml:space="preserve">14.0285520553589</t>
@@ -1268,10 +1268,10 @@
     <t xml:space="preserve">13.9666833877563</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1986904144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.105884552002</t>
+    <t xml:space="preserve">14.1986885070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058864593506</t>
   </si>
   <si>
     <t xml:space="preserve">13.9202823638916</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">14.1677541732788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5389604568481</t>
+    <t xml:space="preserve">14.5389623641968</t>
   </si>
   <si>
     <t xml:space="preserve">14.492561340332</t>
@@ -1289,34 +1289,34 @@
     <t xml:space="preserve">14.4306926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3688259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2914886474609</t>
+    <t xml:space="preserve">14.368824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2914896011353</t>
   </si>
   <si>
     <t xml:space="preserve">14.3533582687378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4616270065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6008281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.781081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3842916488647</t>
+    <t xml:space="preserve">14.4616260528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6008291244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7810802459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3842926025391</t>
   </si>
   <si>
     <t xml:space="preserve">14.5080289840698</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3224220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.569896697998</t>
+    <t xml:space="preserve">14.3224229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5698957443237</t>
   </si>
   <si>
     <t xml:space="preserve">14.306957244873</t>
@@ -1325,43 +1325,43 @@
     <t xml:space="preserve">14.1368198394775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1522884368896</t>
+    <t xml:space="preserve">14.1522874832153</t>
   </si>
   <si>
     <t xml:space="preserve">13.6882772445679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0130834579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4408073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4872074127197</t>
+    <t xml:space="preserve">14.0130844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2088022232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.440806388855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4872064590454</t>
   </si>
   <si>
     <t xml:space="preserve">13.6728115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7037448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5800094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6983919143677</t>
+    <t xml:space="preserve">13.70374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5800075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.698390007019</t>
   </si>
   <si>
     <t xml:space="preserve">12.6829252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5746555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6519908905029</t>
+    <t xml:space="preserve">12.5746545791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6519918441772</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149284362793</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">13.0231981277466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6674566268921</t>
+    <t xml:space="preserve">12.6674575805664</t>
   </si>
   <si>
     <t xml:space="preserve">12.2189140319824</t>
@@ -1379,22 +1379,22 @@
     <t xml:space="preserve">12.5591878890991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2962512969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7394399642944</t>
+    <t xml:space="preserve">12.2962503433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7394390106201</t>
   </si>
   <si>
     <t xml:space="preserve">11.9714431762695</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9405097961426</t>
+    <t xml:space="preserve">11.9405078887939</t>
   </si>
   <si>
     <t xml:space="preserve">12.095178604126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1570463180542</t>
+    <t xml:space="preserve">12.1570472717285</t>
   </si>
   <si>
     <t xml:space="preserve">12.064245223999</t>
@@ -1403,40 +1403,40 @@
     <t xml:space="preserve">11.87864112854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8477087020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6621046066284</t>
+    <t xml:space="preserve">11.8477077484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621036529541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6002359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5074338912964</t>
+    <t xml:space="preserve">11.5074329376221</t>
   </si>
   <si>
     <t xml:space="preserve">11.1362266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4402122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8887548446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2599620819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9351558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.012490272522</t>
+    <t xml:space="preserve">10.4402112960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8887538909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2599630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9351539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0124893188477</t>
   </si>
   <si>
     <t xml:space="preserve">11.3682298660278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4455671310425</t>
+    <t xml:space="preserve">11.4455652236938</t>
   </si>
   <si>
     <t xml:space="preserve">11.5847682952881</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">10.5175466537476</t>
   </si>
   <si>
-    <t xml:space="preserve">10.828667640686</t>
+    <t xml:space="preserve">10.8286666870117</t>
   </si>
   <si>
     <t xml:space="preserve">11.3458585739136</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">11.2973709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9418039321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0226154327393</t>
+    <t xml:space="preserve">10.9418029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0226144790649</t>
   </si>
   <si>
     <t xml:space="preserve">10.6185598373413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1195869445801</t>
+    <t xml:space="preserve">11.1195878982544</t>
   </si>
   <si>
     <t xml:space="preserve">11.7983999252319</t>
@@ -1475,85 +1475,85 @@
     <t xml:space="preserve">11.0711011886597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9902896881104</t>
+    <t xml:space="preserve">10.9902906417847</t>
   </si>
   <si>
     <t xml:space="preserve">11.2327222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2488832473755</t>
+    <t xml:space="preserve">11.2488861083984</t>
   </si>
   <si>
     <t xml:space="preserve">11.2003984451294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6832075119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9094791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8609933853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4751558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5721273422241</t>
+    <t xml:space="preserve">10.6832084655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.909481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8609924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.475154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5721292495728</t>
   </si>
   <si>
     <t xml:space="preserve">11.6367778778076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.555965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4266700744629</t>
+    <t xml:space="preserve">11.5559663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4266681671143</t>
   </si>
   <si>
     <t xml:space="preserve">11.523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7801818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8933162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0549392700195</t>
+    <t xml:space="preserve">10.7801809310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8933153152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0549402236938</t>
   </si>
   <si>
     <t xml:space="preserve">10.9579648971558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9741268157959</t>
+    <t xml:space="preserve">10.9741287231445</t>
   </si>
   <si>
     <t xml:space="preserve">10.8448305130005</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8125047683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1357498168945</t>
+    <t xml:space="preserve">10.8125057220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1357488632202</t>
   </si>
   <si>
     <t xml:space="preserve">11.0872621536255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3296966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6044540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8792104721069</t>
+    <t xml:space="preserve">11.3296957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.604453086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8792095184326</t>
   </si>
   <si>
     <t xml:space="preserve">11.8630485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7337503433228</t>
+    <t xml:space="preserve">11.7337512969971</t>
   </si>
   <si>
     <t xml:space="preserve">11.6529407501221</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">11.8468856811523</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4589929580688</t>
+    <t xml:space="preserve">11.4589939117432</t>
   </si>
   <si>
     <t xml:space="preserve">11.2650461196899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.362021446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0387773513794</t>
+    <t xml:space="preserve">11.3620204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0387763977051</t>
   </si>
   <si>
     <t xml:space="preserve">10.6508836746216</t>
@@ -1580,55 +1580,55 @@
     <t xml:space="preserve">10.5539112091064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5215864181519</t>
+    <t xml:space="preserve">10.5215873718262</t>
   </si>
   <si>
     <t xml:space="preserve">10.1013689041138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98823547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821813583374</t>
+    <t xml:space="preserve">9.98823261260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821804046631</t>
   </si>
   <si>
     <t xml:space="preserve">10.3922882080078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3114786148071</t>
+    <t xml:space="preserve">10.3114776611328</t>
   </si>
   <si>
     <t xml:space="preserve">10.295316696167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3761253356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3599643707275</t>
+    <t xml:space="preserve">10.376127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3599653244019</t>
   </si>
   <si>
     <t xml:space="preserve">10.6023979187012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.586236000061</t>
+    <t xml:space="preserve">10.5862350463867</t>
   </si>
   <si>
     <t xml:space="preserve">10.3438014984131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700750350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7963428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1034259796143</t>
+    <t xml:space="preserve">10.5700721740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7963438034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1034250259399</t>
   </si>
   <si>
     <t xml:space="preserve">11.1842355728149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.151912689209</t>
+    <t xml:space="preserve">11.1519117355347</t>
   </si>
   <si>
     <t xml:space="preserve">10.4730997085571</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">10.4084501266479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6670455932617</t>
+    <t xml:space="preserve">10.667046546936</t>
   </si>
   <si>
     <t xml:space="preserve">10.2465229034424</t>
@@ -1649,28 +1649,28 @@
     <t xml:space="preserve">10.5067520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5880727767944</t>
+    <t xml:space="preserve">10.5880737304688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7669801712036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9458875656128</t>
+    <t xml:space="preserve">10.9458885192871</t>
   </si>
   <si>
     <t xml:space="preserve">10.9621524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7507162094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.344108581543</t>
+    <t xml:space="preserve">10.7507171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3441076278687</t>
   </si>
   <si>
     <t xml:space="preserve">10.4416942596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3115787506104</t>
+    <t xml:space="preserve">10.311580657959</t>
   </si>
   <si>
     <t xml:space="preserve">10.327844619751</t>
@@ -1679,28 +1679,28 @@
     <t xml:space="preserve">10.4254302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4904880523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5230178833008</t>
+    <t xml:space="preserve">10.4904870986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5230159759521</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555448532104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8157749176025</t>
+    <t xml:space="preserve">10.8157739639282</t>
   </si>
   <si>
     <t xml:space="preserve">10.8483018875122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.141058921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9946823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8808298110962</t>
+    <t xml:space="preserve">11.1410598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9946813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8808307647705</t>
   </si>
   <si>
     <t xml:space="preserve">11.0922679901123</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">10.636866569519</t>
   </si>
   <si>
-    <t xml:space="preserve">10.653130531311</t>
+    <t xml:space="preserve">10.6531295776367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9133596420288</t>
@@ -1730,25 +1730,25 @@
     <t xml:space="preserve">11.10853099823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3037042617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2223825454712</t>
+    <t xml:space="preserve">11.3037033081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2223815917969</t>
   </si>
   <si>
     <t xml:space="preserve">11.5639333724976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4338188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1573238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2386455535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7103109359741</t>
+    <t xml:space="preserve">11.4338178634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.157322883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2386465072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7103118896484</t>
   </si>
   <si>
     <t xml:space="preserve">11.7428398132324</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">11.6452531814575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7019243240356</t>
+    <t xml:space="preserve">10.7019233703613</t>
   </si>
   <si>
     <t xml:space="preserve">10.7344522476196</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">10.6856594085693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043376922607</t>
+    <t xml:space="preserve">10.6043367385864</t>
   </si>
   <si>
     <t xml:space="preserve">10.8645658493042</t>
@@ -1778,28 +1778,28 @@
     <t xml:space="preserve">10.4742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6206016540527</t>
+    <t xml:space="preserve">10.6206026077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.2874402999878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6127243041992</t>
+    <t xml:space="preserve">11.6127252578735</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314044952393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6289892196655</t>
+    <t xml:space="preserve">11.6289901733398</t>
   </si>
   <si>
     <t xml:space="preserve">11.5151395797729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2061176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0597381591797</t>
+    <t xml:space="preserve">11.2061166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.059739112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.076003074646</t>
@@ -1808,79 +1808,79 @@
     <t xml:space="preserve">11.1898536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3850250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012899398804</t>
+    <t xml:space="preserve">11.3850259780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012889862061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2549104690552</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3524961471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.450080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0518627166748</t>
+    <t xml:space="preserve">11.3524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4500818252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0518617630005</t>
   </si>
   <si>
     <t xml:space="preserve">12.3771486282349</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4259414672852</t>
+    <t xml:space="preserve">12.4259405136108</t>
   </si>
   <si>
     <t xml:space="preserve">12.1657123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3446197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2470350265503</t>
+    <t xml:space="preserve">12.3446207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.247034072876</t>
   </si>
   <si>
     <t xml:space="preserve">12.5235280990601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3934135437012</t>
+    <t xml:space="preserve">12.3934125900269</t>
   </si>
   <si>
     <t xml:space="preserve">12.4422063827515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6048488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3608846664429</t>
+    <t xml:space="preserve">12.60484790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3608837127686</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795639038086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4096765518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3283557891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5964612960815</t>
+    <t xml:space="preserve">12.4096775054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3283548355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5964603424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.466347694397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8404245376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2958269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5560569763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4584703445435</t>
+    <t xml:space="preserve">11.8404264450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2958278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5560550689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4584693908691</t>
   </si>
   <si>
     <t xml:space="preserve">12.3120918273926</t>
@@ -1892,25 +1892,25 @@
     <t xml:space="preserve">11.9705410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0681257247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9380130767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0355978012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8729543685913</t>
+    <t xml:space="preserve">12.0681266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9380121231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0355997085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8729553222656</t>
   </si>
   <si>
     <t xml:space="preserve">11.9542760848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9217462539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6777820587158</t>
+    <t xml:space="preserve">11.9217472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6777830123901</t>
   </si>
   <si>
     <t xml:space="preserve">11.791633605957</t>
@@ -1919,34 +1919,34 @@
     <t xml:space="preserve">11.7753686904907</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1735877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3687610626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1247959136963</t>
+    <t xml:space="preserve">11.1735897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3687601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1247968673706</t>
   </si>
   <si>
     <t xml:space="preserve">10.7832450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7995109558105</t>
+    <t xml:space="preserve">10.7995100021362</t>
   </si>
   <si>
     <t xml:space="preserve">10.4579591751099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4091663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5392808914185</t>
+    <t xml:space="preserve">10.4091653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5392799377441</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766374588013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2302589416504</t>
+    <t xml:space="preserve">10.2302570343018</t>
   </si>
   <si>
     <t xml:space="preserve">10.360372543335</t>
@@ -1955,31 +1955,31 @@
     <t xml:space="preserve">9.36824893951416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25439834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53089332580566</t>
+    <t xml:space="preserve">9.25439929962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53089237213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.41704082489014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18934154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8477897644043</t>
+    <t xml:space="preserve">9.1893424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84779071807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.75020599365234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62009143829346</t>
+    <t xml:space="preserve">8.62009048461914</t>
   </si>
   <si>
     <t xml:space="preserve">8.60382556915283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50623989105225</t>
+    <t xml:space="preserve">8.50624084472656</t>
   </si>
   <si>
     <t xml:space="preserve">7.81500625610352</t>
@@ -1988,70 +1988,70 @@
     <t xml:space="preserve">7.42466306686401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34334135055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4244065284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70090007781982</t>
+    <t xml:space="preserve">7.34334087371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42440700531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70090055465698</t>
   </si>
   <si>
     <t xml:space="preserve">6.4325385093689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11538553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48920822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52173709869385</t>
+    <t xml:space="preserve">6.11538457870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48920869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52173757553101</t>
   </si>
   <si>
     <t xml:space="preserve">5.77383422851562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86328744888306</t>
+    <t xml:space="preserve">5.86328792572021</t>
   </si>
   <si>
     <t xml:space="preserve">5.73317384719849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6111912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30216884613037</t>
+    <t xml:space="preserve">5.61119079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30216836929321</t>
   </si>
   <si>
     <t xml:space="preserve">5.59492683410645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56239795684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58679389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52986907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69251251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71690940856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01779890060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74943828582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18044233322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13164949417114</t>
+    <t xml:space="preserve">5.5623984336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58679485321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.529869556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69251298904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71690893173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01779985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74943780899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18044185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13164901733398</t>
   </si>
   <si>
     <t xml:space="preserve">6.05845928192139</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">6.15604591369629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54639005661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5301251411438</t>
+    <t xml:space="preserve">6.54638957977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53012418746948</t>
   </si>
   <si>
     <t xml:space="preserve">6.61144685745239</t>
@@ -2075,37 +2075,37 @@
     <t xml:space="preserve">6.70903301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44067049026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74156188964844</t>
+    <t xml:space="preserve">6.44067096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74156141281128</t>
   </si>
   <si>
     <t xml:space="preserve">6.50572824478149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52199268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39187860488892</t>
+    <t xml:space="preserve">6.52199363708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39187908172607</t>
   </si>
   <si>
     <t xml:space="preserve">6.00153493881226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96900653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12351751327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20483827590942</t>
+    <t xml:space="preserve">5.96900606155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12351703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20483875274658</t>
   </si>
   <si>
     <t xml:space="preserve">6.18857431411743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30242443084717</t>
+    <t xml:space="preserve">6.30242395401001</t>
   </si>
   <si>
     <t xml:space="preserve">6.4975962638855</t>
@@ -2114,46 +2114,46 @@
     <t xml:space="preserve">6.63584327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87167549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79035425186157</t>
+    <t xml:space="preserve">6.87167596817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79035472869873</t>
   </si>
   <si>
     <t xml:space="preserve">6.77408981323242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75782585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9123363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39213466644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59543800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40026664733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36773729324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19696187973022</t>
+    <t xml:space="preserve">6.75782632827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91233682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39213371276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5954384803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40026617050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36773824691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19696235656738</t>
   </si>
   <si>
     <t xml:space="preserve">6.80661821365356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89607238769531</t>
+    <t xml:space="preserve">6.89607286453247</t>
   </si>
   <si>
     <t xml:space="preserve">7.0587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83914709091187</t>
+    <t xml:space="preserve">6.83914661407471</t>
   </si>
   <si>
     <t xml:space="preserve">6.85541152954102</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">7.14003705978394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94486474990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31894445419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28641605377197</t>
+    <t xml:space="preserve">6.94486618041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31894493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28641557693481</t>
   </si>
   <si>
     <t xml:space="preserve">7.15630149841309</t>
@@ -2183,34 +2183,34 @@
     <t xml:space="preserve">7.08311176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00992250442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02618741989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16443395614624</t>
+    <t xml:space="preserve">7.00992202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0261869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1644344329834</t>
   </si>
   <si>
     <t xml:space="preserve">6.9529972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01805543899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66837120056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51386117935181</t>
+    <t xml:space="preserve">7.0180549621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66837215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51386165618896</t>
   </si>
   <si>
     <t xml:space="preserve">6.47319984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73342943191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71716403961182</t>
+    <t xml:space="preserve">6.73342895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71716451644897</t>
   </si>
   <si>
     <t xml:space="preserve">6.78222227096558</t>
@@ -2219,31 +2219,31 @@
     <t xml:space="preserve">6.56265354156494</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5870509147644</t>
+    <t xml:space="preserve">6.58705043792725</t>
   </si>
   <si>
     <t xml:space="preserve">6.60331439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40001106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27802848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35935020446777</t>
+    <t xml:space="preserve">6.40001010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27802753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35934972763062</t>
   </si>
   <si>
     <t xml:space="preserve">6.34308576583862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26989603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21297073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19670677185059</t>
+    <t xml:space="preserve">6.26989650726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21297025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19670629501343</t>
   </si>
   <si>
     <t xml:space="preserve">5.97713804244995</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">6.09912061691284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94460964202881</t>
+    <t xml:space="preserve">5.94460916519165</t>
   </si>
   <si>
     <t xml:space="preserve">5.78196668624878</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">5.88768434524536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80636215209961</t>
+    <t xml:space="preserve">5.80636262893677</t>
   </si>
   <si>
     <t xml:space="preserve">5.79009819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72504043579102</t>
+    <t xml:space="preserve">5.72504091262817</t>
   </si>
   <si>
     <t xml:space="preserve">5.76570224761963</t>
@@ -2285,34 +2285,34 @@
     <t xml:space="preserve">6.05032730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16417789459229</t>
+    <t xml:space="preserve">6.16417741775513</t>
   </si>
   <si>
     <t xml:space="preserve">6.22110319137573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92834520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10725259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03406286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31055688858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17230987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92021226882935</t>
+    <t xml:space="preserve">5.9283447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10725355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0340633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31055641174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17231035232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92021322250366</t>
   </si>
   <si>
     <t xml:space="preserve">5.75756978988647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70064496994019</t>
+    <t xml:space="preserve">5.70064449310303</t>
   </si>
   <si>
     <t xml:space="preserve">5.38349008560181</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">5.0012788772583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96875</t>
+    <t xml:space="preserve">4.96875047683716</t>
   </si>
   <si>
     <t xml:space="preserve">5.01754331588745</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04193925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24524402618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40788745880127</t>
+    <t xml:space="preserve">5.0419397354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24524354934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40788698196411</t>
   </si>
   <si>
     <t xml:space="preserve">6.32682132720947</t>
@@ -2348,25 +2348,25 @@
     <t xml:space="preserve">6.36748170852661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30267953872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54664373397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35960483551025</t>
+    <t xml:space="preserve">7.30268001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54664468765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35960531234741</t>
   </si>
   <si>
     <t xml:space="preserve">7.23762273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22949171066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12377309799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07498025894165</t>
+    <t xml:space="preserve">7.22949123382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1237735748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07497978210449</t>
   </si>
   <si>
     <t xml:space="preserve">7.17256546020508</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">7.21322584152222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06684684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96112966537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9204683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27828407287598</t>
+    <t xml:space="preserve">7.0668478012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9611291885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92046928405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27828359603882</t>
   </si>
   <si>
     <t xml:space="preserve">6.92860126495361</t>
@@ -2393,25 +2393,25 @@
     <t xml:space="preserve">6.99365901947021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10750865936279</t>
+    <t xml:space="preserve">7.10750818252563</t>
   </si>
   <si>
     <t xml:space="preserve">7.29454851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45719194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26202011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18069791793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3108115196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47345495223999</t>
+    <t xml:space="preserve">7.457190990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26201915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18069744110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31081199645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47345590591431</t>
   </si>
   <si>
     <t xml:space="preserve">7.4897198677063</t>
@@ -2429,34 +2429,34 @@
     <t xml:space="preserve">7.40839815139771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82288312911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87980890274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8635425567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0912446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38400220870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53851366043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60356998443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57104206085205</t>
+    <t xml:space="preserve">6.82288360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87980794906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86354351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09124422073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38400268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53851318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60357046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57104253768921</t>
   </si>
   <si>
     <t xml:space="preserve">7.78247737884521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99391412734985</t>
+    <t xml:space="preserve">7.99391317367554</t>
   </si>
   <si>
     <t xml:space="preserve">7.94512033462524</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">7.86379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82313776016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90446090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79874229431152</t>
+    <t xml:space="preserve">7.82313871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90445995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79874134063721</t>
   </si>
   <si>
     <t xml:space="preserve">7.83127117156982</t>
@@ -2483,37 +2483,37 @@
     <t xml:space="preserve">7.57917356491089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61983442306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44092750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5629096031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84753513336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26227474212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13216114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14842414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0508394241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11589527130127</t>
+    <t xml:space="preserve">7.61983489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44092655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56290912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8475341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26227569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13216209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14842510223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05083847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11589431762695</t>
   </si>
   <si>
     <t xml:space="preserve">7.87193155288696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55477714538574</t>
+    <t xml:space="preserve">7.55477666854858</t>
   </si>
   <si>
     <t xml:space="preserve">7.69302463531494</t>
@@ -2522,190 +2522,190 @@
     <t xml:space="preserve">7.75808143615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37612438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24601173400879</t>
+    <t xml:space="preserve">8.37612533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24601078033447</t>
   </si>
   <si>
     <t xml:space="preserve">8.21348190307617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05897045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79060983657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07523441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1240291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98578071594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92072486877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01830959320068</t>
+    <t xml:space="preserve">8.0589714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79060888290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07523632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12402820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9857816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9207239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.018310546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.06710433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9532527923584</t>
+    <t xml:space="preserve">7.95325183868408</t>
   </si>
   <si>
     <t xml:space="preserve">7.71742105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73368501663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92885541915894</t>
+    <t xml:space="preserve">7.7336859703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92885637283325</t>
   </si>
   <si>
     <t xml:space="preserve">8.0833683013916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57129764556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65261936187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45744609832764</t>
+    <t xml:space="preserve">8.57129859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65261840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45744705200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44118309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53990936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37536525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30954551696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50699996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91836452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06645584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34618282318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39554691314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46136379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52718257904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60945510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56009197235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54363822937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32972812652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36263751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37909126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21454524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16518402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01709175109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88545608520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03354644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11581897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81963729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73736572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83609199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95127296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90191078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72091102600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42472839355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57281875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58927345275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63863754272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60572719573975</t>
   </si>
   <si>
     <t xml:space="preserve">8.44118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53990936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37536430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30954647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50699996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06645488739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34618186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39554786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46136379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52718257904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60945606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56009197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54363822937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32972812652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36263751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37909126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21454524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16518402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01709270477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88545608520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03354644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11581993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81963729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73736476898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83609199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95127296447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90190982818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72091102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42472839355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57281970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58927345275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63863754272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60572814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44118309020996</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.4082727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24372959136963</t>
+    <t xml:space="preserve">8.243727684021</t>
   </si>
   <si>
     <t xml:space="preserve">8.29309177398682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34245681762695</t>
+    <t xml:space="preserve">8.34245491027832</t>
   </si>
   <si>
     <t xml:space="preserve">8.77027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85254764556885</t>
+    <t xml:space="preserve">8.85254669189453</t>
   </si>
   <si>
     <t xml:space="preserve">8.68800067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80318260192871</t>
+    <t xml:space="preserve">8.80318355560303</t>
   </si>
   <si>
     <t xml:space="preserve">9.08290958404541</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">9.18163681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70445537567139</t>
+    <t xml:space="preserve">8.7044563293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.75381946563721</t>
@@ -2729,16 +2729,16 @@
     <t xml:space="preserve">8.62218284606934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55636501312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96772766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98418235778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35890960693359</t>
+    <t xml:space="preserve">8.55636405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96772861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9841833114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35891056060791</t>
   </si>
   <si>
     <t xml:space="preserve">8.27663803100586</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">8.18613719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26018238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14500141143799</t>
+    <t xml:space="preserve">8.26018142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14499950408936</t>
   </si>
   <si>
     <t xml:space="preserve">7.98045587539673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.996910572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20259284973145</t>
+    <t xml:space="preserve">7.99690961837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20259189605713</t>
   </si>
   <si>
     <t xml:space="preserve">7.94754600524902</t>
@@ -2771,19 +2771,19 @@
     <t xml:space="preserve">8.03804683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1285457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98868274688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13677406311035</t>
+    <t xml:space="preserve">8.12854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98868083953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13677310943604</t>
   </si>
   <si>
     <t xml:space="preserve">7.89818286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95577430725098</t>
+    <t xml:space="preserve">7.95577383041382</t>
   </si>
   <si>
     <t xml:space="preserve">8.0133638381958</t>
@@ -2792,73 +2792,73 @@
     <t xml:space="preserve">7.8323655128479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97222709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08740997314453</t>
+    <t xml:space="preserve">7.97222805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08740901947021</t>
   </si>
   <si>
     <t xml:space="preserve">8.10386562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16968250274658</t>
+    <t xml:space="preserve">8.1696834564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.05000019073486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00063800811768</t>
+    <t xml:space="preserve">9.00063705444336</t>
   </si>
   <si>
     <t xml:space="preserve">9.13227367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88995599746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87349987030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56909227371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60199975967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59377193450928</t>
+    <t xml:space="preserve">7.88995456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87350082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56909132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60200023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59377336502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.15772819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21531915664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12481880187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39631795883179</t>
+    <t xml:space="preserve">7.21531963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12481927871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39631843566895</t>
   </si>
   <si>
     <t xml:space="preserve">7.30581903457642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23999977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69250106811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55263710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52795505523682</t>
+    <t xml:space="preserve">7.24000072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69250059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55263757705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52795457839966</t>
   </si>
   <si>
     <t xml:space="preserve">7.43745517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33872747421265</t>
+    <t xml:space="preserve">7.33872890472412</t>
   </si>
   <si>
     <t xml:space="preserve">7.46213722229004</t>
@@ -2867,16 +2867,16 @@
     <t xml:space="preserve">7.4045467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44568252563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65959167480469</t>
+    <t xml:space="preserve">7.44568204879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65959358215332</t>
   </si>
   <si>
     <t xml:space="preserve">7.70895576477051</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79945373535156</t>
+    <t xml:space="preserve">7.79945468902588</t>
   </si>
   <si>
     <t xml:space="preserve">8.21081829071045</t>
@@ -2885,22 +2885,22 @@
     <t xml:space="preserve">8.12031936645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07918167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7912278175354</t>
+    <t xml:space="preserve">8.07918262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79122686386108</t>
   </si>
   <si>
     <t xml:space="preserve">7.85704612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02159118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81591033935547</t>
+    <t xml:space="preserve">8.02159214019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81590938568115</t>
   </si>
   <si>
     <t xml:space="preserve">7.78300094604492</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">7.70072793960571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67604637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42922830581665</t>
+    <t xml:space="preserve">7.67604684829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42922782897949</t>
   </si>
   <si>
     <t xml:space="preserve">7.29759120941162</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">7.48681926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6102294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68427419662476</t>
+    <t xml:space="preserve">7.61022853851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6842737197876</t>
   </si>
   <si>
     <t xml:space="preserve">7.51150131225586</t>
@@ -2936,28 +2936,28 @@
     <t xml:space="preserve">7.41277360916138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76654529571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65136480331421</t>
+    <t xml:space="preserve">7.76654624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65136432647705</t>
   </si>
   <si>
     <t xml:space="preserve">7.73363637924194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82413768768311</t>
+    <t xml:space="preserve">7.82413721084595</t>
   </si>
   <si>
     <t xml:space="preserve">7.71718263626099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58554697036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47036457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90268230438232</t>
+    <t xml:space="preserve">7.58554649353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47036504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90268325805664</t>
   </si>
   <si>
     <t xml:space="preserve">6.72168302536011</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">6.89445543289185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10836505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2893648147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49504566192627</t>
+    <t xml:space="preserve">7.10836458206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28936433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49504518508911</t>
   </si>
   <si>
     <t xml:space="preserve">7.50327348709106</t>
@@ -2981,28 +2981,28 @@
     <t xml:space="preserve">7.37163686752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42100191116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51972770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22727298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15322780609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02981853485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09563732147217</t>
+    <t xml:space="preserve">7.42100095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5197286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22727489471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15322875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02982044219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09563827514648</t>
   </si>
   <si>
     <t xml:space="preserve">8.07095527648926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75009298324585</t>
+    <t xml:space="preserve">7.75009202957153</t>
   </si>
   <si>
     <t xml:space="preserve">7.80768251419067</t>
@@ -3014,40 +3014,40 @@
     <t xml:space="preserve">7.84881925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54441022872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72541046142578</t>
+    <t xml:space="preserve">7.54440927505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72540950775146</t>
   </si>
   <si>
     <t xml:space="preserve">7.31404638290405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77477216720581</t>
+    <t xml:space="preserve">7.77477407455444</t>
   </si>
   <si>
     <t xml:space="preserve">7.73959636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63831615447998</t>
+    <t xml:space="preserve">7.63831567764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.61299467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80711889266968</t>
+    <t xml:space="preserve">7.80711793899536</t>
   </si>
   <si>
     <t xml:space="preserve">7.89151906967163</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96748018264771</t>
+    <t xml:space="preserve">7.96748113632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.87463903427124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76491641998291</t>
+    <t xml:space="preserve">7.76491737365723</t>
   </si>
   <si>
     <t xml:space="preserve">7.81555795669556</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">7.79023790359497</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64675664901733</t>
+    <t xml:space="preserve">7.64675617218018</t>
   </si>
   <si>
     <t xml:space="preserve">7.35979175567627</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">7.25007009506226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05594730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04750680923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00530624389648</t>
+    <t xml:space="preserve">7.05594682693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04750728607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00530672073364</t>
   </si>
   <si>
     <t xml:space="preserve">7.16566848754883</t>
@@ -3092,22 +3092,22 @@
     <t xml:space="preserve">7.17410898208618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09814739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01374673843384</t>
+    <t xml:space="preserve">7.09814691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.013747215271</t>
   </si>
   <si>
     <t xml:space="preserve">6.92090463638306</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99686622619629</t>
+    <t xml:space="preserve">6.99686574935913</t>
   </si>
   <si>
     <t xml:space="preserve">6.75210237503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76898288726807</t>
+    <t xml:space="preserve">6.76898241043091</t>
   </si>
   <si>
     <t xml:space="preserve">6.86182451248169</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">6.98842573165894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93778514862061</t>
+    <t xml:space="preserve">6.93778562545776</t>
   </si>
   <si>
     <t xml:space="preserve">6.92934465408325</t>
@@ -3134,22 +3134,22 @@
     <t xml:space="preserve">6.76054239273071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68458127975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69302177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9462251663208</t>
+    <t xml:space="preserve">6.6845817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69302129745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94622468948364</t>
   </si>
   <si>
     <t xml:space="preserve">7.14034843444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02218675613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96310615539551</t>
+    <t xml:space="preserve">7.02218627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96310567855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.06438684463501</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">6.74366188049316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77742195129395</t>
+    <t xml:space="preserve">6.7774224281311</t>
   </si>
   <si>
     <t xml:space="preserve">6.72678136825562</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">6.56641960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38073682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46513748168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3554162979126</t>
+    <t xml:space="preserve">6.38073635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46513795852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35541677474976</t>
   </si>
   <si>
     <t xml:space="preserve">6.40605735778809</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">6.2119345664978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22037410736084</t>
+    <t xml:space="preserve">6.22037363052368</t>
   </si>
   <si>
     <t xml:space="preserve">6.24569463729858</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16129350662231</t>
+    <t xml:space="preserve">6.16129398345947</t>
   </si>
   <si>
     <t xml:space="preserve">6.33009624481201</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">6.11909246444702</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14441347122192</t>
+    <t xml:space="preserve">6.14441299438477</t>
   </si>
   <si>
     <t xml:space="preserve">6.04313135147095</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">6.08533191680908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06845188140869</t>
+    <t xml:space="preserve">6.06845235824585</t>
   </si>
   <si>
     <t xml:space="preserve">5.8827691078186</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">5.98405075073242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92496919631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03469181060791</t>
+    <t xml:space="preserve">5.92496967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03469133377075</t>
   </si>
   <si>
     <t xml:space="preserve">5.99249029159546</t>
@@ -3254,28 +3254,28 @@
     <t xml:space="preserve">5.62956523895264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57048416137695</t>
+    <t xml:space="preserve">5.57048368453979</t>
   </si>
   <si>
     <t xml:space="preserve">5.62112474441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59580421447754</t>
+    <t xml:space="preserve">5.5958046913147</t>
   </si>
   <si>
     <t xml:space="preserve">5.66332530975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67176628112793</t>
+    <t xml:space="preserve">5.67176580429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.51140356063843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57892465591431</t>
+    <t xml:space="preserve">5.49452352523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57892513275146</t>
   </si>
   <si>
     <t xml:space="preserve">5.64644575119019</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">5.5873646736145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82368850708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07689237594604</t>
+    <t xml:space="preserve">5.82368803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07689189910889</t>
   </si>
   <si>
     <t xml:space="preserve">5.93341016769409</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">5.79836797714233</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1950535774231</t>
+    <t xml:space="preserve">6.19505405426025</t>
   </si>
   <si>
     <t xml:space="preserve">6.00937128067017</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">5.90808963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85744905471802</t>
+    <t xml:space="preserve">5.85744857788086</t>
   </si>
   <si>
     <t xml:space="preserve">5.89964962005615</t>
@@ -3320,28 +3320,28 @@
     <t xml:space="preserve">5.75616788864136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77304744720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74772787094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8912091255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76460695266724</t>
+    <t xml:space="preserve">5.77304792404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.747727394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89120864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76460647583008</t>
   </si>
   <si>
     <t xml:space="preserve">5.95029067993164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81524753570557</t>
+    <t xml:space="preserve">5.81524801254272</t>
   </si>
   <si>
     <t xml:space="preserve">5.70552682876587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84900856018066</t>
+    <t xml:space="preserve">5.84900903701782</t>
   </si>
   <si>
     <t xml:space="preserve">5.7308464050293</t>
@@ -3356,10 +3356,10 @@
     <t xml:space="preserve">5.68020629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78148794174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01781129837036</t>
+    <t xml:space="preserve">5.78148746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0178108215332</t>
   </si>
   <si>
     <t xml:space="preserve">5.9165301322937</t>
@@ -3389,31 +3389,31 @@
     <t xml:space="preserve">6.20349407196045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06001138687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13597249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11065292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38917684555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36385679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43137741088867</t>
+    <t xml:space="preserve">6.0600118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13597297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11065244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3891773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36385631561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43137788772583</t>
   </si>
   <si>
     <t xml:space="preserve">6.33853626251221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3216552734375</t>
+    <t xml:space="preserve">6.34697532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32165575027466</t>
   </si>
   <si>
     <t xml:space="preserve">6.30477571487427</t>
@@ -3437,16 +3437,16 @@
     <t xml:space="preserve">6.58330011367798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10221242904663</t>
+    <t xml:space="preserve">6.10221290588379</t>
   </si>
   <si>
     <t xml:space="preserve">6.09377193450928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27101516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39761638641357</t>
+    <t xml:space="preserve">6.27101469039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39761686325073</t>
   </si>
   <si>
     <t xml:space="preserve">6.43302440643311</t>
@@ -69954,7 +69954,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6912384259</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>106965</v>
@@ -69975,6 +69975,32 @@
         <v>1477</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911574074</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>173812</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>9.63000011444092</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>9.60999965667725</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1483</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1555">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,76 +38,76 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13600826263428</t>
+    <t xml:space="preserve">8.13600921630859</t>
   </si>
   <si>
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08278465270996</t>
+    <t xml:space="preserve">8.08278369903564</t>
   </si>
   <si>
     <t xml:space="preserve">8.05997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06757545471191</t>
+    <t xml:space="preserve">8.06757640838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.1284065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11319923400879</t>
+    <t xml:space="preserve">8.11320018768311</t>
   </si>
   <si>
     <t xml:space="preserve">7.90029525756836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87748289108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591569900513</t>
+    <t xml:space="preserve">7.87748241424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591617584229</t>
   </si>
   <si>
     <t xml:space="preserve">7.5277099609375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48969078063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95351886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79384183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67978572845459</t>
+    <t xml:space="preserve">7.48969125747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95351839065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79384136199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67978525161743</t>
   </si>
   <si>
     <t xml:space="preserve">7.62655925750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7101993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89268970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82425546646118</t>
+    <t xml:space="preserve">7.71020030975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89269065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82425594329834</t>
   </si>
   <si>
     <t xml:space="preserve">7.60374879837036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69499254226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98393535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84706735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91550207138062</t>
+    <t xml:space="preserve">7.69499158859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9839334487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84706878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91550159454346</t>
   </si>
   <si>
     <t xml:space="preserve">8.01435089111328</t>
@@ -116,70 +116,70 @@
     <t xml:space="preserve">8.20444393157959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10559558868408</t>
+    <t xml:space="preserve">8.10559463500977</t>
   </si>
   <si>
     <t xml:space="preserve">8.24246120452881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25006580352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30329322814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15121746063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23485851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35651874542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28808498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21965217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36412048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29568767547607</t>
+    <t xml:space="preserve">8.25006675720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3032922744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15121841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2348575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35651779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28808689117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.219651222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36412334442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29568862915039</t>
   </si>
   <si>
     <t xml:space="preserve">8.38693332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1436128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18923664093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40974521636963</t>
+    <t xml:space="preserve">8.14361476898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18923759460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40974617004395</t>
   </si>
   <si>
     <t xml:space="preserve">8.40214157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37932968139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51619815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75191402435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82034778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80514049530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82795238494873</t>
+    <t xml:space="preserve">8.37932872772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51619625091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75191497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82034969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80513954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82795143127441</t>
   </si>
   <si>
     <t xml:space="preserve">9.01044082641602</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">8.98002624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12449741363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19293117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78993320465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11689472198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17772388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03325176239014</t>
+    <t xml:space="preserve">9.12449836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19293022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78993225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11689376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17772483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03325080871582</t>
   </si>
   <si>
     <t xml:space="preserve">9.0864782333374</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">9.20053482055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34500503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13970470428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61113834381104</t>
+    <t xml:space="preserve">9.34500598907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13970565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6111364364624</t>
   </si>
   <si>
     <t xml:space="preserve">9.67196750640869</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">9.77081680297852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73252964019775</t>
+    <t xml:space="preserve">9.73252868652344</t>
   </si>
   <si>
     <t xml:space="preserve">9.47217750549316</t>
@@ -248,28 +248,28 @@
     <t xml:space="preserve">9.49515151977539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57172393798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7018985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67892837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69424247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61001110076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6482982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51046657562256</t>
+    <t xml:space="preserve">9.5717248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77847194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67892646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69424152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61001205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64829730987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51046466827393</t>
   </si>
   <si>
     <t xml:space="preserve">9.41857624053955</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">9.22714328765869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1888542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11228179931641</t>
+    <t xml:space="preserve">9.18885517120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11228370666504</t>
   </si>
   <si>
     <t xml:space="preserve">9.34200382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63298225402832</t>
+    <t xml:space="preserve">9.63298320770264</t>
   </si>
   <si>
     <t xml:space="preserve">9.20416927337646</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">9.21182823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30371570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72487163543701</t>
+    <t xml:space="preserve">9.30371475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72487258911133</t>
   </si>
   <si>
     <t xml:space="preserve">9.34965991973877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38794803619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59469699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53343677520752</t>
+    <t xml:space="preserve">9.38794708251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59469604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5334358215332</t>
   </si>
   <si>
     <t xml:space="preserve">9.75550174713135</t>
@@ -341,22 +341,22 @@
     <t xml:space="preserve">9.71721363067627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68658542633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67126941680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36497592926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56406593322754</t>
+    <t xml:space="preserve">9.68658447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6712703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36497402191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56406688690186</t>
   </si>
   <si>
     <t xml:space="preserve">9.57938194274902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80910205841064</t>
+    <t xml:space="preserve">9.80910301208496</t>
   </si>
   <si>
     <t xml:space="preserve">9.70955753326416</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">9.66361236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74018573760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51812076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44920635223389</t>
+    <t xml:space="preserve">9.7401876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51812171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44920539855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.39560604095459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3573169708252</t>
+    <t xml:space="preserve">9.35731792449951</t>
   </si>
   <si>
     <t xml:space="preserve">9.54109477996826</t>
@@ -392,139 +392,139 @@
     <t xml:space="preserve">9.55640983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79378795623779</t>
+    <t xml:space="preserve">9.79378986358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.86270427703857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90864944458008</t>
+    <t xml:space="preserve">9.90865039825439</t>
   </si>
   <si>
     <t xml:space="preserve">9.9392786026001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92396450042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2226009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2685461044312</t>
+    <t xml:space="preserve">9.92396259307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2226028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2685451507568</t>
   </si>
   <si>
     <t xml:space="preserve">10.283860206604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3910636901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4829521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.582498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7050180435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6437578201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7203302383423</t>
+    <t xml:space="preserve">10.3910627365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4829511642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5824995040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7050170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6437587738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7203321456909</t>
   </si>
   <si>
     <t xml:space="preserve">10.3374633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4523220062256</t>
+    <t xml:space="preserve">10.4523229598999</t>
   </si>
   <si>
     <t xml:space="preserve">10.1843156814575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0771102905273</t>
+    <t xml:space="preserve">10.077112197876</t>
   </si>
   <si>
     <t xml:space="preserve">10.0694541931152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2379169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617980957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95459461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.870361328125</t>
+    <t xml:space="preserve">10.2379159927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95459270477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87036323547363</t>
   </si>
   <si>
     <t xml:space="preserve">9.82441806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0388240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98522090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85504722595215</t>
+    <t xml:space="preserve">10.0388231277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98522186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85504817962646</t>
   </si>
   <si>
     <t xml:space="preserve">9.93162059783936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94693565368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89333343505859</t>
+    <t xml:space="preserve">9.94693756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89333438873291</t>
   </si>
   <si>
     <t xml:space="preserve">10.0541400909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97756385803223</t>
+    <t xml:space="preserve">9.97756576538086</t>
   </si>
   <si>
     <t xml:space="preserve">9.88567638397217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1613445281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288963317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5671825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4906091690063</t>
+    <t xml:space="preserve">10.161340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288972854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5671844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906101226807</t>
   </si>
   <si>
     <t xml:space="preserve">10.2991752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2608871459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4063787460327</t>
+    <t xml:space="preserve">10.2608880996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.406379699707</t>
   </si>
   <si>
     <t xml:space="preserve">10.4140357971191</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2455739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153984069824</t>
+    <t xml:space="preserve">10.2455730438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153993606567</t>
   </si>
   <si>
     <t xml:space="preserve">10.3221483230591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2915191650391</t>
+    <t xml:space="preserve">10.2915182113647</t>
   </si>
   <si>
     <t xml:space="preserve">10.3987216949463</t>
@@ -536,16 +536,16 @@
     <t xml:space="preserve">10.4293508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6054706573486</t>
+    <t xml:space="preserve">10.6054716110229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5901556015015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3757486343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.253231048584</t>
+    <t xml:space="preserve">10.3757495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2532329559326</t>
   </si>
   <si>
     <t xml:space="preserve">10.1460266113281</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">10.3068323135376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4752960205078</t>
+    <t xml:space="preserve">10.4752950668335</t>
   </si>
   <si>
     <t xml:space="preserve">10.5212392807007</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">10.4446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3298053741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1230545043945</t>
+    <t xml:space="preserve">10.3298044204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1230554580688</t>
   </si>
   <si>
     <t xml:space="preserve">10.4216938018799</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">10.781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2027473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1797752380371</t>
+    <t xml:space="preserve">11.2027454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1797733306885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1338300704956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3329219818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2946348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.409496307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2793197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3788652420044</t>
+    <t xml:space="preserve">11.3329229354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2946338653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4094953536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2793207168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3788661956787</t>
   </si>
   <si>
     <t xml:space="preserve">11.6775026321411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7081346511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8383092880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6851615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6468734741211</t>
+    <t xml:space="preserve">11.7081336975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8383083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6851606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6468744277954</t>
   </si>
   <si>
     <t xml:space="preserve">11.5473289489746</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">11.401837348938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.524356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6392164230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157917022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7923650741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2288360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2441492080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3513536453247</t>
+    <t xml:space="preserve">11.5243558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.639217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157907485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7923641204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2288341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2441501617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3513526916504</t>
   </si>
   <si>
     <t xml:space="preserve">12.4049558639526</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">12.5198154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.254921913147</t>
+    <t xml:space="preserve">13.2549238204956</t>
   </si>
   <si>
     <t xml:space="preserve">13.5918474197388</t>
@@ -662,25 +662,25 @@
     <t xml:space="preserve">13.2472667694092</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8184547424316</t>
+    <t xml:space="preserve">12.8184537887573</t>
   </si>
   <si>
     <t xml:space="preserve">12.6346769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7112493515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0252017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8643970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2396068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2166376113892</t>
+    <t xml:space="preserve">12.7112503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.025200843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8643980026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2396087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2166385650635</t>
   </si>
   <si>
     <t xml:space="preserve">13.2089786529541</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">13.7373380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3621263504028</t>
+    <t xml:space="preserve">13.3621273040771</t>
   </si>
   <si>
     <t xml:space="preserve">13.4004144668579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7143678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5688772201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5152769088745</t>
+    <t xml:space="preserve">13.7143669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5688762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5152759552002</t>
   </si>
   <si>
     <t xml:space="preserve">13.6684217453003</t>
   </si>
   <si>
-    <t xml:space="preserve">13.614821434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.319299697876</t>
+    <t xml:space="preserve">13.6148195266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3193006515503</t>
   </si>
   <si>
     <t xml:space="preserve">14.3958740234375</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">14.3882160186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4341611862183</t>
+    <t xml:space="preserve">14.4341621398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.5490217208862</t>
@@ -728,73 +728,73 @@
     <t xml:space="preserve">14.6791954040527</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2810134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3269557952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4265022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3422689437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.533709526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2733554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0359754562378</t>
+    <t xml:space="preserve">14.2810115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3269596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4265031814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3422708511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5337076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2733564376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0359773635864</t>
   </si>
   <si>
     <t xml:space="preserve">14.0512914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9897298812866</t>
+    <t xml:space="preserve">13.9897289276123</t>
   </si>
   <si>
     <t xml:space="preserve">14.1282424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3975715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4976100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.082070350647</t>
+    <t xml:space="preserve">14.3975744247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4976081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0820732116699</t>
   </si>
   <si>
     <t xml:space="preserve">14.1436338424683</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2590579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5745601654053</t>
+    <t xml:space="preserve">14.2590599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5745573043823</t>
   </si>
   <si>
     <t xml:space="preserve">14.5976438522339</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6592073440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3437070846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3667907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3514013290405</t>
+    <t xml:space="preserve">14.6592063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3437061309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.366792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3514003753662</t>
   </si>
   <si>
     <t xml:space="preserve">14.2513647079468</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435943603516</t>
+    <t xml:space="preserve">14.0435962677002</t>
   </si>
   <si>
     <t xml:space="preserve">14.5437793731689</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">14.58225440979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3129262924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5360851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4899139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.697681427002</t>
+    <t xml:space="preserve">14.3129253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5360841751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4899120330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6976823806763</t>
   </si>
   <si>
     <t xml:space="preserve">14.6207304000854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.459132194519</t>
+    <t xml:space="preserve">14.4591312408447</t>
   </si>
   <si>
     <t xml:space="preserve">13.774266242981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0974617004395</t>
+    <t xml:space="preserve">14.0974607467651</t>
   </si>
   <si>
     <t xml:space="preserve">13.8896923065186</t>
@@ -833,34 +833,34 @@
     <t xml:space="preserve">13.9127788543701</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8973875045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.243670463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3898773193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4129600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3821811676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4437427520752</t>
+    <t xml:space="preserve">13.897388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2436695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3898763656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4129610061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3821792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4437417984009</t>
   </si>
   <si>
     <t xml:space="preserve">14.5591707229614</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7361555099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5053052902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5283889770508</t>
+    <t xml:space="preserve">14.7361574172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5053043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5283899307251</t>
   </si>
   <si>
     <t xml:space="preserve">14.4283514022827</t>
@@ -869,112 +869,112 @@
     <t xml:space="preserve">14.5514726638794</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4360475540161</t>
+    <t xml:space="preserve">14.4360494613647</t>
   </si>
   <si>
     <t xml:space="preserve">14.2744512557983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0512895584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9666481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6742296218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.120548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1590242385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1513271331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8512191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9743413925171</t>
+    <t xml:space="preserve">14.051290512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9666452407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6742315292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1205472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1590251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1513261795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8512172698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9743404388428</t>
   </si>
   <si>
     <t xml:space="preserve">14.1744136810303</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2051935195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0051202774048</t>
+    <t xml:space="preserve">14.2051954269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0051183700562</t>
   </si>
   <si>
     <t xml:space="preserve">14.305230140686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3590974807739</t>
+    <t xml:space="preserve">14.3590965270996</t>
   </si>
   <si>
     <t xml:space="preserve">14.297534942627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4206581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3283166885376</t>
+    <t xml:space="preserve">14.4206571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3283157348633</t>
   </si>
   <si>
     <t xml:space="preserve">14.3360118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3744859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2359733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5129976272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2205820083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1974973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3902416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2440376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.25172996521</t>
+    <t xml:space="preserve">14.3744869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.23597240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5129985809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2205839157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1974992752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3902444839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2440347671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2517318725586</t>
   </si>
   <si>
     <t xml:space="preserve">15.1670837402344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1055221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978673934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0670499801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9208393096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9285364151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.882363319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.520694732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2898426055908</t>
+    <t xml:space="preserve">15.1055240631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.197865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0670461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9208402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9285345077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8823642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5206909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2898387908936</t>
   </si>
   <si>
     <t xml:space="preserve">14.7515459060669</t>
@@ -983,103 +983,103 @@
     <t xml:space="preserve">14.6438140869141</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5668601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6515111923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7438516616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7900228500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8361911773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7746353149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6361217498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.45143699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4668264389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5899496078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8131065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8515853881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1439981460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2902097702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3440723419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5441436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5826215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5056715011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4287195205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2209482192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9747076034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1286096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9289026260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7365217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8134756088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2367076873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0828056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6210956573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0058498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1212749481201</t>
+    <t xml:space="preserve">14.5668630599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6515102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7438526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7900247573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8361949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7746343612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6361198425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4514379501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4668273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5899515151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8131093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.851583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1440010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2902059555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3440713882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5441427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5826225280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5056705474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4287204742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2209510803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9747047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1286067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9289016723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7365226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8134727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2367057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0828037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6210985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0058536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1212768554688</t>
   </si>
   <si>
     <t xml:space="preserve">15.6980485916138</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7749996185303</t>
+    <t xml:space="preserve">15.774998664856</t>
   </si>
   <si>
     <t xml:space="preserve">15.2671194076538</t>
@@ -1088,127 +1088,127 @@
     <t xml:space="preserve">14.9131460189819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8977518081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8054141998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0208787918091</t>
+    <t xml:space="preserve">14.8977537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8054132461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1747798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0208778381348</t>
   </si>
   <si>
     <t xml:space="preserve">15.0516576766968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8208065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0362682342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.928168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1128511428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2821435928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4822158813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5588035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7127046585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5434122085571</t>
+    <t xml:space="preserve">14.8208026885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0362672805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9281692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1128520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2821464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4822196960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5588045120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7127075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5434131622314</t>
   </si>
   <si>
     <t xml:space="preserve">13.3125591278076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2048273086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4510726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4356813430786</t>
+    <t xml:space="preserve">13.2048282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4510736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4356832504272</t>
   </si>
   <si>
     <t xml:space="preserve">13.2817802429199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6511459350586</t>
+    <t xml:space="preserve">13.6511468887329</t>
   </si>
   <si>
     <t xml:space="preserve">13.3895111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1432676315308</t>
+    <t xml:space="preserve">13.1432666778564</t>
   </si>
   <si>
     <t xml:space="preserve">13.0663166046143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0047569274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0509243011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2971715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2356081008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6357545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8666086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6819267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8819971084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7130727767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9589509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9512147903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8893480300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7656145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9976167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0749521255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5026741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8066606521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3170690536499</t>
+    <t xml:space="preserve">13.0047559738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0509252548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2971706390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2356090545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6357555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8666095733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6819248199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8819961547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7130718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.958948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9512157440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.889349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7656126022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9976177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.074951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5026760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8066596984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3170709609985</t>
   </si>
   <si>
     <t xml:space="preserve">13.146933555603</t>
@@ -1217,76 +1217,76 @@
     <t xml:space="preserve">13.2397365570068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6109418869019</t>
+    <t xml:space="preserve">13.6109428405762</t>
   </si>
   <si>
     <t xml:space="preserve">13.5336084365845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7192115783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4253368377686</t>
+    <t xml:space="preserve">13.7192134857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4253387451172</t>
   </si>
   <si>
     <t xml:space="preserve">13.4562740325928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5645437240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3789377212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3016033172607</t>
+    <t xml:space="preserve">13.5645427703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3789386749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3016042709351</t>
   </si>
   <si>
     <t xml:space="preserve">13.5490760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8274803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8738822937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6573438644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594835281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1213521957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0285520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8584146499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9048147201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.966682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1986885070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.105884552002</t>
+    <t xml:space="preserve">13.8274812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8738813400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6573448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594844818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0285501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9048137664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9666843414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1986875534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058874130249</t>
   </si>
   <si>
     <t xml:space="preserve">13.9202823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1677541732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5389604568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4925622940063</t>
+    <t xml:space="preserve">14.1677532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5389623641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.492561340332</t>
   </si>
   <si>
     <t xml:space="preserve">14.4306936264038</t>
@@ -1295,64 +1295,64 @@
     <t xml:space="preserve">14.3688249588013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3533563613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4616270065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.600830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7810802459717</t>
+    <t xml:space="preserve">14.2914896011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3533592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4616279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6008310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.781081199646</t>
   </si>
   <si>
     <t xml:space="preserve">14.3842926025391</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5080280303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3224248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5698976516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3069562911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1368207931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.152286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6882772445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0130834579468</t>
+    <t xml:space="preserve">14.5080289840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3224239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5698957443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3069543838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1368198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1522884368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6882791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0130844116211</t>
   </si>
   <si>
     <t xml:space="preserve">13.2088012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.440806388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4872074127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6728105545044</t>
+    <t xml:space="preserve">13.4408073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4872055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6728096008301</t>
   </si>
   <si>
     <t xml:space="preserve">13.7037448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5800094604492</t>
+    <t xml:space="preserve">13.5800085067749</t>
   </si>
   <si>
     <t xml:space="preserve">12.6983919143677</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">12.5746555328369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6519908905029</t>
+    <t xml:space="preserve">12.6519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149284362793</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.0231990814209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6674585342407</t>
+    <t xml:space="preserve">12.6674575805664</t>
   </si>
   <si>
     <t xml:space="preserve">12.2189159393311</t>
@@ -1385,25 +1385,25 @@
     <t xml:space="preserve">12.2962503433228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7394380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9714422225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9405088424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0951776504517</t>
+    <t xml:space="preserve">11.7394371032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9714431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9405097961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.095178604126</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.064245223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8786420822144</t>
+    <t xml:space="preserve">12.0642461776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8786430358887</t>
   </si>
   <si>
     <t xml:space="preserve">11.8477087020874</t>
@@ -1412,16 +1412,16 @@
     <t xml:space="preserve">11.6621046066284</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6002359390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5074338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1362266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4402122497559</t>
+    <t xml:space="preserve">11.6002349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5074348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1362257003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4402132034302</t>
   </si>
   <si>
     <t xml:space="preserve">10.8887548446655</t>
@@ -1430,76 +1430,76 @@
     <t xml:space="preserve">11.2599620819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.935154914856</t>
+    <t xml:space="preserve">10.9351539611816</t>
   </si>
   <si>
     <t xml:space="preserve">11.012490272522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3682317733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4455671310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5847673416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5175457000732</t>
+    <t xml:space="preserve">11.3682308197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4455652236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5847692489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5175466537476</t>
   </si>
   <si>
     <t xml:space="preserve">10.828667640686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3458585739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2973718643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9418020248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0226154327393</t>
+    <t xml:space="preserve">11.3458576202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9418039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0226144790649</t>
   </si>
   <si>
     <t xml:space="preserve">10.6185607910156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1195859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7983999252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2165603637695</t>
+    <t xml:space="preserve">11.1195878982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2165613174438</t>
   </si>
   <si>
     <t xml:space="preserve">11.0711002349854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9902896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2327213287354</t>
+    <t xml:space="preserve">10.9902906417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">11.2488851547241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2003984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6832084655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9094791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8609924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.475154876709</t>
+    <t xml:space="preserve">11.2003974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6832094192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.909478187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8609933853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4751558303833</t>
   </si>
   <si>
     <t xml:space="preserve">11.5721282958984</t>
@@ -1511,31 +1511,31 @@
     <t xml:space="preserve">11.5559673309326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4266700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5236434936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7801818847656</t>
+    <t xml:space="preserve">11.4266691207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.523642539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7801809310913</t>
   </si>
   <si>
     <t xml:space="preserve">10.8933172225952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0549392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9579658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9741268157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8448314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8125047683716</t>
+    <t xml:space="preserve">11.0549383163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9579648971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9741277694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8448305130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8125066757202</t>
   </si>
   <si>
     <t xml:space="preserve">11.1357488632202</t>
@@ -1544,25 +1544,25 @@
     <t xml:space="preserve">11.0872640609741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3296966552734</t>
+    <t xml:space="preserve">11.3296976089478</t>
   </si>
   <si>
     <t xml:space="preserve">11.604453086853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8792104721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8630495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7337522506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6529397964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8468866348267</t>
+    <t xml:space="preserve">11.8792095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8630485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7337512969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6529388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8468856811523</t>
   </si>
   <si>
     <t xml:space="preserve">11.4589939117432</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">11.0387763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6508846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5539112091064</t>
+    <t xml:space="preserve">10.6508855819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5539102554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.5215873718262</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">10.1013689041138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98823356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3922891616821</t>
+    <t xml:space="preserve">9.9882345199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3922882080078</t>
   </si>
   <si>
     <t xml:space="preserve">10.3114786148071</t>
@@ -1604,10 +1604,10 @@
     <t xml:space="preserve">10.2953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3761262893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3599643707275</t>
+    <t xml:space="preserve">10.3761253356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3599634170532</t>
   </si>
   <si>
     <t xml:space="preserve">10.6023969650269</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">10.5700731277466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7963428497314</t>
+    <t xml:space="preserve">10.7963447570801</t>
   </si>
   <si>
     <t xml:space="preserve">11.1034250259399</t>
@@ -1634,67 +1634,67 @@
     <t xml:space="preserve">11.151912689209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4730987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4569368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4084510803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.667046546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2465238571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5067520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5880737304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7669792175293</t>
+    <t xml:space="preserve">10.4731006622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4569358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4084520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6670455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2465219497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5067529678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5880746841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7669801712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9458885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9621524810791</t>
+    <t xml:space="preserve">10.9621534347534</t>
   </si>
   <si>
     <t xml:space="preserve">10.7507171630859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.344108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4416952133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3115797042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3278427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4254302978516</t>
+    <t xml:space="preserve">10.3441076278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4416933059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.311580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3278436660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4254293441772</t>
   </si>
   <si>
     <t xml:space="preserve">10.4904870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5230150222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5555438995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8157730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8483028411865</t>
+    <t xml:space="preserve">10.5230140686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5555448532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8157720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8483018875122</t>
   </si>
   <si>
     <t xml:space="preserve">11.1410598754883</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">10.9946804046631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8808307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0922679901123</t>
+    <t xml:space="preserve">10.8808317184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.092267036438</t>
   </si>
   <si>
     <t xml:space="preserve">10.8970947265625</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">10.653130531311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133605957031</t>
+    <t xml:space="preserve">10.9133596420288</t>
   </si>
   <si>
     <t xml:space="preserve">10.8320379257202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1085319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3037023544312</t>
+    <t xml:space="preserve">11.10853099823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3037033081055</t>
   </si>
   <si>
     <t xml:space="preserve">11.2223825454712</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">11.4338188171387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1573247909546</t>
+    <t xml:space="preserve">11.1573257446289</t>
   </si>
   <si>
     <t xml:space="preserve">11.2386465072632</t>
@@ -1754,97 +1754,97 @@
     <t xml:space="preserve">11.7103109359741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7428398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5476675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6452541351318</t>
+    <t xml:space="preserve">11.7428388595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5476684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6452531814575</t>
   </si>
   <si>
     <t xml:space="preserve">10.701922416687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7344522476196</t>
+    <t xml:space="preserve">10.7344512939453</t>
   </si>
   <si>
     <t xml:space="preserve">10.6856603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6043367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8645658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4742231369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6206026077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2874383926392</t>
+    <t xml:space="preserve">10.6043376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8645677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4742240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6206016540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2874393463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.6127262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5314035415649</t>
+    <t xml:space="preserve">11.5314044952393</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5151395797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2061176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0597381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0760049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1898517608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3850259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012889862061</t>
+    <t xml:space="preserve">11.5151405334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2061166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.059739112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.076003074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1898536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3850250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012908935547</t>
   </si>
   <si>
     <t xml:space="preserve">11.2549104690552</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3524961471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4500827789307</t>
+    <t xml:space="preserve">11.3524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4500818252563</t>
   </si>
   <si>
     <t xml:space="preserve">12.0518617630005</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3771486282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4259405136108</t>
+    <t xml:space="preserve">12.3771476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4259424209595</t>
   </si>
   <si>
     <t xml:space="preserve">12.1657123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3446197509766</t>
+    <t xml:space="preserve">12.3446207046509</t>
   </si>
   <si>
     <t xml:space="preserve">12.247034072876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5235261917114</t>
+    <t xml:space="preserve">12.5235271453857</t>
   </si>
   <si>
     <t xml:space="preserve">12.3934125900269</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">12.4422063827515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6048498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3608846664429</t>
+    <t xml:space="preserve">12.604850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3608856201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795629501343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4096775054932</t>
+    <t xml:space="preserve">12.4096765518188</t>
   </si>
   <si>
     <t xml:space="preserve">12.3283548355103</t>
@@ -1871,16 +1871,16 @@
     <t xml:space="preserve">11.5964612960815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4663457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8404264450073</t>
+    <t xml:space="preserve">11.4663467407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8404273986816</t>
   </si>
   <si>
     <t xml:space="preserve">12.2958269119263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.556056022644</t>
+    <t xml:space="preserve">12.5560550689697</t>
   </si>
   <si>
     <t xml:space="preserve">12.4584703445435</t>
@@ -1892,31 +1892,31 @@
     <t xml:space="preserve">12.1331844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9705419540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0681266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9380130767822</t>
+    <t xml:space="preserve">11.9705410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0681276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9380121231079</t>
   </si>
   <si>
     <t xml:space="preserve">12.0355978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8729553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9542760848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9217481613159</t>
+    <t xml:space="preserve">11.8729543685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9542751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9217472076416</t>
   </si>
   <si>
     <t xml:space="preserve">11.6777830123901</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7916326522827</t>
+    <t xml:space="preserve">11.7916316986084</t>
   </si>
   <si>
     <t xml:space="preserve">11.7753686904907</t>
@@ -1925,13 +1925,13 @@
     <t xml:space="preserve">11.1735887527466</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3687610626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1247968673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7832460403442</t>
+    <t xml:space="preserve">11.3687601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1247959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7832450866699</t>
   </si>
   <si>
     <t xml:space="preserve">10.7995090484619</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">10.4091663360596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5392799377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3766384124756</t>
+    <t xml:space="preserve">10.5392808914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3766374588013</t>
   </si>
   <si>
     <t xml:space="preserve">10.2302579879761</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">10.360372543335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36824989318848</t>
+    <t xml:space="preserve">9.36824798583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.25439929962158</t>
@@ -1964,82 +1964,82 @@
     <t xml:space="preserve">9.53089237213135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41704273223877</t>
+    <t xml:space="preserve">9.41704177856445</t>
   </si>
   <si>
     <t xml:space="preserve">9.1893424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84779167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75020503997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62009143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60382556915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50624084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81500673294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42466259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34334087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42440748214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70090055465698</t>
+    <t xml:space="preserve">8.84779071807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75020599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62009048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60382461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50624179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81500577926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4246621131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3433403968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4244065284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70090007781982</t>
   </si>
   <si>
     <t xml:space="preserve">6.43253898620605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11538457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48920869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52173662185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77383375167847</t>
+    <t xml:space="preserve">6.11538505554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48920822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52173709869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77383422851562</t>
   </si>
   <si>
     <t xml:space="preserve">5.86328744888306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73317289352417</t>
+    <t xml:space="preserve">5.73317337036133</t>
   </si>
   <si>
     <t xml:space="preserve">5.6111912727356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30216836929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59492588043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5623984336853</t>
+    <t xml:space="preserve">5.30216884613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59492683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56239795684814</t>
   </si>
   <si>
     <t xml:space="preserve">5.58679437637329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52986907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69251298904419</t>
+    <t xml:space="preserve">5.529869556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69251251220703</t>
   </si>
   <si>
     <t xml:space="preserve">5.71690940856934</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">5.74943780899048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18044233322144</t>
+    <t xml:space="preserve">6.18044281005859</t>
   </si>
   <si>
     <t xml:space="preserve">6.13164949417114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05845975875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09098768234253</t>
+    <t xml:space="preserve">6.05845880508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09098815917969</t>
   </si>
   <si>
     <t xml:space="preserve">6.15604639053345</t>
@@ -2069,25 +2069,25 @@
     <t xml:space="preserve">6.54638957977295</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53012466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61144638061523</t>
+    <t xml:space="preserve">6.5301251411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61144685745239</t>
   </si>
   <si>
     <t xml:space="preserve">6.70903205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44067096710205</t>
+    <t xml:space="preserve">6.44067144393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.74156093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50572824478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52199363708496</t>
+    <t xml:space="preserve">6.50572872161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5219931602478</t>
   </si>
   <si>
     <t xml:space="preserve">6.39187860488892</t>
@@ -2096,43 +2096,43 @@
     <t xml:space="preserve">6.0015344619751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96900653839111</t>
+    <t xml:space="preserve">5.96900606155396</t>
   </si>
   <si>
     <t xml:space="preserve">6.12351703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20483875274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18857431411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30242490768433</t>
+    <t xml:space="preserve">6.20483827590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18857383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30242538452148</t>
   </si>
   <si>
     <t xml:space="preserve">6.4975962638855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63584327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87167549133301</t>
+    <t xml:space="preserve">6.63584280014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87167596817017</t>
   </si>
   <si>
     <t xml:space="preserve">6.79035425186157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77408933639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75782632827759</t>
+    <t xml:space="preserve">6.77408981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75782680511475</t>
   </si>
   <si>
     <t xml:space="preserve">6.9123363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39213418960571</t>
+    <t xml:space="preserve">7.39213275909424</t>
   </si>
   <si>
     <t xml:space="preserve">7.59543895721436</t>
@@ -2144,82 +2144,82 @@
     <t xml:space="preserve">7.36773777008057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1969633102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80661916732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89607238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05871534347534</t>
+    <t xml:space="preserve">7.19696283340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80661869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89607095718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.83914709091187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85541200637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97739315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05058336257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14003610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94486522674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31894540786743</t>
+    <t xml:space="preserve">6.85541152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97739410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05058431625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14003705978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94486618041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31894445419312</t>
   </si>
   <si>
     <t xml:space="preserve">7.28641605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15630054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08311223983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00992202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0261869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16443347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95299816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0180549621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66837215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51386070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47319984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73342895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71716451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78222274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56265354156494</t>
+    <t xml:space="preserve">7.15630197525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0831127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00992298126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02618741989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16443300247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95299768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01805448532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66837167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51386022567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47319936752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73342943191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71716499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78222227096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56265306472778</t>
   </si>
   <si>
     <t xml:space="preserve">6.58705043792725</t>
@@ -2228,34 +2228,34 @@
     <t xml:space="preserve">6.60331392288208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40001153945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27802801132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35934925079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34308576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26989603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21297025680542</t>
+    <t xml:space="preserve">6.40001058578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27802753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35935020446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34308624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26989650726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21297121047974</t>
   </si>
   <si>
     <t xml:space="preserve">6.19670629501343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97713804244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09912061691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94460916519165</t>
+    <t xml:space="preserve">5.97713756561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09912014007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94461011886597</t>
   </si>
   <si>
     <t xml:space="preserve">5.78196620941162</t>
@@ -2267,25 +2267,25 @@
     <t xml:space="preserve">5.80636310577393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79009866714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72504138946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76570177078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9934024810791</t>
+    <t xml:space="preserve">5.79009819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72504091262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76570224761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99340295791626</t>
   </si>
   <si>
     <t xml:space="preserve">6.00966644287109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98527097702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05032825469971</t>
+    <t xml:space="preserve">5.98527050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05032730102539</t>
   </si>
   <si>
     <t xml:space="preserve">6.16417741775513</t>
@@ -2294,43 +2294,43 @@
     <t xml:space="preserve">6.22110319137573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92834520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10725259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0340633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31055688858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17230987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92021322250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75756978988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70064449310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38348960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21271514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00127840042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96875047683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01754331588745</t>
+    <t xml:space="preserve">5.92834568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.107253074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03406381607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31055641174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17231035232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92021369934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75757026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70064544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38349008560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21271467208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00127935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96875095367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01754379272461</t>
   </si>
   <si>
     <t xml:space="preserve">5.0419397354126</t>
@@ -2339,364 +2339,364 @@
     <t xml:space="preserve">5.24524354934692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40788650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32682132720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28616046905518</t>
+    <t xml:space="preserve">5.40788602828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32682085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28615999221802</t>
   </si>
   <si>
     <t xml:space="preserve">6.36748170852661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30268096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5466456413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35960483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23762226104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22949123382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12377166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07497930526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17256593704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21322584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06684684753418</t>
+    <t xml:space="preserve">7.30268001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54664468765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35960578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23762369155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22949171066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12377262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07497882843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21322679519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06684732437134</t>
   </si>
   <si>
     <t xml:space="preserve">6.9611291885376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92046880722046</t>
+    <t xml:space="preserve">6.92046928405762</t>
   </si>
   <si>
     <t xml:space="preserve">7.27828359603882</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92860126495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99365901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10750770568848</t>
+    <t xml:space="preserve">6.92860078811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9936580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10750818252563</t>
   </si>
   <si>
     <t xml:space="preserve">7.29454898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.457190990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26201963424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18069839477539</t>
+    <t xml:space="preserve">7.45719194412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26202011108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18069696426392</t>
   </si>
   <si>
     <t xml:space="preserve">7.31081247329712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47345590591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48972034454346</t>
+    <t xml:space="preserve">7.47345542907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48971939086914</t>
   </si>
   <si>
     <t xml:space="preserve">7.70115661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70928812026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44905948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40839767456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82288312911987</t>
+    <t xml:space="preserve">7.70928859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44905853271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40839862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82288265228271</t>
   </si>
   <si>
     <t xml:space="preserve">6.87980794906616</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86354207992554</t>
+    <t xml:space="preserve">6.86354398727417</t>
   </si>
   <si>
     <t xml:space="preserve">7.09124422073364</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38400173187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53851413726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60356903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57104206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78247690200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99391460418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94512128829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86379909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82313871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90445995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79874134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83127212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72555255889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57917261123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61983346939087</t>
+    <t xml:space="preserve">7.38400268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53851366043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60357046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57104158401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78247737884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99391412734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94512176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86380004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82313776016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90446043014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79874229431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83127164840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72555303573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57917356491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61983442306519</t>
   </si>
   <si>
     <t xml:space="preserve">7.44092655181885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56290912628174</t>
+    <t xml:space="preserve">7.56291055679321</t>
   </si>
   <si>
     <t xml:space="preserve">7.84753465652466</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26227474212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13216018676758</t>
+    <t xml:space="preserve">8.26227569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13216114044189</t>
   </si>
   <si>
     <t xml:space="preserve">8.14842510223389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05083847045898</t>
+    <t xml:space="preserve">8.0508394241333</t>
   </si>
   <si>
     <t xml:space="preserve">8.11589527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8719310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55477666854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69302415847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75808095932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37612533569336</t>
+    <t xml:space="preserve">7.87193202972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55477714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69302272796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75808238983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37612628936768</t>
   </si>
   <si>
     <t xml:space="preserve">8.24601078033447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21348285675049</t>
+    <t xml:space="preserve">8.2134838104248</t>
   </si>
   <si>
     <t xml:space="preserve">8.0589714050293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79060983657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07523441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1240291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98578214645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92072534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.018310546875</t>
+    <t xml:space="preserve">7.79061031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07523632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12402820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9857816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92072439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01830863952637</t>
   </si>
   <si>
     <t xml:space="preserve">8.06710338592529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95325231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71742105484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73368549346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92885684967041</t>
+    <t xml:space="preserve">7.9532527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7174186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7336859703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92885541915894</t>
   </si>
   <si>
     <t xml:space="preserve">8.0833683013916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57129764556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65261936187744</t>
+    <t xml:space="preserve">8.57129669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65262031555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.45744705200195</t>
   </si>
   <si>
+    <t xml:space="preserve">8.44118309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53991031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37536430358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30954742431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50700092315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91836357116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06645584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34618282318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39554691314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46136474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52718257904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60945510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56009101867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54363822937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32972812652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36263751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37909126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2145471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16518306732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01709175109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88545608520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03354454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11581993103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81963729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73736381530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83609199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95127296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90190982818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72091007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42472839355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57281875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58927345275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63863849639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60572910308838</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.44118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53991031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37536525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30954742431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50700187683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06645584106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34618282318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39554691314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46136474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52718257904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60945510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56009197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54363822937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3297290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36263751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3790922164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21454620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16518306732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01709175109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88545513153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03354549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11581993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81963634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73736476898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83609199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95127391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90190982818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72091007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42472839355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57281970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58927345275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63863658905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60572719573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44118309020996</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.40827369689941</t>
   </si>
   <si>
     <t xml:space="preserve">8.24372863769531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29309272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34245586395264</t>
+    <t xml:space="preserve">8.29309177398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34245491027832</t>
   </si>
   <si>
     <t xml:space="preserve">8.77027416229248</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">8.85254669189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68800067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80318164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08290958404541</t>
+    <t xml:space="preserve">8.68800258636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80318260192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08291053771973</t>
   </si>
   <si>
     <t xml:space="preserve">9.099365234375</t>
@@ -2720,55 +2720,55 @@
     <t xml:space="preserve">9.18163776397705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70445537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75381946563721</t>
+    <t xml:space="preserve">8.70445442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75382041931152</t>
   </si>
   <si>
     <t xml:space="preserve">8.65509223937988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6221809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55636501312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96772766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98418235778809</t>
+    <t xml:space="preserve">8.62218189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55636405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96772861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9841833114624</t>
   </si>
   <si>
     <t xml:space="preserve">8.35891056060791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27663707733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18613719940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26018238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14500045776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98045492172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99690961837769</t>
+    <t xml:space="preserve">8.27663612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18613624572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26018333435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14500141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98045539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99691009521484</t>
   </si>
   <si>
     <t xml:space="preserve">8.20259189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94754648208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93931865692139</t>
+    <t xml:space="preserve">7.94754552841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93931818008423</t>
   </si>
   <si>
     <t xml:space="preserve">8.03804683685303</t>
@@ -2777,16 +2777,16 @@
     <t xml:space="preserve">8.12854671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98868322372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13677310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89818286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95577383041382</t>
+    <t xml:space="preserve">7.98868274688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13677406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89818382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95577478408813</t>
   </si>
   <si>
     <t xml:space="preserve">8.0133638381958</t>
@@ -2795,91 +2795,91 @@
     <t xml:space="preserve">7.83236455917358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97222852706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08741092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10386562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1696834564209</t>
+    <t xml:space="preserve">7.97222757339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08740997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1038646697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16968250274658</t>
   </si>
   <si>
     <t xml:space="preserve">9.05000114440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00063705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13227462768555</t>
+    <t xml:space="preserve">9.00063800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13227367401123</t>
   </si>
   <si>
     <t xml:space="preserve">7.88995552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87349939346313</t>
+    <t xml:space="preserve">7.87349987030029</t>
   </si>
   <si>
     <t xml:space="preserve">7.569091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60200023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59377193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15772819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21531963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12481927871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39631843566895</t>
+    <t xml:space="preserve">7.60200119018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59377336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15772724151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21532011032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12481880187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3963189125061</t>
   </si>
   <si>
     <t xml:space="preserve">7.30581951141357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24000024795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69250059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5526385307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52795457839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33872842788696</t>
+    <t xml:space="preserve">7.24000120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69250106811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55263614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52795505523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33872747421265</t>
   </si>
   <si>
     <t xml:space="preserve">7.4621376991272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4045467376709</t>
+    <t xml:space="preserve">7.40454578399658</t>
   </si>
   <si>
     <t xml:space="preserve">7.44568252563477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65959215164185</t>
+    <t xml:space="preserve">7.65959119796753</t>
   </si>
   <si>
     <t xml:space="preserve">7.70895528793335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79945373535156</t>
+    <t xml:space="preserve">7.79945468902588</t>
   </si>
   <si>
     <t xml:space="preserve">8.21081829071045</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">8.12031936645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07918167114258</t>
+    <t xml:space="preserve">8.07918262481689</t>
   </si>
   <si>
     <t xml:space="preserve">7.79122829437256</t>
@@ -2897,70 +2897,70 @@
     <t xml:space="preserve">7.85704660415649</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02159214019775</t>
+    <t xml:space="preserve">8.02159118652344</t>
   </si>
   <si>
     <t xml:space="preserve">7.91463661193848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81590890884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78300094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70072889328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6760458946228</t>
+    <t xml:space="preserve">7.81590986251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78299999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70072841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67604637145996</t>
   </si>
   <si>
     <t xml:space="preserve">7.42922735214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29759120941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66781854629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48681974411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61022853851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68427515029907</t>
+    <t xml:space="preserve">7.29759216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66781902313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48681926727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61022806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6842737197876</t>
   </si>
   <si>
     <t xml:space="preserve">7.51149988174438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41277313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76654720306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65136384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7336368560791</t>
+    <t xml:space="preserve">7.41277408599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76654624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65136528015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73363637924194</t>
   </si>
   <si>
     <t xml:space="preserve">7.82413816452026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71718311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58554649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47036409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90268278121948</t>
+    <t xml:space="preserve">7.71718263626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58554601669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47036504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90268230438232</t>
   </si>
   <si>
     <t xml:space="preserve">6.72168254852295</t>
@@ -2975,19 +2975,19 @@
     <t xml:space="preserve">7.28936386108398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49504566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50327348709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37163591384888</t>
+    <t xml:space="preserve">7.49504613876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50327253341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37163734436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.42100143432617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51972818374634</t>
+    <t xml:space="preserve">7.51972913742065</t>
   </si>
   <si>
     <t xml:space="preserve">8.22727394104004</t>
@@ -2999,37 +2999,37 @@
     <t xml:space="preserve">8.02981948852539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09563732147217</t>
+    <t xml:space="preserve">8.09563636779785</t>
   </si>
   <si>
     <t xml:space="preserve">8.07095623016357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75009250640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80768251419067</t>
+    <t xml:space="preserve">7.75009202957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8076810836792</t>
   </si>
   <si>
     <t xml:space="preserve">7.84059190750122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84881925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54441022872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72540950775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31404590606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77477359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7395977973938</t>
+    <t xml:space="preserve">7.84882020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54441070556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72540998458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31404685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7747745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73959684371948</t>
   </si>
   <si>
     <t xml:space="preserve">7.63831520080566</t>
@@ -3038,34 +3038,34 @@
     <t xml:space="preserve">7.61299562454224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80711841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89151906967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96748065948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8746395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76491737365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81555843353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023790359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64675617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35979175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13190793991089</t>
+    <t xml:space="preserve">7.80711793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89152002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96748018264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87463903427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76491785049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81555891036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64675569534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35979127883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13190841674805</t>
   </si>
   <si>
     <t xml:space="preserve">7.25007009506226</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">7.05594682693481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04750633239746</t>
+    <t xml:space="preserve">7.04750728607178</t>
   </si>
   <si>
     <t xml:space="preserve">7.00530624389648</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">7.03906679153442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11502742767334</t>
+    <t xml:space="preserve">7.1150279045105</t>
   </si>
   <si>
     <t xml:space="preserve">7.17410850524902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09814786911011</t>
+    <t xml:space="preserve">7.09814739227295</t>
   </si>
   <si>
     <t xml:space="preserve">7.013747215271</t>
@@ -3104,16 +3104,16 @@
     <t xml:space="preserve">6.92090463638306</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99686622619629</t>
+    <t xml:space="preserve">6.99686574935913</t>
   </si>
   <si>
     <t xml:space="preserve">6.75210237503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76898336410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86182355880737</t>
+    <t xml:space="preserve">6.76898288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86182403564453</t>
   </si>
   <si>
     <t xml:space="preserve">6.98842620849609</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">6.92934465408325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83650398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89558410644531</t>
+    <t xml:space="preserve">6.8365044593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89558458328247</t>
   </si>
   <si>
     <t xml:space="preserve">6.91246461868286</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">7.02218627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96310567855835</t>
+    <t xml:space="preserve">6.96310520172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.06438732147217</t>
@@ -3161,40 +3161,40 @@
     <t xml:space="preserve">6.78586292266846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74366235733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77742290496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72678136825562</t>
+    <t xml:space="preserve">6.74366188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7774224281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72678184509277</t>
   </si>
   <si>
     <t xml:space="preserve">6.66770124435425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56641960144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38073635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46513748168945</t>
+    <t xml:space="preserve">6.56641912460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38073682785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46513795852661</t>
   </si>
   <si>
     <t xml:space="preserve">6.35541677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40605688095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21193504333496</t>
+    <t xml:space="preserve">6.40605735778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21193408966064</t>
   </si>
   <si>
     <t xml:space="preserve">6.22037410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24569511413574</t>
+    <t xml:space="preserve">6.24569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">6.16129350662231</t>
@@ -3203,19 +3203,19 @@
     <t xml:space="preserve">6.33009576797485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45669841766357</t>
+    <t xml:space="preserve">6.45669794082642</t>
   </si>
   <si>
     <t xml:space="preserve">6.28789520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16973304748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11909294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14441299438477</t>
+    <t xml:space="preserve">6.16973400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11909246444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14441347122192</t>
   </si>
   <si>
     <t xml:space="preserve">6.04313135147095</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">5.98405075073242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92496919631958</t>
+    <t xml:space="preserve">5.92496967315674</t>
   </si>
   <si>
     <t xml:space="preserve">6.03469133377075</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">5.87432909011841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69708633422852</t>
+    <t xml:space="preserve">5.69708585739136</t>
   </si>
   <si>
     <t xml:space="preserve">5.62956523895264</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">5.57048416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6211256980896</t>
+    <t xml:space="preserve">5.62112522125244</t>
   </si>
   <si>
     <t xml:space="preserve">5.5958046913147</t>
@@ -3272,16 +3272,16 @@
     <t xml:space="preserve">5.67176580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51140403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49452352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57892417907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64644527435303</t>
+    <t xml:space="preserve">5.51140356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4945240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57892513275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64644575119019</t>
   </si>
   <si>
     <t xml:space="preserve">5.5873646736145</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">5.82368850708008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07689237594604</t>
+    <t xml:space="preserve">6.07689189910889</t>
   </si>
   <si>
     <t xml:space="preserve">5.93341016769409</t>
@@ -3302,25 +3302,25 @@
     <t xml:space="preserve">5.79836750030518</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19505405426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00937080383301</t>
+    <t xml:space="preserve">6.19505453109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00937128067017</t>
   </si>
   <si>
     <t xml:space="preserve">5.90808916091919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85744905471802</t>
+    <t xml:space="preserve">5.85744857788086</t>
   </si>
   <si>
     <t xml:space="preserve">5.89964914321899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72240734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75616788864136</t>
+    <t xml:space="preserve">5.7224063873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75616693496704</t>
   </si>
   <si>
     <t xml:space="preserve">5.77304744720459</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">5.74772691726685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8912091255188</t>
+    <t xml:space="preserve">5.89120864868164</t>
   </si>
   <si>
     <t xml:space="preserve">5.76460742950439</t>
@@ -3347,13 +3347,13 @@
     <t xml:space="preserve">5.84900856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73084735870361</t>
+    <t xml:space="preserve">5.73084688186646</t>
   </si>
   <si>
     <t xml:space="preserve">5.80680799484253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65488576889038</t>
+    <t xml:space="preserve">5.65488529205322</t>
   </si>
   <si>
     <t xml:space="preserve">5.68020582199097</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">6.01781129837036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9165301322937</t>
+    <t xml:space="preserve">5.91652965545654</t>
   </si>
   <si>
     <t xml:space="preserve">6.22881460189819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41449689865112</t>
+    <t xml:space="preserve">6.41449737548828</t>
   </si>
   <si>
     <t xml:space="preserve">6.44825792312622</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">6.27945518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20349359512329</t>
+    <t xml:space="preserve">6.20349407196045</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001138687134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13597297668457</t>
+    <t xml:space="preserve">6.13597345352173</t>
   </si>
   <si>
     <t xml:space="preserve">6.11065244674683</t>
@@ -3404,40 +3404,40 @@
     <t xml:space="preserve">6.38917684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36385631561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43137741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33853626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3469762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32165622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30477476119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37229633331299</t>
+    <t xml:space="preserve">6.36385679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43137788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33853673934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34697675704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32165575027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30477571487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3722972869873</t>
   </si>
   <si>
     <t xml:space="preserve">6.31321573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97561073303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84056901931763</t>
+    <t xml:space="preserve">5.97561025619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84056854248047</t>
   </si>
   <si>
     <t xml:space="preserve">5.83212804794312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58330011367798</t>
+    <t xml:space="preserve">6.58329963684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.10221242904663</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">6.39761686325073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43302392959595</t>
+    <t xml:space="preserve">6.43302345275879</t>
   </si>
   <si>
     <t xml:space="preserve">6.47591114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27863168716431</t>
+    <t xml:space="preserve">6.27863216400146</t>
   </si>
   <si>
     <t xml:space="preserve">6.57026195526123</t>
@@ -3467,13 +3467,13 @@
     <t xml:space="preserve">6.77611875534058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75896406173706</t>
+    <t xml:space="preserve">6.75896453857422</t>
   </si>
   <si>
     <t xml:space="preserve">6.7503867149353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78469562530518</t>
+    <t xml:space="preserve">6.78469610214233</t>
   </si>
   <si>
     <t xml:space="preserve">6.88762426376343</t>
@@ -3485,43 +3485,43 @@
     <t xml:space="preserve">6.80185079574585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73323202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70749998092651</t>
+    <t xml:space="preserve">6.73323154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70750045776367</t>
   </si>
   <si>
     <t xml:space="preserve">6.690345287323</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64745855331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61314916610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81042766571045</t>
+    <t xml:space="preserve">6.64745807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61314821243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81042814254761</t>
   </si>
   <si>
     <t xml:space="preserve">6.86189222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74180889129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83616018295288</t>
+    <t xml:space="preserve">6.7418098449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83615970611572</t>
   </si>
   <si>
     <t xml:space="preserve">6.79327344894409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72465467453003</t>
+    <t xml:space="preserve">6.72465515136719</t>
   </si>
   <si>
     <t xml:space="preserve">6.69892263412476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71607732772827</t>
+    <t xml:space="preserve">6.71607685089111</t>
   </si>
   <si>
     <t xml:space="preserve">6.63888072967529</t>
@@ -3530,22 +3530,22 @@
     <t xml:space="preserve">6.62172603607178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38155937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39871454238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40729141235352</t>
+    <t xml:space="preserve">6.38156032562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39871501922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40729188919067</t>
   </si>
   <si>
     <t xml:space="preserve">6.5273756980896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5359525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59599447250366</t>
+    <t xml:space="preserve">6.53595209121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5959939956665</t>
   </si>
   <si>
     <t xml:space="preserve">6.63030338287354</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">6.48448848724365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65603590011597</t>
+    <t xml:space="preserve">6.65603542327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.76754140853882</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">6.85331439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93051099777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94766616821289</t>
+    <t xml:space="preserve">6.93051147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94766664505005</t>
   </si>
   <si>
     <t xml:space="preserve">6.87904739379883</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">6.84473752975464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10205888748169</t>
+    <t xml:space="preserve">7.10205841064453</t>
   </si>
   <si>
     <t xml:space="preserve">7.18783235549927</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">6.99913024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9219331741333</t>
+    <t xml:space="preserve">6.92193412780762</t>
   </si>
   <si>
     <t xml:space="preserve">6.91335678100586</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">7.17925500869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07632637023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09348201751709</t>
+    <t xml:space="preserve">7.0763258934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09348106384277</t>
   </si>
   <si>
     <t xml:space="preserve">7.20498609542847</t>
@@ -3623,28 +3623,28 @@
     <t xml:space="preserve">7.14494562149048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15352249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01628589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97339868545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98197555541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55310726165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35582780838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33867263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31294059753418</t>
+    <t xml:space="preserve">7.15352344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01628494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97339820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98197603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55310678482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35582733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33867311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31294107437134</t>
   </si>
   <si>
     <t xml:space="preserve">6.42444658279419</t>
@@ -3653,25 +3653,25 @@
     <t xml:space="preserve">6.26147699356079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20143508911133</t>
+    <t xml:space="preserve">6.20143556594849</t>
   </si>
   <si>
     <t xml:space="preserve">6.3215184211731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13281679153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.218590259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34725046157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29578590393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14997148513794</t>
+    <t xml:space="preserve">6.13281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21858978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34725093841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29578638076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14997100830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.10708427429199</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">6.16712617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03846549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00415563583374</t>
+    <t xml:space="preserve">6.03846502304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0041561126709</t>
   </si>
   <si>
     <t xml:space="preserve">5.89264965057373</t>
@@ -3707,25 +3707,25 @@
     <t xml:space="preserve">6.39013719558716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41586923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56168460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68176794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0591721534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95624351501465</t>
+    <t xml:space="preserve">6.41586875915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56168508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68176746368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05917119979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95624303817749</t>
   </si>
   <si>
     <t xml:space="preserve">7.03343915939331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11921310424805</t>
+    <t xml:space="preserve">7.11921358108521</t>
   </si>
   <si>
     <t xml:space="preserve">7.23929643630981</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">7.29933786392212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37653493881226</t>
+    <t xml:space="preserve">7.3765344619751</t>
   </si>
   <si>
     <t xml:space="preserve">7.55665969848633</t>
@@ -3746,70 +3746,70 @@
     <t xml:space="preserve">7.2907600402832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4365758895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38511085510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47946262359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46230840682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50519561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49661779403687</t>
+    <t xml:space="preserve">7.43657636642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3851113319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47946357727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46230745315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50519418716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49661684036255</t>
   </si>
   <si>
     <t xml:space="preserve">7.59954595565796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53092622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48803949356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40226602554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51377201080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35937976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34222459793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66816377639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81398057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6853199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67674207687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6081223487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69389724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90833139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0713005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2943115234375</t>
+    <t xml:space="preserve">7.53092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48803901672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40226697921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51377296447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35938024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34222507476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66816473007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81397867202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68531894683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67674255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60812282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69389677047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90833234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07130146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29431247711182</t>
   </si>
   <si>
     <t xml:space="preserve">8.23427104949951</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">7.96114015579224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97026062011719</t>
+    <t xml:space="preserve">7.97025966644287</t>
   </si>
   <si>
     <t xml:space="preserve">7.85170841217041</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">7.76051616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60548830032349</t>
+    <t xml:space="preserve">7.60548877716064</t>
   </si>
   <si>
     <t xml:space="preserve">7.6966814994812</t>
@@ -3842,25 +3842,25 @@
     <t xml:space="preserve">7.59636926651001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56901121139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61460781097412</t>
+    <t xml:space="preserve">7.56901168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61460876464844</t>
   </si>
   <si>
     <t xml:space="preserve">7.75139665603638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6237268447876</t>
+    <t xml:space="preserve">7.62372636795044</t>
   </si>
   <si>
     <t xml:space="preserve">7.73315858840942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65108585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76963567733765</t>
+    <t xml:space="preserve">7.6510853767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76963663101196</t>
   </si>
   <si>
     <t xml:space="preserve">7.77875518798828</t>
@@ -3869,28 +3869,28 @@
     <t xml:space="preserve">7.82435178756714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86994743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97938013076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84259080886841</t>
+    <t xml:space="preserve">7.869948387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97937917709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84258985519409</t>
   </si>
   <si>
     <t xml:space="preserve">7.74227809906006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78787469863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86082792282104</t>
+    <t xml:space="preserve">7.7878737449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86082887649536</t>
   </si>
   <si>
     <t xml:space="preserve">7.72403907775879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81523132324219</t>
+    <t xml:space="preserve">7.8152322769165</t>
   </si>
   <si>
     <t xml:space="preserve">7.71491956710815</t>
@@ -3899,22 +3899,22 @@
     <t xml:space="preserve">7.79699325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66932344436646</t>
+    <t xml:space="preserve">7.6693229675293</t>
   </si>
   <si>
     <t xml:space="preserve">7.24983596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20423984527588</t>
+    <t xml:space="preserve">7.20423936843872</t>
   </si>
   <si>
     <t xml:space="preserve">7.10392761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1677622795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22247838973999</t>
+    <t xml:space="preserve">7.16776275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22247791290283</t>
   </si>
   <si>
     <t xml:space="preserve">7.25895547866821</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">7.14952421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35926675796509</t>
+    <t xml:space="preserve">7.35926723480225</t>
   </si>
   <si>
     <t xml:space="preserve">7.47781801223755</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">7.64196586608887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99761819839478</t>
+    <t xml:space="preserve">7.99761915206909</t>
   </si>
   <si>
     <t xml:space="preserve">8.02497673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01585674285889</t>
+    <t xml:space="preserve">8.01585578918457</t>
   </si>
   <si>
     <t xml:space="preserve">8.09792995452881</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">8.00673675537109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15264511108398</t>
+    <t xml:space="preserve">8.1526460647583</t>
   </si>
   <si>
     <t xml:space="preserve">8.10704898834229</t>
@@ -3983,130 +3983,133 @@
     <t xml:space="preserve">8.04321384429932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27119731903076</t>
+    <t xml:space="preserve">8.27119636535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24383926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14217758178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90188550949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21611309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28080654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31777477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.484130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44716262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49337196350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61351776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52109813690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41019439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29928970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33625888824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20687103271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32701587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99430513381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94809579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04975700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04051494598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84643411636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13293552398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97582197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05900001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93885326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8094654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85567569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92961168289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82795000076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81870794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92036962509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76325511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80022382736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03127288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01278972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09596729278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18838691711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08672523498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22535419464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34549999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19762802124023</t>
   </si>
   <si>
     <t xml:space="preserve">8.2438383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14217758178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90188550949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21611309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28080654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31777477264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.484130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44716262817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49337196350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61351776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52109813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41019439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29928970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33625888824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20687103271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32701587677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99430513381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94809579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04975700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04051494598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84643411636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13293552398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97582197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05900001525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93885326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8094654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85567569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92961168289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82795000076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81870794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92036962509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76325511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80022382736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03127288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01278972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09596729278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18838691711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08672523498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22535419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34549999237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19762802124023</t>
   </si>
   <si>
     <t xml:space="preserve">7.86491775512695</t>
@@ -61788,7 +61791,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2184" t="s">
-        <v>1324</v>
+        <v>1365</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61814,7 +61817,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2185" t="s">
-        <v>1324</v>
+        <v>1365</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61866,7 +61869,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2187" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61892,7 +61895,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2188" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61944,7 +61947,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2190" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61996,7 +61999,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2192" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62100,7 +62103,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2196" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62126,7 +62129,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2197" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62152,7 +62155,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2198" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62230,7 +62233,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2201" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62256,7 +62259,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2202" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62360,7 +62363,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2206" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62386,7 +62389,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2207" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62438,7 +62441,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2209" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62464,7 +62467,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2210" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62516,7 +62519,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2212" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62594,7 +62597,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2215" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62620,7 +62623,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2216" t="s">
-        <v>1324</v>
+        <v>1365</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62646,7 +62649,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2217" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62672,7 +62675,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2218" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62698,7 +62701,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2219" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62724,7 +62727,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2220" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62776,7 +62779,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G2222" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62802,7 +62805,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2223" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62828,7 +62831,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2224" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62854,7 +62857,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2225" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62880,7 +62883,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2226" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62906,7 +62909,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G2227" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62932,7 +62935,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62958,7 +62961,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G2229" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62984,7 +62987,7 @@
         <v>9.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63010,7 +63013,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2231" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63036,7 +63039,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G2232" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63062,7 +63065,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2233" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63088,7 +63091,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2234" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63114,7 +63117,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2235" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63140,7 +63143,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2236" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63166,7 +63169,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63192,7 +63195,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63218,7 +63221,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2239" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63244,7 +63247,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2240" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63270,7 +63273,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2241" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63296,7 +63299,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2242" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63322,7 +63325,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2243" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63348,7 +63351,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2244" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63374,7 +63377,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2245" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63400,7 +63403,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G2246" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63426,7 +63429,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2247" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63452,7 +63455,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G2248" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63478,7 +63481,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2249" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63504,7 +63507,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2250" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63530,7 +63533,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2251" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63556,7 +63559,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2252" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63582,7 +63585,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2253" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63608,7 +63611,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2254" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63634,7 +63637,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2255" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63660,7 +63663,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2256" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63686,7 +63689,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2257" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63712,7 +63715,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2258" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63738,7 +63741,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2259" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63764,7 +63767,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2260" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63790,7 +63793,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63816,7 +63819,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2262" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63842,7 +63845,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2263" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63868,7 +63871,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2264" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63894,7 +63897,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2265" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63920,7 +63923,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2266" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63946,7 +63949,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2267" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63972,7 +63975,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63998,7 +64001,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2269" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64024,7 +64027,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2270" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64050,7 +64053,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2271" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64076,7 +64079,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2272" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64102,7 +64105,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2273" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64128,7 +64131,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2274" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64154,7 +64157,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2275" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64180,7 +64183,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2276" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64206,7 +64209,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2277" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64232,7 +64235,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64258,7 +64261,7 @@
         <v>10.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64284,7 +64287,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64310,7 +64313,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64336,7 +64339,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2282" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64362,7 +64365,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2283" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64388,7 +64391,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2284" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64414,7 +64417,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2285" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64440,7 +64443,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2286" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64466,7 +64469,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2287" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64492,7 +64495,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2288" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64518,7 +64521,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64544,7 +64547,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2290" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64570,7 +64573,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64596,7 +64599,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2292" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64622,7 +64625,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64648,7 +64651,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2294" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64674,7 +64677,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64700,7 +64703,7 @@
         <v>10</v>
       </c>
       <c r="G2296" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64726,7 +64729,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2297" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64752,7 +64755,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2298" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64778,7 +64781,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2299" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64804,7 +64807,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2300" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64830,7 +64833,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2301" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64856,7 +64859,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2302" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64882,7 +64885,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2303" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64908,7 +64911,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2304" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64934,7 +64937,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2305" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64960,7 +64963,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2306" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64986,7 +64989,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2307" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65012,7 +65015,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2308" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65038,7 +65041,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65064,7 +65067,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2310" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65090,7 +65093,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2311" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65116,7 +65119,7 @@
         <v>9.5</v>
       </c>
       <c r="G2312" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65142,7 +65145,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2313" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65168,7 +65171,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2314" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65194,7 +65197,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2315" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65220,7 +65223,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2316" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65246,7 +65249,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2317" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65272,7 +65275,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65298,7 +65301,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2319" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65324,7 +65327,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2320" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65350,7 +65353,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2321" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65376,7 +65379,7 @@
         <v>10.5</v>
       </c>
       <c r="G2322" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65402,7 +65405,7 @@
         <v>10.5</v>
       </c>
       <c r="G2323" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65428,7 +65431,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2324" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65454,7 +65457,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2325" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65480,7 +65483,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2326" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65506,7 +65509,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2327" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65532,7 +65535,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2328" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65558,7 +65561,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2329" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65584,7 +65587,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2330" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65610,7 +65613,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2331" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65636,7 +65639,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2332" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65662,7 +65665,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2333" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65688,7 +65691,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2334" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65714,7 +65717,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2335" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65740,7 +65743,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2336" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65766,7 +65769,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G2337" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65792,7 +65795,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2338" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65818,7 +65821,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2339" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65844,7 +65847,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2340" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65870,7 +65873,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2341" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65896,7 +65899,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2342" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65922,7 +65925,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2343" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65948,7 +65951,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2344" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65974,7 +65977,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66000,7 +66003,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2346" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66026,7 +66029,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2347" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66052,7 +66055,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2348" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66078,7 +66081,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2349" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66104,7 +66107,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66130,7 +66133,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2351" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66156,7 +66159,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2352" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66182,7 +66185,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2353" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66208,7 +66211,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2354" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66234,7 +66237,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66260,7 +66263,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66286,7 +66289,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2357" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66312,7 +66315,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2358" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66338,7 +66341,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66364,7 +66367,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2360" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66390,7 +66393,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2361" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66416,7 +66419,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2362" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66442,7 +66445,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2363" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66468,7 +66471,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66494,7 +66497,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2365" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66520,7 +66523,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2366" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66546,7 +66549,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66572,7 +66575,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66598,7 +66601,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2369" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66624,7 +66627,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2370" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66650,7 +66653,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2371" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66676,7 +66679,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2372" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66702,7 +66705,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2373" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66728,7 +66731,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2374" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66754,7 +66757,7 @@
         <v>11.5</v>
       </c>
       <c r="G2375" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66780,7 +66783,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2376" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66806,7 +66809,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2377" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66832,7 +66835,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2378" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66858,7 +66861,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2379" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66884,7 +66887,7 @@
         <v>11.5</v>
       </c>
       <c r="G2380" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66910,7 +66913,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2381" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66936,7 +66939,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2382" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66962,7 +66965,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2383" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66988,7 +66991,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2384" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67014,7 +67017,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2385" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67040,7 +67043,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2386" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67066,7 +67069,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2387" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67092,7 +67095,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2388" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67118,7 +67121,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2389" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67144,7 +67147,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2390" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67170,7 +67173,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2391" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67196,7 +67199,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G2392" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67222,7 +67225,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2393" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67248,7 +67251,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2394" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67274,7 +67277,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G2395" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67300,7 +67303,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2396" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67326,7 +67329,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2397" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67352,7 +67355,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2398" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67378,7 +67381,7 @@
         <v>9.75</v>
       </c>
       <c r="G2399" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67404,7 +67407,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2400" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67430,7 +67433,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67456,7 +67459,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2402" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67482,7 +67485,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2403" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67508,7 +67511,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2404" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67534,7 +67537,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67560,7 +67563,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2406" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67586,7 +67589,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2407" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67612,7 +67615,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2408" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67638,7 +67641,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2409" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67664,7 +67667,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2410" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67690,7 +67693,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2411" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67716,7 +67719,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2412" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67742,7 +67745,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2413" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67768,7 +67771,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2414" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67794,7 +67797,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2415" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67820,7 +67823,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2416" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67846,7 +67849,7 @@
         <v>9.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67872,7 +67875,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2418" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67898,7 +67901,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2419" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67924,7 +67927,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2420" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67950,7 +67953,7 @@
         <v>9.75</v>
       </c>
       <c r="G2421" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67976,7 +67979,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G2422" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68002,7 +68005,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2423" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68028,7 +68031,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2424" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68054,7 +68057,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2425" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68080,7 +68083,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2426" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68106,7 +68109,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2427" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68132,7 +68135,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68158,7 +68161,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G2429" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68184,7 +68187,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2430" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68210,7 +68213,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2431" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68236,7 +68239,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2432" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68262,7 +68265,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2433" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68288,7 +68291,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2434" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68314,7 +68317,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2435" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68340,7 +68343,7 @@
         <v>8.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68366,7 +68369,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2437" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68392,7 +68395,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68418,7 +68421,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68444,7 +68447,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2440" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68470,7 +68473,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2441" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68496,7 +68499,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2442" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68522,7 +68525,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68548,7 +68551,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68574,7 +68577,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2445" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68600,7 +68603,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2446" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68626,7 +68629,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2447" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68652,7 +68655,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2448" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68678,7 +68681,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2449" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68704,7 +68707,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2450" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68730,7 +68733,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2451" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68756,7 +68759,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2452" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68782,7 +68785,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2453" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68808,7 +68811,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2454" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68834,7 +68837,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2455" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68860,7 +68863,7 @@
         <v>8.75</v>
       </c>
       <c r="G2456" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68886,7 +68889,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2457" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68912,7 +68915,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2458" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68938,7 +68941,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68964,7 +68967,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2460" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68990,7 +68993,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2461" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69016,7 +69019,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2462" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69042,7 +69045,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2463" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69068,7 +69071,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2464" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69094,7 +69097,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2465" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69120,7 +69123,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G2466" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69146,7 +69149,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69172,7 +69175,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69198,7 +69201,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69224,7 +69227,7 @@
         <v>9</v>
       </c>
       <c r="G2470" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69250,7 +69253,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2471" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69276,7 +69279,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2472" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69302,7 +69305,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2473" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69328,7 +69331,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2474" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69354,7 +69357,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2475" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69380,7 +69383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69406,7 +69409,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2477" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69432,7 +69435,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69458,7 +69461,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2479" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69484,7 +69487,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2480" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69510,7 +69513,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2481" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69536,7 +69539,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2482" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69562,7 +69565,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2483" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69588,7 +69591,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2484" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69614,7 +69617,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2485" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69640,7 +69643,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2486" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69666,7 +69669,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2487" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69692,7 +69695,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2488" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69718,7 +69721,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2489" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69744,7 +69747,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2490" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69770,7 +69773,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2491" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69796,7 +69799,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2492" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69822,7 +69825,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2493" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69848,7 +69851,7 @@
         <v>9.75</v>
       </c>
       <c r="G2494" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69874,7 +69877,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2495" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69900,7 +69903,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2496" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69926,7 +69929,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2497" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69952,7 +69955,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2498" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69978,7 +69981,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2499" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70004,7 +70007,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2500" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70012,7 +70015,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6911805556</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>92436</v>
@@ -70030,9 +70033,35 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2501" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911574074</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>92996</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>9.5600004196167</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>9.43000030517578</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>9.51000022888184</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1477</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="1553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1555">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08278560638428</t>
+    <t xml:space="preserve">8.08278465270996</t>
   </si>
   <si>
     <t xml:space="preserve">8.05997180938721</t>
@@ -53,67 +53,67 @@
     <t xml:space="preserve">8.06757640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12840557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11319923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90029382705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87748241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52770948410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48969221115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95352172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79384183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67978572845459</t>
+    <t xml:space="preserve">8.12840747833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11319828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9002947807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87748193740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5277099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48969125747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95351982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79384279251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67978382110596</t>
   </si>
   <si>
     <t xml:space="preserve">7.62655925750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71019887924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89269113540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82425737380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60374784469604</t>
+    <t xml:space="preserve">7.71019983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89268922805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82425689697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6037483215332</t>
   </si>
   <si>
     <t xml:space="preserve">7.69499349594116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98393392562866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84706783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91550207138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01434993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20444297790527</t>
+    <t xml:space="preserve">7.98393440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84706687927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91550254821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01435089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20444488525391</t>
   </si>
   <si>
     <t xml:space="preserve">8.10559463500977</t>
@@ -122,61 +122,61 @@
     <t xml:space="preserve">8.24246215820312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25006484985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3032922744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15121841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23485946655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35651874542236</t>
+    <t xml:space="preserve">8.25006675720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30329322814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15121746063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23486042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.356520652771</t>
   </si>
   <si>
     <t xml:space="preserve">8.28808498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.219651222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36412334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29568672180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38693237304688</t>
+    <t xml:space="preserve">8.21965217590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36412143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29568862915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38693428039551</t>
   </si>
   <si>
     <t xml:space="preserve">8.14361476898193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18923568725586</t>
+    <t xml:space="preserve">8.18923759460449</t>
   </si>
   <si>
     <t xml:space="preserve">8.40974617004395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40214061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37932872772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51619815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82034778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80514049530029</t>
+    <t xml:space="preserve">8.40214252471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37932968139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51619625091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75191497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82034587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80513954162598</t>
   </si>
   <si>
     <t xml:space="preserve">8.82795333862305</t>
@@ -185,52 +185,52 @@
     <t xml:space="preserve">9.01044082641602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09408092498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98002624511719</t>
+    <t xml:space="preserve">9.09408187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9800271987915</t>
   </si>
   <si>
     <t xml:space="preserve">9.12449741363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1929292678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78993225097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11689376831055</t>
+    <t xml:space="preserve">9.19293117523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78993320465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11689281463623</t>
   </si>
   <si>
     <t xml:space="preserve">9.17772388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03325366973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0864782333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20053291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34500598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13970470428467</t>
+    <t xml:space="preserve">9.03325176239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08647918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20053482055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34500694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13970279693604</t>
   </si>
   <si>
     <t xml:space="preserve">9.61113739013672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67196846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65676021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80883312225342</t>
+    <t xml:space="preserve">9.67196655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65675926208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80883502960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.90008068084717</t>
@@ -239,52 +239,52 @@
     <t xml:space="preserve">9.7708158493042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73252964019775</t>
+    <t xml:space="preserve">9.73253059387207</t>
   </si>
   <si>
     <t xml:space="preserve">9.47217845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49515056610107</t>
+    <t xml:space="preserve">9.49515151977539</t>
   </si>
   <si>
     <t xml:space="preserve">9.57172393798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70190048217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77847480773926</t>
+    <t xml:space="preserve">9.70190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77847290039062</t>
   </si>
   <si>
     <t xml:space="preserve">9.67892837524414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69424343109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61001300811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6482982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51046657562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41857624053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26542854309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22714233398438</t>
+    <t xml:space="preserve">9.69424247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61001205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64829921722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51046562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41857814788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26542949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22714328765869</t>
   </si>
   <si>
     <t xml:space="preserve">9.18885612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11227989196777</t>
+    <t xml:space="preserve">9.11228275299072</t>
   </si>
   <si>
     <t xml:space="preserve">9.34200286865234</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">9.63298225402832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20416927337646</t>
+    <t xml:space="preserve">9.20417022705078</t>
   </si>
   <si>
     <t xml:space="preserve">9.21182727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30371570587158</t>
+    <t xml:space="preserve">9.30371475219727</t>
   </si>
   <si>
     <t xml:space="preserve">9.72487258911133</t>
@@ -314,34 +314,37 @@
     <t xml:space="preserve">9.59469699859619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53343677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75549983978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76315784454346</t>
+    <t xml:space="preserve">9.53343772888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75550270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76315975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77081680297852</t>
   </si>
   <si>
     <t xml:space="preserve">9.62532615661621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45686340332031</t>
+    <t xml:space="preserve">9.45686435699463</t>
   </si>
   <si>
     <t xml:space="preserve">9.78613185882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74784374237061</t>
+    <t xml:space="preserve">9.74784469604492</t>
   </si>
   <si>
     <t xml:space="preserve">9.71721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68658542633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6712703704834</t>
+    <t xml:space="preserve">9.68658447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67126941680908</t>
   </si>
   <si>
     <t xml:space="preserve">9.36497402191162</t>
@@ -350,55 +353,55 @@
     <t xml:space="preserve">9.56406688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57938194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80910396575928</t>
+    <t xml:space="preserve">9.57938289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80910205841064</t>
   </si>
   <si>
     <t xml:space="preserve">9.70955753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66361141204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74018859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51812267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44920635223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39560413360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35731792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54109382629395</t>
+    <t xml:space="preserve">9.66361236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7401876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51812171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44920539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39560508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3573169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54109477996826</t>
   </si>
   <si>
     <t xml:space="preserve">9.41091823577881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8014440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55641078948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79378986358643</t>
+    <t xml:space="preserve">9.80144596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55640983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79378795623779</t>
   </si>
   <si>
     <t xml:space="preserve">9.86270332336426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90865039825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93927764892578</t>
+    <t xml:space="preserve">9.90864944458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9392786026001</t>
   </si>
   <si>
     <t xml:space="preserve">9.92396354675293</t>
@@ -407,13 +410,13 @@
     <t xml:space="preserve">10.2226009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2685461044312</t>
+    <t xml:space="preserve">10.2685451507568</t>
   </si>
   <si>
     <t xml:space="preserve">10.283860206604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3910636901855</t>
+    <t xml:space="preserve">10.3910646438599</t>
   </si>
   <si>
     <t xml:space="preserve">10.4829521179199</t>
@@ -422,55 +425,55 @@
     <t xml:space="preserve">10.582498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7050180435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6437578201294</t>
+    <t xml:space="preserve">10.7050170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6437568664551</t>
   </si>
   <si>
     <t xml:space="preserve">10.7203311920166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3374633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4523220062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1843156814575</t>
+    <t xml:space="preserve">10.3374624252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4523210525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1843147277832</t>
   </si>
   <si>
     <t xml:space="preserve">10.077112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0694541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2379159927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617952346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95459175109863</t>
+    <t xml:space="preserve">10.0694532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2379179000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95459365844727</t>
   </si>
   <si>
     <t xml:space="preserve">9.870361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82441806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0388231277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98522281646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85504627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93161964416504</t>
+    <t xml:space="preserve">9.8244161605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0388240814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98522186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85504817962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93162059783936</t>
   </si>
   <si>
     <t xml:space="preserve">9.94693565368652</t>
@@ -479,31 +482,31 @@
     <t xml:space="preserve">9.89333438873291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0541391372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97756576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567638397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.161340713501</t>
+    <t xml:space="preserve">10.0541381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97756671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1613426208496</t>
   </si>
   <si>
     <t xml:space="preserve">10.5288972854614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5671834945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.490611076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2991752624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2608880996704</t>
+    <t xml:space="preserve">10.5671825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906101226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2991762161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2608871459961</t>
   </si>
   <si>
     <t xml:space="preserve">10.406379699707</t>
@@ -515,28 +518,28 @@
     <t xml:space="preserve">10.2455730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153993606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3221464157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2915182113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3987216949463</t>
+    <t xml:space="preserve">10.1153984069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3221473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2915191650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.398720741272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4982671737671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.429349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6054706573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5901565551758</t>
+    <t xml:space="preserve">10.4293508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.60546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5901556015015</t>
   </si>
   <si>
     <t xml:space="preserve">10.3757486343384</t>
@@ -545,55 +548,55 @@
     <t xml:space="preserve">10.253231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1460266113281</t>
+    <t xml:space="preserve">10.1460275650024</t>
   </si>
   <si>
     <t xml:space="preserve">10.3068342208862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4752950668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5212392807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4446659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3298034667969</t>
+    <t xml:space="preserve">10.4752960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5212383270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4446640014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3298053741455</t>
   </si>
   <si>
     <t xml:space="preserve">10.1230564117432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4216938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.781590461731</t>
+    <t xml:space="preserve">10.4216947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7815885543823</t>
   </si>
   <si>
     <t xml:space="preserve">11.2027463912964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1797752380371</t>
+    <t xml:space="preserve">11.1797742843628</t>
   </si>
   <si>
     <t xml:space="preserve">11.1338291168213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3329219818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2946348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4094944000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2793207168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3788661956787</t>
+    <t xml:space="preserve">11.3329210281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2946329116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.409496307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2793197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3788652420044</t>
   </si>
   <si>
     <t xml:space="preserve">11.6775035858154</t>
@@ -605,13 +608,13 @@
     <t xml:space="preserve">11.8383092880249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6468744277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5473289489746</t>
+    <t xml:space="preserve">11.6851606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6468753814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5473279953003</t>
   </si>
   <si>
     <t xml:space="preserve">11.401837348938</t>
@@ -629,13 +632,13 @@
     <t xml:space="preserve">11.7923641204834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2288370132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2441501617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3513536453247</t>
+    <t xml:space="preserve">12.228835105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2441492080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3513517379761</t>
   </si>
   <si>
     <t xml:space="preserve">12.4049549102783</t>
@@ -644,82 +647,82 @@
     <t xml:space="preserve">12.5198163986206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2549257278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5918474197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6301364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7832822799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2472686767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8184537887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6346778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7112493515015</t>
+    <t xml:space="preserve">13.2549238204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5918483734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6301355361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7832813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2472677230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.818452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6346769332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7112503051758</t>
   </si>
   <si>
     <t xml:space="preserve">13.0252017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8643970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2396087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2166376113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2089796066284</t>
+    <t xml:space="preserve">12.8643980026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2396078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2166385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2089786529541</t>
   </si>
   <si>
     <t xml:space="preserve">13.7373390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3621253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4004135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7143659591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5688762664795</t>
+    <t xml:space="preserve">13.3621273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.400411605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7143678665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5688743591309</t>
   </si>
   <si>
     <t xml:space="preserve">13.5152759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6684246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6148195266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.319299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3958721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3882169723511</t>
+    <t xml:space="preserve">13.6684226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6148204803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3192987442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3958740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3882179260254</t>
   </si>
   <si>
     <t xml:space="preserve">14.4341611862183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5490198135376</t>
+    <t xml:space="preserve">14.5490217208862</t>
   </si>
   <si>
     <t xml:space="preserve">14.6791944503784</t>
@@ -728,130 +731,130 @@
     <t xml:space="preserve">14.2810115814209</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3269567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4265041351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3422718048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5337066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2733535766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0359764099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512933731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9897308349609</t>
+    <t xml:space="preserve">14.3269577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4265060424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3422708511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5337076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2733564376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0359754562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9897298812866</t>
   </si>
   <si>
     <t xml:space="preserve">14.1282424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3975706100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4976081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0820722579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1436338424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590589523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.574559211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5976448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6592054367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3437042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3667888641357</t>
+    <t xml:space="preserve">14.397572517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4976100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0820713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1436319351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590570449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5745601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5976457595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6592063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3437051773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3667907714844</t>
   </si>
   <si>
     <t xml:space="preserve">14.3514013290405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2513647079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0435962677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5437793731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5822534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129253387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5360841751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4899139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6976804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6207294464111</t>
+    <t xml:space="preserve">14.2513637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0435953140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5437803268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.58225440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3129262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5360832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4899129867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.697681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6207304000854</t>
   </si>
   <si>
     <t xml:space="preserve">14.4591341018677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7742681503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0974636077881</t>
+    <t xml:space="preserve">13.7742652893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0974617004395</t>
   </si>
   <si>
     <t xml:space="preserve">13.8896942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9127798080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8973913192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2436714172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3898754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4129600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3821821212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4437417984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5591697692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7361583709717</t>
+    <t xml:space="preserve">13.9127788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.897388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.243670463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3898773193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4129619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3821811676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4437427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5591707229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7361574172974</t>
   </si>
   <si>
     <t xml:space="preserve">14.5053024291992</t>
@@ -860,127 +863,124 @@
     <t xml:space="preserve">14.5283899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4283542633057</t>
+    <t xml:space="preserve">14.4283504486084</t>
   </si>
   <si>
     <t xml:space="preserve">14.5514736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4360466003418</t>
+    <t xml:space="preserve">14.4360485076904</t>
   </si>
   <si>
     <t xml:space="preserve">14.274450302124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0512914657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9666481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6742315292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1205492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1590242385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1513261795044</t>
+    <t xml:space="preserve">13.9666471481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6742305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1205463409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1590261459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.151328086853</t>
   </si>
   <si>
     <t xml:space="preserve">13.8512182235718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9743413925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1744136810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2051944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0051212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3052282333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3590965270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.297534942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4206562042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3283157348633</t>
+    <t xml:space="preserve">13.9743394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1744117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2051935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0051193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3052310943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3590974807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2975378036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4206571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3283176422119</t>
   </si>
   <si>
     <t xml:space="preserve">14.336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3744869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2359733581543</t>
+    <t xml:space="preserve">14.3744878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2359743118286</t>
   </si>
   <si>
     <t xml:space="preserve">14.5129995346069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2205829620361</t>
+    <t xml:space="preserve">14.2205839157104</t>
   </si>
   <si>
     <t xml:space="preserve">14.1974964141846</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3902416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2440357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2517318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1670837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.105523109436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0670490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9208374023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9285354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8823652267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5206928253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2898406982422</t>
+    <t xml:space="preserve">15.3902425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2440376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2517337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1670866012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1055250167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1978664398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0670471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9208402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9285345077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.882363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5206909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2898397445679</t>
   </si>
   <si>
     <t xml:space="preserve">14.7515468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6438140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5668630599976</t>
+    <t xml:space="preserve">14.6438150405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5668640136719</t>
   </si>
   <si>
     <t xml:space="preserve">14.6515111923218</t>
@@ -989,103 +989,103 @@
     <t xml:space="preserve">14.7438526153564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7900228500366</t>
+    <t xml:space="preserve">14.7900218963623</t>
   </si>
   <si>
     <t xml:space="preserve">14.8361930847168</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7746343612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6361207962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207651138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4514379501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4668283462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5899496078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8131103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.851583480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1439981460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2902069091797</t>
+    <t xml:space="preserve">14.7746334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6361217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4514350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4668302536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5899486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8131084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8515815734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1439990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2902059555054</t>
   </si>
   <si>
     <t xml:space="preserve">15.3440723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5441446304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5826177597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.505672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4287204742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2209501266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9747076034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1286087036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.928900718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7365245819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8134765625</t>
+    <t xml:space="preserve">15.5441417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5826206207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.505669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4287166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2209510803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9747066497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1286096572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9289016723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7365226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8134746551514</t>
   </si>
   <si>
     <t xml:space="preserve">16.2367057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0828018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6210947036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0058536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1212768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6980495452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7749996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671194076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9131460189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8977527618408</t>
+    <t xml:space="preserve">16.0828037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6210966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0058517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1212787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6980485916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7749977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9131441116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8977546691895</t>
   </si>
   <si>
     <t xml:space="preserve">14.8054132461548</t>
@@ -1094,31 +1094,31 @@
     <t xml:space="preserve">15.1747798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0208768844604</t>
+    <t xml:space="preserve">15.0208740234375</t>
   </si>
   <si>
     <t xml:space="preserve">15.0516567230225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8208045959473</t>
+    <t xml:space="preserve">14.8208036422729</t>
   </si>
   <si>
     <t xml:space="preserve">15.0362691879272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9281721115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1128530502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2821445465088</t>
+    <t xml:space="preserve">13.9281692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1128520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2821435928345</t>
   </si>
   <si>
     <t xml:space="preserve">14.4822177886963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5588035583496</t>
+    <t xml:space="preserve">13.5588045120239</t>
   </si>
   <si>
     <t xml:space="preserve">13.7127065658569</t>
@@ -1127,88 +1127,88 @@
     <t xml:space="preserve">13.5434131622314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3125591278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2048263549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4510726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4356822967529</t>
+    <t xml:space="preserve">13.3125619888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2048292160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4510736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.43567943573</t>
   </si>
   <si>
     <t xml:space="preserve">13.2817802429199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6511468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3895120620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1432676315308</t>
+    <t xml:space="preserve">13.6511459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3895111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1432685852051</t>
   </si>
   <si>
     <t xml:space="preserve">13.0663166046143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0047559738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0509252548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2971715927124</t>
+    <t xml:space="preserve">13.0047550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0509271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2971706390381</t>
   </si>
   <si>
     <t xml:space="preserve">13.2356100082397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6357564926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8666095733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6819248199463</t>
+    <t xml:space="preserve">13.6357536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8666086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6819257736206</t>
   </si>
   <si>
     <t xml:space="preserve">13.8819971084595</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7130737304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9589509963989</t>
+    <t xml:space="preserve">14.7130718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9589490890503</t>
   </si>
   <si>
     <t xml:space="preserve">13.9512147903442</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8893489837646</t>
+    <t xml:space="preserve">13.889349937439</t>
   </si>
   <si>
     <t xml:space="preserve">13.7656135559082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9976196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0749530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5026741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.806658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3170700073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1469316482544</t>
+    <t xml:space="preserve">13.9976177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.074951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5026721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8066596984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3170709609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.146933555603</t>
   </si>
   <si>
     <t xml:space="preserve">13.2397365570068</t>
@@ -1217,127 +1217,127 @@
     <t xml:space="preserve">13.6109428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5336074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7192134857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4253387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4562749862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645427703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3789377212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3016042709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5490760803223</t>
+    <t xml:space="preserve">13.5336065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7192125320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4253377914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4562730789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3789405822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3016052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5490751266479</t>
   </si>
   <si>
     <t xml:space="preserve">13.8274812698364</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8738832473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6573448181152</t>
+    <t xml:space="preserve">13.8738813400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6573429107666</t>
   </si>
   <si>
     <t xml:space="preserve">14.0594854354858</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1213550567627</t>
+    <t xml:space="preserve">14.1213541030884</t>
   </si>
   <si>
     <t xml:space="preserve">14.0285511016846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9048166275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.966685295105</t>
+    <t xml:space="preserve">13.8584136962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9048147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9666833877563</t>
   </si>
   <si>
     <t xml:space="preserve">14.1986885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1058883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9202833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1677560806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5389623641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4925603866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4306926727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3688249588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3533582687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4616260528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6008291244507</t>
+    <t xml:space="preserve">14.1058864593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9202823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1677541732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5389642715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.492561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4306945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3688278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2914905548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3533563613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4616279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6008310317993</t>
   </si>
   <si>
     <t xml:space="preserve">13.7810802459717</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3842935562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5080280303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3224248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.569896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3069553375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1368198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1522884368896</t>
+    <t xml:space="preserve">14.3842926025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5080289840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3224239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5698976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.306957244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1368217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.152286529541</t>
   </si>
   <si>
     <t xml:space="preserve">13.6882781982422</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0130853652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4408054351807</t>
+    <t xml:space="preserve">14.0130844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2088031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4408073425293</t>
   </si>
   <si>
     <t xml:space="preserve">13.4872055053711</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">13.6728096008301</t>
   </si>
   <si>
-    <t xml:space="preserve">13.70374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5800094604492</t>
+    <t xml:space="preserve">13.7037439346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5800085067749</t>
   </si>
   <si>
     <t xml:space="preserve">12.6983909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6829242706299</t>
+    <t xml:space="preserve">12.6829233169556</t>
   </si>
   <si>
     <t xml:space="preserve">12.5746545791626</t>
@@ -1367,31 +1367,31 @@
     <t xml:space="preserve">12.9149284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0231981277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6674575805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2189130783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5591897964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2962503433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7394390106201</t>
+    <t xml:space="preserve">13.0232000350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6674556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2189149856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5591878890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2962493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7394380569458</t>
   </si>
   <si>
     <t xml:space="preserve">11.9714422225952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9405078887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0951776504517</t>
+    <t xml:space="preserve">11.9405088424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.095178604126</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570463180542</t>
@@ -1406,37 +1406,37 @@
     <t xml:space="preserve">11.8477077484131</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6621036529541</t>
+    <t xml:space="preserve">11.6621046066284</t>
   </si>
   <si>
     <t xml:space="preserve">11.6002359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5074348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1362257003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4402122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8887548446655</t>
+    <t xml:space="preserve">11.5074338912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1362266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4402112960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8887538909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.2599620819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.935154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0124893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3682308197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4455661773682</t>
+    <t xml:space="preserve">10.9351558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.012490272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3682298660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4455671310425</t>
   </si>
   <si>
     <t xml:space="preserve">11.5847682952881</t>
@@ -1445,22 +1445,22 @@
     <t xml:space="preserve">10.5175476074219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8286685943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3458576202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2973718643188</t>
+    <t xml:space="preserve">10.828667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3458566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2973728179932</t>
   </si>
   <si>
     <t xml:space="preserve">10.9418029785156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0226163864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6185607910156</t>
+    <t xml:space="preserve">11.0226144790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.618558883667</t>
   </si>
   <si>
     <t xml:space="preserve">11.1195869445801</t>
@@ -1472,28 +1472,28 @@
     <t xml:space="preserve">11.2165603637695</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0711002349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9902896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2327222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2488842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2003974914551</t>
+    <t xml:space="preserve">11.0711011886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9902906417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2327213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2488851547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2003984451294</t>
   </si>
   <si>
     <t xml:space="preserve">10.6832084655762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9094800949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8609914779663</t>
+    <t xml:space="preserve">10.909478187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8609924316406</t>
   </si>
   <si>
     <t xml:space="preserve">11.4751558303833</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.5721273422241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6367778778076</t>
+    <t xml:space="preserve">11.6367769241333</t>
   </si>
   <si>
     <t xml:space="preserve">11.5559673309326</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">11.5236434936523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7801818847656</t>
+    <t xml:space="preserve">10.7801828384399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8933172225952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0549383163452</t>
+    <t xml:space="preserve">11.0549392700195</t>
   </si>
   <si>
     <t xml:space="preserve">10.9579658508301</t>
@@ -1538,34 +1538,34 @@
     <t xml:space="preserve">11.1357488632202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0872640609741</t>
+    <t xml:space="preserve">11.0872631072998</t>
   </si>
   <si>
     <t xml:space="preserve">11.3296957015991</t>
   </si>
   <si>
-    <t xml:space="preserve">11.604453086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8792095184326</t>
+    <t xml:space="preserve">11.6044521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8792104721069</t>
   </si>
   <si>
     <t xml:space="preserve">11.8630475997925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7337503433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6529407501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8468866348267</t>
+    <t xml:space="preserve">11.7337512969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6529397964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8468856811523</t>
   </si>
   <si>
     <t xml:space="preserve">11.4589939117432</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2650470733643</t>
+    <t xml:space="preserve">11.2650480270386</t>
   </si>
   <si>
     <t xml:space="preserve">11.3620204925537</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">11.0387773513794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6508846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5539112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5215864181519</t>
+    <t xml:space="preserve">10.6508836746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5539121627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5215873718262</t>
   </si>
   <si>
     <t xml:space="preserve">10.1013698577881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98823356628418</t>
+    <t xml:space="preserve">9.98823261260986</t>
   </si>
   <si>
     <t xml:space="preserve">10.1821804046631</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">10.3922882080078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3114786148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.295316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3761253356934</t>
+    <t xml:space="preserve">10.3114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2953157424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.376127243042</t>
   </si>
   <si>
     <t xml:space="preserve">10.3599653244019</t>
@@ -1616,43 +1616,43 @@
     <t xml:space="preserve">10.3438024520874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5700740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7963428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1034240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1842365264893</t>
+    <t xml:space="preserve">10.5700731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7963447570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1034250259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">11.151912689209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4730987548828</t>
+    <t xml:space="preserve">10.4730997085571</t>
   </si>
   <si>
     <t xml:space="preserve">10.4569368362427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4084520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6670446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2465219497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5067529678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5880737304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7669811248779</t>
+    <t xml:space="preserve">10.4084510803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.667046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2465229034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5067520141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5880746841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7669801712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9458885192871</t>
@@ -1664,25 +1664,25 @@
     <t xml:space="preserve">10.7507171630859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3441095352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4416933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.311580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3278427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4254302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4904870986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5230150222778</t>
+    <t xml:space="preserve">10.344108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4416942596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3115797042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3278455734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4254283905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4904861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5230159759521</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555448532104</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">10.8157739639282</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8483028411865</t>
+    <t xml:space="preserve">10.8483037948608</t>
   </si>
   <si>
     <t xml:space="preserve">11.1410598754883</t>
@@ -1700,22 +1700,22 @@
     <t xml:space="preserve">10.9946813583374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8808317184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0922689437866</t>
+    <t xml:space="preserve">10.8808307647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.092267036438</t>
   </si>
   <si>
     <t xml:space="preserve">10.8970956802368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5718088150024</t>
+    <t xml:space="preserve">10.5718097686768</t>
   </si>
   <si>
     <t xml:space="preserve">10.669394493103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.636866569519</t>
+    <t xml:space="preserve">10.6368656158447</t>
   </si>
   <si>
     <t xml:space="preserve">10.6531314849854</t>
@@ -1727,64 +1727,64 @@
     <t xml:space="preserve">10.8320379257202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1085319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3037033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2223825454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5639324188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4338188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1573257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2386474609375</t>
+    <t xml:space="preserve">11.10853099823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3037042617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2223834991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5639333724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4338178634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1573247909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2386455535889</t>
   </si>
   <si>
     <t xml:space="preserve">11.7103118896484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7428398132324</t>
+    <t xml:space="preserve">11.7428388595581</t>
   </si>
   <si>
     <t xml:space="preserve">11.5476675033569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6452531814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.701922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7344512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6856603622437</t>
+    <t xml:space="preserve">11.6452541351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7019233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7344522476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.685658454895</t>
   </si>
   <si>
     <t xml:space="preserve">10.6043376922607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8645668029785</t>
+    <t xml:space="preserve">10.8645658493042</t>
   </si>
   <si>
     <t xml:space="preserve">10.4742240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6206016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2874383926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6127252578735</t>
+    <t xml:space="preserve">10.6206026077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2874393463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6127262115479</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314044952393</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">11.0597381591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0760021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1898527145386</t>
+    <t xml:space="preserve">11.0760040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1898536682129</t>
   </si>
   <si>
     <t xml:space="preserve">11.3850250244141</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">11.4012889862061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2549104690552</t>
+    <t xml:space="preserve">11.2549114227295</t>
   </si>
   <si>
     <t xml:space="preserve">11.3524951934814</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">12.0518627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3771476745605</t>
+    <t xml:space="preserve">12.3771486282349</t>
   </si>
   <si>
     <t xml:space="preserve">12.4259414672852</t>
@@ -1835,19 +1835,19 @@
     <t xml:space="preserve">12.1657123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3446216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2470350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5235271453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3934135437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4422073364258</t>
+    <t xml:space="preserve">12.3446187973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2470359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5235261917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3934125900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4422063827515</t>
   </si>
   <si>
     <t xml:space="preserve">12.6048498153687</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">12.3608846664429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.27956199646</t>
+    <t xml:space="preserve">12.2795639038086</t>
   </si>
   <si>
     <t xml:space="preserve">12.4096765518188</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">12.3283557891846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5964622497559</t>
+    <t xml:space="preserve">11.5964612960815</t>
   </si>
   <si>
     <t xml:space="preserve">11.4663467407227</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8404273986816</t>
+    <t xml:space="preserve">11.840425491333</t>
   </si>
   <si>
     <t xml:space="preserve">12.2958269119263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5560550689697</t>
+    <t xml:space="preserve">12.556056022644</t>
   </si>
   <si>
     <t xml:space="preserve">12.4584703445435</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">11.9705410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0681276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9380111694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0355968475342</t>
+    <t xml:space="preserve">12.0681257247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9380130767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0355978012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.8729553222656</t>
@@ -1907,46 +1907,46 @@
     <t xml:space="preserve">11.9542760848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9217481613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6777820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7916326522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7753686904907</t>
+    <t xml:space="preserve">11.9217462539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6777830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.791633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7753677368164</t>
   </si>
   <si>
     <t xml:space="preserve">11.1735877990723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3687601089478</t>
+    <t xml:space="preserve">11.3687591552734</t>
   </si>
   <si>
     <t xml:space="preserve">11.1247959136963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7832450866699</t>
+    <t xml:space="preserve">10.7832441329956</t>
   </si>
   <si>
     <t xml:space="preserve">10.7995090484619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4579582214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4091663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5392789840698</t>
+    <t xml:space="preserve">10.4579572677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4091653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5392799377441</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766374588013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2302589416504</t>
+    <t xml:space="preserve">10.2302579879761</t>
   </si>
   <si>
     <t xml:space="preserve">10.3603734970093</t>
@@ -1955,34 +1955,34 @@
     <t xml:space="preserve">9.36824989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2544002532959</t>
+    <t xml:space="preserve">9.25439929962158</t>
   </si>
   <si>
     <t xml:space="preserve">9.53089237213135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41704177856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18934154510498</t>
+    <t xml:space="preserve">9.41704273223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1893424987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.84779071807861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75020599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62009048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60382652282715</t>
+    <t xml:space="preserve">8.75020408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62009143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60382556915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.50623989105225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81500577926636</t>
+    <t xml:space="preserve">7.81500673294067</t>
   </si>
   <si>
     <t xml:space="preserve">7.42466306686401</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">6.43253898620605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11538457870483</t>
+    <t xml:space="preserve">6.11538505554199</t>
   </si>
   <si>
     <t xml:space="preserve">5.48920869827271</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">5.73317337036133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6111912727356</t>
+    <t xml:space="preserve">5.61119174957275</t>
   </si>
   <si>
     <t xml:space="preserve">5.30216884613037</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59492635726929</t>
+    <t xml:space="preserve">5.59492683410645</t>
   </si>
   <si>
     <t xml:space="preserve">5.56239795684814</t>
@@ -2039,19 +2039,19 @@
     <t xml:space="preserve">5.69251251220703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71690940856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01779842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74943780899048</t>
+    <t xml:space="preserve">5.71690893173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01779890060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74943828582764</t>
   </si>
   <si>
     <t xml:space="preserve">6.18044233322144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13164949417114</t>
+    <t xml:space="preserve">6.13164901733398</t>
   </si>
   <si>
     <t xml:space="preserve">6.05845928192139</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">6.15604543685913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54639005661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5301251411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61144685745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70903158187866</t>
+    <t xml:space="preserve">6.54638910293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53012466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61144733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70903301239014</t>
   </si>
   <si>
     <t xml:space="preserve">6.44067144393921</t>
@@ -2081,52 +2081,52 @@
     <t xml:space="preserve">6.74156141281128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50572872161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52199268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39187812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0015344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9690055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12351751327515</t>
+    <t xml:space="preserve">6.50572824478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5219931602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39187860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00153493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96900653839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1235179901123</t>
   </si>
   <si>
     <t xml:space="preserve">6.20483827590942</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18857383728027</t>
+    <t xml:space="preserve">6.18857431411743</t>
   </si>
   <si>
     <t xml:space="preserve">6.30242490768433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4975962638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63584327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87167596817017</t>
+    <t xml:space="preserve">6.49759674072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63584280014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87167549133301</t>
   </si>
   <si>
     <t xml:space="preserve">6.79035425186157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77409029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75782537460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91233730316162</t>
+    <t xml:space="preserve">6.77408933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75782632827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9123363494873</t>
   </si>
   <si>
     <t xml:space="preserve">7.39213418960571</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">7.59543800354004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40026664733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36773872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19696187973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80661821365356</t>
+    <t xml:space="preserve">7.40026760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36773824691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19696378707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80661869049072</t>
   </si>
   <si>
     <t xml:space="preserve">6.896071434021</t>
@@ -2153,46 +2153,46 @@
     <t xml:space="preserve">7.0587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83914756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85541105270386</t>
+    <t xml:space="preserve">6.83914709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85541152954102</t>
   </si>
   <si>
     <t xml:space="preserve">6.97739362716675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05058336257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14003705978394</t>
+    <t xml:space="preserve">7.05058431625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14003658294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.94486522674561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31894445419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28641700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1563024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08311128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00992298126221</t>
+    <t xml:space="preserve">7.31894397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28641557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15630149841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0831127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00992250442505</t>
   </si>
   <si>
     <t xml:space="preserve">7.02618741989136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16443490982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9529972076416</t>
+    <t xml:space="preserve">7.1644344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95299768447876</t>
   </si>
   <si>
     <t xml:space="preserve">7.01805448532104</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">6.66837167739868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51386117935181</t>
+    <t xml:space="preserve">6.51386022567749</t>
   </si>
   <si>
     <t xml:space="preserve">6.47320032119751</t>
@@ -2210,28 +2210,28 @@
     <t xml:space="preserve">6.73342943191528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71716547012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78222179412842</t>
+    <t xml:space="preserve">6.71716451644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78222227096558</t>
   </si>
   <si>
     <t xml:space="preserve">6.56265306472778</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58705043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60331392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40001058578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27802753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35935020446777</t>
+    <t xml:space="preserve">6.5870509147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60331439971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40001010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27802801132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35934972763062</t>
   </si>
   <si>
     <t xml:space="preserve">6.34308576583862</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">6.21297073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19670677185059</t>
+    <t xml:space="preserve">6.19670629501343</t>
   </si>
   <si>
     <t xml:space="preserve">5.97713804244995</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">5.94460964202881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78196620941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88768434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80636262893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79009866714478</t>
+    <t xml:space="preserve">5.78196668624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8876838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80636310577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79009819030762</t>
   </si>
   <si>
     <t xml:space="preserve">5.72504138946533</t>
@@ -2288,25 +2288,25 @@
     <t xml:space="preserve">6.16417789459229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22110366821289</t>
+    <t xml:space="preserve">6.22110319137573</t>
   </si>
   <si>
     <t xml:space="preserve">5.92834520339966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.107253074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03406381607056</t>
+    <t xml:space="preserve">6.10725355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03406286239624</t>
   </si>
   <si>
     <t xml:space="preserve">6.31055688858032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1723108291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92021369934082</t>
+    <t xml:space="preserve">6.17230939865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9202127456665</t>
   </si>
   <si>
     <t xml:space="preserve">5.75756978988647</t>
@@ -2315,25 +2315,25 @@
     <t xml:space="preserve">5.70064449310303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38349056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21271514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00127935409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96875047683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01754283905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0419397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24524354934692</t>
+    <t xml:space="preserve">5.38349008560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21271419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01754331588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04193925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24524307250977</t>
   </si>
   <si>
     <t xml:space="preserve">5.40788698196411</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">6.32682085037231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28615999221802</t>
+    <t xml:space="preserve">6.28616046905518</t>
   </si>
   <si>
     <t xml:space="preserve">6.36748218536377</t>
@@ -2351,70 +2351,70 @@
     <t xml:space="preserve">7.30268001556396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35960531234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23762273788452</t>
+    <t xml:space="preserve">7.54664468765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35960483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23762226104736</t>
   </si>
   <si>
     <t xml:space="preserve">7.22949028015137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12377262115479</t>
+    <t xml:space="preserve">7.12377309799194</t>
   </si>
   <si>
     <t xml:space="preserve">7.07497978210449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17256593704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21322679519653</t>
+    <t xml:space="preserve">7.17256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21322584152222</t>
   </si>
   <si>
     <t xml:space="preserve">7.06684732437134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96113061904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92046976089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27828359603882</t>
+    <t xml:space="preserve">6.96112966537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92046928405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27828407287598</t>
   </si>
   <si>
     <t xml:space="preserve">6.92860126495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99365901947021</t>
+    <t xml:space="preserve">6.99365854263306</t>
   </si>
   <si>
     <t xml:space="preserve">7.10750865936279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29454803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45719194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26202011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18069839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31081247329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47345542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48971939086914</t>
+    <t xml:space="preserve">7.29454851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.457190990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26201963424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18069744110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31081295013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47345495223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48971891403198</t>
   </si>
   <si>
     <t xml:space="preserve">7.70115566253662</t>
@@ -2423,76 +2423,76 @@
     <t xml:space="preserve">7.70928859710693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44905853271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40839767456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82288360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87980794906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86354398727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0912446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38400220870972</t>
+    <t xml:space="preserve">7.44905996322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40839815139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82288312911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87980842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86354351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09124374389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38400173187256</t>
   </si>
   <si>
     <t xml:space="preserve">7.53851366043091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60357046127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57104158401489</t>
+    <t xml:space="preserve">7.60356950759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57104253768921</t>
   </si>
   <si>
     <t xml:space="preserve">7.78247737884521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99391412734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94512176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86380004882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82313776016235</t>
+    <t xml:space="preserve">7.9939136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9451208114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86380052566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82313871383667</t>
   </si>
   <si>
     <t xml:space="preserve">7.90446043014526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79874324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83126974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72555208206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57917261123657</t>
+    <t xml:space="preserve">7.798743724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83127164840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72555255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57917404174805</t>
   </si>
   <si>
     <t xml:space="preserve">7.61983442306519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44092607498169</t>
+    <t xml:space="preserve">7.44092702865601</t>
   </si>
   <si>
     <t xml:space="preserve">7.5629096031189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84753465652466</t>
+    <t xml:space="preserve">7.84753513336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.26227569580078</t>
@@ -2504,46 +2504,46 @@
     <t xml:space="preserve">8.14842510223389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0508394241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11589527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87193202972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55477714538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69302463531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75808238983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37612724304199</t>
+    <t xml:space="preserve">8.05083847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11589622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87193155288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5547776222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6930251121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75808048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37612533569336</t>
   </si>
   <si>
     <t xml:space="preserve">8.24601078033447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21348094940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0589714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79061031341553</t>
+    <t xml:space="preserve">8.21348285675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05897235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79060983657837</t>
   </si>
   <si>
     <t xml:space="preserve">8.07523632049561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1240291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98578262329102</t>
+    <t xml:space="preserve">8.12402725219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98578214645386</t>
   </si>
   <si>
     <t xml:space="preserve">7.92072439193726</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">8.06710243225098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9532527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71742010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73368501663208</t>
+    <t xml:space="preserve">7.95325231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7174186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73368453979492</t>
   </si>
   <si>
     <t xml:space="preserve">7.92885637283325</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">8.57129669189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65261936187744</t>
+    <t xml:space="preserve">8.65262031555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.45744705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44118309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53991031646729</t>
+    <t xml:space="preserve">8.44118213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53990936279297</t>
   </si>
   <si>
     <t xml:space="preserve">8.37536430358887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30954647064209</t>
+    <t xml:space="preserve">8.30954551696777</t>
   </si>
   <si>
     <t xml:space="preserve">8.50700092315674</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">9.06645488739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34618282318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39554786682129</t>
+    <t xml:space="preserve">9.34618186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39554595947266</t>
   </si>
   <si>
     <t xml:space="preserve">9.46136474609375</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">9.60945510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56009101867676</t>
+    <t xml:space="preserve">9.56009197235107</t>
   </si>
   <si>
     <t xml:space="preserve">9.54363822937012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3297290802002</t>
+    <t xml:space="preserve">9.32972812652588</t>
   </si>
   <si>
     <t xml:space="preserve">9.36263751983643</t>
@@ -2636,64 +2636,64 @@
     <t xml:space="preserve">9.16518306732178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01709079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88545608520508</t>
+    <t xml:space="preserve">9.01709175109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88545513153076</t>
   </si>
   <si>
     <t xml:space="preserve">9.03354549407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11581993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81963729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73736381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83609104156494</t>
+    <t xml:space="preserve">9.11581897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8196382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7373628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83609199523926</t>
   </si>
   <si>
     <t xml:space="preserve">8.95127296447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90191078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72091007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.424729347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57281970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58927345275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63863849639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60572719573975</t>
+    <t xml:space="preserve">8.90190982818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72091102600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42472839355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57281875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58927249908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63863754272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60572814941406</t>
   </si>
   <si>
     <t xml:space="preserve">8.40827369689941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24372959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29309177398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34245491027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77027416229248</t>
+    <t xml:space="preserve">8.24372863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29309272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34245586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77027320861816</t>
   </si>
   <si>
     <t xml:space="preserve">8.85254669189453</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">9.099365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18163776397705</t>
+    <t xml:space="preserve">9.18163681030273</t>
   </si>
   <si>
     <t xml:space="preserve">8.70445537567139</t>
@@ -2720,58 +2720,58 @@
     <t xml:space="preserve">8.75381946563721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6550931930542</t>
+    <t xml:space="preserve">8.65509223937988</t>
   </si>
   <si>
     <t xml:space="preserve">8.62218189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55636405944824</t>
+    <t xml:space="preserve">8.55636501312256</t>
   </si>
   <si>
     <t xml:space="preserve">8.96772861480713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9841833114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35891056060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27663612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18613815307617</t>
+    <t xml:space="preserve">8.98418235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35890960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27663707733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18613624572754</t>
   </si>
   <si>
     <t xml:space="preserve">8.26018333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14500045776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98045444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99691009521484</t>
+    <t xml:space="preserve">8.14500141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98045492172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99690961837769</t>
   </si>
   <si>
     <t xml:space="preserve">8.20259189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94754648208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93931913375854</t>
+    <t xml:space="preserve">7.94754600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93931865692139</t>
   </si>
   <si>
     <t xml:space="preserve">8.03804683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1285457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98868274688721</t>
+    <t xml:space="preserve">8.12854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98868322372437</t>
   </si>
   <si>
     <t xml:space="preserve">8.13677406311035</t>
@@ -2780,25 +2780,25 @@
     <t xml:space="preserve">7.89818286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95577478408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01336479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83236455917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97222757339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08740901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10386371612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16968250274658</t>
+    <t xml:space="preserve">7.95577430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0133638381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83236360549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97222709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08741092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1038646697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1696834564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.05000114440918</t>
@@ -2810,31 +2810,31 @@
     <t xml:space="preserve">9.13227367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88995552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87349987030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60200071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59377336502075</t>
+    <t xml:space="preserve">7.88995599746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87350082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56909132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60200119018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59377241134644</t>
   </si>
   <si>
     <t xml:space="preserve">7.15772724151611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21531867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12481832504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39631843566895</t>
+    <t xml:space="preserve">7.21531963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12481880187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3963189125061</t>
   </si>
   <si>
     <t xml:space="preserve">7.30581951141357</t>
@@ -2843,31 +2843,31 @@
     <t xml:space="preserve">7.24000120162964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69250011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55263710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52795600891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745470046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3387279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46213674545288</t>
+    <t xml:space="preserve">7.69250106811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55263662338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52795553207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33872747421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4621376991272</t>
   </si>
   <si>
     <t xml:space="preserve">7.40454578399658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44568157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65959119796753</t>
+    <t xml:space="preserve">7.44568300247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65959167480469</t>
   </si>
   <si>
     <t xml:space="preserve">7.70895624160767</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">8.07918262481689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79122829437256</t>
+    <t xml:space="preserve">7.79122877120972</t>
   </si>
   <si>
     <t xml:space="preserve">7.85704660415649</t>
@@ -2897,52 +2897,52 @@
     <t xml:space="preserve">7.91463661193848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81590986251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78300094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70072841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67604541778564</t>
+    <t xml:space="preserve">7.81591081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78300046920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70072746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67604637145996</t>
   </si>
   <si>
     <t xml:space="preserve">7.42922735214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29759216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66781806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48682069778442</t>
+    <t xml:space="preserve">7.29759168624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66781854629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48681926727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.61022806167603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6842737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5115008354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41277408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76654624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65136432647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73363637924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82413721084595</t>
+    <t xml:space="preserve">7.68427419662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51150035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41277456283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76654529571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65136528015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73363733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82413864135742</t>
   </si>
   <si>
     <t xml:space="preserve">7.71718263626099</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">7.58554601669312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47036504745483</t>
+    <t xml:space="preserve">7.47036457061768</t>
   </si>
   <si>
     <t xml:space="preserve">6.90268230438232</t>
@@ -2963,19 +2963,19 @@
     <t xml:space="preserve">6.89445495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10836458206177</t>
+    <t xml:space="preserve">7.10836505889893</t>
   </si>
   <si>
     <t xml:space="preserve">7.28936386108398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49504613876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50327348709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37163734436035</t>
+    <t xml:space="preserve">7.49504661560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50327301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37163686752319</t>
   </si>
   <si>
     <t xml:space="preserve">7.42100143432617</t>
@@ -2984,55 +2984,55 @@
     <t xml:space="preserve">7.5197286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22727394104004</t>
+    <t xml:space="preserve">8.22727489471436</t>
   </si>
   <si>
     <t xml:space="preserve">8.15322780609131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02982044219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09563636779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07095623016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75009202957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80768203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84059190750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84881925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54441022872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72541093826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31404685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7747745513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73959684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63831520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61299562454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80711793899536</t>
+    <t xml:space="preserve">8.02981853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09563732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07095527648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75009250640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80768156051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84059143066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84881973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54440975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72541046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31404638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77477359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73959732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63831567764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61299610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80711889266968</t>
   </si>
   <si>
     <t xml:space="preserve">7.89151906967163</t>
@@ -3044,19 +3044,19 @@
     <t xml:space="preserve">7.87463903427124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76491785049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81555891036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023790359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64675569534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35979127883911</t>
+    <t xml:space="preserve">7.76491737365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81555795669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023742675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64675617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35979175567627</t>
   </si>
   <si>
     <t xml:space="preserve">7.13190793991089</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">7.25007009506226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05594730377197</t>
+    <t xml:space="preserve">7.05594635009766</t>
   </si>
   <si>
     <t xml:space="preserve">7.04750680923462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00530624389648</t>
+    <t xml:space="preserve">7.00530576705933</t>
   </si>
   <si>
     <t xml:space="preserve">7.16566848754883</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">7.11502742767334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17410850524902</t>
+    <t xml:space="preserve">7.17410898208618</t>
   </si>
   <si>
     <t xml:space="preserve">7.09814739227295</t>
@@ -3098,22 +3098,22 @@
     <t xml:space="preserve">6.92090463638306</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99686622619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75210189819336</t>
+    <t xml:space="preserve">6.99686574935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75210237503052</t>
   </si>
   <si>
     <t xml:space="preserve">6.76898288726807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86182403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98842620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93778562545776</t>
+    <t xml:space="preserve">6.86182355880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98842573165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93778610229492</t>
   </si>
   <si>
     <t xml:space="preserve">6.92934465408325</t>
@@ -3125,16 +3125,16 @@
     <t xml:space="preserve">6.89558458328247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91246461868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76054191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68458127975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69302129745483</t>
+    <t xml:space="preserve">6.9124641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76054239273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6845817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69302082061768</t>
   </si>
   <si>
     <t xml:space="preserve">6.9462251663208</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">7.14034795761108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02218675613403</t>
+    <t xml:space="preserve">7.02218627929688</t>
   </si>
   <si>
     <t xml:space="preserve">6.96310567855835</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">6.78586292266846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74366188049316</t>
+    <t xml:space="preserve">6.74366235733032</t>
   </si>
   <si>
     <t xml:space="preserve">6.7774224281311</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">6.46513795852661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35541725158691</t>
+    <t xml:space="preserve">6.3554162979126</t>
   </si>
   <si>
     <t xml:space="preserve">6.40605688095093</t>
@@ -3188,16 +3188,16 @@
     <t xml:space="preserve">6.22037410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24569511413574</t>
+    <t xml:space="preserve">6.24569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">6.16129350662231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33009624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45669794082642</t>
+    <t xml:space="preserve">6.33009576797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45669841766357</t>
   </si>
   <si>
     <t xml:space="preserve">6.28789520263672</t>
@@ -3206,49 +3206,49 @@
     <t xml:space="preserve">6.16973352432251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11909294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14441347122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04313135147095</t>
+    <t xml:space="preserve">6.11909246444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14441299438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04313182830811</t>
   </si>
   <si>
     <t xml:space="preserve">6.08533239364624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06845188140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88276863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95873022079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00093126296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98405075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92496919631958</t>
+    <t xml:space="preserve">6.06845235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8827691078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95873069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00093078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98405027389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92496967315674</t>
   </si>
   <si>
     <t xml:space="preserve">6.03469133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99249076843262</t>
+    <t xml:space="preserve">5.99249029159546</t>
   </si>
   <si>
     <t xml:space="preserve">5.87432909011841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69708585739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62956523895264</t>
+    <t xml:space="preserve">5.69708633422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62956476211548</t>
   </si>
   <si>
     <t xml:space="preserve">5.57048416137695</t>
@@ -3266,46 +3266,46 @@
     <t xml:space="preserve">5.67176580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51140403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57892465591431</t>
+    <t xml:space="preserve">5.51140356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49452352523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57892513275146</t>
   </si>
   <si>
     <t xml:space="preserve">5.64644527435303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5873646736145</t>
+    <t xml:space="preserve">5.58736419677734</t>
   </si>
   <si>
     <t xml:space="preserve">5.82368850708008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07689237594604</t>
+    <t xml:space="preserve">6.07689189910889</t>
   </si>
   <si>
     <t xml:space="preserve">5.93341016769409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05157136917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79836750030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19505453109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00937128067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90808916091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85744857788086</t>
+    <t xml:space="preserve">6.0515718460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79836797714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19505405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00937080383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90808963775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85744905471802</t>
   </si>
   <si>
     <t xml:space="preserve">5.89964914321899</t>
@@ -3314,28 +3314,28 @@
     <t xml:space="preserve">5.72240686416626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7561674118042</t>
+    <t xml:space="preserve">5.75616693496704</t>
   </si>
   <si>
     <t xml:space="preserve">5.77304744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74772691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89120864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76460742950439</t>
+    <t xml:space="preserve">5.747727394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8912091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76460790634155</t>
   </si>
   <si>
     <t xml:space="preserve">5.95029020309448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81524753570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70552587509155</t>
+    <t xml:space="preserve">5.81524801254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70552635192871</t>
   </si>
   <si>
     <t xml:space="preserve">5.84900856018066</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">5.65488576889038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68020582199097</t>
+    <t xml:space="preserve">5.68020629882812</t>
   </si>
   <si>
     <t xml:space="preserve">5.78148746490479</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">6.22881460189819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41449689865112</t>
+    <t xml:space="preserve">6.41449737548828</t>
   </si>
   <si>
     <t xml:space="preserve">6.44825792312622</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">6.29633522033691</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23725414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27945518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20349407196045</t>
+    <t xml:space="preserve">6.23725461959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27945470809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20349311828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.06001138687134</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">6.38917684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36385679244995</t>
+    <t xml:space="preserve">6.36385631561279</t>
   </si>
   <si>
     <t xml:space="preserve">6.43137788772583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33853673934937</t>
+    <t xml:space="preserve">6.33853626251221</t>
   </si>
   <si>
     <t xml:space="preserve">6.3469762802124</t>
@@ -3413,28 +3413,28 @@
     <t xml:space="preserve">6.32165622711182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30477523803711</t>
+    <t xml:space="preserve">6.30477571487427</t>
   </si>
   <si>
     <t xml:space="preserve">6.37229681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31321573257446</t>
+    <t xml:space="preserve">6.3132152557373</t>
   </si>
   <si>
     <t xml:space="preserve">5.97561073303223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84056901931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83212804794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58329963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10221242904663</t>
+    <t xml:space="preserve">5.84056806564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83212852478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58330011367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10221290588379</t>
   </si>
   <si>
     <t xml:space="preserve">6.09377193450928</t>
@@ -3446,22 +3446,22 @@
     <t xml:space="preserve">6.39761686325073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43302392959595</t>
+    <t xml:space="preserve">6.43302440643311</t>
   </si>
   <si>
     <t xml:space="preserve">6.47591114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27863216400146</t>
+    <t xml:space="preserve">6.27863168716431</t>
   </si>
   <si>
     <t xml:space="preserve">6.57026195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77611923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75896453857422</t>
+    <t xml:space="preserve">6.77611875534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75896406173706</t>
   </si>
   <si>
     <t xml:space="preserve">6.7503867149353</t>
@@ -3482,40 +3482,40 @@
     <t xml:space="preserve">6.73323202133179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70750045776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.690345287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64745807647705</t>
+    <t xml:space="preserve">6.70749998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69034576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64745855331421</t>
   </si>
   <si>
     <t xml:space="preserve">6.61314868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81042766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86189222335815</t>
+    <t xml:space="preserve">6.81042861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86189270019531</t>
   </si>
   <si>
     <t xml:space="preserve">6.74180936813354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83616018295288</t>
+    <t xml:space="preserve">6.83615970611572</t>
   </si>
   <si>
     <t xml:space="preserve">6.79327344894409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72465515136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69892263412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71607732772827</t>
+    <t xml:space="preserve">6.72465467453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6989221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71607685089111</t>
   </si>
   <si>
     <t xml:space="preserve">6.63888072967529</t>
@@ -3524,40 +3524,40 @@
     <t xml:space="preserve">6.62172603607178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3815598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39871501922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40729141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5273756980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5359525680542</t>
+    <t xml:space="preserve">6.38156032562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39871454238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40729188919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52737522125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53595209121704</t>
   </si>
   <si>
     <t xml:space="preserve">6.5959939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63030290603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57883977890015</t>
+    <t xml:space="preserve">6.63030385971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57883930206299</t>
   </si>
   <si>
     <t xml:space="preserve">6.48448848724365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65603590011597</t>
+    <t xml:space="preserve">6.65603542327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.76754140853882</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85331439971924</t>
+    <t xml:space="preserve">6.8533148765564</t>
   </si>
   <si>
     <t xml:space="preserve">6.93051147460938</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">6.84473752975464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10205888748169</t>
+    <t xml:space="preserve">7.10205841064453</t>
   </si>
   <si>
     <t xml:space="preserve">7.18783235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13636827468872</t>
+    <t xml:space="preserve">7.1363673210144</t>
   </si>
   <si>
     <t xml:space="preserve">6.99055290222168</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">6.9047794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99913024902344</t>
+    <t xml:space="preserve">6.99912977218628</t>
   </si>
   <si>
     <t xml:space="preserve">6.92193365097046</t>
@@ -3596,37 +3596,37 @@
     <t xml:space="preserve">6.91335678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12779140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24787330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17925500869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0763258934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09348154067993</t>
+    <t xml:space="preserve">7.12779092788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24787378311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17925453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07632637023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09348106384277</t>
   </si>
   <si>
     <t xml:space="preserve">7.20498609542847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14494562149048</t>
+    <t xml:space="preserve">7.14494514465332</t>
   </si>
   <si>
     <t xml:space="preserve">7.15352296829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01628589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97339868545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98197555541992</t>
+    <t xml:space="preserve">7.01628494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97339820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98197603225708</t>
   </si>
   <si>
     <t xml:space="preserve">6.55310726165771</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">6.35582780838013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33867263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31294107437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42444658279419</t>
+    <t xml:space="preserve">6.33867311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3129415512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42444705963135</t>
   </si>
   <si>
     <t xml:space="preserve">6.26147699356079</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">6.3215184211731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13281679153442</t>
+    <t xml:space="preserve">6.13281631469727</t>
   </si>
   <si>
     <t xml:space="preserve">6.21858978271484</t>
@@ -3665,19 +3665,19 @@
     <t xml:space="preserve">6.29578638076782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14997148513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10708427429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16712617874146</t>
+    <t xml:space="preserve">6.14997053146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10708379745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1671257019043</t>
   </si>
   <si>
     <t xml:space="preserve">6.03846502304077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00415563583374</t>
+    <t xml:space="preserve">6.0041561126709</t>
   </si>
   <si>
     <t xml:space="preserve">5.89264965057373</t>
@@ -3686,10 +3686,10 @@
     <t xml:space="preserve">5.96126890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96984672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08135271072388</t>
+    <t xml:space="preserve">5.96984624862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08135223388672</t>
   </si>
   <si>
     <t xml:space="preserve">6.12423896789551</t>
@@ -3698,25 +3698,25 @@
     <t xml:space="preserve">6.45875644683838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39013719558716</t>
+    <t xml:space="preserve">6.39013767242432</t>
   </si>
   <si>
     <t xml:space="preserve">6.41586923599243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56168460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68176746368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05917167663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95624351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03343915939331</t>
+    <t xml:space="preserve">6.56168508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68176794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05917119979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95624256134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03343963623047</t>
   </si>
   <si>
     <t xml:space="preserve">7.11921358108521</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">7.23929643630981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29933786392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37653541564941</t>
+    <t xml:space="preserve">7.29933834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3765344619751</t>
   </si>
   <si>
     <t xml:space="preserve">7.55665969848633</t>
@@ -3737,25 +3737,25 @@
     <t xml:space="preserve">7.44515323638916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2907600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43657541275024</t>
+    <t xml:space="preserve">7.29076099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43657636642456</t>
   </si>
   <si>
     <t xml:space="preserve">7.3851113319397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47946262359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46230840682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50519514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49661779403687</t>
+    <t xml:space="preserve">7.47946357727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46230792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50519466400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49661731719971</t>
   </si>
   <si>
     <t xml:space="preserve">7.59954595565796</t>
@@ -3764,13 +3764,13 @@
     <t xml:space="preserve">7.53092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48803901672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40226602554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51377201080322</t>
+    <t xml:space="preserve">7.48803949356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40226697921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51377248764038</t>
   </si>
   <si>
     <t xml:space="preserve">7.35938024520874</t>
@@ -3779,58 +3779,58 @@
     <t xml:space="preserve">7.34222507476807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66816377639771</t>
+    <t xml:space="preserve">7.66816425323486</t>
   </si>
   <si>
     <t xml:space="preserve">7.8139796257019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6853199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67674255371094</t>
+    <t xml:space="preserve">7.68531942367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67674160003662</t>
   </si>
   <si>
     <t xml:space="preserve">7.60812282562256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69389677047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90833234786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0713005065918</t>
+    <t xml:space="preserve">7.69389724731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9083309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07130146026611</t>
   </si>
   <si>
     <t xml:space="preserve">8.29431247711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2342700958252</t>
+    <t xml:space="preserve">8.23427104949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.37150859832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12528800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96114015579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97026062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85170841217041</t>
+    <t xml:space="preserve">8.12528896331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96113967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97026014328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85170936584473</t>
   </si>
   <si>
     <t xml:space="preserve">7.76051616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60548830032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6966814994812</t>
+    <t xml:space="preserve">7.60548877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69668102264404</t>
   </si>
   <si>
     <t xml:space="preserve">7.59636926651001</t>
@@ -3839,61 +3839,61 @@
     <t xml:space="preserve">7.56901121139526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61460781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75139665603638</t>
+    <t xml:space="preserve">7.61460876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75139713287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.6237268447876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73315858840942</t>
+    <t xml:space="preserve">7.73315811157227</t>
   </si>
   <si>
     <t xml:space="preserve">7.65108585357666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76963567733765</t>
+    <t xml:space="preserve">7.7696361541748</t>
   </si>
   <si>
     <t xml:space="preserve">7.77875518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82435178756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86994743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97938013076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84259080886841</t>
+    <t xml:space="preserve">7.82435131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.869948387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97937965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84259033203125</t>
   </si>
   <si>
     <t xml:space="preserve">7.74227809906006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78787469863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86082792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72403907775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81523132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71491956710815</t>
+    <t xml:space="preserve">7.78787422180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8608283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72403955459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8152322769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71492004394531</t>
   </si>
   <si>
     <t xml:space="preserve">7.79699325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66932344436646</t>
+    <t xml:space="preserve">7.6693229675293</t>
   </si>
   <si>
     <t xml:space="preserve">7.24983596801758</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">7.10392761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1677622795105</t>
+    <t xml:space="preserve">7.16776275634766</t>
   </si>
   <si>
     <t xml:space="preserve">7.22247838973999</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">7.08568906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99449634552002</t>
+    <t xml:space="preserve">6.99449586868286</t>
   </si>
   <si>
     <t xml:space="preserve">7.19512033462524</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">7.14952421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35926675796509</t>
+    <t xml:space="preserve">7.35926723480225</t>
   </si>
   <si>
     <t xml:space="preserve">7.47781801223755</t>
@@ -3941,22 +3941,22 @@
     <t xml:space="preserve">7.48693799972534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52341461181641</t>
+    <t xml:space="preserve">7.52341508865356</t>
   </si>
   <si>
     <t xml:space="preserve">7.64196586608887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99761819839478</t>
+    <t xml:space="preserve">7.99761915206909</t>
   </si>
   <si>
     <t xml:space="preserve">8.02497673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01585674285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09792995452881</t>
+    <t xml:space="preserve">8.01585578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09793090820312</t>
   </si>
   <si>
     <t xml:space="preserve">8.18000411987305</t>
@@ -3968,16 +3968,16 @@
     <t xml:space="preserve">8.00673675537109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15264511108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10704898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27119731903076</t>
+    <t xml:space="preserve">8.1526460647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1070499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.043212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27119636535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.2438383102417</t>
@@ -4671,6 +4671,12 @@
   </si>
   <si>
     <t xml:space="preserve">9.40999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42000007629395</t>
   </si>
 </sst>
 </file>
@@ -8641,7 +8647,7 @@
         <v>12.2111330032349</v>
       </c>
       <c r="G140" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8745,7 +8751,7 @@
         <v>12.0293064117432</v>
       </c>
       <c r="G144" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8771,7 +8777,7 @@
         <v>11.8187694549561</v>
       </c>
       <c r="G145" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8823,7 +8829,7 @@
         <v>12.2302732467651</v>
       </c>
       <c r="G147" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8849,7 +8855,7 @@
         <v>12.1824235916138</v>
       </c>
       <c r="G148" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8875,7 +8881,7 @@
         <v>12.1441440582275</v>
       </c>
       <c r="G149" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8901,7 +8907,7 @@
         <v>12.1058645248413</v>
       </c>
       <c r="G150" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8927,7 +8933,7 @@
         <v>12.0867252349854</v>
       </c>
       <c r="G151" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8953,7 +8959,7 @@
         <v>11.7039308547974</v>
       </c>
       <c r="G152" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8979,7 +8985,7 @@
         <v>11.9527473449707</v>
       </c>
       <c r="G153" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9031,7 +9037,7 @@
         <v>11.9718866348267</v>
       </c>
       <c r="G155" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9057,7 +9063,7 @@
         <v>12.2111330032349</v>
       </c>
       <c r="G156" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9135,7 +9141,7 @@
         <v>12.2302732467651</v>
       </c>
       <c r="G159" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9161,7 +9167,7 @@
         <v>12.2589826583862</v>
       </c>
       <c r="G160" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9187,7 +9193,7 @@
         <v>12.1345748901367</v>
       </c>
       <c r="G161" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9213,7 +9219,7 @@
         <v>12.0771551132202</v>
       </c>
       <c r="G162" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9239,7 +9245,7 @@
         <v>12.0771551132202</v>
       </c>
       <c r="G163" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9265,7 +9271,7 @@
         <v>12.1728544235229</v>
       </c>
       <c r="G164" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9317,7 +9323,7 @@
         <v>11.9718866348267</v>
       </c>
       <c r="G166" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9343,7 +9349,7 @@
         <v>11.8953275680542</v>
       </c>
       <c r="G167" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9369,7 +9375,7 @@
         <v>11.8092002868652</v>
       </c>
       <c r="G168" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9395,7 +9401,7 @@
         <v>11.8092002868652</v>
       </c>
       <c r="G169" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9447,7 +9453,7 @@
         <v>11.7422113418579</v>
       </c>
       <c r="G171" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9473,7 +9479,7 @@
         <v>11.6943607330322</v>
       </c>
       <c r="G172" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9525,7 +9531,7 @@
         <v>12.2302732467651</v>
       </c>
       <c r="G174" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9551,7 +9557,7 @@
         <v>11.9240379333496</v>
       </c>
       <c r="G175" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9577,7 +9583,7 @@
         <v>12.2589826583862</v>
       </c>
       <c r="G176" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9707,7 +9713,7 @@
         <v>11.7613496780396</v>
       </c>
       <c r="G181" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9759,7 +9765,7 @@
         <v>12.2494125366211</v>
       </c>
       <c r="G183" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9785,7 +9791,7 @@
         <v>12.0867252349854</v>
       </c>
       <c r="G184" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9811,7 +9817,7 @@
         <v>11.9431781768799</v>
       </c>
       <c r="G185" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9863,7 +9869,7 @@
         <v>12.2494125366211</v>
       </c>
       <c r="G187" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9889,7 +9895,7 @@
         <v>12.2398433685303</v>
       </c>
       <c r="G188" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9915,7 +9921,7 @@
         <v>11.9718866348267</v>
       </c>
       <c r="G189" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9967,7 +9973,7 @@
         <v>12.2494125366211</v>
       </c>
       <c r="G191" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9993,7 +9999,7 @@
         <v>12.3259716033936</v>
       </c>
       <c r="G192" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10019,7 +10025,7 @@
         <v>12.3259716033936</v>
       </c>
       <c r="G193" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10045,7 +10051,7 @@
         <v>12.3833913803101</v>
       </c>
       <c r="G194" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10071,7 +10077,7 @@
         <v>12.2589826583862</v>
       </c>
       <c r="G195" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10097,7 +10103,7 @@
         <v>12.421669960022</v>
       </c>
       <c r="G196" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10123,7 +10129,7 @@
         <v>12.402530670166</v>
       </c>
       <c r="G197" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10149,7 +10155,7 @@
         <v>12.3259716033936</v>
       </c>
       <c r="G198" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10175,7 +10181,7 @@
         <v>12.7757549285889</v>
       </c>
       <c r="G199" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10201,7 +10207,7 @@
         <v>12.8331737518311</v>
       </c>
       <c r="G200" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10227,7 +10233,7 @@
         <v>12.8523139953613</v>
       </c>
       <c r="G201" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10253,7 +10259,7 @@
         <v>12.986291885376</v>
       </c>
       <c r="G202" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10279,7 +10285,7 @@
         <v>13.1011295318604</v>
       </c>
       <c r="G203" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10305,7 +10311,7 @@
         <v>13.2255382537842</v>
       </c>
       <c r="G204" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10331,7 +10337,7 @@
         <v>13.3786563873291</v>
       </c>
       <c r="G205" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10357,7 +10363,7 @@
         <v>13.3020973205566</v>
       </c>
       <c r="G206" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10383,7 +10389,7 @@
         <v>13.3977947235107</v>
       </c>
       <c r="G207" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10409,7 +10415,7 @@
         <v>12.9193029403687</v>
       </c>
       <c r="G208" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10435,7 +10441,7 @@
         <v>13.0628499984741</v>
       </c>
       <c r="G209" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10461,7 +10467,7 @@
         <v>12.7279062271118</v>
       </c>
       <c r="G210" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10487,7 +10493,7 @@
         <v>12.7279062271118</v>
       </c>
       <c r="G211" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10513,7 +10519,7 @@
         <v>12.5939283370972</v>
       </c>
       <c r="G212" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10539,7 +10545,7 @@
         <v>12.7757549285889</v>
       </c>
       <c r="G213" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10565,7 +10571,7 @@
         <v>12.7757549285889</v>
       </c>
       <c r="G214" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10591,7 +10597,7 @@
         <v>12.584358215332</v>
       </c>
       <c r="G215" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10617,7 +10623,7 @@
         <v>12.7948951721191</v>
       </c>
       <c r="G216" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10643,7 +10649,7 @@
         <v>12.5747880935669</v>
       </c>
       <c r="G217" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10669,7 +10675,7 @@
         <v>12.3833913803101</v>
       </c>
       <c r="G218" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10773,7 +10779,7 @@
         <v>12.4408102035522</v>
       </c>
       <c r="G222" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10799,7 +10805,7 @@
         <v>12.3355417251587</v>
       </c>
       <c r="G223" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10825,7 +10831,7 @@
         <v>12.1058645248413</v>
       </c>
       <c r="G224" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10851,7 +10857,7 @@
         <v>12.2781219482422</v>
       </c>
       <c r="G225" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10877,7 +10883,7 @@
         <v>12.7757549285889</v>
       </c>
       <c r="G226" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10903,7 +10909,7 @@
         <v>12.4408102035522</v>
       </c>
       <c r="G227" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10929,7 +10935,7 @@
         <v>12.5460777282715</v>
       </c>
       <c r="G228" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10955,7 +10961,7 @@
         <v>12.4790887832642</v>
       </c>
       <c r="G229" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10981,7 +10987,7 @@
         <v>12.3164024353027</v>
       </c>
       <c r="G230" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11007,7 +11013,7 @@
         <v>12.4120998382568</v>
       </c>
       <c r="G231" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11033,7 +11039,7 @@
         <v>12.4312400817871</v>
       </c>
       <c r="G232" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11059,7 +11065,7 @@
         <v>12.3642511367798</v>
       </c>
       <c r="G233" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11085,7 +11091,7 @@
         <v>12.3164024353027</v>
       </c>
       <c r="G234" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11111,7 +11117,7 @@
         <v>12.5652179718018</v>
       </c>
       <c r="G235" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11137,7 +11143,7 @@
         <v>12.421669960022</v>
       </c>
       <c r="G236" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11163,7 +11169,7 @@
         <v>12.4695196151733</v>
       </c>
       <c r="G237" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11189,7 +11195,7 @@
         <v>12.3546810150146</v>
       </c>
       <c r="G238" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11215,7 +11221,7 @@
         <v>12.3833913803101</v>
       </c>
       <c r="G239" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11241,7 +11247,7 @@
         <v>12.6991958618164</v>
       </c>
       <c r="G240" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11267,7 +11273,7 @@
         <v>13.0628499984741</v>
       </c>
       <c r="G241" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11293,7 +11299,7 @@
         <v>13.1585493087769</v>
       </c>
       <c r="G242" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11319,7 +11325,7 @@
         <v>12.986291885376</v>
       </c>
       <c r="G243" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11345,7 +11351,7 @@
         <v>13.2063980102539</v>
       </c>
       <c r="G244" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11371,7 +11377,7 @@
         <v>13.1106996536255</v>
       </c>
       <c r="G245" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11397,7 +11403,7 @@
         <v>12.8714532852173</v>
       </c>
       <c r="G246" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11423,7 +11429,7 @@
         <v>12.8236036300659</v>
       </c>
       <c r="G247" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11449,7 +11455,7 @@
         <v>13.0054311752319</v>
       </c>
       <c r="G248" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11475,7 +11481,7 @@
         <v>13.0150012969971</v>
       </c>
       <c r="G249" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11501,7 +11507,7 @@
         <v>12.80446434021</v>
       </c>
       <c r="G250" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11527,7 +11533,7 @@
         <v>12.6417770385742</v>
       </c>
       <c r="G251" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11553,7 +11559,7 @@
         <v>12.7279062271118</v>
       </c>
       <c r="G252" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11579,7 +11585,7 @@
         <v>12.9001626968384</v>
       </c>
       <c r="G253" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11605,7 +11611,7 @@
         <v>12.8236036300659</v>
       </c>
       <c r="G254" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11631,7 +11637,7 @@
         <v>12.7948951721191</v>
       </c>
       <c r="G255" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11657,7 +11663,7 @@
         <v>12.8618841171265</v>
       </c>
       <c r="G256" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11683,7 +11689,7 @@
         <v>12.9958610534668</v>
       </c>
       <c r="G257" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11709,7 +11715,7 @@
         <v>13.1202697753906</v>
       </c>
       <c r="G258" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11735,7 +11741,7 @@
         <v>13.1585493087769</v>
       </c>
       <c r="G259" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11761,7 +11767,7 @@
         <v>13.034140586853</v>
       </c>
       <c r="G260" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11787,7 +11793,7 @@
         <v>13.2063980102539</v>
       </c>
       <c r="G261" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11813,7 +11819,7 @@
         <v>13.2542476654053</v>
       </c>
       <c r="G262" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11839,7 +11845,7 @@
         <v>13.2542476654053</v>
       </c>
       <c r="G263" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11865,7 +11871,7 @@
         <v>13.2351083755493</v>
       </c>
       <c r="G264" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11891,7 +11897,7 @@
         <v>13.3020973205566</v>
       </c>
       <c r="G265" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11917,7 +11923,7 @@
         <v>12.9671516418457</v>
       </c>
       <c r="G266" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11943,7 +11949,7 @@
         <v>12.8140344619751</v>
       </c>
       <c r="G267" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11969,7 +11975,7 @@
         <v>12.584358215332</v>
       </c>
       <c r="G268" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11995,7 +12001,7 @@
         <v>12.6800556182861</v>
       </c>
       <c r="G269" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12021,7 +12027,7 @@
         <v>12.8810234069824</v>
       </c>
       <c r="G270" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -12047,7 +12053,7 @@
         <v>12.7948951721191</v>
       </c>
       <c r="G271" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12073,7 +12079,7 @@
         <v>12.7757549285889</v>
       </c>
       <c r="G272" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12099,7 +12105,7 @@
         <v>13.0915603637695</v>
       </c>
       <c r="G273" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12125,7 +12131,7 @@
         <v>13.1106996536255</v>
       </c>
       <c r="G274" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12151,7 +12157,7 @@
         <v>13.1489791870117</v>
       </c>
       <c r="G275" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12177,7 +12183,7 @@
         <v>12.9671516418457</v>
       </c>
       <c r="G276" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12203,7 +12209,7 @@
         <v>13.0532808303833</v>
       </c>
       <c r="G277" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12229,7 +12235,7 @@
         <v>12.9097328186035</v>
       </c>
       <c r="G278" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12255,7 +12261,7 @@
         <v>13.0150012969971</v>
       </c>
       <c r="G279" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12281,7 +12287,7 @@
         <v>12.8523139953613</v>
       </c>
       <c r="G280" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12307,7 +12313,7 @@
         <v>12.584358215332</v>
       </c>
       <c r="G281" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12333,7 +12339,7 @@
         <v>12.6513471603394</v>
       </c>
       <c r="G282" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12359,7 +12365,7 @@
         <v>12.9097328186035</v>
       </c>
       <c r="G283" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12385,7 +12391,7 @@
         <v>12.9193029403687</v>
       </c>
       <c r="G284" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12411,7 +12417,7 @@
         <v>13.0245714187622</v>
       </c>
       <c r="G285" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12437,7 +12443,7 @@
         <v>12.8810234069824</v>
       </c>
       <c r="G286" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12463,7 +12469,7 @@
         <v>12.7279062271118</v>
       </c>
       <c r="G287" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12489,7 +12495,7 @@
         <v>13.1106996536255</v>
       </c>
       <c r="G288" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12515,7 +12521,7 @@
         <v>13.4743537902832</v>
       </c>
       <c r="G289" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12541,7 +12547,7 @@
         <v>14.000696182251</v>
       </c>
       <c r="G290" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12567,7 +12573,7 @@
         <v>13.9719867706299</v>
       </c>
       <c r="G291" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12593,7 +12599,7 @@
         <v>13.9145669937134</v>
       </c>
       <c r="G292" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12619,7 +12625,7 @@
         <v>14.163384437561</v>
       </c>
       <c r="G293" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12645,7 +12651,7 @@
         <v>14.1155338287354</v>
       </c>
       <c r="G294" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12671,7 +12677,7 @@
         <v>14.2590818405151</v>
       </c>
       <c r="G295" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12697,7 +12703,7 @@
         <v>14.0963945388794</v>
       </c>
       <c r="G296" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12723,7 +12729,7 @@
         <v>14.2208032608032</v>
       </c>
       <c r="G297" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12749,7 +12755,7 @@
         <v>14.5940265655518</v>
       </c>
       <c r="G298" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12775,7 +12781,7 @@
         <v>14.6323070526123</v>
       </c>
       <c r="G299" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12801,7 +12807,7 @@
         <v>14.794994354248</v>
       </c>
       <c r="G300" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12827,7 +12833,7 @@
         <v>14.6035966873169</v>
       </c>
       <c r="G301" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12853,7 +12859,7 @@
         <v>14.5557479858398</v>
       </c>
       <c r="G302" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12879,7 +12885,7 @@
         <v>14.4313402175903</v>
       </c>
       <c r="G303" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12905,7 +12911,7 @@
         <v>14.24951171875</v>
       </c>
       <c r="G304" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12931,7 +12937,7 @@
         <v>14.4313402175903</v>
       </c>
       <c r="G305" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12957,7 +12963,7 @@
         <v>14.4026298522949</v>
       </c>
       <c r="G306" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12983,7 +12989,7 @@
         <v>14.5461778640747</v>
       </c>
       <c r="G307" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13009,7 +13015,7 @@
         <v>14.5557479858398</v>
       </c>
       <c r="G308" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13035,7 +13041,7 @@
         <v>14.6418762207031</v>
       </c>
       <c r="G309" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13061,7 +13067,7 @@
         <v>14.7375745773315</v>
       </c>
       <c r="G310" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13087,7 +13093,7 @@
         <v>15.2830572128296</v>
       </c>
       <c r="G311" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13113,7 +13119,7 @@
         <v>15.3021955490112</v>
       </c>
       <c r="G312" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13139,7 +13145,7 @@
         <v>15.4361743927002</v>
       </c>
       <c r="G313" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13165,7 +13171,7 @@
         <v>15.5031633377075</v>
       </c>
       <c r="G314" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13191,7 +13197,7 @@
         <v>15.6467113494873</v>
       </c>
       <c r="G315" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13217,7 +13223,7 @@
         <v>16.5654163360596</v>
       </c>
       <c r="G316" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13243,7 +13249,7 @@
         <v>16.9864902496338</v>
       </c>
       <c r="G317" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13269,7 +13275,7 @@
         <v>17.0343399047852</v>
       </c>
       <c r="G318" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13295,7 +13301,7 @@
         <v>17.225736618042</v>
       </c>
       <c r="G319" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13321,7 +13327,7 @@
         <v>16.5558471679688</v>
       </c>
       <c r="G320" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13347,7 +13353,7 @@
         <v>16.0199356079102</v>
       </c>
       <c r="G321" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13373,7 +13379,7 @@
         <v>15.7902593612671</v>
       </c>
       <c r="G322" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13399,7 +13405,7 @@
         <v>15.8859567642212</v>
       </c>
       <c r="G323" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13425,7 +13431,7 @@
         <v>16.2783203125</v>
       </c>
       <c r="G324" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13451,7 +13457,7 @@
         <v>16.0773544311523</v>
       </c>
       <c r="G325" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13477,7 +13483,7 @@
         <v>16.5462760925293</v>
       </c>
       <c r="G326" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13503,7 +13509,7 @@
         <v>16.5558471679688</v>
       </c>
       <c r="G327" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13529,7 +13535,7 @@
         <v>16.5175685882568</v>
       </c>
       <c r="G328" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13555,7 +13561,7 @@
         <v>16.5079975128174</v>
       </c>
       <c r="G329" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13581,7 +13587,7 @@
         <v>17.1683177947998</v>
       </c>
       <c r="G330" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13607,7 +13613,7 @@
         <v>16.6993942260742</v>
       </c>
       <c r="G331" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13633,7 +13639,7 @@
         <v>16.7472438812256</v>
       </c>
       <c r="G332" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13659,7 +13665,7 @@
         <v>17.1396083831787</v>
       </c>
       <c r="G333" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13685,7 +13691,7 @@
         <v>16.9577808380127</v>
       </c>
       <c r="G334" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13711,7 +13717,7 @@
         <v>16.8907928466797</v>
       </c>
       <c r="G335" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13737,7 +13743,7 @@
         <v>17.0821895599365</v>
       </c>
       <c r="G336" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13763,7 +13769,7 @@
         <v>17.0151996612549</v>
       </c>
       <c r="G337" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13789,7 +13795,7 @@
         <v>17.8956260681152</v>
       </c>
       <c r="G338" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13815,7 +13821,7 @@
         <v>17.991325378418</v>
       </c>
       <c r="G339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13841,7 +13847,7 @@
         <v>17.9817562103271</v>
       </c>
       <c r="G340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13867,7 +13873,7 @@
         <v>18.0391750335693</v>
       </c>
       <c r="G341" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13893,7 +13899,7 @@
         <v>17.8956260681152</v>
       </c>
       <c r="G342" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13919,7 +13925,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G343" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13945,7 +13951,7 @@
         <v>18.3454093933105</v>
       </c>
       <c r="G344" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13971,7 +13977,7 @@
         <v>17.8956260681152</v>
       </c>
       <c r="G345" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13997,7 +14003,7 @@
         <v>17.8477783203125</v>
       </c>
       <c r="G346" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14023,7 +14029,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G347" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14049,7 +14055,7 @@
         <v>17.9051971435547</v>
       </c>
       <c r="G348" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14075,7 +14081,7 @@
         <v>18.0296058654785</v>
       </c>
       <c r="G349" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14101,7 +14107,7 @@
         <v>17.9243354797363</v>
       </c>
       <c r="G350" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14127,7 +14133,7 @@
         <v>18.1635837554932</v>
       </c>
       <c r="G351" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14153,7 +14159,7 @@
         <v>17.838207244873</v>
       </c>
       <c r="G352" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14179,7 +14185,7 @@
         <v>17.5415420532227</v>
       </c>
       <c r="G353" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14205,7 +14211,7 @@
         <v>17.5606822967529</v>
       </c>
       <c r="G354" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14231,7 +14237,7 @@
         <v>17.3979930877686</v>
       </c>
       <c r="G355" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14257,7 +14263,7 @@
         <v>17.5702514648438</v>
       </c>
       <c r="G356" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14283,7 +14289,7 @@
         <v>17.9051971435547</v>
       </c>
       <c r="G357" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14309,7 +14315,7 @@
         <v>18.0296058654785</v>
       </c>
       <c r="G358" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14335,7 +14341,7 @@
         <v>17.5128326416016</v>
       </c>
       <c r="G359" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14361,7 +14367,7 @@
         <v>17.589391708374</v>
       </c>
       <c r="G360" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14387,7 +14393,7 @@
         <v>17.7329387664795</v>
       </c>
       <c r="G361" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14413,7 +14419,7 @@
         <v>18.1253032684326</v>
       </c>
       <c r="G362" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14439,7 +14445,7 @@
         <v>18.1540126800537</v>
       </c>
       <c r="G363" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14465,7 +14471,7 @@
         <v>18.2305717468262</v>
       </c>
       <c r="G364" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14491,7 +14497,7 @@
         <v>18.0296058654785</v>
       </c>
       <c r="G365" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14517,7 +14523,7 @@
         <v>17.838207244873</v>
       </c>
       <c r="G366" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14543,7 +14549,7 @@
         <v>17.8669166564941</v>
       </c>
       <c r="G367" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14569,7 +14575,7 @@
         <v>17.8477783203125</v>
       </c>
       <c r="G368" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14595,7 +14601,7 @@
         <v>17.7233695983887</v>
       </c>
       <c r="G369" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14621,7 +14627,7 @@
         <v>17.4649829864502</v>
       </c>
       <c r="G370" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14647,7 +14653,7 @@
         <v>18.0870246887207</v>
       </c>
       <c r="G371" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14673,7 +14679,7 @@
         <v>18.1348724365234</v>
       </c>
       <c r="G372" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14699,7 +14705,7 @@
         <v>17.7999286651611</v>
       </c>
       <c r="G373" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14725,7 +14731,7 @@
         <v>18.0774536132812</v>
       </c>
       <c r="G374" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14751,7 +14757,7 @@
         <v>18.0200347900391</v>
       </c>
       <c r="G375" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14777,7 +14783,7 @@
         <v>18.2784214019775</v>
       </c>
       <c r="G376" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14803,7 +14809,7 @@
         <v>18.2784214019775</v>
       </c>
       <c r="G377" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14829,7 +14835,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G378" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14855,7 +14861,7 @@
         <v>18.0200347900391</v>
       </c>
       <c r="G379" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14881,7 +14887,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G380" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14907,7 +14913,7 @@
         <v>18.2305717468262</v>
       </c>
       <c r="G381" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14933,7 +14939,7 @@
         <v>17.9817562103271</v>
       </c>
       <c r="G382" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14959,7 +14965,7 @@
         <v>17.1300392150879</v>
       </c>
       <c r="G383" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14985,7 +14991,7 @@
         <v>17.5319728851318</v>
       </c>
       <c r="G384" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15011,7 +15017,7 @@
         <v>17.5319728851318</v>
       </c>
       <c r="G385" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15037,7 +15043,7 @@
         <v>17.2735862731934</v>
       </c>
       <c r="G386" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15063,7 +15069,7 @@
         <v>17.3022956848145</v>
       </c>
       <c r="G387" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15089,7 +15095,7 @@
         <v>17.2831554412842</v>
       </c>
       <c r="G388" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15115,7 +15121,7 @@
         <v>17.8477783203125</v>
       </c>
       <c r="G389" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15141,7 +15147,7 @@
         <v>17.7138004302979</v>
       </c>
       <c r="G390" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15167,7 +15173,7 @@
         <v>17.5319728851318</v>
       </c>
       <c r="G391" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15193,7 +15199,7 @@
         <v>18.1540126800537</v>
       </c>
       <c r="G392" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15219,7 +15225,7 @@
         <v>17.8956260681152</v>
       </c>
       <c r="G393" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15245,7 +15251,7 @@
         <v>17.9243354797363</v>
       </c>
       <c r="G394" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15271,7 +15277,7 @@
         <v>17.9817562103271</v>
       </c>
       <c r="G395" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15297,7 +15303,7 @@
         <v>17.8860569000244</v>
       </c>
       <c r="G396" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15323,7 +15329,7 @@
         <v>17.7999286651611</v>
       </c>
       <c r="G397" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15349,7 +15355,7 @@
         <v>17.9051971435547</v>
       </c>
       <c r="G398" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15375,7 +15381,7 @@
         <v>17.9626159667969</v>
       </c>
       <c r="G399" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15401,7 +15407,7 @@
         <v>18.106164932251</v>
       </c>
       <c r="G400" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15427,7 +15433,7 @@
         <v>18.3262691497803</v>
       </c>
       <c r="G401" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15453,7 +15459,7 @@
         <v>18.0391750335693</v>
       </c>
       <c r="G402" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15479,7 +15485,7 @@
         <v>18.0678844451904</v>
       </c>
       <c r="G403" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15505,7 +15511,7 @@
         <v>17.7999286651611</v>
       </c>
       <c r="G404" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15531,7 +15537,7 @@
         <v>17.8477783203125</v>
       </c>
       <c r="G405" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15557,7 +15563,7 @@
         <v>17.9434757232666</v>
       </c>
       <c r="G406" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15583,7 +15589,7 @@
         <v>18.0965938568115</v>
       </c>
       <c r="G407" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15609,7 +15615,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G408" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15635,7 +15641,7 @@
         <v>17.9530467987061</v>
       </c>
       <c r="G409" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15661,7 +15667,7 @@
         <v>17.7520790100098</v>
       </c>
       <c r="G410" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15687,7 +15693,7 @@
         <v>17.7520790100098</v>
       </c>
       <c r="G411" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15713,7 +15719,7 @@
         <v>17.474552154541</v>
       </c>
       <c r="G412" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -16155,7 +16161,7 @@
         <v>17.8477783203125</v>
       </c>
       <c r="G429" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16181,7 +16187,7 @@
         <v>17.7999286651611</v>
       </c>
       <c r="G430" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16285,7 +16291,7 @@
         <v>17.8477783203125</v>
       </c>
       <c r="G434" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16311,7 +16317,7 @@
         <v>17.8477783203125</v>
       </c>
       <c r="G435" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16441,7 +16447,7 @@
         <v>17.9434757232666</v>
       </c>
       <c r="G440" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16467,7 +16473,7 @@
         <v>17.9434757232666</v>
       </c>
       <c r="G441" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16493,7 +16499,7 @@
         <v>17.8956260681152</v>
       </c>
       <c r="G442" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16545,7 +16551,7 @@
         <v>17.9530467987061</v>
       </c>
       <c r="G444" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16571,7 +16577,7 @@
         <v>17.8860569000244</v>
       </c>
       <c r="G445" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16623,7 +16629,7 @@
         <v>17.8669166564941</v>
       </c>
       <c r="G447" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16727,7 +16733,7 @@
         <v>18.0391750335693</v>
       </c>
       <c r="G451" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -17065,7 +17071,7 @@
         <v>18.2305717468262</v>
       </c>
       <c r="G464" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17143,7 +17149,7 @@
         <v>18.0296058654785</v>
       </c>
       <c r="G467" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17169,7 +17175,7 @@
         <v>17.9051971435547</v>
       </c>
       <c r="G468" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17195,7 +17201,7 @@
         <v>17.7999286651611</v>
       </c>
       <c r="G469" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17325,7 +17331,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G474" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17351,7 +17357,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G475" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17429,7 +17435,7 @@
         <v>17.7999286651611</v>
       </c>
       <c r="G478" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17455,7 +17461,7 @@
         <v>17.1300392150879</v>
       </c>
       <c r="G479" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17559,7 +17565,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G483" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17585,7 +17591,7 @@
         <v>18.106164932251</v>
       </c>
       <c r="G484" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17611,7 +17617,7 @@
         <v>17.9434757232666</v>
       </c>
       <c r="G485" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17637,7 +17643,7 @@
         <v>18.2305717468262</v>
       </c>
       <c r="G486" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17819,7 +17825,7 @@
         <v>18.0678844451904</v>
       </c>
       <c r="G493" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17845,7 +17851,7 @@
         <v>18.2784214019775</v>
       </c>
       <c r="G494" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17871,7 +17877,7 @@
         <v>18.2784214019775</v>
       </c>
       <c r="G495" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17897,7 +17903,7 @@
         <v>18.2305717468262</v>
       </c>
       <c r="G496" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17975,7 +17981,7 @@
         <v>18.0870246887207</v>
       </c>
       <c r="G499" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18053,7 +18059,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G502" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18131,7 +18137,7 @@
         <v>17.9243354797363</v>
       </c>
       <c r="G505" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18183,7 +18189,7 @@
         <v>18.2305717468262</v>
       </c>
       <c r="G507" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -19015,7 +19021,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G539" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19067,7 +19073,7 @@
         <v>17.8956260681152</v>
       </c>
       <c r="G541" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19093,7 +19099,7 @@
         <v>17.7999286651611</v>
       </c>
       <c r="G542" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19119,7 +19125,7 @@
         <v>18.0296058654785</v>
       </c>
       <c r="G543" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19197,7 +19203,7 @@
         <v>18.1827220916748</v>
       </c>
       <c r="G546" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19223,7 +19229,7 @@
         <v>18.0678844451904</v>
       </c>
       <c r="G547" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19535,7 +19541,7 @@
         <v>18.106164932251</v>
       </c>
       <c r="G559" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19561,7 +19567,7 @@
         <v>18.0870246887207</v>
       </c>
       <c r="G560" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19613,7 +19619,7 @@
         <v>17.9530467987061</v>
       </c>
       <c r="G562" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19639,7 +19645,7 @@
         <v>17.5702514648438</v>
       </c>
       <c r="G563" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20471,7 +20477,7 @@
         <v>17.1300392150879</v>
       </c>
       <c r="G595" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20523,7 +20529,7 @@
         <v>17.1300392150879</v>
       </c>
       <c r="G597" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20575,7 +20581,7 @@
         <v>18.2784214019775</v>
       </c>
       <c r="G599" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20705,7 +20711,7 @@
         <v>17.7999286651611</v>
       </c>
       <c r="G604" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -70113,27 +70119,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.691087963</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>224781</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>9.43000030517578</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>177908</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>9.55000019073486</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>9.40999984741211</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1552</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>320938</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>9.5</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>9.19999980926514</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>9.39999961853027</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>9.40999984741211</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>1552</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6909953704</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>305862</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>9.6899995803833</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>9.52000045776367</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08278369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05997276306152</t>
+    <t xml:space="preserve">8.08278560638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05997371673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.06757736206055</t>
@@ -59,61 +59,61 @@
     <t xml:space="preserve">8.11319923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90029525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87748193740845</t>
+    <t xml:space="preserve">7.90029287338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87748384475708</t>
   </si>
   <si>
     <t xml:space="preserve">7.94591522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52771091461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48969078063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95351982116699</t>
+    <t xml:space="preserve">7.52771043777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48969125747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95352029800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.79384183883667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67978620529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62655925750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71020030975342</t>
+    <t xml:space="preserve">7.67978429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62655830383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71020078659058</t>
   </si>
   <si>
     <t xml:space="preserve">7.89269065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8242564201355</t>
+    <t xml:space="preserve">7.82425546646118</t>
   </si>
   <si>
     <t xml:space="preserve">7.60374784469604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69499349594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9839334487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84706926345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91550302505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01434993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20444393157959</t>
+    <t xml:space="preserve">7.69499492645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98393487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84706735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91550064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01435089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20444297790527</t>
   </si>
   <si>
     <t xml:space="preserve">8.10559463500977</t>
@@ -122,70 +122,70 @@
     <t xml:space="preserve">8.24246215820312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25006675720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30329322814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15121746063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23486042022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.219651222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36412239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29568767547607</t>
+    <t xml:space="preserve">8.25006771087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3032922744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15121555328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2348575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35651969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28808498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21965026855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36412334442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29568862915039</t>
   </si>
   <si>
     <t xml:space="preserve">8.38693332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1436128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18923568725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40974617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40214157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37932968139648</t>
+    <t xml:space="preserve">8.14361381530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18923664093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40974521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40214061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37932872772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.51619720458984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75191402435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82034969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80514144897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82795333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01044178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09408187866211</t>
+    <t xml:space="preserve">8.75191307067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82034778594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80514049530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82795143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01044082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09408283233643</t>
   </si>
   <si>
     <t xml:space="preserve">8.98002624511719</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">9.12449741363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19293022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7899341583252</t>
+    <t xml:space="preserve">9.19293212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78993225097656</t>
   </si>
   <si>
     <t xml:space="preserve">9.11689376831055</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">9.17772483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03325271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0864782333374</t>
+    <t xml:space="preserve">9.03325176239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08647918701172</t>
   </si>
   <si>
     <t xml:space="preserve">9.20053482055664</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">9.34500598907471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13970279693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61113929748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67196750640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65675926208496</t>
+    <t xml:space="preserve">9.13970470428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61113834381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67196846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65676021575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.80883407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90008068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77081489562988</t>
+    <t xml:space="preserve">9.90007877349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77081680297852</t>
   </si>
   <si>
     <t xml:space="preserve">9.73252964019775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47217750549316</t>
+    <t xml:space="preserve">9.4721794128418</t>
   </si>
   <si>
     <t xml:space="preserve">9.49515056610107</t>
@@ -251,37 +251,37 @@
     <t xml:space="preserve">9.5717248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70189952850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67892837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69424152374268</t>
+    <t xml:space="preserve">9.70190143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77847480773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67892932891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69424247741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.61001110076904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6482982635498</t>
+    <t xml:space="preserve">9.64829921722412</t>
   </si>
   <si>
     <t xml:space="preserve">9.51046466827393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41857528686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26542854309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22714328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18885612487793</t>
+    <t xml:space="preserve">9.41857624053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2654275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22714424133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18885517120361</t>
   </si>
   <si>
     <t xml:space="preserve">9.11228084564209</t>
@@ -290,58 +290,58 @@
     <t xml:space="preserve">9.34200286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63298416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20416927337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21182727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3037166595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72487258911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34966087341309</t>
+    <t xml:space="preserve">9.63298225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2041711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21182823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30371475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7248706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34965991973877</t>
   </si>
   <si>
     <t xml:space="preserve">9.38794708251953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59469604492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53343772888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75550174713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76315879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62532520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45686340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78613185882568</t>
+    <t xml:space="preserve">9.59469509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53343677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75550270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316070556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62532615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.456862449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78613090515137</t>
   </si>
   <si>
     <t xml:space="preserve">9.74784374237061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71721363067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68658542633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67126941680908</t>
+    <t xml:space="preserve">9.71721458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68658447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6712703704834</t>
   </si>
   <si>
     <t xml:space="preserve">9.36497402191162</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">9.56406593322754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57938194274902</t>
+    <t xml:space="preserve">9.57938098907471</t>
   </si>
   <si>
     <t xml:space="preserve">9.80910301208496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70955848693848</t>
+    <t xml:space="preserve">9.70955753326416</t>
   </si>
   <si>
     <t xml:space="preserve">9.66361236572266</t>
@@ -365,34 +365,34 @@
     <t xml:space="preserve">9.74018573760986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51812267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4492073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39560413360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3573169708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54109573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41091918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80144596099854</t>
+    <t xml:space="preserve">9.51812171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44920635223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39560508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35731601715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54109477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41092014312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80144500732422</t>
   </si>
   <si>
     <t xml:space="preserve">9.55641078948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79378890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86270427703857</t>
+    <t xml:space="preserve">9.79378986358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86270332336426</t>
   </si>
   <si>
     <t xml:space="preserve">9.90864944458008</t>
@@ -401,37 +401,37 @@
     <t xml:space="preserve">9.93927764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92396259307861</t>
+    <t xml:space="preserve">9.92396354675293</t>
   </si>
   <si>
     <t xml:space="preserve">10.2226009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2685461044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2838611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3910646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4829521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5825004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7050161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6437587738037</t>
+    <t xml:space="preserve">10.2685451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.283860206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3910636901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4829530715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.582498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7050170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6437559127808</t>
   </si>
   <si>
     <t xml:space="preserve">10.7203302383423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3374633789062</t>
+    <t xml:space="preserve">10.3374624252319</t>
   </si>
   <si>
     <t xml:space="preserve">10.4523220062256</t>
@@ -446,100 +446,100 @@
     <t xml:space="preserve">10.0694532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2379179000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617971420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95459461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.870361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82441711425781</t>
+    <t xml:space="preserve">10.2379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95459270477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87036228179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82441902160645</t>
   </si>
   <si>
     <t xml:space="preserve">10.0388231277466</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98522186279297</t>
+    <t xml:space="preserve">9.98522090911865</t>
   </si>
   <si>
     <t xml:space="preserve">9.85504817962646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93162155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94693565368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89333343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0541381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97756481170654</t>
+    <t xml:space="preserve">9.93162059783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94693470001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89333438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0541391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97756385803223</t>
   </si>
   <si>
     <t xml:space="preserve">9.8856782913208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1613426208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288963317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5671834945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.490611076355</t>
+    <t xml:space="preserve">10.1613416671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288972854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5671825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906101226807</t>
   </si>
   <si>
     <t xml:space="preserve">10.2991752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2608871459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4063777923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4140357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2455739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3221464157104</t>
+    <t xml:space="preserve">10.2608890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4063787460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4140367507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2455749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153993606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3221483230591</t>
   </si>
   <si>
     <t xml:space="preserve">10.2915182113647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3987216949463</t>
+    <t xml:space="preserve">10.398720741272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4982671737671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.429349899292</t>
+    <t xml:space="preserve">10.4293508529663</t>
   </si>
   <si>
     <t xml:space="preserve">10.6054716110229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5901556015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3757495880127</t>
+    <t xml:space="preserve">10.5901575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.375750541687</t>
   </si>
   <si>
     <t xml:space="preserve">10.2532320022583</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">10.3068332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4752950668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5212392807007</t>
+    <t xml:space="preserve">10.4752969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.521240234375</t>
   </si>
   <si>
     <t xml:space="preserve">10.4446668624878</t>
@@ -563,43 +563,43 @@
     <t xml:space="preserve">10.3298044204712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1230545043945</t>
+    <t xml:space="preserve">10.1230564117432</t>
   </si>
   <si>
     <t xml:space="preserve">10.4216928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.781590461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2027454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1797742843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1338300704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3329238891602</t>
+    <t xml:space="preserve">10.7815885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2027463912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1797752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1338291168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3329219818115</t>
   </si>
   <si>
     <t xml:space="preserve">11.2946338653564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4094953536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2793197631836</t>
+    <t xml:space="preserve">11.4094944000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2793207168579</t>
   </si>
   <si>
     <t xml:space="preserve">11.3788661956787</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6775035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7081336975098</t>
+    <t xml:space="preserve">11.6775026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7081346511841</t>
   </si>
   <si>
     <t xml:space="preserve">11.8383092880249</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">11.6851615905762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6468753814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.547327041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.401837348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5243549346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6392164230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157917022705</t>
+    <t xml:space="preserve">11.6468744277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5473279953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4018363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5243558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6392154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157907485962</t>
   </si>
   <si>
     <t xml:space="preserve">11.7923641204834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2288370132446</t>
+    <t xml:space="preserve">12.228835105896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2441492080688</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">12.3513526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4049549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.519814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2549238204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5918483734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6301364898682</t>
+    <t xml:space="preserve">12.4049558639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5198154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2549247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5918474197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6301345825195</t>
   </si>
   <si>
     <t xml:space="preserve">13.7832832336426</t>
@@ -659,22 +659,22 @@
     <t xml:space="preserve">13.2472667694092</t>
   </si>
   <si>
-    <t xml:space="preserve">12.818452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6346778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7112493515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.025200843811</t>
+    <t xml:space="preserve">12.8184537887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6346788406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7112483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0252017974854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8643970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2396068572998</t>
+    <t xml:space="preserve">13.2396087646484</t>
   </si>
   <si>
     <t xml:space="preserve">13.2166376113892</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">13.2089796066284</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7373371124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3621273040771</t>
+    <t xml:space="preserve">13.7373390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3621282577515</t>
   </si>
   <si>
     <t xml:space="preserve">13.4004144668579</t>
@@ -695,43 +695,43 @@
     <t xml:space="preserve">13.7143669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5688781738281</t>
+    <t xml:space="preserve">13.5688762664795</t>
   </si>
   <si>
     <t xml:space="preserve">13.5152750015259</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6684226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.614821434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3192987442017</t>
+    <t xml:space="preserve">13.668420791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6148195266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3192977905273</t>
   </si>
   <si>
     <t xml:space="preserve">14.3958730697632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3882150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4341583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5490188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6791982650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2810134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3269557952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4265050888062</t>
+    <t xml:space="preserve">14.3882169723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4341611862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5490226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6791954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2810125350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.326958656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4265060424805</t>
   </si>
   <si>
     <t xml:space="preserve">14.3422698974609</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">14.5337057113647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2733545303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0359764099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512924194336</t>
+    <t xml:space="preserve">14.2733554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0359754562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512895584106</t>
   </si>
   <si>
     <t xml:space="preserve">13.9897298812866</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">14.1282434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.397572517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4976081848145</t>
+    <t xml:space="preserve">14.3975734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4976110458374</t>
   </si>
   <si>
     <t xml:space="preserve">14.0820713043213</t>
@@ -767,37 +767,37 @@
     <t xml:space="preserve">14.1436319351196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2590579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5745601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5976457595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6592073440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3437042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3667888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3514022827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2513637542725</t>
+    <t xml:space="preserve">14.2590608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.574559211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5976428985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6592044830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3437061309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3667907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3514003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2513647079468</t>
   </si>
   <si>
     <t xml:space="preserve">14.0435962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5437784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5822534561157</t>
+    <t xml:space="preserve">14.5437793731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.58225440979</t>
   </si>
   <si>
     <t xml:space="preserve">14.3129243850708</t>
@@ -806,49 +806,49 @@
     <t xml:space="preserve">14.5360841751099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4899139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6976823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6207294464111</t>
+    <t xml:space="preserve">14.4899120330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6976804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6207313537598</t>
   </si>
   <si>
     <t xml:space="preserve">14.4591341018677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7742671966553</t>
+    <t xml:space="preserve">13.7742681503296</t>
   </si>
   <si>
     <t xml:space="preserve">14.0974626541138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8896942138672</t>
+    <t xml:space="preserve">13.8896932601929</t>
   </si>
   <si>
     <t xml:space="preserve">13.9127798080444</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8973865509033</t>
+    <t xml:space="preserve">13.897388458252</t>
   </si>
   <si>
     <t xml:space="preserve">14.2436695098877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3898754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4129610061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3821802139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4437417984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5591688156128</t>
+    <t xml:space="preserve">14.389874458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4129590988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3821811676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4437427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5591707229614</t>
   </si>
   <si>
     <t xml:space="preserve">14.7361555099487</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">14.5283880233765</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4283504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514726638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4360475540161</t>
+    <t xml:space="preserve">14.4283533096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514764785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4360494613647</t>
   </si>
   <si>
     <t xml:space="preserve">14.274450302124</t>
@@ -875,76 +875,76 @@
     <t xml:space="preserve">14.051290512085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9666481018066</t>
+    <t xml:space="preserve">13.9666433334351</t>
   </si>
   <si>
     <t xml:space="preserve">13.6742305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1205501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1590213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.151328086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8512191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9743404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1744117736816</t>
+    <t xml:space="preserve">14.1205453872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1590223312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1513271331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8512182235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9743413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1744108200073</t>
   </si>
   <si>
     <t xml:space="preserve">14.2051954269409</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0051202774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3052291870117</t>
+    <t xml:space="preserve">14.0051221847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3052310943604</t>
   </si>
   <si>
     <t xml:space="preserve">14.3590974807739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.297534942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4206581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3283176422119</t>
+    <t xml:space="preserve">14.2975330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4206571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3283166885376</t>
   </si>
   <si>
     <t xml:space="preserve">14.336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3744869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2359743118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5129976272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2205820083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1974964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3902435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2440357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2517280578613</t>
+    <t xml:space="preserve">14.3744859695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.23597240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.512996673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2205839157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1974983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3902406692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2440376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.25172996521</t>
   </si>
   <si>
     <t xml:space="preserve">15.1670837402344</t>
@@ -953,79 +953,79 @@
     <t xml:space="preserve">15.1055221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.197865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0670461654663</t>
+    <t xml:space="preserve">15.1978635787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0670471191406</t>
   </si>
   <si>
     <t xml:space="preserve">14.9208402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9285364151001</t>
+    <t xml:space="preserve">14.9285345077515</t>
   </si>
   <si>
     <t xml:space="preserve">14.882363319397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5206909179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2898378372192</t>
+    <t xml:space="preserve">14.5206928253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2898406982422</t>
   </si>
   <si>
     <t xml:space="preserve">14.7515459060669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6438150405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5668649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6515092849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7438516616821</t>
+    <t xml:space="preserve">14.6438159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5668630599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6515121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7438526153564</t>
   </si>
   <si>
     <t xml:space="preserve">14.7900218963623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8361911773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7746343612671</t>
+    <t xml:space="preserve">14.8361930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7746324539185</t>
   </si>
   <si>
     <t xml:space="preserve">14.6361207962036</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7207679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.45143699646</t>
+    <t xml:space="preserve">14.7207660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4514350891113</t>
   </si>
   <si>
     <t xml:space="preserve">14.4668273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5899496078491</t>
+    <t xml:space="preserve">14.5899505615234</t>
   </si>
   <si>
     <t xml:space="preserve">14.8131074905396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8515863418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1440000534058</t>
+    <t xml:space="preserve">14.851583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1439971923828</t>
   </si>
   <si>
     <t xml:space="preserve">15.2902059555054</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3440723419189</t>
+    <t xml:space="preserve">15.3440732955933</t>
   </si>
   <si>
     <t xml:space="preserve">15.5441436767578</t>
@@ -1037,28 +1037,28 @@
     <t xml:space="preserve">15.505669593811</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4287195205688</t>
+    <t xml:space="preserve">15.4287185668945</t>
   </si>
   <si>
     <t xml:space="preserve">15.2209501266479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9747066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.128607749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9289026260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7365236282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8134756088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2367057800293</t>
+    <t xml:space="preserve">14.9747095108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1286087036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9289016723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7365217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8134708404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2367038726807</t>
   </si>
   <si>
     <t xml:space="preserve">16.0828056335449</t>
@@ -1070,94 +1070,94 @@
     <t xml:space="preserve">16.0058517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1212768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6980485916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7749996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9131441116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8977565765381</t>
+    <t xml:space="preserve">16.1212825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6980504989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.774998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671194076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9131460189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8977546691895</t>
   </si>
   <si>
     <t xml:space="preserve">14.8054122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1747798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0208778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0516576766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8208065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0362682342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.928168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1128520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2821445465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4822187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5588054656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7127056121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5434141159058</t>
+    <t xml:space="preserve">15.1747779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0208768844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0516557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8208055496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0362672805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9281692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1128511428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2821455001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4822196960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5588035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7127065658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5434122085571</t>
   </si>
   <si>
     <t xml:space="preserve">13.3125600814819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2048292160034</t>
+    <t xml:space="preserve">13.2048263549805</t>
   </si>
   <si>
     <t xml:space="preserve">13.4510726928711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4356832504272</t>
+    <t xml:space="preserve">13.4356822967529</t>
   </si>
   <si>
     <t xml:space="preserve">13.2817802429199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6511449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3895111083984</t>
+    <t xml:space="preserve">13.6511459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3895130157471</t>
   </si>
   <si>
     <t xml:space="preserve">13.1432676315308</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0663166046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0047540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0509243011475</t>
+    <t xml:space="preserve">13.0663175582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0047559738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0509262084961</t>
   </si>
   <si>
     <t xml:space="preserve">13.2971706390381</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">13.6357555389404</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8666095733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6819257736206</t>
+    <t xml:space="preserve">13.8666086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.681923866272</t>
   </si>
   <si>
     <t xml:space="preserve">13.8819990158081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7130718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9589500427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9512166976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8893508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7656126022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9976177215576</t>
+    <t xml:space="preserve">14.7130727767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9589490890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9512147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8893489837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7656116485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9976167678833</t>
   </si>
   <si>
     <t xml:space="preserve">14.0749521255493</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">12.806658744812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3170700073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1469326019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2397365570068</t>
+    <t xml:space="preserve">13.3170690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1469354629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2397356033325</t>
   </si>
   <si>
     <t xml:space="preserve">13.6109437942505</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">13.7192115783691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4253387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4562740325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645437240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3789386749268</t>
+    <t xml:space="preserve">13.4253396987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4562749862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645418167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3789396286011</t>
   </si>
   <si>
     <t xml:space="preserve">13.3016052246094</t>
@@ -1241,40 +1241,40 @@
     <t xml:space="preserve">13.5490751266479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8274822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8738813400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6573448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0594844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1213521957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0285520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9048147201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9666814804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1986885070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1058883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9202833175659</t>
+    <t xml:space="preserve">13.8274812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8738822937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6573438644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0594854354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1213531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0285501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8584146499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9048156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9666833877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1986875534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1058864593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.920280456543</t>
   </si>
   <si>
     <t xml:space="preserve">14.1677551269531</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">14.5389614105225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4925622940063</t>
+    <t xml:space="preserve">14.492561340332</t>
   </si>
   <si>
     <t xml:space="preserve">14.4306945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3688249588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2914886474609</t>
+    <t xml:space="preserve">14.368824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2914896011353</t>
   </si>
   <si>
     <t xml:space="preserve">14.3533582687378</t>
@@ -1301,58 +1301,58 @@
     <t xml:space="preserve">14.4616260528564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008291244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7810802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3842906951904</t>
+    <t xml:space="preserve">14.6008281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.781081199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3842916488647</t>
   </si>
   <si>
     <t xml:space="preserve">14.5080289840698</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3224248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5698957443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.306957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1368217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.152286529541</t>
+    <t xml:space="preserve">14.3224239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5698976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3069562911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1368207931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1522874832153</t>
   </si>
   <si>
     <t xml:space="preserve">13.6882772445679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0130853652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2088012695312</t>
+    <t xml:space="preserve">14.0130844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2088022232056</t>
   </si>
   <si>
     <t xml:space="preserve">13.4408073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.487208366394</t>
+    <t xml:space="preserve">13.4872074127197</t>
   </si>
   <si>
     <t xml:space="preserve">13.6728115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">13.70374584198</t>
+    <t xml:space="preserve">13.7037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">13.5800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6983919143677</t>
+    <t xml:space="preserve">12.698390007019</t>
   </si>
   <si>
     <t xml:space="preserve">12.6829242706299</t>
@@ -1361,37 +1361,37 @@
     <t xml:space="preserve">12.5746555328369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6519908905029</t>
+    <t xml:space="preserve">12.6519899368286</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149293899536</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0231981277466</t>
+    <t xml:space="preserve">13.0231990814209</t>
   </si>
   <si>
     <t xml:space="preserve">12.6674575805664</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2189140319824</t>
+    <t xml:space="preserve">12.2189149856567</t>
   </si>
   <si>
     <t xml:space="preserve">12.5591897964478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2962484359741</t>
+    <t xml:space="preserve">12.2962503433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.7394371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9714422225952</t>
+    <t xml:space="preserve">11.9714431762695</t>
   </si>
   <si>
     <t xml:space="preserve">11.9405078887939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0951776504517</t>
+    <t xml:space="preserve">12.095178604126</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570463180542</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">12.064245223999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8786420822144</t>
+    <t xml:space="preserve">11.87864112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.8477077484131</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6621046066284</t>
+    <t xml:space="preserve">11.6621036529541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6002359390259</t>
@@ -1415,61 +1415,61 @@
     <t xml:space="preserve">11.5074329376221</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1362266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4402132034302</t>
+    <t xml:space="preserve">11.1362257003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4402122497559</t>
   </si>
   <si>
     <t xml:space="preserve">10.8887538909912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2599611282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9351539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0124893188477</t>
+    <t xml:space="preserve">11.2599620819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.012490272522</t>
   </si>
   <si>
     <t xml:space="preserve">11.3682308197021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4455671310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5847673416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5175457000732</t>
+    <t xml:space="preserve">11.4455652236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5847692489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5175476074219</t>
   </si>
   <si>
     <t xml:space="preserve">10.828667640686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3458585739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9418029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0226163864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6185598373413</t>
+    <t xml:space="preserve">11.3458566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2973728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9418039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0226144790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6185607910156</t>
   </si>
   <si>
     <t xml:space="preserve">11.1195878982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7984008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2165613174438</t>
+    <t xml:space="preserve">11.7984018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2165603637695</t>
   </si>
   <si>
     <t xml:space="preserve">11.0711002349854</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">11.2327222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2488842010498</t>
+    <t xml:space="preserve">11.2488851547241</t>
   </si>
   <si>
     <t xml:space="preserve">11.2003984451294</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">10.6832094192505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9094800949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8609924316406</t>
+    <t xml:space="preserve">10.9094791412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8609914779663</t>
   </si>
   <si>
     <t xml:space="preserve">11.4751558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5721273422241</t>
+    <t xml:space="preserve">11.5721292495728</t>
   </si>
   <si>
     <t xml:space="preserve">11.6367778778076</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">11.523642539978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7801809310913</t>
+    <t xml:space="preserve">10.7801818847656</t>
   </si>
   <si>
     <t xml:space="preserve">10.8933172225952</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">11.0549392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9579648971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9741277694702</t>
+    <t xml:space="preserve">10.9579658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9741268157959</t>
   </si>
   <si>
     <t xml:space="preserve">10.8448305130005</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">11.1357488632202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0872640609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3296966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.604453086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8792095184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8630475997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7337512969971</t>
+    <t xml:space="preserve">11.0872650146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3296957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6044521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8792104721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8630485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7337503433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.6529397964478</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">11.8468866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4589939117432</t>
+    <t xml:space="preserve">11.4589948654175</t>
   </si>
   <si>
     <t xml:space="preserve">11.2650470733643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3620195388794</t>
+    <t xml:space="preserve">11.362021446228</t>
   </si>
   <si>
     <t xml:space="preserve">11.0387773513794</t>
@@ -1577,40 +1577,40 @@
     <t xml:space="preserve">10.6508836746216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5539112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5215873718262</t>
+    <t xml:space="preserve">10.5539102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5215864181519</t>
   </si>
   <si>
     <t xml:space="preserve">10.1013698577881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98823261260986</t>
+    <t xml:space="preserve">9.9882345199585</t>
   </si>
   <si>
     <t xml:space="preserve">10.1821804046631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3922891616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114786148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2953157424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3761262893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3599634170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6023969650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.586236000061</t>
+    <t xml:space="preserve">10.3922872543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2953147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.376127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3599643707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6023960113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5862350463867</t>
   </si>
   <si>
     <t xml:space="preserve">10.3438024520874</t>
@@ -1619,52 +1619,52 @@
     <t xml:space="preserve">10.5700731277466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7963428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1034250259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1842355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.151912689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4730997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.456937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4084501266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.667046546936</t>
+    <t xml:space="preserve">10.7963418960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1034231185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1842365264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1519117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4730987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4569387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4084520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6670475006104</t>
   </si>
   <si>
     <t xml:space="preserve">10.2465229034424</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5067520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5880737304688</t>
+    <t xml:space="preserve">10.5067510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5880727767944</t>
   </si>
   <si>
     <t xml:space="preserve">10.7669811248779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9458894729614</t>
+    <t xml:space="preserve">10.9458875656128</t>
   </si>
   <si>
     <t xml:space="preserve">10.9621524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7507181167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3441095352173</t>
+    <t xml:space="preserve">10.7507171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.344108581543</t>
   </si>
   <si>
     <t xml:space="preserve">10.4416942596436</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">10.3115797042847</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278436660767</t>
+    <t xml:space="preserve">10.327844619751</t>
   </si>
   <si>
     <t xml:space="preserve">10.4254293441772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4904870986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5230159759521</t>
+    <t xml:space="preserve">10.4904861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5230169296265</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555448532104</t>
@@ -1694,28 +1694,28 @@
     <t xml:space="preserve">10.8483018875122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1410608291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9946813583374</t>
+    <t xml:space="preserve">11.1410598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9946804046631</t>
   </si>
   <si>
     <t xml:space="preserve">10.8808307647705</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8970937728882</t>
+    <t xml:space="preserve">11.092267036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8970956802368</t>
   </si>
   <si>
     <t xml:space="preserve">10.5718088150024</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6693935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6368656158447</t>
+    <t xml:space="preserve">10.6693954467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.636866569519</t>
   </si>
   <si>
     <t xml:space="preserve">10.653130531311</t>
@@ -1727,25 +1727,25 @@
     <t xml:space="preserve">10.8320379257202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1085319519043</t>
+    <t xml:space="preserve">11.1085329055786</t>
   </si>
   <si>
     <t xml:space="preserve">11.3037033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2223825454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5639314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.43381690979</t>
+    <t xml:space="preserve">11.2223806381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5639324188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4338188171387</t>
   </si>
   <si>
     <t xml:space="preserve">11.1573257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2386465072632</t>
+    <t xml:space="preserve">11.2386474609375</t>
   </si>
   <si>
     <t xml:space="preserve">11.7103118896484</t>
@@ -1754,40 +1754,40 @@
     <t xml:space="preserve">11.7428398132324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5476675033569</t>
+    <t xml:space="preserve">11.5476684570312</t>
   </si>
   <si>
     <t xml:space="preserve">11.6452541351318</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7019233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7344522476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6856594085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6043367385864</t>
+    <t xml:space="preserve">10.701922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7344532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6856603622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6043376922607</t>
   </si>
   <si>
     <t xml:space="preserve">10.8645658493042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4742221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6206026077271</t>
+    <t xml:space="preserve">10.4742240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6206016540527</t>
   </si>
   <si>
     <t xml:space="preserve">11.2874393463135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6127252578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5314035415649</t>
+    <t xml:space="preserve">11.6127262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5314054489136</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289901733398</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">11.0597381591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0760021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1898536682129</t>
+    <t xml:space="preserve">11.0760040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1898546218872</t>
   </si>
   <si>
     <t xml:space="preserve">11.3850240707397</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">11.4012899398804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2549095153809</t>
+    <t xml:space="preserve">11.2549104690552</t>
   </si>
   <si>
     <t xml:space="preserve">11.3524961471558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500827789307</t>
+    <t xml:space="preserve">11.4500818252563</t>
   </si>
   <si>
     <t xml:space="preserve">12.0518627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3771476745605</t>
+    <t xml:space="preserve">12.3771486282349</t>
   </si>
   <si>
     <t xml:space="preserve">12.4259405136108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1657123565674</t>
+    <t xml:space="preserve">12.1657133102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.3446197509766</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">12.5235271453857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3934125900269</t>
+    <t xml:space="preserve">12.3934144973755</t>
   </si>
   <si>
     <t xml:space="preserve">12.4422063827515</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">12.6048488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3608846664429</t>
+    <t xml:space="preserve">12.3608837127686</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795629501343</t>
@@ -1877,49 +1877,49 @@
     <t xml:space="preserve">12.2958269119263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5560550689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4584684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3120918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1331844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9705410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0681276321411</t>
+    <t xml:space="preserve">12.5560569763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4584703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3120908737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1331825256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9705400466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0681257247925</t>
   </si>
   <si>
     <t xml:space="preserve">11.9380121231079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0355987548828</t>
+    <t xml:space="preserve">12.0355978012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.8729562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9542751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9217472076416</t>
+    <t xml:space="preserve">11.9542770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9217481613159</t>
   </si>
   <si>
     <t xml:space="preserve">11.6777820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7916316986084</t>
+    <t xml:space="preserve">11.7916326522827</t>
   </si>
   <si>
     <t xml:space="preserve">11.7753677368164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1735887527466</t>
+    <t xml:space="preserve">11.1735877990723</t>
   </si>
   <si>
     <t xml:space="preserve">11.3687610626221</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">10.4579582214355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4091663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5392799377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3766384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2302579879761</t>
+    <t xml:space="preserve">10.4091653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5392789840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.376636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2302589416504</t>
   </si>
   <si>
     <t xml:space="preserve">10.360372543335</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">9.36824989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25439929962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53089141845703</t>
+    <t xml:space="preserve">9.25439834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53089237213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.41704273223877</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">9.1893424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84779167175293</t>
+    <t xml:space="preserve">8.84779071807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.75020503997803</t>
@@ -1982,34 +1982,34 @@
     <t xml:space="preserve">8.50623989105225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81500577926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4246621131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34334087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4244065284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70090103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43253946304321</t>
+    <t xml:space="preserve">7.81500673294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42466259002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3433403968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42440700531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70090007781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4325385093689</t>
   </si>
   <si>
     <t xml:space="preserve">6.11538457870483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48920917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52173709869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77383375167847</t>
+    <t xml:space="preserve">5.48920869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52173662185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77383422851562</t>
   </si>
   <si>
     <t xml:space="preserve">5.86328744888306</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">5.73317337036133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6111912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30216836929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59492683410645</t>
+    <t xml:space="preserve">5.61119031906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30216884613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5949273109436</t>
   </si>
   <si>
     <t xml:space="preserve">5.56239795684814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58679437637329</t>
+    <t xml:space="preserve">5.58679389953613</t>
   </si>
   <si>
     <t xml:space="preserve">5.52986907958984</t>
@@ -2039,58 +2039,58 @@
     <t xml:space="preserve">5.69251203536987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71690845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01779937744141</t>
+    <t xml:space="preserve">5.71690940856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01779890060425</t>
   </si>
   <si>
     <t xml:space="preserve">5.74943733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18044233322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13164901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05845928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09098863601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15604591369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54638910293579</t>
+    <t xml:space="preserve">6.18044185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13164854049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0584602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09098815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15604543685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54638957977295</t>
   </si>
   <si>
     <t xml:space="preserve">6.53012466430664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61144685745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70903205871582</t>
+    <t xml:space="preserve">6.61144638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70903253555298</t>
   </si>
   <si>
     <t xml:space="preserve">6.44067144393921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74156141281128</t>
+    <t xml:space="preserve">6.74156093597412</t>
   </si>
   <si>
     <t xml:space="preserve">6.50572872161865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52199363708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39187860488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00153541564941</t>
+    <t xml:space="preserve">6.5219931602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39187812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0015344619751</t>
   </si>
   <si>
     <t xml:space="preserve">5.96900606155396</t>
@@ -2102,22 +2102,22 @@
     <t xml:space="preserve">6.20483875274658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18857383728027</t>
+    <t xml:space="preserve">6.18857431411743</t>
   </si>
   <si>
     <t xml:space="preserve">6.30242443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4975962638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63584280014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87167549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79035472869873</t>
+    <t xml:space="preserve">6.49759578704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63584327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87167501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79035425186157</t>
   </si>
   <si>
     <t xml:space="preserve">6.77408981323242</t>
@@ -2126,40 +2126,40 @@
     <t xml:space="preserve">6.75782537460327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91233682632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39213418960571</t>
+    <t xml:space="preserve">6.91233587265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3921332359314</t>
   </si>
   <si>
     <t xml:space="preserve">7.59543895721436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40026712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36773729324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19696283340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80661916732788</t>
+    <t xml:space="preserve">7.40026617050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36773777008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1969633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80661869049072</t>
   </si>
   <si>
     <t xml:space="preserve">6.89607191085815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05871629714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83914709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85541152954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97739315032959</t>
+    <t xml:space="preserve">7.0587158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83914756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85541200637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97739362716675</t>
   </si>
   <si>
     <t xml:space="preserve">7.05058288574219</t>
@@ -2168,22 +2168,22 @@
     <t xml:space="preserve">7.14003658294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94486522674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31894397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28641605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15630149841309</t>
+    <t xml:space="preserve">6.94486570358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31894445419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28641557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1563024520874</t>
   </si>
   <si>
     <t xml:space="preserve">7.08311176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00992202758789</t>
+    <t xml:space="preserve">7.00992250442505</t>
   </si>
   <si>
     <t xml:space="preserve">7.02618741989136</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">7.16443395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95299816131592</t>
+    <t xml:space="preserve">6.9529972076416</t>
   </si>
   <si>
     <t xml:space="preserve">7.01805543899536</t>
@@ -2201,88 +2201,88 @@
     <t xml:space="preserve">6.66837167739868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51386070251465</t>
+    <t xml:space="preserve">6.51386117935181</t>
   </si>
   <si>
     <t xml:space="preserve">6.47319984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73342895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71716547012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78222179412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56265306472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5870509147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60331392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40001058578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27802753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35935020446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34308528900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26989650726318</t>
+    <t xml:space="preserve">6.73342943191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71716499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78222131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5626540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58705043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6033148765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40001106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27802848815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35934972763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34308576583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26989555358887</t>
   </si>
   <si>
     <t xml:space="preserve">6.21297025680542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19670629501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97713756561279</t>
+    <t xml:space="preserve">6.19670724868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97713851928711</t>
   </si>
   <si>
     <t xml:space="preserve">6.09912061691284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94460964202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78196573257446</t>
+    <t xml:space="preserve">5.94460916519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78196620941162</t>
   </si>
   <si>
     <t xml:space="preserve">5.8876838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80636262893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79009819030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72504138946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76570177078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99340200424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00966691970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98527050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05032777786255</t>
+    <t xml:space="preserve">5.80636310577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79009866714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72504091262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76570272445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9934024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00966644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98527002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05032730102539</t>
   </si>
   <si>
     <t xml:space="preserve">6.16417789459229</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">6.22110319137573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92834520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10725259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03406381607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31055688858032</t>
+    <t xml:space="preserve">5.92834424972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.107253074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03406286239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31055736541748</t>
   </si>
   <si>
     <t xml:space="preserve">6.17230987548828</t>
@@ -2321,67 +2321,67 @@
     <t xml:space="preserve">5.21271467208862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00127792358398</t>
+    <t xml:space="preserve">5.0012788772583</t>
   </si>
   <si>
     <t xml:space="preserve">4.96875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01754283905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0419397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24524354934692</t>
+    <t xml:space="preserve">5.01754331588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04193925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24524307250977</t>
   </si>
   <si>
     <t xml:space="preserve">5.40788698196411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32682132720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28616046905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36748218536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30268001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5466456413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35960626602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23762321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22949123382568</t>
+    <t xml:space="preserve">6.32682085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28615999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36748170852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30267953872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35960578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23762369155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22949075698853</t>
   </si>
   <si>
     <t xml:space="preserve">7.12377309799194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07497882843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17256546020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21322679519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06684732437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96112966537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92046880722046</t>
+    <t xml:space="preserve">7.07497978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21322536468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0668478012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9611291885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92046928405762</t>
   </si>
   <si>
     <t xml:space="preserve">7.27828407287598</t>
@@ -2390,151 +2390,151 @@
     <t xml:space="preserve">6.92860078811646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9936580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10750865936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29454803466797</t>
+    <t xml:space="preserve">6.99365901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10750818252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29454898834229</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26201915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18069887161255</t>
+    <t xml:space="preserve">7.26202011108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18069791793823</t>
   </si>
   <si>
     <t xml:space="preserve">7.31081247329712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47345542907715</t>
+    <t xml:space="preserve">7.47345495223999</t>
   </si>
   <si>
     <t xml:space="preserve">7.48972082138062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70115661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70928812026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40839719772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82288312911987</t>
+    <t xml:space="preserve">7.7011570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70928907394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44905948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40839910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82288360595703</t>
   </si>
   <si>
     <t xml:space="preserve">6.87980842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86354303359985</t>
+    <t xml:space="preserve">6.86354351043701</t>
   </si>
   <si>
     <t xml:space="preserve">7.09124422073364</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38400220870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53851318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60356998443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57104206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78247690200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9939136505127</t>
+    <t xml:space="preserve">7.38400077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53851366043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60357046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57104158401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78247785568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99391460418701</t>
   </si>
   <si>
     <t xml:space="preserve">7.94512128829956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86380004882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82313776016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90446090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79874229431152</t>
+    <t xml:space="preserve">7.86379957199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82313871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90445947647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79874181747437</t>
   </si>
   <si>
     <t xml:space="preserve">7.83127117156982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72555303573608</t>
+    <t xml:space="preserve">7.72555208206177</t>
   </si>
   <si>
     <t xml:space="preserve">7.57917356491089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6198353767395</t>
+    <t xml:space="preserve">7.61983442306519</t>
   </si>
   <si>
     <t xml:space="preserve">7.44092607498169</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56291007995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84753561019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26227474212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13216209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14842510223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05083847045898</t>
+    <t xml:space="preserve">7.56290912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8475341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26227569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13216114044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1484260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0508394241333</t>
   </si>
   <si>
     <t xml:space="preserve">8.11589622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87193202972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55477666854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69302415847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75808095932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37612628936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24600982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21348094940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05897235870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79060935974121</t>
+    <t xml:space="preserve">7.87193298339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55477714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69302463531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75808143615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37612533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24601078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21348285675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0589714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79060983657837</t>
   </si>
   <si>
     <t xml:space="preserve">8.07523536682129</t>
@@ -2546,49 +2546,49 @@
     <t xml:space="preserve">7.98578214645386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92072439193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.018310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06710338592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95325326919556</t>
+    <t xml:space="preserve">7.92072629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01830863952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06710243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95325374603271</t>
   </si>
   <si>
     <t xml:space="preserve">7.71742010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73368453979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92885684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0833683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57129573822021</t>
+    <t xml:space="preserve">7.73368549346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92885732650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08336734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57129669189453</t>
   </si>
   <si>
     <t xml:space="preserve">8.65261936187744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45744800567627</t>
+    <t xml:space="preserve">8.45744705200195</t>
   </si>
   <si>
     <t xml:space="preserve">8.44118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5399112701416</t>
+    <t xml:space="preserve">8.53991031646729</t>
   </si>
   <si>
     <t xml:space="preserve">8.37536525726318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30954551696777</t>
+    <t xml:space="preserve">8.30954742431641</t>
   </si>
   <si>
     <t xml:space="preserve">8.50700092315674</t>
@@ -2597,34 +2597,34 @@
     <t xml:space="preserve">8.91836452484131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06645679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34618186950684</t>
+    <t xml:space="preserve">9.06645584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34618377685547</t>
   </si>
   <si>
     <t xml:space="preserve">9.39554691314697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46136379241943</t>
+    <t xml:space="preserve">9.46136474609375</t>
   </si>
   <si>
     <t xml:space="preserve">9.52718257904053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60945510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56009101867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54363822937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32972717285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36263751983643</t>
+    <t xml:space="preserve">9.60945606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56009197235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5436372756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32972812652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36263656616211</t>
   </si>
   <si>
     <t xml:space="preserve">9.37909126281738</t>
@@ -2639,25 +2639,25 @@
     <t xml:space="preserve">9.01709175109863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88545417785645</t>
+    <t xml:space="preserve">8.88545608520508</t>
   </si>
   <si>
     <t xml:space="preserve">9.03354549407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11581802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8196382522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73736381530762</t>
+    <t xml:space="preserve">9.11581897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81963729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73736476898193</t>
   </si>
   <si>
     <t xml:space="preserve">8.83609199523926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95127487182617</t>
+    <t xml:space="preserve">8.95127391815186</t>
   </si>
   <si>
     <t xml:space="preserve">8.90190982818604</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">8.42472743988037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57281875610352</t>
+    <t xml:space="preserve">8.57281970977783</t>
   </si>
   <si>
     <t xml:space="preserve">8.58927345275879</t>
@@ -2678,82 +2678,82 @@
     <t xml:space="preserve">8.63863658905029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60572814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40827369689941</t>
+    <t xml:space="preserve">8.60572719573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40827465057373</t>
   </si>
   <si>
     <t xml:space="preserve">8.24372959136963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34245586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77027416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85254669189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68800258636475</t>
+    <t xml:space="preserve">8.29309177398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34245491027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77027320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85254573822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68800067901611</t>
   </si>
   <si>
     <t xml:space="preserve">8.80318260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08291053771973</t>
+    <t xml:space="preserve">9.08290958404541</t>
   </si>
   <si>
     <t xml:space="preserve">9.099365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18163776397705</t>
+    <t xml:space="preserve">9.18163871765137</t>
   </si>
   <si>
     <t xml:space="preserve">8.70445537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75381755828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65509223937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62218284606934</t>
+    <t xml:space="preserve">8.75381946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6550931930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62218379974365</t>
   </si>
   <si>
     <t xml:space="preserve">8.55636405944824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96772766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98418426513672</t>
+    <t xml:space="preserve">8.96772861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98418235778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.35890960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27663612365723</t>
+    <t xml:space="preserve">8.27663803100586</t>
   </si>
   <si>
     <t xml:space="preserve">8.18613719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26018333435059</t>
+    <t xml:space="preserve">8.26018238067627</t>
   </si>
   <si>
     <t xml:space="preserve">8.14500045776367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98045492172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.996910572052</t>
+    <t xml:space="preserve">7.98045444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99690961837769</t>
   </si>
   <si>
     <t xml:space="preserve">8.20259284973145</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">7.94754552841187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93931913375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03804588317871</t>
+    <t xml:space="preserve">7.93931865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03804779052734</t>
   </si>
   <si>
     <t xml:space="preserve">8.12854671478271</t>
@@ -2777,88 +2777,88 @@
     <t xml:space="preserve">8.13677406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89818382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9557728767395</t>
+    <t xml:space="preserve">7.89818286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95577383041382</t>
   </si>
   <si>
     <t xml:space="preserve">8.01336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83236455917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97222757339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08740997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10386562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16968250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05000019073486</t>
+    <t xml:space="preserve">7.83236360549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97222805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08740901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1038646697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16968154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05000114440918</t>
   </si>
   <si>
     <t xml:space="preserve">9.00063705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13227462768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88995456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87349987030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56909132003784</t>
+    <t xml:space="preserve">9.13227367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87350034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.569091796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.60200023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59377193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15772724151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21531963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12481880187988</t>
+    <t xml:space="preserve">7.59377241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15772867202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21531915664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12481832504272</t>
   </si>
   <si>
     <t xml:space="preserve">7.39631843566895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30581903457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24000024795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69250249862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55263757705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52795553207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33872890472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4621376991272</t>
+    <t xml:space="preserve">7.30581855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2400016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69250011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55263710021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52795457839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33872747421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46213722229004</t>
   </si>
   <si>
     <t xml:space="preserve">7.4045467376709</t>
@@ -2873,88 +2873,88 @@
     <t xml:space="preserve">7.70895528793335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79945516586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21081924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12031841278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07918262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79122829437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85704660415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02159214019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463661193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81590986251831</t>
+    <t xml:space="preserve">7.7994556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21081829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12031936645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07918357849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79122877120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85704708099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02159309387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81590938568115</t>
   </si>
   <si>
     <t xml:space="preserve">7.78300094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6760458946228</t>
+    <t xml:space="preserve">7.70072793960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67604684829712</t>
   </si>
   <si>
     <t xml:space="preserve">7.42922735214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29759168624878</t>
+    <t xml:space="preserve">7.29759073257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.66781949996948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48681974411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6102294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68427324295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51150035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41277408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76654624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65136480331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7336368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82413816452026</t>
+    <t xml:space="preserve">7.48681926727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61022758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68427419662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5115008354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41277456283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76654577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65136384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73363637924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82413721084595</t>
   </si>
   <si>
     <t xml:space="preserve">7.71718311309814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58554649353027</t>
+    <t xml:space="preserve">7.58554601669312</t>
   </si>
   <si>
     <t xml:space="preserve">7.47036361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90268278121948</t>
+    <t xml:space="preserve">6.9026837348938</t>
   </si>
   <si>
     <t xml:space="preserve">6.72168254852295</t>
@@ -2966,25 +2966,25 @@
     <t xml:space="preserve">7.10836505889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28936386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49504661560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50327396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37163686752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42100143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51972818374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22727394104004</t>
+    <t xml:space="preserve">7.28936433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49504709243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50327348709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37163734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4210000038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5197286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22727298736572</t>
   </si>
   <si>
     <t xml:space="preserve">8.15322780609131</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">8.02981948852539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09563827514648</t>
+    <t xml:space="preserve">8.09563732147217</t>
   </si>
   <si>
     <t xml:space="preserve">8.07095623016357</t>
@@ -3002,100 +3002,100 @@
     <t xml:space="preserve">7.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80768156051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84059190750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84881925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54441022872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72540950775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31404542922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77477359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73959684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63831520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61299562454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80711936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89152097702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96748065948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87463855743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76491737365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81555843353271</t>
+    <t xml:space="preserve">7.80768299102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84059143066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84881973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54440975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72541046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31404638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77477312088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73959732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63831615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61299467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80711793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89151906967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96748018264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87463998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76491785049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81555891036987</t>
   </si>
   <si>
     <t xml:space="preserve">7.79023694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64675617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35979175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13190841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2500696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0559458732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04750728607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00530624389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16566801071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03062629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03906679153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1150279045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17410898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09814786911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01374673843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92090511322021</t>
+    <t xml:space="preserve">7.64675664901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35979127883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13190698623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25007009506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05594635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04750680923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00530576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16566896438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03062677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03906631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11502838134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17410802841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09814691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01374626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9209041595459</t>
   </si>
   <si>
     <t xml:space="preserve">6.99686574935913</t>
@@ -3104,19 +3104,19 @@
     <t xml:space="preserve">6.75210237503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76898336410522</t>
+    <t xml:space="preserve">6.76898288726807</t>
   </si>
   <si>
     <t xml:space="preserve">6.86182403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98842573165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93778514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92934465408325</t>
+    <t xml:space="preserve">6.98842620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93778562545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92934560775757</t>
   </si>
   <si>
     <t xml:space="preserve">6.83650350570679</t>
@@ -3125,28 +3125,28 @@
     <t xml:space="preserve">6.89558458328247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91246461868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76054239273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6845817565918</t>
+    <t xml:space="preserve">6.9124641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76054286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68458127975464</t>
   </si>
   <si>
     <t xml:space="preserve">6.69302129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94622468948364</t>
+    <t xml:space="preserve">6.9462251663208</t>
   </si>
   <si>
     <t xml:space="preserve">7.14034795761108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02218627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96310567855835</t>
+    <t xml:space="preserve">7.02218675613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96310520172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.06438732147217</t>
@@ -3155,19 +3155,19 @@
     <t xml:space="preserve">6.78586292266846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74366235733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7774224281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72678136825562</t>
+    <t xml:space="preserve">6.74366188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77742195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72678184509277</t>
   </si>
   <si>
     <t xml:space="preserve">6.66770172119141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56641960144043</t>
+    <t xml:space="preserve">6.56641912460327</t>
   </si>
   <si>
     <t xml:space="preserve">6.38073635101318</t>
@@ -3182,34 +3182,34 @@
     <t xml:space="preserve">6.40605735778809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21193408966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22037410736084</t>
+    <t xml:space="preserve">6.21193361282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22037363052368</t>
   </si>
   <si>
     <t xml:space="preserve">6.24569463729858</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16129350662231</t>
+    <t xml:space="preserve">6.16129398345947</t>
   </si>
   <si>
     <t xml:space="preserve">6.33009576797485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45669841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28789567947388</t>
+    <t xml:space="preserve">6.45669794082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28789520263672</t>
   </si>
   <si>
     <t xml:space="preserve">6.16973304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11909246444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14441299438477</t>
+    <t xml:space="preserve">6.11909294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14441394805908</t>
   </si>
   <si>
     <t xml:space="preserve">6.04313135147095</t>
@@ -3218,19 +3218,19 @@
     <t xml:space="preserve">6.08533191680908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06845188140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8827691078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95872974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00093126296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98405075073242</t>
+    <t xml:space="preserve">6.06845235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88276863098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95873022079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00093078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98405122756958</t>
   </si>
   <si>
     <t xml:space="preserve">5.92496967315674</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">6.03469181060791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99249124526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87432909011841</t>
+    <t xml:space="preserve">5.99249076843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87432956695557</t>
   </si>
   <si>
     <t xml:space="preserve">5.69708633422852</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62956523895264</t>
+    <t xml:space="preserve">5.62956571578979</t>
   </si>
   <si>
     <t xml:space="preserve">5.57048463821411</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">5.62112522125244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59580516815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66332578659058</t>
+    <t xml:space="preserve">5.5958046913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66332626342773</t>
   </si>
   <si>
     <t xml:space="preserve">5.67176580429077</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">5.51140356063843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49452352523804</t>
+    <t xml:space="preserve">5.49452304840088</t>
   </si>
   <si>
     <t xml:space="preserve">5.57892465591431</t>
@@ -3281,25 +3281,25 @@
     <t xml:space="preserve">5.5873646736145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82368850708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07689189910889</t>
+    <t xml:space="preserve">5.82368803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07689237594604</t>
   </si>
   <si>
     <t xml:space="preserve">5.93341016769409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05157232284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79836797714233</t>
+    <t xml:space="preserve">6.0515718460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79836750030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.19505405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00937080383301</t>
+    <t xml:space="preserve">6.00937128067017</t>
   </si>
   <si>
     <t xml:space="preserve">5.90808916091919</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">5.85744857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89964866638184</t>
+    <t xml:space="preserve">5.89964914321899</t>
   </si>
   <si>
     <t xml:space="preserve">5.72240686416626</t>
@@ -3320,67 +3320,67 @@
     <t xml:space="preserve">5.77304744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74772644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89121007919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76460695266724</t>
+    <t xml:space="preserve">5.74772787094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89120960235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76460742950439</t>
   </si>
   <si>
     <t xml:space="preserve">5.95029020309448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81524801254272</t>
+    <t xml:space="preserve">5.81524753570557</t>
   </si>
   <si>
     <t xml:space="preserve">5.70552682876587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84900808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73084688186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80680799484253</t>
+    <t xml:space="preserve">5.84900856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7308464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80680847167969</t>
   </si>
   <si>
     <t xml:space="preserve">5.65488576889038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68020629882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78148794174194</t>
+    <t xml:space="preserve">5.68020582199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78148746490479</t>
   </si>
   <si>
     <t xml:space="preserve">6.01781129837036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9165301322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22881460189819</t>
+    <t xml:space="preserve">5.91652965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22881507873535</t>
   </si>
   <si>
     <t xml:space="preserve">6.41449689865112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44825792312622</t>
+    <t xml:space="preserve">6.44825744628906</t>
   </si>
   <si>
     <t xml:space="preserve">6.49045848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29633569717407</t>
+    <t xml:space="preserve">6.29633522033691</t>
   </si>
   <si>
     <t xml:space="preserve">6.23725414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27945470809937</t>
+    <t xml:space="preserve">6.27945518493652</t>
   </si>
   <si>
     <t xml:space="preserve">6.20349407196045</t>
@@ -3389,55 +3389,55 @@
     <t xml:space="preserve">6.06001138687134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13597345352173</t>
+    <t xml:space="preserve">6.13597249984741</t>
   </si>
   <si>
     <t xml:space="preserve">6.11065244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3891773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36385583877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43137741088867</t>
+    <t xml:space="preserve">6.38917684555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36385631561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43137788772583</t>
   </si>
   <si>
     <t xml:space="preserve">6.33853626251221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34697675704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3216552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30477523803711</t>
+    <t xml:space="preserve">6.3469762802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32165575027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30477571487427</t>
   </si>
   <si>
     <t xml:space="preserve">6.37229681015015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31321573257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97561073303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84056901931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83212852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58329963684082</t>
+    <t xml:space="preserve">6.31321620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97561025619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84056854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83212900161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58330059051514</t>
   </si>
   <si>
     <t xml:space="preserve">6.10221290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09377241134644</t>
+    <t xml:space="preserve">6.09377193450928</t>
   </si>
   <si>
     <t xml:space="preserve">6.27101516723633</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">6.47591114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27863168716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57026147842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77611875534058</t>
+    <t xml:space="preserve">6.27863121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57026195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77611923217773</t>
   </si>
   <si>
     <t xml:space="preserve">6.75896406173706</t>
@@ -3470,10 +3470,10 @@
     <t xml:space="preserve">6.78469562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88762426376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87046957015991</t>
+    <t xml:space="preserve">6.88762378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87047004699707</t>
   </si>
   <si>
     <t xml:space="preserve">6.80185079574585</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">6.70749998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69034481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64745855331421</t>
+    <t xml:space="preserve">6.69034576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">6.61314868927002</t>
@@ -3497,13 +3497,13 @@
     <t xml:space="preserve">6.81042814254761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86189222335815</t>
+    <t xml:space="preserve">6.86189270019531</t>
   </si>
   <si>
     <t xml:space="preserve">6.74180936813354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83616065979004</t>
+    <t xml:space="preserve">6.83616018295288</t>
   </si>
   <si>
     <t xml:space="preserve">6.79327344894409</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">6.63888072967529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62172603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38155937194824</t>
+    <t xml:space="preserve">6.62172651290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3815598487854</t>
   </si>
   <si>
     <t xml:space="preserve">6.39871454238892</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">6.52737522125244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53595209121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59599447250366</t>
+    <t xml:space="preserve">6.53595304489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5959939956665</t>
   </si>
   <si>
     <t xml:space="preserve">6.63030338287354</t>
@@ -3551,16 +3551,16 @@
     <t xml:space="preserve">6.48448801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65603542327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76754140853882</t>
+    <t xml:space="preserve">6.65603590011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76754093170166</t>
   </si>
   <si>
     <t xml:space="preserve">6.8533148765564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93051147460938</t>
+    <t xml:space="preserve">6.93051099777222</t>
   </si>
   <si>
     <t xml:space="preserve">6.94766616821289</t>
@@ -3572,25 +3572,25 @@
     <t xml:space="preserve">6.84473752975464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10205793380737</t>
+    <t xml:space="preserve">7.10205888748169</t>
   </si>
   <si>
     <t xml:space="preserve">7.18783235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13636779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99055290222168</t>
+    <t xml:space="preserve">7.13636827468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99055242538452</t>
   </si>
   <si>
     <t xml:space="preserve">6.9047794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99912977218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92193412780762</t>
+    <t xml:space="preserve">6.99913024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92193365097046</t>
   </si>
   <si>
     <t xml:space="preserve">6.91335678100586</t>
@@ -3599,28 +3599,28 @@
     <t xml:space="preserve">7.12779092788696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24787425994873</t>
+    <t xml:space="preserve">7.24787282943726</t>
   </si>
   <si>
     <t xml:space="preserve">7.17925500869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07632684707642</t>
+    <t xml:space="preserve">7.07632637023926</t>
   </si>
   <si>
     <t xml:space="preserve">7.09348154067993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20498657226562</t>
+    <t xml:space="preserve">7.20498609542847</t>
   </si>
   <si>
     <t xml:space="preserve">7.14494562149048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15352296829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01628494262695</t>
+    <t xml:space="preserve">7.15352249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01628589630127</t>
   </si>
   <si>
     <t xml:space="preserve">6.97339820861816</t>
@@ -3629,28 +3629,31 @@
     <t xml:space="preserve">6.98197603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55310726165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35582733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33867311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31294107437134</t>
+    <t xml:space="preserve">6.55310678482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35582780838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33009624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33867263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31294059753418</t>
   </si>
   <si>
     <t xml:space="preserve">6.42444658279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26147699356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20143508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3215184211731</t>
+    <t xml:space="preserve">6.26147747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20143556594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32151794433594</t>
   </si>
   <si>
     <t xml:space="preserve">6.13281679153442</t>
@@ -3659,40 +3662,40 @@
     <t xml:space="preserve">6.218590259552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34725093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29578590393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14997148513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10708379745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1671257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03846502304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0041561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89265012741089</t>
+    <t xml:space="preserve">6.34725046157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29578638076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14997100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10708427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16712617874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03846549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00415563583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89264965057373</t>
   </si>
   <si>
     <t xml:space="preserve">5.96126890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96984624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08135223388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12423849105835</t>
+    <t xml:space="preserve">5.96984672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08135271072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12423896789551</t>
   </si>
   <si>
     <t xml:space="preserve">6.45875644683838</t>
@@ -3701,19 +3704,19 @@
     <t xml:space="preserve">6.39013719558716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41586923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56168508529663</t>
+    <t xml:space="preserve">6.41586971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56168460845947</t>
   </si>
   <si>
     <t xml:space="preserve">6.68176794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05917119979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95624303817749</t>
+    <t xml:space="preserve">7.05917167663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95624351501465</t>
   </si>
   <si>
     <t xml:space="preserve">7.03343915939331</t>
@@ -3722,82 +3725,82 @@
     <t xml:space="preserve">7.11921310424805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23929595947266</t>
+    <t xml:space="preserve">7.23929643630981</t>
   </si>
   <si>
     <t xml:space="preserve">7.29933834075928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3765344619751</t>
+    <t xml:space="preserve">7.37653493881226</t>
   </si>
   <si>
     <t xml:space="preserve">7.55665969848633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44515371322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29076051712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43657636642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38511180877686</t>
+    <t xml:space="preserve">7.44515323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2907600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43657541275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3851113319397</t>
   </si>
   <si>
     <t xml:space="preserve">7.47946262359619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46230745315552</t>
+    <t xml:space="preserve">7.46230840682983</t>
   </si>
   <si>
     <t xml:space="preserve">7.50519514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49661731719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59954500198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5309271812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48803901672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40226650238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51377201080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35937929153442</t>
+    <t xml:space="preserve">7.49661684036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59954595565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48803949356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40226697921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51377248764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35937976837158</t>
   </si>
   <si>
     <t xml:space="preserve">7.34222507476807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66816473007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8139796257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68531894683838</t>
+    <t xml:space="preserve">7.66816425323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81398057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68531942367554</t>
   </si>
   <si>
     <t xml:space="preserve">7.67674207687378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60812330245972</t>
+    <t xml:space="preserve">7.6081223487854</t>
   </si>
   <si>
     <t xml:space="preserve">7.69389724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90833139419556</t>
+    <t xml:space="preserve">7.9083309173584</t>
   </si>
   <si>
     <t xml:space="preserve">8.07130146026611</t>
@@ -3806,7 +3809,7 @@
     <t xml:space="preserve">8.29431247711182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2342700958252</t>
+    <t xml:space="preserve">8.23427104949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.37150859832764</t>
@@ -3815,19 +3818,19 @@
     <t xml:space="preserve">8.12528800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96113967895508</t>
+    <t xml:space="preserve">7.96114063262939</t>
   </si>
   <si>
     <t xml:space="preserve">7.97026014328003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85170936584473</t>
+    <t xml:space="preserve">7.85170841217041</t>
   </si>
   <si>
     <t xml:space="preserve">7.76051664352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60548877716064</t>
+    <t xml:space="preserve">7.60548782348633</t>
   </si>
   <si>
     <t xml:space="preserve">7.69668102264404</t>
@@ -3839,7 +3842,7 @@
     <t xml:space="preserve">7.56901121139526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61460876464844</t>
+    <t xml:space="preserve">7.61460781097412</t>
   </si>
   <si>
     <t xml:space="preserve">7.75139713287354</t>
@@ -3851,13 +3854,13 @@
     <t xml:space="preserve">7.73315811157227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65108489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76963567733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77875471115112</t>
+    <t xml:space="preserve">7.65108585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76963663101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77875518798828</t>
   </si>
   <si>
     <t xml:space="preserve">7.82435131072998</t>
@@ -3869,43 +3872,43 @@
     <t xml:space="preserve">7.97937965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84259033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74227714538574</t>
+    <t xml:space="preserve">7.84259080886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7422776222229</t>
   </si>
   <si>
     <t xml:space="preserve">7.78787469863892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86082792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72403955459595</t>
+    <t xml:space="preserve">7.8608283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72403907775879</t>
   </si>
   <si>
     <t xml:space="preserve">7.81523180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71492004394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79699420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66932344436646</t>
+    <t xml:space="preserve">7.71491956710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79699373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6693229675293</t>
   </si>
   <si>
     <t xml:space="preserve">7.24983596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20423984527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10392761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16776275634766</t>
+    <t xml:space="preserve">7.20424032211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10392713546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1677622795105</t>
   </si>
   <si>
     <t xml:space="preserve">7.22247838973999</t>
@@ -3920,13 +3923,13 @@
     <t xml:space="preserve">6.99449634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19512033462524</t>
+    <t xml:space="preserve">7.19511985778809</t>
   </si>
   <si>
     <t xml:space="preserve">7.14952421188354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3592677116394</t>
+    <t xml:space="preserve">7.35926723480225</t>
   </si>
   <si>
     <t xml:space="preserve">7.47781801223755</t>
@@ -3935,40 +3938,40 @@
     <t xml:space="preserve">7.49605751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66020393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48693752288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52341508865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64196586608887</t>
+    <t xml:space="preserve">7.66020345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48693799972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52341461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64196634292603</t>
   </si>
   <si>
     <t xml:space="preserve">7.99761819839478</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02497673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01585578918457</t>
+    <t xml:space="preserve">8.02497577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01585674285889</t>
   </si>
   <si>
     <t xml:space="preserve">8.09793090820312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18000411987305</t>
+    <t xml:space="preserve">8.18000316619873</t>
   </si>
   <si>
     <t xml:space="preserve">8.03409576416016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00673770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1526460647583</t>
+    <t xml:space="preserve">8.00673675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15264511108398</t>
   </si>
   <si>
     <t xml:space="preserve">8.1070499420166</t>
@@ -3977,10 +3980,10 @@
     <t xml:space="preserve">8.04321384429932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27119636535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2438383102417</t>
+    <t xml:space="preserve">8.27119731903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24383926391602</t>
   </si>
   <si>
     <t xml:space="preserve">8.14217758178711</t>
@@ -4101,9 +4104,6 @@
   </si>
   <si>
     <t xml:space="preserve">8.19762897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24383926391602</t>
   </si>
   <si>
     <t xml:space="preserve">7.86491823196411</t>
@@ -56233,7 +56233,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1970" t="s">
-        <v>1060</v>
+        <v>1207</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56259,7 +56259,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1971" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56285,7 +56285,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1972" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56311,7 +56311,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1973" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56337,7 +56337,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1974" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56363,7 +56363,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1975" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56389,7 +56389,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1976" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56415,7 +56415,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56441,7 +56441,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1978" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56467,7 +56467,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1979" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -56493,7 +56493,7 @@
         <v>7.25</v>
       </c>
       <c r="G1980" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -56519,7 +56519,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1981" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56545,7 +56545,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1982" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56571,7 +56571,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1983" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56597,7 +56597,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1984" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56623,7 +56623,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1985" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56649,7 +56649,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1986" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56675,7 +56675,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1987" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56701,7 +56701,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56727,7 +56727,7 @@
         <v>7</v>
       </c>
       <c r="G1989" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56753,7 +56753,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1990" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56779,7 +56779,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1991" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56805,7 +56805,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1992" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56831,7 +56831,7 @@
         <v>7</v>
       </c>
       <c r="G1993" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56857,7 +56857,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56883,7 +56883,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1995" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56909,7 +56909,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1996" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56935,7 +56935,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1997" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56961,7 +56961,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1998" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56987,7 +56987,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1999" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57013,7 +57013,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2000" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57039,7 +57039,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57117,7 +57117,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2004" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57143,7 +57143,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2005" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57247,7 +57247,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G2009" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57403,7 +57403,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G2015" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57481,7 +57481,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2018" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57507,7 +57507,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2019" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57533,7 +57533,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2020" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57559,7 +57559,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2021" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57585,7 +57585,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2022" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57611,7 +57611,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2023" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57637,7 +57637,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2024" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57663,7 +57663,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2025" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57689,7 +57689,7 @@
         <v>8.5</v>
       </c>
       <c r="G2026" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57715,7 +57715,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2027" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57741,7 +57741,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57767,7 +57767,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G2029" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57793,7 +57793,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2030" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57819,7 +57819,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2031" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57845,7 +57845,7 @@
         <v>8.75</v>
       </c>
       <c r="G2032" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57871,7 +57871,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2033" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57897,7 +57897,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2034" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57923,7 +57923,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2035" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57949,7 +57949,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2036" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57975,7 +57975,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2037" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58001,7 +58001,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2038" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58027,7 +58027,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2039" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58053,7 +58053,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2040" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58079,7 +58079,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2041" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58105,7 +58105,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2042" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58131,7 +58131,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G2043" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58157,7 +58157,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2044" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58183,7 +58183,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G2045" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58209,7 +58209,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58235,7 +58235,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2047" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58261,7 +58261,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2048" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58287,7 +58287,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2049" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58313,7 +58313,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2050" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58339,7 +58339,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2051" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58365,7 +58365,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2052" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58391,7 +58391,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2053" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58417,7 +58417,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2054" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58443,7 +58443,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2055" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58469,7 +58469,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2056" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58495,7 +58495,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2057" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58521,7 +58521,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2058" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58547,7 +58547,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G2059" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58573,7 +58573,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2060" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58599,7 +58599,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2061" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58625,7 +58625,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2062" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58651,7 +58651,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G2063" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58677,7 +58677,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2064" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58703,7 +58703,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2065" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58729,7 +58729,7 @@
         <v>8.5</v>
       </c>
       <c r="G2066" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58755,7 +58755,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2067" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58781,7 +58781,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2068" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58807,7 +58807,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2069" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58833,7 +58833,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G2070" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58859,7 +58859,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2071" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58885,7 +58885,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G2072" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58911,7 +58911,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58937,7 +58937,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2074" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58963,7 +58963,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2075" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58989,7 +58989,7 @@
         <v>8.75</v>
       </c>
       <c r="G2076" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59015,7 +59015,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2077" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59041,7 +59041,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2078" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59067,7 +59067,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59093,7 +59093,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2080" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59119,7 +59119,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2081" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59145,7 +59145,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2082" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59171,7 +59171,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2083" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59197,7 +59197,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2084" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59223,7 +59223,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2085" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59249,7 +59249,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2086" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59275,7 +59275,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2087" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59301,7 +59301,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2088" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59327,7 +59327,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2089" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59353,7 +59353,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G2090" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59379,7 +59379,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2091" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59405,7 +59405,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2092" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59431,7 +59431,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2093" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59457,7 +59457,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59483,7 +59483,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2095" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59509,7 +59509,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2096" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59535,7 +59535,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59561,7 +59561,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2098" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59587,7 +59587,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59613,7 +59613,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59639,7 +59639,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59665,7 +59665,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G2102" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59691,7 +59691,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2103" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59717,7 +59717,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G2104" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59743,7 +59743,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2105" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59769,7 +59769,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2106" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59795,7 +59795,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2107" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59821,7 +59821,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G2108" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59847,7 +59847,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2109" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59873,7 +59873,7 @@
         <v>8.25</v>
       </c>
       <c r="G2110" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59899,7 +59899,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G2111" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59925,7 +59925,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2112" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59951,7 +59951,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2113" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59977,7 +59977,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2114" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60003,7 +60003,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2115" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60029,7 +60029,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2116" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60055,7 +60055,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2117" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60081,7 +60081,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2118" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60107,7 +60107,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2119" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60133,7 +60133,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2120" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60159,7 +60159,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2121" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60185,7 +60185,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2122" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60211,7 +60211,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2123" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60237,7 +60237,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2124" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60263,7 +60263,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60289,7 +60289,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2126" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60315,7 +60315,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2127" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60341,7 +60341,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2128" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60367,7 +60367,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2129" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60393,7 +60393,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2130" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60419,7 +60419,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2131" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60445,7 +60445,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60471,7 +60471,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2133" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60497,7 +60497,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2134" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60523,7 +60523,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2135" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60549,7 +60549,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60575,7 +60575,7 @@
         <v>9</v>
       </c>
       <c r="G2137" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60601,7 +60601,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2138" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60627,7 +60627,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G2139" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60653,7 +60653,7 @@
         <v>9</v>
       </c>
       <c r="G2140" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60679,7 +60679,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2141" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60705,7 +60705,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2142" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60731,7 +60731,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2143" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60757,7 +60757,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2144" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60783,7 +60783,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G2145" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60809,7 +60809,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2146" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60835,7 +60835,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2147" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60861,7 +60861,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2148" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60887,7 +60887,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2149" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60913,7 +60913,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G2150" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60939,7 +60939,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2151" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60965,7 +60965,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2152" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60991,7 +60991,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G2153" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61017,7 +61017,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2154" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61043,7 +61043,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2155" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61069,7 +61069,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2156" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61095,7 +61095,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2157" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61121,7 +61121,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2158" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61147,7 +61147,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61173,7 +61173,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2160" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61199,7 +61199,7 @@
         <v>8.5</v>
       </c>
       <c r="G2161" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61225,7 +61225,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2162" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61251,7 +61251,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2163" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61277,7 +61277,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61303,7 +61303,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2165" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61329,7 +61329,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2166" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61355,7 +61355,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2167" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61381,7 +61381,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2168" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61407,7 +61407,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2169" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61433,7 +61433,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2170" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61459,7 +61459,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2171" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61485,7 +61485,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2172" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61511,7 +61511,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2173" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61537,7 +61537,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2174" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61563,7 +61563,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2175" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61589,7 +61589,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2176" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61615,7 +61615,7 @@
         <v>8.75</v>
       </c>
       <c r="G2177" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61641,7 +61641,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G2178" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61667,7 +61667,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2179" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61693,7 +61693,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2180" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61719,7 +61719,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2181" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61745,7 +61745,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2182" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61771,7 +61771,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2183" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61797,7 +61797,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2184" t="s">
-        <v>1363</v>
+        <v>1323</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61823,7 +61823,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2185" t="s">
-        <v>1363</v>
+        <v>1323</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61849,7 +61849,7 @@
         <v>8.75</v>
       </c>
       <c r="G2186" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61927,7 +61927,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2189" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61979,7 +61979,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2191" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62031,7 +62031,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2193" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62057,7 +62057,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2194" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62083,7 +62083,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2195" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62187,7 +62187,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2199" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62213,7 +62213,7 @@
         <v>9</v>
       </c>
       <c r="G2200" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62291,7 +62291,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2203" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62317,7 +62317,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2204" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62343,7 +62343,7 @@
         <v>9</v>
       </c>
       <c r="G2205" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62421,7 +62421,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2208" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62499,7 +62499,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2211" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62551,7 +62551,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2213" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62577,7 +62577,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2214" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62629,7 +62629,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2216" t="s">
-        <v>1363</v>
+        <v>1323</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62759,7 +62759,7 @@
         <v>9</v>
       </c>
       <c r="G2221" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -70281,7 +70281,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6910648148</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>337201</v>
@@ -70302,6 +70302,32 @@
         <v>1556</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6910416667</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>698451</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>9.77999973297119</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>9.55000019073486</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="1580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1582">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79523372650146</t>
+    <t xml:space="preserve">7.79523468017578</t>
   </si>
   <si>
     <t xml:space="preserve">FILA.MI</t>
@@ -47,124 +47,124 @@
     <t xml:space="preserve">7.74423742294312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72238206863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72966623306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78795051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7733793258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56939077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54753494262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61310338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21241426467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17598581314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62038850784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46739673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35811710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30712127685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725996017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56210613250732</t>
+    <t xml:space="preserve">7.72238302230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72966814041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78795099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77337837219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56939125061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54753589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61310148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21241331100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17598676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62038803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46739768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35811805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30712175369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725900650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56210565567017</t>
   </si>
   <si>
     <t xml:space="preserve">7.49653911590576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28526496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37268877029419</t>
+    <t xml:space="preserve">7.28526592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37269020080566</t>
   </si>
   <si>
     <t xml:space="preserve">7.64952850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.518394947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5839638710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67867088317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86080312728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76609325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89722871780396</t>
+    <t xml:space="preserve">7.51839447021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58396244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67867040634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86080074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76609182357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89722776412964</t>
   </si>
   <si>
     <t xml:space="preserve">7.90451335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95551013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80980491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88994264602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00650787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94094181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87537336349487</t>
+    <t xml:space="preserve">7.95550966262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80980539321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88994359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00650691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94094038009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87537240982056</t>
   </si>
   <si>
     <t xml:space="preserve">8.01379203796387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9482250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03564929962158</t>
+    <t xml:space="preserve">7.94822692871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03564739227295</t>
   </si>
   <si>
     <t xml:space="preserve">7.80251979827881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84623003005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05750465393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05021953582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02836418151855</t>
+    <t xml:space="preserve">7.84623050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05750274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05021858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02836513519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.15949821472168</t>
@@ -173,58 +173,58 @@
     <t xml:space="preserve">8.38534164428711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45090770721436</t>
+    <t xml:space="preserve">8.4509105682373</t>
   </si>
   <si>
     <t xml:space="preserve">8.43633842468262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45819282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63304042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71317863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60389804840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74231910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80788803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42176723480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73503398895264</t>
+    <t xml:space="preserve">8.45819473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6330394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71317958831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60389709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7423210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80788707733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42176914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73503303527832</t>
   </si>
   <si>
     <t xml:space="preserve">8.79331684112549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65489768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70589351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81517314910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95359134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75688934326172</t>
+    <t xml:space="preserve">8.6548957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70589256286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81517124176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95359325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75689029693604</t>
   </si>
   <si>
     <t xml:space="preserve">9.20857620239258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26686096191406</t>
+    <t xml:space="preserve">9.26685810089111</t>
   </si>
   <si>
     <t xml:space="preserve">9.25228881835938</t>
@@ -233,130 +233,130 @@
     <t xml:space="preserve">9.39799308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48541736602783</t>
+    <t xml:space="preserve">9.48541831970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32488346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07543754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09744834899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17081546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2955379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36890411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27352714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28820037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20749855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24418067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11212158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02408218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87734794616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84066295623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80398178100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73061561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95071411132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22950744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81865501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82599258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91403007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31754779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95805168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9947338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1928243637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13412952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34689331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35422992706299</t>
   </si>
   <si>
     <t xml:space="preserve">9.36156749725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32488441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07543849945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09744834899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17081356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29553890228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36890411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27352809906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28820037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20749759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24418067932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11212158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02408123016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87734985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84066390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398178100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73061561584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95071411132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22950839996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81865406036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82599067687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91403102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31754779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95805072784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99473571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19282150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13413047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34689331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35423183441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36156845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22217178344727</t>
+    <t xml:space="preserve">9.22217082977295</t>
   </si>
   <si>
     <t xml:space="preserve">9.06076431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37623977661133</t>
+    <t xml:space="preserve">9.37624073028564</t>
   </si>
   <si>
     <t xml:space="preserve">9.33955669403076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31020832061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28086471557617</t>
+    <t xml:space="preserve">9.31021118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28086376190186</t>
   </si>
   <si>
     <t xml:space="preserve">9.26619052886963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97272396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16347789764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17815113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39825057983398</t>
+    <t xml:space="preserve">8.97272491455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16347694396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17815017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39824867248535</t>
   </si>
   <si>
     <t xml:space="preserve">9.30287456512451</t>
@@ -365,34 +365,34 @@
     <t xml:space="preserve">9.25885391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33222198486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11945629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05342864990234</t>
+    <t xml:space="preserve">9.33221912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11945819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05342960357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.00207138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96538829803467</t>
+    <t xml:space="preserve">8.96538734436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.14146709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01674270629883</t>
+    <t xml:space="preserve">9.01674365997314</t>
   </si>
   <si>
     <t xml:space="preserve">9.39091396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15614032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38357830047607</t>
+    <t xml:space="preserve">9.1561393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38357734680176</t>
   </si>
   <si>
     <t xml:space="preserve">9.44960689544678</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">9.52297306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79442882537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8384485244751</t>
+    <t xml:space="preserve">9.50829982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79442977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83844947814941</t>
   </si>
   <si>
     <t xml:space="preserve">9.85312271118164</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">9.95583629608154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0438756942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.139253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2566404342651</t>
+    <t xml:space="preserve">10.0438766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1392526626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2566385269165</t>
   </si>
   <si>
     <t xml:space="preserve">10.1979455947876</t>
@@ -434,31 +434,31 @@
     <t xml:space="preserve">10.2713108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90447902679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0145292282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75774669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6550350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64769649505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80910301208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64036083221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53764629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45694351196289</t>
+    <t xml:space="preserve">9.90447998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0145282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75774765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65503406524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64769554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80910396575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64035797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45694541931152</t>
   </si>
   <si>
     <t xml:space="preserve">9.41292381286621</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">9.61834907531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56699371337891</t>
+    <t xml:space="preserve">9.56699180603027</t>
   </si>
   <si>
     <t xml:space="preserve">9.44227027893066</t>
@@ -476,40 +476,40 @@
     <t xml:space="preserve">9.5156364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53030872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47895336151123</t>
+    <t xml:space="preserve">9.53030967712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47895240783691</t>
   </si>
   <si>
     <t xml:space="preserve">9.63302421569824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47161865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73573589324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0878963470459</t>
+    <t xml:space="preserve">9.55965709686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47161674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7357349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0878953933716</t>
   </si>
   <si>
     <t xml:space="preserve">10.1245775222778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0512113571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86779499053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8311128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97051048278809</t>
+    <t xml:space="preserve">10.051212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8677978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83111095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97050857543945</t>
   </si>
   <si>
     <t xml:space="preserve">9.97784519195557</t>
@@ -521,25 +521,25 @@
     <t xml:space="preserve">9.69171714782715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88980579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86045932769775</t>
+    <t xml:space="preserve">9.88980484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86046028137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.96317195892334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0585508346558</t>
+    <t xml:space="preserve">10.0585489273071</t>
   </si>
   <si>
     <t xml:space="preserve">9.99251842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1612615585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1465883255005</t>
+    <t xml:space="preserve">10.161262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1465892791748</t>
   </si>
   <si>
     <t xml:space="preserve">9.94116306304932</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">9.82377529144287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7210636138916</t>
+    <t xml:space="preserve">9.72106075286865</t>
   </si>
   <si>
     <t xml:space="preserve">9.8751335144043</t>
@@ -560,25 +560,25 @@
     <t xml:space="preserve">10.0805587768555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0071935653687</t>
+    <t xml:space="preserve">10.00719165802</t>
   </si>
   <si>
     <t xml:space="preserve">9.89714241027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69905376434326</t>
+    <t xml:space="preserve">9.69905281066895</t>
   </si>
   <si>
     <t xml:space="preserve">9.985182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3300037384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7335233688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7115116119385</t>
+    <t xml:space="preserve">10.3300046920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7335214614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7115106582642</t>
   </si>
   <si>
     <t xml:space="preserve">10.6674900054932</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">10.8582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8215599060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9316091537476</t>
+    <t xml:space="preserve">10.8215589523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9316110610962</t>
   </si>
   <si>
     <t xml:space="preserve">10.8068876266479</t>
@@ -602,133 +602,133 @@
     <t xml:space="preserve">11.1883926391602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2177410125732</t>
+    <t xml:space="preserve">11.2177419662476</t>
   </si>
   <si>
     <t xml:space="preserve">11.3424625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957292556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1590461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0636711120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0416612625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1517105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2250757217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2984418869019</t>
+    <t xml:space="preserve">11.195728302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.15904712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0636720657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242734909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0416603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1517095565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2250785827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2984428405762</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166328430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7313060760498</t>
+    <t xml:space="preserve">11.7313041687012</t>
   </si>
   <si>
     <t xml:space="preserve">11.8340187072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8853740692139</t>
+    <t xml:space="preserve">11.8853750228882</t>
   </si>
   <si>
     <t xml:space="preserve">11.9954252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6997442245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0225534439087</t>
+    <t xml:space="preserve">12.6997413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0225563049316</t>
   </si>
   <si>
     <t xml:space="preserve">13.0592393875122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2059717178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6924066543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2815551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1054744720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.178840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.479642868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3255739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6850690841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6630592346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619520187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8024568557739</t>
+    <t xml:space="preserve">13.2059726715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6924085617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2815542221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1054763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1788396835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4796438217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3255748748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6850700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6630620956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619539260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8024559020996</t>
   </si>
   <si>
     <t xml:space="preserve">12.8391399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1399431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0005445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491901397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0959234237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0445671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7195358276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929058074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7855682373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295888900757</t>
+    <t xml:space="preserve">13.1399421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0005474090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491910934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0959243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0445652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7195386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929048538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7855672836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295879364014</t>
   </si>
   <si>
     <t xml:space="preserve">13.9396371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">14.064359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828565597534</t>
+    <t xml:space="preserve">14.0643615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828556060791</t>
   </si>
   <si>
     <t xml:space="preserve">13.7268753051758</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">13.8222522735596</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7415475845337</t>
+    <t xml:space="preserve">13.7415466308594</t>
   </si>
   <si>
     <t xml:space="preserve">13.9249649047852</t>
@@ -746,193 +746,193 @@
     <t xml:space="preserve">13.6755170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4480829238892</t>
+    <t xml:space="preserve">13.4480819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.403772354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5364828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8903789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4922466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512294769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6618223190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9641046524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9862241744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0452079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.742919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7650423049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502946853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.654447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4553813934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9346151351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9714794158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7134323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9272413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830032348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0820722579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0083456039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1973352432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069932937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3079252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3300437927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3152990341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6470756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7871589660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8092784881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7797861099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8387670516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9493627548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.118935585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8977499008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9198684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8240222930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9419870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8313961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6765661239624</t>
   </si>
   <si>
     <t xml:space="preserve">13.4627552032471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.403772354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5364837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7945327758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8903789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4922475814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6618204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9641065597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9862251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0452079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7429218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7650394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502956390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.654447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4553804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9346151351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9714794158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7134294509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9272432327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830051422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.082070350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0083436965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8535146713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1973342895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3079271316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3300447463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3152990341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6470756530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7871561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8092775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7797861099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8387699127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9493627548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1189346313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8977518081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9198703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8240222930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9419889450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8313980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4627542495728</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.3816547393799</t>
   </si>
   <si>
     <t xml:space="preserve">13.1014862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5291109085083</t>
+    <t xml:space="preserve">13.529109954834</t>
   </si>
   <si>
     <t xml:space="preserve">13.565975189209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5586023330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2710609436035</t>
+    <t xml:space="preserve">13.5586013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2710618972778</t>
   </si>
   <si>
     <t xml:space="preserve">13.38902759552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5807199478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6102142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4185171127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7060575485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7576675415039</t>
+    <t xml:space="preserve">13.5807189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6102123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4185180664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7060585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7576684951782</t>
   </si>
   <si>
     <t xml:space="preserve">13.6986846923828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8166513442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7281761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7355480194092</t>
+    <t xml:space="preserve">13.8166494369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.728178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7355499267578</t>
   </si>
   <si>
     <t xml:space="preserve">13.7724132537842</t>
   </si>
   <si>
-    <t xml:space="preserve">13.639702796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9051237106323</t>
+    <t xml:space="preserve">13.6397008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9051246643066</t>
   </si>
   <si>
     <t xml:space="preserve">13.6249561309814</t>
@@ -941,100 +941,100 @@
     <t xml:space="preserve">13.602837562561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7456216812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6055421829224</t>
+    <t xml:space="preserve">14.745623588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6055431365967</t>
   </si>
   <si>
     <t xml:space="preserve">14.6129140853882</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5318126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4728298187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5613031387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4359655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2958831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3032550811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590198516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9124937057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.691312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1336793899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304613113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9567317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0378360748291</t>
+    <t xml:space="preserve">14.531813621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4728288650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5613040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4359674453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2958841323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3032560348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590188980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9124984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6913118362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1336803436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9567337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">14.1263074874878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1705455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2147798538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1557998657227</t>
+    <t xml:space="preserve">14.1705446243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2147817611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1558017730713</t>
   </si>
   <si>
     <t xml:space="preserve">14.0230884552002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1041889190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8461389541626</t>
+    <t xml:space="preserve">14.1041917800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8461399078369</t>
   </si>
   <si>
     <t xml:space="preserve">13.8608884811401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9788541793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1926622390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.229528427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5096960067749</t>
+    <t xml:space="preserve">13.978853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1926641464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2295265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5096950531006</t>
   </si>
   <si>
     <t xml:space="preserve">14.6497783660889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7013874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9299440383911</t>
+    <t xml:space="preserve">14.7013883590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9299449920654</t>
   </si>
   <si>
     <t xml:space="preserve">14.8562173843384</t>
@@ -1043,91 +1043,91 @@
     <t xml:space="preserve">14.7824897766113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5834217071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3474931716919</t>
+    <t xml:space="preserve">14.583423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3474941253662</t>
   </si>
   <si>
     <t xml:space="preserve">14.494948387146</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2617225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0774021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1511306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566339492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.33544921875</t>
+    <t xml:space="preserve">15.2617235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0774002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1511287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566377639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4091815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3354473114014</t>
   </si>
   <si>
     <t xml:space="preserve">15.4460401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0405387878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1142663955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6276597976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2885103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2737636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1852912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5391864776611</t>
+    <t xml:space="preserve">15.0405359268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1142673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6276607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2885112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2737646102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1852903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5391874313354</t>
   </si>
   <si>
     <t xml:space="preserve">14.3917303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4212217330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000379562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.406476020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3447895050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5217370986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8756332397461</t>
+    <t xml:space="preserve">14.4212188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000389099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4064741134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3447904586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5217380523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8756341934204</t>
   </si>
   <si>
     <t xml:space="preserve">12.9908952713013</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1383533477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.976149559021</t>
+    <t xml:space="preserve">13.1383514404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9761505126953</t>
   </si>
   <si>
     <t xml:space="preserve">12.7549648284912</t>
@@ -1136,61 +1136,61 @@
     <t xml:space="preserve">12.6517457962036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.887677192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8729305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7254734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0793685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8286962509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5927639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5190372467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.460054397583</t>
+    <t xml:space="preserve">12.8876762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.872932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7254762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0793695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8286933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5927619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5190362930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4600534439087</t>
   </si>
   <si>
     <t xml:space="preserve">12.5042905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7402210235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6812381744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0646209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2858057022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1088609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3005533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0968170166016</t>
+    <t xml:space="preserve">12.7402200698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6812372207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.064624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2858066558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1088590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3005523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0968189239502</t>
   </si>
   <si>
     <t xml:space="preserve">13.3742818832397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3668718338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3075971603394</t>
+    <t xml:space="preserve">13.366870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3075952529907</t>
   </si>
   <si>
     <t xml:space="preserve">13.1890420913696</t>
@@ -1199,25 +1199,25 @@
     <t xml:space="preserve">13.4113292694092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.485424041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9371166229248</t>
+    <t xml:space="preserve">13.4854249954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9371185302734</t>
   </si>
   <si>
     <t xml:space="preserve">12.2702560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7592859268188</t>
+    <t xml:space="preserve">12.7592868804932</t>
   </si>
   <si>
     <t xml:space="preserve">12.5962762832642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.68519115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0408515930176</t>
+    <t xml:space="preserve">12.6851921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0408506393433</t>
   </si>
   <si>
     <t xml:space="preserve">12.9667558670044</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">13.144585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8630218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926610946655</t>
+    <t xml:space="preserve">12.8630208969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926591873169</t>
   </si>
   <si>
     <t xml:space="preserve">12.9963941574097</t>
@@ -1238,34 +1238,34 @@
     <t xml:space="preserve">12.818564414978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7444705963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9815740585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2483205795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2927751541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0853080749512</t>
+    <t xml:space="preserve">12.7444677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.981575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2483196258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2927770614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0853090286255</t>
   </si>
   <si>
     <t xml:space="preserve">13.4706048965454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.529881477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4409675598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2779560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3224143981934</t>
+    <t xml:space="preserve">13.5298824310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4409694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2779550552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.322413444519</t>
   </si>
   <si>
     <t xml:space="preserve">13.3816909790039</t>
@@ -1274,109 +1274,109 @@
     <t xml:space="preserve">13.6039781570435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.515064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3372325897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743389129639</t>
+    <t xml:space="preserve">13.5150651931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3372354507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743398666382</t>
   </si>
   <si>
     <t xml:space="preserve">13.9300012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8855438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8262662887573</t>
+    <t xml:space="preserve">13.8855409622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8262672424316</t>
   </si>
   <si>
     <t xml:space="preserve">13.7669897079468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6928930282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7521696090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8559017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9892778396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2038631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7818078994751</t>
+    <t xml:space="preserve">13.692892074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7521686553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8559045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9892768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2038612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7818088531494</t>
   </si>
   <si>
     <t xml:space="preserve">13.9003629684448</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7225322723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9596385955811</t>
+    <t xml:space="preserve">13.7225332260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9596376419067</t>
   </si>
   <si>
     <t xml:space="preserve">13.7077121734619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5447025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5595207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1149463653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4261465072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.655553817749</t>
+    <t xml:space="preserve">13.5447015762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5595226287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1149454116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4261484146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6555528640747</t>
   </si>
   <si>
     <t xml:space="preserve">12.8778409957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9222984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1001281738281</t>
+    <t xml:space="preserve">12.9222974777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1001262664795</t>
   </si>
   <si>
     <t xml:space="preserve">13.1297645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0112133026123</t>
+    <t xml:space="preserve">13.0112113952637</t>
   </si>
   <si>
     <t xml:space="preserve">12.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1517019271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0479669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3739891052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4777231216431</t>
+    <t xml:space="preserve">12.1517028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220636367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3739881515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4777250289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.1368837356567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.707127571106</t>
+    <t xml:space="preserve">11.7071266174316</t>
   </si>
   <si>
     <t xml:space="preserve">12.033148765564</t>
@@ -1385,34 +1385,34 @@
     <t xml:space="preserve">11.7812252044678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2477340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4700222015381</t>
+    <t xml:space="preserve">11.2477350234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4700212478638</t>
   </si>
   <si>
     <t xml:space="preserve">11.4403829574585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885734558105</t>
+    <t xml:space="preserve">11.5885744094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6478509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5589380264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3811082839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3514671325684</t>
+    <t xml:space="preserve">11.5589351654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3811063766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3514680862427</t>
   </si>
   <si>
     <t xml:space="preserve">11.173638343811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1143617630005</t>
+    <t xml:space="preserve">11.1143608093262</t>
   </si>
   <si>
     <t xml:space="preserve">11.0254459381104</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">10.6697874069214</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0029268264771</t>
+    <t xml:space="preserve">10.0029249191284</t>
   </si>
   <si>
     <t xml:space="preserve">10.4326801300049</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">10.7883405685425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4771385192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.551233291626</t>
+    <t xml:space="preserve">10.4771366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5512342453003</t>
   </si>
   <si>
     <t xml:space="preserve">10.8920745849609</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.9661712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0995416641235</t>
+    <t xml:space="preserve">11.0995426177979</t>
   </si>
   <si>
     <t xml:space="preserve">10.0770206451416</t>
@@ -1451,43 +1451,43 @@
     <t xml:space="preserve">10.375111579895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8706388473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8241834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4835071563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5609350204468</t>
+    <t xml:space="preserve">10.8706378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.824182510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4835090637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5609331130981</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6538457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3042259216309</t>
+    <t xml:space="preserve">10.6538467407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3042249679565</t>
   </si>
   <si>
     <t xml:space="preserve">10.7467575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6073894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5299644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7622413635254</t>
+    <t xml:space="preserve">10.6073884963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5299634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7622423171997</t>
   </si>
   <si>
     <t xml:space="preserve">10.7777271270752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7312707901001</t>
+    <t xml:space="preserve">10.7312717437744</t>
   </si>
   <si>
     <t xml:space="preserve">10.235743522644</t>
@@ -1496,22 +1496,22 @@
     <t xml:space="preserve">10.4525384902954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.406081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9945201873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0874319076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1493711471558</t>
+    <t xml:space="preserve">10.4060821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9945211410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0874328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1493721008301</t>
   </si>
   <si>
     <t xml:space="preserve">11.0719451904297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9480667114258</t>
+    <t xml:space="preserve">10.9480657577515</t>
   </si>
   <si>
     <t xml:space="preserve">11.040976524353</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">10.4370517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5919036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4989938735962</t>
+    <t xml:space="preserve">10.5919046401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4989929199219</t>
   </si>
   <si>
     <t xml:space="preserve">10.5144777297974</t>
@@ -1541,34 +1541,34 @@
     <t xml:space="preserve">10.6693296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.622875213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8551540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3816518783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3661661148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.242283821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3506803512573</t>
+    <t xml:space="preserve">10.6228742599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8551530838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1184024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3816509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3661670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2422847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648588180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3506813049316</t>
   </si>
   <si>
     <t xml:space="preserve">10.9790363311768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7932119369507</t>
+    <t xml:space="preserve">10.7932109832764</t>
   </si>
   <si>
     <t xml:space="preserve">10.8861246109009</t>
@@ -1577,46 +1577,46 @@
     <t xml:space="preserve">10.5764188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2047739028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1118612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0808925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6782751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56987762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75570297241211</t>
+    <t xml:space="preserve">10.2047748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1118621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0808916091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67827606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56987857818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75570106506348</t>
   </si>
   <si>
     <t xml:space="preserve">9.95700931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87958335876465</t>
+    <t xml:space="preserve">9.87958431243896</t>
   </si>
   <si>
     <t xml:space="preserve">9.86409759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94152355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92603969573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1583185195923</t>
+    <t xml:space="preserve">9.94152545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92603874206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.158317565918</t>
   </si>
   <si>
     <t xml:space="preserve">10.1428327560425</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91055393218994</t>
+    <t xml:space="preserve">9.91055297851562</t>
   </si>
   <si>
     <t xml:space="preserve">10.1273469924927</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">10.3441400527954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6383600234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7157869338989</t>
+    <t xml:space="preserve">10.6383609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7157878875732</t>
   </si>
   <si>
     <t xml:space="preserve">10.6848163604736</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">10.0344343185425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0189504623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97249507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2202596664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81734943389893</t>
+    <t xml:space="preserve">10.018949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97249412536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2202577590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81734848022461</t>
   </si>
   <si>
     <t xml:space="preserve">10.0666780471802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1445951461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3160076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4874229431152</t>
+    <t xml:space="preserve">10.1445932388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3160085678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4874210357666</t>
   </si>
   <si>
     <t xml:space="preserve">10.5030040740967</t>
@@ -1667,31 +1667,31 @@
     <t xml:space="preserve">10.3004245758057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91084766387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0043449401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87968158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89526271820068</t>
+    <t xml:space="preserve">9.91084671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0043468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87968254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.895263671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.98876285552979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0510950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0822620391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1134262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.362756729126</t>
+    <t xml:space="preserve">10.0510940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0822601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1134281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3627557754517</t>
   </si>
   <si>
     <t xml:space="preserve">10.3939237594604</t>
@@ -1718,40 +1718,40 @@
     <t xml:space="preserve">10.222508430481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1913433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2069253921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4562540054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3783388137817</t>
+    <t xml:space="preserve">10.1913423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2069263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4562559127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3783397674561</t>
   </si>
   <si>
     <t xml:space="preserve">10.643253326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.830249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7523345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0795793533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9549160003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6900024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7679176330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2198276519775</t>
+    <t xml:space="preserve">10.8302488327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7523336410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0795803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9549150466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6900014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7679166793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2198257446289</t>
   </si>
   <si>
     <t xml:space="preserve">11.2509927749634</t>
@@ -1763,22 +1763,22 @@
     <t xml:space="preserve">11.1574954986572</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2536745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2848415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2380933761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1601762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4095039367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0355129241943</t>
+    <t xml:space="preserve">10.2536754608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.284839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2380924224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.160177230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4095058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.03551197052</t>
   </si>
   <si>
     <t xml:space="preserve">10.1757593154907</t>
@@ -1787,16 +1787,16 @@
     <t xml:space="preserve">10.8146657943726</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1263294219971</t>
+    <t xml:space="preserve">11.1263265609741</t>
   </si>
   <si>
     <t xml:space="preserve">11.0484132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1419115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0328302383423</t>
+    <t xml:space="preserve">11.1419105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0328311920166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367506027222</t>
@@ -1805,76 +1805,76 @@
     <t xml:space="preserve">10.5965032577515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6120862960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7211685180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.908164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237489700317</t>
+    <t xml:space="preserve">10.6120853424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7211694717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9081649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237480163574</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835006713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.970498085022</t>
+    <t xml:space="preserve">10.8769998550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9704971313477</t>
   </si>
   <si>
     <t xml:space="preserve">11.5470714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9054841995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.656153678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8275680541992</t>
+    <t xml:space="preserve">11.8587331771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.905481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6561527252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275690078735</t>
   </si>
   <si>
     <t xml:space="preserve">11.7340688705444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9989805221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8743162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9210653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768976211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.843150138855</t>
+    <t xml:space="preserve">11.9989814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8743171691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9210662841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8431510925293</t>
   </si>
   <si>
     <t xml:space="preserve">11.7652359008789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8899011611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8119850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1107444763184</t>
+    <t xml:space="preserve">11.8899002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8119840621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1107454299927</t>
   </si>
   <si>
     <t xml:space="preserve">10.9860811233521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3444929122925</t>
+    <t xml:space="preserve">11.3444919586182</t>
   </si>
   <si>
     <t xml:space="preserve">11.7808179855347</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">12.0301475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9366483688354</t>
+    <t xml:space="preserve">11.9366502761841</t>
   </si>
   <si>
     <t xml:space="preserve">11.7964019775391</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">11.4691562652588</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5626564025879</t>
+    <t xml:space="preserve">11.5626573562622</t>
   </si>
   <si>
     <t xml:space="preserve">11.4379901885986</t>
@@ -1907,34 +1907,34 @@
     <t xml:space="preserve">11.3756580352783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.453574180603</t>
+    <t xml:space="preserve">11.4535732269287</t>
   </si>
   <si>
     <t xml:space="preserve">11.4224071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2977418899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2821588516235</t>
+    <t xml:space="preserve">11.1886615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2977437973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2821598052979</t>
   </si>
   <si>
     <t xml:space="preserve">10.705584526062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8925819396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6588344573975</t>
+    <t xml:space="preserve">10.8925809860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6588354110718</t>
   </si>
   <si>
     <t xml:space="preserve">10.3315916061401</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3471736907959</t>
+    <t xml:space="preserve">10.3471727371216</t>
   </si>
   <si>
     <t xml:space="preserve">10.0199279785156</t>
@@ -1949,67 +1949,67 @@
     <t xml:space="preserve">9.94201374053955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80176448822021</t>
+    <t xml:space="preserve">9.80176544189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.92642879486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97586154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86677932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13169384002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02261161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80444812774658</t>
+    <t xml:space="preserve">8.97586250305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86678028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13169193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02261066436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80444717407227</t>
   </si>
   <si>
     <t xml:space="preserve">8.47720336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38370418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2590389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24345588684082</t>
+    <t xml:space="preserve">8.38370513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25903987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2434549331665</t>
   </si>
   <si>
     <t xml:space="preserve">8.14995765686035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48767566680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11368131637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03576612472534</t>
+    <t xml:space="preserve">7.48767614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11368227005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0357666015625</t>
   </si>
   <si>
     <t xml:space="preserve">6.15532207489014</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42023372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16311264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85924243927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25929403305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29045963287354</t>
+    <t xml:space="preserve">6.42023420333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16311359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85924339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2592945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29046010971069</t>
   </si>
   <si>
     <t xml:space="preserve">5.53199768066406</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">5.49304056167603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37616729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08008813858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32941722869873</t>
+    <t xml:space="preserve">5.37616682052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08008861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36058473587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32941770553589</t>
   </si>
   <si>
     <t xml:space="preserve">5.35279226303101</t>
@@ -2039,28 +2039,28 @@
     <t xml:space="preserve">5.29825162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45408201217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47745800018311</t>
+    <t xml:space="preserve">5.45408248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47745752334595</t>
   </si>
   <si>
     <t xml:space="preserve">5.76574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5086236000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92157506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87482595443726</t>
+    <t xml:space="preserve">5.50862312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92157554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8748254776001</t>
   </si>
   <si>
     <t xml:space="preserve">5.8047022819519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8358678817749</t>
+    <t xml:space="preserve">5.83586835861206</t>
   </si>
   <si>
     <t xml:space="preserve">5.89820098876953</t>
@@ -2075,25 +2075,25 @@
     <t xml:space="preserve">6.33452749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4280252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17090511322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45919179916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23323726654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24882030487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12415552139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75016164779663</t>
+    <t xml:space="preserve">6.42802619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17090463638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45919227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23323774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24881982803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12415599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75016117095947</t>
   </si>
   <si>
     <t xml:space="preserve">5.71899509429932</t>
@@ -2102,70 +2102,70 @@
     <t xml:space="preserve">5.86703443527222</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94495058059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.929368019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03844881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22544479370117</t>
+    <t xml:space="preserve">5.94495010375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92936658859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03844833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22544574737549</t>
   </si>
   <si>
     <t xml:space="preserve">6.35790205001831</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58385610580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50594139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49035882949829</t>
+    <t xml:space="preserve">6.5838565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50594234466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49035835266113</t>
   </si>
   <si>
     <t xml:space="preserve">6.47477531433105</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6228141784668</t>
+    <t xml:space="preserve">6.62281560897827</t>
   </si>
   <si>
     <t xml:space="preserve">7.08251571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27730417251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09030771255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05914258956909</t>
+    <t xml:space="preserve">7.27730464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09030723571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05914211273193</t>
   </si>
   <si>
     <t xml:space="preserve">6.89551877975464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52152442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60723161697388</t>
+    <t xml:space="preserve">6.52152347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60723114013672</t>
   </si>
   <si>
     <t xml:space="preserve">6.76306200027466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55269050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56827354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68514728546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75527095794678</t>
+    <t xml:space="preserve">6.5526909828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56827402114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68514633178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75527048110962</t>
   </si>
   <si>
     <t xml:space="preserve">6.84097719192505</t>
@@ -2174,58 +2174,58 @@
     <t xml:space="preserve">6.65398073196411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01239156723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98122596740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8565616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78643655776978</t>
+    <t xml:space="preserve">7.01239109039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98122549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85656118392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78643751144409</t>
   </si>
   <si>
     <t xml:space="preserve">6.71631240844727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73189687728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8643536567688</t>
+    <t xml:space="preserve">6.73189640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86435222625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.66177225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72410440444946</t>
+    <t xml:space="preserve">6.72410488128662</t>
   </si>
   <si>
     <t xml:space="preserve">6.38906812667847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24102878570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20207071304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45140075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43581819534302</t>
+    <t xml:space="preserve">6.24102926254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20207166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45140027999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43581771850586</t>
   </si>
   <si>
     <t xml:space="preserve">6.49814987182617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28777742385864</t>
+    <t xml:space="preserve">6.2877779006958</t>
   </si>
   <si>
     <t xml:space="preserve">6.31115293502808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32673597335815</t>
+    <t xml:space="preserve">6.32673501968384</t>
   </si>
   <si>
     <t xml:space="preserve">6.13194704055786</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">6.07740640640259</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00728273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95274209976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93715810775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72678709030151</t>
+    <t xml:space="preserve">6.00728225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95274066925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93715858459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72678661346436</t>
   </si>
   <si>
     <t xml:space="preserve">5.8436598777771</t>
@@ -2258,25 +2258,25 @@
     <t xml:space="preserve">5.69562005996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53978967666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64107942581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56316471099854</t>
+    <t xml:space="preserve">5.53979015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64107990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56316328048706</t>
   </si>
   <si>
     <t xml:space="preserve">5.5475811958313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48524904251099</t>
+    <t xml:space="preserve">5.48524856567383</t>
   </si>
   <si>
     <t xml:space="preserve">5.52420663833618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74236917495728</t>
+    <t xml:space="preserve">5.74237012863159</t>
   </si>
   <si>
     <t xml:space="preserve">5.75795269012451</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">5.79691028594971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90599250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96053266525269</t>
+    <t xml:space="preserve">5.90599203109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96053314208984</t>
   </si>
   <si>
     <t xml:space="preserve">5.68003749847412</t>
@@ -2300,25 +2300,25 @@
     <t xml:space="preserve">5.85145139694214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78132820129395</t>
+    <t xml:space="preserve">5.7813286781311</t>
   </si>
   <si>
     <t xml:space="preserve">6.04624032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91378402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67224645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51641511917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46187448501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15800380706787</t>
+    <t xml:space="preserve">5.91378450393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67224597930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5164155960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46187400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15800428390503</t>
   </si>
   <si>
     <t xml:space="preserve">4.99438142776489</t>
@@ -2330,40 +2330,40 @@
     <t xml:space="preserve">4.7606348991394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8073844909668</t>
+    <t xml:space="preserve">4.80738401412964</t>
   </si>
   <si>
     <t xml:space="preserve">4.83075857162476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02554750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18137836456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06182289123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02286529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10078144073486</t>
+    <t xml:space="preserve">5.02554702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18137788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06182336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02286577224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10078096389771</t>
   </si>
   <si>
     <t xml:space="preserve">6.99680805206299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23055458068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05135059356689</t>
+    <t xml:space="preserve">7.23055505752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05134963989258</t>
   </si>
   <si>
     <t xml:space="preserve">6.93447637557983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92668437957764</t>
+    <t xml:space="preserve">6.92668533325195</t>
   </si>
   <si>
     <t xml:space="preserve">6.82539463043213</t>
@@ -2372,25 +2372,25 @@
     <t xml:space="preserve">6.77864599227905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87214326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9111008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77085399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66956329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63060617446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97343444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63839769363403</t>
+    <t xml:space="preserve">6.87214374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91110229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7708535194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66956472396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63060569763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97343349456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63839673995972</t>
   </si>
   <si>
     <t xml:space="preserve">6.7007303237915</t>
@@ -2399,94 +2399,94 @@
     <t xml:space="preserve">6.80981159210205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98901700973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14484930038452</t>
+    <t xml:space="preserve">6.98901796340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14484882354736</t>
   </si>
   <si>
     <t xml:space="preserve">6.95785045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87993478775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00460004806519</t>
+    <t xml:space="preserve">6.8799352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00459957122803</t>
   </si>
   <si>
     <t xml:space="preserve">7.16043138504028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17601442337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37859582901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38638591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13705682754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09809970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53710842132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59164810180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57606554031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79422855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07472372055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2227635383606</t>
+    <t xml:space="preserve">7.1760139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37859535217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38638544082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13705635070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09809923171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53710699081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5916485786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5760645866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79422760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07472467422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22276401519775</t>
   </si>
   <si>
     <t xml:space="preserve">7.28509569168091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25393009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45650911331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65909004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61234092712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53442525863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49546766281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57338285446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47209310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50325965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40196895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26172208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3006796836853</t>
+    <t xml:space="preserve">7.25392961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45650959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65909051895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61234140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53442573547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4954662322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57338333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47209405899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50325918197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40196847915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26172161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30068016052246</t>
   </si>
   <si>
     <t xml:space="preserve">7.12926387786865</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">7.24613809585571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51884078979492</t>
+    <t xml:space="preserve">7.51884126663208</t>
   </si>
   <si>
     <t xml:space="preserve">7.91621160507202</t>
@@ -2504,88 +2504,88 @@
     <t xml:space="preserve">7.79154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80712985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71363115310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.775963306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54221820831299</t>
+    <t xml:space="preserve">7.80713081359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71363067626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77596235275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54221868515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.23834609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37080240249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43313598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02529144287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90062713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946153640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72142171859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46430158615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73700428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7837553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65129804611206</t>
+    <t xml:space="preserve">7.3708028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43313646316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02529335021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90062761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72142219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46430253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73700571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78375434875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65129852294922</t>
   </si>
   <si>
     <t xml:space="preserve">7.58896684646606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68246412277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72921419143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62013149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39417743682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40976047515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59675884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.744797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21228885650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29020690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1032075881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08762359619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18221664428711</t>
+    <t xml:space="preserve">7.68246459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72921371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62013244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39417695999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40976095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59675788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74479818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21228981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29020500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10320854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08762454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221759796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.02456378936768</t>
@@ -2594,52 +2594,52 @@
     <t xml:space="preserve">7.96150255203247</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15068626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54482078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68670749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95471954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00201606750488</t>
+    <t xml:space="preserve">8.1506872177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54481887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6867094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95471858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00201511383057</t>
   </si>
   <si>
     <t xml:space="preserve">9.06507587432861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12813854217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20696449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15966892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14390277862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9389533996582</t>
+    <t xml:space="preserve">9.12813758850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20696640014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1439037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93895530700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.97048377990723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98625087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82859706878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78130054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63941097259521</t>
+    <t xml:space="preserve">8.98624897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82859802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78129959106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63941287994385</t>
   </si>
   <si>
     <t xml:space="preserve">8.51328945159912</t>
@@ -2651,37 +2651,37 @@
     <t xml:space="preserve">8.73400402069092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45022869110107</t>
+    <t xml:space="preserve">8.45022964477539</t>
   </si>
   <si>
     <t xml:space="preserve">8.3714017868042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4659948348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57635116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52905368804932</t>
+    <t xml:space="preserve">8.46599197387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57635307312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52905464172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.35563564300537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07185840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21374893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22951126098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2768087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24527835845947</t>
+    <t xml:space="preserve">8.07185935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21374702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22951316833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27680969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24527931213379</t>
   </si>
   <si>
     <t xml:space="preserve">8.08762550354004</t>
@@ -2693,46 +2693,46 @@
     <t xml:space="preserve">7.89844131469727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94573593139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99303245544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40293216705322</t>
+    <t xml:space="preserve">7.94573640823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99303388595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40293312072754</t>
   </si>
   <si>
     <t xml:space="preserve">8.4817590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32410526275635</t>
+    <t xml:space="preserve">8.32410621643066</t>
   </si>
   <si>
     <t xml:space="preserve">8.43446254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70247459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71823978424072</t>
+    <t xml:space="preserve">8.70247364044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71823883056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.79706573486328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38716697692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257488250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2610445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19798183441162</t>
+    <t xml:space="preserve">8.33986949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38716793060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257392883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26104259490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19798278808594</t>
   </si>
   <si>
     <t xml:space="preserve">8.592116355896</t>
@@ -2747,52 +2747,52 @@
     <t xml:space="preserve">7.92997217178345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84326219558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91420698165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80384922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64619588851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66196012496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85902786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61466407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60678052902222</t>
+    <t xml:space="preserve">7.84326267242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91420602798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80384826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64619445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6619610786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85902690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61466455459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60678148269653</t>
   </si>
   <si>
     <t xml:space="preserve">7.70137453079224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78808307647705</t>
+    <t xml:space="preserve">7.78808355331421</t>
   </si>
   <si>
     <t xml:space="preserve">7.65407752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56736898422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62254667282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67772626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50430727005005</t>
+    <t xml:space="preserve">7.79596710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56736850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62254810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67772674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50430774688721</t>
   </si>
   <si>
     <t xml:space="preserve">7.63831281661987</t>
@@ -2801,55 +2801,55 @@
     <t xml:space="preserve">7.74867010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76443576812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82749557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67094421386719</t>
+    <t xml:space="preserve">7.7644362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8274974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67094326019287</t>
   </si>
   <si>
     <t xml:space="preserve">8.62364673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74977111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.559485912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54371976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2520604133606</t>
+    <t xml:space="preserve">8.74977016448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55948638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54372024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25206136703491</t>
   </si>
   <si>
     <t xml:space="preserve">7.28359174728394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27570915222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85792827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9131064414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08652544021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99981594085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93675518035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37030124664307</t>
+    <t xml:space="preserve">7.275710105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85792779922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91310691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82639741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08652448654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99981546401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93675470352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37030220031738</t>
   </si>
   <si>
     <t xml:space="preserve">7.23629665374756</t>
@@ -2861,40 +2861,40 @@
     <t xml:space="preserve">7.12593793869019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03134632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14958667755127</t>
+    <t xml:space="preserve">7.03134679794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14958620071411</t>
   </si>
   <si>
     <t xml:space="preserve">7.09440803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13382244110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3387713432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38606786727905</t>
+    <t xml:space="preserve">7.13382053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33877086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38606739044189</t>
   </si>
   <si>
     <t xml:space="preserve">7.47277641296387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86690950393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78020000457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74078750610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46489429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52795553207397</t>
+    <t xml:space="preserve">7.86691093444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78019952774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74078798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46489381790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52795457839966</t>
   </si>
   <si>
     <t xml:space="preserve">7.68560886383057</t>
@@ -2903,148 +2903,148 @@
     <t xml:space="preserve">7.58313417434692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48854160308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45701026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37818336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35453701019287</t>
+    <t xml:space="preserve">7.48854112625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4570107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37818384170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35453653335571</t>
   </si>
   <si>
     <t xml:space="preserve">7.11805582046509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99193239212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34665393829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1732349395752</t>
+    <t xml:space="preserve">6.99193286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3466534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17323446273804</t>
   </si>
   <si>
     <t xml:space="preserve">7.29147529602051</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36241865158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1968822479248</t>
+    <t xml:space="preserve">7.36241817474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19688320159912</t>
   </si>
   <si>
     <t xml:space="preserve">7.10229158401489</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44124460220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33088779449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40971374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49642467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39394998550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26782703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15746879577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61356592178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44014596939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60568237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81063222885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98405027389526</t>
+    <t xml:space="preserve">7.44124555587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33088874816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4097146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49642419815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39395046234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26782751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15746974945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61356496810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44014644622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60568189620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81063175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98405122756958</t>
   </si>
   <si>
     <t xml:space="preserve">7.18111801147461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18900060653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0628776550293</t>
+    <t xml:space="preserve">7.18900012969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06287813186646</t>
   </si>
   <si>
     <t xml:space="preserve">7.11017370223999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20476484298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88267612457275</t>
+    <t xml:space="preserve">7.20476531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88267517089844</t>
   </si>
   <si>
     <t xml:space="preserve">7.81173038482666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69349193572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75655364990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7329044342041</t>
+    <t xml:space="preserve">7.69349145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75655221939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73290491104126</t>
   </si>
   <si>
     <t xml:space="preserve">7.42548036575317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48065900802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5121898651123</t>
+    <t xml:space="preserve">7.48065996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51218938827515</t>
   </si>
   <si>
     <t xml:space="preserve">7.52007341384888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22841453552246</t>
+    <t xml:space="preserve">7.22841358184814</t>
   </si>
   <si>
     <t xml:space="preserve">7.40183210372925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00769758224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4491286277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41542625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31838750839233</t>
+    <t xml:space="preserve">7.00769805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44912815093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4154257774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31838655471802</t>
   </si>
   <si>
     <t xml:space="preserve">7.29412651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48011875152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098508834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63376331329346</t>
+    <t xml:space="preserve">7.48011827468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63376426696777</t>
   </si>
   <si>
     <t xml:space="preserve">7.54481172561646</t>
@@ -3053,46 +3053,46 @@
     <t xml:space="preserve">7.43968486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.488205909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46394491195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32647371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05152797698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83318853378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94640254974365</t>
+    <t xml:space="preserve">7.48820447921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46394538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32647275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05152702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83318948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94640207290649</t>
   </si>
   <si>
     <t xml:space="preserve">6.76040983200073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75232315063477</t>
+    <t xml:space="preserve">6.75232362747192</t>
   </si>
   <si>
     <t xml:space="preserve">6.71189022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86553621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73615026473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7442364692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8170166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87362194061279</t>
+    <t xml:space="preserve">6.86553525924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73614978790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74423694610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81701564788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87362289428711</t>
   </si>
   <si>
     <t xml:space="preserve">6.80084323883057</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">6.63102340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70380306243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46929168701172</t>
+    <t xml:space="preserve">6.70380401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46929121017456</t>
   </si>
   <si>
     <t xml:space="preserve">6.48546504974365</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">6.57441759109497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69571733474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64719772338867</t>
+    <t xml:space="preserve">6.695716381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64719724655151</t>
   </si>
   <si>
     <t xml:space="preserve">6.63911056518555</t>
@@ -3128,31 +3128,31 @@
     <t xml:space="preserve">6.55015754699707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60676431655884</t>
+    <t xml:space="preserve">6.606764793396</t>
   </si>
   <si>
     <t xml:space="preserve">6.62293672561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47737836837769</t>
+    <t xml:space="preserve">6.477379322052</t>
   </si>
   <si>
     <t xml:space="preserve">6.40459871292114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41268539428711</t>
+    <t xml:space="preserve">6.41268587112427</t>
   </si>
   <si>
     <t xml:space="preserve">6.65528345108032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84127569198608</t>
+    <t xml:space="preserve">6.8412766456604</t>
   </si>
   <si>
     <t xml:space="preserve">6.72806310653687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67145729064941</t>
+    <t xml:space="preserve">6.67145681381226</t>
   </si>
   <si>
     <t xml:space="preserve">6.7684965133667</t>
@@ -3167,40 +3167,40 @@
     <t xml:space="preserve">6.49355125427246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44503116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38842582702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29138565063477</t>
+    <t xml:space="preserve">6.44503164291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38842535018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29138660430908</t>
   </si>
   <si>
     <t xml:space="preserve">6.11348056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19434690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08922052383423</t>
+    <t xml:space="preserve">6.19434595108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08922100067139</t>
   </si>
   <si>
     <t xml:space="preserve">6.13774061203003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95174837112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95983457565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90322923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06496095657349</t>
+    <t xml:space="preserve">5.95174789428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95983505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98409509658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90322875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06496047973633</t>
   </si>
   <si>
     <t xml:space="preserve">6.18626022338867</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">5.91131496429443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86279582977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88705587387085</t>
+    <t xml:space="preserve">5.86279535293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88705539703369</t>
   </si>
   <si>
     <t xml:space="preserve">5.79001617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83044862747192</t>
+    <t xml:space="preserve">5.83044910430908</t>
   </si>
   <si>
     <t xml:space="preserve">5.81427621841431</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">5.63637018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70915031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74958372116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73341035842896</t>
+    <t xml:space="preserve">5.7091498374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74958324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73340940475464</t>
   </si>
   <si>
     <t xml:space="preserve">5.67680311203003</t>
@@ -3245,100 +3245,100 @@
     <t xml:space="preserve">5.78192949295044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74149608612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62828350067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45846462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39377164840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33716583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38568496704102</t>
+    <t xml:space="preserve">5.74149656295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62828397750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45846557617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3937726020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33716535568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38568544387817</t>
   </si>
   <si>
     <t xml:space="preserve">5.36142539978027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42611789703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43420457839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28055953979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26438617706299</t>
+    <t xml:space="preserve">5.42611837387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43420505523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28055906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26438665390015</t>
   </si>
   <si>
     <t xml:space="preserve">5.34525203704834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40994548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35333871841431</t>
+    <t xml:space="preserve">5.40994501113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35333919525146</t>
   </si>
   <si>
     <t xml:space="preserve">5.57976388931274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82236289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68489074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79810333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55550336837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93557453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7576699256897</t>
+    <t xml:space="preserve">5.82236242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68489027023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79810237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55550384521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93557548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75766944885254</t>
   </si>
   <si>
     <t xml:space="preserve">5.66063022613525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61211013793945</t>
+    <t xml:space="preserve">5.61211061477661</t>
   </si>
   <si>
     <t xml:space="preserve">5.65254354476929</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48272466659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51507139205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53124380111694</t>
+    <t xml:space="preserve">5.4827241897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51507091522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5312442779541</t>
   </si>
   <si>
     <t xml:space="preserve">5.5069842338562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64445734024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52315711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70106315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57167673110962</t>
+    <t xml:space="preserve">5.64445638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52315759658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70106363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57167720794678</t>
   </si>
   <si>
     <t xml:space="preserve">5.46655130386353</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">5.60402345657349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49081087112427</t>
+    <t xml:space="preserve">5.49081134796143</t>
   </si>
   <si>
     <t xml:space="preserve">5.56359100341797</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">5.41803169250488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44229173660278</t>
+    <t xml:space="preserve">5.44229125976562</t>
   </si>
   <si>
     <t xml:space="preserve">5.53933095932007</t>
@@ -3365,67 +3365,67 @@
     <t xml:space="preserve">5.76575613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66871786117554</t>
+    <t xml:space="preserve">5.66871690750122</t>
   </si>
   <si>
     <t xml:space="preserve">5.9679217338562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14582681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17817354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03261470794678</t>
+    <t xml:space="preserve">6.145827293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17817401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03261423110962</t>
   </si>
   <si>
     <t xml:space="preserve">5.97600793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01644086837769</t>
+    <t xml:space="preserve">6.01644134521484</t>
   </si>
   <si>
     <t xml:space="preserve">5.9436616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80618858337402</t>
+    <t xml:space="preserve">5.80618906021118</t>
   </si>
   <si>
     <t xml:space="preserve">5.87896919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85470867156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1215672492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0973072052002</t>
+    <t xml:space="preserve">5.85470914840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12156772613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09730768203735</t>
   </si>
   <si>
     <t xml:space="preserve">6.16200017929077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07304763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08113384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05687427520752</t>
+    <t xml:space="preserve">6.07304716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08113431930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05687475204468</t>
   </si>
   <si>
     <t xml:space="preserve">6.04070043563843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10539436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04878759384155</t>
+    <t xml:space="preserve">6.105393409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04878807067871</t>
   </si>
   <si>
     <t xml:space="preserve">5.72532320022583</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">5.59593677520752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58785009384155</t>
+    <t xml:space="preserve">5.58785057067871</t>
   </si>
   <si>
     <t xml:space="preserve">6.30755949020386</t>
@@ -3443,25 +3443,25 @@
     <t xml:space="preserve">5.84662246704102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83853578567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00835466384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12965393066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16357755661011</t>
+    <t xml:space="preserve">5.83853483200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00835418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1296534538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16357803344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.2046685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01565217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29506778717041</t>
+    <t xml:space="preserve">6.01565265655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29506731033325</t>
   </si>
   <si>
     <t xml:space="preserve">6.49230194091797</t>
@@ -3470,25 +3470,25 @@
     <t xml:space="preserve">6.47586584091187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46764802932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50051975250244</t>
+    <t xml:space="preserve">6.46764755249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5005202293396</t>
   </si>
   <si>
     <t xml:space="preserve">6.59913730621338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58270168304443</t>
+    <t xml:space="preserve">6.58270215988159</t>
   </si>
   <si>
     <t xml:space="preserve">6.5169563293457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45121145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42655754089355</t>
+    <t xml:space="preserve">6.45121192932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4265570640564</t>
   </si>
   <si>
     <t xml:space="preserve">6.41012144088745</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">6.33615827560425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52517414093018</t>
+    <t xml:space="preserve">6.52517461776733</t>
   </si>
   <si>
     <t xml:space="preserve">6.57448291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4594292640686</t>
+    <t xml:space="preserve">6.45943021774292</t>
   </si>
   <si>
     <t xml:space="preserve">6.54982852935791</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">6.50873851776123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44299364089966</t>
+    <t xml:space="preserve">6.4429931640625</t>
   </si>
   <si>
     <t xml:space="preserve">6.41833925247192</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">6.36081218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34437608718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11426877975464</t>
+    <t xml:space="preserve">6.34437656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1142692565918</t>
   </si>
   <si>
     <t xml:space="preserve">6.1307053565979</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">6.13892316818237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25397777557373</t>
+    <t xml:space="preserve">6.25397682189941</t>
   </si>
   <si>
     <t xml:space="preserve">6.26219511032104</t>
@@ -3548,91 +3548,91 @@
     <t xml:space="preserve">6.31972217559814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35259437561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30328607559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21288681030273</t>
+    <t xml:space="preserve">6.35259342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30328559875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21288633346558</t>
   </si>
   <si>
     <t xml:space="preserve">6.37724876403809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4840841293335</t>
+    <t xml:space="preserve">6.48408365249634</t>
   </si>
   <si>
     <t xml:space="preserve">6.56626462936401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64022779464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65666437149048</t>
+    <t xml:space="preserve">6.64022827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65666389465332</t>
   </si>
   <si>
     <t xml:space="preserve">6.59091949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55804681777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80459022521973</t>
+    <t xml:space="preserve">6.5580472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80458974838257</t>
   </si>
   <si>
     <t xml:space="preserve">6.8867712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83746194839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69775485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61557388305664</t>
+    <t xml:space="preserve">6.83746242523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69775438308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61557340621948</t>
   </si>
   <si>
     <t xml:space="preserve">6.70597267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63200902938843</t>
+    <t xml:space="preserve">6.63200998306274</t>
   </si>
   <si>
     <t xml:space="preserve">6.62379217147827</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82924509048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94429731369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87855291366577</t>
+    <t xml:space="preserve">6.82924461364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94429779052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87855243682861</t>
   </si>
   <si>
     <t xml:space="preserve">6.77993535995483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79637289047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90320634841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84568071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85389852523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72240972518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68131923675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68953657150269</t>
+    <t xml:space="preserve">6.7963719367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90320682525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84568023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8538990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68131875991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68953704833984</t>
   </si>
   <si>
     <t xml:space="preserve">6.27863121032715</t>
@@ -3641,34 +3641,34 @@
     <t xml:space="preserve">6.08961486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0731782913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04852390289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15535974502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99921607971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94168901443481</t>
+    <t xml:space="preserve">6.07317876815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04852437973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15536022186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99921560287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94168949127197</t>
   </si>
   <si>
     <t xml:space="preserve">6.05674266815186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8759446144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95812559127808</t>
+    <t xml:space="preserve">5.87594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95812511444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.08139705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03208780288696</t>
+    <t xml:space="preserve">6.03208875656128</t>
   </si>
   <si>
     <t xml:space="preserve">5.8923807144165</t>
@@ -3677,64 +3677,64 @@
     <t xml:space="preserve">5.85129022598267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90881729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78554534912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75267267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64583683013916</t>
+    <t xml:space="preserve">5.90881633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78554487228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75267314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64583730697632</t>
   </si>
   <si>
     <t xml:space="preserve">5.71158218383789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71979999542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82663631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86772632598877</t>
+    <t xml:space="preserve">5.71980047225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82663583755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86772584915161</t>
   </si>
   <si>
     <t xml:space="preserve">6.188232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12248754501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.147141456604</t>
+    <t xml:space="preserve">6.12248706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14714193344116</t>
   </si>
   <si>
     <t xml:space="preserve">6.28684949874878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40190315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76349973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66488218307495</t>
+    <t xml:space="preserve">6.40190267562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76349925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66488170623779</t>
   </si>
   <si>
     <t xml:space="preserve">6.738844871521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82102584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93607950210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99360609054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06756973266602</t>
+    <t xml:space="preserve">6.82102632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93607997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99360704421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06757020950317</t>
   </si>
   <si>
     <t xml:space="preserve">7.24015045166016</t>
@@ -3743,25 +3743,25 @@
     <t xml:space="preserve">7.13331413269043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98538780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12509632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07578659057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16618633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14975070953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19084167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18262338638306</t>
+    <t xml:space="preserve">6.98538875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1250958442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07578802108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16618585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14975023269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19084119796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1826229095459</t>
   </si>
   <si>
     <t xml:space="preserve">7.28123998641968</t>
@@ -3776,28 +3776,28 @@
     <t xml:space="preserve">7.09222316741943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.199059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05113315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03469657897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34698390960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48669338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36342144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35520315170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28945732116699</t>
+    <t xml:space="preserve">7.19905948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0511326789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03469753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34698343276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48669290542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36342191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35520267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28945827484131</t>
   </si>
   <si>
     <t xml:space="preserve">7.37163972854614</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">7.57709217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73323535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94690561294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88937997817993</t>
+    <t xml:space="preserve">7.73323488235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94690704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88938045501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.02086925506592</t>
@@ -3827,34 +3827,34 @@
     <t xml:space="preserve">7.63642740249634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52284097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4354681968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28693342208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37430715560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27819633483887</t>
+    <t xml:space="preserve">7.5228419303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43546915054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28693437576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37430667877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27819681167603</t>
   </si>
   <si>
     <t xml:space="preserve">7.25198459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29567098617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42673063278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30440807342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40925645828247</t>
+    <t xml:space="preserve">7.29567193984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4267315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30440855026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40925598144531</t>
   </si>
   <si>
     <t xml:space="preserve">7.33062124252319</t>
@@ -3863,25 +3863,25 @@
     <t xml:space="preserve">7.44420576095581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45294332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49663019180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54031610488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64516496658325</t>
+    <t xml:space="preserve">7.45294237136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49662923812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54031658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64516448974609</t>
   </si>
   <si>
     <t xml:space="preserve">7.51410531997681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41799402236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46168088912964</t>
+    <t xml:space="preserve">7.41799354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46168041229248</t>
   </si>
   <si>
     <t xml:space="preserve">7.531578540802</t>
@@ -3893,22 +3893,22 @@
     <t xml:space="preserve">7.48789167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39178133010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47041749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34809494018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94617795944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90249156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80638074874878</t>
+    <t xml:space="preserve">7.39178228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47041797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34809541702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94617748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90249109268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80638027191162</t>
   </si>
   <si>
     <t xml:space="preserve">6.86754179000854</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">6.91996622085571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95491552352905</t>
+    <t xml:space="preserve">6.95491600036621</t>
   </si>
   <si>
     <t xml:space="preserve">6.78890609741211</t>
@@ -3926,37 +3926,37 @@
     <t xml:space="preserve">6.70153284072876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89375400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85006761550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05102491378784</t>
+    <t xml:space="preserve">6.89375352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85006713867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05102586746216</t>
   </si>
   <si>
     <t xml:space="preserve">7.16461086273193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18208646774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33935689926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17334890365601</t>
+    <t xml:space="preserve">7.18208599090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33935785293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17334842681885</t>
   </si>
   <si>
     <t xml:space="preserve">7.20829772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32188320159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263914108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68885183334351</t>
+    <t xml:space="preserve">7.32188272476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68885135650635</t>
   </si>
   <si>
     <t xml:space="preserve">7.68011379241943</t>
@@ -3968,49 +3968,49 @@
     <t xml:space="preserve">7.83738613128662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69758892059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67137575149536</t>
+    <t xml:space="preserve">7.69758939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67137622833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.81117296218872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76748657226562</t>
+    <t xml:space="preserve">7.76748704910278</t>
   </si>
   <si>
     <t xml:space="preserve">7.7063250541687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92475938796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89854669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80114364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57091617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87198257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93396615982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96938610076904</t>
+    <t xml:space="preserve">7.92475891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89854621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80114412307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5709171295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87198162078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93396663665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96938562393188</t>
   </si>
   <si>
     <t xml:space="preserve">8.12877464294434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09335422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13762855529785</t>
+    <t xml:space="preserve">8.09335327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13762760162354</t>
   </si>
   <si>
     <t xml:space="preserve">8.25274181365967</t>
@@ -4028,19 +4028,19 @@
     <t xml:space="preserve">7.98709583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86312770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97824001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65946483612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6151909828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7125940322876</t>
+    <t xml:space="preserve">7.8631272315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97824144363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65946531295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61519145965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71259498596191</t>
   </si>
   <si>
     <t xml:space="preserve">7.70373916625977</t>
@@ -4049,49 +4049,49 @@
     <t xml:space="preserve">7.51778745651245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7922887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64175605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7214503288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60633563995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48236703872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52664184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59748125076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50007772445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58862638473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43809223175049</t>
+    <t xml:space="preserve">7.79228830337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64175510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72144889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60633611679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48236799240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52664232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59748077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49122285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58862543106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4380931854248</t>
   </si>
   <si>
     <t xml:space="preserve">7.47351264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69488430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67717552185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75686883926392</t>
+    <t xml:space="preserve">7.69488477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67717456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75686931610107</t>
   </si>
   <si>
     <t xml:space="preserve">7.84541749954224</t>
@@ -4103,13 +4103,16 @@
     <t xml:space="preserve">7.88083648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99595022201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85427188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53549671173096</t>
+    <t xml:space="preserve">7.99594974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85427236557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89854717254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53549766540527</t>
   </si>
   <si>
     <t xml:space="preserve">7.33183479309082</t>
@@ -4118,22 +4121,22 @@
     <t xml:space="preserve">7.6683201789856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76572465896606</t>
+    <t xml:space="preserve">7.76572418212891</t>
   </si>
   <si>
     <t xml:space="preserve">7.90740156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83656358718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07564353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02251529693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17304706573486</t>
+    <t xml:space="preserve">7.83656311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07564449310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02251625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17304801940918</t>
   </si>
   <si>
     <t xml:space="preserve">8.235032081604</t>
@@ -4145,13 +4148,13 @@
     <t xml:space="preserve">7.92511129379272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81885290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94282102584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20846843719482</t>
+    <t xml:space="preserve">7.81885242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94282150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20846748352051</t>
   </si>
   <si>
     <t xml:space="preserve">8.11991882324219</t>
@@ -4163,16 +4166,16 @@
     <t xml:space="preserve">8.19961261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.288161277771</t>
+    <t xml:space="preserve">8.28816032409668</t>
   </si>
   <si>
     <t xml:space="preserve">8.31472587585449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22617721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19075679779053</t>
+    <t xml:space="preserve">8.22617626190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19075775146484</t>
   </si>
   <si>
     <t xml:space="preserve">8.56266212463379</t>
@@ -4187,28 +4190,28 @@
     <t xml:space="preserve">8.76632404327393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96113204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1736478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0319709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04968070983887</t>
+    <t xml:space="preserve">8.96113109588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17364883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03197002410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04967975616455</t>
   </si>
   <si>
     <t xml:space="preserve">9.13822841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92571258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97884082794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84601783752441</t>
+    <t xml:space="preserve">8.9257116317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97884178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84601879119873</t>
   </si>
   <si>
     <t xml:space="preserve">8.90800189971924</t>
@@ -4220,25 +4223,25 @@
     <t xml:space="preserve">8.81059837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78403377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79288959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74861526489258</t>
+    <t xml:space="preserve">8.78403472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79288864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74861431121826</t>
   </si>
   <si>
     <t xml:space="preserve">8.80174350738525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8371639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99655055999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39441871643066</t>
+    <t xml:space="preserve">8.83716297149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99655151367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39441967010498</t>
   </si>
   <si>
     <t xml:space="preserve">8.62464618682861</t>
@@ -4253,19 +4256,19 @@
     <t xml:space="preserve">8.51838779449463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50067901611328</t>
+    <t xml:space="preserve">8.50067806243896</t>
   </si>
   <si>
     <t xml:space="preserve">8.40327453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43869304656982</t>
+    <t xml:space="preserve">8.43869400024414</t>
   </si>
   <si>
     <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5095329284668</t>
+    <t xml:space="preserve">8.50953197479248</t>
   </si>
   <si>
     <t xml:space="preserve">8.7043399810791</t>
@@ -4280,7 +4283,7 @@
     <t xml:space="preserve">9.0851001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20906829833984</t>
+    <t xml:space="preserve">9.20906734466553</t>
   </si>
   <si>
     <t xml:space="preserve">9.29761695861816</t>
@@ -4289,28 +4292,28 @@
     <t xml:space="preserve">9.19135856628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35074615478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2799072265625</t>
+    <t xml:space="preserve">9.35074710845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27990627288818</t>
   </si>
   <si>
     <t xml:space="preserve">9.45700454711914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10280990600586</t>
+    <t xml:space="preserve">9.10280895233154</t>
   </si>
   <si>
     <t xml:space="preserve">8.85487270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67777633666992</t>
+    <t xml:space="preserve">8.67777538299561</t>
   </si>
   <si>
     <t xml:space="preserve">8.77517890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89029216766357</t>
+    <t xml:space="preserve">8.89029312133789</t>
   </si>
   <si>
     <t xml:space="preserve">8.94342231750488</t>
@@ -4319,13 +4322,13 @@
     <t xml:space="preserve">8.82830905914307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73976039886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72204971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53609752655029</t>
+    <t xml:space="preserve">8.73975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72205066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53609848022461</t>
   </si>
   <si>
     <t xml:space="preserve">8.54495239257812</t>
@@ -4334,16 +4337,16 @@
     <t xml:space="preserve">8.4564037322998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42983913421631</t>
+    <t xml:space="preserve">8.42984008789062</t>
   </si>
   <si>
     <t xml:space="preserve">8.41212940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49182319641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26219654083252</t>
+    <t xml:space="preserve">8.49182415008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26219749450684</t>
   </si>
   <si>
     <t xml:space="preserve">9.12051963806152</t>
@@ -4355,25 +4358,25 @@
     <t xml:space="preserve">8.65121173858643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06738948822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61639213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63410091400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66952228546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.006007194519</t>
+    <t xml:space="preserve">9.06739044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6163911819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6341028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66952133178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0060062408447</t>
   </si>
   <si>
     <t xml:space="preserve">10.0237159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95287704467773</t>
+    <t xml:space="preserve">9.95287799835205</t>
   </si>
   <si>
     <t xml:space="preserve">10.0591354370117</t>
@@ -4382,10 +4385,10 @@
     <t xml:space="preserve">9.8289098739624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75806999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3684549331665</t>
+    <t xml:space="preserve">9.75807094573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36845588684082</t>
   </si>
   <si>
     <t xml:space="preserve">9.31532669067383</t>
@@ -4409,16 +4412,16 @@
     <t xml:space="preserve">10.1653938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2716522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360200881958</t>
+    <t xml:space="preserve">10.271653175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3602018356323</t>
   </si>
   <si>
     <t xml:space="preserve">10.1831035614014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2185230255127</t>
+    <t xml:space="preserve">10.218523979187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2362337112427</t>
@@ -4427,7 +4430,7 @@
     <t xml:space="preserve">10.253942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3424911499023</t>
+    <t xml:space="preserve">10.3424921035767</t>
   </si>
   <si>
     <t xml:space="preserve">9.58115100860596</t>
@@ -4752,6 +4755,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.71000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72999954223633</t>
   </si>
 </sst>
 </file>
@@ -61866,7 +61872,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2184" t="s">
-        <v>1324</v>
+        <v>1365</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61892,7 +61898,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2185" t="s">
-        <v>1324</v>
+        <v>1365</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61944,7 +61950,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2187" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61970,7 +61976,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2188" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62022,7 +62028,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2190" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62074,7 +62080,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2192" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62178,7 +62184,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2196" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62204,7 +62210,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2197" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62230,7 +62236,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2198" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62308,7 +62314,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2201" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62334,7 +62340,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2202" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62438,7 +62444,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2206" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62464,7 +62470,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2207" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62516,7 +62522,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2209" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62542,7 +62548,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2210" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62594,7 +62600,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2212" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62672,7 +62678,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2215" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62698,7 +62704,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2216" t="s">
-        <v>1324</v>
+        <v>1365</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62724,7 +62730,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2217" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62750,7 +62756,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2218" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62776,7 +62782,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2219" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62802,7 +62808,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2220" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62854,7 +62860,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G2222" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62880,7 +62886,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2223" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62906,7 +62912,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2224" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62932,7 +62938,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2225" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62958,7 +62964,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2226" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62984,7 +62990,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G2227" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63010,7 +63016,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63036,7 +63042,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G2229" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63062,7 +63068,7 @@
         <v>9.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63088,7 +63094,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2231" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63114,7 +63120,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G2232" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63140,7 +63146,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2233" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63166,7 +63172,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2234" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63192,7 +63198,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2235" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63218,7 +63224,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2236" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63244,7 +63250,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63270,7 +63276,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63296,7 +63302,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2239" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63322,7 +63328,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2240" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63348,7 +63354,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2241" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63374,7 +63380,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2242" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63400,7 +63406,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2243" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63426,7 +63432,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2244" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63452,7 +63458,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2245" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63478,7 +63484,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G2246" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63504,7 +63510,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2247" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63530,7 +63536,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G2248" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63556,7 +63562,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2249" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63582,7 +63588,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2250" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63608,7 +63614,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2251" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63634,7 +63640,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2252" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63660,7 +63666,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2253" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63686,7 +63692,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2254" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63712,7 +63718,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2255" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63738,7 +63744,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2256" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63764,7 +63770,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2257" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63790,7 +63796,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2258" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63816,7 +63822,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2259" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63842,7 +63848,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2260" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63868,7 +63874,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63894,7 +63900,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2262" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63920,7 +63926,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2263" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63946,7 +63952,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2264" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63972,7 +63978,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2265" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63998,7 +64004,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2266" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64024,7 +64030,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2267" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64050,7 +64056,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64076,7 +64082,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2269" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64102,7 +64108,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2270" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64128,7 +64134,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2271" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64154,7 +64160,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2272" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64180,7 +64186,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2273" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64206,7 +64212,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2274" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64232,7 +64238,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2275" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64258,7 +64264,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2276" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64284,7 +64290,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2277" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64310,7 +64316,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64336,7 +64342,7 @@
         <v>10.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64362,7 +64368,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64388,7 +64394,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64414,7 +64420,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2282" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64440,7 +64446,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2283" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64466,7 +64472,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2284" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64492,7 +64498,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2285" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64518,7 +64524,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2286" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64544,7 +64550,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2287" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64570,7 +64576,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2288" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64596,7 +64602,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64622,7 +64628,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2290" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64648,7 +64654,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64674,7 +64680,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2292" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64700,7 +64706,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64726,7 +64732,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2294" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64752,7 +64758,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64778,7 +64784,7 @@
         <v>10</v>
       </c>
       <c r="G2296" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64804,7 +64810,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2297" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64830,7 +64836,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2298" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64856,7 +64862,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2299" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64882,7 +64888,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2300" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64908,7 +64914,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2301" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64934,7 +64940,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2302" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64960,7 +64966,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2303" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64986,7 +64992,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2304" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65012,7 +65018,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2305" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65038,7 +65044,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2306" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65064,7 +65070,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2307" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65090,7 +65096,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2308" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65116,7 +65122,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65142,7 +65148,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2310" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65168,7 +65174,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2311" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65194,7 +65200,7 @@
         <v>9.5</v>
       </c>
       <c r="G2312" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65220,7 +65226,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2313" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65246,7 +65252,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2314" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65272,7 +65278,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2315" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65298,7 +65304,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2316" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65324,7 +65330,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2317" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65350,7 +65356,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65376,7 +65382,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2319" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65402,7 +65408,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2320" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65428,7 +65434,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2321" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65454,7 +65460,7 @@
         <v>10.5</v>
       </c>
       <c r="G2322" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65480,7 +65486,7 @@
         <v>10.5</v>
       </c>
       <c r="G2323" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65506,7 +65512,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2324" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65532,7 +65538,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2325" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65558,7 +65564,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2326" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65584,7 +65590,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2327" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65610,7 +65616,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2328" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65636,7 +65642,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2329" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65662,7 +65668,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2330" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65688,7 +65694,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2331" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65714,7 +65720,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2332" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65740,7 +65746,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2333" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65766,7 +65772,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2334" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65792,7 +65798,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2335" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65818,7 +65824,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2336" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65844,7 +65850,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G2337" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65870,7 +65876,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2338" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65896,7 +65902,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2339" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65922,7 +65928,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2340" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65948,7 +65954,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2341" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65974,7 +65980,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2342" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66000,7 +66006,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2343" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66026,7 +66032,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2344" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66052,7 +66058,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66078,7 +66084,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2346" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66104,7 +66110,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2347" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66130,7 +66136,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2348" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66156,7 +66162,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2349" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66182,7 +66188,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66208,7 +66214,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2351" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66234,7 +66240,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2352" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66260,7 +66266,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2353" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66286,7 +66292,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2354" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66312,7 +66318,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66338,7 +66344,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66364,7 +66370,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2357" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66390,7 +66396,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2358" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66416,7 +66422,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66442,7 +66448,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2360" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66468,7 +66474,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2361" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66494,7 +66500,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2362" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66520,7 +66526,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2363" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66546,7 +66552,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66572,7 +66578,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2365" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66598,7 +66604,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2366" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66624,7 +66630,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66650,7 +66656,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66676,7 +66682,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2369" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66702,7 +66708,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2370" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66728,7 +66734,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2371" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66754,7 +66760,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2372" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66780,7 +66786,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2373" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66806,7 +66812,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2374" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66832,7 +66838,7 @@
         <v>11.5</v>
       </c>
       <c r="G2375" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66858,7 +66864,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2376" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66884,7 +66890,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2377" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66910,7 +66916,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2378" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66936,7 +66942,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2379" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66962,7 +66968,7 @@
         <v>11.5</v>
       </c>
       <c r="G2380" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66988,7 +66994,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2381" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67014,7 +67020,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2382" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67040,7 +67046,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2383" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67066,7 +67072,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2384" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67092,7 +67098,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2385" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67118,7 +67124,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2386" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67144,7 +67150,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2387" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67170,7 +67176,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2388" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67196,7 +67202,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2389" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67222,7 +67228,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2390" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67248,7 +67254,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2391" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67274,7 +67280,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G2392" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67300,7 +67306,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2393" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67326,7 +67332,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2394" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67352,7 +67358,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G2395" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67378,7 +67384,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2396" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67404,7 +67410,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2397" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67430,7 +67436,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2398" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67456,7 +67462,7 @@
         <v>9.75</v>
       </c>
       <c r="G2399" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67482,7 +67488,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2400" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67508,7 +67514,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67534,7 +67540,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2402" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67560,7 +67566,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2403" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67586,7 +67592,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2404" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67612,7 +67618,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67638,7 +67644,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2406" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67664,7 +67670,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2407" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67690,7 +67696,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2408" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67716,7 +67722,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2409" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67742,7 +67748,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2410" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67768,7 +67774,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2411" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67794,7 +67800,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2412" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67820,7 +67826,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2413" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67846,7 +67852,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2414" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67872,7 +67878,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2415" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67898,7 +67904,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2416" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67924,7 +67930,7 @@
         <v>9.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67950,7 +67956,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2418" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67976,7 +67982,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2419" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68002,7 +68008,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2420" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68028,7 +68034,7 @@
         <v>9.75</v>
       </c>
       <c r="G2421" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68054,7 +68060,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G2422" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68080,7 +68086,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2423" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68106,7 +68112,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2424" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68132,7 +68138,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2425" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68158,7 +68164,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2426" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68184,7 +68190,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2427" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68210,7 +68216,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68236,7 +68242,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G2429" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68262,7 +68268,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2430" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68288,7 +68294,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2431" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68314,7 +68320,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2432" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68340,7 +68346,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2433" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68366,7 +68372,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2434" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68392,7 +68398,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2435" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68418,7 +68424,7 @@
         <v>8.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68444,7 +68450,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2437" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68470,7 +68476,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68496,7 +68502,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68522,7 +68528,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2440" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68548,7 +68554,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2441" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68574,7 +68580,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2442" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68600,7 +68606,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68626,7 +68632,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68652,7 +68658,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2445" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68678,7 +68684,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2446" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68704,7 +68710,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2447" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68730,7 +68736,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2448" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68756,7 +68762,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2449" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68782,7 +68788,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2450" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68808,7 +68814,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2451" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68834,7 +68840,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2452" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68860,7 +68866,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2453" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68886,7 +68892,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2454" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68912,7 +68918,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2455" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68938,7 +68944,7 @@
         <v>8.75</v>
       </c>
       <c r="G2456" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68964,7 +68970,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2457" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68990,7 +68996,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2458" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69016,7 +69022,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69042,7 +69048,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2460" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69068,7 +69074,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2461" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69094,7 +69100,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2462" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69120,7 +69126,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2463" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69146,7 +69152,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2464" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69172,7 +69178,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2465" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69198,7 +69204,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G2466" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69224,7 +69230,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69250,7 +69256,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69276,7 +69282,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69302,7 +69308,7 @@
         <v>9</v>
       </c>
       <c r="G2470" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69328,7 +69334,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2471" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69354,7 +69360,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2472" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69380,7 +69386,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2473" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69406,7 +69412,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2474" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69432,7 +69438,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2475" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69458,7 +69464,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69484,7 +69490,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2477" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69510,7 +69516,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69536,7 +69542,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2479" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69562,7 +69568,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2480" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69588,7 +69594,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2481" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69614,7 +69620,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2482" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69640,7 +69646,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2483" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69666,7 +69672,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2484" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69692,7 +69698,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2485" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69718,7 +69724,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2486" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69744,7 +69750,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2487" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69770,7 +69776,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2488" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69796,7 +69802,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2489" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69822,7 +69828,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2490" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69848,7 +69854,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2491" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69874,7 +69880,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2492" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69900,7 +69906,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2493" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69926,7 +69932,7 @@
         <v>9.75</v>
       </c>
       <c r="G2494" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69952,7 +69958,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2495" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69978,7 +69984,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2496" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70004,7 +70010,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2497" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70030,7 +70036,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2498" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70056,7 +70062,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2499" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70082,7 +70088,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2500" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70108,7 +70114,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2501" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70134,7 +70140,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2502" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70160,7 +70166,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2503" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70186,7 +70192,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2504" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70212,7 +70218,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G2505" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -70238,7 +70244,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2506" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -70264,7 +70270,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2507" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70290,7 +70296,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2508" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -70316,7 +70322,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2509" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -70342,7 +70348,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -70368,7 +70374,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2511" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -70394,7 +70400,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2512" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70420,7 +70426,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2513" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70446,7 +70452,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2514" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70472,7 +70478,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2515" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70498,7 +70504,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2516" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70524,7 +70530,7 @@
         <v>9.25</v>
       </c>
       <c r="G2517" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70550,7 +70556,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2518" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70576,7 +70582,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2519" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70602,7 +70608,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2520" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70628,7 +70634,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2521" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70654,7 +70660,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2522" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70680,7 +70686,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2523" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70706,7 +70712,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2524" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -70732,7 +70738,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2525" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -70758,7 +70764,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2526" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -70784,7 +70790,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2527" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -70810,7 +70816,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2528" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -70836,7 +70842,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2529" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -70862,7 +70868,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2530" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -70888,7 +70894,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2531" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -70914,7 +70920,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2532" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -70940,7 +70946,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G2533" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -70966,7 +70972,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2534" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -70992,7 +70998,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2535" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -71018,7 +71024,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2536" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -71026,7 +71032,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.6912615741</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>99424</v>
@@ -71044,9 +71050,35 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G2537" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.6912731481</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>77117</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>9.76000022888184</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>9.61999988555908</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>9.72999954223633</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>9.72999954223633</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -38,151 +38,151 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79523420333862</t>
+    <t xml:space="preserve">7.79523515701294</t>
   </si>
   <si>
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74423837661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72238159179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72966861724854</t>
+    <t xml:space="preserve">7.74423789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72238206863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72966814041138</t>
   </si>
   <si>
     <t xml:space="preserve">7.78795003890991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7733793258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56939077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54753541946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61310338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21241474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17598724365234</t>
+    <t xml:space="preserve">7.77337741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56939220428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54753494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61310243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21241331100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17598676681519</t>
   </si>
   <si>
     <t xml:space="preserve">7.62038850784302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46739912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35811901092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30712175369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3872594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56210613250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49653959274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28526639938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37269020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64952850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51839447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58396148681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67867040634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86080265045166</t>
+    <t xml:space="preserve">7.46739864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35811853408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30712127685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725996017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5621075630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49653768539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2852668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37268972396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64952898025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.518394947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5839638710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67867183685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8608021736145</t>
   </si>
   <si>
     <t xml:space="preserve">7.76609325408936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89722919464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90451431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95551061630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80980491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88994359970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00650787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87537288665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01379203796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94822692871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03564834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80252122879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84623098373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05750465393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05021953582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02836132049561</t>
+    <t xml:space="preserve">7.89722871780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9045147895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95550870895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80980587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88994312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00650691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94094038009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8753719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01379299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9482250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03564739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80251979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84623146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05750560760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05021858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02836322784424</t>
   </si>
   <si>
     <t xml:space="preserve">8.15949821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38534164428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45090961456299</t>
+    <t xml:space="preserve">8.38533878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45090866088867</t>
   </si>
   <si>
     <t xml:space="preserve">8.4363374710083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45819091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63304233551025</t>
+    <t xml:space="preserve">8.45819282531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6330394744873</t>
   </si>
   <si>
     <t xml:space="preserve">8.71317768096924</t>
@@ -191,58 +191,58 @@
     <t xml:space="preserve">8.6038990020752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74231910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80788707733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42176723480225</t>
+    <t xml:space="preserve">8.74231815338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80788516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42176818847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.73503398895264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79331684112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65489768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70589351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81517314910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95359230041504</t>
+    <t xml:space="preserve">8.79331588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6548957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70589256286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81517219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95359039306641</t>
   </si>
   <si>
     <t xml:space="preserve">8.75688934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20857715606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26686000823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25228881835938</t>
+    <t xml:space="preserve">9.20857810974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26685905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25228786468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.39799308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48541736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36156558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32488536834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07543659210205</t>
+    <t xml:space="preserve">9.48541641235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36156845092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32488441467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07543849945068</t>
   </si>
   <si>
     <t xml:space="preserve">9.09744834899902</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">9.17081451416016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29553699493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3689022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27352809906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28819942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20749759674072</t>
+    <t xml:space="preserve">9.29553604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36890411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27352714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28820133209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20749855041504</t>
   </si>
   <si>
     <t xml:space="preserve">9.24418067932129</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">8.87734794616699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84066581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398273468018</t>
+    <t xml:space="preserve">8.84066390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">8.73061561584473</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">8.95071506500244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22950744628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81865406036377</t>
+    <t xml:space="preserve">9.22950553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81865310668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.8259916305542</t>
@@ -302,25 +302,25 @@
     <t xml:space="preserve">8.91403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31754684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95805072784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99473571777344</t>
+    <t xml:space="preserve">9.31754779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95805168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99473285675049</t>
   </si>
   <si>
     <t xml:space="preserve">9.1928243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13413047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34689331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35422992706299</t>
+    <t xml:space="preserve">9.13413143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34689426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35422897338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.22217082977295</t>
@@ -329,70 +329,70 @@
     <t xml:space="preserve">9.06076431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37624073028564</t>
+    <t xml:space="preserve">9.37624168395996</t>
   </si>
   <si>
     <t xml:space="preserve">9.33955669403076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31021118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26618957519531</t>
+    <t xml:space="preserve">9.31021022796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28086376190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26619052886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.97272396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16347789764404</t>
+    <t xml:space="preserve">9.16347694396973</t>
   </si>
   <si>
     <t xml:space="preserve">9.17815017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39825057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30287456512451</t>
+    <t xml:space="preserve">9.39824962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30287551879883</t>
   </si>
   <si>
     <t xml:space="preserve">9.25885391235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33222103118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11945724487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00207138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96538829803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14146614074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01674461364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39091491699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15614128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38357734680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44960784912109</t>
+    <t xml:space="preserve">9.33222198486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11945819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05342960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00207233428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96538734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14146709442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01674365997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39091300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15614032745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38357639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44960498809814</t>
   </si>
   <si>
     <t xml:space="preserve">9.49362754821777</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">9.52297210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50829982757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79442977905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83844947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312271118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95583724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0438747406006</t>
+    <t xml:space="preserve">9.50830173492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79443073272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83844757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85312366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95583629608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0438756942749</t>
   </si>
   <si>
     <t xml:space="preserve">10.1392526626587</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">10.2566385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1979455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.271312713623</t>
+    <t xml:space="preserve">10.1979446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2713117599487</t>
   </si>
   <si>
     <t xml:space="preserve">9.90447902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0145292282104</t>
+    <t xml:space="preserve">10.0145282745361</t>
   </si>
   <si>
     <t xml:space="preserve">9.75774669647217</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">9.80910301208496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64035892486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53764629364014</t>
+    <t xml:space="preserve">9.64035987854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53764724731445</t>
   </si>
   <si>
     <t xml:space="preserve">9.45694351196289</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">9.56699275970459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44227123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5156364440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53030967712402</t>
+    <t xml:space="preserve">9.44227027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51563549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53031063079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.47895431518555</t>
@@ -482,61 +482,61 @@
     <t xml:space="preserve">9.63302230834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55965805053711</t>
+    <t xml:space="preserve">9.55965614318848</t>
   </si>
   <si>
     <t xml:space="preserve">9.47161674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73573875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0878953933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1245794296265</t>
+    <t xml:space="preserve">9.73573589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0878963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1245775222778</t>
   </si>
   <si>
     <t xml:space="preserve">10.0512113571167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86779594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8311128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97050857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97784519195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81643867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69171619415283</t>
+    <t xml:space="preserve">9.8677978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83111381530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97050952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97784614562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81644058227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69171714782715</t>
   </si>
   <si>
     <t xml:space="preserve">9.88980579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86046123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96317195892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0585489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99251842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.161262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1465892791748</t>
+    <t xml:space="preserve">9.86046028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96317291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0585498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99251747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1612606048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1465883255005</t>
   </si>
   <si>
     <t xml:space="preserve">9.94116306304932</t>
@@ -545,46 +545,46 @@
     <t xml:space="preserve">9.82377624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72106266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8751335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0365381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0805597305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0071935653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.897141456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69905185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98518085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7335214614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7115116119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6674900054932</t>
+    <t xml:space="preserve">9.7210636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87513160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0365390777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0805587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.00719165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89714241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69905281066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.985182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7335205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7115106582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6674909591675</t>
   </si>
   <si>
     <t xml:space="preserve">10.8582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8215627670288</t>
+    <t xml:space="preserve">10.8215599060059</t>
   </si>
   <si>
     <t xml:space="preserve">10.9316101074219</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">10.8068876266479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9022636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1883926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2177381515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3424644470215</t>
+    <t xml:space="preserve">10.9022655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1883935928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2177400588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3424634933472</t>
   </si>
   <si>
     <t xml:space="preserve">11.1957302093506</t>
@@ -614,214 +614,214 @@
     <t xml:space="preserve">11.0636701583862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9242734909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0416593551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1517095565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.225076675415</t>
+    <t xml:space="preserve">10.9242725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0416603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1517105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2250776290894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2984428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166337966919</t>
+    <t xml:space="preserve">11.7166328430176</t>
   </si>
   <si>
     <t xml:space="preserve">11.7313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8340187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8853759765625</t>
+    <t xml:space="preserve">11.8340196609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8853750228882</t>
   </si>
   <si>
     <t xml:space="preserve">11.9954252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6997423171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.022557258606</t>
+    <t xml:space="preserve">12.6997442245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0225563049316</t>
   </si>
   <si>
     <t xml:space="preserve">13.0592393875122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2059736251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6924076080322</t>
+    <t xml:space="preserve">13.2059717178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6924085617065</t>
   </si>
   <si>
     <t xml:space="preserve">12.2815551757812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054735183716</t>
+    <t xml:space="preserve">12.1054754257202</t>
   </si>
   <si>
     <t xml:space="preserve">12.178840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.479642868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3255748748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6850700378418</t>
+    <t xml:space="preserve">12.4796438217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3255739212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6850681304932</t>
   </si>
   <si>
     <t xml:space="preserve">12.6630611419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8024568557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1399440765381</t>
+    <t xml:space="preserve">12.655725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619520187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8024559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391399383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1399431228638</t>
   </si>
   <si>
     <t xml:space="preserve">13.000545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9491901397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0959224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0445652008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7195386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.785569190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295888900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396390914917</t>
+    <t xml:space="preserve">12.9491910934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0959215164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.04456615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.719536781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7855672836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295879364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396381378174</t>
   </si>
   <si>
     <t xml:space="preserve">14.0643606185913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6828536987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7268762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8222522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7415475845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9249639511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6755199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4480800628662</t>
+    <t xml:space="preserve">13.6828556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7268772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8222513198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7415466308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9249649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6755180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4480819702148</t>
   </si>
   <si>
     <t xml:space="preserve">13.4627561569214</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4037704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5364818572998</t>
+    <t xml:space="preserve">13.4037714004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5364837646484</t>
   </si>
   <si>
     <t xml:space="preserve">13.7945337295532</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8903789520264</t>
+    <t xml:space="preserve">13.8903799057007</t>
   </si>
   <si>
     <t xml:space="preserve">13.4922466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.551230430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6618242263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9641056060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9862251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0452079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7429237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7650413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6544494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4553813934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9346141815186</t>
+    <t xml:space="preserve">13.5512294769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6618213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9641075134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9862241744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0452089309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7429227828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7650394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.654447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4553823471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9346160888672</t>
   </si>
   <si>
     <t xml:space="preserve">13.9714794158936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7134304046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9272432327271</t>
+    <t xml:space="preserve">13.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9272422790527</t>
   </si>
   <si>
     <t xml:space="preserve">13.8830041885376</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0820713043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0083446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.853515625</t>
+    <t xml:space="preserve">14.0820732116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0083436965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8535137176514</t>
   </si>
   <si>
     <t xml:space="preserve">13.1973342895508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5069913864136</t>
+    <t xml:space="preserve">13.5069942474365</t>
   </si>
   <si>
     <t xml:space="preserve">13.3079252243042</t>
@@ -830,19 +830,19 @@
     <t xml:space="preserve">13.3300447463989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3152990341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6470746994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7871599197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8092765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7797880172729</t>
+    <t xml:space="preserve">13.315299987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6470775604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7871580123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8092756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7797861099243</t>
   </si>
   <si>
     <t xml:space="preserve">13.8387680053711</t>
@@ -851,73 +851,73 @@
     <t xml:space="preserve">13.9493627548218</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1189346313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8977518081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9198713302612</t>
+    <t xml:space="preserve">14.1189336776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8977508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9198684692383</t>
   </si>
   <si>
     <t xml:space="preserve">13.8240222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.941987991333</t>
+    <t xml:space="preserve">13.9419889450073</t>
   </si>
   <si>
     <t xml:space="preserve">13.8313961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.676568031311</t>
+    <t xml:space="preserve">13.6765670776367</t>
   </si>
   <si>
     <t xml:space="preserve">13.4627552032471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3816537857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1014881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5291118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.565975189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5586013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2710628509521</t>
+    <t xml:space="preserve">13.3816547393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.101487159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5291109085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5659732818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5586004257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2710609436035</t>
   </si>
   <si>
     <t xml:space="preserve">13.3890285491943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5807199478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6102132797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4185190200806</t>
+    <t xml:space="preserve">13.5807209014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6102113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4185171127319</t>
   </si>
   <si>
     <t xml:space="preserve">13.7060565948486</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7576675415039</t>
+    <t xml:space="preserve">13.7576694488525</t>
   </si>
   <si>
     <t xml:space="preserve">13.6986846923828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8166484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.728178024292</t>
+    <t xml:space="preserve">13.816650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7281761169434</t>
   </si>
   <si>
     <t xml:space="preserve">13.7355499267578</t>
@@ -929,61 +929,61 @@
     <t xml:space="preserve">13.6397018432617</t>
   </si>
   <si>
-    <t xml:space="preserve">13.905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6249551773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.602837562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7456245422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6055421829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6129150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.531813621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4728307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5613021850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4359664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2958822250366</t>
+    <t xml:space="preserve">13.9051237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6249561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6028385162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7456226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.605541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6129159927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5318117141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4728317260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5613031387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4359674453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2958841323853</t>
   </si>
   <si>
     <t xml:space="preserve">14.3032550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2590208053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9124956130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6913108825684</t>
+    <t xml:space="preserve">14.2590198516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9124965667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.691312789917</t>
   </si>
   <si>
     <t xml:space="preserve">14.1336812973022</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0304622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9567308425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0378322601318</t>
+    <t xml:space="preserve">14.0304594039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.956732749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0378370285034</t>
   </si>
   <si>
     <t xml:space="preserve">14.1263084411621</t>
@@ -992,130 +992,130 @@
     <t xml:space="preserve">14.1705436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2147817611694</t>
+    <t xml:space="preserve">14.2147808074951</t>
   </si>
   <si>
     <t xml:space="preserve">14.155800819397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0230894088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1041879653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8461427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8608865737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.978853225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1926641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2295274734497</t>
+    <t xml:space="preserve">14.0230865478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8461389541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8608875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9788513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.192663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.229528427124</t>
   </si>
   <si>
     <t xml:space="preserve">14.5096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6497783660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9299449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8562183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.782488822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.583423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3474931716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4949474334717</t>
+    <t xml:space="preserve">14.6497793197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9299440383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8562173843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7824878692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5834226608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3474922180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4949493408203</t>
   </si>
   <si>
     <t xml:space="preserve">15.2617225646973</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0774011611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1511287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566377639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4091777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3354511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4460401535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0405387878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1142663955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6276569366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2885103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2737636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1852922439575</t>
+    <t xml:space="preserve">15.0774002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1511316299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4091787338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668092727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3354520797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.446044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0405406951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1142635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6276607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2885093688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2737646102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1852941513062</t>
   </si>
   <si>
     <t xml:space="preserve">14.5391874313354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4212198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000379562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.406476020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3447914123535</t>
+    <t xml:space="preserve">14.3917303085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4212188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4064769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3447895050049</t>
   </si>
   <si>
     <t xml:space="preserve">13.5217370986938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6839408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8756341934204</t>
+    <t xml:space="preserve">13.6839399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8756322860718</t>
   </si>
   <si>
     <t xml:space="preserve">12.9908962249756</t>
@@ -1124,49 +1124,49 @@
     <t xml:space="preserve">13.138352394104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.976149559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7549657821655</t>
+    <t xml:space="preserve">12.9761486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7549667358398</t>
   </si>
   <si>
     <t xml:space="preserve">12.6517467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.887677192688</t>
+    <t xml:space="preserve">12.8876762390137</t>
   </si>
   <si>
     <t xml:space="preserve">12.8729305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7254753112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0793695449829</t>
+    <t xml:space="preserve">12.725474357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0793685913086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8286943435669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5927648544312</t>
+    <t xml:space="preserve">12.5927629470825</t>
   </si>
   <si>
     <t xml:space="preserve">12.5190362930298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4600534439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5042886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7402191162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6812372207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0646228790283</t>
+    <t xml:space="preserve">12.4600524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5042905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7402219772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6812391281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.064621925354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2858095169067</t>
@@ -1178,64 +1178,64 @@
     <t xml:space="preserve">13.3005523681641</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0968189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3742799758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.366870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3075942993164</t>
+    <t xml:space="preserve">14.0968179702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3742809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3668718338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3075971603394</t>
   </si>
   <si>
     <t xml:space="preserve">13.1890420913696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4113311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4854259490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9371175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2702560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7592878341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5962753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6851921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0408506393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9667539596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.144585609436</t>
+    <t xml:space="preserve">13.4113292694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.485424041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9371185302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2702541351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7592849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5962762832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6851902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0408515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9667568206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1445846557617</t>
   </si>
   <si>
     <t xml:space="preserve">12.8630208969116</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8926601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963941574097</t>
+    <t xml:space="preserve">12.8926620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.996392250061</t>
   </si>
   <si>
     <t xml:space="preserve">12.818564414978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7444677352905</t>
+    <t xml:space="preserve">12.7444696426392</t>
   </si>
   <si>
     <t xml:space="preserve">12.981575012207</t>
@@ -1244,100 +1244,100 @@
     <t xml:space="preserve">13.2483186721802</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2927770614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0853090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4706039428711</t>
+    <t xml:space="preserve">13.2927761077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0853080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4706048965454</t>
   </si>
   <si>
     <t xml:space="preserve">13.5298824310303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4409666061401</t>
+    <t xml:space="preserve">13.4409685134888</t>
   </si>
   <si>
     <t xml:space="preserve">13.2779579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3224143981934</t>
+    <t xml:space="preserve">13.3224153518677</t>
   </si>
   <si>
     <t xml:space="preserve">13.3816909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6039772033691</t>
+    <t xml:space="preserve">13.6039781570435</t>
   </si>
   <si>
     <t xml:space="preserve">13.515064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3372344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743398666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299993515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8855409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.826265335083</t>
+    <t xml:space="preserve">13.337233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743427276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9300003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8855438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.826268196106</t>
   </si>
   <si>
     <t xml:space="preserve">13.7669887542725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6928911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7521715164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8559045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9892778396606</t>
+    <t xml:space="preserve">13.6928930282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7521705627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8559036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9892768859863</t>
   </si>
   <si>
     <t xml:space="preserve">13.2038621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7818078994751</t>
+    <t xml:space="preserve">13.7818088531494</t>
   </si>
   <si>
     <t xml:space="preserve">13.9003620147705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7225332260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9596385955811</t>
+    <t xml:space="preserve">13.7225313186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9596405029297</t>
   </si>
   <si>
     <t xml:space="preserve">13.7077121734619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5447025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5595216751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1149463653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4261465072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6555547714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8778419494629</t>
+    <t xml:space="preserve">13.5447006225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5595207214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1149454116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4261484146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.655553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8778409957886</t>
   </si>
   <si>
     <t xml:space="preserve">12.9222974777222</t>
@@ -1349,121 +1349,121 @@
     <t xml:space="preserve">13.1297655105591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0112113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665210723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1517028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0479669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220655441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3739900588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4777250289917</t>
+    <t xml:space="preserve">13.011212348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.166522026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1517009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3739881515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4777240753174</t>
   </si>
   <si>
     <t xml:space="preserve">12.1368827819824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.707127571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.033148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812242507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2477321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4700202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4403829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5885734558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6478490829468</t>
+    <t xml:space="preserve">11.7071266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0331497192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812232971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2477331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4700212478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4403839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5885744094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6478509902954</t>
   </si>
   <si>
     <t xml:space="preserve">11.5589370727539</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3811054229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.351466178894</t>
+    <t xml:space="preserve">11.3811063766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3514680862427</t>
   </si>
   <si>
     <t xml:space="preserve">11.173638343811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1143608093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.025447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6697864532471</t>
+    <t xml:space="preserve">11.1143617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0254459381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6697883605957</t>
   </si>
   <si>
     <t xml:space="preserve">10.0029258728027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4326801300049</t>
+    <t xml:space="preserve">10.4326810836792</t>
   </si>
   <si>
     <t xml:space="preserve">10.7883405685425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4771375656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5512323379517</t>
+    <t xml:space="preserve">10.4771385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5512342453003</t>
   </si>
   <si>
     <t xml:space="preserve">10.8920745849609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9661703109741</t>
+    <t xml:space="preserve">10.9661712646484</t>
   </si>
   <si>
     <t xml:space="preserve">11.0995426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0770206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3751106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8706378936768</t>
+    <t xml:space="preserve">10.0770225524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.375111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8706388473511</t>
   </si>
   <si>
     <t xml:space="preserve">10.8241815567017</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4835090637207</t>
+    <t xml:space="preserve">10.4835081100464</t>
   </si>
   <si>
     <t xml:space="preserve">10.5609340667725</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1738023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6538457870483</t>
+    <t xml:space="preserve">10.1738042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6538467407227</t>
   </si>
   <si>
     <t xml:space="preserve">11.3042259216309</t>
@@ -1475,22 +1475,22 @@
     <t xml:space="preserve">10.6073894500732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5299625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7622413635254</t>
+    <t xml:space="preserve">10.5299634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7622423171997</t>
   </si>
   <si>
     <t xml:space="preserve">10.7777271270752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7312698364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357454299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4525375366211</t>
+    <t xml:space="preserve">10.7312717437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.235743522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4525365829468</t>
   </si>
   <si>
     <t xml:space="preserve">10.406081199646</t>
@@ -1505,31 +1505,31 @@
     <t xml:space="preserve">11.1493730545044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.071946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9480657577515</t>
+    <t xml:space="preserve">11.0719470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9480667114258</t>
   </si>
   <si>
     <t xml:space="preserve">11.040976524353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3286552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4370527267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5919065475464</t>
+    <t xml:space="preserve">10.3286571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4370517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5919036865234</t>
   </si>
   <si>
     <t xml:space="preserve">10.4989938735962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5144777297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3905954360962</t>
+    <t xml:space="preserve">10.5144786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3905944824219</t>
   </si>
   <si>
     <t xml:space="preserve">10.3596258163452</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">10.6693305969238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6228742599487</t>
+    <t xml:space="preserve">10.622875213623</t>
   </si>
   <si>
     <t xml:space="preserve">10.8551530838013</t>
@@ -1547,34 +1547,34 @@
     <t xml:space="preserve">11.1184024810791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3816499710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3661670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.242283821106</t>
+    <t xml:space="preserve">11.3816518783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3661651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2422847747803</t>
   </si>
   <si>
     <t xml:space="preserve">11.1648578643799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3506803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9790344238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.793212890625</t>
+    <t xml:space="preserve">11.350682258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9790353775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7932109832764</t>
   </si>
   <si>
     <t xml:space="preserve">10.8861255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5764188766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2047748565674</t>
+    <t xml:space="preserve">10.5764198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2047739028931</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118621826172</t>
@@ -1583,46 +1583,46 @@
     <t xml:space="preserve">10.0808916091919</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67827415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56987762451172</t>
+    <t xml:space="preserve">9.6782751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56987953186035</t>
   </si>
   <si>
     <t xml:space="preserve">9.75570106506348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95700836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87958335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94152545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92603778839111</t>
+    <t xml:space="preserve">9.95700931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87958240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94152355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92603969573975</t>
   </si>
   <si>
     <t xml:space="preserve">10.158317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1428327560425</t>
+    <t xml:space="preserve">10.1428318023682</t>
   </si>
   <si>
     <t xml:space="preserve">9.91055297851562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1273469924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3441400527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6383609771729</t>
+    <t xml:space="preserve">10.127347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3441390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6383590698242</t>
   </si>
   <si>
     <t xml:space="preserve">10.7157869338989</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">10.6848154067993</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0344362258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.018949508667</t>
+    <t xml:space="preserve">10.0344352722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0189504623413</t>
   </si>
   <si>
     <t xml:space="preserve">9.97249603271484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2202568054199</t>
+    <t xml:space="preserve">10.2202587127686</t>
   </si>
   <si>
     <t xml:space="preserve">9.81734848022461</t>
@@ -1652,88 +1652,88 @@
     <t xml:space="preserve">10.1445932388306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3160076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4874210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.503005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.30042552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91084766387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0043458938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87968063354492</t>
+    <t xml:space="preserve">10.3160066604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4874229431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5030040740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3004236221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91084861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0043449401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87967967987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.895263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98876190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0510950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0822601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1134281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3627557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3939237594604</t>
+    <t xml:space="preserve">9.98876285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0510940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0822610855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1134262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.362756729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3939247131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.6744184494019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5341711044312</t>
+    <t xml:space="preserve">10.5341701507568</t>
   </si>
   <si>
     <t xml:space="preserve">10.4250888824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6276702880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4406719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1290111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2225093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1913423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2069263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4562549591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3783397674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6432523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302488327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7523345947266</t>
+    <t xml:space="preserve">10.6276693344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4406728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1290102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.222508430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1913433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2069253921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4562540054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3783388137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.643253326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.830249786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7523336410522</t>
   </si>
   <si>
     <t xml:space="preserve">11.0795793533325</t>
@@ -1742,19 +1742,19 @@
     <t xml:space="preserve">10.9549160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6900014877319</t>
+    <t xml:space="preserve">10.6900024414062</t>
   </si>
   <si>
     <t xml:space="preserve">10.7679166793823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2198276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2509918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0639963150024</t>
+    <t xml:space="preserve">11.2198266983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2509937286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0639953613281</t>
   </si>
   <si>
     <t xml:space="preserve">11.1574945449829</t>
@@ -1763,49 +1763,49 @@
     <t xml:space="preserve">10.2536754608154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.284839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.238091468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1601753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4095058441162</t>
+    <t xml:space="preserve">10.2848415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2380933761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1601762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4095048904419</t>
   </si>
   <si>
     <t xml:space="preserve">10.0355129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1757593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8146677017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1263275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.048412322998</t>
+    <t xml:space="preserve">10.175760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8146657943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1263284683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0484132766724</t>
   </si>
   <si>
     <t xml:space="preserve">11.1419115066528</t>
   </si>
   <si>
-    <t xml:space="preserve">11.032829284668</t>
+    <t xml:space="preserve">11.0328302383423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7367506027222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5965023040771</t>
+    <t xml:space="preserve">10.5965032577515</t>
   </si>
   <si>
     <t xml:space="preserve">10.6120862960815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7211675643921</t>
+    <t xml:space="preserve">10.7211694717407</t>
   </si>
   <si>
     <t xml:space="preserve">10.9081649780273</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">10.9237480163574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.783501625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8769989013672</t>
+    <t xml:space="preserve">10.7835006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8769998550415</t>
   </si>
   <si>
     <t xml:space="preserve">10.9704961776733</t>
@@ -1826,19 +1826,19 @@
     <t xml:space="preserve">11.5470714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8587331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9054841995239</t>
+    <t xml:space="preserve">11.8587341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9054832458496</t>
   </si>
   <si>
     <t xml:space="preserve">11.656153678894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7340698242188</t>
+    <t xml:space="preserve">11.8275671005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7340688705444</t>
   </si>
   <si>
     <t xml:space="preserve">11.9989805221558</t>
@@ -1847,10 +1847,10 @@
     <t xml:space="preserve">11.8743171691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9210662841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768976211548</t>
+    <t xml:space="preserve">11.921067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768966674805</t>
   </si>
   <si>
     <t xml:space="preserve">11.843150138855</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">11.8898992538452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8119831085205</t>
+    <t xml:space="preserve">11.8119859695435</t>
   </si>
   <si>
     <t xml:space="preserve">11.1107454299927</t>
@@ -1871,43 +1871,43 @@
     <t xml:space="preserve">10.9860811233521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3444919586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.780818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0301475524902</t>
+    <t xml:space="preserve">11.3444929122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7808170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0301485061646</t>
   </si>
   <si>
     <t xml:space="preserve">11.9366493225098</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7964010238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6249876022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4691572189331</t>
+    <t xml:space="preserve">11.7964019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6249866485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4691562652588</t>
   </si>
   <si>
     <t xml:space="preserve">11.5626554489136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4379911422729</t>
+    <t xml:space="preserve">11.4379892349243</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314884185791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3756589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4535722732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4224061965942</t>
+    <t xml:space="preserve">11.3756580352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4535732269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4224081039429</t>
   </si>
   <si>
     <t xml:space="preserve">11.1886606216431</t>
@@ -1919,49 +1919,49 @@
     <t xml:space="preserve">11.2821578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7055854797363</t>
+    <t xml:space="preserve">10.7055835723877</t>
   </si>
   <si>
     <t xml:space="preserve">10.8925809860229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6588373184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3315896987915</t>
+    <t xml:space="preserve">10.6588344573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3315916061401</t>
   </si>
   <si>
     <t xml:space="preserve">10.3471746444702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199270248413</t>
+    <t xml:space="preserve">10.0199289321899</t>
   </si>
   <si>
     <t xml:space="preserve">9.97317886352539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0978450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94201374053955</t>
+    <t xml:space="preserve">10.0978441238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94201278686523</t>
   </si>
   <si>
     <t xml:space="preserve">9.80176544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92643070220947</t>
+    <t xml:space="preserve">9.92642974853516</t>
   </si>
   <si>
     <t xml:space="preserve">8.97586250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86678028106689</t>
+    <t xml:space="preserve">8.86677932739258</t>
   </si>
   <si>
     <t xml:space="preserve">9.13169384002686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02260875701904</t>
+    <t xml:space="preserve">9.02261161804199</t>
   </si>
   <si>
     <t xml:space="preserve">8.80444812774658</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">8.25903987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24345588684082</t>
+    <t xml:space="preserve">8.24345684051514</t>
   </si>
   <si>
     <t xml:space="preserve">8.14995861053467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48767471313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11368179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03576612472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15532159805298</t>
+    <t xml:space="preserve">7.48767614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11368227005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03576517105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15532207489014</t>
   </si>
   <si>
     <t xml:space="preserve">6.42023372650146</t>
@@ -2003,13 +2003,13 @@
     <t xml:space="preserve">5.85924291610718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25929403305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29045963287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53199815750122</t>
+    <t xml:space="preserve">5.25929355621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29046010971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53199768066406</t>
   </si>
   <si>
     <t xml:space="preserve">5.61770486831665</t>
@@ -2018,22 +2018,22 @@
     <t xml:space="preserve">5.49304056167603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37616729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08008766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36058378219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32941865921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35279273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29825115203857</t>
+    <t xml:space="preserve">5.37616682052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08008813858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36058473587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32941722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35279178619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29825162887573</t>
   </si>
   <si>
     <t xml:space="preserve">5.45408248901367</t>
@@ -2045,79 +2045,79 @@
     <t xml:space="preserve">5.76574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5086236000061</t>
+    <t xml:space="preserve">5.50862407684326</t>
   </si>
   <si>
     <t xml:space="preserve">5.92157506942749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8748254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80470275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8358678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89820051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27219486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25661087036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33452701568604</t>
+    <t xml:space="preserve">5.87482595443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8047022819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83586740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89820098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27219533920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25661134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33452749252319</t>
   </si>
   <si>
     <t xml:space="preserve">6.42802619934082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17090559005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45919132232666</t>
+    <t xml:space="preserve">6.17090463638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45919179916382</t>
   </si>
   <si>
     <t xml:space="preserve">6.23323726654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24882125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12415552139282</t>
+    <t xml:space="preserve">6.24882030487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12415599822998</t>
   </si>
   <si>
     <t xml:space="preserve">5.75016164779663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71899557113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86703491210938</t>
+    <t xml:space="preserve">5.71899461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86703443527222</t>
   </si>
   <si>
     <t xml:space="preserve">5.94494962692261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92936658859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03844881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22544574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35790109634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58385705947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50594139099121</t>
+    <t xml:space="preserve">5.92936706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03844833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22544479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35790205001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5838565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50594186782837</t>
   </si>
   <si>
     <t xml:space="preserve">6.49035835266113</t>
@@ -2129,31 +2129,31 @@
     <t xml:space="preserve">6.62281465530396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08251619338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27730512619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09030771255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05914258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89551830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52152442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60723161697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76306295394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55269050598145</t>
+    <t xml:space="preserve">7.08251476287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27730464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09030675888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05914115905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89551877975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52152395248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60723066329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76306200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55269002914429</t>
   </si>
   <si>
     <t xml:space="preserve">6.56827402114868</t>
@@ -2162,64 +2162,64 @@
     <t xml:space="preserve">6.68514728546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75527143478394</t>
+    <t xml:space="preserve">6.75527048110962</t>
   </si>
   <si>
     <t xml:space="preserve">6.84097719192505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65398073196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01239204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98122549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85656213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78643751144409</t>
+    <t xml:space="preserve">6.65398120880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01239156723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98122501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85656118392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78643608093262</t>
   </si>
   <si>
     <t xml:space="preserve">6.71631288528442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7318959236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8643536567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66177272796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72410535812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38906908035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24102830886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20207023620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45140075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4358172416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49814987182617</t>
+    <t xml:space="preserve">6.73189687728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86435270309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66177225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72410488128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38906812667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24102926254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20207071304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45140027999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43581771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49814891815186</t>
   </si>
   <si>
     <t xml:space="preserve">6.2877779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31115293502808</t>
+    <t xml:space="preserve">6.31115341186523</t>
   </si>
   <si>
     <t xml:space="preserve">6.326735496521</t>
@@ -2228,31 +2228,31 @@
     <t xml:space="preserve">6.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01507377624512</t>
+    <t xml:space="preserve">6.01507425308228</t>
   </si>
   <si>
     <t xml:space="preserve">6.09298944473267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07740592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00728225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95274209976196</t>
+    <t xml:space="preserve">6.07740688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00728178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9527416229248</t>
   </si>
   <si>
     <t xml:space="preserve">5.93715858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7267861366272</t>
+    <t xml:space="preserve">5.72678661346436</t>
   </si>
   <si>
     <t xml:space="preserve">5.8436598777771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6956205368042</t>
+    <t xml:space="preserve">5.69562005996704</t>
   </si>
   <si>
     <t xml:space="preserve">5.53978967666626</t>
@@ -2261,100 +2261,100 @@
     <t xml:space="preserve">5.64107894897461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56316375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54758167266846</t>
+    <t xml:space="preserve">5.56316423416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5475811958313</t>
   </si>
   <si>
     <t xml:space="preserve">5.48524808883667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52420616149902</t>
+    <t xml:space="preserve">5.52420663833618</t>
   </si>
   <si>
     <t xml:space="preserve">5.74236965179443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75795316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73457860946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79691028594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90599155426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96053314208984</t>
+    <t xml:space="preserve">5.75795269012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73457813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79691076278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90599298477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.960533618927</t>
   </si>
   <si>
     <t xml:space="preserve">5.68003749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85145139694214</t>
+    <t xml:space="preserve">5.85145235061646</t>
   </si>
   <si>
     <t xml:space="preserve">5.78132772445679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04623985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91378402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67224597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51641464233398</t>
+    <t xml:space="preserve">6.04624032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91378355026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67224645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">5.46187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15800380706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99438095092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7918004989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7606348991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80738401412964</t>
+    <t xml:space="preserve">5.15800333023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99438142776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79180145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76063537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8073844909668</t>
   </si>
   <si>
     <t xml:space="preserve">4.83075857162476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02554750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18137788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06182336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02286577224731</t>
+    <t xml:space="preserve">5.02554702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18137836456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06182289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02286529541016</t>
   </si>
   <si>
     <t xml:space="preserve">6.10078096389771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99680805206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23055505752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0513482093811</t>
+    <t xml:space="preserve">6.9968090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23055601119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05135011672974</t>
   </si>
   <si>
     <t xml:space="preserve">6.93447589874268</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">6.82539510726929</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77864503860474</t>
+    <t xml:space="preserve">6.77864599227905</t>
   </si>
   <si>
     <t xml:space="preserve">6.87214326858521</t>
@@ -2375,34 +2375,34 @@
     <t xml:space="preserve">6.91110134124756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77085304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66956472396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63060617446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97343349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63839721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70072984695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80981159210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98901748657227</t>
+    <t xml:space="preserve">6.77085447311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66956329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63060569763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97343444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63839769363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70073080062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80981111526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98901796340942</t>
   </si>
   <si>
     <t xml:space="preserve">7.14484834671021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95785188674927</t>
+    <t xml:space="preserve">6.95785045623779</t>
   </si>
   <si>
     <t xml:space="preserve">6.87993574142456</t>
@@ -2411,76 +2411,76 @@
     <t xml:space="preserve">7.00460004806519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16043138504028</t>
+    <t xml:space="preserve">7.16043090820312</t>
   </si>
   <si>
     <t xml:space="preserve">7.17601442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37859439849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3863844871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13705635070801</t>
+    <t xml:space="preserve">7.37859535217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38638544082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13705587387085</t>
   </si>
   <si>
     <t xml:space="preserve">7.09809875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53710699081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5916485786438</t>
+    <t xml:space="preserve">6.53710889816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59164810180664</t>
   </si>
   <si>
     <t xml:space="preserve">6.57606506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79422855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07472467422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22276401519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28509616851807</t>
+    <t xml:space="preserve">6.79422903060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07472324371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22276496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28509569168091</t>
   </si>
   <si>
     <t xml:space="preserve">7.25392961502075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45650959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65909004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61234188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53442621231079</t>
+    <t xml:space="preserve">7.45651054382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65909099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61234140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53442573547363</t>
   </si>
   <si>
     <t xml:space="preserve">7.49546766281128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57338428497314</t>
+    <t xml:space="preserve">7.57338380813599</t>
   </si>
   <si>
     <t xml:space="preserve">7.47209405899048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50325965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40196895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26172208786011</t>
+    <t xml:space="preserve">7.50325918197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40196847915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26172161102295</t>
   </si>
   <si>
     <t xml:space="preserve">7.30067920684814</t>
@@ -2492,88 +2492,88 @@
     <t xml:space="preserve">7.24613761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51884174346924</t>
+    <t xml:space="preserve">7.51884078979492</t>
   </si>
   <si>
     <t xml:space="preserve">7.91621160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79154586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80712938308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71363067626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77596378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54221773147583</t>
+    <t xml:space="preserve">7.79154682159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80713033676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71363019943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.775963306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54221630096436</t>
   </si>
   <si>
     <t xml:space="preserve">7.23834705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37080383300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43313550949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02529430389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90062808990479</t>
+    <t xml:space="preserve">7.37080335617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43313598632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02529239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9006290435791</t>
   </si>
   <si>
     <t xml:space="preserve">7.86946249008179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72142267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46430110931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73700666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7837553024292</t>
+    <t xml:space="preserve">7.72142171859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46430158615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73700523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78375482559204</t>
   </si>
   <si>
     <t xml:space="preserve">7.65129804611206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58896684646606</t>
+    <t xml:space="preserve">7.58896589279175</t>
   </si>
   <si>
     <t xml:space="preserve">7.68246412277222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72921323776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62013244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39417743682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40975999832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59675645828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74479722976685</t>
+    <t xml:space="preserve">7.72921419143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6201319694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39417791366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40976142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59675788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74479675292969</t>
   </si>
   <si>
     <t xml:space="preserve">8.21228885650635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29020595550537</t>
+    <t xml:space="preserve">8.29020500183105</t>
   </si>
   <si>
     <t xml:space="preserve">8.10320854187012</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">8.02456378936768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96150302886963</t>
+    <t xml:space="preserve">7.96150255203247</t>
   </si>
   <si>
     <t xml:space="preserve">8.15068626403809</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">8.68670845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95471858978271</t>
+    <t xml:space="preserve">8.95471954345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.00201606750488</t>
@@ -2609,25 +2609,25 @@
     <t xml:space="preserve">9.06507682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12813663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20696449279785</t>
+    <t xml:space="preserve">9.12813949584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20696544647217</t>
   </si>
   <si>
     <t xml:space="preserve">9.15966987609863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14390468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93895530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97048473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98625087738037</t>
+    <t xml:space="preserve">9.1439037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93895435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97048377990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98624992370605</t>
   </si>
   <si>
     <t xml:space="preserve">8.8285961151123</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">8.78130054473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63941383361816</t>
+    <t xml:space="preserve">8.63941192626953</t>
   </si>
   <si>
     <t xml:space="preserve">8.51328945159912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65517616271973</t>
+    <t xml:space="preserve">8.65517711639404</t>
   </si>
   <si>
     <t xml:space="preserve">8.73400402069092</t>
@@ -2651,10 +2651,10 @@
     <t xml:space="preserve">8.45022773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37140083312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46599388122559</t>
+    <t xml:space="preserve">8.3714017868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4659948348999</t>
   </si>
   <si>
     <t xml:space="preserve">8.57635116577148</t>
@@ -2669,34 +2669,34 @@
     <t xml:space="preserve">8.07186031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21374702453613</t>
+    <t xml:space="preserve">8.21374893188477</t>
   </si>
   <si>
     <t xml:space="preserve">8.22951316833496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27681064605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24527931213379</t>
+    <t xml:space="preserve">8.2768087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24527835845947</t>
   </si>
   <si>
     <t xml:space="preserve">8.0560941696167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89844083786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94573640823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99303293228149</t>
+    <t xml:space="preserve">7.89844131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94573593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99303245544434</t>
   </si>
   <si>
     <t xml:space="preserve">8.40293216705322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4817590713501</t>
+    <t xml:space="preserve">8.48175811767578</t>
   </si>
   <si>
     <t xml:space="preserve">8.32410621643066</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">8.43446254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70247364044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71823978424072</t>
+    <t xml:space="preserve">8.70247459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71823883056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.7970666885376</t>
@@ -2723,85 +2723,85 @@
     <t xml:space="preserve">8.29257488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26104259490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19798278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.592116355896</t>
+    <t xml:space="preserve">8.26104354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19798183441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59211540222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.60788154602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00879859924316</t>
+    <t xml:space="preserve">8.00879955291748</t>
   </si>
   <si>
     <t xml:space="preserve">7.92997169494629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91420650482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80384826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64619398117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66196155548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85902786254883</t>
+    <t xml:space="preserve">7.84326219558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91420698165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80384922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64619588851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66196060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85902690887451</t>
   </si>
   <si>
     <t xml:space="preserve">7.61466407775879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60678148269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70137500762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78808355331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65407848358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79596614837646</t>
+    <t xml:space="preserve">7.60678100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70137357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78808403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65407800674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79596662521362</t>
   </si>
   <si>
     <t xml:space="preserve">7.56736898422241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62254810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67772674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50430727005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63831233978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74867010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76443529129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82749795913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67094230651855</t>
+    <t xml:space="preserve">7.6225471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67772626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50430679321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63831281661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74867105484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76443576812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82749652862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67094421386719</t>
   </si>
   <si>
     <t xml:space="preserve">8.62364673614502</t>
@@ -2810,43 +2810,43 @@
     <t xml:space="preserve">8.74977016448975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55948686599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54372024536133</t>
+    <t xml:space="preserve">7.55948638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54372072219849</t>
   </si>
   <si>
     <t xml:space="preserve">7.25206136703491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28359222412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27570915222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8579273223877</t>
+    <t xml:space="preserve">7.28359127044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27570867538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85792827606201</t>
   </si>
   <si>
     <t xml:space="preserve">6.9131064414978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82639741897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08652496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99981641769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93675565719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37030172348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23629570007324</t>
+    <t xml:space="preserve">6.82639646530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08652591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99981546401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93675470352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37030124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23629665374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.21264791488647</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">7.1259388923645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03134536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14958667755127</t>
+    <t xml:space="preserve">7.03134632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14958620071411</t>
   </si>
   <si>
     <t xml:space="preserve">7.09440803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13382005691528</t>
+    <t xml:space="preserve">7.13382148742676</t>
   </si>
   <si>
     <t xml:space="preserve">7.33877086639404</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">7.38606691360474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47277498245239</t>
+    <t xml:space="preserve">7.47277688980103</t>
   </si>
   <si>
     <t xml:space="preserve">7.86691045761108</t>
@@ -2882,31 +2882,31 @@
     <t xml:space="preserve">7.78020095825195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7407865524292</t>
+    <t xml:space="preserve">7.74078750610352</t>
   </si>
   <si>
     <t xml:space="preserve">7.46489381790161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52795505523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68560743331909</t>
+    <t xml:space="preserve">7.52795553207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68560886383057</t>
   </si>
   <si>
     <t xml:space="preserve">7.58313369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48854160308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45701217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37818431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35453605651855</t>
+    <t xml:space="preserve">7.48854112625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45701169967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37818384170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35453701019287</t>
   </si>
   <si>
     <t xml:space="preserve">7.11805582046509</t>
@@ -2915,46 +2915,46 @@
     <t xml:space="preserve">6.99193286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34665441513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1732349395752</t>
+    <t xml:space="preserve">7.34665393829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17323446273804</t>
   </si>
   <si>
     <t xml:space="preserve">7.29147434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36241960525513</t>
+    <t xml:space="preserve">7.36241865158081</t>
   </si>
   <si>
     <t xml:space="preserve">7.19688272476196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10229206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44124460220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33088779449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4097146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49642372131348</t>
+    <t xml:space="preserve">7.10229158401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44124507904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33088827133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40971565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49642419815063</t>
   </si>
   <si>
     <t xml:space="preserve">7.39394903182983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26782751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15746974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61356449127197</t>
+    <t xml:space="preserve">7.26782703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15746879577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61356592178345</t>
   </si>
   <si>
     <t xml:space="preserve">6.44014596939087</t>
@@ -2963,16 +2963,16 @@
     <t xml:space="preserve">6.60568237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.810631275177</t>
+    <t xml:space="preserve">6.81063222885132</t>
   </si>
   <si>
     <t xml:space="preserve">6.98405027389526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18111753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18899965286255</t>
+    <t xml:space="preserve">7.18111705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18900156021118</t>
   </si>
   <si>
     <t xml:space="preserve">7.06287717819214</t>
@@ -2981,85 +2981,85 @@
     <t xml:space="preserve">7.11017322540283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20476675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88267517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81173181533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75655364990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73290538787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42548036575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48065900802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51218938827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52007246017456</t>
+    <t xml:space="preserve">7.20476579666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88267612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81173133850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69349193572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75655269622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7329044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42548084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48065948486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5121898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52007293701172</t>
   </si>
   <si>
     <t xml:space="preserve">7.22841358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40183305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00769901275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44912910461426</t>
+    <t xml:space="preserve">7.40183210372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00769853591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44912767410278</t>
   </si>
   <si>
     <t xml:space="preserve">7.41542530059814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31838512420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29412698745728</t>
+    <t xml:space="preserve">7.31838655471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29412603378296</t>
   </si>
   <si>
     <t xml:space="preserve">7.48011827468872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56098461151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63376331329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5448112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4396858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48820495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46394538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32647371292114</t>
+    <t xml:space="preserve">7.56098413467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63376379013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54481172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43968534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.488205909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46394348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32647323608398</t>
   </si>
   <si>
     <t xml:space="preserve">7.05152797698975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83318948745728</t>
+    <t xml:space="preserve">6.83318853378296</t>
   </si>
   <si>
     <t xml:space="preserve">6.94640207290649</t>
@@ -3068,37 +3068,37 @@
     <t xml:space="preserve">6.76040983200073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75232267379761</t>
+    <t xml:space="preserve">6.75232315063477</t>
   </si>
   <si>
     <t xml:space="preserve">6.71189022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86553573608398</t>
+    <t xml:space="preserve">6.86553621292114</t>
   </si>
   <si>
     <t xml:space="preserve">6.73615026473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74423694610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81701564788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87362241744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80084276199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71997737884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63102436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70380258560181</t>
+    <t xml:space="preserve">6.74423599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8170166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87362146377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80084228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7199764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63102340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70380306243896</t>
   </si>
   <si>
     <t xml:space="preserve">6.46929121017456</t>
@@ -3110,118 +3110,118 @@
     <t xml:space="preserve">6.57441806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.695716381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64719724655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63911008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55015802383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60676383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62293720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47737789154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4045991897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41268491744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65528392791748</t>
+    <t xml:space="preserve">6.69571733474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64719820022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63911056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55015754699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60676431655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6229362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47737884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40459871292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41268539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65528345108032</t>
   </si>
   <si>
     <t xml:space="preserve">6.84127569198608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72806310653687</t>
+    <t xml:space="preserve">6.72806358337402</t>
   </si>
   <si>
     <t xml:space="preserve">6.67145681381226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76849603652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50163841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46120500564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4935507774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44503211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38842535018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29138708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11348056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19434642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08922100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13774061203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95174884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95983505249023</t>
+    <t xml:space="preserve">6.7684965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50163745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46120405197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49355125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44503164291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38842630386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29138565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11348009109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19434690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08922052383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13774108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95174837112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95983457565308</t>
   </si>
   <si>
     <t xml:space="preserve">5.98409461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90322875976562</t>
+    <t xml:space="preserve">5.90322923660278</t>
   </si>
   <si>
     <t xml:space="preserve">6.06496095657349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18626022338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02452802658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91131544113159</t>
+    <t xml:space="preserve">6.18626070022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02452754974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91131496429443</t>
   </si>
   <si>
     <t xml:space="preserve">5.86279535293579</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88705539703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83044862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81427574157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63637018203735</t>
+    <t xml:space="preserve">5.88705587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001569747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83044910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81427621841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6363697052002</t>
   </si>
   <si>
     <t xml:space="preserve">5.70914936065674</t>
@@ -3230,37 +3230,37 @@
     <t xml:space="preserve">5.74958276748657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73340940475464</t>
+    <t xml:space="preserve">5.73341035842896</t>
   </si>
   <si>
     <t xml:space="preserve">5.67680311203003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78192901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74149656295776</t>
+    <t xml:space="preserve">5.78192949295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74149560928345</t>
   </si>
   <si>
     <t xml:space="preserve">5.62828397750854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45846509933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39377164840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33716487884521</t>
+    <t xml:space="preserve">5.45846462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39377212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33716583251953</t>
   </si>
   <si>
     <t xml:space="preserve">5.38568496704102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36142492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42611837387085</t>
+    <t xml:space="preserve">5.36142539978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42611885070801</t>
   </si>
   <si>
     <t xml:space="preserve">5.43420457839966</t>
@@ -3269,43 +3269,43 @@
     <t xml:space="preserve">5.28055953979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26438570022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34525299072266</t>
+    <t xml:space="preserve">5.26438617706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3452525138855</t>
   </si>
   <si>
     <t xml:space="preserve">5.40994501113892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35333919525146</t>
+    <t xml:space="preserve">5.35333824157715</t>
   </si>
   <si>
     <t xml:space="preserve">5.57976388931274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82236289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68489074707031</t>
+    <t xml:space="preserve">5.82236242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68489027023315</t>
   </si>
   <si>
     <t xml:space="preserve">5.79810333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.555504322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93557548522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75766944885254</t>
+    <t xml:space="preserve">5.55550384521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93557500839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7576699256897</t>
   </si>
   <si>
     <t xml:space="preserve">5.66063022613525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61211109161377</t>
+    <t xml:space="preserve">5.61211061477661</t>
   </si>
   <si>
     <t xml:space="preserve">5.65254306793213</t>
@@ -3317,28 +3317,28 @@
     <t xml:space="preserve">5.51507139205933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53124475479126</t>
+    <t xml:space="preserve">5.5312442779541</t>
   </si>
   <si>
     <t xml:space="preserve">5.50698471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64445686340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52315759658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70106363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57167720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46655178070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60402297973633</t>
+    <t xml:space="preserve">5.64445734024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52315711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70106315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57167673110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46655130386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60402393341064</t>
   </si>
   <si>
     <t xml:space="preserve">5.49081087112427</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">5.44229173660278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53933095932007</t>
+    <t xml:space="preserve">5.53933048248291</t>
   </si>
   <si>
     <t xml:space="preserve">5.76575613021851</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">5.66871690750122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96792125701904</t>
+    <t xml:space="preserve">5.96792221069336</t>
   </si>
   <si>
     <t xml:space="preserve">6.14582681655884</t>
@@ -3371,16 +3371,16 @@
     <t xml:space="preserve">6.17817354202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21860694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03261423110962</t>
+    <t xml:space="preserve">6.21860647201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03261470794678</t>
   </si>
   <si>
     <t xml:space="preserve">5.97600793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01644086837769</t>
+    <t xml:space="preserve">6.016441822052</t>
   </si>
   <si>
     <t xml:space="preserve">5.94366121292114</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">5.80618858337402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87896871566772</t>
+    <t xml:space="preserve">5.87896823883057</t>
   </si>
   <si>
     <t xml:space="preserve">5.85470867156982</t>
@@ -3398,22 +3398,22 @@
     <t xml:space="preserve">6.1215672492981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09730672836304</t>
+    <t xml:space="preserve">6.0973072052002</t>
   </si>
   <si>
     <t xml:space="preserve">6.16200017929077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07304763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08113431930542</t>
+    <t xml:space="preserve">6.07304811477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08113384246826</t>
   </si>
   <si>
     <t xml:space="preserve">6.05687427520752</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04070043563843</t>
+    <t xml:space="preserve">6.04070091247559</t>
   </si>
   <si>
     <t xml:space="preserve">6.10539436340332</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">6.04878759384155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72532320022583</t>
+    <t xml:space="preserve">5.72532272338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.59593725204468</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">5.58785057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3075590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84662294387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83853530883789</t>
+    <t xml:space="preserve">6.30755996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84662246704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83853578567505</t>
   </si>
   <si>
     <t xml:space="preserve">6.00835466384888</t>
@@ -3452,16 +3452,16 @@
     <t xml:space="preserve">6.2046685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01565265655518</t>
+    <t xml:space="preserve">6.01565217971802</t>
   </si>
   <si>
     <t xml:space="preserve">6.29506778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49230194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47586584091187</t>
+    <t xml:space="preserve">6.49230241775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47586631774902</t>
   </si>
   <si>
     <t xml:space="preserve">6.46764802932739</t>
@@ -3473,34 +3473,34 @@
     <t xml:space="preserve">6.59913730621338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58270120620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5169563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45121192932129</t>
+    <t xml:space="preserve">6.58270215988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51695680618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45121145248413</t>
   </si>
   <si>
     <t xml:space="preserve">6.42655754089355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41012144088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36903095245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33615827560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52517509460449</t>
+    <t xml:space="preserve">6.41012191772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36903047561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33615779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52517461776733</t>
   </si>
   <si>
     <t xml:space="preserve">6.57448291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45942974090576</t>
+    <t xml:space="preserve">6.45943021774292</t>
   </si>
   <si>
     <t xml:space="preserve">6.54982852935791</t>
@@ -3515,16 +3515,16 @@
     <t xml:space="preserve">6.41833877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43477487564087</t>
+    <t xml:space="preserve">6.43477535247803</t>
   </si>
   <si>
     <t xml:space="preserve">6.36081218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34437608718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1142692565918</t>
+    <t xml:space="preserve">6.34437656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11426973342896</t>
   </si>
   <si>
     <t xml:space="preserve">6.13070583343506</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">6.13892364501953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25397682189941</t>
+    <t xml:space="preserve">6.25397729873657</t>
   </si>
   <si>
     <t xml:space="preserve">6.26219511032104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31972217559814</t>
+    <t xml:space="preserve">6.31972169876099</t>
   </si>
   <si>
     <t xml:space="preserve">6.35259437561035</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">6.37724876403809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4840841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56626510620117</t>
+    <t xml:space="preserve">6.48408365249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56626462936401</t>
   </si>
   <si>
     <t xml:space="preserve">6.64022827148438</t>
@@ -3569,10 +3569,10 @@
     <t xml:space="preserve">6.59091949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5580472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80458974838257</t>
+    <t xml:space="preserve">6.55804681777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80459022521973</t>
   </si>
   <si>
     <t xml:space="preserve">6.8867712020874</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">6.83746242523193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69775438308716</t>
+    <t xml:space="preserve">6.69775485992432</t>
   </si>
   <si>
     <t xml:space="preserve">6.61557388305664</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">6.62379217147827</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8292441368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94429779052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87855339050293</t>
+    <t xml:space="preserve">6.82924461364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94429731369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87855291366577</t>
   </si>
   <si>
     <t xml:space="preserve">6.77993535995483</t>
@@ -3611,37 +3611,37 @@
     <t xml:space="preserve">6.79637241363525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90320682525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84568023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8538990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72240877151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68131875991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.689537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27863168716431</t>
+    <t xml:space="preserve">6.90320634841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84568071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85389852523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72240972518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68131923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68953657150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27863121032715</t>
   </si>
   <si>
     <t xml:space="preserve">6.08961486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07317876815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04852390289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15535926818848</t>
+    <t xml:space="preserve">6.0731782913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04852437973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15535974502563</t>
   </si>
   <si>
     <t xml:space="preserve">5.99921655654907</t>
@@ -3650,13 +3650,13 @@
     <t xml:space="preserve">5.94168949127197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05674314498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95812559127808</t>
+    <t xml:space="preserve">6.05674266815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8759446144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95812511444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.08139705657959</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">5.8923807144165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85128974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90881681442261</t>
+    <t xml:space="preserve">5.85129022598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90881729125977</t>
   </si>
   <si>
     <t xml:space="preserve">5.78554487228394</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">5.75267314910889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64583730697632</t>
+    <t xml:space="preserve">5.64583683013916</t>
   </si>
   <si>
     <t xml:space="preserve">5.71158218383789</t>
@@ -3692,16 +3692,16 @@
     <t xml:space="preserve">5.82663631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86772584915161</t>
+    <t xml:space="preserve">5.86772632598877</t>
   </si>
   <si>
     <t xml:space="preserve">6.188232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12248706817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14714193344116</t>
+    <t xml:space="preserve">6.12248754501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.147141456604</t>
   </si>
   <si>
     <t xml:space="preserve">6.28684997558594</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">6.76349925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66488122940063</t>
+    <t xml:space="preserve">6.66488218307495</t>
   </si>
   <si>
     <t xml:space="preserve">6.738844871521</t>
@@ -3725,43 +3725,43 @@
     <t xml:space="preserve">6.93607950210571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99360704421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06756973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.240149974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331460952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98538827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12509632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07578754425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16618633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14975023269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19084119796753</t>
+    <t xml:space="preserve">6.99360656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06757020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24015045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331413269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98538780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1250958442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07578706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16618680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14975070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19084072113037</t>
   </si>
   <si>
     <t xml:space="preserve">7.1826229095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28123903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21549558639526</t>
+    <t xml:space="preserve">7.28123950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21549510955811</t>
   </si>
   <si>
     <t xml:space="preserve">7.17440414428711</t>
@@ -3776,61 +3776,61 @@
     <t xml:space="preserve">7.05113315582275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03469753265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34698486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48669195175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36342144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35520267486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28945827484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37163925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57709169387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73323535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94690704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88937950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02087020874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78496122360229</t>
+    <t xml:space="preserve">7.03469657897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34698438644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48669242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36342096328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35520315170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28945779800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3716402053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57709217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73323631286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94690656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88937997817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02086925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78496170043945</t>
   </si>
   <si>
     <t xml:space="preserve">7.62768888473511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63642692565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52284145355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43546867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28693437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37430667877197</t>
+    <t xml:space="preserve">7.63642740249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52284097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4354681968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28693342208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37430715560913</t>
   </si>
   <si>
     <t xml:space="preserve">7.27819633483887</t>
@@ -3839,61 +3839,61 @@
     <t xml:space="preserve">7.25198459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29567193984985</t>
+    <t xml:space="preserve">7.29567098617554</t>
   </si>
   <si>
     <t xml:space="preserve">7.42673063278198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30440855026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40925598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33062028884888</t>
+    <t xml:space="preserve">7.30440807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40925645828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33062124252319</t>
   </si>
   <si>
     <t xml:space="preserve">7.44420576095581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45294284820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49662971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54031658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64516448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51410436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41799306869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46168041229248</t>
+    <t xml:space="preserve">7.45294332504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49663019180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54031610488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64516496658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51410531997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41799402236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46168088912964</t>
   </si>
   <si>
     <t xml:space="preserve">7.531578540802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40051937103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48789215087891</t>
+    <t xml:space="preserve">7.40051889419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48789167404175</t>
   </si>
   <si>
     <t xml:space="preserve">7.39178133010864</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47041845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34809541702271</t>
+    <t xml:space="preserve">7.47041749954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34809494018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.94617795944214</t>
@@ -3902,10 +3902,10 @@
     <t xml:space="preserve">6.90249156951904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80638027191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8675422668457</t>
+    <t xml:space="preserve">6.80638074874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86754179000854</t>
   </si>
   <si>
     <t xml:space="preserve">6.91996622085571</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">6.70153284072876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89375352859497</t>
+    <t xml:space="preserve">6.89375400543213</t>
   </si>
   <si>
     <t xml:space="preserve">6.85006761550903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05102586746216</t>
+    <t xml:space="preserve">7.05102491378784</t>
   </si>
   <si>
     <t xml:space="preserve">7.16461086273193</t>
@@ -3935,10 +3935,10 @@
     <t xml:space="preserve">7.18208646774292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33935737609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17334842681885</t>
+    <t xml:space="preserve">7.33935689926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17334890365601</t>
   </si>
   <si>
     <t xml:space="preserve">7.20829772949219</t>
@@ -3947,46 +3947,46 @@
     <t xml:space="preserve">7.32188320159912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66263961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68885135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68011331558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75874996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83738565444946</t>
+    <t xml:space="preserve">7.66263914108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68885183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68011379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75874948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83738613128662</t>
   </si>
   <si>
     <t xml:space="preserve">7.69758892059326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67137670516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81117343902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76748752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70632553100586</t>
+    <t xml:space="preserve">7.67137575149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81117296218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76748657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7063250541687</t>
   </si>
   <si>
     <t xml:space="preserve">7.92475938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89854621887207</t>
+    <t xml:space="preserve">7.89854669570923</t>
   </si>
   <si>
     <t xml:space="preserve">7.80114364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5709171295166</t>
+    <t xml:space="preserve">7.57091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">7.87198257446289</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">8.09335422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13762760162354</t>
+    <t xml:space="preserve">8.13762855529785</t>
   </si>
   <si>
     <t xml:space="preserve">8.25274181365967</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">8.05793476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95167636871338</t>
+    <t xml:space="preserve">7.95167541503906</t>
   </si>
   <si>
     <t xml:space="preserve">7.98709583282471</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">7.86312770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97824096679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65946531295776</t>
+    <t xml:space="preserve">7.97824001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65946483612061</t>
   </si>
   <si>
     <t xml:space="preserve">7.6151909828186</t>
@@ -4040,22 +4040,22 @@
     <t xml:space="preserve">7.70373916625977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51778650283813</t>
+    <t xml:space="preserve">7.51778745651245</t>
   </si>
   <si>
     <t xml:space="preserve">7.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6417555809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72144937515259</t>
+    <t xml:space="preserve">7.64175605773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7214503288269</t>
   </si>
   <si>
     <t xml:space="preserve">7.60633563995361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48236799240112</t>
+    <t xml:space="preserve">7.48236703872681</t>
   </si>
   <si>
     <t xml:space="preserve">7.52664184570312</t>
@@ -4070,10 +4070,10 @@
     <t xml:space="preserve">7.4912223815918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43809270858765</t>
+    <t xml:space="preserve">7.58862638473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43809223175049</t>
   </si>
   <si>
     <t xml:space="preserve">7.47351264953613</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">7.75686883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84541654586792</t>
+    <t xml:space="preserve">7.84541749954224</t>
   </si>
   <si>
     <t xml:space="preserve">7.74801397323608</t>
@@ -4100,22 +4100,19 @@
     <t xml:space="preserve">7.99595022201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85427236557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89854717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53549718856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33183431625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66831922531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76572418212891</t>
+    <t xml:space="preserve">7.85427188873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53549671173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33183479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6683201789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76572465896606</t>
   </si>
   <si>
     <t xml:space="preserve">7.90740156173706</t>
@@ -4124,7 +4121,7 @@
     <t xml:space="preserve">7.83656358718872</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07564449310303</t>
+    <t xml:space="preserve">8.07564353942871</t>
   </si>
   <si>
     <t xml:space="preserve">8.02251529693604</t>
@@ -4136,7 +4133,7 @@
     <t xml:space="preserve">8.235032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10220909118652</t>
+    <t xml:space="preserve">8.10220813751221</t>
   </si>
   <si>
     <t xml:space="preserve">7.92511129379272</t>
@@ -4169,16 +4166,16 @@
     <t xml:space="preserve">8.22617721557617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19075775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56266307830811</t>
+    <t xml:space="preserve">8.19075679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56266212463379</t>
   </si>
   <si>
     <t xml:space="preserve">8.66892147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68663120269775</t>
+    <t xml:space="preserve">8.68663024902344</t>
   </si>
   <si>
     <t xml:space="preserve">8.76632404327393</t>
@@ -4190,22 +4187,22 @@
     <t xml:space="preserve">9.1736478805542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03197002410889</t>
+    <t xml:space="preserve">9.0319709777832</t>
   </si>
   <si>
     <t xml:space="preserve">9.04968070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13822937011719</t>
+    <t xml:space="preserve">9.13822841644287</t>
   </si>
   <si>
     <t xml:space="preserve">8.92571258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97884178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84601879119873</t>
+    <t xml:space="preserve">8.97884082794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84601783752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.90800189971924</t>
@@ -4217,10 +4214,10 @@
     <t xml:space="preserve">8.81059837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78403472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79288864135742</t>
+    <t xml:space="preserve">8.78403377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79288959503174</t>
   </si>
   <si>
     <t xml:space="preserve">8.74861526489258</t>
@@ -4229,13 +4226,13 @@
     <t xml:space="preserve">8.80174350738525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83716297149658</t>
+    <t xml:space="preserve">8.8371639251709</t>
   </si>
   <si>
     <t xml:space="preserve">8.99655055999756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39441967010498</t>
+    <t xml:space="preserve">8.39441871643066</t>
   </si>
   <si>
     <t xml:space="preserve">8.62464618682861</t>
@@ -4244,16 +4241,16 @@
     <t xml:space="preserve">8.59808158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61579036712646</t>
+    <t xml:space="preserve">8.61579132080078</t>
   </si>
   <si>
     <t xml:space="preserve">8.51838779449463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50067806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4032735824585</t>
+    <t xml:space="preserve">8.50067901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40327453613281</t>
   </si>
   <si>
     <t xml:space="preserve">8.43869304656982</t>
@@ -4274,10 +4271,10 @@
     <t xml:space="preserve">9.01426124572754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08509922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20906734466553</t>
+    <t xml:space="preserve">9.0851001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20906829833984</t>
   </si>
   <si>
     <t xml:space="preserve">9.29761695861816</t>
@@ -4301,7 +4298,7 @@
     <t xml:space="preserve">8.85487270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67777538299561</t>
+    <t xml:space="preserve">8.67777633666992</t>
   </si>
   <si>
     <t xml:space="preserve">8.77517890930176</t>
@@ -4319,7 +4316,7 @@
     <t xml:space="preserve">8.73976039886475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72205066680908</t>
+    <t xml:space="preserve">8.72204971313477</t>
   </si>
   <si>
     <t xml:space="preserve">8.53609752655029</t>
@@ -4331,7 +4328,7 @@
     <t xml:space="preserve">8.4564037322998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42984008789062</t>
+    <t xml:space="preserve">8.42983913421631</t>
   </si>
   <si>
     <t xml:space="preserve">8.41212940216064</t>
@@ -4340,7 +4337,7 @@
     <t xml:space="preserve">8.49182319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26219749450684</t>
+    <t xml:space="preserve">9.26219654083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.12051963806152</t>
@@ -4358,7 +4355,7 @@
     <t xml:space="preserve">9.61639213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63410186767578</t>
+    <t xml:space="preserve">9.63410091400146</t>
   </si>
   <si>
     <t xml:space="preserve">9.66952228546143</t>
@@ -4367,7 +4364,7 @@
     <t xml:space="preserve">10.006007194519</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0237169265747</t>
+    <t xml:space="preserve">10.0237159729004</t>
   </si>
   <si>
     <t xml:space="preserve">9.95287704467773</t>
@@ -4379,13 +4376,13 @@
     <t xml:space="preserve">9.8289098739624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75807094573975</t>
+    <t xml:space="preserve">9.75806999206543</t>
   </si>
   <si>
     <t xml:space="preserve">9.3684549331665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31532764434814</t>
+    <t xml:space="preserve">9.31532669067383</t>
   </si>
   <si>
     <t xml:space="preserve">9.56326293945312</t>
@@ -4400,7 +4397,7 @@
     <t xml:space="preserve">10.112265586853</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97058773040771</t>
+    <t xml:space="preserve">9.9705867767334</t>
   </si>
   <si>
     <t xml:space="preserve">10.1653938293457</t>
@@ -4424,7 +4421,7 @@
     <t xml:space="preserve">10.253942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3424921035767</t>
+    <t xml:space="preserve">10.3424911499023</t>
   </si>
   <si>
     <t xml:space="preserve">9.58115100860596</t>
@@ -4764,6 +4761,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.93000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2200002670288</t>
   </si>
 </sst>
 </file>
@@ -61878,7 +61878,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2184" t="s">
-        <v>1363</v>
+        <v>1322</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61904,7 +61904,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2185" t="s">
-        <v>1363</v>
+        <v>1322</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61956,7 +61956,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2187" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61982,7 +61982,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2188" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62034,7 +62034,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2190" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62086,7 +62086,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2192" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62190,7 +62190,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2196" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62216,7 +62216,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2197" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62242,7 +62242,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2198" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62320,7 +62320,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2201" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62346,7 +62346,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2202" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62450,7 +62450,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2206" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62476,7 +62476,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2207" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62528,7 +62528,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2209" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62554,7 +62554,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2210" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62606,7 +62606,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2212" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62684,7 +62684,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2215" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62710,7 +62710,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2216" t="s">
-        <v>1363</v>
+        <v>1322</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62736,7 +62736,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2217" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62762,7 +62762,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2218" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62788,7 +62788,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2219" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62814,7 +62814,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2220" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62866,7 +62866,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G2222" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62892,7 +62892,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2223" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62918,7 +62918,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2224" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62944,7 +62944,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2225" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62970,7 +62970,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2226" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62996,7 +62996,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G2227" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63022,7 +63022,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63048,7 +63048,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G2229" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63074,7 +63074,7 @@
         <v>9.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63100,7 +63100,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2231" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63126,7 +63126,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G2232" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63152,7 +63152,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2233" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63178,7 +63178,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2234" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63204,7 +63204,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2235" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63230,7 +63230,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2236" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63256,7 +63256,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63282,7 +63282,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63308,7 +63308,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2239" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63334,7 +63334,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2240" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63360,7 +63360,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2241" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63386,7 +63386,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2242" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63412,7 +63412,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2243" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63438,7 +63438,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2244" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63464,7 +63464,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2245" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63490,7 +63490,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G2246" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63516,7 +63516,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2247" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63542,7 +63542,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G2248" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63568,7 +63568,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2249" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63594,7 +63594,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2250" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63620,7 +63620,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2251" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63646,7 +63646,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2252" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63672,7 +63672,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2253" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63698,7 +63698,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2254" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63724,7 +63724,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2255" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63750,7 +63750,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2256" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63776,7 +63776,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2257" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63802,7 +63802,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2258" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63828,7 +63828,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2259" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63854,7 +63854,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2260" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63880,7 +63880,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63906,7 +63906,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2262" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63932,7 +63932,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2263" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63958,7 +63958,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2264" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63984,7 +63984,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2265" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64010,7 +64010,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2266" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64036,7 +64036,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2267" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64062,7 +64062,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64088,7 +64088,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2269" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64114,7 +64114,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2270" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64140,7 +64140,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2271" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64166,7 +64166,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2272" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64192,7 +64192,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2273" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64218,7 +64218,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2274" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64244,7 +64244,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2275" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64270,7 +64270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2276" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64296,7 +64296,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2277" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64322,7 +64322,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64348,7 +64348,7 @@
         <v>10.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64374,7 +64374,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64400,7 +64400,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64426,7 +64426,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2282" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64452,7 +64452,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2283" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64478,7 +64478,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2284" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64504,7 +64504,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2285" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64530,7 +64530,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2286" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64556,7 +64556,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2287" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64582,7 +64582,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2288" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64608,7 +64608,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64634,7 +64634,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2290" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64660,7 +64660,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64686,7 +64686,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2292" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64712,7 +64712,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64738,7 +64738,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2294" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64764,7 +64764,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64790,7 +64790,7 @@
         <v>10</v>
       </c>
       <c r="G2296" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64816,7 +64816,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2297" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64842,7 +64842,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2298" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64868,7 +64868,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2299" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64894,7 +64894,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2300" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64920,7 +64920,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2301" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64946,7 +64946,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2302" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64972,7 +64972,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2303" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64998,7 +64998,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2304" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65024,7 +65024,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2305" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65050,7 +65050,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2306" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65076,7 +65076,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2307" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65102,7 +65102,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2308" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65128,7 +65128,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65154,7 +65154,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2310" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65180,7 +65180,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2311" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65206,7 +65206,7 @@
         <v>9.5</v>
       </c>
       <c r="G2312" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65232,7 +65232,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2313" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65258,7 +65258,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2314" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65284,7 +65284,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2315" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65310,7 +65310,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2316" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65336,7 +65336,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2317" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65362,7 +65362,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65388,7 +65388,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2319" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65414,7 +65414,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2320" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65440,7 +65440,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2321" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65466,7 +65466,7 @@
         <v>10.5</v>
       </c>
       <c r="G2322" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65492,7 +65492,7 @@
         <v>10.5</v>
       </c>
       <c r="G2323" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65518,7 +65518,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2324" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65544,7 +65544,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2325" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65570,7 +65570,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2326" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65596,7 +65596,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2327" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65622,7 +65622,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2328" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65648,7 +65648,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2329" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65674,7 +65674,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2330" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65700,7 +65700,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2331" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65726,7 +65726,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2332" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65752,7 +65752,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2333" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65778,7 +65778,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2334" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65804,7 +65804,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2335" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65830,7 +65830,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2336" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65856,7 +65856,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G2337" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65882,7 +65882,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2338" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65908,7 +65908,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2339" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65934,7 +65934,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2340" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65960,7 +65960,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2341" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65986,7 +65986,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2342" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66012,7 +66012,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2343" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66038,7 +66038,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2344" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66064,7 +66064,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66090,7 +66090,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2346" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66116,7 +66116,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2347" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66142,7 +66142,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2348" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66168,7 +66168,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2349" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66194,7 +66194,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66220,7 +66220,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2351" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66246,7 +66246,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2352" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66272,7 +66272,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2353" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66298,7 +66298,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2354" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66324,7 +66324,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66350,7 +66350,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66376,7 +66376,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2357" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66402,7 +66402,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2358" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66428,7 +66428,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66454,7 +66454,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2360" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66480,7 +66480,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2361" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66506,7 +66506,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2362" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66532,7 +66532,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2363" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66558,7 +66558,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66584,7 +66584,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2365" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66610,7 +66610,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2366" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66636,7 +66636,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66662,7 +66662,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66688,7 +66688,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2369" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66714,7 +66714,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2370" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66740,7 +66740,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2371" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66766,7 +66766,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2372" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66792,7 +66792,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2373" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66818,7 +66818,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2374" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66844,7 +66844,7 @@
         <v>11.5</v>
       </c>
       <c r="G2375" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66870,7 +66870,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2376" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66896,7 +66896,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2377" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66922,7 +66922,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2378" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66948,7 +66948,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2379" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66974,7 +66974,7 @@
         <v>11.5</v>
       </c>
       <c r="G2380" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67000,7 +67000,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2381" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67026,7 +67026,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2382" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67052,7 +67052,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2383" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67078,7 +67078,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2384" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67104,7 +67104,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2385" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67130,7 +67130,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2386" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67156,7 +67156,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2387" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67182,7 +67182,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2388" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67208,7 +67208,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2389" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67234,7 +67234,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2390" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67260,7 +67260,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2391" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67286,7 +67286,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G2392" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67312,7 +67312,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2393" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67338,7 +67338,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2394" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67364,7 +67364,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G2395" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67390,7 +67390,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2396" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67416,7 +67416,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2397" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67442,7 +67442,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2398" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67468,7 +67468,7 @@
         <v>9.75</v>
       </c>
       <c r="G2399" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67494,7 +67494,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2400" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67520,7 +67520,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67546,7 +67546,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2402" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67572,7 +67572,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2403" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67598,7 +67598,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2404" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67624,7 +67624,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67650,7 +67650,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2406" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67676,7 +67676,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2407" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67702,7 +67702,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2408" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67728,7 +67728,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2409" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67754,7 +67754,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2410" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67780,7 +67780,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2411" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67806,7 +67806,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2412" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67832,7 +67832,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2413" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67858,7 +67858,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2414" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67884,7 +67884,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2415" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67910,7 +67910,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2416" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67936,7 +67936,7 @@
         <v>9.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67962,7 +67962,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2418" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67988,7 +67988,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2419" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68014,7 +68014,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2420" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68040,7 +68040,7 @@
         <v>9.75</v>
       </c>
       <c r="G2421" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68066,7 +68066,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G2422" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68092,7 +68092,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2423" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68118,7 +68118,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2424" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68144,7 +68144,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2425" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68170,7 +68170,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2426" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68196,7 +68196,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2427" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68222,7 +68222,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68248,7 +68248,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G2429" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68274,7 +68274,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2430" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68300,7 +68300,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2431" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68326,7 +68326,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2432" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68352,7 +68352,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2433" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68378,7 +68378,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2434" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68404,7 +68404,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2435" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68430,7 +68430,7 @@
         <v>8.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68456,7 +68456,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2437" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68482,7 +68482,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68508,7 +68508,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68534,7 +68534,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2440" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68560,7 +68560,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2441" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68586,7 +68586,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2442" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68612,7 +68612,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68638,7 +68638,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68664,7 +68664,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2445" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68690,7 +68690,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2446" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68716,7 +68716,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2447" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68742,7 +68742,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2448" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68768,7 +68768,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2449" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68794,7 +68794,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2450" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68820,7 +68820,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2451" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68846,7 +68846,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2452" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68872,7 +68872,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2453" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68898,7 +68898,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2454" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68924,7 +68924,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2455" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68950,7 +68950,7 @@
         <v>8.75</v>
       </c>
       <c r="G2456" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68976,7 +68976,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2457" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69002,7 +69002,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2458" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69028,7 +69028,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69054,7 +69054,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2460" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69080,7 +69080,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2461" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69106,7 +69106,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2462" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69132,7 +69132,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2463" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69158,7 +69158,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2464" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69184,7 +69184,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2465" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69210,7 +69210,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G2466" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69236,7 +69236,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69262,7 +69262,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69288,7 +69288,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69314,7 +69314,7 @@
         <v>9</v>
       </c>
       <c r="G2470" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69340,7 +69340,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2471" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69366,7 +69366,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2472" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69392,7 +69392,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2473" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69418,7 +69418,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2474" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69444,7 +69444,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2475" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69470,7 +69470,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69496,7 +69496,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2477" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69522,7 +69522,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69548,7 +69548,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2479" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69574,7 +69574,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2480" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69600,7 +69600,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2481" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69626,7 +69626,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2482" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69652,7 +69652,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2483" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69678,7 +69678,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2484" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69704,7 +69704,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2485" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69730,7 +69730,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2486" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69756,7 +69756,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2487" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69782,7 +69782,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2488" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69808,7 +69808,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2489" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69834,7 +69834,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2490" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69860,7 +69860,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2491" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69886,7 +69886,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2492" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69912,7 +69912,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2493" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69938,7 +69938,7 @@
         <v>9.75</v>
       </c>
       <c r="G2494" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69964,7 +69964,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2495" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69990,7 +69990,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2496" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70016,7 +70016,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2497" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70042,7 +70042,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2498" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70068,7 +70068,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2499" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70094,7 +70094,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2500" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70120,7 +70120,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2501" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70146,7 +70146,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2502" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70172,7 +70172,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2503" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70198,7 +70198,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2504" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70224,7 +70224,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G2505" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -70250,7 +70250,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2506" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -70276,7 +70276,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2507" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70302,7 +70302,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2508" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -70328,7 +70328,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2509" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -70354,7 +70354,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -70380,7 +70380,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2511" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -70406,7 +70406,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2512" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70432,7 +70432,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2513" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70458,7 +70458,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2514" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70484,7 +70484,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2515" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70510,7 +70510,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2516" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70536,7 +70536,7 @@
         <v>9.25</v>
       </c>
       <c r="G2517" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70562,7 +70562,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2518" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70588,7 +70588,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2519" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70614,7 +70614,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2520" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70640,7 +70640,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2521" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70666,7 +70666,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2522" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70692,7 +70692,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2523" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70718,7 +70718,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2524" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -70744,7 +70744,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2525" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -70770,7 +70770,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2526" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -70796,7 +70796,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2527" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -70822,7 +70822,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2528" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -70848,7 +70848,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2529" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -70874,7 +70874,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2530" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -70900,7 +70900,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2531" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -70926,7 +70926,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2532" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -70952,7 +70952,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G2533" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -70978,7 +70978,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2534" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -71004,7 +71004,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2535" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -71030,7 +71030,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2536" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -71056,7 +71056,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G2537" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -71082,7 +71082,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2538" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -71108,7 +71108,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2539" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -71134,7 +71134,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2540" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -71160,7 +71160,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2541" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>
@@ -71186,7 +71186,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2542" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2542" t="s">
         <v>9</v>
@@ -71212,7 +71212,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2543" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2543" t="s">
         <v>9</v>
@@ -71238,7 +71238,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G2544" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2544" t="s">
         <v>9</v>
@@ -71264,7 +71264,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2545" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2545" t="s">
         <v>9</v>
@@ -71272,7 +71272,7 @@
     </row>
     <row r="2546">
       <c r="A2546" s="1" t="n">
-        <v>46030.6912962963</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2546" t="n">
         <v>108024</v>
@@ -71290,9 +71290,35 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2546" t="s">
+        <v>1582</v>
+      </c>
+      <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.6912268518</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>375099</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>10.2399997711182</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>9.88000011444092</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>9.92000007629395</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>10.2200002670288</v>
+      </c>
+      <c r="G2547" t="s">
         <v>1583</v>
       </c>
-      <c r="H2546" t="s">
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74423742294312</t>
+    <t xml:space="preserve">7.74423837661743</t>
   </si>
   <si>
     <t xml:space="preserve">7.72238302230835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7296667098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78794860839844</t>
+    <t xml:space="preserve">7.72966814041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78794956207275</t>
   </si>
   <si>
     <t xml:space="preserve">7.77337837219238</t>
@@ -62,106 +62,106 @@
     <t xml:space="preserve">7.56939268112183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54753589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61310291290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21241426467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17598676681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62038946151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4673957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35811948776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30712175369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3872594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56210565567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49653720855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28526639938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37268877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64952945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51839447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58396196365356</t>
+    <t xml:space="preserve">7.54753494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61310243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2124137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17598724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62038850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46739721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35811901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30712080001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38726043701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56210803985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49653816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28526592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37268924713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64952659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.518394947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58396053314209</t>
   </si>
   <si>
     <t xml:space="preserve">7.67867088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86080312728882</t>
+    <t xml:space="preserve">7.86080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">7.76609325408936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89722728729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90451335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95551156997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80980539321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88994359970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00650691986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093942642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8753719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0137939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94822549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03564643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80251932144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84623050689697</t>
+    <t xml:space="preserve">7.89722871780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90451431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95551061630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80980634689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88994264602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00650787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87537240982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01379299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94822359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03564929962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80252075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84623146057129</t>
   </si>
   <si>
     <t xml:space="preserve">8.05750465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05021858215332</t>
+    <t xml:space="preserve">8.050217628479</t>
   </si>
   <si>
     <t xml:space="preserve">8.02836227416992</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">8.15949821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38534069061279</t>
+    <t xml:space="preserve">8.38534259796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.45090961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43633842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45819568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63304042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71317863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60389995574951</t>
+    <t xml:space="preserve">8.4363374710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45819473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63303852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71317672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6038990020752</t>
   </si>
   <si>
     <t xml:space="preserve">8.74231910705566</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">8.42176723480225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73503494262695</t>
+    <t xml:space="preserve">8.73503398895264</t>
   </si>
   <si>
     <t xml:space="preserve">8.79331684112549</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">8.65489673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70589160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81517219543457</t>
+    <t xml:space="preserve">8.70589256286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81517124176025</t>
   </si>
   <si>
     <t xml:space="preserve">8.95359039306641</t>
@@ -221,28 +221,28 @@
     <t xml:space="preserve">8.75688934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20857810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2668571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25228691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39799308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48541641235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36156845092773</t>
+    <t xml:space="preserve">9.20857620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26685905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25228977203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39799118041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48541736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36156558990479</t>
   </si>
   <si>
     <t xml:space="preserve">9.32488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07543849945068</t>
+    <t xml:space="preserve">9.07543754577637</t>
   </si>
   <si>
     <t xml:space="preserve">9.09744834899902</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">9.17081451416016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29553604125977</t>
+    <t xml:space="preserve">9.29553699493408</t>
   </si>
   <si>
     <t xml:space="preserve">9.36890411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27352809906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28819942474365</t>
+    <t xml:space="preserve">9.27352714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28820037841797</t>
   </si>
   <si>
     <t xml:space="preserve">9.20749855041504</t>
@@ -269,91 +269,91 @@
     <t xml:space="preserve">9.24418067932129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11212158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02408027648926</t>
+    <t xml:space="preserve">9.11211967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02408123016357</t>
   </si>
   <si>
     <t xml:space="preserve">8.87734794616699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84066486358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398082733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73061466217041</t>
+    <t xml:space="preserve">8.84066581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80398178100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73061656951904</t>
   </si>
   <si>
     <t xml:space="preserve">8.95071506500244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22950649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81865501403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82599258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91403007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31754684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95805168151855</t>
+    <t xml:space="preserve">9.22950839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81865406036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8259916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91403102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31754875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95805072784424</t>
   </si>
   <si>
     <t xml:space="preserve">8.99473571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19282531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13413143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34689426422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35422897338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36156558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22216892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06076431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37624168395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33955574035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31021118164062</t>
+    <t xml:space="preserve">9.1928243637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13413047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34689331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35422992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22217082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06076622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37623977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33955669403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31021022796631</t>
   </si>
   <si>
     <t xml:space="preserve">9.28086376190186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26619052886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97272491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16347694396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17815113067627</t>
+    <t xml:space="preserve">9.26618957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97272300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16347789764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17815017700195</t>
   </si>
   <si>
     <t xml:space="preserve">9.39825057983398</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">9.30287456512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25885391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33221912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11945629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05342769622803</t>
+    <t xml:space="preserve">9.25885486602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33222007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11945533752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05342864990234</t>
   </si>
   <si>
     <t xml:space="preserve">9.00207233428955</t>
@@ -380,70 +380,70 @@
     <t xml:space="preserve">8.96538829803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14146709442139</t>
+    <t xml:space="preserve">9.1414680480957</t>
   </si>
   <si>
     <t xml:space="preserve">9.01674365997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39091300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15614223480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38357543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44960689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49362754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52297210693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50830078125</t>
+    <t xml:space="preserve">9.39091396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15614128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38357639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44960784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49362659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52297401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50830173492432</t>
   </si>
   <si>
     <t xml:space="preserve">9.79442977905273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83844947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312271118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95583629608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0438766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1392517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2566394805908</t>
+    <t xml:space="preserve">9.83845043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85312366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95583724975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0438747406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.139253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2566375732422</t>
   </si>
   <si>
     <t xml:space="preserve">10.1979465484619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2713108062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90447998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0145292282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75774574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65503120422363</t>
+    <t xml:space="preserve">10.2713117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90448093414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0145273208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75774765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65503406524658</t>
   </si>
   <si>
     <t xml:space="preserve">9.64769744873047</t>
@@ -452,73 +452,73 @@
     <t xml:space="preserve">9.80910301208496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64036083221436</t>
+    <t xml:space="preserve">9.64035892486572</t>
   </si>
   <si>
     <t xml:space="preserve">9.53764724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45694351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41292476654053</t>
+    <t xml:space="preserve">9.45694446563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41292285919189</t>
   </si>
   <si>
     <t xml:space="preserve">9.61834907531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56699371337891</t>
+    <t xml:space="preserve">9.56699275970459</t>
   </si>
   <si>
     <t xml:space="preserve">9.44227123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5156364440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53031063079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47895431518555</t>
+    <t xml:space="preserve">9.51563739776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47895336151123</t>
   </si>
   <si>
     <t xml:space="preserve">9.63302326202393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55965709686279</t>
+    <t xml:space="preserve">9.55965614318848</t>
   </si>
   <si>
     <t xml:space="preserve">9.47161769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73573684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0878953933716</t>
+    <t xml:space="preserve">9.73573589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0878963470459</t>
   </si>
   <si>
     <t xml:space="preserve">10.1245784759521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.051212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86779499053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8311128616333</t>
+    <t xml:space="preserve">10.0512113571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86779594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83111190795898</t>
   </si>
   <si>
     <t xml:space="preserve">9.97050952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97784519195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81643962860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69171619415283</t>
+    <t xml:space="preserve">9.97784614562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81643867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69171714782715</t>
   </si>
   <si>
     <t xml:space="preserve">9.88980579376221</t>
@@ -527,40 +527,40 @@
     <t xml:space="preserve">9.86045932769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96317195892334</t>
+    <t xml:space="preserve">9.96317291259766</t>
   </si>
   <si>
     <t xml:space="preserve">10.0585489273071</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99251937866211</t>
+    <t xml:space="preserve">9.99252033233643</t>
   </si>
   <si>
     <t xml:space="preserve">10.161262512207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1465892791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94116115570068</t>
+    <t xml:space="preserve">10.1465911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.941162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.82377624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7210636138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8751335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0365381240845</t>
+    <t xml:space="preserve">9.72106266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87513160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0365390777588</t>
   </si>
   <si>
     <t xml:space="preserve">10.0805587768555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.00719165802</t>
+    <t xml:space="preserve">10.0071926116943</t>
   </si>
   <si>
     <t xml:space="preserve">9.89714241027832</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">9.985182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3300046920776</t>
+    <t xml:space="preserve">10.3300065994263</t>
   </si>
   <si>
     <t xml:space="preserve">10.7335214614868</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7115125656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6674928665161</t>
+    <t xml:space="preserve">10.7115097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6674909591675</t>
   </si>
   <si>
     <t xml:space="preserve">10.8582439422607</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">10.9316110610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8068876266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022655487061</t>
+    <t xml:space="preserve">10.8068866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022645950317</t>
   </si>
   <si>
     <t xml:space="preserve">11.1883926391602</t>
@@ -605,79 +605,79 @@
     <t xml:space="preserve">11.2177410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3424625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1590461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0636701583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0416584014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1517105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.225076675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2984428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7166328430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7313051223755</t>
+    <t xml:space="preserve">11.3424634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.15904712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0636711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242734909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0416612625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1517095565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2250776290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2984418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7166337966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7313060760498</t>
   </si>
   <si>
     <t xml:space="preserve">11.8340187072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8853759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9954233169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6997423171997</t>
+    <t xml:space="preserve">11.8853750228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9954242706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.699743270874</t>
   </si>
   <si>
     <t xml:space="preserve">13.0225553512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0592403411865</t>
+    <t xml:space="preserve">13.0592384338379</t>
   </si>
   <si>
     <t xml:space="preserve">13.2059726715088</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6924057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2815532684326</t>
+    <t xml:space="preserve">12.6924085617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2815542221069</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1788396835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.479642868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3255729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6850700378418</t>
+    <t xml:space="preserve">12.1788415908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4796438217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3255739212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6850728988647</t>
   </si>
   <si>
     <t xml:space="preserve">12.6630601882935</t>
@@ -686,25 +686,25 @@
     <t xml:space="preserve">12.655722618103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1619520187378</t>
+    <t xml:space="preserve">13.1619510650635</t>
   </si>
   <si>
     <t xml:space="preserve">12.8024559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391408920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1399431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0005464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491910934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0959224700928</t>
+    <t xml:space="preserve">12.8391380310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1399440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.000545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0959215164185</t>
   </si>
   <si>
     <t xml:space="preserve">13.04456615448</t>
@@ -713,34 +713,34 @@
     <t xml:space="preserve">13.7195386886597</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7855682373047</t>
+    <t xml:space="preserve">13.7929058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7855710983276</t>
   </si>
   <si>
     <t xml:space="preserve">13.8295879364014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9396362304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0643615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7268743515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8222522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7415475845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9249668121338</t>
+    <t xml:space="preserve">13.9396371841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0643606185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828546524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7268762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8222513198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7415466308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9249649047852</t>
   </si>
   <si>
     <t xml:space="preserve">13.6755180358887</t>
@@ -749,34 +749,34 @@
     <t xml:space="preserve">13.4480819702148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4627561569214</t>
+    <t xml:space="preserve">13.4627552032471</t>
   </si>
   <si>
     <t xml:space="preserve">13.4037704467773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5364847183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7945308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8903789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4922475814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512285232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6618194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9641036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9862251281738</t>
+    <t xml:space="preserve">13.5364828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945327758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8903770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4922456741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512294769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6618223190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9641056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9862232208252</t>
   </si>
   <si>
     <t xml:space="preserve">14.0452070236206</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">13.7429218292236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7650394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502956390381</t>
+    <t xml:space="preserve">13.765040397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502965927124</t>
   </si>
   <si>
     <t xml:space="preserve">13.654447555542</t>
@@ -797,43 +797,43 @@
     <t xml:space="preserve">13.4553823471069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9346141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9714803695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7134304046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9272422790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830060958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0820732116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0083436965942</t>
+    <t xml:space="preserve">13.9346160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9714784622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7134294509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9272413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830041885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0820713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0083427429199</t>
   </si>
   <si>
     <t xml:space="preserve">13.8535146713257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1973361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3079252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3300466537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3152980804443</t>
+    <t xml:space="preserve">13.1973342895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3079271316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3300437927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.315299987793</t>
   </si>
   <si>
     <t xml:space="preserve">13.6470766067505</t>
@@ -842,154 +842,154 @@
     <t xml:space="preserve">13.7871599197388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8092756271362</t>
+    <t xml:space="preserve">13.8092765808105</t>
   </si>
   <si>
     <t xml:space="preserve">13.7797861099243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8387689590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9493618011475</t>
+    <t xml:space="preserve">13.8387670516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9493608474731</t>
   </si>
   <si>
     <t xml:space="preserve">14.1189346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8977527618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9198694229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8240232467651</t>
+    <t xml:space="preserve">13.8977499008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9198684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8240222930908</t>
   </si>
   <si>
     <t xml:space="preserve">13.9419870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8313970565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.676568031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4627552032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.101487159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5291109085083</t>
+    <t xml:space="preserve">13.8313941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6765661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4627542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1014890670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.529109954834</t>
   </si>
   <si>
     <t xml:space="preserve">13.565975189209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5586013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2710599899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3890285491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5807209014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6102094650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4185161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7060594558716</t>
+    <t xml:space="preserve">13.5586023330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2710609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3890256881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5807189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6102113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4185180664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7060546875</t>
   </si>
   <si>
     <t xml:space="preserve">13.7576675415039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6986856460571</t>
+    <t xml:space="preserve">13.6986846923828</t>
   </si>
   <si>
     <t xml:space="preserve">13.816650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7281770706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7355499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7724142074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6397018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6249551773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.602837562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7456245422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.605541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6129150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5318145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4728298187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5613021850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4359674453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2958841323853</t>
+    <t xml:space="preserve">13.728178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7355518341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7724113464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6397008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9051237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6249561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6028394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7456254959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6055421829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6129159927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.531813621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4728288650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5613059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4359645843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2958812713623</t>
   </si>
   <si>
     <t xml:space="preserve">14.3032560348511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2590179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9124946594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6913146972656</t>
+    <t xml:space="preserve">14.2590208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9124937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.691312789917</t>
   </si>
   <si>
     <t xml:space="preserve">14.1336822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">14.030463218689</t>
+    <t xml:space="preserve">14.0304613113403</t>
   </si>
   <si>
     <t xml:space="preserve">13.9567308425903</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1263084411621</t>
+    <t xml:space="preserve">14.0378360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1263055801392</t>
   </si>
   <si>
     <t xml:space="preserve">14.1705455780029</t>
@@ -998,118 +998,118 @@
     <t xml:space="preserve">14.2147827148438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1557998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0230903625488</t>
+    <t xml:space="preserve">14.155800819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">14.104190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8461408615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8608856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9788551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1926641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.229528427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5096940994263</t>
+    <t xml:space="preserve">13.8461399078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8608875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9788513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1926622390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2295255661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5096950531006</t>
   </si>
   <si>
     <t xml:space="preserve">14.6497783660889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7013883590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9299440383911</t>
+    <t xml:space="preserve">14.7013902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9299421310425</t>
   </si>
   <si>
     <t xml:space="preserve">14.8562154769897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7824907302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.583423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3474922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4949474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2617225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0774011611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1511306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566358566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4091777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668073654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3354501724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4460401535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0405387878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1142654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6276588439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2885112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2737655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1852922439575</t>
+    <t xml:space="preserve">14.7824897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5834226608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3474931716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4949502944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2617244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0773992538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1511287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668092727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3354511260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4460430145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0405359268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1142644882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6276617050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2885122299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2737674713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1852912902832</t>
   </si>
   <si>
     <t xml:space="preserve">14.5391845703125</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917303085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4212226867676</t>
+    <t xml:space="preserve">14.3917322158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4212217330933</t>
   </si>
   <si>
     <t xml:space="preserve">14.2000360488892</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4064750671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3447914123535</t>
+    <t xml:space="preserve">14.406476020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3447895050049</t>
   </si>
   <si>
     <t xml:space="preserve">13.5217361450195</t>
@@ -1118,187 +1118,187 @@
     <t xml:space="preserve">13.6839399337769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8756332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9908962249756</t>
+    <t xml:space="preserve">13.8756313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9908971786499</t>
   </si>
   <si>
     <t xml:space="preserve">13.1383514404297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9761486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7549638748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6517457962036</t>
+    <t xml:space="preserve">12.976149559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7549657821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6517448425293</t>
   </si>
   <si>
     <t xml:space="preserve">12.887677192688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8729305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7254753112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0793695449829</t>
+    <t xml:space="preserve">12.8729314804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7254734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0793676376343</t>
   </si>
   <si>
     <t xml:space="preserve">12.8286933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5927639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5190353393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.460054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5042905807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7402210235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6812381744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.064621925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2858076095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1088600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3005533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0968170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3742828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3668727874756</t>
+    <t xml:space="preserve">12.5927629470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5190362930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4600534439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5042896270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7402200698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6812391281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0646238327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2858057022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1088609695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3005523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0968179702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3742818832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3668689727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.3075942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1890430450439</t>
+    <t xml:space="preserve">13.1890439987183</t>
   </si>
   <si>
     <t xml:space="preserve">13.4113311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4854249954224</t>
+    <t xml:space="preserve">13.485426902771</t>
   </si>
   <si>
     <t xml:space="preserve">12.9371175765991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2702550888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7592887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5962753295898</t>
+    <t xml:space="preserve">12.2702560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7592859268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5962743759155</t>
   </si>
   <si>
     <t xml:space="preserve">12.6851921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0408487319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9667558670044</t>
+    <t xml:space="preserve">13.0408515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9667549133301</t>
   </si>
   <si>
     <t xml:space="preserve">13.1445846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8630199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963941574097</t>
+    <t xml:space="preserve">12.8630208969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963932037354</t>
   </si>
   <si>
     <t xml:space="preserve">12.8185625076294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7444696426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.981575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2483186721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2927761077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0853071212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4706039428711</t>
+    <t xml:space="preserve">12.7444677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9815740585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2483196258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2927770614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0853099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4706048965454</t>
   </si>
   <si>
     <t xml:space="preserve">13.529881477356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4409694671631</t>
+    <t xml:space="preserve">13.4409675598145</t>
   </si>
   <si>
     <t xml:space="preserve">13.2779560089111</t>
   </si>
   <si>
-    <t xml:space="preserve">13.322413444519</t>
+    <t xml:space="preserve">13.3224153518677</t>
   </si>
   <si>
     <t xml:space="preserve">13.3816909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6039781570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5150632858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3372325897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743398666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299983978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8855428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8262662887573</t>
+    <t xml:space="preserve">13.6039772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5150651931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3372344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743389129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9300012588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8855438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.826265335083</t>
   </si>
   <si>
     <t xml:space="preserve">13.7669887542725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.692892074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7521705627441</t>
+    <t xml:space="preserve">13.6928939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7521696090698</t>
   </si>
   <si>
     <t xml:space="preserve">13.8559045791626</t>
@@ -1307,85 +1307,85 @@
     <t xml:space="preserve">13.989275932312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2038621902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7818078994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9003629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7225313186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9596395492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7077121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5447015762329</t>
+    <t xml:space="preserve">13.2038612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7818098068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9003620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7225322723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9596376419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7077131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5447034835815</t>
   </si>
   <si>
     <t xml:space="preserve">13.5595207214355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1149454116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4261484146118</t>
+    <t xml:space="preserve">13.1149482727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4261474609375</t>
   </si>
   <si>
     <t xml:space="preserve">12.6555528640747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8778390884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9222965240479</t>
+    <t xml:space="preserve">12.8778419494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9222984313965</t>
   </si>
   <si>
     <t xml:space="preserve">13.1001281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1297655105591</t>
+    <t xml:space="preserve">13.1297664642334</t>
   </si>
   <si>
     <t xml:space="preserve">13.0112133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.166522026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1517019271851</t>
+    <t xml:space="preserve">12.1665201187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1517009735107</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1220636367798</t>
+    <t xml:space="preserve">12.1220645904541</t>
   </si>
   <si>
     <t xml:space="preserve">12.3739891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4777240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1368818283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.707127571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0331497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7812242507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2477350234985</t>
+    <t xml:space="preserve">12.4777250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1368837356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7071266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0331478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7812223434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2477331161499</t>
   </si>
   <si>
     <t xml:space="preserve">11.4700202941895</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">11.4403829574585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885744094849</t>
+    <t xml:space="preserve">11.5885734558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6478509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5589380264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3811044692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3514680862427</t>
+    <t xml:space="preserve">11.5589361190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3811054229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.351469039917</t>
   </si>
   <si>
     <t xml:space="preserve">11.173638343811</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">11.1143617630005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6697883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0029239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4326801300049</t>
+    <t xml:space="preserve">11.0254468917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6697854995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0029249191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4326810836792</t>
   </si>
   <si>
     <t xml:space="preserve">10.7883405685425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4771366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5512342453003</t>
+    <t xml:space="preserve">10.4771375656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5512323379517</t>
   </si>
   <si>
     <t xml:space="preserve">10.8920736312866</t>
@@ -1442,55 +1442,55 @@
     <t xml:space="preserve">10.9661703109741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0995426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0770206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3751106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8706378936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8241815567017</t>
+    <t xml:space="preserve">11.0995416641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0770215988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3751096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8706369400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.824182510376</t>
   </si>
   <si>
     <t xml:space="preserve">10.4835081100464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609359741211</t>
+    <t xml:space="preserve">10.5609331130981</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.653844833374</t>
+    <t xml:space="preserve">10.6538457870483</t>
   </si>
   <si>
     <t xml:space="preserve">11.3042259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7467575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6073894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5299634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7622423171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7777261734009</t>
+    <t xml:space="preserve">10.7467584609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6073913574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5299625396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7622413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7777290344238</t>
   </si>
   <si>
     <t xml:space="preserve">10.7312707901001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.235743522644</t>
+    <t xml:space="preserve">10.2357444763184</t>
   </si>
   <si>
     <t xml:space="preserve">10.4525365829468</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">10.9945201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0874328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1493721008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0719480514526</t>
+    <t xml:space="preserve">11.0874319076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1493730545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.071946144104</t>
   </si>
   <si>
     <t xml:space="preserve">10.9480657577515</t>
@@ -1517,16 +1517,16 @@
     <t xml:space="preserve">11.0409755706787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3286552429199</t>
+    <t xml:space="preserve">10.3286561965942</t>
   </si>
   <si>
     <t xml:space="preserve">10.4370527267456</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5919055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4989938735962</t>
+    <t xml:space="preserve">10.5919046401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4989929199219</t>
   </si>
   <si>
     <t xml:space="preserve">10.5144786834717</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">10.3905954360962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3596267700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6693305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228742599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8551540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1184034347534</t>
+    <t xml:space="preserve">10.3596258163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6693296432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.622875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8551530838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1184024810791</t>
   </si>
   <si>
     <t xml:space="preserve">11.3816518783569</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">11.3661670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2422847747803</t>
+    <t xml:space="preserve">11.2422857284546</t>
   </si>
   <si>
     <t xml:space="preserve">11.1648578643799</t>
@@ -1565,31 +1565,31 @@
     <t xml:space="preserve">11.3506803512573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9790353775024</t>
+    <t xml:space="preserve">10.9790344238281</t>
   </si>
   <si>
     <t xml:space="preserve">10.793212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8861255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5764179229736</t>
+    <t xml:space="preserve">10.8861246109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5764188766479</t>
   </si>
   <si>
     <t xml:space="preserve">10.2047729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1118631362915</t>
+    <t xml:space="preserve">10.1118621826172</t>
   </si>
   <si>
     <t xml:space="preserve">10.0808916091919</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67827415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56987953186035</t>
+    <t xml:space="preserve">9.6782751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56987857818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.75570106506348</t>
@@ -1598,19 +1598,19 @@
     <t xml:space="preserve">9.95700931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87958240509033</t>
+    <t xml:space="preserve">9.87958335876465</t>
   </si>
   <si>
     <t xml:space="preserve">9.86409759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94152450561523</t>
+    <t xml:space="preserve">9.94152545928955</t>
   </si>
   <si>
     <t xml:space="preserve">9.92603874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1583194732666</t>
+    <t xml:space="preserve">10.1583185195923</t>
   </si>
   <si>
     <t xml:space="preserve">10.1428327560425</t>
@@ -1622,58 +1622,58 @@
     <t xml:space="preserve">10.1273469924927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3441390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6383609771729</t>
+    <t xml:space="preserve">10.3441410064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6383600234985</t>
   </si>
   <si>
     <t xml:space="preserve">10.7157869338989</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6848163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0344362258911</t>
+    <t xml:space="preserve">10.6848154067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0344352722168</t>
   </si>
   <si>
     <t xml:space="preserve">10.0189504623413</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97249507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2202587127686</t>
+    <t xml:space="preserve">9.97249412536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2202577590942</t>
   </si>
   <si>
     <t xml:space="preserve">9.81734848022461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0666770935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1445932388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3160066604614</t>
+    <t xml:space="preserve">10.0666780471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1445941925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3160076141357</t>
   </si>
   <si>
     <t xml:space="preserve">10.4874219894409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.503005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3004245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91084766387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0043458938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87968158721924</t>
+    <t xml:space="preserve">10.5030059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.30042552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91084861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0043468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87968063354492</t>
   </si>
   <si>
     <t xml:space="preserve">9.895263671875</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">9.98876190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0510959625244</t>
+    <t xml:space="preserve">10.0510940551758</t>
   </si>
   <si>
     <t xml:space="preserve">10.0822610855103</t>
@@ -1691,31 +1691,31 @@
     <t xml:space="preserve">10.1134271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3627557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3939228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6744184494019</t>
+    <t xml:space="preserve">10.3627576828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3939237594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6744203567505</t>
   </si>
   <si>
     <t xml:space="preserve">10.5341701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4250898361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6276712417603</t>
+    <t xml:space="preserve">10.4250888824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6276693344116</t>
   </si>
   <si>
     <t xml:space="preserve">10.4406719207764</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1290102005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2225103378296</t>
+    <t xml:space="preserve">10.1290111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2225093841553</t>
   </si>
   <si>
     <t xml:space="preserve">10.1913423538208</t>
@@ -1727,82 +1727,82 @@
     <t xml:space="preserve">10.4562549591064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3783407211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6432514190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.830249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7523345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0795803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9549160003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6900014877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7679176330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2198257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2509927749634</t>
+    <t xml:space="preserve">10.3783397674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6432523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302488327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7523336410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0795783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9549150466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6900024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.767915725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2198266983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2509918212891</t>
   </si>
   <si>
     <t xml:space="preserve">11.0639953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1574954986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2536745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2848415374756</t>
+    <t xml:space="preserve">11.1574945449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2536754608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2848405838013</t>
   </si>
   <si>
     <t xml:space="preserve">10.2380924224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1601753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4095048904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.03551197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1757612228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8146667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1263265609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0484132766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1419124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0328311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7367506027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5965032577515</t>
+    <t xml:space="preserve">10.1601762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4095058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0355110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.175760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8146686553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1263284683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.048412322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1419105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0328302383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7367496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5965023040771</t>
   </si>
   <si>
     <t xml:space="preserve">10.6120872497559</t>
@@ -1811,43 +1811,43 @@
     <t xml:space="preserve">10.7211675643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9081659317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237489700317</t>
+    <t xml:space="preserve">10.908164024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237480163574</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835006713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.970498085022</t>
+    <t xml:space="preserve">10.8769979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9704961776733</t>
   </si>
   <si>
     <t xml:space="preserve">11.5470714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8587331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9054822921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6561527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8275690078735</t>
+    <t xml:space="preserve">11.8587341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9054841995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6561546325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275661468506</t>
   </si>
   <si>
     <t xml:space="preserve">11.7340698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9989814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8743162155151</t>
+    <t xml:space="preserve">11.9989805221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8743171691895</t>
   </si>
   <si>
     <t xml:space="preserve">11.9210662841797</t>
@@ -1856,49 +1856,49 @@
     <t xml:space="preserve">12.0768976211548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8431510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7652359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8899011611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8119840621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1107444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9860801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3444919586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.780818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0301475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9366502761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7964010238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6249876022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4691562652588</t>
+    <t xml:space="preserve">11.843150138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7652349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8899002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8119850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1107454299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9860820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3444929122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7808179855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0301465988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9366483688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7964019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6249866485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4691572189331</t>
   </si>
   <si>
     <t xml:space="preserve">11.5626554489136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4379911422729</t>
+    <t xml:space="preserve">11.4379901885986</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314893722534</t>
@@ -1913,43 +1913,43 @@
     <t xml:space="preserve">11.4224061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886615753174</t>
+    <t xml:space="preserve">11.1886606216431</t>
   </si>
   <si>
     <t xml:space="preserve">11.2977428436279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2821578979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7055854797363</t>
+    <t xml:space="preserve">11.2821588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.705584526062</t>
   </si>
   <si>
     <t xml:space="preserve">10.8925809860229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6588363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3315916061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3471736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0199289321899</t>
+    <t xml:space="preserve">10.6588354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3315896987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3471727371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0199279785156</t>
   </si>
   <si>
     <t xml:space="preserve">9.97317981719971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0978450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94201278686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80176639556885</t>
+    <t xml:space="preserve">10.0978441238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94201374053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80176544189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.92642974853516</t>
@@ -1961,49 +1961,49 @@
     <t xml:space="preserve">8.86678028106689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13169193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02261161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80444622039795</t>
+    <t xml:space="preserve">9.13169288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02261066436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80444717407227</t>
   </si>
   <si>
     <t xml:space="preserve">8.47720241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25904083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24345779418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14995765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48767614364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11368131637573</t>
+    <t xml:space="preserve">8.38370323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2590389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2434549331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14995861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48767518997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11368179321289</t>
   </si>
   <si>
     <t xml:space="preserve">7.03576564788818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15532207489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42023324966431</t>
+    <t xml:space="preserve">6.15532159805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42023468017578</t>
   </si>
   <si>
     <t xml:space="preserve">6.16311311721802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85924243927002</t>
+    <t xml:space="preserve">5.85924386978149</t>
   </si>
   <si>
     <t xml:space="preserve">5.25929355621338</t>
@@ -2018,31 +2018,31 @@
     <t xml:space="preserve">5.61770486831665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49304008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37616729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08008766174316</t>
+    <t xml:space="preserve">5.49304103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37616682052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08008813858032</t>
   </si>
   <si>
     <t xml:space="preserve">5.36058378219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32941818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35279273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29825162887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45408296585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47745800018311</t>
+    <t xml:space="preserve">5.32941770553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35279226303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29825115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45408201217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47745752334595</t>
   </si>
   <si>
     <t xml:space="preserve">5.76574468612671</t>
@@ -2051,70 +2051,70 @@
     <t xml:space="preserve">5.5086236000061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92157554626465</t>
+    <t xml:space="preserve">5.92157506942749</t>
   </si>
   <si>
     <t xml:space="preserve">5.87482595443726</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8047022819519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8358678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89820051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27219533920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25661134719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33452701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42802619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17090511322021</t>
+    <t xml:space="preserve">5.80470180511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83586835861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89820098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27219486236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25661182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33452749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42802572250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17090463638306</t>
   </si>
   <si>
     <t xml:space="preserve">6.45919179916382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23323726654053</t>
+    <t xml:space="preserve">6.23323678970337</t>
   </si>
   <si>
     <t xml:space="preserve">6.24882030487061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12415504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75016117095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71899557113647</t>
+    <t xml:space="preserve">6.12415599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75016164779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71899509429932</t>
   </si>
   <si>
     <t xml:space="preserve">5.86703491210938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94495058059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92936658859253</t>
+    <t xml:space="preserve">5.94495010375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92936706542969</t>
   </si>
   <si>
     <t xml:space="preserve">6.03844881057739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22544527053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35790157318115</t>
+    <t xml:space="preserve">6.22544574737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35790205001831</t>
   </si>
   <si>
     <t xml:space="preserve">6.5838565826416</t>
@@ -2123,46 +2123,46 @@
     <t xml:space="preserve">6.50594139099121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49035787582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47477531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6228141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08251714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27730560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09030628204346</t>
+    <t xml:space="preserve">6.49035835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47477626800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62281370162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08251523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27730464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09030818939209</t>
   </si>
   <si>
     <t xml:space="preserve">7.05914211273193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89551877975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52152442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60723114013672</t>
+    <t xml:space="preserve">6.8955192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52152395248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60723066329956</t>
   </si>
   <si>
     <t xml:space="preserve">6.76306247711182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5526909828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56827449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68514633178711</t>
+    <t xml:space="preserve">6.55269050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56827354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68514728546143</t>
   </si>
   <si>
     <t xml:space="preserve">6.75527143478394</t>
@@ -2171,43 +2171,43 @@
     <t xml:space="preserve">6.84097719192505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65398073196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01239204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98122549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85656118392944</t>
+    <t xml:space="preserve">6.65398120880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01239156723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98122596740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85656070709229</t>
   </si>
   <si>
     <t xml:space="preserve">6.78643655776978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71631240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73189640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86435270309448</t>
+    <t xml:space="preserve">6.71631336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7318959236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86435317993164</t>
   </si>
   <si>
     <t xml:space="preserve">6.66177272796631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72410440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38906764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24102878570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20207166671753</t>
+    <t xml:space="preserve">6.72410488128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38906812667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24102830886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20207118988037</t>
   </si>
   <si>
     <t xml:space="preserve">6.45140075683594</t>
@@ -2216,37 +2216,37 @@
     <t xml:space="preserve">6.4358172416687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49815034866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28777742385864</t>
+    <t xml:space="preserve">6.49814939498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28777837753296</t>
   </si>
   <si>
     <t xml:space="preserve">6.31115293502808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32673597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13194751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01507377624512</t>
+    <t xml:space="preserve">6.32673501968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13194704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01507329940796</t>
   </si>
   <si>
     <t xml:space="preserve">6.09298944473267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07740688323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00728273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95274114608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93715810775757</t>
+    <t xml:space="preserve">6.07740640640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00728225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95274209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93715858459473</t>
   </si>
   <si>
     <t xml:space="preserve">5.72678661346436</t>
@@ -2255,94 +2255,94 @@
     <t xml:space="preserve">5.8436598777771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69562005996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53979015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64107894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56316328048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5475811958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48524904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52420663833618</t>
+    <t xml:space="preserve">5.6956205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5397891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64107942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56316423416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54758071899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48524808883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52420616149902</t>
   </si>
   <si>
     <t xml:space="preserve">5.74237012863159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75795221328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73457813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79691076278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90599203109741</t>
+    <t xml:space="preserve">5.75795269012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73457860946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79691028594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90599250793457</t>
   </si>
   <si>
     <t xml:space="preserve">5.96053314208984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68003797531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85145092010498</t>
+    <t xml:space="preserve">5.68003749847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8514518737793</t>
   </si>
   <si>
     <t xml:space="preserve">5.78132772445679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04623985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91378450393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67224597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5164155960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46187448501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15800333023071</t>
+    <t xml:space="preserve">6.04624080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91378307342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67224645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51641511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46187400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15800380706787</t>
   </si>
   <si>
     <t xml:space="preserve">4.99438095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79180097579956</t>
+    <t xml:space="preserve">4.79180192947388</t>
   </si>
   <si>
     <t xml:space="preserve">4.76063537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80738353729248</t>
+    <t xml:space="preserve">4.8073844909668</t>
   </si>
   <si>
     <t xml:space="preserve">4.8307580947876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02554798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18137788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06182384490967</t>
+    <t xml:space="preserve">5.02554702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18137884140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06182336807251</t>
   </si>
   <si>
     <t xml:space="preserve">6.02286529541016</t>
@@ -2351,55 +2351,55 @@
     <t xml:space="preserve">6.10078048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9968090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23055553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05134963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93447637557983</t>
+    <t xml:space="preserve">6.99680852890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23055505752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05134868621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93447589874268</t>
   </si>
   <si>
     <t xml:space="preserve">6.92668485641479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82539415359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77864551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87214469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9111008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77085304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66956472396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63060569763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97343397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63839864730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70072984695435</t>
+    <t xml:space="preserve">6.82539558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77864456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87214374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91110181808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7708535194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66956424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63060617446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97343444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63839817047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7007303237915</t>
   </si>
   <si>
     <t xml:space="preserve">6.80981159210205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98901748657227</t>
+    <t xml:space="preserve">6.98901700973511</t>
   </si>
   <si>
     <t xml:space="preserve">7.14484834671021</t>
@@ -2411,64 +2411,64 @@
     <t xml:space="preserve">6.87993574142456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00460052490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16042995452881</t>
+    <t xml:space="preserve">7.00460004806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16043138504028</t>
   </si>
   <si>
     <t xml:space="preserve">7.17601442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37859439849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38638496398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13705682754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09809827804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53710794448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59164905548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5760645866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79422903060913</t>
+    <t xml:space="preserve">7.37859535217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38638591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13705635070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09809923171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53710746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59164762496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57606506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79422855377197</t>
   </si>
   <si>
     <t xml:space="preserve">7.0747241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22276449203491</t>
+    <t xml:space="preserve">7.22276306152344</t>
   </si>
   <si>
     <t xml:space="preserve">7.28509569168091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25393056869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45650959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65909194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61234092712402</t>
+    <t xml:space="preserve">7.25392913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45651006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65909099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61234188079834</t>
   </si>
   <si>
     <t xml:space="preserve">7.53442573547363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49546718597412</t>
+    <t xml:space="preserve">7.49546670913696</t>
   </si>
   <si>
     <t xml:space="preserve">7.57338333129883</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">7.47209358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50326013565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40196895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26172065734863</t>
+    <t xml:space="preserve">7.50325918197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40196943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26172018051147</t>
   </si>
   <si>
     <t xml:space="preserve">7.30067873001099</t>
@@ -2492,13 +2492,13 @@
     <t xml:space="preserve">7.12926530838013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24613761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5188422203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91621160507202</t>
+    <t xml:space="preserve">7.24613809585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51884269714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91621112823486</t>
   </si>
   <si>
     <t xml:space="preserve">7.79154634475708</t>
@@ -2507,76 +2507,76 @@
     <t xml:space="preserve">7.80713081359863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71363115310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77596187591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54221677780151</t>
+    <t xml:space="preserve">7.71363067626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.775963306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54221725463867</t>
   </si>
   <si>
     <t xml:space="preserve">7.23834657669067</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37080240249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43313503265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02529239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946249008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72142267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46430253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73700523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78375434875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65129852294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58896589279175</t>
+    <t xml:space="preserve">7.37080335617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43313598632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02529430389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90062856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946201324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72142124176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46430158615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73700714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78375482559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65129804611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58896684646606</t>
   </si>
   <si>
     <t xml:space="preserve">7.68246412277222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72921466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62013149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39417695999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40976142883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5967583656311</t>
+    <t xml:space="preserve">7.72921419143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62013244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3941764831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40976095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59675741195679</t>
   </si>
   <si>
     <t xml:space="preserve">7.744797706604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21228885650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29020595550537</t>
+    <t xml:space="preserve">8.21229076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29020690917969</t>
   </si>
   <si>
     <t xml:space="preserve">8.1032075881958</t>
@@ -2585,34 +2585,34 @@
     <t xml:space="preserve">8.08762550354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18221759796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02456378936768</t>
+    <t xml:space="preserve">8.18221664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02456188201904</t>
   </si>
   <si>
     <t xml:space="preserve">7.96150207519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1506872177124</t>
+    <t xml:space="preserve">8.15068626403809</t>
   </si>
   <si>
     <t xml:space="preserve">8.54481983184814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6867094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95471858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00201511383057</t>
+    <t xml:space="preserve">8.68670749664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00201606750488</t>
   </si>
   <si>
     <t xml:space="preserve">9.06507682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12813949584961</t>
+    <t xml:space="preserve">9.12813758850098</t>
   </si>
   <si>
     <t xml:space="preserve">9.20696449279785</t>
@@ -2624,49 +2624,49 @@
     <t xml:space="preserve">9.1439037322998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93895530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97048473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98624992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82859706878662</t>
+    <t xml:space="preserve">8.93895435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97048568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98624897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8285961151123</t>
   </si>
   <si>
     <t xml:space="preserve">8.78130054473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63941287994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51328945159912</t>
+    <t xml:space="preserve">8.63941192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51329040527344</t>
   </si>
   <si>
     <t xml:space="preserve">8.65517711639404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73400402069092</t>
+    <t xml:space="preserve">8.73400497436523</t>
   </si>
   <si>
     <t xml:space="preserve">8.45022773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37140083312988</t>
+    <t xml:space="preserve">8.3714017868042</t>
   </si>
   <si>
     <t xml:space="preserve">8.46599292755127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57635021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52905464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.355637550354</t>
+    <t xml:space="preserve">8.57635116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52905368804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35563659667969</t>
   </si>
   <si>
     <t xml:space="preserve">8.07186031341553</t>
@@ -2675,31 +2675,31 @@
     <t xml:space="preserve">8.21374797821045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22951412200928</t>
+    <t xml:space="preserve">8.22951126098633</t>
   </si>
   <si>
     <t xml:space="preserve">8.27680969238281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24527835845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0560941696167</t>
+    <t xml:space="preserve">8.24527931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05609512329102</t>
   </si>
   <si>
     <t xml:space="preserve">7.89844226837158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94573831558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99303245544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40293121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48176097869873</t>
+    <t xml:space="preserve">7.9457368850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99303293228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40293216705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48175811767578</t>
   </si>
   <si>
     <t xml:space="preserve">8.32410526275635</t>
@@ -2708,64 +2708,64 @@
     <t xml:space="preserve">8.43446254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70247459411621</t>
+    <t xml:space="preserve">8.70247554779053</t>
   </si>
   <si>
     <t xml:space="preserve">8.71823978424072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79706573486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33987140655518</t>
+    <t xml:space="preserve">8.7970666885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33987045288086</t>
   </si>
   <si>
     <t xml:space="preserve">8.38716697692871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29257583618164</t>
+    <t xml:space="preserve">8.29257678985596</t>
   </si>
   <si>
     <t xml:space="preserve">8.26104354858398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19798183441162</t>
+    <t xml:space="preserve">8.19798278808594</t>
   </si>
   <si>
     <t xml:space="preserve">8.592116355896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60788154602051</t>
+    <t xml:space="preserve">8.60788249969482</t>
   </si>
   <si>
     <t xml:space="preserve">8.00879859924316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92997169494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84326219558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9142050743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80384874343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64619541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6619610786438</t>
+    <t xml:space="preserve">7.92997121810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84326267242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91420650482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80384826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64619493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66196060180664</t>
   </si>
   <si>
     <t xml:space="preserve">7.85902786254883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61466407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60678148269653</t>
+    <t xml:space="preserve">7.61466503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60678195953369</t>
   </si>
   <si>
     <t xml:space="preserve">7.70137453079224</t>
@@ -2774,43 +2774,43 @@
     <t xml:space="preserve">7.78808307647705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65407752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79596710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56736898422241</t>
+    <t xml:space="preserve">7.6540789604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79596567153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673680305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.62254810333252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67772531509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50430679321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63831281661987</t>
+    <t xml:space="preserve">7.67772579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50430774688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63831233978271</t>
   </si>
   <si>
     <t xml:space="preserve">7.74867057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76443576812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82749652862549</t>
+    <t xml:space="preserve">7.7644362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82749795913696</t>
   </si>
   <si>
     <t xml:space="preserve">8.67094326019287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62364768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74976921081543</t>
+    <t xml:space="preserve">8.62364673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74977016448975</t>
   </si>
   <si>
     <t xml:space="preserve">7.559485912323</t>
@@ -2819,31 +2819,31 @@
     <t xml:space="preserve">7.54372024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25206136703491</t>
+    <t xml:space="preserve">7.25206089019775</t>
   </si>
   <si>
     <t xml:space="preserve">7.28359270095825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27570867538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85792779922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91310691833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08652544021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99981594085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93675422668457</t>
+    <t xml:space="preserve">7.27570915222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8579273223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9131064414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82639741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08652496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99981689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93675518035889</t>
   </si>
   <si>
     <t xml:space="preserve">7.37030124664307</t>
@@ -2852,61 +2852,61 @@
     <t xml:space="preserve">7.23629665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21264839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12593841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03134727478027</t>
+    <t xml:space="preserve">7.21264791488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12593793869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0313458442688</t>
   </si>
   <si>
     <t xml:space="preserve">7.14958667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09440851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13382148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33877229690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38606691360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47277545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86690902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78019952774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74078798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46489429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52795457839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68560886383057</t>
+    <t xml:space="preserve">7.09440755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1338210105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33877038955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38606739044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47277688980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86690998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78020048141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74078702926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46489524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52795505523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68560838699341</t>
   </si>
   <si>
     <t xml:space="preserve">7.58313274383545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48854160308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45701026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37818384170532</t>
+    <t xml:space="preserve">7.48854207992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45701122283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3781852722168</t>
   </si>
   <si>
     <t xml:space="preserve">7.35453605651855</t>
@@ -2915,25 +2915,25 @@
     <t xml:space="preserve">7.11805534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99193239212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34665298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17323446273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29147529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36242008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19688272476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10229063034058</t>
+    <t xml:space="preserve">6.99193286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34665250778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17323541641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29147481918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36241865158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19688320159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10229110717773</t>
   </si>
   <si>
     <t xml:space="preserve">7.44124507904053</t>
@@ -2942,40 +2942,40 @@
     <t xml:space="preserve">7.33088779449463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40971565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49642562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39394998550415</t>
+    <t xml:space="preserve">7.4097146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49642419815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39395046234131</t>
   </si>
   <si>
     <t xml:space="preserve">7.26782703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15746927261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61356544494629</t>
+    <t xml:space="preserve">7.15746974945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61356449127197</t>
   </si>
   <si>
     <t xml:space="preserve">6.44014596939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60568189620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81063175201416</t>
+    <t xml:space="preserve">6.60568237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.810631275177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98405027389526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18111705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18900012969971</t>
+    <t xml:space="preserve">7.18111753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18900108337402</t>
   </si>
   <si>
     <t xml:space="preserve">7.06287717819214</t>
@@ -2984,82 +2984,82 @@
     <t xml:space="preserve">7.11017370223999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20476531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88267660140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81173181533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69349241256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75655269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73290491104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42548084259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48065853118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5121898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52007246017456</t>
+    <t xml:space="preserve">7.20476627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8826756477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81173038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6934928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75655221939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73290538787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42548036575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48065805435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51218938827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52007293701172</t>
   </si>
   <si>
     <t xml:space="preserve">7.22841358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40183210372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00769853591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4491286277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41542482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31838607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29412698745728</t>
+    <t xml:space="preserve">7.40183305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00769948959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44912910461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4154257774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3183856010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29412651062012</t>
   </si>
   <si>
     <t xml:space="preserve">7.48011827468872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56098508834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63376379013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54481220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4396858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48820447921753</t>
+    <t xml:space="preserve">7.56098413467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63376331329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5448112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43968486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48820495605469</t>
   </si>
   <si>
     <t xml:space="preserve">7.46394491195679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32647323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0515284538269</t>
+    <t xml:space="preserve">7.32647275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05152797698975</t>
   </si>
   <si>
     <t xml:space="preserve">6.83318901062012</t>
@@ -3068,43 +3068,43 @@
     <t xml:space="preserve">6.94640207290649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76041030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75232362747192</t>
+    <t xml:space="preserve">6.76040983200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75232315063477</t>
   </si>
   <si>
     <t xml:space="preserve">6.71189022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86553573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73614931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74423694610596</t>
+    <t xml:space="preserve">6.86553525924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73615026473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7442364692688</t>
   </si>
   <si>
     <t xml:space="preserve">6.81701564788818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87362241744995</t>
+    <t xml:space="preserve">6.87362194061279</t>
   </si>
   <si>
     <t xml:space="preserve">6.80084276199341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71997690200806</t>
+    <t xml:space="preserve">6.71997737884521</t>
   </si>
   <si>
     <t xml:space="preserve">6.63102340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70380353927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46929121017456</t>
+    <t xml:space="preserve">6.70380306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46929168701172</t>
   </si>
   <si>
     <t xml:space="preserve">6.48546504974365</t>
@@ -3113,37 +3113,37 @@
     <t xml:space="preserve">6.57441806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69571685791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64719724655151</t>
+    <t xml:space="preserve">6.69571733474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64719772338867</t>
   </si>
   <si>
     <t xml:space="preserve">6.63911056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55015754699707</t>
+    <t xml:space="preserve">6.55015802383423</t>
   </si>
   <si>
     <t xml:space="preserve">6.60676383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62293720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47737836837769</t>
+    <t xml:space="preserve">6.62293767929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47737789154053</t>
   </si>
   <si>
     <t xml:space="preserve">6.40459871292114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41268491744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65528297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8412766456604</t>
+    <t xml:space="preserve">6.41268539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65528345108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84127569198608</t>
   </si>
   <si>
     <t xml:space="preserve">6.72806358337402</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">6.67145681381226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76849555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50163793563843</t>
+    <t xml:space="preserve">6.76849603652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50163841247559</t>
   </si>
   <si>
     <t xml:space="preserve">6.46120452880859</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">6.49355125427246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44503164291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38842582702637</t>
+    <t xml:space="preserve">6.44503116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38842630386353</t>
   </si>
   <si>
     <t xml:space="preserve">6.29138612747192</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">6.19434642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08922004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13774061203003</t>
+    <t xml:space="preserve">6.08922052383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13773965835571</t>
   </si>
   <si>
     <t xml:space="preserve">5.95174837112427</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">5.98409461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90322875976562</t>
+    <t xml:space="preserve">5.90322828292847</t>
   </si>
   <si>
     <t xml:space="preserve">6.06496095657349</t>
@@ -3212,25 +3212,25 @@
     <t xml:space="preserve">5.86279582977295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88705587387085</t>
+    <t xml:space="preserve">5.88705539703369</t>
   </si>
   <si>
     <t xml:space="preserve">5.79001569747925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83044910430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81427526473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63637065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70915031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74958324432373</t>
+    <t xml:space="preserve">5.83044862747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81427574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63637018203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7091498374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74958276748657</t>
   </si>
   <si>
     <t xml:space="preserve">5.73340940475464</t>
@@ -3239,37 +3239,37 @@
     <t xml:space="preserve">5.67680311203003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78192949295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74149608612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62828302383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45846509933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39377164840698</t>
+    <t xml:space="preserve">5.78192901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74149656295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62828397750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45846462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39377212524414</t>
   </si>
   <si>
     <t xml:space="preserve">5.33716487884521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38568496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36142539978027</t>
+    <t xml:space="preserve">5.38568544387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36142492294312</t>
   </si>
   <si>
     <t xml:space="preserve">5.42611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43420553207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28055906295776</t>
+    <t xml:space="preserve">5.43420505523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28056001663208</t>
   </si>
   <si>
     <t xml:space="preserve">5.26438617706299</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">5.40994453430176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35333824157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5797643661499</t>
+    <t xml:space="preserve">5.35333871841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57976388931274</t>
   </si>
   <si>
     <t xml:space="preserve">5.82236242294312</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">5.75766944885254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6606297492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61211013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65254306793213</t>
+    <t xml:space="preserve">5.66063022613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61211109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65254354476929</t>
   </si>
   <si>
     <t xml:space="preserve">5.48272466659546</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">5.50698471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64445686340332</t>
+    <t xml:space="preserve">5.64445638656616</t>
   </si>
   <si>
     <t xml:space="preserve">5.52315759658813</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">5.70106363296509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57167720794678</t>
+    <t xml:space="preserve">5.57167673110962</t>
   </si>
   <si>
     <t xml:space="preserve">5.46655130386353</t>
@@ -3347,10 +3347,10 @@
     <t xml:space="preserve">5.49081134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56359148025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41803216934204</t>
+    <t xml:space="preserve">5.56359052658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41803169250488</t>
   </si>
   <si>
     <t xml:space="preserve">5.44229125976562</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">6.21860694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03261470794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97600841522217</t>
+    <t xml:space="preserve">6.03261423110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97600793838501</t>
   </si>
   <si>
     <t xml:space="preserve">6.01644086837769</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">5.9436616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80618953704834</t>
+    <t xml:space="preserve">5.80618906021118</t>
   </si>
   <si>
     <t xml:space="preserve">5.87896871566772</t>
@@ -3401,22 +3401,22 @@
     <t xml:space="preserve">6.1215672492981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09730768203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16200017929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07304716110229</t>
+    <t xml:space="preserve">6.0973072052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16200065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07304811477661</t>
   </si>
   <si>
     <t xml:space="preserve">6.08113479614258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05687379837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04070091247559</t>
+    <t xml:space="preserve">6.05687427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04070043563843</t>
   </si>
   <si>
     <t xml:space="preserve">6.10539388656616</t>
@@ -3434,25 +3434,25 @@
     <t xml:space="preserve">5.58785057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3075590133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84662199020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83853578567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00835418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1296534538269</t>
+    <t xml:space="preserve">6.30755949020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84662246704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83853530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00835466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12965393066406</t>
   </si>
   <si>
     <t xml:space="preserve">6.16357803344727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20466804504395</t>
+    <t xml:space="preserve">6.2046685218811</t>
   </si>
   <si>
     <t xml:space="preserve">6.01565217971802</t>
@@ -3461,19 +3461,19 @@
     <t xml:space="preserve">6.29506778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49230194091797</t>
+    <t xml:space="preserve">6.49230289459229</t>
   </si>
   <si>
     <t xml:space="preserve">6.47586631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46764755249023</t>
+    <t xml:space="preserve">6.46764802932739</t>
   </si>
   <si>
     <t xml:space="preserve">6.5005202293396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59913730621338</t>
+    <t xml:space="preserve">6.59913682937622</t>
   </si>
   <si>
     <t xml:space="preserve">6.58270168304443</t>
@@ -3497,25 +3497,25 @@
     <t xml:space="preserve">6.33615779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52517414093018</t>
+    <t xml:space="preserve">6.52517461776733</t>
   </si>
   <si>
     <t xml:space="preserve">6.57448291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45943021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54982852935791</t>
+    <t xml:space="preserve">6.45942974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54982900619507</t>
   </si>
   <si>
     <t xml:space="preserve">6.50873851776123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4429931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41833877563477</t>
+    <t xml:space="preserve">6.44299364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41833925247192</t>
   </si>
   <si>
     <t xml:space="preserve">6.43477535247803</t>
@@ -3527,34 +3527,34 @@
     <t xml:space="preserve">6.34437608718872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1142692565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1307053565979</t>
+    <t xml:space="preserve">6.11426877975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13070583343506</t>
   </si>
   <si>
     <t xml:space="preserve">6.13892364501953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25397682189941</t>
+    <t xml:space="preserve">6.25397729873657</t>
   </si>
   <si>
     <t xml:space="preserve">6.26219511032104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31972217559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35259389877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30328559875488</t>
+    <t xml:space="preserve">6.31972169876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35259437561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30328607559204</t>
   </si>
   <si>
     <t xml:space="preserve">6.21288681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37724924087524</t>
+    <t xml:space="preserve">6.37724876403809</t>
   </si>
   <si>
     <t xml:space="preserve">6.48408365249634</t>
@@ -3569,16 +3569,16 @@
     <t xml:space="preserve">6.65666437149048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59091997146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5580472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80459022521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8867712020874</t>
+    <t xml:space="preserve">6.59091949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55804681777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80459070205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88677167892456</t>
   </si>
   <si>
     <t xml:space="preserve">6.83746242523193</t>
@@ -3590,52 +3590,52 @@
     <t xml:space="preserve">6.61557388305664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70597314834595</t>
+    <t xml:space="preserve">6.70597267150879</t>
   </si>
   <si>
     <t xml:space="preserve">6.63200950622559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62379264831543</t>
+    <t xml:space="preserve">6.62379217147827</t>
   </si>
   <si>
     <t xml:space="preserve">6.82924461364746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9442982673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87855243682861</t>
+    <t xml:space="preserve">6.94429731369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87855291366577</t>
   </si>
   <si>
     <t xml:space="preserve">6.77993583679199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7963719367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90320730209351</t>
+    <t xml:space="preserve">6.79637289047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90320634841919</t>
   </si>
   <si>
     <t xml:space="preserve">6.84568023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8538990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72240972518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68131828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68953704833984</t>
+    <t xml:space="preserve">6.85389852523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72241020202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68131875991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68953657150269</t>
   </si>
   <si>
     <t xml:space="preserve">6.27863121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0896143913269</t>
+    <t xml:space="preserve">6.08961486816406</t>
   </si>
   <si>
     <t xml:space="preserve">6.07317876815796</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">6.04852437973022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15535974502563</t>
+    <t xml:space="preserve">6.15536022186279</t>
   </si>
   <si>
     <t xml:space="preserve">5.99921607971191</t>
@@ -3653,46 +3653,46 @@
     <t xml:space="preserve">5.94168901443481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05674314498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95812463760376</t>
+    <t xml:space="preserve">6.05674266815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8759446144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95812559127808</t>
   </si>
   <si>
     <t xml:space="preserve">6.08139705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03208827972412</t>
+    <t xml:space="preserve">6.03208780288696</t>
   </si>
   <si>
     <t xml:space="preserve">5.8923807144165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85128974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90881681442261</t>
+    <t xml:space="preserve">5.85129022598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90881729125977</t>
   </si>
   <si>
     <t xml:space="preserve">5.78554487228394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75267314910889</t>
+    <t xml:space="preserve">5.75267267227173</t>
   </si>
   <si>
     <t xml:space="preserve">5.64583730697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71158218383789</t>
+    <t xml:space="preserve">5.71158170700073</t>
   </si>
   <si>
     <t xml:space="preserve">5.71979999542236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82663583755493</t>
+    <t xml:space="preserve">5.82663631439209</t>
   </si>
   <si>
     <t xml:space="preserve">5.86772584915161</t>
@@ -3701,13 +3701,13 @@
     <t xml:space="preserve">6.188232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12248659133911</t>
+    <t xml:space="preserve">6.12248706817627</t>
   </si>
   <si>
     <t xml:space="preserve">6.14714193344116</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28684949874878</t>
+    <t xml:space="preserve">6.28684902191162</t>
   </si>
   <si>
     <t xml:space="preserve">6.40190267562866</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">6.76349925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66488170623779</t>
+    <t xml:space="preserve">6.66488218307495</t>
   </si>
   <si>
     <t xml:space="preserve">6.738844871521</t>
@@ -3728,16 +3728,16 @@
     <t xml:space="preserve">6.93607950210571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99360704421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06756973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24015045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13331413269043</t>
+    <t xml:space="preserve">6.99360656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06757020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.240149974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13331460952759</t>
   </si>
   <si>
     <t xml:space="preserve">6.98538827896118</t>
@@ -3746,13 +3746,13 @@
     <t xml:space="preserve">7.1250958442688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07578754425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16618585586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14974975585938</t>
+    <t xml:space="preserve">7.07578659057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16618633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14975070953369</t>
   </si>
   <si>
     <t xml:space="preserve">7.19084119796753</t>
@@ -3761,34 +3761,34 @@
     <t xml:space="preserve">7.1826229095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28123998641968</t>
+    <t xml:space="preserve">7.28124046325684</t>
   </si>
   <si>
     <t xml:space="preserve">7.21549463272095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17440414428711</t>
+    <t xml:space="preserve">7.17440462112427</t>
   </si>
   <si>
     <t xml:space="preserve">7.09222364425659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19905948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0511326789856</t>
+    <t xml:space="preserve">7.199059009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05113315582275</t>
   </si>
   <si>
     <t xml:space="preserve">7.03469753265381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34698390960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48669290542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36342144012451</t>
+    <t xml:space="preserve">7.34698438644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48669195175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36342191696167</t>
   </si>
   <si>
     <t xml:space="preserve">7.35520315170288</t>
@@ -3797,40 +3797,40 @@
     <t xml:space="preserve">7.28945827484131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37163972854614</t>
+    <t xml:space="preserve">7.37163877487183</t>
   </si>
   <si>
     <t xml:space="preserve">7.57709217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73323535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94690608978271</t>
+    <t xml:space="preserve">7.73323583602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94690704345703</t>
   </si>
   <si>
     <t xml:space="preserve">7.88937950134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02086925506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78496217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62768888473511</t>
+    <t xml:space="preserve">8.0208683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78496170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62768936157227</t>
   </si>
   <si>
     <t xml:space="preserve">7.63642692565918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5228419303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43546915054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28693437576294</t>
+    <t xml:space="preserve">7.52284097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43546867370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28693342208862</t>
   </si>
   <si>
     <t xml:space="preserve">7.37430667877197</t>
@@ -3842,91 +3842,91 @@
     <t xml:space="preserve">7.25198459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29567193984985</t>
+    <t xml:space="preserve">7.29567098617554</t>
   </si>
   <si>
     <t xml:space="preserve">7.42673110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30440902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40925550460815</t>
+    <t xml:space="preserve">7.30440807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40925598144531</t>
   </si>
   <si>
     <t xml:space="preserve">7.33062124252319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294237136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49662923812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54031610488892</t>
+    <t xml:space="preserve">7.44420671463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294332504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49662971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54031658172607</t>
   </si>
   <si>
     <t xml:space="preserve">7.64516448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51410484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41799402236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46167993545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.531578540802</t>
+    <t xml:space="preserve">7.51410531997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41799354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46168088912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53157901763916</t>
   </si>
   <si>
     <t xml:space="preserve">7.40051889419556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48789167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3917818069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47041845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34809541702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94617748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90249109268188</t>
+    <t xml:space="preserve">7.48789215087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39178133010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47041797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34809446334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94617795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9024920463562</t>
   </si>
   <si>
     <t xml:space="preserve">6.80638027191162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8675422668457</t>
+    <t xml:space="preserve">6.86754179000854</t>
   </si>
   <si>
     <t xml:space="preserve">6.91996622085571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95491600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78890562057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7015323638916</t>
+    <t xml:space="preserve">6.95491552352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78890609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70153284072876</t>
   </si>
   <si>
     <t xml:space="preserve">6.89375352859497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85006713867188</t>
+    <t xml:space="preserve">6.85006761550903</t>
   </si>
   <si>
     <t xml:space="preserve">7.051025390625</t>
@@ -3935,22 +3935,22 @@
     <t xml:space="preserve">7.16461086273193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18208599090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33935785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17334842681885</t>
+    <t xml:space="preserve">7.18208646774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33935689926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17334890365601</t>
   </si>
   <si>
     <t xml:space="preserve">7.20829772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32188320159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263961791992</t>
+    <t xml:space="preserve">7.32188367843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263914108276</t>
   </si>
   <si>
     <t xml:space="preserve">7.68885087966919</t>
@@ -3959,52 +3959,52 @@
     <t xml:space="preserve">7.68011379241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75874948501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83738613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69758939743042</t>
+    <t xml:space="preserve">7.75875043869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8373851776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69758892059326</t>
   </si>
   <si>
     <t xml:space="preserve">7.67137575149536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81117248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76748657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70632553100586</t>
+    <t xml:space="preserve">7.81117296218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76748752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7063250541687</t>
   </si>
   <si>
     <t xml:space="preserve">7.92475938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89854621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80114412307739</t>
+    <t xml:space="preserve">7.89854717254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80114364624023</t>
   </si>
   <si>
     <t xml:space="preserve">7.5709171295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87198162078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93396663665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96938562393188</t>
+    <t xml:space="preserve">7.87198257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93396615982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96938610076904</t>
   </si>
   <si>
     <t xml:space="preserve">8.12877464294434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09335327148438</t>
+    <t xml:space="preserve">8.09335422515869</t>
   </si>
   <si>
     <t xml:space="preserve">8.13762760162354</t>
@@ -4019,79 +4019,79 @@
     <t xml:space="preserve">8.05793476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95167541503906</t>
+    <t xml:space="preserve">7.95167636871338</t>
   </si>
   <si>
     <t xml:space="preserve">7.98709583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8631272315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97824144363403</t>
+    <t xml:space="preserve">7.86312770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97824096679688</t>
   </si>
   <si>
     <t xml:space="preserve">7.65946531295776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61519145965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71259498596191</t>
+    <t xml:space="preserve">7.6151909828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7125940322876</t>
   </si>
   <si>
     <t xml:space="preserve">7.70373916625977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51778745651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79228830337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64175510406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72144889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60633611679077</t>
+    <t xml:space="preserve">7.51778650283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7922887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6417555809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72144937515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60633563995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.48236799240112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52664232254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59748077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49122285842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58862543106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4380931854248</t>
+    <t xml:space="preserve">7.52664184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59748125076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50007772445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4912223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58862590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43809270858765</t>
   </si>
   <si>
     <t xml:space="preserve">7.47351264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69488477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67717456817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75686931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84541749954224</t>
+    <t xml:space="preserve">7.69488430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67717552185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75686883926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84541654586792</t>
   </si>
   <si>
     <t xml:space="preserve">7.74801397323608</t>
@@ -4100,22 +4100,19 @@
     <t xml:space="preserve">7.88083648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99594974517822</t>
+    <t xml:space="preserve">7.99595022201538</t>
   </si>
   <si>
     <t xml:space="preserve">7.85427236557007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89854717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53549766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33183479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6683201789856</t>
+    <t xml:space="preserve">7.53549718856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33183431625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66831922531128</t>
   </si>
   <si>
     <t xml:space="preserve">7.76572418212891</t>
@@ -4124,34 +4121,34 @@
     <t xml:space="preserve">7.90740156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83656311035156</t>
+    <t xml:space="preserve">7.83656358718872</t>
   </si>
   <si>
     <t xml:space="preserve">8.07564449310303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02251625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17304801940918</t>
+    <t xml:space="preserve">8.02251529693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17304706573486</t>
   </si>
   <si>
     <t xml:space="preserve">8.235032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10220813751221</t>
+    <t xml:space="preserve">8.10220909118652</t>
   </si>
   <si>
     <t xml:space="preserve">7.92511129379272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81885242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94282150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20846748352051</t>
+    <t xml:space="preserve">7.81885290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94282102584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20846843719482</t>
   </si>
   <si>
     <t xml:space="preserve">8.11991882324219</t>
@@ -4163,46 +4160,46 @@
     <t xml:space="preserve">8.19961261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28816032409668</t>
+    <t xml:space="preserve">8.288161277771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31472587585449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22617626190186</t>
+    <t xml:space="preserve">8.22617721557617</t>
   </si>
   <si>
     <t xml:space="preserve">8.19075775146484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56266212463379</t>
+    <t xml:space="preserve">8.56266307830811</t>
   </si>
   <si>
     <t xml:space="preserve">8.66892147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68663024902344</t>
+    <t xml:space="preserve">8.68663120269775</t>
   </si>
   <si>
     <t xml:space="preserve">8.76632404327393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96113109588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17364883422852</t>
+    <t xml:space="preserve">8.96113204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1736478805542</t>
   </si>
   <si>
     <t xml:space="preserve">9.03197002410889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04967975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13822841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9257116317749</t>
+    <t xml:space="preserve">9.04968070983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13822937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92571258544922</t>
   </si>
   <si>
     <t xml:space="preserve">8.97884178161621</t>
@@ -4226,7 +4223,7 @@
     <t xml:space="preserve">8.79288864135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74861431121826</t>
+    <t xml:space="preserve">8.74861526489258</t>
   </si>
   <si>
     <t xml:space="preserve">8.80174350738525</t>
@@ -4235,7 +4232,7 @@
     <t xml:space="preserve">8.83716297149658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99655151367188</t>
+    <t xml:space="preserve">8.99655055999756</t>
   </si>
   <si>
     <t xml:space="preserve">8.39441967010498</t>
@@ -4247,7 +4244,7 @@
     <t xml:space="preserve">8.59808158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61579132080078</t>
+    <t xml:space="preserve">8.61579036712646</t>
   </si>
   <si>
     <t xml:space="preserve">8.51838779449463</t>
@@ -4256,16 +4253,16 @@
     <t xml:space="preserve">8.50067806243896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40327453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43869400024414</t>
+    <t xml:space="preserve">8.4032735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43869304656982</t>
   </si>
   <si>
     <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50953197479248</t>
+    <t xml:space="preserve">8.5095329284668</t>
   </si>
   <si>
     <t xml:space="preserve">8.7043399810791</t>
@@ -4277,7 +4274,7 @@
     <t xml:space="preserve">9.01426124572754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0851001739502</t>
+    <t xml:space="preserve">9.08509922027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.20906734466553</t>
@@ -4289,16 +4286,16 @@
     <t xml:space="preserve">9.19135856628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35074710845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27990627288818</t>
+    <t xml:space="preserve">9.35074615478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2799072265625</t>
   </si>
   <si>
     <t xml:space="preserve">9.45700454711914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10280895233154</t>
+    <t xml:space="preserve">9.10280990600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.85487270355225</t>
@@ -4310,7 +4307,7 @@
     <t xml:space="preserve">8.77517890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89029312133789</t>
+    <t xml:space="preserve">8.89029216766357</t>
   </si>
   <si>
     <t xml:space="preserve">8.94342231750488</t>
@@ -4319,13 +4316,13 @@
     <t xml:space="preserve">8.82830905914307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73975944519043</t>
+    <t xml:space="preserve">8.73976039886475</t>
   </si>
   <si>
     <t xml:space="preserve">8.72205066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53609848022461</t>
+    <t xml:space="preserve">8.53609752655029</t>
   </si>
   <si>
     <t xml:space="preserve">8.54495239257812</t>
@@ -4340,7 +4337,7 @@
     <t xml:space="preserve">8.41212940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49182415008545</t>
+    <t xml:space="preserve">8.49182319641113</t>
   </si>
   <si>
     <t xml:space="preserve">9.26219749450684</t>
@@ -4355,25 +4352,25 @@
     <t xml:space="preserve">8.65121173858643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06739044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6163911819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6341028213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66952133178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0060062408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0237159729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95287799835205</t>
+    <t xml:space="preserve">9.06738948822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61639213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63410186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66952228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.006007194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0237169265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95287704467773</t>
   </si>
   <si>
     <t xml:space="preserve">10.0591354370117</t>
@@ -4385,10 +4382,10 @@
     <t xml:space="preserve">9.75807094573975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36845588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31532669067383</t>
+    <t xml:space="preserve">9.3684549331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31532764434814</t>
   </si>
   <si>
     <t xml:space="preserve">9.56326293945312</t>
@@ -4403,22 +4400,22 @@
     <t xml:space="preserve">10.112265586853</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9705867767334</t>
+    <t xml:space="preserve">9.97058773040771</t>
   </si>
   <si>
     <t xml:space="preserve">10.1653938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.271653175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3602018356323</t>
+    <t xml:space="preserve">10.2716522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.360200881958</t>
   </si>
   <si>
     <t xml:space="preserve">10.1831035614014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.218523979187</t>
+    <t xml:space="preserve">10.2185230255127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2362337112427</t>
@@ -4797,6 +4794,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.52000045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27000045776367</t>
   </si>
 </sst>
 </file>
@@ -61911,7 +61911,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2184" t="s">
-        <v>1364</v>
+        <v>1323</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61937,7 +61937,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2185" t="s">
-        <v>1364</v>
+        <v>1323</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61989,7 +61989,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2187" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62015,7 +62015,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2188" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62067,7 +62067,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2190" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62119,7 +62119,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2192" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62223,7 +62223,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2196" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62249,7 +62249,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2197" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62275,7 +62275,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2198" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62353,7 +62353,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2201" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62379,7 +62379,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2202" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62483,7 +62483,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2206" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62509,7 +62509,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2207" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62561,7 +62561,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2209" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62587,7 +62587,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2210" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62639,7 +62639,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2212" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62717,7 +62717,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2215" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62743,7 +62743,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2216" t="s">
-        <v>1364</v>
+        <v>1323</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62769,7 +62769,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G2217" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62795,7 +62795,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2218" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62821,7 +62821,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2219" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62847,7 +62847,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2220" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62899,7 +62899,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G2222" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62925,7 +62925,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2223" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62951,7 +62951,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2224" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62977,7 +62977,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2225" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63003,7 +63003,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2226" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63029,7 +63029,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G2227" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63055,7 +63055,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63081,7 +63081,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G2229" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63107,7 +63107,7 @@
         <v>9.25</v>
       </c>
       <c r="G2230" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63133,7 +63133,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2231" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63159,7 +63159,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G2232" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63185,7 +63185,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2233" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63211,7 +63211,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2234" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63237,7 +63237,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2235" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63263,7 +63263,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2236" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63289,7 +63289,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63315,7 +63315,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63341,7 +63341,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2239" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63367,7 +63367,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2240" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63393,7 +63393,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2241" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63419,7 +63419,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2242" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63445,7 +63445,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2243" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63471,7 +63471,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2244" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63497,7 +63497,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2245" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63523,7 +63523,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G2246" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63549,7 +63549,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2247" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63575,7 +63575,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G2248" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63601,7 +63601,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2249" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63627,7 +63627,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2250" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63653,7 +63653,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2251" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63679,7 +63679,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2252" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63705,7 +63705,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2253" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63731,7 +63731,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2254" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63757,7 +63757,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2255" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63783,7 +63783,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2256" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63809,7 +63809,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2257" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63835,7 +63835,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2258" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63861,7 +63861,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2259" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63887,7 +63887,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2260" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63913,7 +63913,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G2261" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63939,7 +63939,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2262" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63965,7 +63965,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2263" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63991,7 +63991,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2264" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64017,7 +64017,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2265" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64043,7 +64043,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2266" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64069,7 +64069,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2267" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64095,7 +64095,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2268" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64121,7 +64121,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2269" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64147,7 +64147,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2270" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64173,7 +64173,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2271" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64199,7 +64199,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2272" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64225,7 +64225,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2273" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64251,7 +64251,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2274" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64277,7 +64277,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2275" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64303,7 +64303,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2276" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64329,7 +64329,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2277" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64355,7 +64355,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2278" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64381,7 +64381,7 @@
         <v>10.5</v>
       </c>
       <c r="G2279" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64407,7 +64407,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64433,7 +64433,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64459,7 +64459,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2282" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64485,7 +64485,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2283" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64511,7 +64511,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2284" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64537,7 +64537,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2285" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64563,7 +64563,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2286" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64589,7 +64589,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2287" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64615,7 +64615,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2288" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64641,7 +64641,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64667,7 +64667,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2290" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64693,7 +64693,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2291" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64719,7 +64719,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2292" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64745,7 +64745,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2293" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64771,7 +64771,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2294" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64797,7 +64797,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64823,7 +64823,7 @@
         <v>10</v>
       </c>
       <c r="G2296" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64849,7 +64849,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2297" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64875,7 +64875,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2298" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64901,7 +64901,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2299" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64927,7 +64927,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2300" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64953,7 +64953,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2301" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64979,7 +64979,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2302" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65005,7 +65005,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2303" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65031,7 +65031,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2304" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65057,7 +65057,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2305" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65083,7 +65083,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2306" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65109,7 +65109,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2307" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65135,7 +65135,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2308" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65161,7 +65161,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65187,7 +65187,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2310" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65213,7 +65213,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2311" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65239,7 +65239,7 @@
         <v>9.5</v>
       </c>
       <c r="G2312" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65265,7 +65265,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2313" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65291,7 +65291,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2314" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65317,7 +65317,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2315" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65343,7 +65343,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2316" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65369,7 +65369,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2317" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65395,7 +65395,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2318" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65421,7 +65421,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2319" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65447,7 +65447,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2320" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65473,7 +65473,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2321" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65499,7 +65499,7 @@
         <v>10.5</v>
       </c>
       <c r="G2322" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65525,7 +65525,7 @@
         <v>10.5</v>
       </c>
       <c r="G2323" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65551,7 +65551,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2324" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65577,7 +65577,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2325" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65603,7 +65603,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2326" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65629,7 +65629,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2327" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65655,7 +65655,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2328" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65681,7 +65681,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2329" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65707,7 +65707,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2330" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65733,7 +65733,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2331" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65759,7 +65759,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2332" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65785,7 +65785,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2333" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65811,7 +65811,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2334" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65837,7 +65837,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2335" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65863,7 +65863,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2336" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65889,7 +65889,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G2337" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65915,7 +65915,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2338" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65941,7 +65941,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2339" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65967,7 +65967,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2340" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65993,7 +65993,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2341" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66019,7 +66019,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2342" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66045,7 +66045,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2343" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66071,7 +66071,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2344" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66097,7 +66097,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2345" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66123,7 +66123,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2346" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66149,7 +66149,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2347" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66175,7 +66175,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2348" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66201,7 +66201,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2349" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66227,7 +66227,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G2350" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66253,7 +66253,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2351" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66279,7 +66279,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2352" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66305,7 +66305,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2353" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66331,7 +66331,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2354" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66357,7 +66357,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66383,7 +66383,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66409,7 +66409,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2357" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66435,7 +66435,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2358" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66461,7 +66461,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2359" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66487,7 +66487,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2360" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66513,7 +66513,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2361" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66539,7 +66539,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2362" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66565,7 +66565,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2363" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66591,7 +66591,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66617,7 +66617,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2365" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66643,7 +66643,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2366" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66669,7 +66669,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66695,7 +66695,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2368" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66721,7 +66721,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2369" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66747,7 +66747,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2370" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66773,7 +66773,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2371" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66799,7 +66799,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2372" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66825,7 +66825,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2373" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66851,7 +66851,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2374" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66877,7 +66877,7 @@
         <v>11.5</v>
       </c>
       <c r="G2375" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66903,7 +66903,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2376" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66929,7 +66929,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2377" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66955,7 +66955,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G2378" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66981,7 +66981,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G2379" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67007,7 +67007,7 @@
         <v>11.5</v>
       </c>
       <c r="G2380" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67033,7 +67033,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2381" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67059,7 +67059,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2382" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67085,7 +67085,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G2383" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67111,7 +67111,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G2384" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67137,7 +67137,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2385" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67163,7 +67163,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2386" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67189,7 +67189,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2387" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67215,7 +67215,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G2388" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67241,7 +67241,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2389" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67267,7 +67267,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2390" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67293,7 +67293,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2391" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67319,7 +67319,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G2392" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67345,7 +67345,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2393" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67371,7 +67371,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2394" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67397,7 +67397,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G2395" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67423,7 +67423,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2396" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67449,7 +67449,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2397" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67475,7 +67475,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2398" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67501,7 +67501,7 @@
         <v>9.75</v>
       </c>
       <c r="G2399" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67527,7 +67527,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2400" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67553,7 +67553,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2401" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67579,7 +67579,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2402" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67605,7 +67605,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2403" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67631,7 +67631,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2404" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67657,7 +67657,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2405" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67683,7 +67683,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2406" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67709,7 +67709,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2407" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67735,7 +67735,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2408" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67761,7 +67761,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2409" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67787,7 +67787,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2410" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67813,7 +67813,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2411" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67839,7 +67839,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2412" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67865,7 +67865,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2413" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67891,7 +67891,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2414" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67917,7 +67917,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2415" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67943,7 +67943,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2416" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67969,7 +67969,7 @@
         <v>9.75</v>
       </c>
       <c r="G2417" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67995,7 +67995,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2418" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68021,7 +68021,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2419" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68047,7 +68047,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2420" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68073,7 +68073,7 @@
         <v>9.75</v>
       </c>
       <c r="G2421" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68099,7 +68099,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G2422" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68125,7 +68125,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2423" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68151,7 +68151,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2424" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68177,7 +68177,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2425" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68203,7 +68203,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2426" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68229,7 +68229,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2427" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68255,7 +68255,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2428" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68281,7 +68281,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G2429" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68307,7 +68307,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G2430" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68333,7 +68333,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G2431" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68359,7 +68359,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2432" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68385,7 +68385,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2433" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68411,7 +68411,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2434" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68437,7 +68437,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2435" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68463,7 +68463,7 @@
         <v>8.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68489,7 +68489,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2437" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68515,7 +68515,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2438" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68541,7 +68541,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68567,7 +68567,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2440" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68593,7 +68593,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2441" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68619,7 +68619,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2442" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68645,7 +68645,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2443" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68671,7 +68671,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2444" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68697,7 +68697,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2445" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68723,7 +68723,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2446" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68749,7 +68749,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2447" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68775,7 +68775,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2448" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68801,7 +68801,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2449" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68827,7 +68827,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2450" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68853,7 +68853,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2451" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68879,7 +68879,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2452" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68905,7 +68905,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2453" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68931,7 +68931,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2454" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68957,7 +68957,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2455" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68983,7 +68983,7 @@
         <v>8.75</v>
       </c>
       <c r="G2456" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69009,7 +69009,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2457" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69035,7 +69035,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2458" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69061,7 +69061,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69087,7 +69087,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2460" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69113,7 +69113,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2461" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69139,7 +69139,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2462" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69165,7 +69165,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2463" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69191,7 +69191,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2464" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69217,7 +69217,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G2465" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69243,7 +69243,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G2466" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69269,7 +69269,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69295,7 +69295,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69321,7 +69321,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69347,7 +69347,7 @@
         <v>9</v>
       </c>
       <c r="G2470" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69373,7 +69373,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2471" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69399,7 +69399,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2472" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69425,7 +69425,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2473" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69451,7 +69451,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2474" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69477,7 +69477,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2475" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69503,7 +69503,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69529,7 +69529,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2477" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69555,7 +69555,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69581,7 +69581,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2479" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69607,7 +69607,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2480" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69633,7 +69633,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G2481" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69659,7 +69659,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2482" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69685,7 +69685,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2483" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69711,7 +69711,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2484" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69737,7 +69737,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2485" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69763,7 +69763,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G2486" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69789,7 +69789,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2487" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69815,7 +69815,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2488" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69841,7 +69841,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2489" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69867,7 +69867,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2490" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69893,7 +69893,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2491" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69919,7 +69919,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2492" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69945,7 +69945,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2493" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69971,7 +69971,7 @@
         <v>9.75</v>
       </c>
       <c r="G2494" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69997,7 +69997,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2495" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70023,7 +70023,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G2496" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70049,7 +70049,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2497" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70075,7 +70075,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2498" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70101,7 +70101,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2499" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70127,7 +70127,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2500" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70153,7 +70153,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2501" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70179,7 +70179,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2502" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70205,7 +70205,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G2503" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70231,7 +70231,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2504" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70257,7 +70257,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G2505" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -70283,7 +70283,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2506" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -70309,7 +70309,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2507" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70335,7 +70335,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2508" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -70361,7 +70361,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G2509" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -70387,7 +70387,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -70413,7 +70413,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2511" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -70439,7 +70439,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2512" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70465,7 +70465,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2513" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70491,7 +70491,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2514" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70517,7 +70517,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G2515" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70543,7 +70543,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G2516" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70569,7 +70569,7 @@
         <v>9.25</v>
       </c>
       <c r="G2517" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70595,7 +70595,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G2518" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70621,7 +70621,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2519" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70647,7 +70647,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2520" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70673,7 +70673,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G2521" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70699,7 +70699,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2522" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70725,7 +70725,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2523" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70751,7 +70751,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2524" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -70777,7 +70777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2525" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -70803,7 +70803,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G2526" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -70829,7 +70829,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2527" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -70855,7 +70855,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2528" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -70881,7 +70881,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G2529" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -70907,7 +70907,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G2530" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -70933,7 +70933,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2531" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -70959,7 +70959,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2532" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -70985,7 +70985,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G2533" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -71011,7 +71011,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2534" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -71037,7 +71037,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G2535" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -71063,7 +71063,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2536" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -71089,7 +71089,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G2537" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -71115,7 +71115,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2538" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -71141,7 +71141,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G2539" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -71167,7 +71167,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2540" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -71193,7 +71193,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2541" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>
@@ -71219,7 +71219,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2542" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2542" t="s">
         <v>9</v>
@@ -71245,7 +71245,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2543" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2543" t="s">
         <v>9</v>
@@ -71271,7 +71271,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G2544" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2544" t="s">
         <v>9</v>
@@ -71297,7 +71297,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2545" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2545" t="s">
         <v>9</v>
@@ -71323,7 +71323,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G2546" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2546" t="s">
         <v>9</v>
@@ -71349,7 +71349,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2547" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2547" t="s">
         <v>9</v>
@@ -71375,7 +71375,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2548" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2548" t="s">
         <v>9</v>
@@ -71401,7 +71401,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2549" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2549" t="s">
         <v>9</v>
@@ -71427,7 +71427,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2550" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2550" t="s">
         <v>9</v>
@@ -71453,7 +71453,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G2551" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2551" t="s">
         <v>9</v>
@@ -71479,7 +71479,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G2552" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2552" t="s">
         <v>9</v>
@@ -71505,7 +71505,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2553" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2553" t="s">
         <v>9</v>
@@ -71531,7 +71531,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G2554" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2554" t="s">
         <v>9</v>
@@ -71557,7 +71557,7 @@
         <v>9.75</v>
       </c>
       <c r="G2555" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2555" t="s">
         <v>9</v>
@@ -71583,7 +71583,7 @@
         <v>10</v>
       </c>
       <c r="G2556" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2556" t="s">
         <v>9</v>
@@ -71609,7 +71609,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2557" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2557" t="s">
         <v>9</v>
@@ -71635,7 +71635,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2558" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2558" t="s">
         <v>9</v>
@@ -71643,7 +71643,7 @@
     </row>
     <row r="2559">
       <c r="A2559" s="1" t="n">
-        <v>46049.6912384259</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B2559" t="n">
         <v>249334</v>
@@ -71661,9 +71661,35 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2559" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46050.6912268518</v>
+      </c>
+      <c r="B2560" t="n">
+        <v>203439</v>
+      </c>
+      <c r="C2560" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>9.31999969482422</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>9.27000045776367</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>1594</v>
+      </c>
+      <c r="H2560" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="1598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="1599">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,205 +38,205 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79523611068726</t>
+    <t xml:space="preserve">7.79523658752441</t>
   </si>
   <si>
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74423742294312</t>
+    <t xml:space="preserve">7.74423694610596</t>
   </si>
   <si>
     <t xml:space="preserve">7.72238206863403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72966814041138</t>
+    <t xml:space="preserve">7.72966861724854</t>
   </si>
   <si>
     <t xml:space="preserve">7.78794956207275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77337884902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56938982009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54753398895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61310291290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21241474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17598676681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62038898468018</t>
+    <t xml:space="preserve">7.77337980270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56939172744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54753446578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6131010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21241426467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1759877204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62038803100586</t>
   </si>
   <si>
     <t xml:space="preserve">7.46739816665649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35811901092529</t>
+    <t xml:space="preserve">7.35811758041382</t>
   </si>
   <si>
     <t xml:space="preserve">7.30712175369263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38726043701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56210708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4965386390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2852668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37269020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64952850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51839590072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58396196365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67867136001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8608021736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76609420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89722871780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90451288223267</t>
+    <t xml:space="preserve">7.38725996017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56210565567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49653816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28526639938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37268924713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64952802658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51839542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58396244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67866897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86080312728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76609325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8972282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90451335906982</t>
   </si>
   <si>
     <t xml:space="preserve">7.95551061630249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80980539321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88994455337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00650882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94094038009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87537145614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01379203796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94822454452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03564834594727</t>
+    <t xml:space="preserve">7.80980682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88994407653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00650596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87537336349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01379299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94822549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03564929962158</t>
   </si>
   <si>
     <t xml:space="preserve">7.80252027511597</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84623098373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05750274658203</t>
+    <t xml:space="preserve">7.84623146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05750465393066</t>
   </si>
   <si>
     <t xml:space="preserve">8.05021858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02836513519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15949821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38534069061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45090961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43633937835693</t>
+    <t xml:space="preserve">8.02836322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38534164428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45090866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4363374710083</t>
   </si>
   <si>
     <t xml:space="preserve">8.45819282531738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63304042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71317768096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6038990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74232006072998</t>
+    <t xml:space="preserve">8.6330394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71317863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60389995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74231910705566</t>
   </si>
   <si>
     <t xml:space="preserve">8.80788612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42176628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79331493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6548957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70589256286621</t>
+    <t xml:space="preserve">8.42176723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73503398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79331588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65489673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70589351654053</t>
   </si>
   <si>
     <t xml:space="preserve">8.81517219543457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95359325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75689029693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20857620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26686000823975</t>
+    <t xml:space="preserve">8.95359134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75688934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20857715606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26685905456543</t>
   </si>
   <si>
     <t xml:space="preserve">9.25228881835938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39799308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48541736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3615665435791</t>
+    <t xml:space="preserve">9.39799213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4854154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36156845092773</t>
   </si>
   <si>
     <t xml:space="preserve">9.32488441467285</t>
@@ -245,166 +245,166 @@
     <t xml:space="preserve">9.07543849945068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09744739532471</t>
+    <t xml:space="preserve">9.09744930267334</t>
   </si>
   <si>
     <t xml:space="preserve">9.17081451416016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29553699493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3689022064209</t>
+    <t xml:space="preserve">9.2955379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36890411376953</t>
   </si>
   <si>
     <t xml:space="preserve">9.27352714538574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28820133209229</t>
+    <t xml:space="preserve">9.28820037841797</t>
   </si>
   <si>
     <t xml:space="preserve">9.20749759674072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24418067932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11212253570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02408123016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87734699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84066486358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73061466217041</t>
+    <t xml:space="preserve">9.24418163299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11212158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02408027648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87734794616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84066581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80398082733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73061561584473</t>
   </si>
   <si>
     <t xml:space="preserve">8.95071506500244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22950553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81865310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82599067687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91403007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31754779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95804977416992</t>
+    <t xml:space="preserve">9.22950744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81865406036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8259916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91403102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31754684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95804882049561</t>
   </si>
   <si>
     <t xml:space="preserve">8.99473476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19282245635986</t>
+    <t xml:space="preserve">9.1928243637085</t>
   </si>
   <si>
     <t xml:space="preserve">9.13413047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34689331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3542308807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22217178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06076431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37623977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33955669403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31021118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28086376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26618957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97272491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16347694396973</t>
+    <t xml:space="preserve">9.34689521789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35422992706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22217082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06076526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37624073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33955764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31021022796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28086280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26619052886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97272396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16347789764404</t>
   </si>
   <si>
     <t xml:space="preserve">9.17815017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39825057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30287456512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2588529586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33222103118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11945724487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05342769622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00207138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96538734436035</t>
+    <t xml:space="preserve">9.39824962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3028736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25885391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33221912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11945819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05342864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00207042694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96538829803467</t>
   </si>
   <si>
     <t xml:space="preserve">9.1414680480957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01674365997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39091396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15614032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38357734680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44960784912109</t>
+    <t xml:space="preserve">9.01674461364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39091491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15614223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38357925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44960689544678</t>
   </si>
   <si>
     <t xml:space="preserve">9.49362850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52297306060791</t>
+    <t xml:space="preserve">9.52297210693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.50829982757568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79442977905273</t>
+    <t xml:space="preserve">9.79442882537842</t>
   </si>
   <si>
     <t xml:space="preserve">9.8384485244751</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">9.85312271118164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95583534240723</t>
+    <t xml:space="preserve">9.95583629608154</t>
   </si>
   <si>
     <t xml:space="preserve">10.0438747406006</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">10.1979446411133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2713108062744</t>
+    <t xml:space="preserve">10.2713088989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.90447902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0145282745361</t>
+    <t xml:space="preserve">10.0145292282104</t>
   </si>
   <si>
     <t xml:space="preserve">9.7577486038208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6550350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64769744873047</t>
+    <t xml:space="preserve">9.65503311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64769649505615</t>
   </si>
   <si>
     <t xml:space="preserve">9.80910301208496</t>
@@ -458,79 +458,79 @@
     <t xml:space="preserve">9.45694351196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41292285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61834907531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56699371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44227123260498</t>
+    <t xml:space="preserve">9.41292476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61834812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56699180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44227027893066</t>
   </si>
   <si>
     <t xml:space="preserve">9.5156364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53031063079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47895431518555</t>
+    <t xml:space="preserve">9.53030872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47895336151123</t>
   </si>
   <si>
     <t xml:space="preserve">9.63302326202393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4716157913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73573589324951</t>
+    <t xml:space="preserve">9.55965614318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47161674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73573684692383</t>
   </si>
   <si>
     <t xml:space="preserve">10.0878963470459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1245794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.051212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8677978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83111381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97050857543945</t>
+    <t xml:space="preserve">10.1245784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0512132644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86779594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83111190795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97050952911377</t>
   </si>
   <si>
     <t xml:space="preserve">9.97784614562988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81643962860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69171714782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88980484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86045932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96317291259766</t>
+    <t xml:space="preserve">9.81643867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69171619415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88980579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86046028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96317100524902</t>
   </si>
   <si>
     <t xml:space="preserve">10.0585489273071</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99251747131348</t>
+    <t xml:space="preserve">9.99251937866211</t>
   </si>
   <si>
     <t xml:space="preserve">10.1612615585327</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">9.82377624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72106266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87513160705566</t>
+    <t xml:space="preserve">9.7210636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87513256072998</t>
   </si>
   <si>
     <t xml:space="preserve">10.0365400314331</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">9.89714241027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69905281066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300046920776</t>
+    <t xml:space="preserve">9.69905376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98518371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.330005645752</t>
   </si>
   <si>
     <t xml:space="preserve">10.7335214614868</t>
@@ -578,28 +578,28 @@
     <t xml:space="preserve">10.7115106582642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6674909591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8582448959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8215599060059</t>
+    <t xml:space="preserve">10.6674900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8582429885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8215608596802</t>
   </si>
   <si>
     <t xml:space="preserve">10.9316101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8068885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1883926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2177391052246</t>
+    <t xml:space="preserve">10.8068876266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1883916854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2177400588989</t>
   </si>
   <si>
     <t xml:space="preserve">11.3424634933472</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">11.1957302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1590480804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0636701583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242734909058</t>
+    <t xml:space="preserve">11.15904712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0636711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242725372314</t>
   </si>
   <si>
     <t xml:space="preserve">11.0416603088379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1517095565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.225076675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2984437942505</t>
+    <t xml:space="preserve">11.1517114639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2250747680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2984428405762</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166328430176</t>
@@ -638,28 +638,28 @@
     <t xml:space="preserve">11.8340177536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8853759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9954261779785</t>
+    <t xml:space="preserve">11.8853750228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9954252243042</t>
   </si>
   <si>
     <t xml:space="preserve">12.6997423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.022554397583</t>
+    <t xml:space="preserve">13.022557258606</t>
   </si>
   <si>
     <t xml:space="preserve">13.0592384338379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2059707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6924085617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2815542221069</t>
+    <t xml:space="preserve">13.2059726715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6924076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2815551757812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054744720459</t>
@@ -668,76 +668,76 @@
     <t xml:space="preserve">12.1788396835327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.479642868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3255739212036</t>
+    <t xml:space="preserve">12.4796419143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3255748748779</t>
   </si>
   <si>
     <t xml:space="preserve">12.6850690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6630601882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.655722618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8024578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391389846802</t>
+    <t xml:space="preserve">12.6630611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619520187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8024559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391380310059</t>
   </si>
   <si>
     <t xml:space="preserve">13.1399431228638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.000545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491901397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0959224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0445680618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7195377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7855682373047</t>
+    <t xml:space="preserve">13.0005464553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491891860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0959243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0445671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.719536781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929048538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7855663299561</t>
   </si>
   <si>
     <t xml:space="preserve">13.8295879364014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9396390914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0643625259399</t>
+    <t xml:space="preserve">13.9396362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0643615722656</t>
   </si>
   <si>
     <t xml:space="preserve">13.6828556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7268753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8222522735596</t>
+    <t xml:space="preserve">13.7268743515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8222551345825</t>
   </si>
   <si>
     <t xml:space="preserve">13.7415466308594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9249639511108</t>
+    <t xml:space="preserve">13.9249658584595</t>
   </si>
   <si>
     <t xml:space="preserve">13.6755180358887</t>
@@ -749,175 +749,175 @@
     <t xml:space="preserve">13.4627552032471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4037733078003</t>
+    <t xml:space="preserve">13.403772354126</t>
   </si>
   <si>
     <t xml:space="preserve">13.5364818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7945327758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8903789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4922466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512294769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6618223190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9641065597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9862260818481</t>
+    <t xml:space="preserve">13.794529914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8903799057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4922475814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512285232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6618204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9641084671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9862241744995</t>
   </si>
   <si>
     <t xml:space="preserve">14.0452070236206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7429218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7650375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7502956390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6544485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9346160888672</t>
+    <t xml:space="preserve">13.7429208755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7650394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7502965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.654447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4553823471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9346151351929</t>
   </si>
   <si>
     <t xml:space="preserve">13.9714784622192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7134304046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9272432327271</t>
+    <t xml:space="preserve">13.7134323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9272403717041</t>
   </si>
   <si>
     <t xml:space="preserve">13.8830051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">14.082070350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0083446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8535146713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1973333358765</t>
+    <t xml:space="preserve">14.0820722579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0083436965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1973342895508</t>
   </si>
   <si>
     <t xml:space="preserve">13.5069932937622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3079261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3300466537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.315299987793</t>
+    <t xml:space="preserve">13.3079280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3300457000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3152990341187</t>
   </si>
   <si>
     <t xml:space="preserve">13.6470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7871589660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8092756271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.77978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9493618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1189336776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8977508544922</t>
+    <t xml:space="preserve">13.7871599197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8092775344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7797880172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8387699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9493627548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1189346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8977527618408</t>
   </si>
   <si>
     <t xml:space="preserve">13.9198703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8240232467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9419889450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8313970565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6765642166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4627523422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1014890670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5291109085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5659732818604</t>
+    <t xml:space="preserve">13.8240222930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.941987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8313941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6765651702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4627532958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816547393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.101487159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5291118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.565975189209</t>
   </si>
   <si>
     <t xml:space="preserve">13.5586004257202</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2710599899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.38902759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5807199478149</t>
+    <t xml:space="preserve">13.2710618972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3890285491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5807209014893</t>
   </si>
   <si>
     <t xml:space="preserve">13.6102142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4185171127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7060594558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7576694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6986827850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8166494369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7281770706177</t>
+    <t xml:space="preserve">13.4185190200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7060575485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7576684951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6986856460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.816650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.728178024292</t>
   </si>
   <si>
     <t xml:space="preserve">13.7355489730835</t>
@@ -926,205 +926,205 @@
     <t xml:space="preserve">13.7724142074585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6397018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6249561309814</t>
+    <t xml:space="preserve">13.6397037506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9051246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6249551773071</t>
   </si>
   <si>
     <t xml:space="preserve">13.6028356552124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7456254959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6055431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6129159927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5318117141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4728307723999</t>
+    <t xml:space="preserve">14.7456274032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6055421829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6129140853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5318126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4728317260742</t>
   </si>
   <si>
     <t xml:space="preserve">14.5613050460815</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4359664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2958831787109</t>
+    <t xml:space="preserve">14.4359674453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2958850860596</t>
   </si>
   <si>
     <t xml:space="preserve">14.3032560348511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2590217590332</t>
+    <t xml:space="preserve">14.2590179443359</t>
   </si>
   <si>
     <t xml:space="preserve">13.9124965667725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6913118362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1336832046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.030460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9567317962646</t>
+    <t xml:space="preserve">13.6913108825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1336803436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.956732749939</t>
   </si>
   <si>
     <t xml:space="preserve">14.0378370285034</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1263103485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1705446243286</t>
+    <t xml:space="preserve">14.1263065338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1705465316772</t>
   </si>
   <si>
     <t xml:space="preserve">14.2147808074951</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1557989120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0230884552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8461418151855</t>
+    <t xml:space="preserve">14.1558017730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0230875015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.104190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8461437225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.8608865737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9788522720337</t>
+    <t xml:space="preserve">13.9788541793823</t>
   </si>
   <si>
     <t xml:space="preserve">14.192663192749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2295274734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5096940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6497802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9299459457397</t>
+    <t xml:space="preserve">14.2295293807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5096969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6497793197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9299449920654</t>
   </si>
   <si>
     <t xml:space="preserve">14.8562173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7824869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.583420753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3474941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4949464797974</t>
+    <t xml:space="preserve">14.782488822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5834197998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3474922180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4949493408203</t>
   </si>
   <si>
     <t xml:space="preserve">15.2617216110229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0774040222168</t>
+    <t xml:space="preserve">15.0774011611938</t>
   </si>
   <si>
     <t xml:space="preserve">15.1511297225952</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5566358566284</t>
+    <t xml:space="preserve">15.5566329956055</t>
   </si>
   <si>
     <t xml:space="preserve">15.4091777801514</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9668102264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3354501724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4460411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0405359268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1142654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6276597976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2885093688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2737655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1852922439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5391874313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917303085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4212198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000398635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.406476020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3447895050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5217380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839389801025</t>
+    <t xml:space="preserve">14.9668083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3354482650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4460430145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0405397415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1142663955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6276617050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2885103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2737646102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1852903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5391864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4212207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000350952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4064769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3447904586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5217351913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839399337769</t>
   </si>
   <si>
     <t xml:space="preserve">13.8756341934204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9908952713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1383504867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.976149559021</t>
+    <t xml:space="preserve">12.990894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138352394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9761486053467</t>
   </si>
   <si>
     <t xml:space="preserve">12.7549667358398</t>
@@ -1136,46 +1136,46 @@
     <t xml:space="preserve">12.8876762390137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8729314804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.725474357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0793685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8286943435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5927639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5190362930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.460054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5042896270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7402229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6812381744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0646228790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2858066558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1088619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3005514144897</t>
+    <t xml:space="preserve">12.8729295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7254753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0793704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8286933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5927629470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5190353393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4600534439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5042905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7402219772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6812372207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0646238327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2858057022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1088609695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3005542755127</t>
   </si>
   <si>
     <t xml:space="preserve">14.0968179702759</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">13.3742818832397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3668699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3075971603394</t>
+    <t xml:space="preserve">13.3668718338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3075942993164</t>
   </si>
   <si>
     <t xml:space="preserve">13.1890411376953</t>
@@ -1196,67 +1196,67 @@
     <t xml:space="preserve">13.4113292694092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.485424041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9371185302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2702541351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7592878341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5962772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.68519115448</t>
+    <t xml:space="preserve">13.4854249954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9371166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2702560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7592887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5962781906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6851921081543</t>
   </si>
   <si>
     <t xml:space="preserve">13.0408515930176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9667549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1445846557617</t>
+    <t xml:space="preserve">12.9667530059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.144585609436</t>
   </si>
   <si>
     <t xml:space="preserve">12.8630208969116</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8926610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8185653686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7444686889648</t>
+    <t xml:space="preserve">12.8926591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.818564414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7444696426392</t>
   </si>
   <si>
     <t xml:space="preserve">12.9815740585327</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2483205795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2927742004395</t>
+    <t xml:space="preserve">13.2483177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2927761077881</t>
   </si>
   <si>
     <t xml:space="preserve">13.0853071212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.470606803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.529881477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4409685134888</t>
+    <t xml:space="preserve">13.4706048965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5298833847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4409675598145</t>
   </si>
   <si>
     <t xml:space="preserve">13.2779560089111</t>
@@ -1265,22 +1265,22 @@
     <t xml:space="preserve">13.3224143981934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3816928863525</t>
+    <t xml:space="preserve">13.3816900253296</t>
   </si>
   <si>
     <t xml:space="preserve">13.6039772033691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5150651931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3372325897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9299993515015</t>
+    <t xml:space="preserve">13.515064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3372344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743417739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9300003051758</t>
   </si>
   <si>
     <t xml:space="preserve">13.8855419158936</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">13.8262672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7669868469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6928930282593</t>
+    <t xml:space="preserve">13.7669887542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6928949356079</t>
   </si>
   <si>
     <t xml:space="preserve">13.7521696090698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8559036254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9892778396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2038602828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7818069458008</t>
+    <t xml:space="preserve">13.8559055328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9892768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2038621902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7818088531494</t>
   </si>
   <si>
     <t xml:space="preserve">13.9003629684448</t>
@@ -1316,61 +1316,61 @@
     <t xml:space="preserve">13.7225313186646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9596385955811</t>
+    <t xml:space="preserve">13.9596405029297</t>
   </si>
   <si>
     <t xml:space="preserve">13.7077121734619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5447006225586</t>
+    <t xml:space="preserve">13.5447015762329</t>
   </si>
   <si>
     <t xml:space="preserve">13.5595216751099</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1149444580078</t>
+    <t xml:space="preserve">13.1149454116821</t>
   </si>
   <si>
     <t xml:space="preserve">13.4261474609375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6555519104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8778409957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9222974777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1001281738281</t>
+    <t xml:space="preserve">12.655553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8778400421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9222984313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1001272201538</t>
   </si>
   <si>
     <t xml:space="preserve">13.1297645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0112113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.166522026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1517009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0479679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3739891052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4777231216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1368827819824</t>
+    <t xml:space="preserve">13.011212348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665201187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1517019271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0479669570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220636367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3739881515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4777240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1368837356567</t>
   </si>
   <si>
     <t xml:space="preserve">11.7071266174316</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">11.7812232971191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2477312088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4700202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4403829574585</t>
+    <t xml:space="preserve">11.2477331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4700193405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4403820037842</t>
   </si>
   <si>
     <t xml:space="preserve">11.5885725021362</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">11.6478500366211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5589380264282</t>
+    <t xml:space="preserve">11.5589370727539</t>
   </si>
   <si>
     <t xml:space="preserve">11.3811073303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3514680862427</t>
+    <t xml:space="preserve">11.3514671325684</t>
   </si>
   <si>
     <t xml:space="preserve">11.173638343811</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">11.1143617630005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0254468917847</t>
+    <t xml:space="preserve">11.025447845459</t>
   </si>
   <si>
     <t xml:space="preserve">10.6697874069214</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">10.4326810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7883405685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771385192871</t>
+    <t xml:space="preserve">10.7883396148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4771366119385</t>
   </si>
   <si>
     <t xml:space="preserve">10.551233291626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8920745849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9661703109741</t>
+    <t xml:space="preserve">10.8920736312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9661712646484</t>
   </si>
   <si>
     <t xml:space="preserve">11.0995426177979</t>
@@ -1445,34 +1445,34 @@
     <t xml:space="preserve">10.0770215988159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3751106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8706388473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8241844177246</t>
+    <t xml:space="preserve">10.375111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8706378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8241834640503</t>
   </si>
   <si>
     <t xml:space="preserve">10.4835071563721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609340667725</t>
+    <t xml:space="preserve">10.5609331130981</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6538457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3042268753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7467575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6073894500732</t>
+    <t xml:space="preserve">10.6538467407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3042249679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7467565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6073904037476</t>
   </si>
   <si>
     <t xml:space="preserve">10.5299644470215</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">10.7622423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7777271270752</t>
+    <t xml:space="preserve">10.7777280807495</t>
   </si>
   <si>
     <t xml:space="preserve">10.7312717437744</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">10.4525375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4060821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9945211410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0874309539795</t>
+    <t xml:space="preserve">10.406081199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9945201873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0874300003052</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493730545044</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">10.9480657577515</t>
   </si>
   <si>
-    <t xml:space="preserve">11.040976524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3286552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4370517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5919046401978</t>
+    <t xml:space="preserve">11.0409774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3286561965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4370527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5919055938721</t>
   </si>
   <si>
     <t xml:space="preserve">10.4989929199219</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">10.3596248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6693296432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228761672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8551540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1184034347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3816518783569</t>
+    <t xml:space="preserve">10.6693305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.622875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8551549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1184005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3816509246826</t>
   </si>
   <si>
     <t xml:space="preserve">11.3661661148071</t>
@@ -1562,34 +1562,34 @@
     <t xml:space="preserve">11.3506813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9790363311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7932109832764</t>
+    <t xml:space="preserve">10.9790353775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.793212890625</t>
   </si>
   <si>
     <t xml:space="preserve">10.8861236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5764188766479</t>
+    <t xml:space="preserve">10.5764198303223</t>
   </si>
   <si>
     <t xml:space="preserve">10.2047729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1118631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0808925628662</t>
+    <t xml:space="preserve">10.1118621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0808935165405</t>
   </si>
   <si>
     <t xml:space="preserve">9.6782751083374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56987953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75570297241211</t>
+    <t xml:space="preserve">9.56987762451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75570201873779</t>
   </si>
   <si>
     <t xml:space="preserve">9.95700931549072</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">9.86409759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94152450561523</t>
+    <t xml:space="preserve">9.94152545928955</t>
   </si>
   <si>
     <t xml:space="preserve">9.92603874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.158317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1428318023682</t>
+    <t xml:space="preserve">10.1583185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1428327560425</t>
   </si>
   <si>
     <t xml:space="preserve">9.91055393218994</t>
@@ -1619,58 +1619,58 @@
     <t xml:space="preserve">10.1273469924927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3441390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6383590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7157859802246</t>
+    <t xml:space="preserve">10.3441400527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6383609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7157869338989</t>
   </si>
   <si>
     <t xml:space="preserve">10.6848154067993</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0344343185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.018949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97249698638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2202587127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81734943389893</t>
+    <t xml:space="preserve">10.0344352722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0189485549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97249603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2202577590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81734848022461</t>
   </si>
   <si>
     <t xml:space="preserve">10.0666780471802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1445932388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3160085678101</t>
+    <t xml:space="preserve">10.1445941925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3160066604614</t>
   </si>
   <si>
     <t xml:space="preserve">10.4874219894409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.503005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3004236221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91084861755371</t>
+    <t xml:space="preserve">10.5030040740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.30042552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91084766387939</t>
   </si>
   <si>
     <t xml:space="preserve">10.0043449401855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87968063354492</t>
+    <t xml:space="preserve">9.87967967987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.895263671875</t>
@@ -1679,61 +1679,61 @@
     <t xml:space="preserve">9.98876190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0510950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0822620391846</t>
+    <t xml:space="preserve">10.0510940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0822601318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.1134271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3627576828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3939247131348</t>
+    <t xml:space="preserve">10.362756729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3939237594604</t>
   </si>
   <si>
     <t xml:space="preserve">10.6744194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5341720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.425087928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6276702880859</t>
+    <t xml:space="preserve">10.5341701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4250888824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6276693344116</t>
   </si>
   <si>
     <t xml:space="preserve">10.4406709671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1290102005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2225093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1913433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2069253921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4562568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3783388137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6432514190674</t>
+    <t xml:space="preserve">10.1290111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.222508430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1913423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2069272994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4562559127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3783407211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.643253326416</t>
   </si>
   <si>
     <t xml:space="preserve">10.8302488327026</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7523345947266</t>
+    <t xml:space="preserve">10.7523355484009</t>
   </si>
   <si>
     <t xml:space="preserve">11.0795793533325</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">10.6900014877319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7679176330566</t>
+    <t xml:space="preserve">10.7679166793823</t>
   </si>
   <si>
     <t xml:space="preserve">11.2198276519775</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">11.1574935913086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2536754608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2848405838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2380924224854</t>
+    <t xml:space="preserve">10.2536745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.284839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2380933761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.1601753234863</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">10.4095058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0355129241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1757612228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8146667480469</t>
+    <t xml:space="preserve">10.03551197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.175760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8146677017212</t>
   </si>
   <si>
     <t xml:space="preserve">11.1263275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0484142303467</t>
+    <t xml:space="preserve">11.0484132766724</t>
   </si>
   <si>
     <t xml:space="preserve">11.1419115066528</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.032829284668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7367496490479</t>
+    <t xml:space="preserve">10.7367506027222</t>
   </si>
   <si>
     <t xml:space="preserve">10.5965023040771</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">10.7211675643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9081659317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237480163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7834997177124</t>
+    <t xml:space="preserve">10.9081649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237489700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.783501625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.8769979476929</t>
@@ -1826,94 +1826,94 @@
     <t xml:space="preserve">11.5470714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8587350845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9054832458496</t>
+    <t xml:space="preserve">11.8587331771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9054841995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.6561546325684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275671005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7340688705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9989805221558</t>
+    <t xml:space="preserve">11.8275661468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7340698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9989814758301</t>
   </si>
   <si>
     <t xml:space="preserve">11.8743171691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9210662841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0768995285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.843150138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7652368545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8899002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8119840621948</t>
+    <t xml:space="preserve">11.9210653305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0768976211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8431510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7652349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8898992538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8119850158691</t>
   </si>
   <si>
     <t xml:space="preserve">11.1107454299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9860792160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3444929122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7808179855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0301485061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9366502761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7964019775391</t>
+    <t xml:space="preserve">10.9860811233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3444919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.780818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0301475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9366493225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7964010238647</t>
   </si>
   <si>
     <t xml:space="preserve">11.6249885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4691553115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5626544952393</t>
+    <t xml:space="preserve">11.4691562652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5626554489136</t>
   </si>
   <si>
     <t xml:space="preserve">11.4379901885986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5314893722534</t>
+    <t xml:space="preserve">11.5314884185791</t>
   </si>
   <si>
     <t xml:space="preserve">11.3756589889526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4535732269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4224071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886606216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2977409362793</t>
+    <t xml:space="preserve">11.4535722732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4224061965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2977428436279</t>
   </si>
   <si>
     <t xml:space="preserve">11.2821588516235</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">10.705584526062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8925828933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6588354110718</t>
+    <t xml:space="preserve">10.8925819396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6588363647461</t>
   </si>
   <si>
     <t xml:space="preserve">10.3315906524658</t>
@@ -1937,25 +1937,25 @@
     <t xml:space="preserve">10.0199279785156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97317981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0978450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94201374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80176544189453</t>
+    <t xml:space="preserve">9.97318077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0978441238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94201469421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80176448822021</t>
   </si>
   <si>
     <t xml:space="preserve">9.92642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97586154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86677932739258</t>
+    <t xml:space="preserve">8.97586250305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86678123474121</t>
   </si>
   <si>
     <t xml:space="preserve">9.13169288635254</t>
@@ -1964,19 +1964,19 @@
     <t xml:space="preserve">9.02260971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80444717407227</t>
+    <t xml:space="preserve">8.8044490814209</t>
   </si>
   <si>
     <t xml:space="preserve">8.47720241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38370418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25903987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24345684051514</t>
+    <t xml:space="preserve">8.38370323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25904083251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2434549331665</t>
   </si>
   <si>
     <t xml:space="preserve">8.14995765686035</t>
@@ -1985,28 +1985,28 @@
     <t xml:space="preserve">7.48767566680908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11368227005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03576564788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15532255172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42023420333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16311311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85924291610718</t>
+    <t xml:space="preserve">7.11368179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0357666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15532159805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42023468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16311359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85924243927002</t>
   </si>
   <si>
     <t xml:space="preserve">5.25929403305054</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29045963287354</t>
+    <t xml:space="preserve">5.29046010971069</t>
   </si>
   <si>
     <t xml:space="preserve">5.53199815750122</t>
@@ -2015,10 +2015,10 @@
     <t xml:space="preserve">5.61770486831665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49303960800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37616729736328</t>
+    <t xml:space="preserve">5.49304056167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37616777420044</t>
   </si>
   <si>
     <t xml:space="preserve">5.08008766174316</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">5.36058378219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32941770553589</t>
+    <t xml:space="preserve">5.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">5.35279226303101</t>
@@ -2036,55 +2036,55 @@
     <t xml:space="preserve">5.29825115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45408296585083</t>
+    <t xml:space="preserve">5.45408248901367</t>
   </si>
   <si>
     <t xml:space="preserve">5.47745752334595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76574468612671</t>
+    <t xml:space="preserve">5.76574420928955</t>
   </si>
   <si>
     <t xml:space="preserve">5.5086236000061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92157506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87482643127441</t>
+    <t xml:space="preserve">5.92157554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87482595443726</t>
   </si>
   <si>
     <t xml:space="preserve">5.80470180511475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8358678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89820098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27219438552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25661182403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33452749252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42802572250366</t>
+    <t xml:space="preserve">5.83586740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89820051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27219486236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25661087036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33452701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4280252456665</t>
   </si>
   <si>
     <t xml:space="preserve">6.17090511322021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45919132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23323774337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24882030487061</t>
+    <t xml:space="preserve">6.45919227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23323726654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24882125854492</t>
   </si>
   <si>
     <t xml:space="preserve">6.12415599822998</t>
@@ -2096,25 +2096,25 @@
     <t xml:space="preserve">5.71899509429932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86703443527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94495010375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92936754226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03844976425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22544527053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35790157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5838565826416</t>
+    <t xml:space="preserve">5.86703491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94494962692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92936658859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03844881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22544574737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35790205001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58385705947876</t>
   </si>
   <si>
     <t xml:space="preserve">6.50594139099121</t>
@@ -2123,22 +2123,22 @@
     <t xml:space="preserve">6.49035835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47477531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62281465530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08251571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27730417251587</t>
+    <t xml:space="preserve">6.47477579116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6228141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08251619338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27730369567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.09030771255493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05914211273193</t>
+    <t xml:space="preserve">7.05914163589478</t>
   </si>
   <si>
     <t xml:space="preserve">6.8955192565918</t>
@@ -2150,46 +2150,46 @@
     <t xml:space="preserve">6.60723114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76306295394897</t>
+    <t xml:space="preserve">6.76306200027466</t>
   </si>
   <si>
     <t xml:space="preserve">6.55269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56827354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68514680862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84097719192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65398073196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01239156723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98122549057007</t>
+    <t xml:space="preserve">6.56827449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68514728546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75527143478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84097671508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65398025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01239204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98122501373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.8565616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78643703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71631288528442</t>
+    <t xml:space="preserve">6.78643751144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71631336212158</t>
   </si>
   <si>
     <t xml:space="preserve">6.7318959236145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86435270309448</t>
+    <t xml:space="preserve">6.8643536567688</t>
   </si>
   <si>
     <t xml:space="preserve">6.66177225112915</t>
@@ -2198,58 +2198,58 @@
     <t xml:space="preserve">6.72410488128662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38906812667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24102926254272</t>
+    <t xml:space="preserve">6.38906860351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24102878570557</t>
   </si>
   <si>
     <t xml:space="preserve">6.20207071304321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4514012336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4358172416687</t>
+    <t xml:space="preserve">6.45140075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43581771850586</t>
   </si>
   <si>
     <t xml:space="preserve">6.49814939498901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28777742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31115341186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.326735496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1319465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01507425308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09298992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07740640640259</t>
+    <t xml:space="preserve">6.2877779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31115293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32673597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13194704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01507377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09298896789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07740592956543</t>
   </si>
   <si>
     <t xml:space="preserve">6.00728225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9527416229248</t>
+    <t xml:space="preserve">5.95274209976196</t>
   </si>
   <si>
     <t xml:space="preserve">5.93715858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72678661346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84365892410278</t>
+    <t xml:space="preserve">5.7267861366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8436598777771</t>
   </si>
   <si>
     <t xml:space="preserve">5.69562005996704</t>
@@ -2264,58 +2264,58 @@
     <t xml:space="preserve">5.56316375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54758071899414</t>
+    <t xml:space="preserve">5.5475811958313</t>
   </si>
   <si>
     <t xml:space="preserve">5.48524856567383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52420711517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74237012863159</t>
+    <t xml:space="preserve">5.52420663833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74236965179443</t>
   </si>
   <si>
     <t xml:space="preserve">5.75795269012451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73457765579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79691028594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90599203109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96053314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68003797531128</t>
+    <t xml:space="preserve">5.73457813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79691076278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90599250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96053266525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68003749847412</t>
   </si>
   <si>
     <t xml:space="preserve">5.8514518737793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78132724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04623985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91378355026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67224645614624</t>
+    <t xml:space="preserve">5.78132772445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04624032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91378307342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67224597930908</t>
   </si>
   <si>
     <t xml:space="preserve">5.51641464233398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46187400817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15800428390503</t>
+    <t xml:space="preserve">5.46187448501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15800333023071</t>
   </si>
   <si>
     <t xml:space="preserve">4.99438095092773</t>
@@ -2327,46 +2327,46 @@
     <t xml:space="preserve">4.7606348991394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80738401412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83075904846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02554750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18137884140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06182241439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02286529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10078144073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99680757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23055505752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05135011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93447685241699</t>
+    <t xml:space="preserve">4.8073844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8307580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02554702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18137836456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06182289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02286577224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10078096389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99680805206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23055553436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05134963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93447589874268</t>
   </si>
   <si>
     <t xml:space="preserve">6.92668533325195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82539415359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77864599227905</t>
+    <t xml:space="preserve">6.82539558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77864503860474</t>
   </si>
   <si>
     <t xml:space="preserve">6.87214279174805</t>
@@ -2375,79 +2375,79 @@
     <t xml:space="preserve">6.91110134124756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77085447311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66956472396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63060617446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97343397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63839817047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7007303237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80981254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98901700973511</t>
+    <t xml:space="preserve">6.77085304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66956377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63060569763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97343444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63839769363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70072984695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80981159210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98901748657227</t>
   </si>
   <si>
     <t xml:space="preserve">7.14484834671021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95785045623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87993574142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00460004806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16043090820312</t>
+    <t xml:space="preserve">6.95785140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87993478775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0046010017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16043138504028</t>
   </si>
   <si>
     <t xml:space="preserve">7.1760139465332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37859582901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38638687133789</t>
+    <t xml:space="preserve">7.37859487533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38638496398926</t>
   </si>
   <si>
     <t xml:space="preserve">7.13705635070801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09809875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53710842132568</t>
+    <t xml:space="preserve">7.09809923171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53710794448853</t>
   </si>
   <si>
     <t xml:space="preserve">6.59164810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5760645866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79422855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0747241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22276449203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28509664535522</t>
+    <t xml:space="preserve">6.57606554031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79422903060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07472324371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22276401519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28509569168091</t>
   </si>
   <si>
     <t xml:space="preserve">7.25392961502075</t>
@@ -2456,13 +2456,13 @@
     <t xml:space="preserve">7.45650959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65909051895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61234140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53442525863647</t>
+    <t xml:space="preserve">7.65909004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61234092712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53442573547363</t>
   </si>
   <si>
     <t xml:space="preserve">7.49546766281128</t>
@@ -2471,37 +2471,37 @@
     <t xml:space="preserve">7.57338285446167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47209310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50326013565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40196847915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26172065734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30067825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12926387786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24613857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51884269714355</t>
+    <t xml:space="preserve">7.472092628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50325965881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40196943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26172208786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3006796836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12926530838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2461371421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51884174346924</t>
   </si>
   <si>
     <t xml:space="preserve">7.91621160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7915472984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80712985992432</t>
+    <t xml:space="preserve">7.79154586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80712938308716</t>
   </si>
   <si>
     <t xml:space="preserve">7.71363019943237</t>
@@ -2513,193 +2513,193 @@
     <t xml:space="preserve">7.54221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23834657669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37080335617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43313598632812</t>
+    <t xml:space="preserve">7.23834609985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3708028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43313646316528</t>
   </si>
   <si>
     <t xml:space="preserve">8.02529335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90062952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946249008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72142171859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46430253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73700618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78375482559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65129804611206</t>
+    <t xml:space="preserve">7.90062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946153640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72142219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46430206298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73700714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7837553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65129852294922</t>
   </si>
   <si>
     <t xml:space="preserve">7.58896636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68246507644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72921323776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62013149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39417791366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40976047515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59675788879395</t>
+    <t xml:space="preserve">7.68246412277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72921371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62013292312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39417695999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40976095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59675693511963</t>
   </si>
   <si>
     <t xml:space="preserve">7.74479675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21228885650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29020690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1032075881958</t>
+    <t xml:space="preserve">8.21228790283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29020595550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10320854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08762454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18221664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02456378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96150207519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15068626403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54481983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68670845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95471858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00201606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06507587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12813758850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20696544647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14390468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93895530700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97048568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98625087738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8285961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78130054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63941287994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5132884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65517711639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73400497436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45022869110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37139987945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46599388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57635116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52905559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.355637550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07185935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21374702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22951316833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2768087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24527835845947</t>
   </si>
   <si>
     <t xml:space="preserve">8.08762550354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18221759796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02456283569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96150302886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15068626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54481983184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68670749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95471954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00201606750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06507682800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12813758850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20696544647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15966987609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14390468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9389533996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97048377990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98624897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8285961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78130054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63941192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51328945159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65517807006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73400497436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45022773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37140083312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46599388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57635116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52905368804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35563659667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07185935974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21374893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22951126098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27680969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24527835845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08762454986572</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.05609512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89844131469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94573640823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99303436279297</t>
+    <t xml:space="preserve">7.89844083786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94573736190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99303293228149</t>
   </si>
   <si>
     <t xml:space="preserve">8.40293121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4817590713501</t>
+    <t xml:space="preserve">8.48175811767578</t>
   </si>
   <si>
     <t xml:space="preserve">8.32410621643066</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">8.7970666885376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33987140655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38716793060303</t>
+    <t xml:space="preserve">8.33986949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38716697692871</t>
   </si>
   <si>
     <t xml:space="preserve">8.29257583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26104354858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19798183441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59211730957031</t>
+    <t xml:space="preserve">8.2610445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19798278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.592116355896</t>
   </si>
   <si>
     <t xml:space="preserve">8.60788154602051</t>
@@ -2744,64 +2744,64 @@
     <t xml:space="preserve">7.92997169494629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84326124191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91420698165894</t>
+    <t xml:space="preserve">7.84326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91420555114746</t>
   </si>
   <si>
     <t xml:space="preserve">7.8038477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64619445800781</t>
+    <t xml:space="preserve">7.64619588851929</t>
   </si>
   <si>
     <t xml:space="preserve">7.66196012496948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85902786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61466407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60678243637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70137453079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78808307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65407752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79596614837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673680305481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6225471496582</t>
+    <t xml:space="preserve">7.85902690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61466503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60678148269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70137405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78808355331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65407705307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56736850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62254762649536</t>
   </si>
   <si>
     <t xml:space="preserve">7.67772626876831</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50430727005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63831281661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74867057800293</t>
+    <t xml:space="preserve">7.50430822372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63831186294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74867010116577</t>
   </si>
   <si>
     <t xml:space="preserve">7.7644362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8274974822998</t>
+    <t xml:space="preserve">7.82749843597412</t>
   </si>
   <si>
     <t xml:space="preserve">8.67094326019287</t>
@@ -2810,73 +2810,73 @@
     <t xml:space="preserve">8.62364673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74977016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.559485912323</t>
+    <t xml:space="preserve">8.74976921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55948543548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.54372024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25206089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28359222412109</t>
+    <t xml:space="preserve">7.25206136703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28359317779541</t>
   </si>
   <si>
     <t xml:space="preserve">7.27570962905884</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85792827606201</t>
+    <t xml:space="preserve">6.8579273223877</t>
   </si>
   <si>
     <t xml:space="preserve">6.9131064414978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82639646530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08652496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99981594085693</t>
+    <t xml:space="preserve">6.82639741897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08652591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99981641769409</t>
   </si>
   <si>
     <t xml:space="preserve">6.93675518035889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37030220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23629665374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21264696121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1259388923645</t>
+    <t xml:space="preserve">7.37030124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2362961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21264839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12593841552734</t>
   </si>
   <si>
     <t xml:space="preserve">7.0313458442688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14958763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09440755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13382196426392</t>
+    <t xml:space="preserve">7.14958715438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09440803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13382148742676</t>
   </si>
   <si>
     <t xml:space="preserve">7.33877086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38606595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47277736663818</t>
+    <t xml:space="preserve">7.38606786727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47277545928955</t>
   </si>
   <si>
     <t xml:space="preserve">7.86690998077393</t>
@@ -2885,82 +2885,82 @@
     <t xml:space="preserve">7.78020048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74078702926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46489524841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52795457839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68560886383057</t>
+    <t xml:space="preserve">7.74078750610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46489429473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52795505523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68560791015625</t>
   </si>
   <si>
     <t xml:space="preserve">7.58313369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48854112625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45701169967651</t>
+    <t xml:space="preserve">7.48854207992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45701122283936</t>
   </si>
   <si>
     <t xml:space="preserve">7.37818479537964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35453605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11805534362793</t>
+    <t xml:space="preserve">7.35453701019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11805629730225</t>
   </si>
   <si>
     <t xml:space="preserve">6.99193286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34665298461914</t>
+    <t xml:space="preserve">7.34665441513062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1732349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29147529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36241865158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19688320159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10229158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44124460220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33088874816895</t>
+    <t xml:space="preserve">7.29147434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36241817474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19688272476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10229110717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44124507904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33088731765747</t>
   </si>
   <si>
     <t xml:space="preserve">7.4097146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49642419815063</t>
+    <t xml:space="preserve">7.49642467498779</t>
   </si>
   <si>
     <t xml:space="preserve">7.39394950866699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26782703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15746927261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61356592178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44014644622803</t>
+    <t xml:space="preserve">7.26782751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15746831893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61356544494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44014596939087</t>
   </si>
   <si>
     <t xml:space="preserve">6.60568237304688</t>
@@ -2969,49 +2969,49 @@
     <t xml:space="preserve">6.810631275177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98405075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18111753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18900108337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06287717819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11017274856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88267660140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81173086166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69349193572998</t>
+    <t xml:space="preserve">6.98405027389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18111801147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18899917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06287670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11017322540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88267517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81173133850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69349145889282</t>
   </si>
   <si>
     <t xml:space="preserve">7.75655269622803</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73290491104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42548131942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48065948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51219034194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52007293701172</t>
+    <t xml:space="preserve">7.7329044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42547988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48065853118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51218891143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52007341384888</t>
   </si>
   <si>
     <t xml:space="preserve">7.22841358184814</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">7.00769901275635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44912815093994</t>
+    <t xml:space="preserve">7.44912910461426</t>
   </si>
   <si>
     <t xml:space="preserve">7.4154257774353</t>
@@ -3032,10 +3032,10 @@
     <t xml:space="preserve">7.31838655471802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2941255569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48011827468872</t>
+    <t xml:space="preserve">7.29412698745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4801173210144</t>
   </si>
   <si>
     <t xml:space="preserve">7.56098508834839</t>
@@ -3044,19 +3044,19 @@
     <t xml:space="preserve">7.63376331329346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5448112487793</t>
+    <t xml:space="preserve">7.54481172561646</t>
   </si>
   <si>
     <t xml:space="preserve">7.43968486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48820495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46394491195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32647371292114</t>
+    <t xml:space="preserve">7.48820543289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46394538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32647323608398</t>
   </si>
   <si>
     <t xml:space="preserve">7.05152797698975</t>
@@ -3068,73 +3068,73 @@
     <t xml:space="preserve">6.94640207290649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76040983200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75232267379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71189022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86553525924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73615026473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74423599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81701564788818</t>
+    <t xml:space="preserve">6.76040935516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75232315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71188974380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86553573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73614978790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74423694610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81701612472534</t>
   </si>
   <si>
     <t xml:space="preserve">6.87362241744995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80084228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71997690200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63102340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70380258560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46929216384888</t>
+    <t xml:space="preserve">6.80084276199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71997737884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63102436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70380353927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46929121017456</t>
   </si>
   <si>
     <t xml:space="preserve">6.48546504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57441854476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69571733474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64719724655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63911056518555</t>
+    <t xml:space="preserve">6.57441806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.695716381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64719772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63911008834839</t>
   </si>
   <si>
     <t xml:space="preserve">6.55015802383423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60676431655884</t>
+    <t xml:space="preserve">6.60676383972168</t>
   </si>
   <si>
     <t xml:space="preserve">6.62293720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47737836837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4045991897583</t>
+    <t xml:space="preserve">6.47737789154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40459823608398</t>
   </si>
   <si>
     <t xml:space="preserve">6.41268539428711</t>
@@ -3143,85 +3143,85 @@
     <t xml:space="preserve">6.65528392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84127521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72806310653687</t>
+    <t xml:space="preserve">6.84127616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72806358337402</t>
   </si>
   <si>
     <t xml:space="preserve">6.67145681381226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7684965133667</t>
+    <t xml:space="preserve">6.76849603652954</t>
   </si>
   <si>
     <t xml:space="preserve">6.50163793563843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46120452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49355125427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44503116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38842630386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29138565063477</t>
+    <t xml:space="preserve">6.46120548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4935507774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44503164291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38842535018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29138660430908</t>
   </si>
   <si>
     <t xml:space="preserve">6.11348056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19434690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08922052383423</t>
+    <t xml:space="preserve">6.19434642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08922100067139</t>
   </si>
   <si>
     <t xml:space="preserve">6.13774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95174789428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95983505249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90322875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06496047973633</t>
+    <t xml:space="preserve">5.95174884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95983457565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98409509658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90322923660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06496095657349</t>
   </si>
   <si>
     <t xml:space="preserve">6.18626022338867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02452754974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91131496429443</t>
+    <t xml:space="preserve">6.02452707290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91131544113159</t>
   </si>
   <si>
     <t xml:space="preserve">5.86279535293579</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88705587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79001569747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83044862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81427574157715</t>
+    <t xml:space="preserve">5.88705539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79001617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83044910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81427526473999</t>
   </si>
   <si>
     <t xml:space="preserve">5.6363697052002</t>
@@ -3233,85 +3233,85 @@
     <t xml:space="preserve">5.74958276748657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7334098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67680311203003</t>
+    <t xml:space="preserve">5.73340940475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67680358886719</t>
   </si>
   <si>
     <t xml:space="preserve">5.78192949295044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74149656295776</t>
+    <t xml:space="preserve">5.74149608612061</t>
   </si>
   <si>
     <t xml:space="preserve">5.62828397750854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45846462249756</t>
+    <t xml:space="preserve">5.45846509933472</t>
   </si>
   <si>
     <t xml:space="preserve">5.39377212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33716487884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38568496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36142539978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42611885070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43420505523682</t>
+    <t xml:space="preserve">5.33716535568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38568544387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36142492294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42611837387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43420457839966</t>
   </si>
   <si>
     <t xml:space="preserve">5.28056001663208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26438617706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34525203704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40994453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35333919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5797643661499</t>
+    <t xml:space="preserve">5.26438570022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3452525138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40994548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35333871841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57976388931274</t>
   </si>
   <si>
     <t xml:space="preserve">5.82236242294312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68489027023315</t>
+    <t xml:space="preserve">5.68489074707031</t>
   </si>
   <si>
     <t xml:space="preserve">5.79810285568237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.555504322052</t>
+    <t xml:space="preserve">5.55550384521484</t>
   </si>
   <si>
     <t xml:space="preserve">5.93557500839233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75766944885254</t>
+    <t xml:space="preserve">5.7576699256897</t>
   </si>
   <si>
     <t xml:space="preserve">5.66063022613525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61211061477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65254402160645</t>
+    <t xml:space="preserve">5.61211109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65254306793213</t>
   </si>
   <si>
     <t xml:space="preserve">5.48272466659546</t>
@@ -3326,34 +3326,34 @@
     <t xml:space="preserve">5.50698471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64445638656616</t>
+    <t xml:space="preserve">5.644455909729</t>
   </si>
   <si>
     <t xml:space="preserve">5.52315759658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70106315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57167673110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46655178070068</t>
+    <t xml:space="preserve">5.70106363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57167768478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46655225753784</t>
   </si>
   <si>
     <t xml:space="preserve">5.60402393341064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49081087112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56359052658081</t>
+    <t xml:space="preserve">5.49081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56359148025513</t>
   </si>
   <si>
     <t xml:space="preserve">5.41803169250488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44229173660278</t>
+    <t xml:space="preserve">5.44229125976562</t>
   </si>
   <si>
     <t xml:space="preserve">5.53933095932007</t>
@@ -3365,19 +3365,19 @@
     <t xml:space="preserve">5.66871690750122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9679217338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14582681655884</t>
+    <t xml:space="preserve">5.96792125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.145827293396</t>
   </si>
   <si>
     <t xml:space="preserve">6.17817354202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21860694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03261470794678</t>
+    <t xml:space="preserve">6.21860647201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03261375427246</t>
   </si>
   <si>
     <t xml:space="preserve">5.97600793838501</t>
@@ -3392,25 +3392,25 @@
     <t xml:space="preserve">5.80618906021118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87896919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85470867156982</t>
+    <t xml:space="preserve">5.87896871566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85470914840698</t>
   </si>
   <si>
     <t xml:space="preserve">6.1215672492981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09730768203735</t>
+    <t xml:space="preserve">6.0973072052002</t>
   </si>
   <si>
     <t xml:space="preserve">6.16200017929077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07304763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08113431930542</t>
+    <t xml:space="preserve">6.07304811477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08113384246826</t>
   </si>
   <si>
     <t xml:space="preserve">6.05687427520752</t>
@@ -3419,37 +3419,37 @@
     <t xml:space="preserve">6.04070091247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10539436340332</t>
+    <t xml:space="preserve">6.105393409729</t>
   </si>
   <si>
     <t xml:space="preserve">6.04878807067871</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72532320022583</t>
+    <t xml:space="preserve">5.72532272338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.59593677520752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58785104751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30755949020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84662199020386</t>
+    <t xml:space="preserve">5.58785009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3075590133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84662246704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.83853530883789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00835466384888</t>
+    <t xml:space="preserve">6.00835418701172</t>
   </si>
   <si>
     <t xml:space="preserve">6.12965393066406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16357803344727</t>
+    <t xml:space="preserve">6.16357755661011</t>
   </si>
   <si>
     <t xml:space="preserve">6.2046685218811</t>
@@ -3458,13 +3458,13 @@
     <t xml:space="preserve">6.01565217971802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49230289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47586631774902</t>
+    <t xml:space="preserve">6.29506731033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49230194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47586584091187</t>
   </si>
   <si>
     <t xml:space="preserve">6.46764802932739</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">6.5005202293396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59913682937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58270168304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5169563293457</t>
+    <t xml:space="preserve">6.59913730621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58270120620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51695680618286</t>
   </si>
   <si>
     <t xml:space="preserve">6.45121145248413</t>
@@ -3491,22 +3491,22 @@
     <t xml:space="preserve">6.41012144088745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36903047561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33615779876709</t>
+    <t xml:space="preserve">6.36903095245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33615827560425</t>
   </si>
   <si>
     <t xml:space="preserve">6.52517461776733</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57448291778564</t>
+    <t xml:space="preserve">6.5744833946228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45942974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54982900619507</t>
+    <t xml:space="preserve">6.54982852935791</t>
   </si>
   <si>
     <t xml:space="preserve">6.50873851776123</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">6.44299364089966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41833925247192</t>
+    <t xml:space="preserve">6.41833877563477</t>
   </si>
   <si>
     <t xml:space="preserve">6.43477535247803</t>
@@ -3524,25 +3524,25 @@
     <t xml:space="preserve">6.36081218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34437608718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11426877975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13070583343506</t>
+    <t xml:space="preserve">6.34437656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11426973342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1307053565979</t>
   </si>
   <si>
     <t xml:space="preserve">6.13892364501953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25397729873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26219511032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31972169876099</t>
+    <t xml:space="preserve">6.25397682189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2621955871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31972217559814</t>
   </si>
   <si>
     <t xml:space="preserve">6.35259437561035</t>
@@ -3551,16 +3551,16 @@
     <t xml:space="preserve">6.30328607559204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21288681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37724876403809</t>
+    <t xml:space="preserve">6.21288633346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37724828720093</t>
   </si>
   <si>
     <t xml:space="preserve">6.48408365249634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56626462936401</t>
+    <t xml:space="preserve">6.56626510620117</t>
   </si>
   <si>
     <t xml:space="preserve">6.64022827148438</t>
@@ -3575,19 +3575,19 @@
     <t xml:space="preserve">6.55804681777954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80459070205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88677167892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83746242523193</t>
+    <t xml:space="preserve">6.80459022521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8867712020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83746194839478</t>
   </si>
   <si>
     <t xml:space="preserve">6.69775438308716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61557388305664</t>
+    <t xml:space="preserve">6.61557340621948</t>
   </si>
   <si>
     <t xml:space="preserve">6.70597267150879</t>
@@ -3596,49 +3596,46 @@
     <t xml:space="preserve">6.63200950622559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62379217147827</t>
+    <t xml:space="preserve">6.62379264831543</t>
   </si>
   <si>
     <t xml:space="preserve">6.82924461364746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94429731369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87855291366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77993583679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79637289047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90320634841919</t>
+    <t xml:space="preserve">6.94429779052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87855243682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77993535995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7963719367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90320730209351</t>
   </si>
   <si>
     <t xml:space="preserve">6.84568023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85389852523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72241020202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68131875991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68953657150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27863121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08961486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06496095657349</t>
+    <t xml:space="preserve">6.8538990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68131923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68953704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27863168716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0896143913269</t>
   </si>
   <si>
     <t xml:space="preserve">6.07317876815796</t>
@@ -3647,37 +3644,37 @@
     <t xml:space="preserve">6.04852437973022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15536022186279</t>
+    <t xml:space="preserve">6.15535974502563</t>
   </si>
   <si>
     <t xml:space="preserve">5.99921607971191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94168901443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05674266815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8759446144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95812559127808</t>
+    <t xml:space="preserve">5.94168949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05674314498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95812511444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.08139705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03208780288696</t>
+    <t xml:space="preserve">6.03208875656128</t>
   </si>
   <si>
     <t xml:space="preserve">5.8923807144165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85129022598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90881729125977</t>
+    <t xml:space="preserve">5.85128974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90881633758545</t>
   </si>
   <si>
     <t xml:space="preserve">5.78554487228394</t>
@@ -3689,28 +3686,28 @@
     <t xml:space="preserve">5.64583730697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71158170700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71979999542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82663631439209</t>
+    <t xml:space="preserve">5.71158218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71980047225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82663583755493</t>
   </si>
   <si>
     <t xml:space="preserve">5.86772584915161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.188232421875</t>
+    <t xml:space="preserve">6.18823289871216</t>
   </si>
   <si>
     <t xml:space="preserve">6.12248706817627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14714193344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28684902191162</t>
+    <t xml:space="preserve">6.147141456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28684997558594</t>
   </si>
   <si>
     <t xml:space="preserve">6.40190267562866</t>
@@ -3719,7 +3716,7 @@
     <t xml:space="preserve">6.76349925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66488218307495</t>
+    <t xml:space="preserve">6.66488170623779</t>
   </si>
   <si>
     <t xml:space="preserve">6.738844871521</t>
@@ -3731,10 +3728,10 @@
     <t xml:space="preserve">6.93607950210571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99360656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06757020950317</t>
+    <t xml:space="preserve">6.99360704421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06756973266602</t>
   </si>
   <si>
     <t xml:space="preserve">7.240149974823</t>
@@ -3743,16 +3740,16 @@
     <t xml:space="preserve">7.13331460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98538827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1250958442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07578659057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16618633270264</t>
+    <t xml:space="preserve">6.98538875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12509536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07578754425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16618680953979</t>
   </si>
   <si>
     <t xml:space="preserve">7.14975070953369</t>
@@ -3761,25 +3758,25 @@
     <t xml:space="preserve">7.19084119796753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1826229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28124046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21549463272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17440462112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09222364425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.199059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05113315582275</t>
+    <t xml:space="preserve">7.18262243270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28123950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21549510955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17440366744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09222412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19905948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0511326789856</t>
   </si>
   <si>
     <t xml:space="preserve">7.03469753265381</t>
@@ -3791,19 +3788,19 @@
     <t xml:space="preserve">7.48669195175171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36342191696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35520315170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28945827484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37163877487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57709217071533</t>
+    <t xml:space="preserve">7.36342144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35520267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28945779800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3716402053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57709264755249</t>
   </si>
   <si>
     <t xml:space="preserve">7.73323583602905</t>
@@ -3812,28 +3809,28 @@
     <t xml:space="preserve">7.94690704345703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88937950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0208683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78496170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62768936157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63642692565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52284097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43546867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28693342208862</t>
+    <t xml:space="preserve">7.88937997817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02086925506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78496217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62768888473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63642644882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52284145355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43546915054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28693437576294</t>
   </si>
   <si>
     <t xml:space="preserve">7.37430667877197</t>
@@ -3845,28 +3842,28 @@
     <t xml:space="preserve">7.25198459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29567098617554</t>
+    <t xml:space="preserve">7.29567193984985</t>
   </si>
   <si>
     <t xml:space="preserve">7.42673110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30440807342529</t>
+    <t xml:space="preserve">7.30440855026245</t>
   </si>
   <si>
     <t xml:space="preserve">7.40925598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33062124252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44420671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49662971496582</t>
+    <t xml:space="preserve">7.33062076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44420528411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294284820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49662923812866</t>
   </si>
   <si>
     <t xml:space="preserve">7.54031658172607</t>
@@ -3875,37 +3872,37 @@
     <t xml:space="preserve">7.64516448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51410531997681</t>
+    <t xml:space="preserve">7.51410484313965</t>
   </si>
   <si>
     <t xml:space="preserve">7.41799354553223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46168088912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53157901763916</t>
+    <t xml:space="preserve">7.46168041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53157806396484</t>
   </si>
   <si>
     <t xml:space="preserve">7.40051889419556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48789215087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39178133010864</t>
+    <t xml:space="preserve">7.48789167404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3917818069458</t>
   </si>
   <si>
     <t xml:space="preserve">7.47041797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34809446334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94617795944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9024920463562</t>
+    <t xml:space="preserve">7.34809541702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94617748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90249156951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.80638027191162</t>
@@ -3938,40 +3935,40 @@
     <t xml:space="preserve">7.16461086273193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18208646774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33935689926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17334890365601</t>
+    <t xml:space="preserve">7.18208599090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33935785293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17334842681885</t>
   </si>
   <si>
     <t xml:space="preserve">7.20829772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32188367843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263914108276</t>
+    <t xml:space="preserve">7.32188320159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66264009475708</t>
   </si>
   <si>
     <t xml:space="preserve">7.68885087966919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68011379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75875043869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8373851776123</t>
+    <t xml:space="preserve">7.68011331558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75874948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83738660812378</t>
   </si>
   <si>
     <t xml:space="preserve">7.69758892059326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67137575149536</t>
+    <t xml:space="preserve">7.67137622833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.81117296218872</t>
@@ -3980,31 +3977,31 @@
     <t xml:space="preserve">7.76748752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7063250541687</t>
+    <t xml:space="preserve">7.70632553100586</t>
   </si>
   <si>
     <t xml:space="preserve">7.92475938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89854717254639</t>
+    <t xml:space="preserve">7.89854621887207</t>
   </si>
   <si>
     <t xml:space="preserve">7.80114364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5709171295166</t>
+    <t xml:space="preserve">7.57091665267944</t>
   </si>
   <si>
     <t xml:space="preserve">7.87198257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93396615982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96938610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12877464294434</t>
+    <t xml:space="preserve">7.93396663665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96938562393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12877368927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.09335422515869</t>
@@ -4016,40 +4013,40 @@
     <t xml:space="preserve">8.25274181365967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16419315338135</t>
+    <t xml:space="preserve">8.16419410705566</t>
   </si>
   <si>
     <t xml:space="preserve">8.05793476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95167636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98709583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86312770843506</t>
+    <t xml:space="preserve">7.9516749382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98709630966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8631272315979</t>
   </si>
   <si>
     <t xml:space="preserve">7.97824096679688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65946531295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6151909828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7125940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70373916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51778650283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7922887802124</t>
+    <t xml:space="preserve">7.65946483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61519145965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71259498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70373964309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51778697967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79228830337524</t>
   </si>
   <si>
     <t xml:space="preserve">7.6417555809021</t>
@@ -4058,28 +4055,28 @@
     <t xml:space="preserve">7.72144937515259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60633563995361</t>
+    <t xml:space="preserve">7.60633611679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.48236799240112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52664184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59748125076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50007772445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4912223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43809270858765</t>
+    <t xml:space="preserve">7.52664232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59748077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49122285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58862543106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4380931854248</t>
   </si>
   <si>
     <t xml:space="preserve">7.47351264953613</t>
@@ -4088,19 +4085,19 @@
     <t xml:space="preserve">7.69488430023193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67717552185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75686883926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84541654586792</t>
+    <t xml:space="preserve">7.67717456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75686931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84541702270508</t>
   </si>
   <si>
     <t xml:space="preserve">7.74801397323608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88083648681641</t>
+    <t xml:space="preserve">7.88083696365356</t>
   </si>
   <si>
     <t xml:space="preserve">7.99595022201538</t>
@@ -4109,22 +4106,25 @@
     <t xml:space="preserve">7.85427236557007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53549718856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33183431625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66831922531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76572418212891</t>
+    <t xml:space="preserve">7.89854669570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53549766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33183479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6683201789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76572465896606</t>
   </si>
   <si>
     <t xml:space="preserve">7.90740156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83656358718872</t>
+    <t xml:space="preserve">7.8365626335144</t>
   </si>
   <si>
     <t xml:space="preserve">8.07564449310303</t>
@@ -4136,10 +4136,10 @@
     <t xml:space="preserve">8.17304706573486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.235032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10220909118652</t>
+    <t xml:space="preserve">8.23503112792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10220813751221</t>
   </si>
   <si>
     <t xml:space="preserve">7.92511129379272</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">7.81885290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94282102584839</t>
+    <t xml:space="preserve">7.94282197952271</t>
   </si>
   <si>
     <t xml:space="preserve">8.20846843719482</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">8.19961261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.288161277771</t>
+    <t xml:space="preserve">8.28816032409668</t>
   </si>
   <si>
     <t xml:space="preserve">8.31472587585449</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">8.22617721557617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19075775146484</t>
+    <t xml:space="preserve">8.19075679779053</t>
   </si>
   <si>
     <t xml:space="preserve">8.56266307830811</t>
@@ -4181,16 +4181,16 @@
     <t xml:space="preserve">8.66892147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68663120269775</t>
+    <t xml:space="preserve">8.68663024902344</t>
   </si>
   <si>
     <t xml:space="preserve">8.76632404327393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96113204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1736478805542</t>
+    <t xml:space="preserve">8.96113109588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17364883422852</t>
   </si>
   <si>
     <t xml:space="preserve">9.03197002410889</t>
@@ -4199,16 +4199,16 @@
     <t xml:space="preserve">9.04968070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13822937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92571258544922</t>
+    <t xml:space="preserve">9.13822841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9257116317749</t>
   </si>
   <si>
     <t xml:space="preserve">8.97884178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84601879119873</t>
+    <t xml:space="preserve">8.84601783752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.90800189971924</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">8.79288864135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74861526489258</t>
+    <t xml:space="preserve">8.74861431121826</t>
   </si>
   <si>
     <t xml:space="preserve">8.80174350738525</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">8.83716297149658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99655055999756</t>
+    <t xml:space="preserve">8.99655151367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.39441967010498</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">8.59808158874512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61579036712646</t>
+    <t xml:space="preserve">8.61579132080078</t>
   </si>
   <si>
     <t xml:space="preserve">8.51838779449463</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">8.50067806243896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4032735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43869304656982</t>
+    <t xml:space="preserve">8.40327453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43869400024414</t>
   </si>
   <si>
     <t xml:space="preserve">8.34129047393799</t>
@@ -4274,31 +4274,31 @@
     <t xml:space="preserve">8.87258338928223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01426124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08509922027588</t>
+    <t xml:space="preserve">9.01426029205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0851001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.20906734466553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29761695861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19135856628418</t>
+    <t xml:space="preserve">9.29761600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19135761260986</t>
   </si>
   <si>
     <t xml:space="preserve">9.35074615478516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2799072265625</t>
+    <t xml:space="preserve">9.27990627288818</t>
   </si>
   <si>
     <t xml:space="preserve">9.45700454711914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10280990600586</t>
+    <t xml:space="preserve">9.10280895233154</t>
   </si>
   <si>
     <t xml:space="preserve">8.85487270355225</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">8.77517890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89029216766357</t>
+    <t xml:space="preserve">8.89029312133789</t>
   </si>
   <si>
     <t xml:space="preserve">8.94342231750488</t>
@@ -4319,28 +4319,28 @@
     <t xml:space="preserve">8.82830905914307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73976039886475</t>
+    <t xml:space="preserve">8.73975944519043</t>
   </si>
   <si>
     <t xml:space="preserve">8.72205066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53609752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54495239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4564037322998</t>
+    <t xml:space="preserve">8.53609848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54495143890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45640277862549</t>
   </si>
   <si>
     <t xml:space="preserve">8.42984008789062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41212940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49182319641113</t>
+    <t xml:space="preserve">8.41212844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49182415008545</t>
   </si>
   <si>
     <t xml:space="preserve">9.26219749450684</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">8.65121173858643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06738948822021</t>
+    <t xml:space="preserve">9.06739044189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.61639213562012</t>
@@ -4367,19 +4367,19 @@
     <t xml:space="preserve">9.66952228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.006007194519</t>
+    <t xml:space="preserve">10.0060062408447</t>
   </si>
   <si>
     <t xml:space="preserve">10.0237169265747</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95287704467773</t>
+    <t xml:space="preserve">9.95287799835205</t>
   </si>
   <si>
     <t xml:space="preserve">10.0591354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8289098739624</t>
+    <t xml:space="preserve">9.82890892028809</t>
   </si>
   <si>
     <t xml:space="preserve">9.75807094573975</t>
@@ -4388,13 +4388,13 @@
     <t xml:space="preserve">9.3684549331665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31532764434814</t>
+    <t xml:space="preserve">9.31532669067383</t>
   </si>
   <si>
     <t xml:space="preserve">9.56326293945312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65181159973145</t>
+    <t xml:space="preserve">9.65181064605713</t>
   </si>
   <si>
     <t xml:space="preserve">9.77577972412109</t>
@@ -4403,22 +4403,22 @@
     <t xml:space="preserve">10.112265586853</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97058773040771</t>
+    <t xml:space="preserve">9.9705867767334</t>
   </si>
   <si>
     <t xml:space="preserve">10.1653938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2716522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360200881958</t>
+    <t xml:space="preserve">10.271653175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3602018356323</t>
   </si>
   <si>
     <t xml:space="preserve">10.1831035614014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2185230255127</t>
+    <t xml:space="preserve">10.218523979187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2362337112427</t>
@@ -4806,6 +4806,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.22999954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18000030517578</t>
   </si>
 </sst>
 </file>
@@ -56356,7 +56359,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1970" t="s">
-        <v>1208</v>
+        <v>1061</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56382,7 +56385,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1971" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56408,7 +56411,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1972" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56434,7 +56437,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1973" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56460,7 +56463,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1974" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56486,7 +56489,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1975" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56512,7 +56515,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1976" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56538,7 +56541,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1977" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56564,7 +56567,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1978" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56590,7 +56593,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1979" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -56616,7 +56619,7 @@
         <v>7.25</v>
       </c>
       <c r="G1980" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -56642,7 +56645,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1981" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56668,7 +56671,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1982" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56694,7 +56697,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1983" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56720,7 +56723,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1984" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56746,7 +56749,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1985" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56772,7 +56775,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1986" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56798,7 +56801,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1987" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56824,7 +56827,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56850,7 +56853,7 @@
         <v>7</v>
       </c>
       <c r="G1989" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56876,7 +56879,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1990" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56902,7 +56905,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1991" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56928,7 +56931,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1992" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56954,7 +56957,7 @@
         <v>7</v>
       </c>
       <c r="G1993" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56980,7 +56983,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57006,7 +57009,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1995" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57032,7 +57035,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1996" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57058,7 +57061,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1997" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57084,7 +57087,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1998" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57110,7 +57113,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1999" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57136,7 +57139,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2000" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57162,7 +57165,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57240,7 +57243,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2004" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57266,7 +57269,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2005" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57370,7 +57373,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G2009" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57526,7 +57529,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G2015" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57604,7 +57607,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2018" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57630,7 +57633,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2019" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57656,7 +57659,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2020" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57682,7 +57685,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2021" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57708,7 +57711,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2022" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57734,7 +57737,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2023" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57760,7 +57763,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2024" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57786,7 +57789,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2025" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57812,7 +57815,7 @@
         <v>8.5</v>
       </c>
       <c r="G2026" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57838,7 +57841,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2027" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57864,7 +57867,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57890,7 +57893,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G2029" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57916,7 +57919,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2030" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57942,7 +57945,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2031" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57968,7 +57971,7 @@
         <v>8.75</v>
       </c>
       <c r="G2032" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57994,7 +57997,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2033" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58020,7 +58023,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2034" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58046,7 +58049,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2035" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58072,7 +58075,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2036" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58098,7 +58101,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2037" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58124,7 +58127,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2038" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58150,7 +58153,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2039" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58176,7 +58179,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2040" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58202,7 +58205,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2041" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58228,7 +58231,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2042" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58254,7 +58257,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G2043" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58280,7 +58283,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2044" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58306,7 +58309,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G2045" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58332,7 +58335,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2046" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58358,7 +58361,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G2047" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58384,7 +58387,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2048" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58410,7 +58413,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2049" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58436,7 +58439,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2050" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58462,7 +58465,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2051" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58488,7 +58491,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G2052" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58514,7 +58517,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G2053" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58540,7 +58543,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2054" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58566,7 +58569,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G2055" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58592,7 +58595,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2056" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58618,7 +58621,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2057" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58644,7 +58647,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2058" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58670,7 +58673,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G2059" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58696,7 +58699,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2060" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58722,7 +58725,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2061" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58748,7 +58751,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2062" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58774,7 +58777,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G2063" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58800,7 +58803,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2064" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58826,7 +58829,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2065" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58852,7 +58855,7 @@
         <v>8.5</v>
       </c>
       <c r="G2066" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58878,7 +58881,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2067" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58904,7 +58907,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2068" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58930,7 +58933,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2069" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58956,7 +58959,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G2070" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58982,7 +58985,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2071" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59008,7 +59011,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G2072" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59034,7 +59037,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59060,7 +59063,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2074" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59086,7 +59089,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2075" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59112,7 +59115,7 @@
         <v>8.75</v>
       </c>
       <c r="G2076" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59138,7 +59141,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2077" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59164,7 +59167,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2078" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59190,7 +59193,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59216,7 +59219,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2080" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59242,7 +59245,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2081" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59268,7 +59271,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2082" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59294,7 +59297,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2083" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59320,7 +59323,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2084" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59346,7 +59349,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2085" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59372,7 +59375,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2086" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59398,7 +59401,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2087" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59424,7 +59427,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2088" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59450,7 +59453,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2089" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59476,7 +59479,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G2090" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59502,7 +59505,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2091" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59528,7 +59531,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2092" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59554,7 +59557,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2093" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59580,7 +59583,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2094" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59606,7 +59609,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2095" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59632,7 +59635,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2096" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59658,7 +59661,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59684,7 +59687,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2098" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59710,7 +59713,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59736,7 +59739,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2100" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59762,7 +59765,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59788,7 +59791,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G2102" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59814,7 +59817,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2103" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59840,7 +59843,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G2104" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59866,7 +59869,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2105" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59892,7 +59895,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2106" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59918,7 +59921,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2107" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59944,7 +59947,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G2108" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59970,7 +59973,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2109" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59996,7 +59999,7 @@
         <v>8.25</v>
       </c>
       <c r="G2110" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60022,7 +60025,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G2111" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60048,7 +60051,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2112" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60074,7 +60077,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2113" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60100,7 +60103,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2114" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60126,7 +60129,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2115" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60152,7 +60155,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2116" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60178,7 +60181,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2117" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60204,7 +60207,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2118" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60230,7 +60233,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G2119" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60256,7 +60259,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2120" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60282,7 +60285,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2121" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60308,7 +60311,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2122" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60334,7 +60337,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G2123" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60360,7 +60363,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2124" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60386,7 +60389,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60412,7 +60415,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2126" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60438,7 +60441,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2127" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60464,7 +60467,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2128" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60490,7 +60493,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2129" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60516,7 +60519,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2130" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60542,7 +60545,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2131" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60568,7 +60571,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2132" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60594,7 +60597,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2133" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60620,7 +60623,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2134" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60646,7 +60649,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2135" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60672,7 +60675,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60698,7 +60701,7 @@
         <v>9</v>
       </c>
       <c r="G2137" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60724,7 +60727,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2138" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60750,7 +60753,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G2139" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60776,7 +60779,7 @@
         <v>9</v>
       </c>
       <c r="G2140" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60802,7 +60805,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2141" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60828,7 +60831,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G2142" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60854,7 +60857,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2143" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60880,7 +60883,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2144" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60906,7 +60909,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G2145" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60932,7 +60935,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2146" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60958,7 +60961,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2147" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60984,7 +60987,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2148" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61010,7 +61013,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2149" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61036,7 +61039,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G2150" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61062,7 +61065,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2151" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61088,7 +61091,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2152" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61114,7 +61117,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G2153" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61140,7 +61143,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2154" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61166,7 +61169,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2155" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61192,7 +61195,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2156" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61218,7 +61221,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2157" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61244,7 +61247,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2158" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61270,7 +61273,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61296,7 +61299,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2160" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61322,7 +61325,7 @@
         <v>8.5</v>
       </c>
       <c r="G2161" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61348,7 +61351,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2162" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61374,7 +61377,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2163" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61400,7 +61403,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2164" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61426,7 +61429,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2165" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61452,7 +61455,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2166" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61478,7 +61481,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2167" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61504,7 +61507,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2168" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61530,7 +61533,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2169" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61556,7 +61559,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2170" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61582,7 +61585,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2171" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61608,7 +61611,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2172" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61634,7 +61637,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2173" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61660,7 +61663,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2174" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61686,7 +61689,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2175" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61712,7 +61715,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2176" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61738,7 +61741,7 @@
         <v>8.75</v>
       </c>
       <c r="G2177" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61764,7 +61767,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G2178" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61790,7 +61793,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2179" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61816,7 +61819,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2180" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61842,7 +61845,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2181" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61868,7 +61871,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2182" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61894,7 +61897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2183" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61920,7 +61923,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2184" t="s">
-        <v>1324</v>
+        <v>1364</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61946,7 +61949,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2185" t="s">
-        <v>1324</v>
+        <v>1364</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61972,7 +61975,7 @@
         <v>8.75</v>
       </c>
       <c r="G2186" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62050,7 +62053,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2189" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62102,7 +62105,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2191" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62154,7 +62157,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2193" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62180,7 +62183,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2194" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62206,7 +62209,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2195" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62310,7 +62313,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2199" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62336,7 +62339,7 @@
         <v>9</v>
       </c>
       <c r="G2200" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62414,7 +62417,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2203" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62440,7 +62443,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2204" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62466,7 +62469,7 @@
         <v>9</v>
       </c>
       <c r="G2205" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62544,7 +62547,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2208" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62622,7 +62625,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2211" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62674,7 +62677,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2213" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62700,7 +62703,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2214" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62752,7 +62755,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2216" t="s">
-        <v>1324</v>
+        <v>1364</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62882,7 +62885,7 @@
         <v>9</v>
       </c>
       <c r="G2221" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -71756,7 +71759,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.6912962963</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>282810</v>
@@ -71777,6 +71780,32 @@
         <v>1597</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6911458333</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>241165</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>9.22999954223633</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>9.22999954223633</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>1598</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="1599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="1600">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,193 +38,193 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79523658752441</t>
+    <t xml:space="preserve">7.79523372650146</t>
   </si>
   <si>
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74423694610596</t>
+    <t xml:space="preserve">7.74423980712891</t>
   </si>
   <si>
     <t xml:space="preserve">7.72238206863403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72966861724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78794956207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77337980270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56939172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54753446578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6131010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21241426467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1759877204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62038803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46739816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35811758041382</t>
+    <t xml:space="preserve">7.7296667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78795003890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77337884902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56939125061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54753494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61310195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21241283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17598676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62038850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46739721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35811901092529</t>
   </si>
   <si>
     <t xml:space="preserve">7.30712175369263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38725996017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56210565567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49653816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28526639938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37268924713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64952802658081</t>
+    <t xml:space="preserve">7.3872594833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56210613250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49653768539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28526592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37268972396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64952945709229</t>
   </si>
   <si>
     <t xml:space="preserve">7.51839542388916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58396244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67866897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86080312728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76609325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8972282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90451335906982</t>
+    <t xml:space="preserve">7.58396148681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67867136001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86080360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76609420776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89722728729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90451288223267</t>
   </si>
   <si>
     <t xml:space="preserve">7.95551061630249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80980682373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88994407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00650596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94093990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87537336349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01379299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94822549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03564929962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80252027511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84623146057129</t>
+    <t xml:space="preserve">7.80980634689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88994359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00650691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94093942642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87537145614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01379203796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94822406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03564739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80252122879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84623241424561</t>
   </si>
   <si>
     <t xml:space="preserve">8.05750465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05021858215332</t>
+    <t xml:space="preserve">8.05021953582764</t>
   </si>
   <si>
     <t xml:space="preserve">8.02836322784424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38534164428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45090866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4363374710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45819282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6330394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71317863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60389995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74231910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80788612365723</t>
+    <t xml:space="preserve">8.15949821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38534355163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4509105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43633842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4581937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63304042816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71317958831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60389804840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74232006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80788707733154</t>
   </si>
   <si>
     <t xml:space="preserve">8.42176723480225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73503398895264</t>
+    <t xml:space="preserve">8.73503494262695</t>
   </si>
   <si>
     <t xml:space="preserve">8.79331588745117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65489673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70589351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81517219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95359134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75688934326172</t>
+    <t xml:space="preserve">8.6548957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70589065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81517124176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95359230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75689029693604</t>
   </si>
   <si>
     <t xml:space="preserve">9.20857715606689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26685905456543</t>
+    <t xml:space="preserve">9.26685810089111</t>
   </si>
   <si>
     <t xml:space="preserve">9.25228881835938</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">9.39799213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4854154586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36156845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32488441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07543849945068</t>
+    <t xml:space="preserve">9.48541736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32488346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07543659210205</t>
   </si>
   <si>
     <t xml:space="preserve">9.09744930267334</t>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">9.17081451416016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2955379486084</t>
+    <t xml:space="preserve">9.29553699493408</t>
   </si>
   <si>
     <t xml:space="preserve">9.36890411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27352714538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28820037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20749759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24418163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11212158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02408027648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87734794616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84066581726074</t>
+    <t xml:space="preserve">9.27352809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28819942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20749568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24418067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11212062835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02408218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87734699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84066486358643</t>
   </si>
   <si>
     <t xml:space="preserve">8.80398082733154</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">8.73061561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95071506500244</t>
+    <t xml:space="preserve">8.95071601867676</t>
   </si>
   <si>
     <t xml:space="preserve">9.22950744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81865406036377</t>
+    <t xml:space="preserve">8.8186559677124</t>
   </si>
   <si>
     <t xml:space="preserve">8.8259916305542</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">9.31754684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95804882049561</t>
+    <t xml:space="preserve">8.95805168151855</t>
   </si>
   <si>
     <t xml:space="preserve">8.99473476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1928243637085</t>
+    <t xml:space="preserve">9.19282341003418</t>
   </si>
   <si>
     <t xml:space="preserve">9.13413047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34689521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35422992706299</t>
+    <t xml:space="preserve">9.34689331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3542308807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.22217082977295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06076526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37624073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33955764770508</t>
+    <t xml:space="preserve">9.06076431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37624168395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33955574035645</t>
   </si>
   <si>
     <t xml:space="preserve">9.31021022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28086280822754</t>
+    <t xml:space="preserve">9.28086376190186</t>
   </si>
   <si>
     <t xml:space="preserve">9.26619052886963</t>
@@ -356,25 +356,25 @@
     <t xml:space="preserve">9.39824962615967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3028736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25885391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33221912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11945819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00207042694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96538829803467</t>
+    <t xml:space="preserve">9.30287456512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2588529586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33222198486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11945629119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05342769622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00207233428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96538734436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.1414680480957</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">9.01674461364746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39091491699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15614223480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38357925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44960689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49362850189209</t>
+    <t xml:space="preserve">9.39091110229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1561393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38357734680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44960594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49362659454346</t>
   </si>
   <si>
     <t xml:space="preserve">9.52297210693359</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">9.50829982757568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79442882537842</t>
+    <t xml:space="preserve">9.79442977905273</t>
   </si>
   <si>
     <t xml:space="preserve">9.8384485244751</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">9.95583629608154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0438747406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1392526626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2566394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1979446411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2713088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90447902679443</t>
+    <t xml:space="preserve">10.0438756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.139253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2566404342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1979465484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2713117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90447998046875</t>
   </si>
   <si>
     <t xml:space="preserve">10.0145292282104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7577486038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65503311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64769649505615</t>
+    <t xml:space="preserve">9.75774765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65503406524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64769744873047</t>
   </si>
   <si>
     <t xml:space="preserve">9.80910301208496</t>
@@ -452,70 +452,70 @@
     <t xml:space="preserve">9.64035892486572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53764724731445</t>
+    <t xml:space="preserve">9.53764533996582</t>
   </si>
   <si>
     <t xml:space="preserve">9.45694351196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41292476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61834812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56699180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44227027893066</t>
+    <t xml:space="preserve">9.41292381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6183500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56699371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44226932525635</t>
   </si>
   <si>
     <t xml:space="preserve">9.5156364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53030872344971</t>
+    <t xml:space="preserve">9.53030967712402</t>
   </si>
   <si>
     <t xml:space="preserve">9.47895336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63302326202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55965614318848</t>
+    <t xml:space="preserve">9.63302135467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55965709686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.47161674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73573684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0878963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1245784759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0512132644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86779594421387</t>
+    <t xml:space="preserve">9.73573589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0878953933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1245803833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0512104034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86779499053955</t>
   </si>
   <si>
     <t xml:space="preserve">9.83111190795898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97050952911377</t>
+    <t xml:space="preserve">9.97050857543945</t>
   </si>
   <si>
     <t xml:space="preserve">9.97784614562988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81643867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69171619415283</t>
+    <t xml:space="preserve">9.81643962860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69171714782715</t>
   </si>
   <si>
     <t xml:space="preserve">9.88980579376221</t>
@@ -524,37 +524,37 @@
     <t xml:space="preserve">9.86046028137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96317100524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0585489273071</t>
+    <t xml:space="preserve">9.96317291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0585508346558</t>
   </si>
   <si>
     <t xml:space="preserve">9.99251937866211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1612615585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1465883255005</t>
+    <t xml:space="preserve">10.1612634658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1465892791748</t>
   </si>
   <si>
     <t xml:space="preserve">9.941162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82377624511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7210636138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87513256072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0365400314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0805587768555</t>
+    <t xml:space="preserve">9.8237771987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72106170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87513446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0365390777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0805578231812</t>
   </si>
   <si>
     <t xml:space="preserve">10.0071935653687</t>
@@ -563,112 +563,112 @@
     <t xml:space="preserve">9.89714241027832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69905376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98518371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.330005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7335214614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7115106582642</t>
+    <t xml:space="preserve">9.69905281066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3300046920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7335205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7115116119385</t>
   </si>
   <si>
     <t xml:space="preserve">10.6674900054932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8582429885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8215608596802</t>
+    <t xml:space="preserve">10.8582439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8215618133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.9316101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8068876266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022636413574</t>
+    <t xml:space="preserve">10.8068866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022655487061</t>
   </si>
   <si>
     <t xml:space="preserve">11.1883916854858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2177400588989</t>
+    <t xml:space="preserve">11.2177410125732</t>
   </si>
   <si>
     <t xml:space="preserve">11.3424634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957302093506</t>
+    <t xml:space="preserve">11.1957311630249</t>
   </si>
   <si>
     <t xml:space="preserve">11.15904712677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0636711120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9242725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0416603088379</t>
+    <t xml:space="preserve">11.0636730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9242734909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0416593551636</t>
   </si>
   <si>
     <t xml:space="preserve">11.1517114639282</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2250747680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2984428405762</t>
+    <t xml:space="preserve">11.2250776290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2984437942505</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166328430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7313051223755</t>
+    <t xml:space="preserve">11.7313032150269</t>
   </si>
   <si>
     <t xml:space="preserve">11.8340177536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8853750228882</t>
+    <t xml:space="preserve">11.8853759765625</t>
   </si>
   <si>
     <t xml:space="preserve">11.9954252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6997423171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.022557258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0592384338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2059726715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6924076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2815551757812</t>
+    <t xml:space="preserve">12.6997451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.022554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0592403411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2059717178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6924085617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2815561294556</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1788396835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4796419143677</t>
+    <t xml:space="preserve">12.178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4796438217163</t>
   </si>
   <si>
     <t xml:space="preserve">12.3255748748779</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">12.6630611419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619520187378</t>
+    <t xml:space="preserve">12.6557235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619529724121</t>
   </si>
   <si>
     <t xml:space="preserve">12.8024559020996</t>
@@ -692,58 +692,58 @@
     <t xml:space="preserve">12.8391380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1399431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0005464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491891860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0959243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0445671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.719536781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929048538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7855663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295879364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396362304688</t>
+    <t xml:space="preserve">13.1399412155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.000545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491901397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0959224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0445652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7195377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7855672836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.82958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396371841431</t>
   </si>
   <si>
     <t xml:space="preserve">14.0643615722656</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6828556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7268743515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8222551345825</t>
+    <t xml:space="preserve">13.6828546524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.726879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8222522735596</t>
   </si>
   <si>
     <t xml:space="preserve">13.7415466308594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9249658584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6755180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4480829238892</t>
+    <t xml:space="preserve">13.9249639511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.675518989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4480819702148</t>
   </si>
   <si>
     <t xml:space="preserve">13.4627552032471</t>
@@ -752,73 +752,73 @@
     <t xml:space="preserve">13.403772354126</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5364818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.794529914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8903799057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4922475814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512285232544</t>
+    <t xml:space="preserve">13.5364828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945356369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8903789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4922456741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512294769287</t>
   </si>
   <si>
     <t xml:space="preserve">13.6618204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9641084671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9862241744995</t>
+    <t xml:space="preserve">13.9641056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9862251281738</t>
   </si>
   <si>
     <t xml:space="preserve">14.0452070236206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7429208755493</t>
+    <t xml:space="preserve">13.7429227828979</t>
   </si>
   <si>
     <t xml:space="preserve">13.7650394439697</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7502965927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.654447555542</t>
+    <t xml:space="preserve">13.7502946853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6544485092163</t>
   </si>
   <si>
     <t xml:space="preserve">13.4553823471069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9346151351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9714784622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7134323120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9272403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830051422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0820722579956</t>
+    <t xml:space="preserve">13.9346141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9714775085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9272413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830060958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.082070350647</t>
   </si>
   <si>
     <t xml:space="preserve">14.0083436965942</t>
   </si>
   <si>
-    <t xml:space="preserve">13.853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1973342895508</t>
+    <t xml:space="preserve">13.8535137176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1973333358765</t>
   </si>
   <si>
     <t xml:space="preserve">13.5069932937622</t>
@@ -827,97 +827,97 @@
     <t xml:space="preserve">13.3079280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3300457000732</t>
+    <t xml:space="preserve">13.3300437927246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3152990341187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6470775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7871599197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8092775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7797880172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8387699127197</t>
+    <t xml:space="preserve">13.6470785140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7871589660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8092765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7797861099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8387689590454</t>
   </si>
   <si>
     <t xml:space="preserve">13.9493627548218</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1189346313477</t>
+    <t xml:space="preserve">14.1189336776733</t>
   </si>
   <si>
     <t xml:space="preserve">13.8977527618408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9198703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8240222930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.941987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8313941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6765651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4627532958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816547393799</t>
+    <t xml:space="preserve">13.9198684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8240213394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9419898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8313989639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6765670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4627561569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816528320312</t>
   </si>
   <si>
     <t xml:space="preserve">13.101487159729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5291118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.565975189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5586004257202</t>
+    <t xml:space="preserve">13.5291109085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5659742355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5586023330688</t>
   </si>
   <si>
     <t xml:space="preserve">13.2710618972778</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3890285491943</t>
+    <t xml:space="preserve">13.38902759552</t>
   </si>
   <si>
     <t xml:space="preserve">13.5807209014893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6102142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4185190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7060575485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7576684951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6986856460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.816650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.728178024292</t>
+    <t xml:space="preserve">13.6102132797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4185180664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7576656341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6986846923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8166494369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7281789779663</t>
   </si>
   <si>
     <t xml:space="preserve">13.7355489730835</t>
@@ -929,124 +929,124 @@
     <t xml:space="preserve">13.6397037506104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9051246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6249551773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6028356552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7456274032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6055421829224</t>
+    <t xml:space="preserve">13.905122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6249561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6028385162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7456245422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6055402755737</t>
   </si>
   <si>
     <t xml:space="preserve">14.6129140853882</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5318126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4728317260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5613050460815</t>
+    <t xml:space="preserve">14.531813621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4728288650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5613031387329</t>
   </si>
   <si>
     <t xml:space="preserve">14.4359674453735</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2958850860596</t>
+    <t xml:space="preserve">14.2958831787109</t>
   </si>
   <si>
     <t xml:space="preserve">14.3032560348511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2590179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9124965667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6913108825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1336803436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.956732749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0378370285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1263065338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1705465316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2147808074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1558017730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0230875015259</t>
+    <t xml:space="preserve">14.2590188980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9124937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6913118362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1336812973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.030460357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9567346572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0378341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1263074874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1705455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2147827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1557998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0230913162231</t>
   </si>
   <si>
     <t xml:space="preserve">14.104190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8461437225342</t>
+    <t xml:space="preserve">13.8461418151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.8608865737915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9788541793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.192663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2295293807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5096969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6497793197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7013854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9299449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8562173843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.782488822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5834197998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3474922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4949493408203</t>
+    <t xml:space="preserve">13.9788522720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1926641464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2295265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5096960067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6497812271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7013902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9299430847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8562183380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7824878692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5834217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3474941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4949502944946</t>
   </si>
   <si>
     <t xml:space="preserve">15.2617216110229</t>
@@ -1055,76 +1055,76 @@
     <t xml:space="preserve">15.0774011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1511297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4091777801514</t>
+    <t xml:space="preserve">15.1511278152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4091796875</t>
   </si>
   <si>
     <t xml:space="preserve">14.9668083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3354482650757</t>
+    <t xml:space="preserve">15.33544921875</t>
   </si>
   <si>
     <t xml:space="preserve">15.4460430145264</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0405397415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1142663955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6276617050171</t>
+    <t xml:space="preserve">15.0405387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1142644882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6276588439941</t>
   </si>
   <si>
     <t xml:space="preserve">14.2885103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2737646102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1852903366089</t>
+    <t xml:space="preserve">14.2737655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1852912902832</t>
   </si>
   <si>
     <t xml:space="preserve">14.5391864776611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3917293548584</t>
+    <t xml:space="preserve">14.3917284011841</t>
   </si>
   <si>
     <t xml:space="preserve">14.4212207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2000350952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4064769744873</t>
+    <t xml:space="preserve">14.2000370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.406476020813</t>
   </si>
   <si>
     <t xml:space="preserve">13.3447904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5217351913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839399337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8756341934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.138352394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9761486053467</t>
+    <t xml:space="preserve">13.5217380523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839389801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8756322860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9908971786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1383495330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.976149559021</t>
   </si>
   <si>
     <t xml:space="preserve">12.7549667358398</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">12.6517467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8876762390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8729295730591</t>
+    <t xml:space="preserve">12.887677192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8729305267334</t>
   </si>
   <si>
     <t xml:space="preserve">12.7254753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0793704986572</t>
+    <t xml:space="preserve">13.0793695449829</t>
   </si>
   <si>
     <t xml:space="preserve">12.8286933898926</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">12.5042905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7402219772339</t>
+    <t xml:space="preserve">12.7402191162109</t>
   </si>
   <si>
     <t xml:space="preserve">12.6812372207642</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">13.0646238327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2858057022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1088609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3005542755127</t>
+    <t xml:space="preserve">13.2858066558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1088590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3005523681641</t>
   </si>
   <si>
     <t xml:space="preserve">14.0968179702759</t>
@@ -1184,67 +1184,67 @@
     <t xml:space="preserve">13.3742818832397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3668718338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3075942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1890411376953</t>
+    <t xml:space="preserve">13.366870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3075952529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1890430450439</t>
   </si>
   <si>
     <t xml:space="preserve">13.4113292694092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4854249954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9371166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2702560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7592887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5962781906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6851921081543</t>
+    <t xml:space="preserve">13.485424041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9371175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2702569961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7592868804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5962762832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6851902008057</t>
   </si>
   <si>
     <t xml:space="preserve">13.0408515930176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9667530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.144585609436</t>
+    <t xml:space="preserve">12.9667549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1445846557617</t>
   </si>
   <si>
     <t xml:space="preserve">12.8630208969116</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8926591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.818564414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7444696426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9815740585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2483177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2927761077881</t>
+    <t xml:space="preserve">12.8926601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963941574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8185625076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7444686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9815759658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2483196258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2927742004395</t>
   </si>
   <si>
     <t xml:space="preserve">13.0853071212769</t>
@@ -1253,106 +1253,106 @@
     <t xml:space="preserve">13.4706048965454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5298833847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4409675598145</t>
+    <t xml:space="preserve">13.529881477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4409685134888</t>
   </si>
   <si>
     <t xml:space="preserve">13.2779560089111</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3224143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816900253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6039772033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.515064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3372344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9300003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8855419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8262672424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7669887542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6928949356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7521696090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8559055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9892768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2038621902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7818088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9003629684448</t>
+    <t xml:space="preserve">13.322413444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816919326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6039791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5150632858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3372325897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299974441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8855457305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.826268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7669897079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.692892074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7521705627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8559045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9892778396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2038612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7818078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9003610610962</t>
   </si>
   <si>
     <t xml:space="preserve">13.7225313186646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9596405029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7077121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5447015762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5595216751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1149454116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4261474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.655553817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8778400421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9222984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1001272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1297645568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.011212348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665201187134</t>
+    <t xml:space="preserve">13.9596385955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7077112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5447006225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5595207214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1149463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4261484146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6555519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8778390884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9222974777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1001281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1297664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0112142562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.166522026062</t>
   </si>
   <si>
     <t xml:space="preserve">12.1517019271851</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">12.1220636367798</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3739881515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4777240753174</t>
+    <t xml:space="preserve">12.3739900588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4777231216431</t>
   </si>
   <si>
     <t xml:space="preserve">12.1368837356567</t>
@@ -1376,43 +1376,43 @@
     <t xml:space="preserve">11.7071266174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.033148765564</t>
+    <t xml:space="preserve">12.0331497192383</t>
   </si>
   <si>
     <t xml:space="preserve">11.7812232971191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2477331161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4700193405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4403820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5885725021362</t>
+    <t xml:space="preserve">11.2477340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4700202941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4403829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5885734558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6478500366211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5589370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3811073303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3514671325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.173638343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.025447845459</t>
+    <t xml:space="preserve">11.5589361190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3811063766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.351469039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1736364364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0254468917847</t>
   </si>
   <si>
     <t xml:space="preserve">10.6697874069214</t>
@@ -1421,31 +1421,31 @@
     <t xml:space="preserve">10.0029258728027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4326810836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7883396148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4771366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.551233291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8920736312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0995426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0770215988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.375111579895</t>
+    <t xml:space="preserve">10.4326801300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7883405685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4771375656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5512351989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8920755386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9661693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0995416641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0770206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3751106262207</t>
   </si>
   <si>
     <t xml:space="preserve">10.8706378936768</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">10.4835071563721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609331130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1738033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6538467407227</t>
+    <t xml:space="preserve">10.5609340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1738023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6538438796997</t>
   </si>
   <si>
     <t xml:space="preserve">11.3042249679565</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">10.7467565536499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6073904037476</t>
+    <t xml:space="preserve">10.6073894500732</t>
   </si>
   <si>
     <t xml:space="preserve">10.5299644470215</t>
@@ -1484,25 +1484,25 @@
     <t xml:space="preserve">10.7777280807495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7312717437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357444763184</t>
+    <t xml:space="preserve">10.7312707901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.235743522644</t>
   </si>
   <si>
     <t xml:space="preserve">10.4525375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.406081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9945201873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0874300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1493730545044</t>
+    <t xml:space="preserve">10.4060802459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9945211410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0874338150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1493721008301</t>
   </si>
   <si>
     <t xml:space="preserve">11.071946144104</t>
@@ -1514,46 +1514,46 @@
     <t xml:space="preserve">11.0409774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3286561965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4370527267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5919055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4989929199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5144777297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3905963897705</t>
+    <t xml:space="preserve">10.3286542892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4370517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5919046401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4989938735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5144786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3905954360962</t>
   </si>
   <si>
     <t xml:space="preserve">10.3596248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6693305969238</t>
+    <t xml:space="preserve">10.6693315505981</t>
   </si>
   <si>
     <t xml:space="preserve">10.622875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8551549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1184005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3816509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3661661148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.242283821106</t>
+    <t xml:space="preserve">10.8551540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1184015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3816518783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3661670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2422847747803</t>
   </si>
   <si>
     <t xml:space="preserve">11.1648588180542</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">11.3506813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9790353775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.793212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8861236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5764198303223</t>
+    <t xml:space="preserve">10.9790363311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7932119369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8861246109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5764188766479</t>
   </si>
   <si>
     <t xml:space="preserve">10.2047729492188</t>
@@ -1580,124 +1580,124 @@
     <t xml:space="preserve">10.1118621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0808935165405</t>
+    <t xml:space="preserve">10.0808906555176</t>
   </si>
   <si>
     <t xml:space="preserve">9.6782751083374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56987762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75570201873779</t>
+    <t xml:space="preserve">9.56987857818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75570297241211</t>
   </si>
   <si>
     <t xml:space="preserve">9.95700931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87958335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94152545928955</t>
+    <t xml:space="preserve">9.87958431243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94152450561523</t>
   </si>
   <si>
     <t xml:space="preserve">9.92603874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1583185195923</t>
+    <t xml:space="preserve">10.1583166122437</t>
   </si>
   <si>
     <t xml:space="preserve">10.1428327560425</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91055393218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1273469924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3441400527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6383609771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7157869338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6848154067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0344352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0189485549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97249603271484</t>
+    <t xml:space="preserve">9.91055488586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.127347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.344141960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6383590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7157878875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6848173141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0344362258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0189514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97249412536621</t>
   </si>
   <si>
     <t xml:space="preserve">10.2202577590942</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81734848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0666780471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1445941925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3160066604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4874219894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5030040740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.30042552948</t>
+    <t xml:space="preserve">9.81734943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0666790008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1445932388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3160076141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4874210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.503005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3004245758057</t>
   </si>
   <si>
     <t xml:space="preserve">9.91084766387939</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0043449401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87967967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.895263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98876190185547</t>
+    <t xml:space="preserve">10.0043458938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87968063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89526271820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98876285552979</t>
   </si>
   <si>
     <t xml:space="preserve">10.0510940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0822601318359</t>
+    <t xml:space="preserve">10.0822620391846</t>
   </si>
   <si>
     <t xml:space="preserve">10.1134271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.362756729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3939237594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6744194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5341701507568</t>
+    <t xml:space="preserve">10.3627576828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3939228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6744174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5341711044312</t>
   </si>
   <si>
     <t xml:space="preserve">10.4250888824463</t>
@@ -1706,31 +1706,31 @@
     <t xml:space="preserve">10.6276693344116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4406709671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1290111541748</t>
+    <t xml:space="preserve">10.4406719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1290092468262</t>
   </si>
   <si>
     <t xml:space="preserve">10.222508430481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1913423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2069272994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4562559127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3783407211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.643253326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302488327026</t>
+    <t xml:space="preserve">10.1913433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2069263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4562549591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3783397674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6432514190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.830249786377</t>
   </si>
   <si>
     <t xml:space="preserve">10.7523355484009</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">11.0795793533325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9549150466919</t>
+    <t xml:space="preserve">10.9549140930176</t>
   </si>
   <si>
     <t xml:space="preserve">10.6900014877319</t>
@@ -1748,64 +1748,64 @@
     <t xml:space="preserve">10.7679166793823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2198276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2509918212891</t>
+    <t xml:space="preserve">11.2198257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2509927749634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0639963150024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1574935913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2536745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.284839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2380933761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1601753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4095058441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.03551197052</t>
+    <t xml:space="preserve">11.1574954986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2536754608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2848405838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.238091468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1601762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4095067977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0355110168457</t>
   </si>
   <si>
     <t xml:space="preserve">10.175760269165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8146677017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1263275146484</t>
+    <t xml:space="preserve">10.8146667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1263284683228</t>
   </si>
   <si>
     <t xml:space="preserve">11.0484132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1419115066528</t>
+    <t xml:space="preserve">11.1419105529785</t>
   </si>
   <si>
     <t xml:space="preserve">11.032829284668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7367506027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5965023040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6120872497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7211675643921</t>
+    <t xml:space="preserve">10.7367525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5965042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6120862960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7211666107178</t>
   </si>
   <si>
     <t xml:space="preserve">10.9081649780273</t>
@@ -1817,25 +1817,25 @@
     <t xml:space="preserve">10.783501625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8769979476929</t>
+    <t xml:space="preserve">10.8769989013672</t>
   </si>
   <si>
     <t xml:space="preserve">10.9704971313477</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5470714569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8587331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9054841995239</t>
+    <t xml:space="preserve">11.5470705032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8587341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9054832458496</t>
   </si>
   <si>
     <t xml:space="preserve">11.6561546325684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275661468506</t>
+    <t xml:space="preserve">11.8275680541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.7340698242188</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">11.8743171691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9210653305054</t>
+    <t xml:space="preserve">11.9210662841797</t>
   </si>
   <si>
     <t xml:space="preserve">12.0768976211548</t>
@@ -1859,10 +1859,10 @@
     <t xml:space="preserve">11.7652349472046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8898992538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8119850158691</t>
+    <t xml:space="preserve">11.8899011611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8119831085205</t>
   </si>
   <si>
     <t xml:space="preserve">11.1107454299927</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">11.3444919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.780818939209</t>
+    <t xml:space="preserve">11.7808170318604</t>
   </si>
   <si>
     <t xml:space="preserve">12.0301475524902</t>
@@ -1886,40 +1886,40 @@
     <t xml:space="preserve">11.7964010238647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6249885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4691562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5626554489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4379901885986</t>
+    <t xml:space="preserve">11.6249866485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4691553115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5626544952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4379911422729</t>
   </si>
   <si>
     <t xml:space="preserve">11.5314884185791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3756589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4535722732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4224061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2977428436279</t>
+    <t xml:space="preserve">11.375657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4535732269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4224071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2977418899536</t>
   </si>
   <si>
     <t xml:space="preserve">11.2821588516235</t>
   </si>
   <si>
-    <t xml:space="preserve">10.705584526062</t>
+    <t xml:space="preserve">10.7055835723877</t>
   </si>
   <si>
     <t xml:space="preserve">10.8925819396973</t>
@@ -1928,28 +1928,28 @@
     <t xml:space="preserve">10.6588363647461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3315906524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3471736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0199279785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97318077087402</t>
+    <t xml:space="preserve">10.3315916061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3471746444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0199289321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97317981719971</t>
   </si>
   <si>
     <t xml:space="preserve">10.0978441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94201469421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80176448822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92642974853516</t>
+    <t xml:space="preserve">9.94201374053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80176544189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92643070220947</t>
   </si>
   <si>
     <t xml:space="preserve">8.97586250305176</t>
@@ -1961,52 +1961,52 @@
     <t xml:space="preserve">9.13169288635254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02260971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8044490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47720241546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38370323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25904083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2434549331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14995765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48767566680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11368179321289</t>
+    <t xml:space="preserve">9.02261161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80444717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47720336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38370418548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25903987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24345684051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14995861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48767614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11368227005005</t>
   </si>
   <si>
     <t xml:space="preserve">7.0357666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15532159805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42023468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16311359405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85924243927002</t>
+    <t xml:space="preserve">6.15532207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42023372650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16311311721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85924291610718</t>
   </si>
   <si>
     <t xml:space="preserve">5.25929403305054</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29046010971069</t>
+    <t xml:space="preserve">5.29046058654785</t>
   </si>
   <si>
     <t xml:space="preserve">5.53199815750122</t>
@@ -2021,31 +2021,31 @@
     <t xml:space="preserve">5.37616777420044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08008766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36058378219604</t>
+    <t xml:space="preserve">5.08008813858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36058330535889</t>
   </si>
   <si>
     <t xml:space="preserve">5.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35279226303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29825115203857</t>
+    <t xml:space="preserve">5.35279178619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29825210571289</t>
   </si>
   <si>
     <t xml:space="preserve">5.45408248901367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47745752334595</t>
+    <t xml:space="preserve">5.47745704650879</t>
   </si>
   <si>
     <t xml:space="preserve">5.76574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5086236000061</t>
+    <t xml:space="preserve">5.50862407684326</t>
   </si>
   <si>
     <t xml:space="preserve">5.92157554626465</t>
@@ -2057,52 +2057,52 @@
     <t xml:space="preserve">5.80470180511475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83586740493774</t>
+    <t xml:space="preserve">5.83586835861206</t>
   </si>
   <si>
     <t xml:space="preserve">5.89820051193237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27219486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25661087036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33452701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4280252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17090511322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45919227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23323726654053</t>
+    <t xml:space="preserve">6.27219533920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25661182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33452749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42802572250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17090463638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45919132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23323774337769</t>
   </si>
   <si>
     <t xml:space="preserve">6.24882125854492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12415599822998</t>
+    <t xml:space="preserve">6.12415552139282</t>
   </si>
   <si>
     <t xml:space="preserve">5.75016164779663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71899509429932</t>
+    <t xml:space="preserve">5.71899557113647</t>
   </si>
   <si>
     <t xml:space="preserve">5.86703491210938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94494962692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92936658859253</t>
+    <t xml:space="preserve">5.94495058059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92936706542969</t>
   </si>
   <si>
     <t xml:space="preserve">6.03844881057739</t>
@@ -2111,109 +2111,109 @@
     <t xml:space="preserve">6.22544574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35790205001831</t>
+    <t xml:space="preserve">6.35790157318115</t>
   </si>
   <si>
     <t xml:space="preserve">6.58385705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50594139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49035835266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47477579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6228141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08251619338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27730369567871</t>
+    <t xml:space="preserve">6.50594091415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49035787582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47477531433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62281465530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08251523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27730464935303</t>
   </si>
   <si>
     <t xml:space="preserve">7.09030771255493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05914163589478</t>
+    <t xml:space="preserve">7.05914115905762</t>
   </si>
   <si>
     <t xml:space="preserve">6.8955192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52152490615845</t>
+    <t xml:space="preserve">6.52152442932129</t>
   </si>
   <si>
     <t xml:space="preserve">6.60723114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76306200027466</t>
+    <t xml:space="preserve">6.76306343078613</t>
   </si>
   <si>
     <t xml:space="preserve">6.55269050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56827449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68514728546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75527143478394</t>
+    <t xml:space="preserve">6.56827402114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68514680862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75527048110962</t>
   </si>
   <si>
     <t xml:space="preserve">6.84097671508789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65398025512695</t>
+    <t xml:space="preserve">6.65398073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.01239204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98122501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8565616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78643751144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71631336212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7318959236145</t>
+    <t xml:space="preserve">6.98122549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85656070709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78643655776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71631240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73189687728882</t>
   </si>
   <si>
     <t xml:space="preserve">6.8643536567688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66177225112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72410488128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38906860351562</t>
+    <t xml:space="preserve">6.66177368164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72410440444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38906812667847</t>
   </si>
   <si>
     <t xml:space="preserve">6.24102878570557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20207071304321</t>
+    <t xml:space="preserve">6.20207166671753</t>
   </si>
   <si>
     <t xml:space="preserve">6.45140075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43581771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49814939498901</t>
+    <t xml:space="preserve">6.4358172416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49814987182617</t>
   </si>
   <si>
     <t xml:space="preserve">6.2877779006958</t>
@@ -2225,31 +2225,31 @@
     <t xml:space="preserve">6.32673597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13194704055786</t>
+    <t xml:space="preserve">6.13194751739502</t>
   </si>
   <si>
     <t xml:space="preserve">6.01507377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09298896789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07740592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00728225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95274209976196</t>
+    <t xml:space="preserve">6.09298944473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07740640640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00728178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9527416229248</t>
   </si>
   <si>
     <t xml:space="preserve">5.93715858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7267861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8436598777771</t>
+    <t xml:space="preserve">5.72678661346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84366035461426</t>
   </si>
   <si>
     <t xml:space="preserve">5.69562005996704</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">5.64107942581177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56316375732422</t>
+    <t xml:space="preserve">5.56316423416138</t>
   </si>
   <si>
     <t xml:space="preserve">5.5475811958313</t>
@@ -2273,37 +2273,37 @@
     <t xml:space="preserve">5.52420663833618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74236965179443</t>
+    <t xml:space="preserve">5.74237012863159</t>
   </si>
   <si>
     <t xml:space="preserve">5.75795269012451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73457813262939</t>
+    <t xml:space="preserve">5.73457765579224</t>
   </si>
   <si>
     <t xml:space="preserve">5.79691076278687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90599250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96053266525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68003749847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8514518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78132772445679</t>
+    <t xml:space="preserve">5.90599155426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96053314208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68003797531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85145139694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78132724761963</t>
   </si>
   <si>
     <t xml:space="preserve">6.04624032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91378307342529</t>
+    <t xml:space="preserve">5.91378402709961</t>
   </si>
   <si>
     <t xml:space="preserve">5.67224597930908</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">5.46187448501587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15800333023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99438095092773</t>
+    <t xml:space="preserve">5.15800380706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99438142776489</t>
   </si>
   <si>
     <t xml:space="preserve">4.79180097579956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7606348991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8073844909668</t>
+    <t xml:space="preserve">4.76063537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80738401412964</t>
   </si>
   <si>
     <t xml:space="preserve">4.8307580947876</t>
@@ -2336,19 +2336,19 @@
     <t xml:space="preserve">5.02554702758789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18137836456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06182289123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02286577224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10078096389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99680805206299</t>
+    <t xml:space="preserve">5.18137884140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06182336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02286529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10078048706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9968090057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.23055553436279</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">7.05134963989258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93447589874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92668533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82539558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77864503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87214279174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91110134124756</t>
+    <t xml:space="preserve">6.93447637557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92668390274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82539463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77864599227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87214374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9111008644104</t>
   </si>
   <si>
     <t xml:space="preserve">6.77085304260254</t>
@@ -2381,22 +2381,22 @@
     <t xml:space="preserve">6.66956377029419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63060569763184</t>
+    <t xml:space="preserve">6.63060617446899</t>
   </si>
   <si>
     <t xml:space="preserve">6.97343444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63839769363403</t>
+    <t xml:space="preserve">6.63839817047119</t>
   </si>
   <si>
     <t xml:space="preserve">6.70072984695435</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80981159210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98901748657227</t>
+    <t xml:space="preserve">6.80981111526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98901700973511</t>
   </si>
   <si>
     <t xml:space="preserve">7.14484834671021</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">6.95785140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87993478775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0046010017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16043138504028</t>
+    <t xml:space="preserve">6.8799352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00460004806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16043043136597</t>
   </si>
   <si>
     <t xml:space="preserve">7.1760139465332</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">7.37859487533569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38638496398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13705635070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09809923171997</t>
+    <t xml:space="preserve">7.38638591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13705682754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09809827804565</t>
   </si>
   <si>
     <t xml:space="preserve">6.53710794448853</t>
@@ -2435,43 +2435,43 @@
     <t xml:space="preserve">6.59164810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57606554031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79422903060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07472324371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22276401519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28509569168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25392961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45650959014893</t>
+    <t xml:space="preserve">6.5760645866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79422807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07472372055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2227635383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28509521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25393104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45650863647461</t>
   </si>
   <si>
     <t xml:space="preserve">7.65909004211426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61234092712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53442573547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49546766281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57338285446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.472092628479</t>
+    <t xml:space="preserve">7.61234140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53442621231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49546813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57338380813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47209358215332</t>
   </si>
   <si>
     <t xml:space="preserve">7.50325965881348</t>
@@ -2480,145 +2480,145 @@
     <t xml:space="preserve">7.40196943283081</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26172208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3006796836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12926530838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2461371421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51884174346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91621160507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79154586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80712938308716</t>
+    <t xml:space="preserve">7.26172065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30067825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12926483154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24613761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51884269714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91621208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79154539108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80712890625</t>
   </si>
   <si>
     <t xml:space="preserve">7.71363019943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.775963306427</t>
+    <t xml:space="preserve">7.77596235275269</t>
   </si>
   <si>
     <t xml:space="preserve">7.54221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23834609985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3708028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43313646316528</t>
+    <t xml:space="preserve">7.23834800720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37080240249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43313503265381</t>
   </si>
   <si>
     <t xml:space="preserve">8.02529335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86946153640747</t>
+    <t xml:space="preserve">7.90062952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86946249008179</t>
   </si>
   <si>
     <t xml:space="preserve">7.72142219543457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46430206298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73700714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7837553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65129852294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58896636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68246412277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72921371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62013292312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39417695999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40976095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59675693511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74479675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21228790283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29020595550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10320854187012</t>
+    <t xml:space="preserve">7.46430110931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73700618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78375577926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65129947662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58896684646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68246364593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72921562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62013244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39417743682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40976142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59675741195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74479627609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21228981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29020500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10320949554443</t>
   </si>
   <si>
     <t xml:space="preserve">8.08762454986572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18221664428711</t>
+    <t xml:space="preserve">8.18221759796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.02456378936768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96150207519531</t>
+    <t xml:space="preserve">7.96150302886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.15068626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54481983184814</t>
+    <t xml:space="preserve">8.54482078552246</t>
   </si>
   <si>
     <t xml:space="preserve">8.68670845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95471858978271</t>
+    <t xml:space="preserve">8.95471954345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.00201606750488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06507587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12813758850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20696544647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14390468597412</t>
+    <t xml:space="preserve">9.06507682800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12813854217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20696640014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15966892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14390563964844</t>
   </si>
   <si>
     <t xml:space="preserve">8.93895530700684</t>
@@ -2627,10 +2627,10 @@
     <t xml:space="preserve">8.97048568725586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98625087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8285961151123</t>
+    <t xml:space="preserve">8.98624992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82859706878662</t>
   </si>
   <si>
     <t xml:space="preserve">8.78130054473877</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">8.63941287994385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5132884979248</t>
+    <t xml:space="preserve">8.51328945159912</t>
   </si>
   <si>
     <t xml:space="preserve">8.65517711639404</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">8.73400497436523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45022869110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37139987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46599388122559</t>
+    <t xml:space="preserve">8.45022773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3714017868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46599292755127</t>
   </si>
   <si>
     <t xml:space="preserve">8.57635116577148</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">8.05609512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89844083786011</t>
+    <t xml:space="preserve">7.89844036102295</t>
   </si>
   <si>
     <t xml:space="preserve">7.94573736190796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99303293228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40293121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48175811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32410621643066</t>
+    <t xml:space="preserve">7.99303388595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40293312072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4817590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32410526275635</t>
   </si>
   <si>
     <t xml:space="preserve">8.43446254730225</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">8.71823883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7970666885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33986949920654</t>
+    <t xml:space="preserve">8.79706573486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33987140655518</t>
   </si>
   <si>
     <t xml:space="preserve">8.38716697692871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29257583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2610445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19798278808594</t>
+    <t xml:space="preserve">8.29257488250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26104354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19798374176025</t>
   </si>
   <si>
     <t xml:space="preserve">8.592116355896</t>
@@ -2738,55 +2738,55 @@
     <t xml:space="preserve">8.60788154602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00879859924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92997169494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91420555114746</t>
+    <t xml:space="preserve">8.00879669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92997217178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84326124191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91420650482178</t>
   </si>
   <si>
     <t xml:space="preserve">7.8038477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64619588851929</t>
+    <t xml:space="preserve">7.64619541168213</t>
   </si>
   <si>
     <t xml:space="preserve">7.66196012496948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85902690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61466503143311</t>
+    <t xml:space="preserve">7.85902881622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61466455459595</t>
   </si>
   <si>
     <t xml:space="preserve">7.60678148269653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70137405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78808355331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65407705307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56736850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62254762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67772626876831</t>
+    <t xml:space="preserve">7.70137453079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78808498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65407752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79596614837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56736898422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62254810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67772579193115</t>
   </si>
   <si>
     <t xml:space="preserve">7.50430822372437</t>
@@ -2795,61 +2795,61 @@
     <t xml:space="preserve">7.63831186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74867010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7644362449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82749843597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67094326019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62364673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74976921081543</t>
+    <t xml:space="preserve">7.74866962432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76443529129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82749700546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67094421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6236457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74977016448975</t>
   </si>
   <si>
     <t xml:space="preserve">7.55948543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54372024536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25206136703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28359317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27570962905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8579273223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9131064414978</t>
+    <t xml:space="preserve">7.54371976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25206184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28359222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27570867538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85792779922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91310739517212</t>
   </si>
   <si>
     <t xml:space="preserve">6.82639741897583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08652591705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99981641769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93675518035889</t>
+    <t xml:space="preserve">7.08652544021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99981594085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93675374984741</t>
   </si>
   <si>
     <t xml:space="preserve">7.37030124664307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2362961769104</t>
+    <t xml:space="preserve">7.23629760742188</t>
   </si>
   <si>
     <t xml:space="preserve">7.21264839172363</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">7.12593841552734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0313458442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14958715438843</t>
+    <t xml:space="preserve">7.03134679794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14958810806274</t>
   </si>
   <si>
     <t xml:space="preserve">7.09440803527832</t>
@@ -2870,22 +2870,22 @@
     <t xml:space="preserve">7.13382148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33877086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38606786727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47277545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86690998077393</t>
+    <t xml:space="preserve">7.3387713432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38606739044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47277593612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86690950393677</t>
   </si>
   <si>
     <t xml:space="preserve">7.78020048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74078750610352</t>
+    <t xml:space="preserve">7.74078702926636</t>
   </si>
   <si>
     <t xml:space="preserve">7.46489429473877</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">7.68560791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58313369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48854207992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45701122283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37818479537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35453701019287</t>
+    <t xml:space="preserve">7.58313417434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48854112625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4570107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37818431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35453605651855</t>
   </si>
   <si>
     <t xml:space="preserve">7.11805629730225</t>
@@ -2918,43 +2918,43 @@
     <t xml:space="preserve">6.99193286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34665441513062</t>
+    <t xml:space="preserve">7.34665298461914</t>
   </si>
   <si>
     <t xml:space="preserve">7.1732349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29147434234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36241817474365</t>
+    <t xml:space="preserve">7.29147529602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36241865158081</t>
   </si>
   <si>
     <t xml:space="preserve">7.19688272476196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10229110717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44124507904053</t>
+    <t xml:space="preserve">7.10229063034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44124603271484</t>
   </si>
   <si>
     <t xml:space="preserve">7.33088731765747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4097146987915</t>
+    <t xml:space="preserve">7.40971565246582</t>
   </si>
   <si>
     <t xml:space="preserve">7.49642467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39394950866699</t>
+    <t xml:space="preserve">7.39394998550415</t>
   </si>
   <si>
     <t xml:space="preserve">7.26782751083374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15746831893921</t>
+    <t xml:space="preserve">7.15746879577637</t>
   </si>
   <si>
     <t xml:space="preserve">6.61356544494629</t>
@@ -2963,10 +2963,10 @@
     <t xml:space="preserve">6.44014596939087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60568237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.810631275177</t>
+    <t xml:space="preserve">6.60568189620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81063222885132</t>
   </si>
   <si>
     <t xml:space="preserve">6.98405027389526</t>
@@ -2975,70 +2975,70 @@
     <t xml:space="preserve">7.18111801147461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18899917602539</t>
+    <t xml:space="preserve">7.18899965286255</t>
   </si>
   <si>
     <t xml:space="preserve">7.06287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11017322540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88267517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81173133850098</t>
+    <t xml:space="preserve">7.11017370223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476579666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8826756477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81173038482666</t>
   </si>
   <si>
     <t xml:space="preserve">7.69349145889282</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75655269622803</t>
+    <t xml:space="preserve">7.75655317306519</t>
   </si>
   <si>
     <t xml:space="preserve">7.7329044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42547988891602</t>
+    <t xml:space="preserve">7.42548036575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.48065853118896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51218891143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52007341384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22841358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40183210372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00769901275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44912910461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4154257774353</t>
+    <t xml:space="preserve">7.51218938827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52007246017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22841310501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40183258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00769758224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44912815093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41542625427246</t>
   </si>
   <si>
     <t xml:space="preserve">7.31838655471802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29412698745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4801173210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098508834839</t>
+    <t xml:space="preserve">7.29412746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48011827468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098461151123</t>
   </si>
   <si>
     <t xml:space="preserve">7.63376331329346</t>
@@ -3047,16 +3047,16 @@
     <t xml:space="preserve">7.54481172561646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43968486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48820543289185</t>
+    <t xml:space="preserve">7.43968534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48820495605469</t>
   </si>
   <si>
     <t xml:space="preserve">7.46394538879395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32647323608398</t>
+    <t xml:space="preserve">7.32647275924683</t>
   </si>
   <si>
     <t xml:space="preserve">7.05152797698975</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">6.83318901062012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94640207290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76040935516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75232315063477</t>
+    <t xml:space="preserve">6.94640159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76040983200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75232362747192</t>
   </si>
   <si>
     <t xml:space="preserve">6.71188974380493</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">6.86553573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73614978790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74423694610596</t>
+    <t xml:space="preserve">6.73614931106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7442364692688</t>
   </si>
   <si>
     <t xml:space="preserve">6.81701612472534</t>
@@ -3092,31 +3092,31 @@
     <t xml:space="preserve">6.87362241744995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80084276199341</t>
+    <t xml:space="preserve">6.80084323883057</t>
   </si>
   <si>
     <t xml:space="preserve">6.71997737884521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63102436065674</t>
+    <t xml:space="preserve">6.63102388381958</t>
   </si>
   <si>
     <t xml:space="preserve">6.70380353927612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46929121017456</t>
+    <t xml:space="preserve">6.46929168701172</t>
   </si>
   <si>
     <t xml:space="preserve">6.48546504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57441806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.695716381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64719772338867</t>
+    <t xml:space="preserve">6.57441759109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69571685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64719724655151</t>
   </si>
   <si>
     <t xml:space="preserve">6.63911008834839</t>
@@ -3125,19 +3125,19 @@
     <t xml:space="preserve">6.55015802383423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60676383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62293720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47737789154053</t>
+    <t xml:space="preserve">6.60676431655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62293672561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47737836837769</t>
   </si>
   <si>
     <t xml:space="preserve">6.40459823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41268539428711</t>
+    <t xml:space="preserve">6.41268587112427</t>
   </si>
   <si>
     <t xml:space="preserve">6.65528392791748</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">6.72806358337402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67145681381226</t>
+    <t xml:space="preserve">6.6714563369751</t>
   </si>
   <si>
     <t xml:space="preserve">6.76849603652954</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">6.50163793563843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46120548248291</t>
+    <t xml:space="preserve">6.46120500564575</t>
   </si>
   <si>
     <t xml:space="preserve">6.4935507774353</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">6.44503164291382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38842535018921</t>
+    <t xml:space="preserve">6.38842582702637</t>
   </si>
   <si>
     <t xml:space="preserve">6.29138660430908</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">6.08922100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13774013519287</t>
+    <t xml:space="preserve">6.13774061203003</t>
   </si>
   <si>
     <t xml:space="preserve">5.95174884796143</t>
@@ -3194,25 +3194,25 @@
     <t xml:space="preserve">5.98409509658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90322923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06496095657349</t>
+    <t xml:space="preserve">5.90322875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06496047973633</t>
   </si>
   <si>
     <t xml:space="preserve">6.18626022338867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02452707290649</t>
+    <t xml:space="preserve">6.02452754974365</t>
   </si>
   <si>
     <t xml:space="preserve">5.91131544113159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86279535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88705539703369</t>
+    <t xml:space="preserve">5.86279582977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88705587387085</t>
   </si>
   <si>
     <t xml:space="preserve">5.79001617431641</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">5.83044910430908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81427526473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6363697052002</t>
+    <t xml:space="preserve">5.81427574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63637018203735</t>
   </si>
   <si>
     <t xml:space="preserve">5.7091498374939</t>
@@ -3236,37 +3236,37 @@
     <t xml:space="preserve">5.73340940475464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67680358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78192949295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74149608612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62828397750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45846509933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39377212524414</t>
+    <t xml:space="preserve">5.67680311203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78192901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74149656295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62828350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45846462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39377164840698</t>
   </si>
   <si>
     <t xml:space="preserve">5.33716535568237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38568544387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36142492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42611837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43420457839966</t>
+    <t xml:space="preserve">5.38568496704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36142539978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42611885070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43420505523682</t>
   </si>
   <si>
     <t xml:space="preserve">5.28056001663208</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">5.26438570022583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3452525138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40994548797607</t>
+    <t xml:space="preserve">5.34525203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40994501113892</t>
   </si>
   <si>
     <t xml:space="preserve">5.35333871841431</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">5.57976388931274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82236242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68489074707031</t>
+    <t xml:space="preserve">5.82236194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68489027023315</t>
   </si>
   <si>
     <t xml:space="preserve">5.79810285568237</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">5.93557500839233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7576699256897</t>
+    <t xml:space="preserve">5.75766944885254</t>
   </si>
   <si>
     <t xml:space="preserve">5.66063022613525</t>
@@ -3314,40 +3314,40 @@
     <t xml:space="preserve">5.65254306793213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48272466659546</t>
+    <t xml:space="preserve">5.4827241897583</t>
   </si>
   <si>
     <t xml:space="preserve">5.51507139205933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5312442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50698471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.644455909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52315759658813</t>
+    <t xml:space="preserve">5.53124380111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5069842338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64445638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52315807342529</t>
   </si>
   <si>
     <t xml:space="preserve">5.70106363296509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57167768478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46655225753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60402393341064</t>
+    <t xml:space="preserve">5.57167720794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46655178070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60402345657349</t>
   </si>
   <si>
     <t xml:space="preserve">5.49081134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56359148025513</t>
+    <t xml:space="preserve">5.56359100341797</t>
   </si>
   <si>
     <t xml:space="preserve">5.41803169250488</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">5.96792125701904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.145827293396</t>
+    <t xml:space="preserve">6.14582681655884</t>
   </si>
   <si>
     <t xml:space="preserve">6.17817354202271</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">6.21860647201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03261375427246</t>
+    <t xml:space="preserve">6.03261423110962</t>
   </si>
   <si>
     <t xml:space="preserve">5.97600793838501</t>
@@ -3386,19 +3386,19 @@
     <t xml:space="preserve">6.01644086837769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9436616897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80618906021118</t>
+    <t xml:space="preserve">5.94366121292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80618953704834</t>
   </si>
   <si>
     <t xml:space="preserve">5.87896871566772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85470914840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1215672492981</t>
+    <t xml:space="preserve">5.85470867156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12156677246094</t>
   </si>
   <si>
     <t xml:space="preserve">6.0973072052002</t>
@@ -3407,19 +3407,19 @@
     <t xml:space="preserve">6.16200017929077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07304811477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08113384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05687427520752</t>
+    <t xml:space="preserve">6.07304763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08113431930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05687379837036</t>
   </si>
   <si>
     <t xml:space="preserve">6.04070091247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.105393409729</t>
+    <t xml:space="preserve">6.10539388656616</t>
   </si>
   <si>
     <t xml:space="preserve">6.04878807067871</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">5.59593677520752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58785009384155</t>
+    <t xml:space="preserve">5.58785057067871</t>
   </si>
   <si>
     <t xml:space="preserve">6.3075590133667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84662246704102</t>
+    <t xml:space="preserve">5.84662199020386</t>
   </si>
   <si>
     <t xml:space="preserve">5.83853530883789</t>
@@ -3449,25 +3449,25 @@
     <t xml:space="preserve">6.12965393066406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16357755661011</t>
+    <t xml:space="preserve">6.16357803344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.2046685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01565217971802</t>
+    <t xml:space="preserve">6.01565170288086</t>
   </si>
   <si>
     <t xml:space="preserve">6.29506731033325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49230194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47586584091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46764802932739</t>
+    <t xml:space="preserve">6.49230241775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47586631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46764755249023</t>
   </si>
   <si>
     <t xml:space="preserve">6.5005202293396</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">6.59913730621338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58270120620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51695680618286</t>
+    <t xml:space="preserve">6.58270168304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5169563293457</t>
   </si>
   <si>
     <t xml:space="preserve">6.45121145248413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42655754089355</t>
+    <t xml:space="preserve">6.4265570640564</t>
   </si>
   <si>
     <t xml:space="preserve">6.41012144088745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36903095245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33615827560425</t>
+    <t xml:space="preserve">6.36903142929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33615779876709</t>
   </si>
   <si>
     <t xml:space="preserve">6.52517461776733</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">6.45942974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54982852935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50873851776123</t>
+    <t xml:space="preserve">6.54982900619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50873804092407</t>
   </si>
   <si>
     <t xml:space="preserve">6.44299364089966</t>
@@ -3530,13 +3530,13 @@
     <t xml:space="preserve">6.11426973342896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1307053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13892364501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25397682189941</t>
+    <t xml:space="preserve">6.13070583343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13892316818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25397729873657</t>
   </si>
   <si>
     <t xml:space="preserve">6.2621955871582</t>
@@ -3545,13 +3545,13 @@
     <t xml:space="preserve">6.31972217559814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35259437561035</t>
+    <t xml:space="preserve">6.35259389877319</t>
   </si>
   <si>
     <t xml:space="preserve">6.30328607559204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21288633346558</t>
+    <t xml:space="preserve">6.21288681030273</t>
   </si>
   <si>
     <t xml:space="preserve">6.37724828720093</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">6.48408365249634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56626510620117</t>
+    <t xml:space="preserve">6.56626462936401</t>
   </si>
   <si>
     <t xml:space="preserve">6.64022827148438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65666437149048</t>
+    <t xml:space="preserve">6.65666484832764</t>
   </si>
   <si>
     <t xml:space="preserve">6.59091949462891</t>
@@ -3575,43 +3575,43 @@
     <t xml:space="preserve">6.55804681777954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80459022521973</t>
+    <t xml:space="preserve">6.80458974838257</t>
   </si>
   <si>
     <t xml:space="preserve">6.8867712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83746194839478</t>
+    <t xml:space="preserve">6.83746290206909</t>
   </si>
   <si>
     <t xml:space="preserve">6.69775438308716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61557340621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70597267150879</t>
+    <t xml:space="preserve">6.61557388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70597314834595</t>
   </si>
   <si>
     <t xml:space="preserve">6.63200950622559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62379264831543</t>
+    <t xml:space="preserve">6.62379217147827</t>
   </si>
   <si>
     <t xml:space="preserve">6.82924461364746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94429779052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87855243682861</t>
+    <t xml:space="preserve">6.9442982673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87855291366577</t>
   </si>
   <si>
     <t xml:space="preserve">6.77993535995483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7963719367981</t>
+    <t xml:space="preserve">6.79637241363525</t>
   </si>
   <si>
     <t xml:space="preserve">6.90320730209351</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">6.72240924835205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68131923675537</t>
+    <t xml:space="preserve">6.68131875991821</t>
   </si>
   <si>
     <t xml:space="preserve">6.68953704833984</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">6.27863168716431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0896143913269</t>
+    <t xml:space="preserve">6.08961486816406</t>
   </si>
   <si>
     <t xml:space="preserve">6.07317876815796</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04852437973022</t>
+    <t xml:space="preserve">6.04852485656738</t>
   </si>
   <si>
     <t xml:space="preserve">6.15535974502563</t>
@@ -3653,16 +3653,16 @@
     <t xml:space="preserve">5.94168949127197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05674314498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87594413757324</t>
+    <t xml:space="preserve">6.05674266815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8759446144104</t>
   </si>
   <si>
     <t xml:space="preserve">5.95812511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08139705657959</t>
+    <t xml:space="preserve">6.08139657974243</t>
   </si>
   <si>
     <t xml:space="preserve">6.03208875656128</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">5.90881633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78554487228394</t>
+    <t xml:space="preserve">5.78554534912109</t>
   </si>
   <si>
     <t xml:space="preserve">5.75267267227173</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">5.71158218383789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71980047225952</t>
+    <t xml:space="preserve">5.71979999542236</t>
   </si>
   <si>
     <t xml:space="preserve">5.82663583755493</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">6.147141456604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28684997558594</t>
+    <t xml:space="preserve">6.28684949874878</t>
   </si>
   <si>
     <t xml:space="preserve">6.40190267562866</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">6.76349925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66488170623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.738844871521</t>
+    <t xml:space="preserve">6.66488218307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73884439468384</t>
   </si>
   <si>
     <t xml:space="preserve">6.82102632522583</t>
@@ -3731,22 +3731,22 @@
     <t xml:space="preserve">6.99360704421997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06756973266602</t>
+    <t xml:space="preserve">7.06757020950317</t>
   </si>
   <si>
     <t xml:space="preserve">7.240149974823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13331460952759</t>
+    <t xml:space="preserve">7.13331413269043</t>
   </si>
   <si>
     <t xml:space="preserve">6.98538875579834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12509536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07578754425049</t>
+    <t xml:space="preserve">7.1250958442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07578706741333</t>
   </si>
   <si>
     <t xml:space="preserve">7.16618680953979</t>
@@ -3755,13 +3755,13 @@
     <t xml:space="preserve">7.14975070953369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19084119796753</t>
+    <t xml:space="preserve">7.19084072113037</t>
   </si>
   <si>
     <t xml:space="preserve">7.18262243270874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28123950958252</t>
+    <t xml:space="preserve">7.28123998641968</t>
   </si>
   <si>
     <t xml:space="preserve">7.21549510955811</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">7.09222412109375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19905948638916</t>
+    <t xml:space="preserve">7.19905996322632</t>
   </si>
   <si>
     <t xml:space="preserve">7.0511326789856</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">7.48669195175171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36342144012451</t>
+    <t xml:space="preserve">7.36342191696167</t>
   </si>
   <si>
     <t xml:space="preserve">7.35520267486572</t>
@@ -3797,31 +3797,31 @@
     <t xml:space="preserve">7.28945779800415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3716402053833</t>
+    <t xml:space="preserve">7.37164068222046</t>
   </si>
   <si>
     <t xml:space="preserve">7.57709264755249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73323583602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94690704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88937997817993</t>
+    <t xml:space="preserve">7.73323678970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94690752029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88937950134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.02086925506592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78496217727661</t>
+    <t xml:space="preserve">7.78496265411377</t>
   </si>
   <si>
     <t xml:space="preserve">7.62768888473511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63642644882202</t>
+    <t xml:space="preserve">7.63642692565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.52284145355225</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">7.43546915054321</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28693437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37430667877197</t>
+    <t xml:space="preserve">7.28693389892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37430715560913</t>
   </si>
   <si>
     <t xml:space="preserve">7.27819633483887</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">7.42673110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30440855026245</t>
+    <t xml:space="preserve">7.30440807342529</t>
   </si>
   <si>
     <t xml:space="preserve">7.40925598144531</t>
@@ -3857,10 +3857,10 @@
     <t xml:space="preserve">7.33062076568604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44420528411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45294284820557</t>
+    <t xml:space="preserve">7.44420576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45294237136841</t>
   </si>
   <si>
     <t xml:space="preserve">7.49662923812866</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">7.64516448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51410484313965</t>
+    <t xml:space="preserve">7.51410531997681</t>
   </si>
   <si>
     <t xml:space="preserve">7.41799354553223</t>
@@ -3881,22 +3881,22 @@
     <t xml:space="preserve">7.46168041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53157806396484</t>
+    <t xml:space="preserve">7.531578540802</t>
   </si>
   <si>
     <t xml:space="preserve">7.40051889419556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48789167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3917818069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47041797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34809541702271</t>
+    <t xml:space="preserve">7.48789215087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39178228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47041749954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34809589385986</t>
   </si>
   <si>
     <t xml:space="preserve">6.94617748260498</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">6.86754179000854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91996622085571</t>
+    <t xml:space="preserve">6.91996574401855</t>
   </si>
   <si>
     <t xml:space="preserve">6.95491552352905</t>
@@ -3923,16 +3923,16 @@
     <t xml:space="preserve">6.70153284072876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89375352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85006761550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.051025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16461086273193</t>
+    <t xml:space="preserve">6.89375400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85006713867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05102586746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16461038589478</t>
   </si>
   <si>
     <t xml:space="preserve">7.18208599090576</t>
@@ -3959,13 +3959,13 @@
     <t xml:space="preserve">7.68011331558228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75874948501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83738660812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69758892059326</t>
+    <t xml:space="preserve">7.75874900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83738708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6975884437561</t>
   </si>
   <si>
     <t xml:space="preserve">7.67137622833252</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">7.81117296218872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76748752593994</t>
+    <t xml:space="preserve">7.76748704910278</t>
   </si>
   <si>
     <t xml:space="preserve">7.70632553100586</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">7.92475938796997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89854621887207</t>
+    <t xml:space="preserve">7.89854574203491</t>
   </si>
   <si>
     <t xml:space="preserve">7.80114364624023</t>
@@ -4809,6 +4809,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.18000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10999965667725</t>
   </si>
 </sst>
 </file>
@@ -71785,7 +71788,7 @@
     </row>
     <row r="2564">
       <c r="A2564" s="1" t="n">
-        <v>46056.6911458333</v>
+        <v>46056.3333333333</v>
       </c>
       <c r="B2564" t="n">
         <v>241165</v>
@@ -71806,6 +71809,32 @@
         <v>1598</v>
       </c>
       <c r="H2564" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" s="1" t="n">
+        <v>46057.6911805556</v>
+      </c>
+      <c r="B2565" t="n">
+        <v>258983</v>
+      </c>
+      <c r="C2565" t="n">
+        <v>9.28999996185303</v>
+      </c>
+      <c r="D2565" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="E2565" t="n">
+        <v>9.27999973297119</v>
+      </c>
+      <c r="F2565" t="n">
+        <v>9.10999965667725</v>
+      </c>
+      <c r="G2565" t="s">
+        <v>1599</v>
+      </c>
+      <c r="H2565" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FILA.MI.xlsx
+++ b/data/FILA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="1601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="1603">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,94 +38,94 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79523420333862</t>
+    <t xml:space="preserve">7.79523468017578</t>
   </si>
   <si>
     <t xml:space="preserve">FILA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74423789978027</t>
+    <t xml:space="preserve">7.74423694610596</t>
   </si>
   <si>
     <t xml:space="preserve">7.72238159179688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72966575622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78794860839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7733793258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56939268112183</t>
+    <t xml:space="preserve">7.7296667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7879490852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77337980270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56939172744751</t>
   </si>
   <si>
     <t xml:space="preserve">7.54753541946411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61310243606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21241283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17598724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62038707733154</t>
+    <t xml:space="preserve">7.61310195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21241331100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17598676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6203875541687</t>
   </si>
   <si>
     <t xml:space="preserve">7.46739768981934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35811805725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30712175369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3872594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56210613250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4965386390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28526592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37269020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64952898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51839542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58396244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67867040634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86080312728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76609325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8972282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90451383590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95551109313965</t>
+    <t xml:space="preserve">7.35811853408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30712127685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725996017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56210708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49653816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2852668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37268877029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64952754974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51839399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58396339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67867088317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86080265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76609373092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89722776412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90451240539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95551061630249</t>
   </si>
   <si>
     <t xml:space="preserve">7.80980491638184</t>
@@ -137,34 +137,34 @@
     <t xml:space="preserve">8.00650787353516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94094181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8753719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01379299163818</t>
+    <t xml:space="preserve">7.94093990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87537097930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01379203796387</t>
   </si>
   <si>
     <t xml:space="preserve">7.94822454452515</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03564834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80251884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84623050689697</t>
+    <t xml:space="preserve">8.03564739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80251932144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84623098373413</t>
   </si>
   <si>
     <t xml:space="preserve">8.05750465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05021953582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02836418151855</t>
+    <t xml:space="preserve">8.05022048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02836322784424</t>
   </si>
   <si>
     <t xml:space="preserve">8.15949821472168</t>
@@ -173,196 +173,196 @@
     <t xml:space="preserve">8.38534164428711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45090961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43633937835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45819282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63304042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71317863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60389995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74231910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80788612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42176818847656</t>
+    <t xml:space="preserve">8.45090770721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43634033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45819473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6330394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71318054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60389804840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7423210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80788707733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42176723480225</t>
   </si>
   <si>
     <t xml:space="preserve">8.73503398895264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79331588745117</t>
+    <t xml:space="preserve">8.79331684112549</t>
   </si>
   <si>
     <t xml:space="preserve">8.6548957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70589351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81517219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95359039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7568883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20857715606689</t>
+    <t xml:space="preserve">8.70589160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81517314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95359134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75689029693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20857620239258</t>
   </si>
   <si>
     <t xml:space="preserve">9.26685905456543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25228881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39799213409424</t>
+    <t xml:space="preserve">9.25228977203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39799118041992</t>
   </si>
   <si>
     <t xml:space="preserve">9.48541641235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36156940460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32488441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07543754577637</t>
+    <t xml:space="preserve">9.3615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32488346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07543659210205</t>
   </si>
   <si>
     <t xml:space="preserve">9.09744834899902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17081451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29553699493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36890506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27352809906006</t>
+    <t xml:space="preserve">9.17081356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29553890228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36890411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27352714538574</t>
   </si>
   <si>
     <t xml:space="preserve">9.28820037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20749759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24418258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11212253570557</t>
+    <t xml:space="preserve">9.20749855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24418067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11211967468262</t>
   </si>
   <si>
     <t xml:space="preserve">9.02408027648926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87734794616699</t>
+    <t xml:space="preserve">8.87734889984131</t>
   </si>
   <si>
     <t xml:space="preserve">8.84066486358643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80398082733154</t>
+    <t xml:space="preserve">8.80398178100586</t>
   </si>
   <si>
     <t xml:space="preserve">8.73061561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95071411132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22950553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81865406036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8259916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91403102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31754684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95804977416992</t>
+    <t xml:space="preserve">8.95071601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22950744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81865501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82599067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91403007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31754779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95805072784424</t>
   </si>
   <si>
     <t xml:space="preserve">8.99473476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1928243637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13413047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34689617156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35423183441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36156845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22216987609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06076335906982</t>
+    <t xml:space="preserve">9.19282627105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13413143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34689331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3542308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36156558990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22217082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06076431274414</t>
   </si>
   <si>
     <t xml:space="preserve">9.37624073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33955860137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31020927429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28086376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26619243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97272300720215</t>
+    <t xml:space="preserve">9.33955574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31021213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28086280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26619148254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97272396087646</t>
   </si>
   <si>
     <t xml:space="preserve">9.16347885131836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17815017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39825057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3028736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25885486602783</t>
+    <t xml:space="preserve">9.17815113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3982515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30287456512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2588529586792</t>
   </si>
   <si>
     <t xml:space="preserve">9.33222103118896</t>
@@ -371,97 +371,97 @@
     <t xml:space="preserve">9.11945724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05342674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00207138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96538543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14146709442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01674270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39091491699219</t>
+    <t xml:space="preserve">9.05342769622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00207233428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96538734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14146900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01674365997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39091396331787</t>
   </si>
   <si>
     <t xml:space="preserve">9.15614223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38357830047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44960689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49362754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52297401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50830173492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79443073272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83844947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312271118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95583724975586</t>
+    <t xml:space="preserve">9.38357734680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44960594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49362659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52297210693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50829982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7944278717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8384485244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85312366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95583629608154</t>
   </si>
   <si>
     <t xml:space="preserve">10.0438756942749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1392526626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2566385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1979455947876</t>
+    <t xml:space="preserve">10.1392517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2566394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1979475021362</t>
   </si>
   <si>
     <t xml:space="preserve">10.2713117599487</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90447807312012</t>
+    <t xml:space="preserve">9.90447902679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.0145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75774669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65503311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64769554138184</t>
+    <t xml:space="preserve">9.75774765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65503406524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64769744873047</t>
   </si>
   <si>
     <t xml:space="preserve">9.80910301208496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64035797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53764724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45694255828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41292285919189</t>
+    <t xml:space="preserve">9.64035892486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53764629364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45694351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41292476654053</t>
   </si>
   <si>
     <t xml:space="preserve">9.61834907531738</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">9.44227027893066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51563739776611</t>
+    <t xml:space="preserve">9.5156364440918</t>
   </si>
   <si>
     <t xml:space="preserve">9.53031158447266</t>
@@ -482,130 +482,130 @@
     <t xml:space="preserve">9.47895336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63302230834961</t>
+    <t xml:space="preserve">9.63302326202393</t>
   </si>
   <si>
     <t xml:space="preserve">9.55965614318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47161674499512</t>
+    <t xml:space="preserve">9.4716157913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.73573589324951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0878953933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1245784759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0512132644653</t>
+    <t xml:space="preserve">10.0878963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1245794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0512113571167</t>
   </si>
   <si>
     <t xml:space="preserve">9.86779594421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83111381530762</t>
+    <t xml:space="preserve">9.8311128616333</t>
   </si>
   <si>
     <t xml:space="preserve">9.97050952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97784614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81643962860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69171714782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88980484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86045932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96317386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0585498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99251747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1612606048584</t>
+    <t xml:space="preserve">9.9778470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81643772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69171524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88980674743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86046028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96317195892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0585489273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99251937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.161262512207</t>
   </si>
   <si>
     <t xml:space="preserve">10.1465883255005</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94116306304932</t>
+    <t xml:space="preserve">9.941162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.82377624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72106075286865</t>
+    <t xml:space="preserve">9.72106266021729</t>
   </si>
   <si>
     <t xml:space="preserve">9.8751335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0365390777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0805587768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.00719165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89714241027832</t>
+    <t xml:space="preserve">10.0365400314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0805597305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0071926116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.897141456604</t>
   </si>
   <si>
     <t xml:space="preserve">9.69905281066895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.985182762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3300037384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7335214614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7115106582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6674900054932</t>
+    <t xml:space="preserve">9.98518371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.330005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7335205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7115116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6674909591675</t>
   </si>
   <si>
     <t xml:space="preserve">10.8582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8215599060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9316091537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8068866729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1883926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2177400588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3424634933472</t>
+    <t xml:space="preserve">10.8215608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9316110610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8068876266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1883907318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2177410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3424625396729</t>
   </si>
   <si>
     <t xml:space="preserve">11.1957302093506</t>
@@ -617,46 +617,46 @@
     <t xml:space="preserve">11.0636711120605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9242734909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0416603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1517114639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.225076675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2984428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7166318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7313041687012</t>
+    <t xml:space="preserve">10.9242744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0416612625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1517105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2250776290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2984409332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7166328430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7313051223755</t>
   </si>
   <si>
     <t xml:space="preserve">11.8340187072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8853759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9954242706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6997423171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0225553512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0592384338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2059717178345</t>
+    <t xml:space="preserve">11.8853740692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9954252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.699743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0225563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0592412948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2059736251831</t>
   </si>
   <si>
     <t xml:space="preserve">12.6924066543579</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">12.2815542221069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054754257202</t>
+    <t xml:space="preserve">12.1054763793945</t>
   </si>
   <si>
     <t xml:space="preserve">12.178840637207</t>
@@ -674,94 +674,94 @@
     <t xml:space="preserve">12.4796438217163</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3255758285522</t>
+    <t xml:space="preserve">12.3255748748779</t>
   </si>
   <si>
     <t xml:space="preserve">12.6850700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6630611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.655722618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619520187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8024549484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391370773315</t>
+    <t xml:space="preserve">12.6630601882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8024578094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391399383545</t>
   </si>
   <si>
     <t xml:space="preserve">13.1399440765381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.000545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491920471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0959243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0445652008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.719536781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7855682373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9396381378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.064359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828565597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7268743515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8222541809082</t>
+    <t xml:space="preserve">13.0005474090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491910934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0959234237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.04456615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7195377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7855701446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.82958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9396371841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0643606185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828536987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7268753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8222522735596</t>
   </si>
   <si>
     <t xml:space="preserve">13.7415475845337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9249668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6755199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4480829238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4037714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5364828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7945318222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8903799057007</t>
+    <t xml:space="preserve">13.9249658584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6755180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4480819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4627561569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4037733078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5364847183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945327758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.890380859375</t>
   </si>
   <si>
     <t xml:space="preserve">13.4922456741333</t>
@@ -773,55 +773,55 @@
     <t xml:space="preserve">13.6618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9641075134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9862241744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0452070236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7429237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7650375366211</t>
+    <t xml:space="preserve">13.9641036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9862251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0452079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7429218292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7650394439697</t>
   </si>
   <si>
     <t xml:space="preserve">13.7502946853638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6544494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4553823471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9346179962158</t>
+    <t xml:space="preserve">13.6544466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4553842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9346141815186</t>
   </si>
   <si>
     <t xml:space="preserve">13.9714775085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9272403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8830041885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0820722579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0083417892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8535165786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1973352432251</t>
+    <t xml:space="preserve">13.7134304046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9272413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8830051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0820713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0083446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8535146713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1973361968994</t>
   </si>
   <si>
     <t xml:space="preserve">13.5069932937622</t>
@@ -830,91 +830,91 @@
     <t xml:space="preserve">13.3079261779785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3300428390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.31529712677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6470746994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7871580123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8092765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.77978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8387699127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9493637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.118935585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8977518081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9198713302612</t>
+    <t xml:space="preserve">13.3300457000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3152980804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6470737457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7871589660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8092756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7797861099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8387689590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9493618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1189346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8977527618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9198703765869</t>
   </si>
   <si>
     <t xml:space="preserve">13.8240213394165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9419870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8313961029053</t>
+    <t xml:space="preserve">13.9419889450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.831395149231</t>
   </si>
   <si>
     <t xml:space="preserve">13.6765670776367</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4627552032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3816547393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1014881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5291109085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5659761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5586004257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2710618972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3890266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5807199478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6102123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4185171127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7060575485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7576694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6986846923828</t>
+    <t xml:space="preserve">13.4627542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3816566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.101487159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5291128158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.565975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5585994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2710638046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3890256881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5807189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6102094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4185180664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7576665878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6986837387085</t>
   </si>
   <si>
     <t xml:space="preserve">13.8166494369507</t>
@@ -923,160 +923,160 @@
     <t xml:space="preserve">13.728178024292</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7355461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7724161148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6397018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9051246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6249570846558</t>
+    <t xml:space="preserve">13.7355499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7724113464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.639702796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9051237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6249561309814</t>
   </si>
   <si>
     <t xml:space="preserve">13.602837562561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7456245422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.605544090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6129131317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.531813621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4728336334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5613050460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4359645843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2958831787109</t>
+    <t xml:space="preserve">14.7456254959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6055421829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6129150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5318145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4728307723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5613040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4359674453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2958812713623</t>
   </si>
   <si>
     <t xml:space="preserve">14.3032569885254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2590179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9124946594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6913146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1336803436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.030460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.956732749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1263084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1705446243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2147817611694</t>
+    <t xml:space="preserve">14.2590208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9124956130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6913137435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1336784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304594039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9567337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0378341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1263065338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1705455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2147827148438</t>
   </si>
   <si>
     <t xml:space="preserve">14.1557998657227</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0230884552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8461418151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8608884811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9788541793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.192663192749</t>
+    <t xml:space="preserve">14.0230894088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.104190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8461427688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8608865737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9788503646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1926622390747</t>
   </si>
   <si>
     <t xml:space="preserve">14.2295274734497</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5096950531006</t>
+    <t xml:space="preserve">14.5096969604492</t>
   </si>
   <si>
     <t xml:space="preserve">14.6497774124146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7013874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9299430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8562154769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.782488822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5834197998047</t>
+    <t xml:space="preserve">14.7013883590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930826187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9299468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8562183380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7824897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.583423614502</t>
   </si>
   <si>
     <t xml:space="preserve">14.3474931716919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.494948387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2617225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0773992538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1511278152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5566329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4091787338257</t>
+    <t xml:space="preserve">14.4949493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2617235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0774002075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1511306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5566320419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4091768264771</t>
   </si>
   <si>
     <t xml:space="preserve">14.9668092727661</t>
   </si>
   <si>
-    <t xml:space="preserve">15.33544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4460420608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0405387878418</t>
+    <t xml:space="preserve">15.3354539871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4460391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0405378341675</t>
   </si>
   <si>
     <t xml:space="preserve">15.1142644882202</t>
@@ -1088,46 +1088,46 @@
     <t xml:space="preserve">14.2885084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2737598419189</t>
+    <t xml:space="preserve">14.2737636566162</t>
   </si>
   <si>
     <t xml:space="preserve">14.1852903366089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5391864776611</t>
+    <t xml:space="preserve">14.5391874313354</t>
   </si>
   <si>
     <t xml:space="preserve">14.3917284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.421217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000389099121</t>
+    <t xml:space="preserve">14.4212217330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000370025635</t>
   </si>
   <si>
     <t xml:space="preserve">14.4064750671387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3447904586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5217380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6839380264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8756332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9908952713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.138352394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.976149559021</t>
+    <t xml:space="preserve">13.3447895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5217390060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6839399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8756313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9908971786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1383533477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9761505126953</t>
   </si>
   <si>
     <t xml:space="preserve">12.7549657821655</t>
@@ -1136,46 +1136,46 @@
     <t xml:space="preserve">12.6517477035522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8876752853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8729305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7254753112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0793695449829</t>
+    <t xml:space="preserve">12.887677192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8729295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.725474357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0793685913086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8286943435669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5927629470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5190362930298</t>
+    <t xml:space="preserve">12.5927639007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5190353393555</t>
   </si>
   <si>
     <t xml:space="preserve">12.4600534439087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5042905807495</t>
+    <t xml:space="preserve">12.5042896270752</t>
   </si>
   <si>
     <t xml:space="preserve">12.7402200698853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6812362670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0646238327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2858076095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1088590621948</t>
+    <t xml:space="preserve">12.6812372207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.064624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2858057022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1088600158691</t>
   </si>
   <si>
     <t xml:space="preserve">13.3005533218384</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">14.0968170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3742799758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3668727874756</t>
+    <t xml:space="preserve">13.3742818832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3668718338013</t>
   </si>
   <si>
     <t xml:space="preserve">13.3075971603394</t>
@@ -1202,136 +1202,136 @@
     <t xml:space="preserve">13.4854249954224</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9371175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2702560424805</t>
+    <t xml:space="preserve">12.9371166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2702541351318</t>
   </si>
   <si>
     <t xml:space="preserve">12.7592868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5962772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6851930618286</t>
+    <t xml:space="preserve">12.5962762832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.68519115448</t>
   </si>
   <si>
     <t xml:space="preserve">13.0408506393433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9667530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1445837020874</t>
+    <t xml:space="preserve">12.9667558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1445846557617</t>
   </si>
   <si>
     <t xml:space="preserve">12.8630199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8926601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.818564414978</t>
+    <t xml:space="preserve">12.8926591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8185634613037</t>
   </si>
   <si>
     <t xml:space="preserve">12.7444686889648</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9815740585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2483196258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2927770614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0853071212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4706048965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5298833847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4409656524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2779550552368</t>
+    <t xml:space="preserve">12.9815759658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2483167648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.292778968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0853099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4706077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.529881477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4409694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2779579162598</t>
   </si>
   <si>
     <t xml:space="preserve">13.3224143981934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3816890716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6039781570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.515064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.337233543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5743408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9300012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8855428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.826268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7669897079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6928930282593</t>
+    <t xml:space="preserve">13.3816919326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6039800643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5150632858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3372354507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5743417739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9299983978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8855419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8262643814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7669878005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.692892074585</t>
   </si>
   <si>
     <t xml:space="preserve">13.7521705627441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.855902671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.989278793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2038612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.781810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9003629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7225322723389</t>
+    <t xml:space="preserve">13.8559036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.989275932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2038621902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7818078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9003620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7225303649902</t>
   </si>
   <si>
     <t xml:space="preserve">13.9596405029297</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7077112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5447006225586</t>
+    <t xml:space="preserve">13.7077131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5447025299072</t>
   </si>
   <si>
     <t xml:space="preserve">13.5595197677612</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1149454116821</t>
+    <t xml:space="preserve">13.1149473190308</t>
   </si>
   <si>
     <t xml:space="preserve">13.4261484146118</t>
@@ -1340,16 +1340,16 @@
     <t xml:space="preserve">12.655553817749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8778390884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9222965240479</t>
+    <t xml:space="preserve">12.8778409957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9222984313965</t>
   </si>
   <si>
     <t xml:space="preserve">13.1001281738281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1297655105591</t>
+    <t xml:space="preserve">13.129768371582</t>
   </si>
   <si>
     <t xml:space="preserve">13.0112113952637</t>
@@ -1358,22 +1358,22 @@
     <t xml:space="preserve">12.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1517009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0479669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1220636367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3739891052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4777240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1368818283081</t>
+    <t xml:space="preserve">12.1517019271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1220645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3739900588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4777221679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1368827819824</t>
   </si>
   <si>
     <t xml:space="preserve">11.7071285247803</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">12.0331497192383</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7812232971191</t>
+    <t xml:space="preserve">11.7812252044678</t>
   </si>
   <si>
     <t xml:space="preserve">11.2477340698242</t>
@@ -1391,76 +1391,76 @@
     <t xml:space="preserve">11.4700212478638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4403820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5885744094849</t>
+    <t xml:space="preserve">11.4403829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5885734558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6478509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5589351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3811054229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.351469039917</t>
+    <t xml:space="preserve">11.5589361190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3811063766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3514671325684</t>
   </si>
   <si>
     <t xml:space="preserve">11.173638343811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1143617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0254459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6697864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0029258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4326801300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7883396148682</t>
+    <t xml:space="preserve">11.1143627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.025447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6697874069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0029249191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4326820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7883405685425</t>
   </si>
   <si>
     <t xml:space="preserve">10.4771385192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5512342453003</t>
+    <t xml:space="preserve">10.5512323379517</t>
   </si>
   <si>
     <t xml:space="preserve">10.8920736312866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9661693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0995416641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0770225524902</t>
+    <t xml:space="preserve">10.9661703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0995426177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0770215988159</t>
   </si>
   <si>
     <t xml:space="preserve">10.375111579895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8706378936768</t>
+    <t xml:space="preserve">10.8706388473511</t>
   </si>
   <si>
     <t xml:space="preserve">10.824182510376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4835071563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5609340667725</t>
+    <t xml:space="preserve">10.4835081100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5609350204468</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738033294678</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">11.3042268753052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7467565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6073894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5299644470215</t>
+    <t xml:space="preserve">10.7467575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6073884963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5299615859985</t>
   </si>
   <si>
     <t xml:space="preserve">10.7622423171997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7777280807495</t>
+    <t xml:space="preserve">10.7777271270752</t>
   </si>
   <si>
     <t xml:space="preserve">10.7312717437744</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">10.2357444763184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4525365829468</t>
+    <t xml:space="preserve">10.4525384902954</t>
   </si>
   <si>
     <t xml:space="preserve">10.406081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9945201873779</t>
+    <t xml:space="preserve">10.9945211410522</t>
   </si>
   <si>
     <t xml:space="preserve">11.0874319076538</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">11.0719470977783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9480657577515</t>
+    <t xml:space="preserve">10.9480638504028</t>
   </si>
   <si>
     <t xml:space="preserve">11.040976524353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3286561965942</t>
+    <t xml:space="preserve">10.3286542892456</t>
   </si>
   <si>
     <t xml:space="preserve">10.4370517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5919055938721</t>
+    <t xml:space="preserve">10.5919046401978</t>
   </si>
   <si>
     <t xml:space="preserve">10.4989929199219</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">10.3905963897705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3596267700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6693305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228742599487</t>
+    <t xml:space="preserve">10.3596258163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6693296432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228761672974</t>
   </si>
   <si>
     <t xml:space="preserve">10.8551530838013</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">11.3816509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3661661148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2422847747803</t>
+    <t xml:space="preserve">11.3661670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2422857284546</t>
   </si>
   <si>
     <t xml:space="preserve">11.1648578643799</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">10.9790353775024</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7932109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8861246109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5764198303223</t>
+    <t xml:space="preserve">10.793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8861236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5764188766479</t>
   </si>
   <si>
     <t xml:space="preserve">10.2047739028931</t>
@@ -1589,61 +1589,61 @@
     <t xml:space="preserve">9.6782751083374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56987762451172</t>
+    <t xml:space="preserve">9.56987857818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.75570201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95700931549072</t>
+    <t xml:space="preserve">9.95701026916504</t>
   </si>
   <si>
     <t xml:space="preserve">9.87958431243896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86409664154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94152545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92603874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1583166122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1428346633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91055488586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1273488998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3441400527954</t>
+    <t xml:space="preserve">9.86409950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94152355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92604064941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.158317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1428327560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91055393218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1273469924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3441410064697</t>
   </si>
   <si>
     <t xml:space="preserve">10.6383600234985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7157878875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6848154067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0344343185425</t>
+    <t xml:space="preserve">10.7157869338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6848163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0344352722168</t>
   </si>
   <si>
     <t xml:space="preserve">10.018949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97249507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2202568054199</t>
+    <t xml:space="preserve">9.97249412536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2202577590942</t>
   </si>
   <si>
     <t xml:space="preserve">9.81734943389893</t>
@@ -1652,37 +1652,37 @@
     <t xml:space="preserve">10.0666780471802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1445932388306</t>
+    <t xml:space="preserve">10.1445941925049</t>
   </si>
   <si>
     <t xml:space="preserve">10.3160066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4874210357666</t>
+    <t xml:space="preserve">10.4874229431152</t>
   </si>
   <si>
     <t xml:space="preserve">10.503005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.30042552948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91084766387939</t>
+    <t xml:space="preserve">10.3004245758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91084671020508</t>
   </si>
   <si>
     <t xml:space="preserve">10.0043458938599</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87968063354492</t>
+    <t xml:space="preserve">9.87968158721924</t>
   </si>
   <si>
     <t xml:space="preserve">9.895263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98876190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0510940551758</t>
+    <t xml:space="preserve">9.98876285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0510931015015</t>
   </si>
   <si>
     <t xml:space="preserve">10.0822620391846</t>
@@ -1697,31 +1697,31 @@
     <t xml:space="preserve">10.3939228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6744184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5341701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4250898361206</t>
+    <t xml:space="preserve">10.6744174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5341711044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4250888824463</t>
   </si>
   <si>
     <t xml:space="preserve">10.6276702880859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4406719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1290111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2225093841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1913423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2069253921509</t>
+    <t xml:space="preserve">10.4406728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1290102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.222508430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1913433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2069263458252</t>
   </si>
   <si>
     <t xml:space="preserve">10.4562549591064</t>
@@ -1733,19 +1733,19 @@
     <t xml:space="preserve">10.6432523727417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.830249786377</t>
+    <t xml:space="preserve">10.8302488327026</t>
   </si>
   <si>
     <t xml:space="preserve">10.7523345947266</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0795812606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9549140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6900024414062</t>
+    <t xml:space="preserve">11.0795783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9549150466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6900033950806</t>
   </si>
   <si>
     <t xml:space="preserve">10.7679176330566</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">11.2198266983032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2509937286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0639944076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1574945449829</t>
+    <t xml:space="preserve">11.2509927749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0639953613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1574935913086</t>
   </si>
   <si>
     <t xml:space="preserve">10.2536745071411</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">10.2848415374756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2380924224854</t>
+    <t xml:space="preserve">10.2380933761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.1601762771606</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">10.03551197052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1757612228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8146667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1263275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.048412322998</t>
+    <t xml:space="preserve">10.175760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8146657943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1263284683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0484132766724</t>
   </si>
   <si>
     <t xml:space="preserve">11.1419115066528</t>
@@ -1799,46 +1799,46 @@
     <t xml:space="preserve">11.0328302383423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7367506027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5965032577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6120872497559</t>
+    <t xml:space="preserve">10.7367496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5965042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6120862960815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7211675643921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.908164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9237489700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7835006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8769998550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.970498085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5470714569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8587331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9054841995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6561527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8275690078735</t>
+    <t xml:space="preserve">10.9081649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9237480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7834997177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8769979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9704971313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5470724105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8587341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9054832458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.656153678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8275680541992</t>
   </si>
   <si>
     <t xml:space="preserve">11.7340698242188</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">11.9989805221558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8743162155151</t>
+    <t xml:space="preserve">11.8743171691895</t>
   </si>
   <si>
     <t xml:space="preserve">11.9210653305054</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">11.7652349472046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8899002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8119850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.110746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9860811233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3444919586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7808198928833</t>
+    <t xml:space="preserve">11.8898992538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8119840621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1107473373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9860801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3444910049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7808170318604</t>
   </si>
   <si>
     <t xml:space="preserve">12.0301475524902</t>
@@ -1886,52 +1886,52 @@
     <t xml:space="preserve">11.9366493225098</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7964010238647</t>
+    <t xml:space="preserve">11.7964019775391</t>
   </si>
   <si>
     <t xml:space="preserve">11.6249876022339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4691553115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5626564025879</t>
+    <t xml:space="preserve">11.4691572189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5626544952393</t>
   </si>
   <si>
     <t xml:space="preserve">11.4379901885986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5314884185791</t>
+    <t xml:space="preserve">11.5314893722534</t>
   </si>
   <si>
     <t xml:space="preserve">11.3756580352783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.453574180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4224061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2977418899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2821588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.705584526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8925809860229</t>
+    <t xml:space="preserve">11.4535732269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4224071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2977409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2821598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7055854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8925819396973</t>
   </si>
   <si>
     <t xml:space="preserve">10.6588354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3315906524658</t>
+    <t xml:space="preserve">10.3315916061401</t>
   </si>
   <si>
     <t xml:space="preserve">10.3471746444702</t>
@@ -1940,22 +1940,22 @@
     <t xml:space="preserve">10.0199289321899</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97317886352539</t>
+    <t xml:space="preserve">9.97318077087402</t>
   </si>
   <si>
     <t xml:space="preserve">10.0978441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94201278686523</t>
+    <t xml:space="preserve">9.94201374053955</t>
   </si>
   <si>
     <t xml:space="preserve">9.80176544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92642974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97586154937744</t>
+    <t xml:space="preserve">9.92643070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97586250305176</t>
   </si>
 